--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -62863,6 +62863,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2718">
+      <c r="A2718" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2718" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2718" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="D2718" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="E2718" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="F2718" t="n">
+        <v>1.12000000476837</v>
+      </c>
+      <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>6700</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>1.08500003814697</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>2064</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>1.09500002861023</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>1.08000004291534</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -62920,7 +62920,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="D2720" t="n">
-        <v>1.09500002861023</v>
+        <v>1.08000004291534</v>
       </c>
       <c r="E2720" t="n">
         <v>1.09500002861023</v>
@@ -62929,6 +62929,29 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>29727</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>1.13499999046326</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="G2721" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>19920</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>1.10500001907349</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>16000</v>
+        <v>5845</v>
       </c>
       <c r="C2715" t="n">
-        <v>1.12000000476837</v>
+        <v>1.11500000953674</v>
       </c>
       <c r="D2715" t="n">
-        <v>1.11000001430511</v>
+        <v>1.0900000333786</v>
       </c>
       <c r="E2715" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="F2715" t="n">
         <v>1.11500000953674</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>1.11000001430511</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>1000</v>
+        <v>16000</v>
       </c>
       <c r="C2716" t="n">
-        <v>1.11500000953674</v>
+        <v>1.12000000476837</v>
       </c>
       <c r="D2716" t="n">
-        <v>1.11500000953674</v>
+        <v>1.11000001430511</v>
       </c>
       <c r="E2716" t="n">
         <v>1.11500000953674</v>
       </c>
       <c r="F2716" t="n">
-        <v>1.11500000953674</v>
+        <v>1.11000001430511</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>925</v>
+        <v>1000</v>
       </c>
       <c r="C2717" t="n">
-        <v>1.12000000476837</v>
+        <v>1.11500000953674</v>
       </c>
       <c r="D2717" t="n">
-        <v>1.12000000476837</v>
+        <v>1.11500000953674</v>
       </c>
       <c r="E2717" t="n">
-        <v>1.12000000476837</v>
+        <v>1.11500000953674</v>
       </c>
       <c r="F2717" t="n">
-        <v>1.12000000476837</v>
+        <v>1.11500000953674</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,10 +62865,10 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>0</v>
+        <v>925</v>
       </c>
       <c r="C2718" t="n">
         <v>1.12000000476837</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>6700</v>
+        <v>0</v>
       </c>
       <c r="C2719" t="n">
-        <v>1.10500001907349</v>
+        <v>1.12000000476837</v>
       </c>
       <c r="D2719" t="n">
-        <v>1.08000004291534</v>
+        <v>1.12000000476837</v>
       </c>
       <c r="E2719" t="n">
-        <v>1.08500003814697</v>
+        <v>1.12000000476837</v>
       </c>
       <c r="F2719" t="n">
-        <v>1.10500001907349</v>
+        <v>1.12000000476837</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>2064</v>
+        <v>6700</v>
       </c>
       <c r="C2720" t="n">
-        <v>1.09500002861023</v>
+        <v>1.10500001907349</v>
       </c>
       <c r="D2720" t="n">
         <v>1.08000004291534</v>
       </c>
       <c r="E2720" t="n">
-        <v>1.09500002861023</v>
+        <v>1.08500003814697</v>
       </c>
       <c r="F2720" t="n">
-        <v>1.08000004291534</v>
+        <v>1.10500001907349</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>29727</v>
+        <v>2064</v>
       </c>
       <c r="C2721" t="n">
-        <v>1.13499999046326</v>
+        <v>1.09500002861023</v>
       </c>
       <c r="D2721" t="n">
-        <v>1.0900000333786</v>
+        <v>1.08000004291534</v>
       </c>
       <c r="E2721" t="n">
-        <v>1.0900000333786</v>
+        <v>1.09500002861023</v>
       </c>
       <c r="F2721" t="n">
-        <v>1.10000002384186</v>
+        <v>1.08000004291534</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>19920</v>
+        <v>29727</v>
       </c>
       <c r="C2722" t="n">
+        <v>1.13499999046326</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>1.10000002384186</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>38193</v>
+      </c>
+      <c r="C2723" t="n">
         <v>1.13999998569489</v>
       </c>
-      <c r="D2722" t="n">
-        <v>1.10500001907349</v>
-      </c>
-      <c r="E2722" t="n">
-        <v>1.12999999523163</v>
-      </c>
-      <c r="F2722" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="G2722" t="s">
+      <c r="D2723" t="n">
+        <v>1.11500000953674</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>1.11500000953674</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>1.13999998569489</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>1.44454109668732</v>
+        <v>1.44454121589661</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G5" t="n">
-        <v>1.46544921398163</v>
+        <v>1.46544909477234</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G6" t="n">
-        <v>1.53482496738434</v>
+        <v>1.53482508659363</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>1.46354830265045</v>
+        <v>1.46354842185974</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G8" t="n">
-        <v>1.49205911159515</v>
+        <v>1.49205923080444</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.557000041008</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4797043800354</v>
+        <v>1.47970449924469</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G17" t="n">
-        <v>1.30198776721954</v>
+        <v>1.30198788642883</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G18" t="n">
-        <v>1.30198776721954</v>
+        <v>1.30198788642883</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G30" t="n">
-        <v>1.13662588596344</v>
+        <v>1.13662576675415</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>1.16100001335144</v>
       </c>
       <c r="G31" t="n">
-        <v>1.10336339473724</v>
+        <v>1.10336351394653</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.35899996757507</v>
       </c>
       <c r="G35" t="n">
-        <v>1.29153394699097</v>
+        <v>1.29153406620026</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G42" t="n">
-        <v>1.29723608493805</v>
+        <v>1.29723620414734</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G44" t="n">
-        <v>1.32289564609528</v>
+        <v>1.32289552688599</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G45" t="n">
-        <v>1.32099485397339</v>
+        <v>1.32099497318268</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G52" t="n">
-        <v>1.32194530963898</v>
+        <v>1.32194542884827</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G53" t="n">
-        <v>1.32194530963898</v>
+        <v>1.32194542884827</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G54" t="n">
-        <v>1.32099485397339</v>
+        <v>1.32099497318268</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>1.32574665546417</v>
+        <v>1.32574677467346</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G64" t="n">
-        <v>1.24116504192352</v>
+        <v>1.24116492271423</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G66" t="n">
-        <v>1.23926448822021</v>
+        <v>1.23926436901093</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G67" t="n">
-        <v>1.22786009311676</v>
+        <v>1.22786021232605</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G68" t="n">
-        <v>1.30578923225403</v>
+        <v>1.30578935146332</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G69" t="n">
-        <v>1.30578923225403</v>
+        <v>1.30578935146332</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G71" t="n">
-        <v>1.24306571483612</v>
+        <v>1.24306583404541</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G73" t="n">
-        <v>1.29058361053467</v>
+        <v>1.29058349132538</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.32700002193451</v>
       </c>
       <c r="G77" t="n">
-        <v>1.26112246513367</v>
+        <v>1.26112258434296</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G84" t="n">
-        <v>1.27347731590271</v>
+        <v>1.27347719669342</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G96" t="n">
-        <v>1.19744861125946</v>
+        <v>1.19744873046875</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.26900005340576</v>
       </c>
       <c r="G97" t="n">
-        <v>1.20600175857544</v>
+        <v>1.20600187778473</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>1.25</v>
       </c>
       <c r="G100" t="n">
-        <v>1.18794512748718</v>
+        <v>1.18794500827789</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G101" t="n">
-        <v>1.19744861125946</v>
+        <v>1.19744873046875</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G103" t="n">
-        <v>1.16133522987366</v>
+        <v>1.16133511066437</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G106" t="n">
-        <v>1.17844152450562</v>
+        <v>1.1784416437149</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G107" t="n">
-        <v>1.17749130725861</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G108" t="n">
-        <v>1.17749130725861</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G109" t="n">
-        <v>1.17559051513672</v>
+        <v>1.17559039592743</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G111" t="n">
-        <v>1.14803004264832</v>
+        <v>1.1480301618576</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G112" t="n">
-        <v>1.18224287033081</v>
+        <v>1.1822429895401</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>1.14993107318878</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.14993107318878</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G119" t="n">
-        <v>1.18699479103088</v>
+        <v>1.18699467182159</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>1.13092386722565</v>
+        <v>1.13092374801636</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G122" t="n">
-        <v>1.13092386722565</v>
+        <v>1.13092374801636</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G123" t="n">
-        <v>1.13662588596344</v>
+        <v>1.13662576675415</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>1.09599995613098</v>
       </c>
       <c r="G125" t="n">
-        <v>1.04159033298492</v>
+        <v>1.04159021377563</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G126" t="n">
-        <v>0.975065350532532</v>
+        <v>0.975065410137177</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G127" t="n">
-        <v>1.00737750530243</v>
+        <v>1.00737738609314</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G131" t="n">
-        <v>1.09005856513977</v>
+        <v>1.09005844593048</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G133" t="n">
-        <v>0.99502295255661</v>
+        <v>0.995022833347321</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G134" t="n">
-        <v>1.02068245410919</v>
+        <v>1.02068257331848</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G135" t="n">
-        <v>1.00547659397125</v>
+        <v>1.00547671318054</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.05200004577637</v>
       </c>
       <c r="G136" t="n">
-        <v>0.999774634838104</v>
+        <v>0.999774694442749</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G138" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G140" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G141" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G145" t="n">
-        <v>0.975065350532532</v>
+        <v>0.975065410137177</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G147" t="n">
-        <v>0.99502295255661</v>
+        <v>0.995022833347321</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G149" t="n">
-        <v>1.00927817821503</v>
+        <v>1.00927829742432</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G150" t="n">
-        <v>1.03588807582855</v>
+        <v>1.03588819503784</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G151" t="n">
-        <v>0.98742002248764</v>
+        <v>0.987420082092285</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G152" t="n">
-        <v>0.986469686031342</v>
+        <v>0.986469566822052</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G153" t="n">
-        <v>0.986469686031342</v>
+        <v>0.986469566822052</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>1.00737750530243</v>
+        <v>1.00737738609314</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G155" t="n">
-        <v>1.00737750530243</v>
+        <v>1.00737738609314</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G156" t="n">
-        <v>1.01402986049652</v>
+        <v>1.01402997970581</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G157" t="n">
-        <v>1.01402986049652</v>
+        <v>1.01402997970581</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G158" t="n">
-        <v>1.01402986049652</v>
+        <v>1.01402997970581</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.07700002193451</v>
       </c>
       <c r="G159" t="n">
-        <v>1.02353346347809</v>
+        <v>1.02353358268738</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G160" t="n">
-        <v>1.02163290977478</v>
+        <v>1.02163279056549</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G161" t="n">
-        <v>0.980767428874969</v>
+        <v>0.980767369270325</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G164" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G165" t="n">
-        <v>0.963661074638367</v>
+        <v>0.963661193847656</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G166" t="n">
-        <v>0.967462480068207</v>
+        <v>0.967462539672852</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G169" t="n">
-        <v>0.986469686031342</v>
+        <v>0.986469566822052</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G170" t="n">
-        <v>0.973164618015289</v>
+        <v>0.973164677619934</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G171" t="n">
-        <v>0.99502295255661</v>
+        <v>0.995022833347321</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G172" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G173" t="n">
-        <v>1.00547659397125</v>
+        <v>1.00547671318054</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G175" t="n">
-        <v>1.05204403400421</v>
+        <v>1.0520441532135</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G178" t="n">
-        <v>1.15183162689209</v>
+        <v>1.15183174610138</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G179" t="n">
-        <v>1.12427127361298</v>
+        <v>1.12427115440369</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.12100005149841</v>
       </c>
       <c r="G183" t="n">
-        <v>1.06534922122955</v>
+        <v>1.06534934043884</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G185" t="n">
-        <v>1.08910810947418</v>
+        <v>1.08910799026489</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G188" t="n">
-        <v>1.03588807582855</v>
+        <v>1.03588819503784</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G189" t="n">
-        <v>1.00072491168976</v>
+        <v>1.00072503089905</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>1.04299998283386</v>
       </c>
       <c r="G191" t="n">
-        <v>0.991221487522125</v>
+        <v>0.991221368312836</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G192" t="n">
-        <v>0.98742002248764</v>
+        <v>0.987420082092285</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G196" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G199" t="n">
-        <v>0.986469686031342</v>
+        <v>0.986469566822052</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G200" t="n">
-        <v>0.984568893909454</v>
+        <v>0.98456883430481</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G202" t="n">
-        <v>0.963661074638367</v>
+        <v>0.963661193847656</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G203" t="n">
-        <v>0.984568893909454</v>
+        <v>0.98456883430481</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G207" t="n">
-        <v>0.98742002248764</v>
+        <v>0.987420082092285</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G209" t="n">
-        <v>1.00357615947723</v>
+        <v>1.00357604026794</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G212" t="n">
-        <v>0.973164618015289</v>
+        <v>0.973164677619934</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.00699996948242</v>
       </c>
       <c r="G218" t="n">
-        <v>0.957008600234985</v>
+        <v>0.957008540630341</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G223" t="n">
-        <v>0.973164618015289</v>
+        <v>0.973164677619934</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638471126556</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G227" t="n">
-        <v>0.967462480068207</v>
+        <v>0.967462539672852</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G230" t="n">
-        <v>0.984568893909454</v>
+        <v>0.98456883430481</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G231" t="n">
-        <v>0.984568893909454</v>
+        <v>0.98456883430481</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G236" t="n">
-        <v>0.973164618015289</v>
+        <v>0.973164677619934</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>0.985499978065491</v>
       </c>
       <c r="G238" t="n">
-        <v>0.936575949192047</v>
+        <v>0.936575889587402</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G241" t="n">
-        <v>1.00357615947723</v>
+        <v>1.00357604026794</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G244" t="n">
-        <v>0.980767428874969</v>
+        <v>0.980767369270325</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G245" t="n">
-        <v>0.975065350532532</v>
+        <v>0.975065410137177</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.00100004673004</v>
       </c>
       <c r="G246" t="n">
-        <v>0.951306462287903</v>
+        <v>0.951306521892548</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G247" t="n">
-        <v>0.984568893909454</v>
+        <v>0.98456883430481</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G248" t="n">
-        <v>0.98742002248764</v>
+        <v>0.987420082092285</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G249" t="n">
-        <v>0.982668340206146</v>
+        <v>0.982668220996857</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G250" t="n">
-        <v>0.973164618015289</v>
+        <v>0.973164677619934</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G252" t="n">
-        <v>0.963661074638367</v>
+        <v>0.963661193847656</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G258" t="n">
-        <v>0.9836186170578</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G259" t="n">
-        <v>0.984568893909454</v>
+        <v>0.98456883430481</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G261" t="n">
-        <v>1.04254066944122</v>
+        <v>1.04254055023193</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>1.5</v>
       </c>
       <c r="G265" t="n">
-        <v>1.42553424835205</v>
+        <v>1.42553412914276</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G266" t="n">
-        <v>1.39227163791656</v>
+        <v>1.39227175712585</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G267" t="n">
-        <v>1.30864024162292</v>
+        <v>1.30864036083221</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G271" t="n">
-        <v>1.32289564609528</v>
+        <v>1.32289552688599</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G275" t="n">
-        <v>1.38371849060059</v>
+        <v>1.3837183713913</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>1.36099994182587</v>
       </c>
       <c r="G277" t="n">
-        <v>1.29343450069427</v>
+        <v>1.29343461990356</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>1.31099998950958</v>
       </c>
       <c r="G280" t="n">
-        <v>1.24591684341431</v>
+        <v>1.2459169626236</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G283" t="n">
-        <v>1.17749130725861</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>1.14993107318878</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G289" t="n">
-        <v>1.09005856513977</v>
+        <v>1.09005844593048</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G290" t="n">
-        <v>1.09671103954315</v>
+        <v>1.09671092033386</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G296" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>1.20695221424103</v>
+        <v>1.20695233345032</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G305" t="n">
-        <v>1.13092386722565</v>
+        <v>1.13092374801636</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G306" t="n">
-        <v>1.15753388404846</v>
+        <v>1.15753376483917</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G307" t="n">
-        <v>1.15088105201721</v>
+        <v>1.1508811712265</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G308" t="n">
-        <v>1.15943431854248</v>
+        <v>1.15943443775177</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G309" t="n">
-        <v>1.14993107318878</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G310" t="n">
-        <v>1.13662588596344</v>
+        <v>1.13662576675415</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G311" t="n">
-        <v>1.15183162689209</v>
+        <v>1.15183174610138</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>1.14042747020721</v>
+        <v>1.14042735099792</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G315" t="n">
-        <v>1.13282454013824</v>
+        <v>1.13282442092896</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>1.14993107318878</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G318" t="n">
-        <v>1.12902295589447</v>
+        <v>1.12902307510376</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G322" t="n">
-        <v>1.16323578357697</v>
+        <v>1.16323590278625</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G325" t="n">
-        <v>1.13092386722565</v>
+        <v>1.13092374801636</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G328" t="n">
-        <v>1.12807285785675</v>
+        <v>1.12807273864746</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G329" t="n">
-        <v>1.12902295589447</v>
+        <v>1.12902307510376</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G334" t="n">
-        <v>1.10621464252472</v>
+        <v>1.10621452331543</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G335" t="n">
-        <v>1.13092386722565</v>
+        <v>1.13092374801636</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G336" t="n">
-        <v>1.11666834354401</v>
+        <v>1.1166684627533</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G337" t="n">
-        <v>1.115718126297</v>
+        <v>1.11571800708771</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G346" t="n">
-        <v>1.08910810947418</v>
+        <v>1.08910799026489</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G348" t="n">
-        <v>1.115718126297</v>
+        <v>1.11571800708771</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>1.13092386722565</v>
+        <v>1.13092374801636</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G354" t="n">
-        <v>1.07865428924561</v>
+        <v>1.07865417003632</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G356" t="n">
-        <v>1.09386003017426</v>
+        <v>1.09385979175568</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G360" t="n">
-        <v>1.04919302463531</v>
+        <v>1.0491931438446</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G362" t="n">
-        <v>1.09956192970276</v>
+        <v>1.09956204891205</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G363" t="n">
-        <v>1.07865428924561</v>
+        <v>1.07865417003632</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G366" t="n">
-        <v>1.04919302463531</v>
+        <v>1.0491931438446</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.12100005149841</v>
       </c>
       <c r="G370" t="n">
-        <v>1.06534922122955</v>
+        <v>1.06534934043884</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.10099995136261</v>
       </c>
       <c r="G371" t="n">
-        <v>1.04634201526642</v>
+        <v>1.04634189605713</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G372" t="n">
-        <v>1.0510938167572</v>
+        <v>1.05109393596649</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G373" t="n">
-        <v>1.0510938167572</v>
+        <v>1.05109393596649</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G374" t="n">
-        <v>1.09386003017426</v>
+        <v>1.09385979175568</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G377" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G382" t="n">
-        <v>1.09005856513977</v>
+        <v>1.09005844593048</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G384" t="n">
-        <v>1.09290945529938</v>
+        <v>1.09290933609009</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G386" t="n">
-        <v>1.12902295589447</v>
+        <v>1.12902307510376</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G388" t="n">
-        <v>1.14042747020721</v>
+        <v>1.14042735099792</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G393" t="n">
-        <v>1.14042747020721</v>
+        <v>1.14042735099792</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G394" t="n">
-        <v>1.12427127361298</v>
+        <v>1.12427115440369</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G395" t="n">
-        <v>1.13092386722565</v>
+        <v>1.13092374801636</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>1.14042747020721</v>
+        <v>1.14042735099792</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G402" t="n">
-        <v>1.14042747020721</v>
+        <v>1.14042735099792</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G407" t="n">
-        <v>1.115718126297</v>
+        <v>1.11571800708771</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G409" t="n">
-        <v>1.11476767063141</v>
+        <v>1.1147677898407</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G414" t="n">
-        <v>1.10621464252472</v>
+        <v>1.10621452331543</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G416" t="n">
-        <v>1.09671103954315</v>
+        <v>1.09671092033386</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G418" t="n">
-        <v>1.11096632480621</v>
+        <v>1.1109664440155</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G419" t="n">
-        <v>1.10621464252472</v>
+        <v>1.10621452331543</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G422" t="n">
-        <v>1.13092386722565</v>
+        <v>1.13092374801636</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G424" t="n">
-        <v>1.16133522987366</v>
+        <v>1.16133511066437</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>1.14993107318878</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G428" t="n">
-        <v>1.12902295589447</v>
+        <v>1.12902307510376</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G429" t="n">
-        <v>1.12427127361298</v>
+        <v>1.12427115440369</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G436" t="n">
-        <v>1.11476767063141</v>
+        <v>1.1147677898407</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G440" t="n">
-        <v>1.115718126297</v>
+        <v>1.11571800708771</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.20700001716614</v>
       </c>
       <c r="G449" t="n">
-        <v>1.14707970619202</v>
+        <v>1.14707982540131</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G450" t="n">
-        <v>1.15088105201721</v>
+        <v>1.1508811712265</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G451" t="n">
-        <v>1.14993107318878</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>1.25</v>
       </c>
       <c r="G454" t="n">
-        <v>1.18794512748718</v>
+        <v>1.18794500827789</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G455" t="n">
-        <v>1.16133522987366</v>
+        <v>1.16133511066437</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G460" t="n">
-        <v>1.17749130725861</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>1.14993107318878</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G464" t="n">
-        <v>1.19744861125946</v>
+        <v>1.19744873046875</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G465" t="n">
-        <v>1.17844152450562</v>
+        <v>1.1784416437149</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G466" t="n">
-        <v>1.15468263626099</v>
+        <v>1.15468275547028</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G467" t="n">
-        <v>1.15468263626099</v>
+        <v>1.15468275547028</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G469" t="n">
-        <v>1.17844152450562</v>
+        <v>1.1784416437149</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>1.20695221424103</v>
+        <v>1.20695233345032</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G476" t="n">
-        <v>1.17749130725861</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>1.14993107318878</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G479" t="n">
-        <v>1.11476767063141</v>
+        <v>1.1147677898407</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G480" t="n">
-        <v>1.13282454013824</v>
+        <v>1.13282442092896</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G484" t="n">
-        <v>1.15563297271729</v>
+        <v>1.15563309192657</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G494" t="n">
-        <v>1.10621464252472</v>
+        <v>1.10621452331543</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G495" t="n">
-        <v>1.11476767063141</v>
+        <v>1.1147677898407</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G498" t="n">
-        <v>1.11096632480621</v>
+        <v>1.1109664440155</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G499" t="n">
-        <v>1.11096632480621</v>
+        <v>1.1109664440155</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G500" t="n">
-        <v>1.11096632480621</v>
+        <v>1.1109664440155</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G508" t="n">
-        <v>1.10431361198425</v>
+        <v>1.10431373119354</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G509" t="n">
-        <v>1.11096632480621</v>
+        <v>1.1109664440155</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G510" t="n">
-        <v>1.12427127361298</v>
+        <v>1.12427115440369</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G512" t="n">
-        <v>1.11666834354401</v>
+        <v>1.1166684627533</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G513" t="n">
-        <v>1.13092386722565</v>
+        <v>1.13092374801636</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G514" t="n">
-        <v>1.13092386722565</v>
+        <v>1.13092374801636</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G518" t="n">
-        <v>1.11666834354401</v>
+        <v>1.1166684627533</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G523" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G529" t="n">
-        <v>1.09290945529938</v>
+        <v>1.09290933609009</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G530" t="n">
-        <v>1.11666834354401</v>
+        <v>1.1166684627533</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G532" t="n">
-        <v>1.09290945529938</v>
+        <v>1.09290933609009</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G533" t="n">
-        <v>1.09290945529938</v>
+        <v>1.09290933609009</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G534" t="n">
-        <v>1.09290945529938</v>
+        <v>1.09290933609009</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G535" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G550" t="n">
-        <v>1.04063999652863</v>
+        <v>1.04063987731934</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G551" t="n">
-        <v>1.07865428924561</v>
+        <v>1.07865417003632</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G554" t="n">
-        <v>1.02163290977478</v>
+        <v>1.02163279056549</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G562" t="n">
-        <v>1.04063999652863</v>
+        <v>1.04063987731934</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G563" t="n">
-        <v>1.03588807582855</v>
+        <v>1.03588819503784</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G564" t="n">
-        <v>1.04063999652863</v>
+        <v>1.04063987731934</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G567" t="n">
-        <v>1.07865428924561</v>
+        <v>1.07865417003632</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G568" t="n">
-        <v>1.07865428924561</v>
+        <v>1.07865417003632</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G578" t="n">
-        <v>1.07865428924561</v>
+        <v>1.07865417003632</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G579" t="n">
-        <v>1.07865428924561</v>
+        <v>1.07865417003632</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G581" t="n">
-        <v>1.07865428924561</v>
+        <v>1.07865417003632</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G583" t="n">
-        <v>1.07865428924561</v>
+        <v>1.07865417003632</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G586" t="n">
-        <v>1.07865428924561</v>
+        <v>1.07865417003632</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G588" t="n">
-        <v>1.04063999652863</v>
+        <v>1.04063987731934</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G595" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638471126556</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G596" t="n">
-        <v>1.02163290977478</v>
+        <v>1.02163279056549</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G597" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638471126556</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G599" t="n">
-        <v>1.03588807582855</v>
+        <v>1.03588819503784</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G602" t="n">
-        <v>1.02163290977478</v>
+        <v>1.02163279056549</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G605" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638471126556</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G606" t="n">
-        <v>1.04063999652863</v>
+        <v>1.04063987731934</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G607" t="n">
-        <v>1.00737750530243</v>
+        <v>1.00737738609314</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G608" t="n">
-        <v>1.02163290977478</v>
+        <v>1.02163279056549</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G610" t="n">
-        <v>1.01212930679321</v>
+        <v>1.0121294260025</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G611" t="n">
-        <v>1.04063999652863</v>
+        <v>1.04063987731934</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G612" t="n">
-        <v>1.02163290977478</v>
+        <v>1.02163279056549</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G615" t="n">
-        <v>0.940852522850037</v>
+        <v>0.940852582454681</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G616" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G622" t="n">
-        <v>0.948455393314362</v>
+        <v>0.948455452919006</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>0.940852522850037</v>
+        <v>0.940852582454681</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G628" t="n">
-        <v>0.946554601192474</v>
+        <v>0.946554660797119</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G630" t="n">
-        <v>0.948455393314362</v>
+        <v>0.948455452919006</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G633" t="n">
-        <v>0.940852522850037</v>
+        <v>0.940852582454681</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G634" t="n">
-        <v>0.933249711990356</v>
+        <v>0.933249652385712</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G635" t="n">
-        <v>0.933249711990356</v>
+        <v>0.933249652385712</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G638" t="n">
-        <v>0.916143238544464</v>
+        <v>0.916143298149109</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G639" t="n">
-        <v>0.935150504112244</v>
+        <v>0.935150444507599</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G642" t="n">
-        <v>0.927547514438629</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G643" t="n">
-        <v>0.940852522850037</v>
+        <v>0.940852582454681</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G644" t="n">
-        <v>0.938951790332794</v>
+        <v>0.938951849937439</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G645" t="n">
-        <v>0.937051177024841</v>
+        <v>0.937051117420197</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G647" t="n">
-        <v>0.927547514438629</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G648" t="n">
-        <v>0.927547514438629</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G652" t="n">
-        <v>0.923746109008789</v>
+        <v>0.923746168613434</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G663" t="n">
-        <v>0.916143238544464</v>
+        <v>0.916143298149109</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G664" t="n">
-        <v>0.916143238544464</v>
+        <v>0.916143298149109</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G680" t="n">
-        <v>0.883831202983856</v>
+        <v>0.883831143379211</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G685" t="n">
-        <v>0.935150504112244</v>
+        <v>0.935150444507599</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G687" t="n">
-        <v>0.925646781921387</v>
+        <v>0.925646841526031</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G695" t="n">
-        <v>0.921845376491547</v>
+        <v>0.921845436096191</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G701" t="n">
-        <v>0.921845376491547</v>
+        <v>0.921845436096191</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G705" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G707" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G708" t="n">
-        <v>0.836313426494598</v>
+        <v>0.836313366889954</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G709" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114712715149</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G711" t="n">
-        <v>0.828710496425629</v>
+        <v>0.828710436820984</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G712" t="n">
-        <v>0.800199866294861</v>
+        <v>0.800199806690216</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G718" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G719" t="n">
-        <v>0.802100539207458</v>
+        <v>0.802100479602814</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G720" t="n">
-        <v>0.802100539207458</v>
+        <v>0.802100479602814</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G721" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G726" t="n">
-        <v>0.800199866294861</v>
+        <v>0.800199806690216</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>0.800199866294861</v>
+        <v>0.800199806690216</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G730" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G731" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G732" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G733" t="n">
-        <v>0.783093392848969</v>
+        <v>0.783093452453613</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G734" t="n">
-        <v>0.804001271724701</v>
+        <v>0.804001212120056</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G735" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G737" t="n">
-        <v>0.796398401260376</v>
+        <v>0.796398460865021</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G738" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G739" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G740" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G741" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G743" t="n">
-        <v>0.802100539207458</v>
+        <v>0.802100479602814</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G747" t="n">
-        <v>0.796398401260376</v>
+        <v>0.796398460865021</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G748" t="n">
-        <v>0.802100539207458</v>
+        <v>0.802100479602814</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G749" t="n">
-        <v>0.802100539207458</v>
+        <v>0.802100479602814</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G751" t="n">
-        <v>0.800199866294861</v>
+        <v>0.800199806690216</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G754" t="n">
-        <v>0.773589849472046</v>
+        <v>0.773589909076691</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>0.800199866294861</v>
+        <v>0.800199806690216</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G766" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G768" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G774" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G778" t="n">
-        <v>0.800199866294861</v>
+        <v>0.800199806690216</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G779" t="n">
-        <v>0.872426807880402</v>
+        <v>0.872426867485046</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G783" t="n">
-        <v>0.874327600002289</v>
+        <v>0.874327659606934</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G785" t="n">
-        <v>0.883831202983856</v>
+        <v>0.883831143379211</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G789" t="n">
-        <v>0.874327600002289</v>
+        <v>0.874327659606934</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G791" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G797" t="n">
-        <v>0.836313426494598</v>
+        <v>0.836313366889954</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G800" t="n">
-        <v>0.845816969871521</v>
+        <v>0.845816910266876</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G803" t="n">
-        <v>0.887632668018341</v>
+        <v>0.887632608413696</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G805" t="n">
-        <v>0.876228272914886</v>
+        <v>0.876228332519531</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>0.853419780731201</v>
+        <v>0.853419721126556</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G832" t="n">
-        <v>0.876228272914886</v>
+        <v>0.876228332519531</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G833" t="n">
-        <v>0.872426807880402</v>
+        <v>0.872426867485046</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G834" t="n">
-        <v>0.885731935501099</v>
+        <v>0.885731875896454</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G838" t="n">
-        <v>1.03588807582855</v>
+        <v>1.03588819503784</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G839" t="n">
-        <v>1.00737750530243</v>
+        <v>1.00737738609314</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G840" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G841" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G846" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G850" t="n">
-        <v>0.938951790332794</v>
+        <v>0.938951849937439</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G854" t="n">
-        <v>0.923746109008789</v>
+        <v>0.923746168613434</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G861" t="n">
-        <v>0.948455393314362</v>
+        <v>0.948455452919006</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G865" t="n">
-        <v>0.883831202983856</v>
+        <v>0.883831143379211</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G869" t="n">
-        <v>0.887632668018341</v>
+        <v>0.887632608413696</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G870" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G873" t="n">
-        <v>0.885731935501099</v>
+        <v>0.885731875896454</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G874" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G875" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G876" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G877" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G878" t="n">
-        <v>0.881930470466614</v>
+        <v>0.881930410861969</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G880" t="n">
-        <v>0.874327600002289</v>
+        <v>0.874327659606934</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G902" t="n">
-        <v>0.853419780731201</v>
+        <v>0.853419721126556</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G903" t="n">
-        <v>0.836313426494598</v>
+        <v>0.836313366889954</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>0.853419780731201</v>
+        <v>0.853419721126556</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G905" t="n">
-        <v>0.845816969871521</v>
+        <v>0.845816910266876</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G906" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>0.853419780731201</v>
+        <v>0.853419721126556</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G908" t="n">
-        <v>0.845816969871521</v>
+        <v>0.845816910266876</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G909" t="n">
-        <v>0.845816969871521</v>
+        <v>0.845816910266876</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G910" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114712715149</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G915" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G919" t="n">
-        <v>0.845816969871521</v>
+        <v>0.845816910266876</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G920" t="n">
-        <v>0.845816969871521</v>
+        <v>0.845816910266876</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G921" t="n">
-        <v>0.845816969871521</v>
+        <v>0.845816910266876</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G923" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114712715149</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G924" t="n">
-        <v>0.887632668018341</v>
+        <v>0.887632608413696</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G925" t="n">
-        <v>0.883831202983856</v>
+        <v>0.883831143379211</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G926" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G928" t="n">
-        <v>0.885731935501099</v>
+        <v>0.885731875896454</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G929" t="n">
-        <v>0.885731935501099</v>
+        <v>0.885731875896454</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G930" t="n">
-        <v>0.921845376491547</v>
+        <v>0.921845436096191</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G931" t="n">
-        <v>0.937051177024841</v>
+        <v>0.937051117420197</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G938" t="n">
-        <v>0.927547514438629</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G941" t="n">
-        <v>0.927547514438629</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G948" t="n">
-        <v>0.927547514438629</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G950" t="n">
-        <v>0.937051177024841</v>
+        <v>0.937051117420197</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G953" t="n">
-        <v>0.935150504112244</v>
+        <v>0.935150444507599</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G956" t="n">
-        <v>0.916143238544464</v>
+        <v>0.916143298149109</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G961" t="n">
-        <v>0.883831202983856</v>
+        <v>0.883831143379211</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G971" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G975" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G978" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G989" t="n">
-        <v>0.940852522850037</v>
+        <v>0.940852582454681</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G990" t="n">
-        <v>0.935150504112244</v>
+        <v>0.935150444507599</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G996" t="n">
-        <v>0.9836186170578</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G997" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G998" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.9836186170578</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.01212930679321</v>
+        <v>1.0121294260025</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.03588807582855</v>
+        <v>1.03588819503784</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.02163290977478</v>
+        <v>1.02163279056549</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638471126556</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.00737750530243</v>
+        <v>1.00737738609314</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.01212930679321</v>
+        <v>1.0121294260025</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.9836186170578</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.00737750530243</v>
+        <v>1.00737738609314</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.03588807582855</v>
+        <v>1.03588819503784</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.07865428924561</v>
+        <v>1.07865417003632</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.03588807582855</v>
+        <v>1.03588819503784</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.9836186170578</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.937051177024841</v>
+        <v>0.937051117420197</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.925646781921387</v>
+        <v>0.925646841526031</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.938951790332794</v>
+        <v>0.938951849937439</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>0.990000009536743</v>
       </c>
       <c r="G1060" t="n">
-        <v>0.940852522850037</v>
+        <v>0.940852582454681</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.925646781921387</v>
+        <v>0.925646841526031</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.771689057350159</v>
+        <v>0.771689176559448</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.836313426494598</v>
+        <v>0.836313366889954</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.872426807880402</v>
+        <v>0.872426867485046</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114712715149</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.836313426494598</v>
+        <v>0.836313366889954</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.845816969871521</v>
+        <v>0.845816910266876</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114712715149</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114712715149</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.872426807880402</v>
+        <v>0.872426867485046</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.834412693977356</v>
+        <v>0.834412634372711</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.845816969871521</v>
+        <v>0.845816910266876</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.834412693977356</v>
+        <v>0.834412634372711</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.804001271724701</v>
+        <v>0.804001212120056</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.804001271724701</v>
+        <v>0.804001212120056</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.815405488014221</v>
+        <v>0.815405428409576</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.815405488014221</v>
+        <v>0.815405428409576</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.815405488014221</v>
+        <v>0.815405428409576</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.815405488014221</v>
+        <v>0.815405428409576</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.836313426494598</v>
+        <v>0.836313366889954</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1133" t="n">
-        <v>0.828710496425629</v>
+        <v>0.828710436820984</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114712715149</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114712715149</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1136" t="n">
-        <v>0.845816969871521</v>
+        <v>0.845816910266876</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.845816969871521</v>
+        <v>0.845816910266876</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.845816969871521</v>
+        <v>0.845816910266876</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.834412693977356</v>
+        <v>0.834412634372711</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.828710496425629</v>
+        <v>0.828710436820984</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.828710496425629</v>
+        <v>0.828710436820984</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.828710496425629</v>
+        <v>0.828710436820984</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.836313426494598</v>
+        <v>0.836313366889954</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.845816969871521</v>
+        <v>0.845816910266876</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1152" t="n">
-        <v>0.836313426494598</v>
+        <v>0.836313366889954</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.824909031391144</v>
+        <v>0.824909090995789</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.824909031391144</v>
+        <v>0.824909090995789</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.800199866294861</v>
+        <v>0.800199806690216</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.804001271724701</v>
+        <v>0.804001212120056</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.815405488014221</v>
+        <v>0.815405428409576</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.811604142189026</v>
+        <v>0.811604082584381</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.811604142189026</v>
+        <v>0.811604082584381</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.783093392848969</v>
+        <v>0.783093452453613</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.804001271724701</v>
+        <v>0.804001212120056</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.773589849472046</v>
+        <v>0.773589909076691</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.773589849472046</v>
+        <v>0.773589909076691</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.783093392848969</v>
+        <v>0.783093452453613</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.802100539207458</v>
+        <v>0.802100479602814</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.783093392848969</v>
+        <v>0.783093452453613</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.796398401260376</v>
+        <v>0.796398460865021</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.771689057350159</v>
+        <v>0.771689176559448</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.69376003742218</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.756483435630798</v>
+        <v>0.756483495235443</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.783093392848969</v>
+        <v>0.783093452453613</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.754582703113556</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.754582703113556</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.756483435630798</v>
+        <v>0.756483495235443</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.771689057350159</v>
+        <v>0.771689176559448</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.756483435630798</v>
+        <v>0.756483495235443</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.74317854642868</v>
+        <v>0.743178486824036</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.733674883842468</v>
+        <v>0.733674943447113</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.733674883842468</v>
+        <v>0.733674943447113</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.733674883842468</v>
+        <v>0.733674943447113</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.720369935035706</v>
+        <v>0.72036999464035</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.74317854642868</v>
+        <v>0.743178486824036</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.783093392848969</v>
+        <v>0.783093452453613</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.796398401260376</v>
+        <v>0.796398460865021</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1313" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.754582703113556</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.754582703113556</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.754582703113556</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.74317854642868</v>
+        <v>0.743178486824036</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1348" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.756483435630798</v>
+        <v>0.756483495235443</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.754582703113556</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.746979892253876</v>
+        <v>0.746979951858521</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.722270548343658</v>
+        <v>0.722270607948303</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.746979892253876</v>
+        <v>0.746979951858521</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1365" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1371" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.783093392848969</v>
+        <v>0.783093452453613</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.834412693977356</v>
+        <v>0.834412634372711</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1390" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.796398401260376</v>
+        <v>0.796398460865021</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.800199866294861</v>
+        <v>0.800199806690216</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.796398401260376</v>
+        <v>0.796398460865021</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1401" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.754582703113556</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.74317854642868</v>
+        <v>0.743178486824036</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.771689057350159</v>
+        <v>0.771689176559448</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.746979892253876</v>
+        <v>0.746979951858521</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.754582703113556</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.74317854642868</v>
+        <v>0.743178486824036</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.756483435630798</v>
+        <v>0.756483495235443</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1434" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.746979892253876</v>
+        <v>0.746979951858521</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.756483435630798</v>
+        <v>0.756483495235443</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1442" t="n">
-        <v>0.773589849472046</v>
+        <v>0.773589909076691</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.746979892253876</v>
+        <v>0.746979951858521</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.756483435630798</v>
+        <v>0.756483495235443</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.74317854642868</v>
+        <v>0.743178486824036</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1455" t="n">
-        <v>0.754582703113556</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.754582703113556</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1457" t="n">
-        <v>0.754582703113556</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.746979892253876</v>
+        <v>0.746979951858521</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.754582703113556</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.756483435630798</v>
+        <v>0.756483495235443</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1463" t="n">
-        <v>0.74317854642868</v>
+        <v>0.743178486824036</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.74317854642868</v>
+        <v>0.743178486824036</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.729873478412628</v>
+        <v>0.729873538017273</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.733674883842468</v>
+        <v>0.733674943447113</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.729873478412628</v>
+        <v>0.729873538017273</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.729873478412628</v>
+        <v>0.729873538017273</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.729873478412628</v>
+        <v>0.729873538017273</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.722270548343658</v>
+        <v>0.722270607948303</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.733674883842468</v>
+        <v>0.733674943447113</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1491" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1492" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.729873478412628</v>
+        <v>0.729873538017273</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.720369935035706</v>
+        <v>0.72036999464035</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.710866391658783</v>
+        <v>0.710866332054138</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.708965659141541</v>
+        <v>0.708965599536896</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>0.75</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.712767124176025</v>
+        <v>0.712767064571381</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.710866391658783</v>
+        <v>0.710866332054138</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.710866391658783</v>
+        <v>0.710866332054138</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.708965659141541</v>
+        <v>0.708965599536896</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>0.75</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.712767124176025</v>
+        <v>0.712767064571381</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.708965659141541</v>
+        <v>0.708965599536896</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.708965659141541</v>
+        <v>0.708965599536896</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1521" t="n">
-        <v>0.710866391658783</v>
+        <v>0.710866332054138</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.691859245300293</v>
+        <v>0.691859185695648</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1527" t="n">
-        <v>0.691859245300293</v>
+        <v>0.691859185695648</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.69376003742218</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.69376003742218</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1533" t="n">
-        <v>0.691859245300293</v>
+        <v>0.691859185695648</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.69376003742218</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.69376003742218</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.69376003742218</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.695660710334778</v>
+        <v>0.695660650730133</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1553" t="n">
-        <v>0.680454969406128</v>
+        <v>0.680455029010773</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1555" t="n">
-        <v>0.680454969406128</v>
+        <v>0.680455029010773</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1556" t="n">
-        <v>0.680454969406128</v>
+        <v>0.680455029010773</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1559" t="n">
-        <v>0.729873478412628</v>
+        <v>0.729873538017273</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.708965659141541</v>
+        <v>0.708965599536896</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>0.75</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.712767124176025</v>
+        <v>0.712767064571381</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.69376003742218</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.657646417617798</v>
+        <v>0.657646358013153</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.62153285741806</v>
+        <v>0.621532917022705</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.62153285741806</v>
+        <v>0.621532917022705</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1579" t="n">
-        <v>0.670951426029205</v>
+        <v>0.670951366424561</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1581" t="n">
-        <v>0.657646417617798</v>
+        <v>0.657646358013153</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1586" t="n">
-        <v>0.644341468811035</v>
+        <v>0.644341349601746</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.644341468811035</v>
+        <v>0.644341349601746</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1600" t="n">
-        <v>0.636738657951355</v>
+        <v>0.63673859834671</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1603" t="n">
-        <v>0.636738657951355</v>
+        <v>0.63673859834671</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.615830719470978</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.581617891788483</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.615830719470978</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.615830719470978</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1633" t="n">
-        <v>0.61393004655838</v>
+        <v>0.613930106163025</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1635" t="n">
-        <v>0.615830719470978</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1636" t="n">
-        <v>0.615830719470978</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.615830719470978</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1639" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1646" t="n">
-        <v>0.581617891788483</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1648" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1649" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1650" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1651" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G1656" t="n">
-        <v>0.496085911989212</v>
+        <v>0.49608588218689</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.49798658490181</v>
+        <v>0.497986555099487</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G1658" t="n">
-        <v>0.490383714437485</v>
+        <v>0.490383684635162</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.524596512317657</v>
+        <v>0.524596571922302</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1670" t="n">
-        <v>0.577816486358643</v>
+        <v>0.577816545963287</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1673" t="n">
-        <v>0.577816486358643</v>
+        <v>0.577816545963287</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1676" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1679" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1698" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1699" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1705" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1716" t="n">
-        <v>0.564511477947235</v>
+        <v>0.56451153755188</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1721" t="n">
-        <v>0.577816486358643</v>
+        <v>0.577816545963287</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1722" t="n">
-        <v>0.57971715927124</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.57971715927124</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1727" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.57971715927124</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1738" t="n">
-        <v>0.581617891788483</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.581617891788483</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.577816486358643</v>
+        <v>0.577816545963287</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1743" t="n">
-        <v>0.575915813446045</v>
+        <v>0.57591587305069</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.575915813446045</v>
+        <v>0.57591587305069</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.564511477947235</v>
+        <v>0.56451153755188</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1754" t="n">
-        <v>0.581617891788483</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.581617891788483</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1765" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1768" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1779" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1781" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1782" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1783" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1784" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1785" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1789" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1795" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1796" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1800" t="n">
-        <v>0.581617891788483</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1801" t="n">
-        <v>0.581617891788483</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1805" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1806" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1812" t="n">
-        <v>0.581617891788483</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1817" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1818" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1820" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1821" t="n">
-        <v>0.575915813446045</v>
+        <v>0.57591587305069</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.577816486358643</v>
+        <v>0.577816545963287</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1825" t="n">
-        <v>0.577816486358643</v>
+        <v>0.577816545963287</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1827" t="n">
-        <v>0.57971715927124</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1828" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.575915813446045</v>
+        <v>0.57591587305069</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1842" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1844" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.57971715927124</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1846" t="n">
-        <v>0.59872430562973</v>
+        <v>0.598724365234375</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1852" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1853" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1854" t="n">
-        <v>0.581617891788483</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1855" t="n">
-        <v>0.581617891788483</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1860" t="n">
-        <v>0.57971715927124</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1863" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1864" t="n">
-        <v>0.57971715927124</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.564511477947235</v>
+        <v>0.56451153755188</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1873" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1874" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1875" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1879" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1880" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1881" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1882" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1898" t="n">
-        <v>0.564511477947235</v>
+        <v>0.56451153755188</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1903" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1904" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1914" t="n">
-        <v>0.55310732126236</v>
+        <v>0.553107261657715</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1929" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1935" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1937" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1938" t="n">
-        <v>0.57971715927124</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1941" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1949" t="n">
-        <v>0.55310732126236</v>
+        <v>0.553107261657715</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1961" t="n">
-        <v>0.564511477947235</v>
+        <v>0.56451153755188</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1967" t="n">
-        <v>0.55310732126236</v>
+        <v>0.553107261657715</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1973" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G1979" t="n">
-        <v>0.557727873325348</v>
+        <v>0.557727932929993</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G1981" t="n">
-        <v>0.544218897819519</v>
+        <v>0.544218957424164</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1986" t="n">
-        <v>0.521060705184937</v>
+        <v>0.521060645580292</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1989" t="n">
-        <v>0.521060705184937</v>
+        <v>0.521060645580292</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1992" t="n">
-        <v>0.522990524768829</v>
+        <v>0.522990465164185</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1994" t="n">
-        <v>0.521060705184937</v>
+        <v>0.521060645580292</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1995" t="n">
-        <v>0.521060705184937</v>
+        <v>0.521060645580292</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52265,7 +52265,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1996" t="n">
-        <v>0.521060705184937</v>
+        <v>0.521060645580292</v>
       </c>
       <c r="H1996" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1998" t="n">
-        <v>0.522990524768829</v>
+        <v>0.522990465164185</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1999" t="n">
-        <v>0.519130766391754</v>
+        <v>0.519130825996399</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2000" t="n">
-        <v>0.524920344352722</v>
+        <v>0.524920403957367</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2002" t="n">
-        <v>0.507551729679108</v>
+        <v>0.507551670074463</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52473,7 +52473,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2004" t="n">
-        <v>0.50176215171814</v>
+        <v>0.501762092113495</v>
       </c>
       <c r="H2004" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2007" t="n">
-        <v>0.524920344352722</v>
+        <v>0.524920403957367</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G2010" t="n">
-        <v>0.503691971302032</v>
+        <v>0.503692030906677</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52655,7 +52655,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2011" t="n">
-        <v>0.521060705184937</v>
+        <v>0.521060645580292</v>
       </c>
       <c r="H2011" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G2012" t="n">
-        <v>0.519130766391754</v>
+        <v>0.519130825996399</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52707,7 +52707,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2013" t="n">
-        <v>0.517200946807861</v>
+        <v>0.517201006412506</v>
       </c>
       <c r="H2013" t="s">
         <v>8</v>
@@ -52759,7 +52759,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2015" t="n">
-        <v>0.50176215171814</v>
+        <v>0.501762092113495</v>
       </c>
       <c r="H2015" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2016" t="n">
-        <v>0.517200946807861</v>
+        <v>0.517201006412506</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2017" t="n">
-        <v>0.517200946807861</v>
+        <v>0.517201006412506</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2018" t="n">
-        <v>0.509481549263</v>
+        <v>0.509481489658356</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2019" t="n">
-        <v>0.509481549263</v>
+        <v>0.509481489658356</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G2022" t="n">
-        <v>0.503691971302032</v>
+        <v>0.503692030906677</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G2023" t="n">
-        <v>0.497902363538742</v>
+        <v>0.497902393341064</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -52993,7 +52993,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2024" t="n">
-        <v>0.507551729679108</v>
+        <v>0.507551670074463</v>
       </c>
       <c r="H2024" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2025" t="n">
-        <v>0.509481549263</v>
+        <v>0.509481489658356</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2026" t="n">
-        <v>0.509481549263</v>
+        <v>0.509481489658356</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53097,7 +53097,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G2028" t="n">
-        <v>0.497902363538742</v>
+        <v>0.497902393341064</v>
       </c>
       <c r="H2028" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G2029" t="n">
-        <v>0.497902363538742</v>
+        <v>0.497902393341064</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G2030" t="n">
-        <v>0.49983224272728</v>
+        <v>0.499832302331924</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2031" t="n">
-        <v>0.495972573757172</v>
+        <v>0.495972543954849</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G2032" t="n">
-        <v>0.497902363538742</v>
+        <v>0.497902393341064</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2033" t="n">
-        <v>0.490183025598526</v>
+        <v>0.490182965993881</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G2034" t="n">
-        <v>0.497902363538742</v>
+        <v>0.497902393341064</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G2035" t="n">
-        <v>0.497902363538742</v>
+        <v>0.497902393341064</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2036" t="n">
-        <v>0.492112785577774</v>
+        <v>0.492112815380096</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G2037" t="n">
-        <v>0.497902363538742</v>
+        <v>0.497902393341064</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2038" t="n">
-        <v>0.488253116607666</v>
+        <v>0.488253146409988</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2039" t="n">
-        <v>0.495972573757172</v>
+        <v>0.495972543954849</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2040" t="n">
-        <v>0.492112785577774</v>
+        <v>0.492112815380096</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2041" t="n">
-        <v>0.492112785577774</v>
+        <v>0.492112815380096</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2042" t="n">
-        <v>0.492112785577774</v>
+        <v>0.492112815380096</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G2043" t="n">
-        <v>0.497902363538742</v>
+        <v>0.497902393341064</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53513,7 +53513,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2044" t="n">
-        <v>0.495972573757172</v>
+        <v>0.495972543954849</v>
       </c>
       <c r="H2044" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2045" t="n">
-        <v>0.484393388032913</v>
+        <v>0.484393417835236</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>0.5</v>
       </c>
       <c r="G2046" t="n">
-        <v>0.482463538646698</v>
+        <v>0.48246356844902</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53591,7 +53591,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2047" t="n">
-        <v>0.490183025598526</v>
+        <v>0.490182965993881</v>
       </c>
       <c r="H2047" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2048" t="n">
-        <v>0.490183025598526</v>
+        <v>0.490182965993881</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2049" t="n">
-        <v>0.492112785577774</v>
+        <v>0.492112815380096</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2050" t="n">
-        <v>0.492112785577774</v>
+        <v>0.492112815380096</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2051" t="n">
-        <v>0.492112785577774</v>
+        <v>0.492112815380096</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>0.5</v>
       </c>
       <c r="G2052" t="n">
-        <v>0.482463538646698</v>
+        <v>0.48246356844902</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2053" t="n">
-        <v>0.467989653348923</v>
+        <v>0.467989683151245</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G2054" t="n">
-        <v>0.470884442329407</v>
+        <v>0.470884472131729</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G2055" t="n">
-        <v>0.470884442329407</v>
+        <v>0.470884472131729</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2056" t="n">
-        <v>0.460270255804062</v>
+        <v>0.46027022600174</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53851,7 +53851,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2057" t="n">
-        <v>0.464129984378815</v>
+        <v>0.46412992477417</v>
       </c>
       <c r="H2057" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2058" t="n">
-        <v>0.460270255804062</v>
+        <v>0.46027022600174</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2060" t="n">
-        <v>0.460270255804062</v>
+        <v>0.46027022600174</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G2061" t="n">
-        <v>0.470884442329407</v>
+        <v>0.470884472131729</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -54007,7 +54007,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G2063" t="n">
-        <v>0.466059803962708</v>
+        <v>0.46605983376503</v>
       </c>
       <c r="H2063" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G2064" t="n">
-        <v>0.466059803962708</v>
+        <v>0.46605983376503</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54059,7 +54059,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2065" t="n">
-        <v>0.467989653348923</v>
+        <v>0.467989683151245</v>
       </c>
       <c r="H2065" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2066" t="n">
-        <v>0.467989653348923</v>
+        <v>0.467989683151245</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54111,7 +54111,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2067" t="n">
-        <v>0.467989653348923</v>
+        <v>0.467989683151245</v>
       </c>
       <c r="H2067" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2068" t="n">
-        <v>0.467989653348923</v>
+        <v>0.467989683151245</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2073" t="n">
-        <v>0.460270255804062</v>
+        <v>0.46027022600174</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2074" t="n">
-        <v>0.460270255804062</v>
+        <v>0.46027022600174</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G2076" t="n">
-        <v>0.462200075387955</v>
+        <v>0.462200105190277</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2077" t="n">
-        <v>0.450620979070663</v>
+        <v>0.450620949268341</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G2080" t="n">
-        <v>0.459305316209793</v>
+        <v>0.459305346012115</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2081" t="n">
-        <v>0.443866521120071</v>
+        <v>0.443866461515427</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G2083" t="n">
-        <v>0.452550828456879</v>
+        <v>0.452550858259201</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2084" t="n">
-        <v>0.434217214584351</v>
+        <v>0.434217184782028</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2088" t="n">
-        <v>0.39465519785881</v>
+        <v>0.394655227661133</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2092" t="n">
-        <v>0.376321583986282</v>
+        <v>0.37632155418396</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2102" t="n">
-        <v>0.38211116194725</v>
+        <v>0.382111132144928</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2105" t="n">
-        <v>0.38211116194725</v>
+        <v>0.382111132144928</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55125,7 +55125,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G2106" t="n">
-        <v>0.360882729291916</v>
+        <v>0.360882759094238</v>
       </c>
       <c r="H2106" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G2109" t="n">
-        <v>0.364742428064346</v>
+        <v>0.364742457866669</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2110" t="n">
-        <v>0.38018125295639</v>
+        <v>0.380181282758713</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55281,7 +55281,7 @@
         <v>0.398000001907349</v>
       </c>
       <c r="G2112" t="n">
-        <v>0.384040981531143</v>
+        <v>0.384041011333466</v>
       </c>
       <c r="H2112" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2113" t="n">
-        <v>0.376321583986282</v>
+        <v>0.37632155418396</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>0.375</v>
       </c>
       <c r="G2115" t="n">
-        <v>0.361847698688507</v>
+        <v>0.361847668886185</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G2117" t="n">
-        <v>0.356058090925217</v>
+        <v>0.356058120727539</v>
       </c>
       <c r="H2117" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2120" t="n">
-        <v>0.373426795005798</v>
+        <v>0.373426765203476</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2121" t="n">
-        <v>0.434217214584351</v>
+        <v>0.434217184782028</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2122" t="n">
-        <v>0.424567967653275</v>
+        <v>0.424567937850952</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2123" t="n">
-        <v>0.416848510503769</v>
+        <v>0.416848540306091</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2127" t="n">
-        <v>0.405269414186478</v>
+        <v>0.405269354581833</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55827,7 +55827,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2133" t="n">
-        <v>0.381146252155304</v>
+        <v>0.381146222352982</v>
       </c>
       <c r="H2133" t="s">
         <v>8</v>
@@ -55879,7 +55879,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2135" t="n">
-        <v>0.39465519785881</v>
+        <v>0.394655227661133</v>
       </c>
       <c r="H2135" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2141" t="n">
-        <v>0.39465519785881</v>
+        <v>0.394655227661133</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56061,7 +56061,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2142" t="n">
-        <v>0.39465519785881</v>
+        <v>0.394655227661133</v>
       </c>
       <c r="H2142" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2154" t="n">
-        <v>0.414918690919876</v>
+        <v>0.414918661117554</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56399,7 +56399,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2155" t="n">
-        <v>0.409129083156586</v>
+        <v>0.409129112958908</v>
       </c>
       <c r="H2155" t="s">
         <v>8</v>
@@ -56711,7 +56711,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2167" t="n">
-        <v>0.41202387213707</v>
+        <v>0.412023842334747</v>
       </c>
       <c r="H2167" t="s">
         <v>8</v>
@@ -56737,7 +56737,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2168" t="n">
-        <v>0.409129083156586</v>
+        <v>0.409129112958908</v>
       </c>
       <c r="H2168" t="s">
         <v>8</v>
@@ -56763,7 +56763,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2169" t="n">
-        <v>0.408164173364639</v>
+        <v>0.408164203166962</v>
       </c>
       <c r="H2169" t="s">
         <v>8</v>
@@ -56971,7 +56971,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2177" t="n">
-        <v>0.396585077047348</v>
+        <v>0.396585047245026</v>
       </c>
       <c r="H2177" t="s">
         <v>8</v>
@@ -56997,7 +56997,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2178" t="n">
-        <v>0.399024069309235</v>
+        <v>0.399024099111557</v>
       </c>
       <c r="H2178" t="s">
         <v>8</v>
@@ -57127,7 +57127,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2183" t="n">
-        <v>0.403902143239975</v>
+        <v>0.403902113437653</v>
       </c>
       <c r="H2183" t="s">
         <v>8</v>
@@ -57179,7 +57179,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2185" t="n">
-        <v>0.403902143239975</v>
+        <v>0.403902113437653</v>
       </c>
       <c r="H2185" t="s">
         <v>8</v>
@@ -57387,7 +57387,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G2193" t="n">
-        <v>0.376585066318512</v>
+        <v>0.376585096120834</v>
       </c>
       <c r="H2193" t="s">
         <v>8</v>
@@ -57543,7 +57543,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2199" t="n">
-        <v>0.380487501621246</v>
+        <v>0.380487471818924</v>
       </c>
       <c r="H2199" t="s">
         <v>8</v>
@@ -57725,7 +57725,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G2206" t="n">
-        <v>0.378536313772202</v>
+        <v>0.378536283969879</v>
       </c>
       <c r="H2206" t="s">
         <v>8</v>
@@ -57751,7 +57751,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G2207" t="n">
-        <v>0.378536313772202</v>
+        <v>0.378536283969879</v>
       </c>
       <c r="H2207" t="s">
         <v>8</v>
@@ -57803,7 +57803,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2209" t="n">
-        <v>0.380487501621246</v>
+        <v>0.380487471818924</v>
       </c>
       <c r="H2209" t="s">
         <v>8</v>
@@ -57959,7 +57959,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2215" t="n">
-        <v>0.377560675144196</v>
+        <v>0.377560645341873</v>
       </c>
       <c r="H2215" t="s">
         <v>8</v>
@@ -57985,7 +57985,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G2216" t="n">
-        <v>0.376585066318512</v>
+        <v>0.376585096120834</v>
       </c>
       <c r="H2216" t="s">
         <v>8</v>
@@ -58089,7 +58089,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2220" t="n">
-        <v>0.377560675144196</v>
+        <v>0.377560645341873</v>
       </c>
       <c r="H2220" t="s">
         <v>8</v>
@@ -58115,7 +58115,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G2221" t="n">
-        <v>0.376585066318512</v>
+        <v>0.376585096120834</v>
       </c>
       <c r="H2221" t="s">
         <v>8</v>
@@ -58271,7 +58271,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2227" t="n">
-        <v>0.418536216020584</v>
+        <v>0.418536245822906</v>
       </c>
       <c r="H2227" t="s">
         <v>8</v>
@@ -58401,7 +58401,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2232" t="n">
-        <v>0.396097213029861</v>
+        <v>0.396097242832184</v>
       </c>
       <c r="H2232" t="s">
         <v>8</v>
@@ -58479,7 +58479,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2235" t="n">
-        <v>0.399024069309235</v>
+        <v>0.399024099111557</v>
       </c>
       <c r="H2235" t="s">
         <v>8</v>
@@ -58505,7 +58505,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2236" t="n">
-        <v>0.400975316762924</v>
+        <v>0.400975286960602</v>
       </c>
       <c r="H2236" t="s">
         <v>8</v>
@@ -58609,7 +58609,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2240" t="n">
-        <v>0.400975316762924</v>
+        <v>0.400975286960602</v>
       </c>
       <c r="H2240" t="s">
         <v>8</v>
@@ -58661,7 +58661,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2242" t="n">
-        <v>0.399024069309235</v>
+        <v>0.399024099111557</v>
       </c>
       <c r="H2242" t="s">
         <v>8</v>
@@ -58765,7 +58765,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2246" t="n">
-        <v>0.384389907121658</v>
+        <v>0.384389936923981</v>
       </c>
       <c r="H2246" t="s">
         <v>8</v>
@@ -58869,7 +58869,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G2250" t="n">
-        <v>0.376585066318512</v>
+        <v>0.376585096120834</v>
       </c>
       <c r="H2250" t="s">
         <v>8</v>
@@ -58895,7 +58895,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2251" t="n">
-        <v>0.380487501621246</v>
+        <v>0.380487471818924</v>
       </c>
       <c r="H2251" t="s">
         <v>8</v>
@@ -58921,7 +58921,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2252" t="n">
-        <v>0.380487501621246</v>
+        <v>0.380487471818924</v>
       </c>
       <c r="H2252" t="s">
         <v>8</v>
@@ -58947,7 +58947,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2253" t="n">
-        <v>0.396097213029861</v>
+        <v>0.396097242832184</v>
       </c>
       <c r="H2253" t="s">
         <v>8</v>
@@ -59025,7 +59025,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2256" t="n">
-        <v>0.380487501621246</v>
+        <v>0.380487471818924</v>
       </c>
       <c r="H2256" t="s">
         <v>8</v>
@@ -59233,7 +59233,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2264" t="n">
-        <v>0.396097213029861</v>
+        <v>0.396097242832184</v>
       </c>
       <c r="H2264" t="s">
         <v>8</v>
@@ -59285,7 +59285,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2266" t="n">
-        <v>0.384389907121658</v>
+        <v>0.384389936923981</v>
       </c>
       <c r="H2266" t="s">
         <v>8</v>
@@ -59363,7 +59363,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G2269" t="n">
-        <v>0.378536313772202</v>
+        <v>0.378536283969879</v>
       </c>
       <c r="H2269" t="s">
         <v>8</v>
@@ -59597,7 +59597,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2278" t="n">
-        <v>0.418536216020584</v>
+        <v>0.418536245822906</v>
       </c>
       <c r="H2278" t="s">
         <v>8</v>
@@ -59649,7 +59649,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G2280" t="n">
-        <v>0.478048384189606</v>
+        <v>0.478048413991928</v>
       </c>
       <c r="H2280" t="s">
         <v>8</v>
@@ -59753,7 +59753,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G2284" t="n">
-        <v>0.483902037143707</v>
+        <v>0.48390206694603</v>
       </c>
       <c r="H2284" t="s">
         <v>8</v>
@@ -59779,7 +59779,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2285" t="n">
-        <v>0.469267934560776</v>
+        <v>0.469267904758453</v>
       </c>
       <c r="H2285" t="s">
         <v>8</v>
@@ -59805,7 +59805,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G2286" t="n">
-        <v>0.478048384189606</v>
+        <v>0.478048413991928</v>
       </c>
       <c r="H2286" t="s">
         <v>8</v>
@@ -60013,7 +60013,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G2294" t="n">
-        <v>0.467316687107086</v>
+        <v>0.467316716909409</v>
       </c>
       <c r="H2294" t="s">
         <v>8</v>
@@ -60065,7 +60065,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G2296" t="n">
-        <v>0.463414281606674</v>
+        <v>0.463414251804352</v>
       </c>
       <c r="H2296" t="s">
         <v>8</v>
@@ -60143,7 +60143,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2299" t="n">
-        <v>0.439024031162262</v>
+        <v>0.43902400135994</v>
       </c>
       <c r="H2299" t="s">
         <v>8</v>
@@ -60325,7 +60325,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2306" t="n">
-        <v>0.44878014922142</v>
+        <v>0.448780119419098</v>
       </c>
       <c r="H2306" t="s">
         <v>8</v>
@@ -60507,7 +60507,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2313" t="n">
-        <v>0.493658125400543</v>
+        <v>0.493658155202866</v>
       </c>
       <c r="H2313" t="s">
         <v>8</v>
@@ -60533,7 +60533,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2314" t="n">
-        <v>0.491706937551498</v>
+        <v>0.491706907749176</v>
       </c>
       <c r="H2314" t="s">
         <v>8</v>
@@ -60559,7 +60559,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2315" t="n">
-        <v>0.491706937551498</v>
+        <v>0.491706907749176</v>
       </c>
       <c r="H2315" t="s">
         <v>8</v>
@@ -60611,7 +60611,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2317" t="n">
-        <v>0.495609402656555</v>
+        <v>0.49560934305191</v>
       </c>
       <c r="H2317" t="s">
         <v>8</v>
@@ -60689,7 +60689,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2320" t="n">
-        <v>0.51317036151886</v>
+        <v>0.513170301914215</v>
       </c>
       <c r="H2320" t="s">
         <v>8</v>
@@ -60715,7 +60715,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2321" t="n">
-        <v>0.581462919712067</v>
+        <v>0.581462979316711</v>
       </c>
       <c r="H2321" t="s">
         <v>8</v>
@@ -60767,7 +60767,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2323" t="n">
-        <v>0.72780430316925</v>
+        <v>0.727804243564606</v>
       </c>
       <c r="H2323" t="s">
         <v>8</v>
@@ -60845,7 +60845,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2326" t="n">
-        <v>0.682926297187805</v>
+        <v>0.68292623758316</v>
       </c>
       <c r="H2326" t="s">
         <v>8</v>
@@ -61053,7 +61053,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G2334" t="n">
-        <v>0.647804319858551</v>
+        <v>0.647804379463196</v>
       </c>
       <c r="H2334" t="s">
         <v>8</v>
@@ -61079,7 +61079,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2335" t="n">
-        <v>0.669267773628235</v>
+        <v>0.66926771402359</v>
       </c>
       <c r="H2335" t="s">
         <v>8</v>
@@ -61209,7 +61209,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G2340" t="n">
-        <v>0.710243344306946</v>
+        <v>0.710243284702301</v>
       </c>
       <c r="H2340" t="s">
         <v>8</v>
@@ -61235,7 +61235,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G2341" t="n">
-        <v>0.710243344306946</v>
+        <v>0.710243284702301</v>
       </c>
       <c r="H2341" t="s">
         <v>8</v>
@@ -61261,7 +61261,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G2342" t="n">
-        <v>0.706340849399567</v>
+        <v>0.706340909004211</v>
       </c>
       <c r="H2342" t="s">
         <v>8</v>
@@ -61287,7 +61287,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2343" t="n">
-        <v>0.682926297187805</v>
+        <v>0.68292623758316</v>
       </c>
       <c r="H2343" t="s">
         <v>8</v>
@@ -61339,7 +61339,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2345" t="n">
-        <v>0.682926297187805</v>
+        <v>0.68292623758316</v>
       </c>
       <c r="H2345" t="s">
         <v>8</v>
@@ -61391,7 +61391,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G2347" t="n">
-        <v>0.688779950141907</v>
+        <v>0.688779890537262</v>
       </c>
       <c r="H2347" t="s">
         <v>8</v>
@@ -61495,7 +61495,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2351" t="n">
-        <v>0.675121366977692</v>
+        <v>0.675121426582336</v>
       </c>
       <c r="H2351" t="s">
         <v>8</v>
@@ -61521,7 +61521,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2352" t="n">
-        <v>0.571706891059875</v>
+        <v>0.571706831455231</v>
       </c>
       <c r="H2352" t="s">
         <v>8</v>
@@ -61547,7 +61547,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2353" t="n">
-        <v>0.57560932636261</v>
+        <v>0.575609266757965</v>
       </c>
       <c r="H2353" t="s">
         <v>8</v>
@@ -61599,7 +61599,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2355" t="n">
-        <v>0.536584913730621</v>
+        <v>0.536584973335266</v>
       </c>
       <c r="H2355" t="s">
         <v>8</v>
@@ -61781,7 +61781,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2362" t="n">
-        <v>0.57560932636261</v>
+        <v>0.575609266757965</v>
       </c>
       <c r="H2362" t="s">
         <v>8</v>
@@ -61885,7 +61885,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2366" t="n">
-        <v>0.675121366977692</v>
+        <v>0.675121426582336</v>
       </c>
       <c r="H2366" t="s">
         <v>8</v>
@@ -61911,7 +61911,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2367" t="n">
-        <v>0.669267773628235</v>
+        <v>0.66926771402359</v>
       </c>
       <c r="H2367" t="s">
         <v>8</v>
@@ -61937,7 +61937,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2368" t="n">
-        <v>0.663414120674133</v>
+        <v>0.663414061069489</v>
       </c>
       <c r="H2368" t="s">
         <v>8</v>
@@ -62015,7 +62015,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2371" t="n">
-        <v>0.63804829120636</v>
+        <v>0.638048231601715</v>
       </c>
       <c r="H2371" t="s">
         <v>8</v>
@@ -62067,7 +62067,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2373" t="n">
-        <v>0.65560919046402</v>
+        <v>0.655609250068665</v>
       </c>
       <c r="H2373" t="s">
         <v>8</v>
@@ -62093,7 +62093,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2374" t="n">
-        <v>0.616584897041321</v>
+        <v>0.616584956645966</v>
       </c>
       <c r="H2374" t="s">
         <v>8</v>
@@ -62145,7 +62145,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2376" t="n">
-        <v>0.616584897041321</v>
+        <v>0.616584956645966</v>
       </c>
       <c r="H2376" t="s">
         <v>8</v>
@@ -62275,7 +62275,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2381" t="n">
-        <v>0.616584897041321</v>
+        <v>0.616584956645966</v>
       </c>
       <c r="H2381" t="s">
         <v>8</v>
@@ -62327,7 +62327,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2383" t="n">
-        <v>0.616584897041321</v>
+        <v>0.616584956645966</v>
       </c>
       <c r="H2383" t="s">
         <v>8</v>
@@ -62587,7 +62587,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2393" t="n">
-        <v>0.663414120674133</v>
+        <v>0.663414061069489</v>
       </c>
       <c r="H2393" t="s">
         <v>8</v>
@@ -62613,7 +62613,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2394" t="n">
-        <v>0.673170149326324</v>
+        <v>0.673170208930969</v>
       </c>
       <c r="H2394" t="s">
         <v>8</v>
@@ -62665,7 +62665,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2396" t="n">
-        <v>0.669267773628235</v>
+        <v>0.66926771402359</v>
       </c>
       <c r="H2396" t="s">
         <v>8</v>
@@ -62717,7 +62717,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2398" t="n">
-        <v>0.675121366977692</v>
+        <v>0.675121426582336</v>
       </c>
       <c r="H2398" t="s">
         <v>8</v>
@@ -62873,7 +62873,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2404" t="n">
-        <v>0.663414120674133</v>
+        <v>0.663414061069489</v>
       </c>
       <c r="H2404" t="s">
         <v>8</v>
@@ -62951,7 +62951,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G2407" t="n">
-        <v>0.647804319858551</v>
+        <v>0.647804379463196</v>
       </c>
       <c r="H2407" t="s">
         <v>8</v>
@@ -63003,7 +63003,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2409" t="n">
-        <v>0.628292143344879</v>
+        <v>0.628292202949524</v>
       </c>
       <c r="H2409" t="s">
         <v>8</v>
@@ -63029,7 +63029,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2410" t="n">
-        <v>0.63804829120636</v>
+        <v>0.638048231601715</v>
       </c>
       <c r="H2410" t="s">
         <v>8</v>
@@ -63055,7 +63055,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2411" t="n">
-        <v>0.63804829120636</v>
+        <v>0.638048231601715</v>
       </c>
       <c r="H2411" t="s">
         <v>8</v>
@@ -63107,7 +63107,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G2413" t="n">
-        <v>0.647804319858551</v>
+        <v>0.647804379463196</v>
       </c>
       <c r="H2413" t="s">
         <v>8</v>
@@ -63133,7 +63133,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2414" t="n">
-        <v>0.628292143344879</v>
+        <v>0.628292202949524</v>
       </c>
       <c r="H2414" t="s">
         <v>8</v>
@@ -63289,7 +63289,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2420" t="n">
-        <v>0.620487332344055</v>
+        <v>0.62048727273941</v>
       </c>
       <c r="H2420" t="s">
         <v>8</v>
@@ -63341,7 +63341,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2422" t="n">
-        <v>0.628292143344879</v>
+        <v>0.628292202949524</v>
       </c>
       <c r="H2422" t="s">
         <v>8</v>
@@ -63367,7 +63367,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G2423" t="n">
-        <v>0.618536114692688</v>
+        <v>0.618536055088043</v>
       </c>
       <c r="H2423" t="s">
         <v>8</v>
@@ -63445,7 +63445,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2426" t="n">
-        <v>0.628292143344879</v>
+        <v>0.628292202949524</v>
       </c>
       <c r="H2426" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>1.22500002384186</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>152316</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -499,7 +499,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G5" t="n">
-        <v>1.46544909477234</v>
+        <v>1.46544921398163</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G8" t="n">
-        <v>1.49205923080444</v>
+        <v>1.49205899238586</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.557000041008</v>
       </c>
       <c r="G9" t="n">
-        <v>1.47970449924469</v>
+        <v>1.4797043800354</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>1.22595930099487</v>
+        <v>1.22595942020416</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1.375</v>
       </c>
       <c r="G21" t="n">
-        <v>1.30673968791962</v>
+        <v>1.30673956871033</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G24" t="n">
-        <v>1.33049845695496</v>
+        <v>1.33049857616425</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G25" t="n">
-        <v>1.28298079967499</v>
+        <v>1.2829806804657</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G26" t="n">
-        <v>1.25447010993958</v>
+        <v>1.25446999073029</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G28" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G30" t="n">
-        <v>1.13662576675415</v>
+        <v>1.13662588596344</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>1.16100001335144</v>
       </c>
       <c r="G31" t="n">
-        <v>1.10336351394653</v>
+        <v>1.10336339473724</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G32" t="n">
-        <v>1.22595930099487</v>
+        <v>1.22595942020416</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.375</v>
       </c>
       <c r="G33" t="n">
-        <v>1.30673968791962</v>
+        <v>1.30673956871033</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.35899996757507</v>
       </c>
       <c r="G35" t="n">
-        <v>1.29153406620026</v>
+        <v>1.29153394699097</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G39" t="n">
-        <v>1.31719362735748</v>
+        <v>1.31719350814819</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G42" t="n">
-        <v>1.29723620414734</v>
+        <v>1.29723608493805</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G44" t="n">
-        <v>1.32289552688599</v>
+        <v>1.32289564609528</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>1.28773248195648</v>
+        <v>1.28773260116577</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G51" t="n">
-        <v>1.33049845695496</v>
+        <v>1.33049857616425</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G52" t="n">
-        <v>1.32194542884827</v>
+        <v>1.32194530963898</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G53" t="n">
-        <v>1.32194542884827</v>
+        <v>1.32194530963898</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G58" t="n">
-        <v>1.26967561244965</v>
+        <v>1.26967573165894</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G64" t="n">
-        <v>1.24116492271423</v>
+        <v>1.24116516113281</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G65" t="n">
-        <v>1.26017224788666</v>
+        <v>1.26017212867737</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G67" t="n">
-        <v>1.22786021232605</v>
+        <v>1.22786009311676</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G68" t="n">
-        <v>1.30578935146332</v>
+        <v>1.30578923225403</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G69" t="n">
-        <v>1.30578935146332</v>
+        <v>1.30578923225403</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G70" t="n">
-        <v>1.24781763553619</v>
+        <v>1.2478175163269</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G71" t="n">
-        <v>1.24306583404541</v>
+        <v>1.24306571483612</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G72" t="n">
-        <v>1.30483889579773</v>
+        <v>1.30483877658844</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G73" t="n">
-        <v>1.29058349132538</v>
+        <v>1.29058372974396</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G76" t="n">
-        <v>1.26967561244965</v>
+        <v>1.26967573165894</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27917921543121</v>
+        <v>1.2791793346405</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G81" t="n">
-        <v>1.27917921543121</v>
+        <v>1.2791793346405</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G87" t="n">
-        <v>1.2848813533783</v>
+        <v>1.28488147258759</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G89" t="n">
-        <v>1.30483889579773</v>
+        <v>1.30483877658844</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G93" t="n">
-        <v>1.23546278476715</v>
+        <v>1.23546290397644</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G94" t="n">
-        <v>1.25447010993958</v>
+        <v>1.25446999073029</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>1.25</v>
       </c>
       <c r="G100" t="n">
-        <v>1.18794500827789</v>
+        <v>1.18794512748718</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G103" t="n">
-        <v>1.16133511066437</v>
+        <v>1.16133522987366</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>1.22099995613098</v>
       </c>
       <c r="G104" t="n">
-        <v>1.16038477420807</v>
+        <v>1.16038465499878</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G106" t="n">
-        <v>1.1784416437149</v>
+        <v>1.17844140529633</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G111" t="n">
-        <v>1.1480301618576</v>
+        <v>1.14803004264832</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G112" t="n">
-        <v>1.1822429895401</v>
+        <v>1.18224287033081</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G118" t="n">
-        <v>1.17273938655853</v>
+        <v>1.17273926734924</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G123" t="n">
-        <v>1.13662576675415</v>
+        <v>1.13662588596344</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>1.09599995613098</v>
       </c>
       <c r="G125" t="n">
-        <v>1.04159021377563</v>
+        <v>1.04159033298492</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G126" t="n">
-        <v>0.975065410137177</v>
+        <v>0.975065290927887</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G127" t="n">
-        <v>1.00737738609314</v>
+        <v>1.00737750530243</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G130" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G132" t="n">
-        <v>0.955107867717743</v>
+        <v>0.955107927322388</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G133" t="n">
-        <v>0.995022833347321</v>
+        <v>0.99502295255661</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G134" t="n">
-        <v>1.02068257331848</v>
+        <v>1.02068245410919</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G135" t="n">
-        <v>1.00547671318054</v>
+        <v>1.00547683238983</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>1.05200004577637</v>
       </c>
       <c r="G136" t="n">
-        <v>0.999774694442749</v>
+        <v>0.999774754047394</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>1.02699995040894</v>
       </c>
       <c r="G137" t="n">
-        <v>0.976015627384186</v>
+        <v>0.976015567779541</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G138" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G139" t="n">
-        <v>0.996923446655273</v>
+        <v>0.996923565864563</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G140" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G141" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G145" t="n">
-        <v>0.975065410137177</v>
+        <v>0.975065290927887</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G146" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G147" t="n">
-        <v>0.995022833347321</v>
+        <v>0.99502295255661</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G149" t="n">
-        <v>1.00927829742432</v>
+        <v>1.00927817821503</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G151" t="n">
-        <v>0.987420082092285</v>
+        <v>0.987419903278351</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G152" t="n">
-        <v>0.986469566822052</v>
+        <v>0.986469626426697</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G153" t="n">
-        <v>0.986469566822052</v>
+        <v>0.986469626426697</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>1.00737738609314</v>
+        <v>1.00737750530243</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G155" t="n">
-        <v>1.00737738609314</v>
+        <v>1.00737750530243</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G161" t="n">
-        <v>0.980767369270325</v>
+        <v>0.980767428874969</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.03299999237061</v>
       </c>
       <c r="G162" t="n">
-        <v>0.981717824935913</v>
+        <v>0.981717765331268</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>1.02699995040894</v>
       </c>
       <c r="G163" t="n">
-        <v>0.976015627384186</v>
+        <v>0.976015567779541</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G164" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G165" t="n">
-        <v>0.963661193847656</v>
+        <v>0.963661134243011</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G166" t="n">
-        <v>0.967462539672852</v>
+        <v>0.967462480068207</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G169" t="n">
-        <v>0.986469566822052</v>
+        <v>0.986469626426697</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G171" t="n">
-        <v>0.995022833347321</v>
+        <v>0.99502295255661</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G172" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G173" t="n">
-        <v>1.00547671318054</v>
+        <v>1.00547683238983</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G174" t="n">
-        <v>0.996923446655273</v>
+        <v>0.996923565864563</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G178" t="n">
-        <v>1.15183174610138</v>
+        <v>1.15183162689209</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G179" t="n">
-        <v>1.12427115440369</v>
+        <v>1.12427127361298</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G180" t="n">
-        <v>1.06820023059845</v>
+        <v>1.06820011138916</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.12100005149841</v>
       </c>
       <c r="G183" t="n">
-        <v>1.06534934043884</v>
+        <v>1.06534922122955</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G185" t="n">
-        <v>1.08910799026489</v>
+        <v>1.08910810947418</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G189" t="n">
-        <v>1.00072503089905</v>
+        <v>1.00072491168976</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G190" t="n">
-        <v>1.00262558460236</v>
+        <v>1.00262570381165</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G192" t="n">
-        <v>0.987420082092285</v>
+        <v>0.987419903278351</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G194" t="n">
-        <v>0.996923446655273</v>
+        <v>0.996923565864563</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.03299999237061</v>
       </c>
       <c r="G195" t="n">
-        <v>0.981717824935913</v>
+        <v>0.981717765331268</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G196" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G197" t="n">
-        <v>0.989320635795593</v>
+        <v>0.989320755004883</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.03299999237061</v>
       </c>
       <c r="G198" t="n">
-        <v>0.981717824935913</v>
+        <v>0.981717765331268</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G199" t="n">
-        <v>0.986469566822052</v>
+        <v>0.986469626426697</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G200" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568893909454</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G202" t="n">
-        <v>0.963661193847656</v>
+        <v>0.963661134243011</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G203" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568893909454</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G207" t="n">
-        <v>0.987420082092285</v>
+        <v>0.987419903278351</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>1.02699995040894</v>
       </c>
       <c r="G208" t="n">
-        <v>0.976015627384186</v>
+        <v>0.976015567779541</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>1.02699995040894</v>
       </c>
       <c r="G211" t="n">
-        <v>0.976015627384186</v>
+        <v>0.976015567779541</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G217" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G219" t="n">
-        <v>0.955107867717743</v>
+        <v>0.955107927322388</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G220" t="n">
-        <v>0.955107867717743</v>
+        <v>0.955107927322388</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G225" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G227" t="n">
-        <v>0.967462539672852</v>
+        <v>0.967462480068207</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G230" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568893909454</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G231" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568893909454</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>0.982500016689301</v>
       </c>
       <c r="G233" t="n">
-        <v>0.933724880218506</v>
+        <v>0.933724820613861</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G234" t="n">
-        <v>0.957958936691284</v>
+        <v>0.957958996295929</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G235" t="n">
-        <v>0.989320635795593</v>
+        <v>0.989320755004883</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G237" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1</v>
       </c>
       <c r="G240" t="n">
-        <v>0.950356125831604</v>
+        <v>0.950356066226959</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G242" t="n">
-        <v>1.00262558460236</v>
+        <v>1.00262570381165</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.03299999237061</v>
       </c>
       <c r="G243" t="n">
-        <v>0.981717824935913</v>
+        <v>0.981717765331268</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G244" t="n">
-        <v>0.980767369270325</v>
+        <v>0.980767428874969</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G245" t="n">
-        <v>0.975065410137177</v>
+        <v>0.975065290927887</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.00100004673004</v>
       </c>
       <c r="G246" t="n">
-        <v>0.951306521892548</v>
+        <v>0.951306462287903</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G247" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568893909454</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G248" t="n">
-        <v>0.987420082092285</v>
+        <v>0.987419903278351</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G249" t="n">
-        <v>0.982668220996857</v>
+        <v>0.982668340206146</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G251" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G252" t="n">
-        <v>0.963661193847656</v>
+        <v>0.963661134243011</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G256" t="n">
-        <v>1.016881108284</v>
+        <v>1.01688098907471</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G257" t="n">
-        <v>0.989320635795593</v>
+        <v>0.989320755004883</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G259" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568893909454</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G261" t="n">
-        <v>1.04254055023193</v>
+        <v>1.04254066944122</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G262" t="n">
-        <v>1.17654085159302</v>
+        <v>1.17654097080231</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>1.5</v>
       </c>
       <c r="G265" t="n">
-        <v>1.42553412914276</v>
+        <v>1.42553424835205</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G266" t="n">
-        <v>1.39227175712585</v>
+        <v>1.39227163791656</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G268" t="n">
-        <v>1.33049845695496</v>
+        <v>1.33049857616425</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G271" t="n">
-        <v>1.32289552688599</v>
+        <v>1.32289564609528</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G273" t="n">
-        <v>1.23071110248566</v>
+        <v>1.23071098327637</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G275" t="n">
-        <v>1.3837183713913</v>
+        <v>1.38371849060059</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G278" t="n">
-        <v>1.23546278476715</v>
+        <v>1.23546290397644</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>1.31099998950958</v>
       </c>
       <c r="G280" t="n">
-        <v>1.2459169626236</v>
+        <v>1.24591672420502</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G281" t="n">
-        <v>1.24781763553619</v>
+        <v>1.2478175163269</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G285" t="n">
-        <v>1.13947689533234</v>
+        <v>1.13947701454163</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G288" t="n">
-        <v>1.12142014503479</v>
+        <v>1.12142026424408</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G290" t="n">
-        <v>1.09671092033386</v>
+        <v>1.09671103954315</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>1.14100003242493</v>
       </c>
       <c r="G291" t="n">
-        <v>1.08435642719269</v>
+        <v>1.0843563079834</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G293" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>1.20695233345032</v>
+        <v>1.20695221424103</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G310" t="n">
-        <v>1.13662576675415</v>
+        <v>1.13662588596344</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G311" t="n">
-        <v>1.15183174610138</v>
+        <v>1.15183162689209</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G317" t="n">
-        <v>1.12522172927856</v>
+        <v>1.12522161006927</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G319" t="n">
-        <v>1.13472509384155</v>
+        <v>1.13472521305084</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G322" t="n">
-        <v>1.16323590278625</v>
+        <v>1.16323578357697</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G327" t="n">
-        <v>1.13472509384155</v>
+        <v>1.13472521305084</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G331" t="n">
-        <v>1.13472509384155</v>
+        <v>1.13472521305084</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G334" t="n">
-        <v>1.10621452331543</v>
+        <v>1.10621464252472</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G336" t="n">
-        <v>1.1166684627533</v>
+        <v>1.11666834354401</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G337" t="n">
-        <v>1.11571800708771</v>
+        <v>1.115718126297</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G342" t="n">
-        <v>1.12142014503479</v>
+        <v>1.12142026424408</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G343" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G344" t="n">
-        <v>1.10811519622803</v>
+        <v>1.10811507701874</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G345" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G346" t="n">
-        <v>1.08910799026489</v>
+        <v>1.08910810947418</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G348" t="n">
-        <v>1.11571800708771</v>
+        <v>1.115718126297</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G349" t="n">
-        <v>1.12522172927856</v>
+        <v>1.12522161006927</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G350" t="n">
-        <v>1.12142014503479</v>
+        <v>1.12142026424408</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G356" t="n">
-        <v>1.09385979175568</v>
+        <v>1.09386003017426</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G357" t="n">
-        <v>1.07010102272034</v>
+        <v>1.07010114192963</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G360" t="n">
-        <v>1.0491931438446</v>
+        <v>1.04919302463531</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G366" t="n">
-        <v>1.0491931438446</v>
+        <v>1.04919302463531</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.12100005149841</v>
       </c>
       <c r="G370" t="n">
-        <v>1.06534934043884</v>
+        <v>1.06534922122955</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.10099995136261</v>
       </c>
       <c r="G371" t="n">
-        <v>1.04634189605713</v>
+        <v>1.04634201526642</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G372" t="n">
-        <v>1.05109393596649</v>
+        <v>1.0510938167572</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G373" t="n">
-        <v>1.05109393596649</v>
+        <v>1.0510938167572</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G374" t="n">
-        <v>1.09385979175568</v>
+        <v>1.09386003017426</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>1.14100003242493</v>
       </c>
       <c r="G376" t="n">
-        <v>1.08435642719269</v>
+        <v>1.0843563079834</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G377" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G384" t="n">
-        <v>1.09290933609009</v>
+        <v>1.09290945529938</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G387" t="n">
-        <v>1.11001586914062</v>
+        <v>1.11001598834991</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G389" t="n">
-        <v>1.13947689533234</v>
+        <v>1.13947701454163</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G390" t="n">
-        <v>1.13947689533234</v>
+        <v>1.13947701454163</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>1.22899997234344</v>
       </c>
       <c r="G391" t="n">
-        <v>1.16798758506775</v>
+        <v>1.16798770427704</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G392" t="n">
-        <v>1.17464017868042</v>
+        <v>1.17464005947113</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G394" t="n">
-        <v>1.12427115440369</v>
+        <v>1.12427127361298</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G397" t="n">
-        <v>1.14898061752319</v>
+        <v>1.1489804983139</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G398" t="n">
-        <v>1.13947689533234</v>
+        <v>1.13947701454163</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G407" t="n">
-        <v>1.11571800708771</v>
+        <v>1.115718126297</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G409" t="n">
-        <v>1.1147677898407</v>
+        <v>1.11476767063141</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G412" t="n">
-        <v>1.11951947212219</v>
+        <v>1.1195193529129</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G413" t="n">
-        <v>1.1138174533844</v>
+        <v>1.11381733417511</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G414" t="n">
-        <v>1.10621452331543</v>
+        <v>1.10621464252472</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G415" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G416" t="n">
-        <v>1.09671092033386</v>
+        <v>1.09671103954315</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G418" t="n">
-        <v>1.1109664440155</v>
+        <v>1.11096620559692</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G419" t="n">
-        <v>1.10621452331543</v>
+        <v>1.10621464252472</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G420" t="n">
-        <v>1.11951947212219</v>
+        <v>1.1195193529129</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G421" t="n">
-        <v>1.14898061752319</v>
+        <v>1.1489804983139</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G424" t="n">
-        <v>1.16133511066437</v>
+        <v>1.16133522987366</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G429" t="n">
-        <v>1.12427115440369</v>
+        <v>1.12427127361298</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G431" t="n">
-        <v>1.13472509384155</v>
+        <v>1.13472521305084</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G434" t="n">
-        <v>1.12142014503479</v>
+        <v>1.12142026424408</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G435" t="n">
-        <v>1.12142014503479</v>
+        <v>1.12142026424408</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G436" t="n">
-        <v>1.1147677898407</v>
+        <v>1.11476767063141</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G437" t="n">
-        <v>1.12522172927856</v>
+        <v>1.12522161006927</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G438" t="n">
-        <v>1.12142014503479</v>
+        <v>1.12142026424408</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>1.12522172927856</v>
+        <v>1.12522161006927</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G440" t="n">
-        <v>1.11571800708771</v>
+        <v>1.115718126297</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G444" t="n">
-        <v>1.11001586914062</v>
+        <v>1.11001598834991</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G447" t="n">
-        <v>1.1860443353653</v>
+        <v>1.18604445457458</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G452" t="n">
-        <v>1.22025728225708</v>
+        <v>1.22025740146637</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G453" t="n">
-        <v>1.20505166053772</v>
+        <v>1.20505154132843</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>1.25</v>
       </c>
       <c r="G454" t="n">
-        <v>1.18794500827789</v>
+        <v>1.18794512748718</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G455" t="n">
-        <v>1.16133511066437</v>
+        <v>1.16133522987366</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G457" t="n">
-        <v>1.17273938655853</v>
+        <v>1.17273926734924</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>1.22099995613098</v>
       </c>
       <c r="G458" t="n">
-        <v>1.16038477420807</v>
+        <v>1.16038465499878</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G459" t="n">
-        <v>1.17654085159302</v>
+        <v>1.17654097080231</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G461" t="n">
-        <v>1.17464017868042</v>
+        <v>1.17464005947113</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>1.22099995613098</v>
       </c>
       <c r="G463" t="n">
-        <v>1.16038477420807</v>
+        <v>1.16038465499878</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G465" t="n">
-        <v>1.1784416437149</v>
+        <v>1.17844140529633</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G466" t="n">
-        <v>1.15468275547028</v>
+        <v>1.15468263626099</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G467" t="n">
-        <v>1.15468275547028</v>
+        <v>1.15468263626099</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G469" t="n">
-        <v>1.1784416437149</v>
+        <v>1.17844140529633</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G471" t="n">
-        <v>1.19364726543427</v>
+        <v>1.19364738464355</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G472" t="n">
-        <v>1.1860443353653</v>
+        <v>1.18604445457458</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>1.20695233345032</v>
+        <v>1.20695221424103</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G479" t="n">
-        <v>1.1147677898407</v>
+        <v>1.11476767063141</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G481" t="n">
-        <v>1.11951947212219</v>
+        <v>1.1195193529129</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G484" t="n">
-        <v>1.15563309192657</v>
+        <v>1.15563297271729</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G486" t="n">
-        <v>1.1138174533844</v>
+        <v>1.11381733417511</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G487" t="n">
-        <v>1.13472509384155</v>
+        <v>1.13472521305084</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G494" t="n">
-        <v>1.10621452331543</v>
+        <v>1.10621464252472</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G495" t="n">
-        <v>1.1147677898407</v>
+        <v>1.11476767063141</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G496" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G498" t="n">
-        <v>1.1109664440155</v>
+        <v>1.11096620559692</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G499" t="n">
-        <v>1.1109664440155</v>
+        <v>1.11096620559692</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G500" t="n">
-        <v>1.1109664440155</v>
+        <v>1.11096620559692</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G505" t="n">
-        <v>1.12142014503479</v>
+        <v>1.12142026424408</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G509" t="n">
-        <v>1.1109664440155</v>
+        <v>1.11096620559692</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G510" t="n">
-        <v>1.12427115440369</v>
+        <v>1.12427127361298</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G512" t="n">
-        <v>1.1166684627533</v>
+        <v>1.11666834354401</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G517" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G518" t="n">
-        <v>1.1166684627533</v>
+        <v>1.11666834354401</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G523" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G529" t="n">
-        <v>1.09290933609009</v>
+        <v>1.09290945529938</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G530" t="n">
-        <v>1.1166684627533</v>
+        <v>1.11666834354401</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G531" t="n">
-        <v>1.12142014503479</v>
+        <v>1.12142026424408</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G532" t="n">
-        <v>1.09290933609009</v>
+        <v>1.09290945529938</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G533" t="n">
-        <v>1.09290933609009</v>
+        <v>1.09290945529938</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G534" t="n">
-        <v>1.09290933609009</v>
+        <v>1.09290945529938</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>1.125</v>
       </c>
       <c r="G537" t="n">
-        <v>1.06915056705475</v>
+        <v>1.06915068626404</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>1.125</v>
       </c>
       <c r="G571" t="n">
-        <v>1.06915056705475</v>
+        <v>1.06915068626404</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G577" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G598" t="n">
-        <v>1.016881108284</v>
+        <v>1.01688098907471</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G607" t="n">
-        <v>1.00737738609314</v>
+        <v>1.00737750530243</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G610" t="n">
-        <v>1.0121294260025</v>
+        <v>1.01212930679321</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G614" t="n">
-        <v>0.931348979473114</v>
+        <v>0.931349039077759</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G616" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G617" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>0.950356125831604</v>
+        <v>0.950356066226959</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0.950356125831604</v>
+        <v>0.950356066226959</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G622" t="n">
-        <v>0.948455452919006</v>
+        <v>0.948455393314362</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>1</v>
       </c>
       <c r="G625" t="n">
-        <v>0.950356125831604</v>
+        <v>0.950356066226959</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G627" t="n">
-        <v>0.918044030666351</v>
+        <v>0.918043971061707</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G628" t="n">
-        <v>0.946554660797119</v>
+        <v>0.946554720401764</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G630" t="n">
-        <v>0.948455452919006</v>
+        <v>0.948455393314362</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G634" t="n">
-        <v>0.933249652385712</v>
+        <v>0.933249711990356</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G635" t="n">
-        <v>0.933249652385712</v>
+        <v>0.933249711990356</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G636" t="n">
-        <v>0.931348979473114</v>
+        <v>0.931349039077759</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G637" t="n">
-        <v>0.910441160202026</v>
+        <v>0.910441100597382</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G638" t="n">
-        <v>0.916143298149109</v>
+        <v>0.916143238544464</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G642" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G645" t="n">
-        <v>0.937051117420197</v>
+        <v>0.937051057815552</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G647" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G648" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G649" t="n">
-        <v>0.931348979473114</v>
+        <v>0.931349039077759</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G652" t="n">
-        <v>0.923746168613434</v>
+        <v>0.923746109008789</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G653" t="n">
-        <v>0.931348979473114</v>
+        <v>0.931349039077759</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G656" t="n">
-        <v>0.904739022254944</v>
+        <v>0.904738962650299</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G660" t="n">
-        <v>0.908540368080139</v>
+        <v>0.908540427684784</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G663" t="n">
-        <v>0.916143298149109</v>
+        <v>0.916143238544464</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G664" t="n">
-        <v>0.916143298149109</v>
+        <v>0.916143238544464</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G665" t="n">
-        <v>0.910441160202026</v>
+        <v>0.910441100597382</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G666" t="n">
-        <v>0.908540368080139</v>
+        <v>0.908540427684784</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G680" t="n">
-        <v>0.883831143379211</v>
+        <v>0.883831202983856</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G682" t="n">
-        <v>0.866724789142609</v>
+        <v>0.866724729537964</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G686" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753195762634</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G687" t="n">
-        <v>0.925646841526031</v>
+        <v>0.925646781921387</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>0.906639695167542</v>
+        <v>0.906639754772186</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G692" t="n">
-        <v>0.904739022254944</v>
+        <v>0.904738962650299</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G693" t="n">
-        <v>0.904739022254944</v>
+        <v>0.904738962650299</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G699" t="n">
-        <v>0.918044030666351</v>
+        <v>0.918043971061707</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G703" t="n">
-        <v>0.897136151790619</v>
+        <v>0.897136211395264</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G707" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G708" t="n">
-        <v>0.836313366889954</v>
+        <v>0.836313426494598</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G709" t="n">
-        <v>0.840114712715149</v>
+        <v>0.840114772319794</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G711" t="n">
-        <v>0.828710436820984</v>
+        <v>0.828710496425629</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G715" t="n">
-        <v>0.821107685565948</v>
+        <v>0.821107625961304</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G718" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G719" t="n">
-        <v>0.802100479602814</v>
+        <v>0.802100539207458</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G720" t="n">
-        <v>0.802100479602814</v>
+        <v>0.802100539207458</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G721" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G725" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G730" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G731" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G732" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G733" t="n">
-        <v>0.783093452453613</v>
+        <v>0.783093392848969</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G734" t="n">
-        <v>0.804001212120056</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G735" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G742" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G743" t="n">
-        <v>0.802100479602814</v>
+        <v>0.802100539207458</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G748" t="n">
-        <v>0.802100479602814</v>
+        <v>0.802100539207458</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G749" t="n">
-        <v>0.802100479602814</v>
+        <v>0.802100539207458</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G754" t="n">
-        <v>0.773589909076691</v>
+        <v>0.773589849472046</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G756" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G757" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G758" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G763" t="n">
-        <v>0.790696263313293</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>0.790696263313293</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G765" t="n">
-        <v>0.790696263313293</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G766" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G769" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G770" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G771" t="n">
-        <v>0.790696263313293</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G772" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G773" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G774" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G779" t="n">
-        <v>0.872426867485046</v>
+        <v>0.872426807880402</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G780" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G781" t="n">
-        <v>0.918044030666351</v>
+        <v>0.918043971061707</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G785" t="n">
-        <v>0.883831143379211</v>
+        <v>0.883831202983856</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G791" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G797" t="n">
-        <v>0.836313366889954</v>
+        <v>0.836313426494598</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G799" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G801" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G804" t="n">
-        <v>0.866724789142609</v>
+        <v>0.866724729537964</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G805" t="n">
-        <v>0.876228332519531</v>
+        <v>0.876228272914886</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>0.853419721126556</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G813" t="n">
-        <v>0.857221186161041</v>
+        <v>0.857221245765686</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G814" t="n">
-        <v>0.857221186161041</v>
+        <v>0.857221245765686</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G816" t="n">
-        <v>0.832511901855469</v>
+        <v>0.832511842250824</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G820" t="n">
-        <v>0.857221186161041</v>
+        <v>0.857221245765686</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G823" t="n">
-        <v>0.847717642784119</v>
+        <v>0.847717702388763</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G824" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G828" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G829" t="n">
-        <v>0.866724789142609</v>
+        <v>0.866724729537964</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G831" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G832" t="n">
-        <v>0.876228332519531</v>
+        <v>0.876228272914886</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G833" t="n">
-        <v>0.872426867485046</v>
+        <v>0.872426807880402</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G839" t="n">
-        <v>1.00737738609314</v>
+        <v>1.00737750530243</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G840" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G841" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1</v>
       </c>
       <c r="G842" t="n">
-        <v>0.950356125831604</v>
+        <v>0.950356066226959</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G843" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G844" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G846" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G848" t="n">
-        <v>0.96461147069931</v>
+        <v>0.964611351490021</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1</v>
       </c>
       <c r="G849" t="n">
-        <v>0.950356125831604</v>
+        <v>0.950356066226959</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G851" t="n">
-        <v>0.931348979473114</v>
+        <v>0.931349039077759</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G852" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753195762634</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G853" t="n">
-        <v>0.931348979473114</v>
+        <v>0.931349039077759</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G854" t="n">
-        <v>0.923746168613434</v>
+        <v>0.923746109008789</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G855" t="n">
-        <v>0.910441160202026</v>
+        <v>0.910441100597382</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G856" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>0.931348979473114</v>
+        <v>0.931349039077759</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G860" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G861" t="n">
-        <v>0.948455452919006</v>
+        <v>0.948455393314362</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G862" t="n">
-        <v>0.897136151790619</v>
+        <v>0.897136211395264</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1</v>
       </c>
       <c r="G863" t="n">
-        <v>0.950356125831604</v>
+        <v>0.950356066226959</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G865" t="n">
-        <v>0.883831143379211</v>
+        <v>0.883831202983856</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G866" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G878" t="n">
-        <v>0.881930410861969</v>
+        <v>0.881930470466614</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G885" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G886" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G891" t="n">
-        <v>0.857221186161041</v>
+        <v>0.857221245765686</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G892" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G896" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G897" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G901" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G902" t="n">
-        <v>0.853419721126556</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G903" t="n">
-        <v>0.836313366889954</v>
+        <v>0.836313426494598</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>0.853419721126556</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G906" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>0.853419721126556</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G910" t="n">
-        <v>0.840114712715149</v>
+        <v>0.840114772319794</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G912" t="n">
-        <v>0.847717642784119</v>
+        <v>0.847717702388763</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G913" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G914" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G915" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G923" t="n">
-        <v>0.840114712715149</v>
+        <v>0.840114772319794</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G925" t="n">
-        <v>0.883831143379211</v>
+        <v>0.883831202983856</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G927" t="n">
-        <v>0.908540368080139</v>
+        <v>0.908540427684784</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G931" t="n">
-        <v>0.937051117420197</v>
+        <v>0.937051057815552</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G932" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753195762634</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G933" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G934" t="n">
-        <v>0.955107867717743</v>
+        <v>0.955107927322388</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G935" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1</v>
       </c>
       <c r="G936" t="n">
-        <v>0.950356125831604</v>
+        <v>0.950356066226959</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G937" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753195762634</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G938" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G941" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G942" t="n">
-        <v>0.908540368080139</v>
+        <v>0.908540427684784</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G947" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G948" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G950" t="n">
-        <v>0.937051117420197</v>
+        <v>0.937051057815552</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1</v>
       </c>
       <c r="G951" t="n">
-        <v>0.950356125831604</v>
+        <v>0.950356066226959</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G952" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753195762634</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G954" t="n">
-        <v>0.910441160202026</v>
+        <v>0.910441100597382</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G955" t="n">
-        <v>0.918044030666351</v>
+        <v>0.918043971061707</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G956" t="n">
-        <v>0.916143298149109</v>
+        <v>0.916143238544464</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G957" t="n">
-        <v>0.906639695167542</v>
+        <v>0.906639754772186</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G961" t="n">
-        <v>0.883831143379211</v>
+        <v>0.883831202983856</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G962" t="n">
-        <v>0.897136151790619</v>
+        <v>0.897136211395264</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G964" t="n">
-        <v>0.897136151790619</v>
+        <v>0.897136211395264</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G966" t="n">
-        <v>0.897136151790619</v>
+        <v>0.897136211395264</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G975" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G976" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G977" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G978" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G979" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G980" t="n">
-        <v>0.955107867717743</v>
+        <v>0.955107927322388</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G982" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G984" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G985" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G986" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G987" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G991" t="n">
-        <v>0.931348979473114</v>
+        <v>0.931349039077759</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G993" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G994" t="n">
-        <v>0.96461147069931</v>
+        <v>0.964611351490021</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G995" t="n">
-        <v>0.96461147069931</v>
+        <v>0.964611351490021</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G997" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G998" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G999" t="n">
-        <v>0.96461147069931</v>
+        <v>0.964611351490021</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.0121294260025</v>
+        <v>1.01212930679321</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.016881108284</v>
+        <v>1.01688098907471</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.00737738609314</v>
+        <v>1.00737750530243</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.00262558460236</v>
+        <v>1.00262570381165</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.0121294260025</v>
+        <v>1.01212930679321</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1030" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.00262558460236</v>
+        <v>1.00262570381165</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.00737738609314</v>
+        <v>1.00737750530243</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.016881108284</v>
+        <v>1.01688098907471</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.00262558460236</v>
+        <v>1.00262570381165</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.937051117420197</v>
+        <v>0.937051057815552</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.925646841526031</v>
+        <v>0.925646781921387</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>0.973999977111816</v>
       </c>
       <c r="G1061" t="n">
-        <v>0.925646841526031</v>
+        <v>0.925646781921387</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.771689176559448</v>
+        <v>0.771689116954803</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.836313366889954</v>
+        <v>0.836313426494598</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.872426867485046</v>
+        <v>0.872426807880402</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.842015504837036</v>
+        <v>0.842015564441681</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.840114712715149</v>
+        <v>0.840114772319794</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.836313366889954</v>
+        <v>0.836313426494598</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.840114712715149</v>
+        <v>0.840114772319794</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.840114712715149</v>
+        <v>0.840114772319794</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.872426867485046</v>
+        <v>0.872426807880402</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.834412634372711</v>
+        <v>0.834412693977356</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.842015504837036</v>
+        <v>0.842015564441681</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.834412634372711</v>
+        <v>0.834412693977356</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.804001212120056</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.804001212120056</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.815405428409576</v>
+        <v>0.815405488014221</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.815405428409576</v>
+        <v>0.815405488014221</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.815405428409576</v>
+        <v>0.815405488014221</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.790696263313293</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.813504755496979</v>
+        <v>0.813504815101624</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.815405428409576</v>
+        <v>0.815405488014221</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.821107685565948</v>
+        <v>0.821107625961304</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.809703350067139</v>
+        <v>0.809703409671783</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.832511901855469</v>
+        <v>0.832511842250824</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.836313366889954</v>
+        <v>0.836313426494598</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.842015504837036</v>
+        <v>0.842015564441681</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.842015504837036</v>
+        <v>0.842015564441681</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1133" t="n">
-        <v>0.828710436820984</v>
+        <v>0.828710496425629</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.840114712715149</v>
+        <v>0.840114772319794</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.840114712715149</v>
+        <v>0.840114772319794</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.832511901855469</v>
+        <v>0.832511842250824</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.834412634372711</v>
+        <v>0.834412693977356</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.828710436820984</v>
+        <v>0.828710496425629</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.828710436820984</v>
+        <v>0.828710496425629</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.828710436820984</v>
+        <v>0.828710496425629</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.857221186161041</v>
+        <v>0.857221245765686</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.836313366889954</v>
+        <v>0.836313426494598</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.832511901855469</v>
+        <v>0.832511842250824</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1152" t="n">
-        <v>0.836313366889954</v>
+        <v>0.836313426494598</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.813504755496979</v>
+        <v>0.813504815101624</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.821107685565948</v>
+        <v>0.821107625961304</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.804001212120056</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.790696263313293</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.815405428409576</v>
+        <v>0.815405488014221</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.813504755496979</v>
+        <v>0.813504815101624</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.813504755496979</v>
+        <v>0.813504815101624</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.813504755496979</v>
+        <v>0.813504815101624</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.813504755496979</v>
+        <v>0.813504815101624</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.783093452453613</v>
+        <v>0.783093392848969</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.804001212120056</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.775490581989288</v>
+        <v>0.775490522384644</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.773589909076691</v>
+        <v>0.773589849472046</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.773589909076691</v>
+        <v>0.773589849472046</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.783093452453613</v>
+        <v>0.783093392848969</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.802100479602814</v>
+        <v>0.802100539207458</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.809703350067139</v>
+        <v>0.809703409671783</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.790696263313293</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.783093452453613</v>
+        <v>0.783093392848969</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.771689176559448</v>
+        <v>0.771689116954803</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752682089805603</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752682089805603</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.665249228477478</v>
+        <v>0.665249288082123</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.7051642537117</v>
+        <v>0.705164194107056</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.783093452453613</v>
+        <v>0.783093392848969</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.775490581989288</v>
+        <v>0.775490522384644</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.771689176559448</v>
+        <v>0.771689116954803</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.743178486824036</v>
+        <v>0.743178427219391</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.72417140007019</v>
+        <v>0.724171340465546</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.733674943447113</v>
+        <v>0.733674883842468</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.727972745895386</v>
+        <v>0.727972686290741</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.733674943447113</v>
+        <v>0.733674883842468</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.733674943447113</v>
+        <v>0.733674883842468</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.743178486824036</v>
+        <v>0.743178427219391</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.809703350067139</v>
+        <v>0.809703409671783</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.809703350067139</v>
+        <v>0.809703409671783</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.783093452453613</v>
+        <v>0.783093392848969</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.809703350067139</v>
+        <v>0.809703409671783</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.790696263313293</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1319" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752682089805603</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.775490581989288</v>
+        <v>0.775490522384644</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.743178486824036</v>
+        <v>0.743178427219391</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1348" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752682089805603</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1361" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1365" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.783093452453613</v>
+        <v>0.783093392848969</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.809703350067139</v>
+        <v>0.809703409671783</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.834412634372711</v>
+        <v>0.834412693977356</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.842015504837036</v>
+        <v>0.842015564441681</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.813504755496979</v>
+        <v>0.813504815101624</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1390" t="n">
-        <v>0.813504755496979</v>
+        <v>0.813504815101624</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G1396" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1401" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1412" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1413" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752682089805603</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.743178486824036</v>
+        <v>0.743178427219391</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.771689176559448</v>
+        <v>0.771689116954803</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752682089805603</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.743178486824036</v>
+        <v>0.743178427219391</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1434" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1442" t="n">
-        <v>0.773589909076691</v>
+        <v>0.773589849472046</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.775490581989288</v>
+        <v>0.775490522384644</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.743178486824036</v>
+        <v>0.743178427219391</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1463" t="n">
-        <v>0.743178486824036</v>
+        <v>0.743178427219391</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.743178486824036</v>
+        <v>0.743178427219391</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1466" t="n">
-        <v>0.727972745895386</v>
+        <v>0.727972686290741</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.729873538017273</v>
+        <v>0.729873478412628</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.718469202518463</v>
+        <v>0.718469142913818</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.727972745895386</v>
+        <v>0.727972686290741</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.733674943447113</v>
+        <v>0.733674883842468</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.729873538017273</v>
+        <v>0.729873478412628</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.729873538017273</v>
+        <v>0.729873478412628</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.729873538017273</v>
+        <v>0.729873478412628</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.733674943447113</v>
+        <v>0.733674883842468</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.72417140007019</v>
+        <v>0.724171340465546</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.729873538017273</v>
+        <v>0.729873478412628</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1496" t="n">
-        <v>0.727972745895386</v>
+        <v>0.727972686290741</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.708965599536896</v>
+        <v>0.708965659141541</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.727972745895386</v>
+        <v>0.727972686290741</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>0.75</v>
       </c>
       <c r="G1502" t="n">
-        <v>0.712767064571381</v>
+        <v>0.712767124176025</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1504" t="n">
-        <v>0.714667737483978</v>
+        <v>0.714667797088623</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.7051642537117</v>
+        <v>0.705164194107056</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.7051642537117</v>
+        <v>0.705164194107056</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.7051642537117</v>
+        <v>0.705164194107056</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.7051642537117</v>
+        <v>0.705164194107056</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.714667737483978</v>
+        <v>0.714667797088623</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.708965599536896</v>
+        <v>0.708965659141541</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>0.75</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.712767064571381</v>
+        <v>0.712767124176025</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.708965599536896</v>
+        <v>0.708965659141541</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.708965599536896</v>
+        <v>0.708965659141541</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.691859185695648</v>
+        <v>0.691859245300293</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.7051642537117</v>
+        <v>0.705164194107056</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1526" t="n">
-        <v>0.7051642537117</v>
+        <v>0.705164194107056</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1527" t="n">
-        <v>0.691859185695648</v>
+        <v>0.691859245300293</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1528" t="n">
-        <v>0.7051642537117</v>
+        <v>0.705164194107056</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1533" t="n">
-        <v>0.691859185695648</v>
+        <v>0.691859245300293</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1535" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.665249228477478</v>
+        <v>0.665249288082123</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1559" t="n">
-        <v>0.729873538017273</v>
+        <v>0.729873478412628</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.708965599536896</v>
+        <v>0.708965659141541</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>0.75</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.712767064571381</v>
+        <v>0.712767124176025</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.665249228477478</v>
+        <v>0.665249288082123</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.657646358013153</v>
+        <v>0.657646417617798</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.621532917022705</v>
+        <v>0.62153285741806</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.621532917022705</v>
+        <v>0.62153285741806</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.617731392383575</v>
+        <v>0.61773145198822</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.627235054969788</v>
+        <v>0.627234995365143</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1581" t="n">
-        <v>0.657646358013153</v>
+        <v>0.657646417617798</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1586" t="n">
-        <v>0.644341349601746</v>
+        <v>0.64434140920639</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.642440676689148</v>
+        <v>0.642440736293793</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1591" t="n">
-        <v>0.64814281463623</v>
+        <v>0.64814293384552</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1592" t="n">
-        <v>0.64814281463623</v>
+        <v>0.64814293384552</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.644341349601746</v>
+        <v>0.64434140920639</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1595" t="n">
-        <v>0.638639271259308</v>
+        <v>0.638639211654663</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.634837806224823</v>
+        <v>0.634837865829468</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.634837806224823</v>
+        <v>0.634837865829468</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.627235054969788</v>
+        <v>0.627234995365143</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1599" t="n">
-        <v>0.627235054969788</v>
+        <v>0.627234995365143</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.634837806224823</v>
+        <v>0.634837865829468</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.627235054969788</v>
+        <v>0.627234995365143</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.612029373645782</v>
+        <v>0.612029314041138</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.617731392383575</v>
+        <v>0.61773145198822</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1628" t="n">
-        <v>0.627235054969788</v>
+        <v>0.627234995365143</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1633" t="n">
-        <v>0.613930106163025</v>
+        <v>0.61393004655838</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.61012864112854</v>
+        <v>0.610128700733185</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1635" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1636" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1641" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1643" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1645" t="n">
-        <v>0.59492290019989</v>
+        <v>0.594922840595245</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1646" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1647" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1652" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1653" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1654" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G1656" t="n">
-        <v>0.49608588218689</v>
+        <v>0.496085911989212</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.497986555099487</v>
+        <v>0.49798658490181</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G1658" t="n">
-        <v>0.490383684635162</v>
+        <v>0.490383714437485</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.524596571922302</v>
+        <v>0.524596512317657</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1666" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.61012864112854</v>
+        <v>0.610128700733185</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1670" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1673" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1676" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220702648163</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1679" t="n">
-        <v>0.574015080928802</v>
+        <v>0.574015021324158</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.612029373645782</v>
+        <v>0.612029314041138</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.61012864112854</v>
+        <v>0.610128700733185</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1685" t="n">
-        <v>0.59492290019989</v>
+        <v>0.594922840595245</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121435165405</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1692" t="n">
-        <v>0.59492290019989</v>
+        <v>0.594922840595245</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1705" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220702648163</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220702648163</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220702648163</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121435165405</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121435165405</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1719" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1721" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220702648163</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1727" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121435165405</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1730" t="n">
-        <v>0.59492290019989</v>
+        <v>0.594922840595245</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1731" t="n">
-        <v>0.59492290019989</v>
+        <v>0.594922840595245</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.59492290019989</v>
+        <v>0.594922840595245</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1735" t="n">
-        <v>0.59492290019989</v>
+        <v>0.594922840595245</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45557,7 +45557,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1738" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1738" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.574015080928802</v>
+        <v>0.574015021324158</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1741" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1743" t="n">
-        <v>0.57591587305069</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.574015080928802</v>
+        <v>0.574015021324158</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.57591587305069</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121435165405</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.574015080928802</v>
+        <v>0.574015021324158</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121435165405</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1754" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121435165405</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1759" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220702648163</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1767" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1768" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220702648163</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1774" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1776" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1779" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220702648163</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46649,7 +46649,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1780" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1781" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121435165405</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1785" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220702648163</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1786" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1787" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1788" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1793" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1795" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220702648163</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1796" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220702648163</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1800" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1801" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1802" t="n">
-        <v>0.59492290019989</v>
+        <v>0.594922840595245</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121435165405</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220702648163</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1805" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220702648163</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1806" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220702648163</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1807" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220702648163</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1812" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1818" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1821" t="n">
-        <v>0.57591587305069</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1825" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.57591587305069</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48027,7 +48027,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1833" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1833" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1837" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1841" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1844" t="n">
-        <v>0.574015080928802</v>
+        <v>0.574015021324158</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1847" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1848" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.574015080928802</v>
+        <v>0.574015021324158</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48521,7 +48521,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1852" t="n">
-        <v>0.574015080928802</v>
+        <v>0.574015021324158</v>
       </c>
       <c r="H1852" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1854" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1855" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1858" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1859" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.574015080928802</v>
+        <v>0.574015021324158</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1878" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49405,7 +49405,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1886" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1894" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1895" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1897" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1901" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1903" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1904" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1906" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1907" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1908" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1910" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1911" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1914" t="n">
-        <v>0.553107261657715</v>
+        <v>0.55310732126236</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1925" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1926" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1927" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1928" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1929" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220702648163</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1930" t="n">
-        <v>0.59492290019989</v>
+        <v>0.594922840595245</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1931" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1932" t="n">
-        <v>0.612029373645782</v>
+        <v>0.612029314041138</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1933" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1934" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50679,7 +50679,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1935" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121435165405</v>
       </c>
       <c r="H1935" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1941" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50887,7 +50887,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1943" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1943" t="s">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1944" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1944" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1945" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -50965,7 +50965,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1946" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1946" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1947" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1948" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1949" t="n">
-        <v>0.553107261657715</v>
+        <v>0.55310732126236</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1950" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1951" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1953" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1955" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1956" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1957" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1958" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1960" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1962" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1965" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1966" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1967" t="n">
-        <v>0.553107261657715</v>
+        <v>0.55310732126236</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1969" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1970" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1971" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1972" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51823,7 +51823,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G1979" t="n">
-        <v>0.557727932929993</v>
+        <v>0.557727873325348</v>
       </c>
       <c r="H1979" t="s">
         <v>8</v>
@@ -51875,7 +51875,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G1981" t="n">
-        <v>0.544218957424164</v>
+        <v>0.544218897819519</v>
       </c>
       <c r="H1981" t="s">
         <v>8</v>
@@ -52005,7 +52005,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1986" t="n">
-        <v>0.521060645580292</v>
+        <v>0.521060705184937</v>
       </c>
       <c r="H1986" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1989" t="n">
-        <v>0.521060645580292</v>
+        <v>0.521060705184937</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1992" t="n">
-        <v>0.522990465164185</v>
+        <v>0.522990524768829</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1994" t="n">
-        <v>0.521060645580292</v>
+        <v>0.521060705184937</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1995" t="n">
-        <v>0.521060645580292</v>
+        <v>0.521060705184937</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52265,7 +52265,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1996" t="n">
-        <v>0.521060645580292</v>
+        <v>0.521060705184937</v>
       </c>
       <c r="H1996" t="s">
         <v>8</v>
@@ -52317,7 +52317,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1998" t="n">
-        <v>0.522990465164185</v>
+        <v>0.522990524768829</v>
       </c>
       <c r="H1998" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1999" t="n">
-        <v>0.519130825996399</v>
+        <v>0.519130766391754</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2000" t="n">
-        <v>0.524920403957367</v>
+        <v>0.524920344352722</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52421,7 +52421,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2002" t="n">
-        <v>0.507551670074463</v>
+        <v>0.507551729679108</v>
       </c>
       <c r="H2002" t="s">
         <v>8</v>
@@ -52473,7 +52473,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2004" t="n">
-        <v>0.501762092113495</v>
+        <v>0.50176215171814</v>
       </c>
       <c r="H2004" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2007" t="n">
-        <v>0.524920403957367</v>
+        <v>0.524920344352722</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G2010" t="n">
-        <v>0.503692030906677</v>
+        <v>0.503691971302032</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52655,7 +52655,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2011" t="n">
-        <v>0.521060645580292</v>
+        <v>0.521060705184937</v>
       </c>
       <c r="H2011" t="s">
         <v>8</v>
@@ -52681,7 +52681,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G2012" t="n">
-        <v>0.519130825996399</v>
+        <v>0.519130766391754</v>
       </c>
       <c r="H2012" t="s">
         <v>8</v>
@@ -52707,7 +52707,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2013" t="n">
-        <v>0.517201006412506</v>
+        <v>0.517200946807861</v>
       </c>
       <c r="H2013" t="s">
         <v>8</v>
@@ -52759,7 +52759,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2015" t="n">
-        <v>0.501762092113495</v>
+        <v>0.50176215171814</v>
       </c>
       <c r="H2015" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2016" t="n">
-        <v>0.517201006412506</v>
+        <v>0.517200946807861</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52811,7 +52811,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2017" t="n">
-        <v>0.517201006412506</v>
+        <v>0.517200946807861</v>
       </c>
       <c r="H2017" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2018" t="n">
-        <v>0.509481489658356</v>
+        <v>0.509481549263</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2019" t="n">
-        <v>0.509481489658356</v>
+        <v>0.509481549263</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G2022" t="n">
-        <v>0.503692030906677</v>
+        <v>0.503691971302032</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G2023" t="n">
-        <v>0.497902393341064</v>
+        <v>0.497902363538742</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -52993,7 +52993,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2024" t="n">
-        <v>0.507551670074463</v>
+        <v>0.507551729679108</v>
       </c>
       <c r="H2024" t="s">
         <v>8</v>
@@ -53019,7 +53019,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2025" t="n">
-        <v>0.509481489658356</v>
+        <v>0.509481549263</v>
       </c>
       <c r="H2025" t="s">
         <v>8</v>
@@ -53045,7 +53045,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2026" t="n">
-        <v>0.509481489658356</v>
+        <v>0.509481549263</v>
       </c>
       <c r="H2026" t="s">
         <v>8</v>
@@ -53097,7 +53097,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G2028" t="n">
-        <v>0.497902393341064</v>
+        <v>0.497902363538742</v>
       </c>
       <c r="H2028" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G2029" t="n">
-        <v>0.497902393341064</v>
+        <v>0.497902363538742</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G2030" t="n">
-        <v>0.499832302331924</v>
+        <v>0.49983224272728</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2031" t="n">
-        <v>0.495972543954849</v>
+        <v>0.495972573757172</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G2032" t="n">
-        <v>0.497902393341064</v>
+        <v>0.497902363538742</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2033" t="n">
-        <v>0.490182965993881</v>
+        <v>0.490183025598526</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G2034" t="n">
-        <v>0.497902393341064</v>
+        <v>0.497902363538742</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G2035" t="n">
-        <v>0.497902393341064</v>
+        <v>0.497902363538742</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53305,7 +53305,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2036" t="n">
-        <v>0.492112815380096</v>
+        <v>0.492112785577774</v>
       </c>
       <c r="H2036" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G2037" t="n">
-        <v>0.497902393341064</v>
+        <v>0.497902363538742</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2038" t="n">
-        <v>0.488253146409988</v>
+        <v>0.488253116607666</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2039" t="n">
-        <v>0.495972543954849</v>
+        <v>0.495972573757172</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2040" t="n">
-        <v>0.492112815380096</v>
+        <v>0.492112785577774</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2041" t="n">
-        <v>0.492112815380096</v>
+        <v>0.492112785577774</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53461,7 +53461,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2042" t="n">
-        <v>0.492112815380096</v>
+        <v>0.492112785577774</v>
       </c>
       <c r="H2042" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G2043" t="n">
-        <v>0.497902393341064</v>
+        <v>0.497902363538742</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53513,7 +53513,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2044" t="n">
-        <v>0.495972543954849</v>
+        <v>0.495972573757172</v>
       </c>
       <c r="H2044" t="s">
         <v>8</v>
@@ -53539,7 +53539,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2045" t="n">
-        <v>0.484393417835236</v>
+        <v>0.484393388032913</v>
       </c>
       <c r="H2045" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>0.5</v>
       </c>
       <c r="G2046" t="n">
-        <v>0.48246356844902</v>
+        <v>0.482463538646698</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53591,7 +53591,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2047" t="n">
-        <v>0.490182965993881</v>
+        <v>0.490183025598526</v>
       </c>
       <c r="H2047" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2048" t="n">
-        <v>0.490182965993881</v>
+        <v>0.490183025598526</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2049" t="n">
-        <v>0.492112815380096</v>
+        <v>0.492112785577774</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2050" t="n">
-        <v>0.492112815380096</v>
+        <v>0.492112785577774</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2051" t="n">
-        <v>0.492112815380096</v>
+        <v>0.492112785577774</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>0.5</v>
       </c>
       <c r="G2052" t="n">
-        <v>0.48246356844902</v>
+        <v>0.482463538646698</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53747,7 +53747,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2053" t="n">
-        <v>0.467989683151245</v>
+        <v>0.467989653348923</v>
       </c>
       <c r="H2053" t="s">
         <v>8</v>
@@ -53773,7 +53773,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G2054" t="n">
-        <v>0.470884472131729</v>
+        <v>0.470884442329407</v>
       </c>
       <c r="H2054" t="s">
         <v>8</v>
@@ -53799,7 +53799,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G2055" t="n">
-        <v>0.470884472131729</v>
+        <v>0.470884442329407</v>
       </c>
       <c r="H2055" t="s">
         <v>8</v>
@@ -53825,7 +53825,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2056" t="n">
-        <v>0.46027022600174</v>
+        <v>0.460270255804062</v>
       </c>
       <c r="H2056" t="s">
         <v>8</v>
@@ -53851,7 +53851,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2057" t="n">
-        <v>0.46412992477417</v>
+        <v>0.464129984378815</v>
       </c>
       <c r="H2057" t="s">
         <v>8</v>
@@ -53877,7 +53877,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2058" t="n">
-        <v>0.46027022600174</v>
+        <v>0.460270255804062</v>
       </c>
       <c r="H2058" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2060" t="n">
-        <v>0.46027022600174</v>
+        <v>0.460270255804062</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G2061" t="n">
-        <v>0.470884472131729</v>
+        <v>0.470884442329407</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -54007,7 +54007,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G2063" t="n">
-        <v>0.46605983376503</v>
+        <v>0.466059803962708</v>
       </c>
       <c r="H2063" t="s">
         <v>8</v>
@@ -54033,7 +54033,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G2064" t="n">
-        <v>0.46605983376503</v>
+        <v>0.466059803962708</v>
       </c>
       <c r="H2064" t="s">
         <v>8</v>
@@ -54059,7 +54059,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2065" t="n">
-        <v>0.467989683151245</v>
+        <v>0.467989653348923</v>
       </c>
       <c r="H2065" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2066" t="n">
-        <v>0.467989683151245</v>
+        <v>0.467989653348923</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54111,7 +54111,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2067" t="n">
-        <v>0.467989683151245</v>
+        <v>0.467989653348923</v>
       </c>
       <c r="H2067" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2068" t="n">
-        <v>0.467989683151245</v>
+        <v>0.467989653348923</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2073" t="n">
-        <v>0.46027022600174</v>
+        <v>0.460270255804062</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54293,7 +54293,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2074" t="n">
-        <v>0.46027022600174</v>
+        <v>0.460270255804062</v>
       </c>
       <c r="H2074" t="s">
         <v>8</v>
@@ -54345,7 +54345,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G2076" t="n">
-        <v>0.462200105190277</v>
+        <v>0.462200075387955</v>
       </c>
       <c r="H2076" t="s">
         <v>8</v>
@@ -54371,7 +54371,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2077" t="n">
-        <v>0.450620949268341</v>
+        <v>0.450620979070663</v>
       </c>
       <c r="H2077" t="s">
         <v>8</v>
@@ -54449,7 +54449,7 @@
         <v>0.476000010967255</v>
       </c>
       <c r="G2080" t="n">
-        <v>0.459305346012115</v>
+        <v>0.459305316209793</v>
       </c>
       <c r="H2080" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2081" t="n">
-        <v>0.443866461515427</v>
+        <v>0.443866521120071</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G2083" t="n">
-        <v>0.452550858259201</v>
+        <v>0.452550828456879</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54553,7 +54553,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2084" t="n">
-        <v>0.434217184782028</v>
+        <v>0.434217214584351</v>
       </c>
       <c r="H2084" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2088" t="n">
-        <v>0.394655227661133</v>
+        <v>0.39465519785881</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2092" t="n">
-        <v>0.37632155418396</v>
+        <v>0.376321583986282</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -55021,7 +55021,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2102" t="n">
-        <v>0.382111132144928</v>
+        <v>0.38211116194725</v>
       </c>
       <c r="H2102" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2105" t="n">
-        <v>0.382111132144928</v>
+        <v>0.38211116194725</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55125,7 +55125,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G2106" t="n">
-        <v>0.360882759094238</v>
+        <v>0.360882729291916</v>
       </c>
       <c r="H2106" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>0.377999991178513</v>
       </c>
       <c r="G2109" t="n">
-        <v>0.364742457866669</v>
+        <v>0.364742428064346</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2110" t="n">
-        <v>0.380181282758713</v>
+        <v>0.38018125295639</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55281,7 +55281,7 @@
         <v>0.398000001907349</v>
       </c>
       <c r="G2112" t="n">
-        <v>0.384041011333466</v>
+        <v>0.384040981531143</v>
       </c>
       <c r="H2112" t="s">
         <v>8</v>
@@ -55307,7 +55307,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2113" t="n">
-        <v>0.37632155418396</v>
+        <v>0.376321583986282</v>
       </c>
       <c r="H2113" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>0.375</v>
       </c>
       <c r="G2115" t="n">
-        <v>0.361847668886185</v>
+        <v>0.361847698688507</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G2117" t="n">
-        <v>0.356058120727539</v>
+        <v>0.356058090925217</v>
       </c>
       <c r="H2117" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2120" t="n">
-        <v>0.373426765203476</v>
+        <v>0.373426795005798</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2121" t="n">
-        <v>0.434217184782028</v>
+        <v>0.434217214584351</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>0.439999997615814</v>
       </c>
       <c r="G2122" t="n">
-        <v>0.424567937850952</v>
+        <v>0.424567967653275</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2123" t="n">
-        <v>0.416848540306091</v>
+        <v>0.416848510503769</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2127" t="n">
-        <v>0.405269354581833</v>
+        <v>0.405269414186478</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55827,7 +55827,7 @@
         <v>0.395000010728836</v>
       </c>
       <c r="G2133" t="n">
-        <v>0.381146222352982</v>
+        <v>0.381146252155304</v>
       </c>
       <c r="H2133" t="s">
         <v>8</v>
@@ -55879,7 +55879,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2135" t="n">
-        <v>0.394655227661133</v>
+        <v>0.39465519785881</v>
       </c>
       <c r="H2135" t="s">
         <v>8</v>
@@ -56035,7 +56035,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2141" t="n">
-        <v>0.394655227661133</v>
+        <v>0.39465519785881</v>
       </c>
       <c r="H2141" t="s">
         <v>8</v>
@@ -56061,7 +56061,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2142" t="n">
-        <v>0.394655227661133</v>
+        <v>0.39465519785881</v>
       </c>
       <c r="H2142" t="s">
         <v>8</v>
@@ -56373,7 +56373,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2154" t="n">
-        <v>0.414918661117554</v>
+        <v>0.414918690919876</v>
       </c>
       <c r="H2154" t="s">
         <v>8</v>
@@ -56399,7 +56399,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2155" t="n">
-        <v>0.409129112958908</v>
+        <v>0.409129083156586</v>
       </c>
       <c r="H2155" t="s">
         <v>8</v>
@@ -56711,7 +56711,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2167" t="n">
-        <v>0.412023842334747</v>
+        <v>0.41202387213707</v>
       </c>
       <c r="H2167" t="s">
         <v>8</v>
@@ -56737,7 +56737,7 @@
         <v>0.42399999499321</v>
       </c>
       <c r="G2168" t="n">
-        <v>0.409129112958908</v>
+        <v>0.409129083156586</v>
       </c>
       <c r="H2168" t="s">
         <v>8</v>
@@ -56763,7 +56763,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2169" t="n">
-        <v>0.408164203166962</v>
+        <v>0.408164173364639</v>
       </c>
       <c r="H2169" t="s">
         <v>8</v>
@@ -56971,7 +56971,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2177" t="n">
-        <v>0.396585047245026</v>
+        <v>0.396585077047348</v>
       </c>
       <c r="H2177" t="s">
         <v>8</v>
@@ -56997,7 +56997,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2178" t="n">
-        <v>0.399024099111557</v>
+        <v>0.399024069309235</v>
       </c>
       <c r="H2178" t="s">
         <v>8</v>
@@ -57127,7 +57127,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2183" t="n">
-        <v>0.403902113437653</v>
+        <v>0.403902143239975</v>
       </c>
       <c r="H2183" t="s">
         <v>8</v>
@@ -57179,7 +57179,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2185" t="n">
-        <v>0.403902113437653</v>
+        <v>0.403902143239975</v>
       </c>
       <c r="H2185" t="s">
         <v>8</v>
@@ -57387,7 +57387,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G2193" t="n">
-        <v>0.376585096120834</v>
+        <v>0.376585066318512</v>
       </c>
       <c r="H2193" t="s">
         <v>8</v>
@@ -57543,7 +57543,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2199" t="n">
-        <v>0.380487471818924</v>
+        <v>0.380487501621246</v>
       </c>
       <c r="H2199" t="s">
         <v>8</v>
@@ -57725,7 +57725,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G2206" t="n">
-        <v>0.378536283969879</v>
+        <v>0.378536313772202</v>
       </c>
       <c r="H2206" t="s">
         <v>8</v>
@@ -57751,7 +57751,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G2207" t="n">
-        <v>0.378536283969879</v>
+        <v>0.378536313772202</v>
       </c>
       <c r="H2207" t="s">
         <v>8</v>
@@ -57803,7 +57803,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2209" t="n">
-        <v>0.380487471818924</v>
+        <v>0.380487501621246</v>
       </c>
       <c r="H2209" t="s">
         <v>8</v>
@@ -57959,7 +57959,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2215" t="n">
-        <v>0.377560645341873</v>
+        <v>0.377560675144196</v>
       </c>
       <c r="H2215" t="s">
         <v>8</v>
@@ -57985,7 +57985,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G2216" t="n">
-        <v>0.376585096120834</v>
+        <v>0.376585066318512</v>
       </c>
       <c r="H2216" t="s">
         <v>8</v>
@@ -58089,7 +58089,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2220" t="n">
-        <v>0.377560645341873</v>
+        <v>0.377560675144196</v>
       </c>
       <c r="H2220" t="s">
         <v>8</v>
@@ -58115,7 +58115,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G2221" t="n">
-        <v>0.376585096120834</v>
+        <v>0.376585066318512</v>
       </c>
       <c r="H2221" t="s">
         <v>8</v>
@@ -58271,7 +58271,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2227" t="n">
-        <v>0.418536245822906</v>
+        <v>0.418536216020584</v>
       </c>
       <c r="H2227" t="s">
         <v>8</v>
@@ -58401,7 +58401,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2232" t="n">
-        <v>0.396097242832184</v>
+        <v>0.396097213029861</v>
       </c>
       <c r="H2232" t="s">
         <v>8</v>
@@ -58479,7 +58479,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2235" t="n">
-        <v>0.399024099111557</v>
+        <v>0.399024069309235</v>
       </c>
       <c r="H2235" t="s">
         <v>8</v>
@@ -58505,7 +58505,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2236" t="n">
-        <v>0.400975286960602</v>
+        <v>0.400975316762924</v>
       </c>
       <c r="H2236" t="s">
         <v>8</v>
@@ -58609,7 +58609,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2240" t="n">
-        <v>0.400975286960602</v>
+        <v>0.400975316762924</v>
       </c>
       <c r="H2240" t="s">
         <v>8</v>
@@ -58661,7 +58661,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2242" t="n">
-        <v>0.399024099111557</v>
+        <v>0.399024069309235</v>
       </c>
       <c r="H2242" t="s">
         <v>8</v>
@@ -58765,7 +58765,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2246" t="n">
-        <v>0.384389936923981</v>
+        <v>0.384389907121658</v>
       </c>
       <c r="H2246" t="s">
         <v>8</v>
@@ -58869,7 +58869,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G2250" t="n">
-        <v>0.376585096120834</v>
+        <v>0.376585066318512</v>
       </c>
       <c r="H2250" t="s">
         <v>8</v>
@@ -58895,7 +58895,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2251" t="n">
-        <v>0.380487471818924</v>
+        <v>0.380487501621246</v>
       </c>
       <c r="H2251" t="s">
         <v>8</v>
@@ -58921,7 +58921,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2252" t="n">
-        <v>0.380487471818924</v>
+        <v>0.380487501621246</v>
       </c>
       <c r="H2252" t="s">
         <v>8</v>
@@ -58947,7 +58947,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2253" t="n">
-        <v>0.396097242832184</v>
+        <v>0.396097213029861</v>
       </c>
       <c r="H2253" t="s">
         <v>8</v>
@@ -59025,7 +59025,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2256" t="n">
-        <v>0.380487471818924</v>
+        <v>0.380487501621246</v>
       </c>
       <c r="H2256" t="s">
         <v>8</v>
@@ -59233,7 +59233,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2264" t="n">
-        <v>0.396097242832184</v>
+        <v>0.396097213029861</v>
       </c>
       <c r="H2264" t="s">
         <v>8</v>
@@ -59285,7 +59285,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2266" t="n">
-        <v>0.384389936923981</v>
+        <v>0.384389907121658</v>
       </c>
       <c r="H2266" t="s">
         <v>8</v>
@@ -59363,7 +59363,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G2269" t="n">
-        <v>0.378536283969879</v>
+        <v>0.378536313772202</v>
       </c>
       <c r="H2269" t="s">
         <v>8</v>
@@ -59597,7 +59597,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2278" t="n">
-        <v>0.418536245822906</v>
+        <v>0.418536216020584</v>
       </c>
       <c r="H2278" t="s">
         <v>8</v>
@@ -59649,7 +59649,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G2280" t="n">
-        <v>0.478048413991928</v>
+        <v>0.478048384189606</v>
       </c>
       <c r="H2280" t="s">
         <v>8</v>
@@ -59753,7 +59753,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G2284" t="n">
-        <v>0.48390206694603</v>
+        <v>0.483902037143707</v>
       </c>
       <c r="H2284" t="s">
         <v>8</v>
@@ -59779,7 +59779,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2285" t="n">
-        <v>0.469267904758453</v>
+        <v>0.469267934560776</v>
       </c>
       <c r="H2285" t="s">
         <v>8</v>
@@ -59805,7 +59805,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G2286" t="n">
-        <v>0.478048413991928</v>
+        <v>0.478048384189606</v>
       </c>
       <c r="H2286" t="s">
         <v>8</v>
@@ -60013,7 +60013,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G2294" t="n">
-        <v>0.467316716909409</v>
+        <v>0.467316687107086</v>
       </c>
       <c r="H2294" t="s">
         <v>8</v>
@@ -60065,7 +60065,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G2296" t="n">
-        <v>0.463414251804352</v>
+        <v>0.463414281606674</v>
       </c>
       <c r="H2296" t="s">
         <v>8</v>
@@ -60143,7 +60143,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2299" t="n">
-        <v>0.43902400135994</v>
+        <v>0.439024031162262</v>
       </c>
       <c r="H2299" t="s">
         <v>8</v>
@@ -60325,7 +60325,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2306" t="n">
-        <v>0.448780119419098</v>
+        <v>0.44878014922142</v>
       </c>
       <c r="H2306" t="s">
         <v>8</v>
@@ -60507,7 +60507,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2313" t="n">
-        <v>0.493658155202866</v>
+        <v>0.493658125400543</v>
       </c>
       <c r="H2313" t="s">
         <v>8</v>
@@ -60533,7 +60533,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2314" t="n">
-        <v>0.491706907749176</v>
+        <v>0.491706937551498</v>
       </c>
       <c r="H2314" t="s">
         <v>8</v>
@@ -60559,7 +60559,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2315" t="n">
-        <v>0.491706907749176</v>
+        <v>0.491706937551498</v>
       </c>
       <c r="H2315" t="s">
         <v>8</v>
@@ -60611,7 +60611,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2317" t="n">
-        <v>0.49560934305191</v>
+        <v>0.495609402656555</v>
       </c>
       <c r="H2317" t="s">
         <v>8</v>
@@ -60689,7 +60689,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2320" t="n">
-        <v>0.513170301914215</v>
+        <v>0.51317036151886</v>
       </c>
       <c r="H2320" t="s">
         <v>8</v>
@@ -60715,7 +60715,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2321" t="n">
-        <v>0.581462979316711</v>
+        <v>0.581462919712067</v>
       </c>
       <c r="H2321" t="s">
         <v>8</v>
@@ -60767,7 +60767,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2323" t="n">
-        <v>0.727804243564606</v>
+        <v>0.72780430316925</v>
       </c>
       <c r="H2323" t="s">
         <v>8</v>
@@ -60845,7 +60845,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2326" t="n">
-        <v>0.68292623758316</v>
+        <v>0.682926297187805</v>
       </c>
       <c r="H2326" t="s">
         <v>8</v>
@@ -61053,7 +61053,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G2334" t="n">
-        <v>0.647804379463196</v>
+        <v>0.647804319858551</v>
       </c>
       <c r="H2334" t="s">
         <v>8</v>
@@ -61079,7 +61079,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2335" t="n">
-        <v>0.66926771402359</v>
+        <v>0.669267773628235</v>
       </c>
       <c r="H2335" t="s">
         <v>8</v>
@@ -61209,7 +61209,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G2340" t="n">
-        <v>0.710243284702301</v>
+        <v>0.710243344306946</v>
       </c>
       <c r="H2340" t="s">
         <v>8</v>
@@ -61235,7 +61235,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G2341" t="n">
-        <v>0.710243284702301</v>
+        <v>0.710243344306946</v>
       </c>
       <c r="H2341" t="s">
         <v>8</v>
@@ -61261,7 +61261,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G2342" t="n">
-        <v>0.706340909004211</v>
+        <v>0.706340849399567</v>
       </c>
       <c r="H2342" t="s">
         <v>8</v>
@@ -61287,7 +61287,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2343" t="n">
-        <v>0.68292623758316</v>
+        <v>0.682926297187805</v>
       </c>
       <c r="H2343" t="s">
         <v>8</v>
@@ -61339,7 +61339,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2345" t="n">
-        <v>0.68292623758316</v>
+        <v>0.682926297187805</v>
       </c>
       <c r="H2345" t="s">
         <v>8</v>
@@ -61391,7 +61391,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G2347" t="n">
-        <v>0.688779890537262</v>
+        <v>0.688779950141907</v>
       </c>
       <c r="H2347" t="s">
         <v>8</v>
@@ -61495,7 +61495,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2351" t="n">
-        <v>0.675121426582336</v>
+        <v>0.675121366977692</v>
       </c>
       <c r="H2351" t="s">
         <v>8</v>
@@ -61521,7 +61521,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2352" t="n">
-        <v>0.571706831455231</v>
+        <v>0.571706891059875</v>
       </c>
       <c r="H2352" t="s">
         <v>8</v>
@@ -61547,7 +61547,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2353" t="n">
-        <v>0.575609266757965</v>
+        <v>0.57560932636261</v>
       </c>
       <c r="H2353" t="s">
         <v>8</v>
@@ -61599,7 +61599,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2355" t="n">
-        <v>0.536584973335266</v>
+        <v>0.536584913730621</v>
       </c>
       <c r="H2355" t="s">
         <v>8</v>
@@ -61781,7 +61781,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2362" t="n">
-        <v>0.575609266757965</v>
+        <v>0.57560932636261</v>
       </c>
       <c r="H2362" t="s">
         <v>8</v>
@@ -61885,7 +61885,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2366" t="n">
-        <v>0.675121426582336</v>
+        <v>0.675121366977692</v>
       </c>
       <c r="H2366" t="s">
         <v>8</v>
@@ -61911,7 +61911,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2367" t="n">
-        <v>0.66926771402359</v>
+        <v>0.669267773628235</v>
       </c>
       <c r="H2367" t="s">
         <v>8</v>
@@ -61937,7 +61937,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2368" t="n">
-        <v>0.663414061069489</v>
+        <v>0.663414120674133</v>
       </c>
       <c r="H2368" t="s">
         <v>8</v>
@@ -62015,7 +62015,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2371" t="n">
-        <v>0.638048231601715</v>
+        <v>0.63804829120636</v>
       </c>
       <c r="H2371" t="s">
         <v>8</v>
@@ -62067,7 +62067,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2373" t="n">
-        <v>0.655609250068665</v>
+        <v>0.65560919046402</v>
       </c>
       <c r="H2373" t="s">
         <v>8</v>
@@ -62093,7 +62093,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2374" t="n">
-        <v>0.616584956645966</v>
+        <v>0.616584897041321</v>
       </c>
       <c r="H2374" t="s">
         <v>8</v>
@@ -62145,7 +62145,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2376" t="n">
-        <v>0.616584956645966</v>
+        <v>0.616584897041321</v>
       </c>
       <c r="H2376" t="s">
         <v>8</v>
@@ -62275,7 +62275,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2381" t="n">
-        <v>0.616584956645966</v>
+        <v>0.616584897041321</v>
       </c>
       <c r="H2381" t="s">
         <v>8</v>
@@ -62327,7 +62327,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2383" t="n">
-        <v>0.616584956645966</v>
+        <v>0.616584897041321</v>
       </c>
       <c r="H2383" t="s">
         <v>8</v>
@@ -62587,7 +62587,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2393" t="n">
-        <v>0.663414061069489</v>
+        <v>0.663414120674133</v>
       </c>
       <c r="H2393" t="s">
         <v>8</v>
@@ -62613,7 +62613,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2394" t="n">
-        <v>0.673170208930969</v>
+        <v>0.673170149326324</v>
       </c>
       <c r="H2394" t="s">
         <v>8</v>
@@ -62665,7 +62665,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2396" t="n">
-        <v>0.66926771402359</v>
+        <v>0.669267773628235</v>
       </c>
       <c r="H2396" t="s">
         <v>8</v>
@@ -62717,7 +62717,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2398" t="n">
-        <v>0.675121426582336</v>
+        <v>0.675121366977692</v>
       </c>
       <c r="H2398" t="s">
         <v>8</v>
@@ -62873,7 +62873,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2404" t="n">
-        <v>0.663414061069489</v>
+        <v>0.663414120674133</v>
       </c>
       <c r="H2404" t="s">
         <v>8</v>
@@ -62951,7 +62951,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G2407" t="n">
-        <v>0.647804379463196</v>
+        <v>0.647804319858551</v>
       </c>
       <c r="H2407" t="s">
         <v>8</v>
@@ -63003,7 +63003,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2409" t="n">
-        <v>0.628292202949524</v>
+        <v>0.628292143344879</v>
       </c>
       <c r="H2409" t="s">
         <v>8</v>
@@ -63029,7 +63029,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2410" t="n">
-        <v>0.638048231601715</v>
+        <v>0.63804829120636</v>
       </c>
       <c r="H2410" t="s">
         <v>8</v>
@@ -63055,7 +63055,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2411" t="n">
-        <v>0.638048231601715</v>
+        <v>0.63804829120636</v>
       </c>
       <c r="H2411" t="s">
         <v>8</v>
@@ -63107,7 +63107,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G2413" t="n">
-        <v>0.647804379463196</v>
+        <v>0.647804319858551</v>
       </c>
       <c r="H2413" t="s">
         <v>8</v>
@@ -63133,7 +63133,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2414" t="n">
-        <v>0.628292202949524</v>
+        <v>0.628292143344879</v>
       </c>
       <c r="H2414" t="s">
         <v>8</v>
@@ -63289,7 +63289,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2420" t="n">
-        <v>0.62048727273941</v>
+        <v>0.620487332344055</v>
       </c>
       <c r="H2420" t="s">
         <v>8</v>
@@ -63341,7 +63341,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2422" t="n">
-        <v>0.628292202949524</v>
+        <v>0.628292143344879</v>
       </c>
       <c r="H2422" t="s">
         <v>8</v>
@@ -63367,7 +63367,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G2423" t="n">
-        <v>0.618536055088043</v>
+        <v>0.618536114692688</v>
       </c>
       <c r="H2423" t="s">
         <v>8</v>
@@ -63445,7 +63445,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2426" t="n">
-        <v>0.628292202949524</v>
+        <v>0.628292143344879</v>
       </c>
       <c r="H2426" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>1.24000000953674</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>96740</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>1.27999997138977</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>1.22500002384186</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>1.23500001430511</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>1.44454121589661</v>
+        <v>1.44454109668732</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>1.46354842185974</v>
+        <v>1.46354830265045</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G10" t="n">
-        <v>1.40652704238892</v>
+        <v>1.40652716159821</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>1.22595942020416</v>
+        <v>1.22595930099487</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G25" t="n">
-        <v>1.2829806804657</v>
+        <v>1.28298079967499</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G26" t="n">
-        <v>1.25446999073029</v>
+        <v>1.25447010993958</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G32" t="n">
-        <v>1.22595942020416</v>
+        <v>1.22595930099487</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G36" t="n">
-        <v>1.25922191143036</v>
+        <v>1.25922179222107</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G39" t="n">
-        <v>1.31719350814819</v>
+        <v>1.31719362735748</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G40" t="n">
-        <v>1.3114914894104</v>
+        <v>1.31149137020111</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G41" t="n">
-        <v>1.3114914894104</v>
+        <v>1.31149137020111</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G43" t="n">
-        <v>1.3114914894104</v>
+        <v>1.31149137020111</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G45" t="n">
-        <v>1.32099497318268</v>
+        <v>1.32099485397339</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>1.28773260116577</v>
+        <v>1.28773248195648</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>1.30103743076324</v>
+        <v>1.30103754997253</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G54" t="n">
-        <v>1.32099497318268</v>
+        <v>1.32099485397339</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G61" t="n">
-        <v>1.27157652378082</v>
+        <v>1.27157640457153</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G64" t="n">
-        <v>1.24116516113281</v>
+        <v>1.24116504192352</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G68" t="n">
-        <v>1.30578923225403</v>
+        <v>1.30578911304474</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G69" t="n">
-        <v>1.30578923225403</v>
+        <v>1.30578911304474</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G72" t="n">
-        <v>1.30483877658844</v>
+        <v>1.30483889579773</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G73" t="n">
-        <v>1.29058372974396</v>
+        <v>1.29058361053467</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G89" t="n">
-        <v>1.30483877658844</v>
+        <v>1.30483889579773</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G90" t="n">
-        <v>1.30103743076324</v>
+        <v>1.30103754997253</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G91" t="n">
-        <v>1.30103743076324</v>
+        <v>1.30103754997253</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G92" t="n">
-        <v>1.25922191143036</v>
+        <v>1.25922179222107</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G94" t="n">
-        <v>1.25446999073029</v>
+        <v>1.25447010993958</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G103" t="n">
-        <v>1.16133522987366</v>
+        <v>1.16133511066437</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G109" t="n">
-        <v>1.17559039592743</v>
+        <v>1.17559051513672</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G118" t="n">
-        <v>1.17273926734924</v>
+        <v>1.17273938655853</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G119" t="n">
-        <v>1.18699467182159</v>
+        <v>1.18699479103088</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G121" t="n">
-        <v>1.13187408447266</v>
+        <v>1.13187396526337</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>1.02300000190735</v>
       </c>
       <c r="G124" t="n">
-        <v>0.97221428155899</v>
+        <v>0.972214341163635</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G134" t="n">
-        <v>1.02068245410919</v>
+        <v>1.0206823348999</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G135" t="n">
-        <v>1.00547683238983</v>
+        <v>1.00547671318054</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G150" t="n">
-        <v>1.03588819503784</v>
+        <v>1.03588807582855</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G152" t="n">
-        <v>0.986469626426697</v>
+        <v>0.986469686031342</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G153" t="n">
-        <v>0.986469626426697</v>
+        <v>0.986469686031342</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>1.07700002193451</v>
       </c>
       <c r="G159" t="n">
-        <v>1.02353358268738</v>
+        <v>1.02353346347809</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>1.03299999237061</v>
       </c>
       <c r="G162" t="n">
-        <v>0.981717765331268</v>
+        <v>0.981717824935913</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G164" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G165" t="n">
-        <v>0.963661134243011</v>
+        <v>0.963661074638367</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.01699995994568</v>
       </c>
       <c r="G167" t="n">
-        <v>0.966512143611908</v>
+        <v>0.966512203216553</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>1.02300000190735</v>
       </c>
       <c r="G168" t="n">
-        <v>0.97221428155899</v>
+        <v>0.972214341163635</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G169" t="n">
-        <v>0.986469626426697</v>
+        <v>0.986469686031342</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G172" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G173" t="n">
-        <v>1.00547683238983</v>
+        <v>1.00547671318054</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G177" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G181" t="n">
-        <v>1.07295203208923</v>
+        <v>1.07295191287994</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G182" t="n">
-        <v>1.07295203208923</v>
+        <v>1.07295191287994</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.12100005149841</v>
       </c>
       <c r="G183" t="n">
-        <v>1.06534922122955</v>
+        <v>1.06534934043884</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G188" t="n">
-        <v>1.03588819503784</v>
+        <v>1.03588807582855</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G189" t="n">
-        <v>1.00072491168976</v>
+        <v>1.00072503089905</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G190" t="n">
-        <v>1.00262570381165</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>1.03299999237061</v>
       </c>
       <c r="G195" t="n">
-        <v>0.981717765331268</v>
+        <v>0.981717824935913</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G196" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G197" t="n">
-        <v>0.989320755004883</v>
+        <v>0.989320635795593</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>1.03299999237061</v>
       </c>
       <c r="G198" t="n">
-        <v>0.981717765331268</v>
+        <v>0.981717824935913</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G199" t="n">
-        <v>0.986469626426697</v>
+        <v>0.986469686031342</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G200" t="n">
-        <v>0.984568893909454</v>
+        <v>0.984569013118744</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G202" t="n">
-        <v>0.963661134243011</v>
+        <v>0.963661074638367</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G203" t="n">
-        <v>0.984568893909454</v>
+        <v>0.984569013118744</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.01900005340576</v>
       </c>
       <c r="G213" t="n">
-        <v>0.968412935733795</v>
+        <v>0.96841287612915</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.01900005340576</v>
       </c>
       <c r="G214" t="n">
-        <v>0.968412935733795</v>
+        <v>0.96841287612915</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.01900005340576</v>
       </c>
       <c r="G216" t="n">
-        <v>0.968412935733795</v>
+        <v>0.96841287612915</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>1.00699996948242</v>
       </c>
       <c r="G218" t="n">
-        <v>0.957008540630341</v>
+        <v>0.957008600234985</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>1.02638471126556</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G230" t="n">
-        <v>0.984568893909454</v>
+        <v>0.984569013118744</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G231" t="n">
-        <v>0.984568893909454</v>
+        <v>0.984569013118744</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>0.998499989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>0.948930561542511</v>
+        <v>0.948930621147156</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>0.982500016689301</v>
       </c>
       <c r="G233" t="n">
-        <v>0.933724820613861</v>
+        <v>0.933724880218506</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G235" t="n">
-        <v>0.989320755004883</v>
+        <v>0.989320635795593</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>1</v>
       </c>
       <c r="G240" t="n">
-        <v>0.950356066226959</v>
+        <v>0.950356125831604</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G242" t="n">
-        <v>1.00262570381165</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>1.03299999237061</v>
       </c>
       <c r="G243" t="n">
-        <v>0.981717765331268</v>
+        <v>0.981717824935913</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>1.00100004673004</v>
       </c>
       <c r="G246" t="n">
-        <v>0.951306462287903</v>
+        <v>0.951306402683258</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G247" t="n">
-        <v>0.984568893909454</v>
+        <v>0.984569013118744</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G252" t="n">
-        <v>0.963661134243011</v>
+        <v>0.963661074638367</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G256" t="n">
-        <v>1.01688098907471</v>
+        <v>1.016881108284</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G257" t="n">
-        <v>0.989320755004883</v>
+        <v>0.989320635795593</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G258" t="n">
-        <v>0.983618557453156</v>
+        <v>0.9836186170578</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G259" t="n">
-        <v>0.984568893909454</v>
+        <v>0.984569013118744</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G262" t="n">
-        <v>1.17654097080231</v>
+        <v>1.17654085159302</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>1.40652704238892</v>
+        <v>1.40652716159821</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>1.37699997425079</v>
       </c>
       <c r="G267" t="n">
-        <v>1.30864036083221</v>
+        <v>1.30864024162292</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>1.36099994182587</v>
       </c>
       <c r="G277" t="n">
-        <v>1.29343461990356</v>
+        <v>1.29343450069427</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>1.31099998950958</v>
       </c>
       <c r="G280" t="n">
-        <v>1.24591672420502</v>
+        <v>1.24591684341431</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>1.09766125679016</v>
+        <v>1.09766113758087</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G296" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G306" t="n">
-        <v>1.15753376483917</v>
+        <v>1.15753388404846</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>1.14042735099792</v>
+        <v>1.14042747020721</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G317" t="n">
-        <v>1.12522161006927</v>
+        <v>1.12522172927856</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G318" t="n">
-        <v>1.12902307510376</v>
+        <v>1.12902295589447</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G319" t="n">
-        <v>1.13472521305084</v>
+        <v>1.13472509384155</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G327" t="n">
-        <v>1.13472521305084</v>
+        <v>1.13472509384155</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G328" t="n">
-        <v>1.12807273864746</v>
+        <v>1.12807285785675</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G329" t="n">
-        <v>1.12902307510376</v>
+        <v>1.12902295589447</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G331" t="n">
-        <v>1.13472521305084</v>
+        <v>1.13472509384155</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G344" t="n">
-        <v>1.10811507701874</v>
+        <v>1.10811519622803</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G349" t="n">
-        <v>1.12522161006927</v>
+        <v>1.12522172927856</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G353" t="n">
-        <v>1.07770371437073</v>
+        <v>1.07770383358002</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G354" t="n">
-        <v>1.07865417003632</v>
+        <v>1.07865428924561</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G357" t="n">
-        <v>1.07010114192963</v>
+        <v>1.07010102272034</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G360" t="n">
-        <v>1.04919302463531</v>
+        <v>1.0491931438446</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G362" t="n">
-        <v>1.09956204891205</v>
+        <v>1.09956192970276</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G363" t="n">
-        <v>1.07865417003632</v>
+        <v>1.07865428924561</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G366" t="n">
-        <v>1.04919302463531</v>
+        <v>1.0491931438446</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G367" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.12100005149841</v>
       </c>
       <c r="G370" t="n">
-        <v>1.06534922122955</v>
+        <v>1.06534934043884</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.10099995136261</v>
       </c>
       <c r="G371" t="n">
-        <v>1.04634201526642</v>
+        <v>1.04634213447571</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G372" t="n">
-        <v>1.0510938167572</v>
+        <v>1.05109369754791</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G373" t="n">
-        <v>1.0510938167572</v>
+        <v>1.05109369754791</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G384" t="n">
-        <v>1.09290945529938</v>
+        <v>1.09290957450867</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G386" t="n">
-        <v>1.12902307510376</v>
+        <v>1.12902295589447</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G388" t="n">
-        <v>1.14042735099792</v>
+        <v>1.14042747020721</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G392" t="n">
-        <v>1.17464005947113</v>
+        <v>1.17464017868042</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G393" t="n">
-        <v>1.14042735099792</v>
+        <v>1.14042747020721</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G396" t="n">
-        <v>1.14232790470123</v>
+        <v>1.14232802391052</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>1.14042735099792</v>
+        <v>1.14042747020721</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G402" t="n">
-        <v>1.14042735099792</v>
+        <v>1.14042747020721</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G404" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G409" t="n">
-        <v>1.11476767063141</v>
+        <v>1.11476755142212</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>1.15299999713898</v>
       </c>
       <c r="G410" t="n">
-        <v>1.09576046466827</v>
+        <v>1.09576058387756</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G418" t="n">
-        <v>1.11096620559692</v>
+        <v>1.11096632480621</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G424" t="n">
-        <v>1.16133522987366</v>
+        <v>1.16133511066437</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G428" t="n">
-        <v>1.12902307510376</v>
+        <v>1.12902295589447</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G431" t="n">
-        <v>1.13472521305084</v>
+        <v>1.13472509384155</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G436" t="n">
-        <v>1.11476767063141</v>
+        <v>1.11476755142212</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G437" t="n">
-        <v>1.12522161006927</v>
+        <v>1.12522172927856</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>1.12522161006927</v>
+        <v>1.12522172927856</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>1.20700001716614</v>
       </c>
       <c r="G449" t="n">
-        <v>1.14707982540131</v>
+        <v>1.14707970619202</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G453" t="n">
-        <v>1.20505154132843</v>
+        <v>1.20505166053772</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G455" t="n">
-        <v>1.16133522987366</v>
+        <v>1.16133511066437</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G457" t="n">
-        <v>1.17273926734924</v>
+        <v>1.17273938655853</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G459" t="n">
-        <v>1.17654097080231</v>
+        <v>1.17654085159302</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G461" t="n">
-        <v>1.17464005947113</v>
+        <v>1.17464017868042</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G471" t="n">
-        <v>1.19364738464355</v>
+        <v>1.19364726543427</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G478" t="n">
-        <v>1.16703736782074</v>
+        <v>1.16703724861145</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G479" t="n">
-        <v>1.11476767063141</v>
+        <v>1.11476755142212</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G487" t="n">
-        <v>1.13472521305084</v>
+        <v>1.13472509384155</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G495" t="n">
-        <v>1.11476767063141</v>
+        <v>1.11476755142212</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G497" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G498" t="n">
-        <v>1.11096620559692</v>
+        <v>1.11096632480621</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G499" t="n">
-        <v>1.11096620559692</v>
+        <v>1.11096632480621</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G500" t="n">
-        <v>1.11096620559692</v>
+        <v>1.11096632480621</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G501" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G509" t="n">
-        <v>1.11096620559692</v>
+        <v>1.11096632480621</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G511" t="n">
-        <v>1.13187408447266</v>
+        <v>1.13187396526337</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G520" t="n">
-        <v>1.09766125679016</v>
+        <v>1.09766113758087</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G522" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G526" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G527" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G528" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G529" t="n">
-        <v>1.09290945529938</v>
+        <v>1.09290957450867</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G532" t="n">
-        <v>1.09290945529938</v>
+        <v>1.09290957450867</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G533" t="n">
-        <v>1.09290945529938</v>
+        <v>1.09290957450867</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G534" t="n">
-        <v>1.09290945529938</v>
+        <v>1.09290957450867</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G535" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G543" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G550" t="n">
-        <v>1.04063987731934</v>
+        <v>1.04063999652863</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G551" t="n">
-        <v>1.07865417003632</v>
+        <v>1.07865428924561</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>1.03113639354706</v>
+        <v>1.03113651275635</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G562" t="n">
-        <v>1.04063987731934</v>
+        <v>1.04063999652863</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G563" t="n">
-        <v>1.03588819503784</v>
+        <v>1.03588807582855</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G564" t="n">
-        <v>1.04063987731934</v>
+        <v>1.04063999652863</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G567" t="n">
-        <v>1.07865417003632</v>
+        <v>1.07865428924561</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G568" t="n">
-        <v>1.07865417003632</v>
+        <v>1.07865428924561</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G569" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G573" t="n">
-        <v>1.03113639354706</v>
+        <v>1.03113651275635</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G578" t="n">
-        <v>1.07865417003632</v>
+        <v>1.07865428924561</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G579" t="n">
-        <v>1.07865417003632</v>
+        <v>1.07865428924561</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G581" t="n">
-        <v>1.07865417003632</v>
+        <v>1.07865428924561</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G583" t="n">
-        <v>1.07865417003632</v>
+        <v>1.07865428924561</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G586" t="n">
-        <v>1.07865417003632</v>
+        <v>1.07865428924561</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G588" t="n">
-        <v>1.04063987731934</v>
+        <v>1.04063999652863</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>1.03113639354706</v>
+        <v>1.03113651275635</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G591" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G592" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>1.03113639354706</v>
+        <v>1.03113651275635</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G595" t="n">
-        <v>1.02638471126556</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G597" t="n">
-        <v>1.02638471126556</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G598" t="n">
-        <v>1.01688098907471</v>
+        <v>1.016881108284</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G599" t="n">
-        <v>1.03588819503784</v>
+        <v>1.03588807582855</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G605" t="n">
-        <v>1.02638471126556</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G606" t="n">
-        <v>1.04063987731934</v>
+        <v>1.04063999652863</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G611" t="n">
-        <v>1.04063987731934</v>
+        <v>1.04063999652863</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G614" t="n">
-        <v>0.931349039077759</v>
+        <v>0.931348979473114</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G616" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>1</v>
       </c>
       <c r="G618" t="n">
-        <v>0.950356066226959</v>
+        <v>0.950356125831604</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1</v>
       </c>
       <c r="G621" t="n">
-        <v>0.950356066226959</v>
+        <v>0.950356125831604</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>1</v>
       </c>
       <c r="G625" t="n">
-        <v>0.950356066226959</v>
+        <v>0.950356125831604</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G627" t="n">
-        <v>0.918043971061707</v>
+        <v>0.918044030666351</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G628" t="n">
-        <v>0.946554720401764</v>
+        <v>0.946554660797119</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G636" t="n">
-        <v>0.931349039077759</v>
+        <v>0.931348979473114</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G637" t="n">
-        <v>0.910441100597382</v>
+        <v>0.910441160202026</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G639" t="n">
-        <v>0.935150444507599</v>
+        <v>0.935150504112244</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G644" t="n">
-        <v>0.938951849937439</v>
+        <v>0.938951790332794</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G645" t="n">
-        <v>0.937051057815552</v>
+        <v>0.937051117420197</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G649" t="n">
-        <v>0.931349039077759</v>
+        <v>0.931348979473114</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G650" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G653" t="n">
-        <v>0.931349039077759</v>
+        <v>0.931348979473114</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G655" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G657" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G665" t="n">
-        <v>0.910441100597382</v>
+        <v>0.910441160202026</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G667" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G668" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G669" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G670" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G678" t="n">
-        <v>0.880029737949371</v>
+        <v>0.880029678344727</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G679" t="n">
-        <v>0.880029737949371</v>
+        <v>0.880029678344727</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G684" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G685" t="n">
-        <v>0.935150444507599</v>
+        <v>0.935150504112244</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G686" t="n">
-        <v>0.942753195762634</v>
+        <v>0.942753255367279</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>0.906639754772186</v>
+        <v>0.906639695167542</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G695" t="n">
-        <v>0.921845436096191</v>
+        <v>0.921845376491547</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G699" t="n">
-        <v>0.918043971061707</v>
+        <v>0.918044030666351</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G701" t="n">
-        <v>0.921845436096191</v>
+        <v>0.921845376491547</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G703" t="n">
-        <v>0.897136211395264</v>
+        <v>0.897136151790619</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G705" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G706" t="n">
-        <v>0.864824056625366</v>
+        <v>0.864823997020721</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G709" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114831924438</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G712" t="n">
-        <v>0.800199806690216</v>
+        <v>0.800199866294861</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G715" t="n">
-        <v>0.821107625961304</v>
+        <v>0.821107685565948</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G726" t="n">
-        <v>0.800199806690216</v>
+        <v>0.800199866294861</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G727" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>0.800199806690216</v>
+        <v>0.800199866294861</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G729" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G737" t="n">
-        <v>0.796398460865021</v>
+        <v>0.796398401260376</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G747" t="n">
-        <v>0.796398460865021</v>
+        <v>0.796398401260376</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G751" t="n">
-        <v>0.800199806690216</v>
+        <v>0.800199866294861</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>0.800199806690216</v>
+        <v>0.800199866294861</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G776" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G778" t="n">
-        <v>0.800199806690216</v>
+        <v>0.800199866294861</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G780" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G781" t="n">
-        <v>0.918043971061707</v>
+        <v>0.918044030666351</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G783" t="n">
-        <v>0.874327659606934</v>
+        <v>0.874327600002289</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G788" t="n">
-        <v>0.880029737949371</v>
+        <v>0.880029678344727</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G789" t="n">
-        <v>0.874327659606934</v>
+        <v>0.874327600002289</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G800" t="n">
-        <v>0.845816910266876</v>
+        <v>0.845816969871521</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G801" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G803" t="n">
-        <v>0.887632608413696</v>
+        <v>0.887632668018341</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>0.853419780731201</v>
+        <v>0.853419840335846</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G813" t="n">
-        <v>0.857221245765686</v>
+        <v>0.857221186161041</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G814" t="n">
-        <v>0.857221245765686</v>
+        <v>0.857221186161041</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G815" t="n">
-        <v>0.864824056625366</v>
+        <v>0.864823997020721</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G816" t="n">
-        <v>0.832511842250824</v>
+        <v>0.832511901855469</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G817" t="n">
-        <v>0.864824056625366</v>
+        <v>0.864823997020721</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G820" t="n">
-        <v>0.857221245765686</v>
+        <v>0.857221186161041</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G831" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G834" t="n">
-        <v>0.885731875896454</v>
+        <v>0.885731935501099</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G837" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G838" t="n">
-        <v>1.03588819503784</v>
+        <v>1.03588807582855</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G840" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1</v>
       </c>
       <c r="G842" t="n">
-        <v>0.950356066226959</v>
+        <v>0.950356125831604</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G848" t="n">
-        <v>0.964611351490021</v>
+        <v>0.964611411094666</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>1</v>
       </c>
       <c r="G849" t="n">
-        <v>0.950356066226959</v>
+        <v>0.950356125831604</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G850" t="n">
-        <v>0.938951849937439</v>
+        <v>0.938951790332794</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G851" t="n">
-        <v>0.931349039077759</v>
+        <v>0.931348979473114</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G852" t="n">
-        <v>0.942753195762634</v>
+        <v>0.942753255367279</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G853" t="n">
-        <v>0.931349039077759</v>
+        <v>0.931348979473114</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G855" t="n">
-        <v>0.910441100597382</v>
+        <v>0.910441160202026</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G857" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>0.931349039077759</v>
+        <v>0.931348979473114</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G862" t="n">
-        <v>0.897136211395264</v>
+        <v>0.897136151790619</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>1</v>
       </c>
       <c r="G863" t="n">
-        <v>0.950356066226959</v>
+        <v>0.950356125831604</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G864" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G866" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G869" t="n">
-        <v>0.887632608413696</v>
+        <v>0.887632668018341</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G870" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G871" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G873" t="n">
-        <v>0.885731875896454</v>
+        <v>0.885731935501099</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G874" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G875" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G876" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G877" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G878" t="n">
-        <v>0.881930470466614</v>
+        <v>0.881930410861969</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G879" t="n">
-        <v>0.880029737949371</v>
+        <v>0.880029678344727</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G880" t="n">
-        <v>0.874327659606934</v>
+        <v>0.874327600002289</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G884" t="n">
-        <v>0.880029737949371</v>
+        <v>0.880029678344727</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G886" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G891" t="n">
-        <v>0.857221245765686</v>
+        <v>0.857221186161041</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G894" t="n">
-        <v>0.864824056625366</v>
+        <v>0.864823997020721</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G895" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G896" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G897" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G902" t="n">
-        <v>0.853419780731201</v>
+        <v>0.853419840335846</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>0.853419780731201</v>
+        <v>0.853419840335846</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G905" t="n">
-        <v>0.845816910266876</v>
+        <v>0.845816969871521</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>0.853419780731201</v>
+        <v>0.853419840335846</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G908" t="n">
-        <v>0.845816910266876</v>
+        <v>0.845816969871521</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G909" t="n">
-        <v>0.845816910266876</v>
+        <v>0.845816969871521</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G910" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114831924438</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G916" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G917" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G918" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G919" t="n">
-        <v>0.845816910266876</v>
+        <v>0.845816969871521</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G920" t="n">
-        <v>0.845816910266876</v>
+        <v>0.845816969871521</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G921" t="n">
-        <v>0.845816910266876</v>
+        <v>0.845816969871521</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G923" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114831924438</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G924" t="n">
-        <v>0.887632608413696</v>
+        <v>0.887632668018341</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G926" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G928" t="n">
-        <v>0.885731875896454</v>
+        <v>0.885731935501099</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G929" t="n">
-        <v>0.885731875896454</v>
+        <v>0.885731935501099</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G930" t="n">
-        <v>0.921845436096191</v>
+        <v>0.921845376491547</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G931" t="n">
-        <v>0.937051057815552</v>
+        <v>0.937051117420197</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G932" t="n">
-        <v>0.942753195762634</v>
+        <v>0.942753255367279</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1</v>
       </c>
       <c r="G936" t="n">
-        <v>0.950356066226959</v>
+        <v>0.950356125831604</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G937" t="n">
-        <v>0.942753195762634</v>
+        <v>0.942753255367279</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G940" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G945" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G950" t="n">
-        <v>0.937051057815552</v>
+        <v>0.937051117420197</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1</v>
       </c>
       <c r="G951" t="n">
-        <v>0.950356066226959</v>
+        <v>0.950356125831604</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G952" t="n">
-        <v>0.942753195762634</v>
+        <v>0.942753255367279</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G953" t="n">
-        <v>0.935150444507599</v>
+        <v>0.935150504112244</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G954" t="n">
-        <v>0.910441100597382</v>
+        <v>0.910441160202026</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G955" t="n">
-        <v>0.918043971061707</v>
+        <v>0.918044030666351</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>0.953999996185303</v>
       </c>
       <c r="G957" t="n">
-        <v>0.906639754772186</v>
+        <v>0.906639695167542</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G958" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G959" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G962" t="n">
-        <v>0.897136211395264</v>
+        <v>0.897136151790619</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G963" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G964" t="n">
-        <v>0.897136211395264</v>
+        <v>0.897136151790619</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G966" t="n">
-        <v>0.897136211395264</v>
+        <v>0.897136151790619</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G967" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G968" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G969" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G970" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G971" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G972" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G973" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G974" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G975" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G978" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G990" t="n">
-        <v>0.935150444507599</v>
+        <v>0.935150504112244</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G991" t="n">
-        <v>0.931349039077759</v>
+        <v>0.931348979473114</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G994" t="n">
-        <v>0.964611351490021</v>
+        <v>0.964611411094666</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G995" t="n">
-        <v>0.964611351490021</v>
+        <v>0.964611411094666</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G996" t="n">
-        <v>0.983618557453156</v>
+        <v>0.9836186170578</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G997" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G998" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G999" t="n">
-        <v>0.964611351490021</v>
+        <v>0.964611411094666</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.983618557453156</v>
+        <v>0.9836186170578</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.03588819503784</v>
+        <v>1.03588807582855</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.02638471126556</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.03113639354706</v>
+        <v>1.03113651275635</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.03113639354706</v>
+        <v>1.03113651275635</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.03113639354706</v>
+        <v>1.03113651275635</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.01688098907471</v>
+        <v>1.016881108284</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.00262570381165</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.983618557453156</v>
+        <v>0.9836186170578</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.00262570381165</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.01688098907471</v>
+        <v>1.016881108284</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.00262570381165</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.03588819503784</v>
+        <v>1.03588807582855</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.09766125679016</v>
+        <v>1.09766113758087</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.07865417003632</v>
+        <v>1.07865428924561</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.03588819503784</v>
+        <v>1.03588807582855</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.983618557453156</v>
+        <v>0.9836186170578</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.937051057815552</v>
+        <v>0.937051117420197</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.938951849937439</v>
+        <v>0.938951790332794</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.771689116954803</v>
+        <v>0.771689057350159</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.817306280136108</v>
+        <v>0.817306220531464</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.842015564441681</v>
+        <v>0.842015504837036</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114831924438</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.817306280136108</v>
+        <v>0.817306220531464</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1080" t="n">
-        <v>0.845816910266876</v>
+        <v>0.845816969871521</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114831924438</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114831924438</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.845816910266876</v>
+        <v>0.845816969871521</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.842015564441681</v>
+        <v>0.842015504837036</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.817306280136108</v>
+        <v>0.817306220531464</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.817306280136108</v>
+        <v>0.817306220531464</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.817306280136108</v>
+        <v>0.817306220531464</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.821107625961304</v>
+        <v>0.821107685565948</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.864824056625366</v>
+        <v>0.864823997020721</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.832511842250824</v>
+        <v>0.832511901855469</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.842015564441681</v>
+        <v>0.842015504837036</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.842015564441681</v>
+        <v>0.842015504837036</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114831924438</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114831924438</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1136" t="n">
-        <v>0.845816910266876</v>
+        <v>0.845816969871521</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.845816910266876</v>
+        <v>0.845816969871521</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.845816910266876</v>
+        <v>0.845816969871521</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.832511842250824</v>
+        <v>0.832511901855469</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.857221245765686</v>
+        <v>0.857221186161041</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G1149" t="n">
-        <v>0.845816910266876</v>
+        <v>0.845816969871521</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.832511842250824</v>
+        <v>0.832511901855469</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.824909090995789</v>
+        <v>0.824909031391144</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.824909090995789</v>
+        <v>0.824909031391144</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.821107625961304</v>
+        <v>0.821107685565948</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.800199806690216</v>
+        <v>0.800199866294861</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.775490522384644</v>
+        <v>0.775490581989288</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.796398460865021</v>
+        <v>0.796398401260376</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.771689116954803</v>
+        <v>0.771689057350159</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1225" t="n">
-        <v>0.703263521194458</v>
+        <v>0.703263580799103</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.703263521194458</v>
+        <v>0.703263580799103</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582703113556</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582703113556</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.775490522384644</v>
+        <v>0.775490581989288</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.771689116954803</v>
+        <v>0.771689057350159</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.743178427219391</v>
+        <v>0.743178486824036</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1285" t="n">
-        <v>0.727972686290741</v>
+        <v>0.727972745895386</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1293" t="n">
-        <v>0.703263521194458</v>
+        <v>0.703263580799103</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.743178427219391</v>
+        <v>0.743178486824036</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.796398460865021</v>
+        <v>0.796398401260376</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582703113556</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582703113556</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.775490522384644</v>
+        <v>0.775490581989288</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582703113556</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1345" t="n">
-        <v>0.743178427219391</v>
+        <v>0.743178486824036</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1347" t="n">
-        <v>0.737476348876953</v>
+        <v>0.737476408481598</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582703113556</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.746979951858521</v>
+        <v>0.746979892253876</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.722270607948303</v>
+        <v>0.722270548343658</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.737476348876953</v>
+        <v>0.737476408481598</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1361" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.746979951858521</v>
+        <v>0.746979892253876</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.737476348876953</v>
+        <v>0.737476408481598</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1371" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1372" t="n">
-        <v>0.737476348876953</v>
+        <v>0.737476408481598</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1386" t="n">
-        <v>0.817306280136108</v>
+        <v>0.817306220531464</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.842015564441681</v>
+        <v>0.842015504837036</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.817306280136108</v>
+        <v>0.817306220531464</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.796398460865021</v>
+        <v>0.796398401260376</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.800199806690216</v>
+        <v>0.800199866294861</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.796398460865021</v>
+        <v>0.796398401260376</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1410" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582703113556</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1412" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.743178427219391</v>
+        <v>0.743178486824036</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.771689116954803</v>
+        <v>0.771689057350159</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.746979951858521</v>
+        <v>0.746979892253876</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582703113556</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.743178427219391</v>
+        <v>0.743178486824036</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.746979951858521</v>
+        <v>0.746979892253876</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.775490522384644</v>
+        <v>0.775490581989288</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.746979951858521</v>
+        <v>0.746979892253876</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1454" t="n">
-        <v>0.743178427219391</v>
+        <v>0.743178486824036</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1455" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582703113556</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582703113556</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1457" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582703113556</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.746979951858521</v>
+        <v>0.746979892253876</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582703113556</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.737476348876953</v>
+        <v>0.737476408481598</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1463" t="n">
-        <v>0.743178427219391</v>
+        <v>0.743178486824036</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1464" t="n">
-        <v>0.743178427219391</v>
+        <v>0.743178486824036</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1466" t="n">
-        <v>0.727972686290741</v>
+        <v>0.727972745895386</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.737476348876953</v>
+        <v>0.737476408481598</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.718469142913818</v>
+        <v>0.718469202518463</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.727972686290741</v>
+        <v>0.727972745895386</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1472" t="n">
-        <v>0.737476348876953</v>
+        <v>0.737476408481598</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.722270607948303</v>
+        <v>0.722270548343658</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1490" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1491" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1492" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1496" t="n">
-        <v>0.727972686290741</v>
+        <v>0.727972745895386</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.710866332054138</v>
+        <v>0.710866391658783</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>0.765999972820282</v>
       </c>
       <c r="G1501" t="n">
-        <v>0.727972686290741</v>
+        <v>0.727972745895386</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.710866332054138</v>
+        <v>0.710866391658783</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1504" t="n">
-        <v>0.714667797088623</v>
+        <v>0.714667737483978</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1506" t="n">
-        <v>0.703263521194458</v>
+        <v>0.703263580799103</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.703263521194458</v>
+        <v>0.703263580799103</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.703263521194458</v>
+        <v>0.703263580799103</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.714667797088623</v>
+        <v>0.714667737483978</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.710866332054138</v>
+        <v>0.710866391658783</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1521" t="n">
-        <v>0.710866332054138</v>
+        <v>0.710866391658783</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1523" t="n">
-        <v>0.688057780265808</v>
+        <v>0.688057720661163</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.699462115764618</v>
+        <v>0.699462056159973</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1530" t="n">
-        <v>0.688057780265808</v>
+        <v>0.688057720661163</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.688057780265808</v>
+        <v>0.688057720661163</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1541" t="n">
-        <v>0.688057780265808</v>
+        <v>0.688057720661163</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.699462115764618</v>
+        <v>0.699462056159973</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.695660650730133</v>
+        <v>0.695660710334778</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1551" t="n">
-        <v>0.686157047748566</v>
+        <v>0.68615710735321</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1552" t="n">
-        <v>0.688057780265808</v>
+        <v>0.688057720661163</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1553" t="n">
-        <v>0.680455029010773</v>
+        <v>0.680454969406128</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1555" t="n">
-        <v>0.680455029010773</v>
+        <v>0.680454969406128</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1556" t="n">
-        <v>0.680455029010773</v>
+        <v>0.680454969406128</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.686157047748566</v>
+        <v>0.68615710735321</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1567" t="n">
-        <v>0.703263521194458</v>
+        <v>0.703263580799103</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1569" t="n">
-        <v>0.6557457447052</v>
+        <v>0.655745685100555</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.627234995365143</v>
+        <v>0.627235054969788</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1578" t="n">
-        <v>0.703263521194458</v>
+        <v>0.703263580799103</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1579" t="n">
-        <v>0.670951366424561</v>
+        <v>0.670951426029205</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1591" t="n">
-        <v>0.64814293384552</v>
+        <v>0.648142874240875</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1592" t="n">
-        <v>0.64814293384552</v>
+        <v>0.648142874240875</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.627234995365143</v>
+        <v>0.627235054969788</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1599" t="n">
-        <v>0.627234995365143</v>
+        <v>0.627235054969788</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.627234995365143</v>
+        <v>0.627235054969788</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1628" t="n">
-        <v>0.627234995365143</v>
+        <v>0.627235054969788</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1635" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1636" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1643" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252583026886</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1645" t="n">
-        <v>0.594922840595245</v>
+        <v>0.59492290019989</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1647" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1652" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1653" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1654" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.524596512317657</v>
+        <v>0.524596571922302</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1685" t="n">
-        <v>0.594922840595245</v>
+        <v>0.59492290019989</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252583026886</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252583026886</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252583026886</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1692" t="n">
-        <v>0.594922840595245</v>
+        <v>0.59492290019989</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252583026886</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1713" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1716" t="n">
-        <v>0.56451153755188</v>
+        <v>0.564511477947235</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1730" t="n">
-        <v>0.594922840595245</v>
+        <v>0.59492290019989</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1731" t="n">
-        <v>0.594922840595245</v>
+        <v>0.59492290019989</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1734" t="n">
-        <v>0.594922840595245</v>
+        <v>0.59492290019989</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1735" t="n">
-        <v>0.594922840595245</v>
+        <v>0.59492290019989</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1741" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.56451153755188</v>
+        <v>0.564511477947235</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1756" t="n">
-        <v>0.58351868391037</v>
+        <v>0.583518624305725</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1759" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1767" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252583026886</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252583026886</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1776" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1786" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1787" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1791" t="n">
-        <v>0.58351868391037</v>
+        <v>0.583518624305725</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1793" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47221,7 +47221,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1802" t="n">
-        <v>0.594922840595245</v>
+        <v>0.59492290019989</v>
       </c>
       <c r="H1802" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1807" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1808" t="n">
-        <v>0.58351868391037</v>
+        <v>0.583518624305725</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1817" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1820" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1823" t="n">
-        <v>0.58351868391037</v>
+        <v>0.583518624305725</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47897,7 +47897,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1828" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1828" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1830" t="n">
-        <v>0.58351868391037</v>
+        <v>0.583518624305725</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1842" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1847" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1848" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1858" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1859" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48963,7 +48963,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1869" t="n">
-        <v>0.58351868391037</v>
+        <v>0.583518624305725</v>
       </c>
       <c r="H1869" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1870" t="n">
-        <v>0.58351868391037</v>
+        <v>0.583518624305725</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.56451153755188</v>
+        <v>0.564511477947235</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49249,7 +49249,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1880" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1880" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1881" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1882" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1898" t="n">
-        <v>0.56451153755188</v>
+        <v>0.564511477947235</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1906" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1907" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1908" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1912" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1913" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1921" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1922" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50549,7 +50549,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1930" t="n">
-        <v>0.594922840595245</v>
+        <v>0.59492290019989</v>
       </c>
       <c r="H1930" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1934" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50731,7 +50731,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1937" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1937" t="s">
         <v>8</v>
@@ -50783,7 +50783,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1939" t="n">
-        <v>0.58351868391037</v>
+        <v>0.583518624305725</v>
       </c>
       <c r="H1939" t="s">
         <v>8</v>
@@ -51303,7 +51303,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1959" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1961" t="n">
-        <v>0.56451153755188</v>
+        <v>0.564511477947235</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1963" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>1.24000000953674</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>31739</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>1.26999998092651</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>1.2150000333786</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>1.24000000953674</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>1.18499994277954</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>1.22000002861023</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>108437</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>1.18499994277954</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>1.18499994277954</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>1.18499994277954</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>1.25</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>14396</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>1.22500002384186</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>1.22500002384186</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>1.21000003814697</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>23210</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>1.23500001430511</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>1.23500001430511</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>1.23500001430511</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>1.23000001907349</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>22124</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>1.22500002384186</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>1.20500004291534</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>6900</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>1.2150000333786</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>1.20000004768372</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>1.2150000333786</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -447,7 +447,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G3" t="n">
-        <v>1.55858397483826</v>
+        <v>1.55858409404755</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G4" t="n">
-        <v>1.56808757781982</v>
+        <v>1.56808745861053</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G8" t="n">
-        <v>1.49205923080444</v>
+        <v>1.49205911159515</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G11" t="n">
-        <v>1.34000205993652</v>
+        <v>1.34000217914581</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>1.26872551441193</v>
+        <v>1.26872539520264</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G19" t="n">
-        <v>1.36851274967194</v>
+        <v>1.36851286888123</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G22" t="n">
-        <v>1.32669711112976</v>
+        <v>1.32669699192047</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G28" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G30" t="n">
-        <v>1.13662576675415</v>
+        <v>1.13662588596344</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G40" t="n">
-        <v>1.3114914894104</v>
+        <v>1.31149137020111</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G41" t="n">
-        <v>1.3114914894104</v>
+        <v>1.31149137020111</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G42" t="n">
-        <v>1.29723620414734</v>
+        <v>1.29723608493805</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G43" t="n">
-        <v>1.3114914894104</v>
+        <v>1.31149137020111</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G45" t="n">
-        <v>1.32099497318268</v>
+        <v>1.32099509239197</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>1.28773248195648</v>
+        <v>1.28773260116577</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G52" t="n">
-        <v>1.32194542884827</v>
+        <v>1.32194530963898</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G53" t="n">
-        <v>1.32194542884827</v>
+        <v>1.32194530963898</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G54" t="n">
-        <v>1.32099497318268</v>
+        <v>1.32099509239197</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G62" t="n">
-        <v>1.26207280158997</v>
+        <v>1.26207292079926</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G68" t="n">
-        <v>1.30578935146332</v>
+        <v>1.30578923225403</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G69" t="n">
-        <v>1.30578935146332</v>
+        <v>1.30578923225403</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G70" t="n">
-        <v>1.24781763553619</v>
+        <v>1.2478175163269</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G72" t="n">
-        <v>1.30483889579773</v>
+        <v>1.30483901500702</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G73" t="n">
-        <v>1.29058349132538</v>
+        <v>1.29058361053467</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.32700002193451</v>
       </c>
       <c r="G77" t="n">
-        <v>1.26112258434296</v>
+        <v>1.26112270355225</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G83" t="n">
-        <v>1.26207280158997</v>
+        <v>1.26207292079926</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G84" t="n">
-        <v>1.27347719669342</v>
+        <v>1.27347707748413</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G85" t="n">
-        <v>1.26207280158997</v>
+        <v>1.26207292079926</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G88" t="n">
-        <v>1.26207280158997</v>
+        <v>1.26207292079926</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G89" t="n">
-        <v>1.30483889579773</v>
+        <v>1.30483901500702</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G93" t="n">
-        <v>1.23546278476715</v>
+        <v>1.23546290397644</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G96" t="n">
-        <v>1.19744873046875</v>
+        <v>1.19744884967804</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G98" t="n">
-        <v>1.1803423166275</v>
+        <v>1.18034219741821</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G99" t="n">
-        <v>1.1803423166275</v>
+        <v>1.18034219741821</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G101" t="n">
-        <v>1.19744873046875</v>
+        <v>1.19744884967804</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>1.25899994373322</v>
       </c>
       <c r="G102" t="n">
-        <v>1.19649827480316</v>
+        <v>1.19649839401245</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G106" t="n">
-        <v>1.1784416437149</v>
+        <v>1.17844152450562</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G107" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749106884003</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G108" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749106884003</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G123" t="n">
-        <v>1.13662576675415</v>
+        <v>1.13662588596344</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G130" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G131" t="n">
-        <v>1.09005844593048</v>
+        <v>1.09005832672119</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G135" t="n">
-        <v>1.00547671318054</v>
+        <v>1.00547683238983</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G138" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873723506927</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G140" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873723506927</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G141" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873723506927</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>1.01300001144409</v>
       </c>
       <c r="G142" t="n">
-        <v>0.962710738182068</v>
+        <v>0.962710797786713</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>1.01300001144409</v>
       </c>
       <c r="G143" t="n">
-        <v>0.962710738182068</v>
+        <v>0.962710797786713</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>1.01300001144409</v>
       </c>
       <c r="G144" t="n">
-        <v>0.962710738182068</v>
+        <v>0.962710797786713</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G146" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G160" t="n">
-        <v>1.02163279056549</v>
+        <v>1.02163290977478</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G164" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G165" t="n">
-        <v>0.963661193847656</v>
+        <v>0.963661253452301</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G166" t="n">
-        <v>0.967462539672852</v>
+        <v>0.967462480068207</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>1.01699995994568</v>
       </c>
       <c r="G167" t="n">
-        <v>0.966512143611908</v>
+        <v>0.966512084007263</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G172" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G173" t="n">
-        <v>1.00547671318054</v>
+        <v>1.00547683238983</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G175" t="n">
-        <v>1.0520441532135</v>
+        <v>1.05204427242279</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G177" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G178" t="n">
-        <v>1.15183174610138</v>
+        <v>1.15183162689209</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>1.12100005149841</v>
       </c>
       <c r="G183" t="n">
-        <v>1.06534934043884</v>
+        <v>1.06534922122955</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>1.10800004005432</v>
       </c>
       <c r="G186" t="n">
-        <v>1.05299460887909</v>
+        <v>1.05299472808838</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G196" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G197" t="n">
-        <v>0.989320635795593</v>
+        <v>0.989320755004883</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G200" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G202" t="n">
-        <v>0.963661193847656</v>
+        <v>0.963661253452301</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G203" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G210" t="n">
-        <v>0.971263945102692</v>
+        <v>0.971263885498047</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>1.01900005340576</v>
       </c>
       <c r="G213" t="n">
-        <v>0.968412935733795</v>
+        <v>0.96841287612915</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>1.01900005340576</v>
       </c>
       <c r="G214" t="n">
-        <v>0.968412935733795</v>
+        <v>0.96841287612915</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>1.01900005340576</v>
       </c>
       <c r="G216" t="n">
-        <v>0.968412935733795</v>
+        <v>0.96841287612915</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G217" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G222" t="n">
-        <v>0.971263945102692</v>
+        <v>0.971263885498047</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>1.02638471126556</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G225" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G226" t="n">
-        <v>0.961760342121124</v>
+        <v>0.961760401725769</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G227" t="n">
-        <v>0.967462539672852</v>
+        <v>0.967462480068207</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G230" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G231" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>0.998499989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>0.948930561542511</v>
+        <v>0.948930501937866</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>0.982500016689301</v>
       </c>
       <c r="G233" t="n">
-        <v>0.933724880218506</v>
+        <v>0.933724820613861</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G235" t="n">
-        <v>0.989320635795593</v>
+        <v>0.989320755004883</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G237" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G239" t="n">
-        <v>0.961760342121124</v>
+        <v>0.961760401725769</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G247" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G251" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G252" t="n">
-        <v>0.963661193847656</v>
+        <v>0.963661253452301</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G253" t="n">
-        <v>0.956058263778687</v>
+        <v>0.956058323383331</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G254" t="n">
-        <v>0.956058263778687</v>
+        <v>0.956058323383331</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G257" t="n">
-        <v>0.989320635795593</v>
+        <v>0.989320755004883</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G259" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G261" t="n">
-        <v>1.04254055023193</v>
+        <v>1.04254066944122</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G269" t="n">
-        <v>1.34000205993652</v>
+        <v>1.34000217914581</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G270" t="n">
-        <v>1.30008721351624</v>
+        <v>1.30008709430695</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G272" t="n">
-        <v>1.26777505874634</v>
+        <v>1.26777493953705</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>1.26872551441193</v>
+        <v>1.26872539520264</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G278" t="n">
-        <v>1.23546278476715</v>
+        <v>1.23546290397644</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G281" t="n">
-        <v>1.24781763553619</v>
+        <v>1.2478175163269</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G282" t="n">
-        <v>1.26207280158997</v>
+        <v>1.26207292079926</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G283" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749106884003</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G285" t="n">
-        <v>1.13947689533234</v>
+        <v>1.13947701454163</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G289" t="n">
-        <v>1.09005844593048</v>
+        <v>1.09005832672119</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>1.14100003242493</v>
       </c>
       <c r="G291" t="n">
-        <v>1.08435642719269</v>
+        <v>1.0843563079834</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G293" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G296" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G297" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>1.20695233345032</v>
+        <v>1.20695221424103</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G308" t="n">
-        <v>1.15943443775177</v>
+        <v>1.15943455696106</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G310" t="n">
-        <v>1.13662576675415</v>
+        <v>1.13662588596344</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G311" t="n">
-        <v>1.15183174610138</v>
+        <v>1.15183162689209</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G315" t="n">
-        <v>1.13282442092896</v>
+        <v>1.13282454013824</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G317" t="n">
-        <v>1.12522172927856</v>
+        <v>1.12522161006927</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G318" t="n">
-        <v>1.12902307510376</v>
+        <v>1.12902295589447</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G329" t="n">
-        <v>1.12902307510376</v>
+        <v>1.12902295589447</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G330" t="n">
-        <v>1.14612948894501</v>
+        <v>1.14612936973572</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G334" t="n">
-        <v>1.10621452331543</v>
+        <v>1.10621464252472</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G336" t="n">
-        <v>1.1166684627533</v>
+        <v>1.11666834354401</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G343" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G345" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G349" t="n">
-        <v>1.12522172927856</v>
+        <v>1.12522161006927</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G365" t="n">
-        <v>1.07960450649261</v>
+        <v>1.0796046257019</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>1.10899996757507</v>
       </c>
       <c r="G369" t="n">
-        <v>1.05394494533539</v>
+        <v>1.05394506454468</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>1.12100005149841</v>
       </c>
       <c r="G370" t="n">
-        <v>1.06534934043884</v>
+        <v>1.06534922122955</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>1.10099995136261</v>
       </c>
       <c r="G371" t="n">
-        <v>1.04634189605713</v>
+        <v>1.04634201526642</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>1.14100003242493</v>
       </c>
       <c r="G376" t="n">
-        <v>1.08435642719269</v>
+        <v>1.0843563079834</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G377" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716497898102</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>1.15900003910065</v>
       </c>
       <c r="G379" t="n">
-        <v>1.10146272182465</v>
+        <v>1.10146284103394</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G382" t="n">
-        <v>1.09005844593048</v>
+        <v>1.09005832672119</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G383" t="n">
-        <v>1.08340585231781</v>
+        <v>1.0834059715271</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G386" t="n">
-        <v>1.12902307510376</v>
+        <v>1.12902295589447</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G387" t="n">
-        <v>1.11001586914062</v>
+        <v>1.11001598834991</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G389" t="n">
-        <v>1.13947689533234</v>
+        <v>1.13947701454163</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G390" t="n">
-        <v>1.13947689533234</v>
+        <v>1.13947701454163</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G392" t="n">
-        <v>1.17464017868042</v>
+        <v>1.17464005947113</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G396" t="n">
-        <v>1.14232790470123</v>
+        <v>1.14232802391052</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G398" t="n">
-        <v>1.13947689533234</v>
+        <v>1.13947701454163</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G404" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716497898102</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716497898102</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G409" t="n">
-        <v>1.1147677898407</v>
+        <v>1.11476767063141</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>1.15299999713898</v>
       </c>
       <c r="G410" t="n">
-        <v>1.09576046466827</v>
+        <v>1.09576058387756</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G412" t="n">
-        <v>1.11951947212219</v>
+        <v>1.1195193529129</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G413" t="n">
-        <v>1.1138174533844</v>
+        <v>1.11381733417511</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G414" t="n">
-        <v>1.10621452331543</v>
+        <v>1.10621464252472</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G415" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G419" t="n">
-        <v>1.10621452331543</v>
+        <v>1.10621464252472</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G420" t="n">
-        <v>1.11951947212219</v>
+        <v>1.1195193529129</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G428" t="n">
-        <v>1.12902307510376</v>
+        <v>1.12902295589447</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G436" t="n">
-        <v>1.1147677898407</v>
+        <v>1.11476767063141</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G437" t="n">
-        <v>1.12522172927856</v>
+        <v>1.12522161006927</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>1.12522172927856</v>
+        <v>1.12522161006927</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G444" t="n">
-        <v>1.11001586914062</v>
+        <v>1.11001598834991</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716497898102</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G447" t="n">
-        <v>1.1860443353653</v>
+        <v>1.18604445457458</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G453" t="n">
-        <v>1.20505166053772</v>
+        <v>1.20505154132843</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G460" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749106884003</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G461" t="n">
-        <v>1.17464017868042</v>
+        <v>1.17464005947113</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G464" t="n">
-        <v>1.19744873046875</v>
+        <v>1.19744884967804</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G465" t="n">
-        <v>1.1784416437149</v>
+        <v>1.17844152450562</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G469" t="n">
-        <v>1.1784416437149</v>
+        <v>1.17844152450562</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G472" t="n">
-        <v>1.1860443353653</v>
+        <v>1.18604445457458</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>1.20695233345032</v>
+        <v>1.20695221424103</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G476" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749106884003</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G479" t="n">
-        <v>1.1147677898407</v>
+        <v>1.11476767063141</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G480" t="n">
-        <v>1.13282442092896</v>
+        <v>1.13282454013824</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G481" t="n">
-        <v>1.11951947212219</v>
+        <v>1.1195193529129</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G484" t="n">
-        <v>1.15563309192657</v>
+        <v>1.15563297271729</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G486" t="n">
-        <v>1.1138174533844</v>
+        <v>1.11381733417511</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716497898102</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.16400003433228</v>
       </c>
       <c r="G494" t="n">
-        <v>1.10621452331543</v>
+        <v>1.10621464252472</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G495" t="n">
-        <v>1.1147677898407</v>
+        <v>1.11476767063141</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G496" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G497" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G501" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716497898102</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716497898102</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G512" t="n">
-        <v>1.1166684627533</v>
+        <v>1.11666834354401</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G517" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G518" t="n">
-        <v>1.1166684627533</v>
+        <v>1.11666834354401</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716497898102</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716497898102</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G522" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G523" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716497898102</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G526" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G527" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G528" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G530" t="n">
-        <v>1.1166684627533</v>
+        <v>1.11666834354401</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G535" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>1.125</v>
       </c>
       <c r="G537" t="n">
-        <v>1.06915056705475</v>
+        <v>1.06915068626404</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G538" t="n">
-        <v>1.08340585231781</v>
+        <v>1.0834059715271</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.08340585231781</v>
+        <v>1.0834059715271</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G554" t="n">
-        <v>1.02163279056549</v>
+        <v>1.02163290977478</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G558" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G566" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G570" t="n">
-        <v>1.08340585231781</v>
+        <v>1.0834059715271</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>1.125</v>
       </c>
       <c r="G571" t="n">
-        <v>1.06915056705475</v>
+        <v>1.06915068626404</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G572" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G577" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G595" t="n">
-        <v>1.02638471126556</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G596" t="n">
-        <v>1.02163279056549</v>
+        <v>1.02163290977478</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G597" t="n">
-        <v>1.02638471126556</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G601" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G602" t="n">
-        <v>1.02163279056549</v>
+        <v>1.02163290977478</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G603" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G605" t="n">
-        <v>1.02638471126556</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G608" t="n">
-        <v>1.02163279056549</v>
+        <v>1.02163290977478</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G610" t="n">
-        <v>1.0121294260025</v>
+        <v>1.01212930679321</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G612" t="n">
-        <v>1.02163279056549</v>
+        <v>1.02163290977478</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G616" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G617" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G619" t="n">
-        <v>0.974115014076233</v>
+        <v>0.974114954471588</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G620" t="n">
-        <v>0.974115014076233</v>
+        <v>0.974114954471588</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G640" t="n">
-        <v>0.929448306560516</v>
+        <v>0.929448246955872</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G641" t="n">
-        <v>0.929448306560516</v>
+        <v>0.929448246955872</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G650" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G658" t="n">
-        <v>0.900937616825104</v>
+        <v>0.900937557220459</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G660" t="n">
-        <v>0.908540368080139</v>
+        <v>0.908540427684784</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G666" t="n">
-        <v>0.908540368080139</v>
+        <v>0.908540427684784</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G670" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G683" t="n">
-        <v>0.868625462055206</v>
+        <v>0.868625521659851</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G686" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753314971924</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G694" t="n">
-        <v>0.929448306560516</v>
+        <v>0.929448246955872</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G695" t="n">
-        <v>0.921845436096191</v>
+        <v>0.921845495700836</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G700" t="n">
-        <v>0.929448306560516</v>
+        <v>0.929448246955872</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G701" t="n">
-        <v>0.921845436096191</v>
+        <v>0.921845495700836</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G703" t="n">
-        <v>0.897136151790619</v>
+        <v>0.897136211395264</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G707" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G723" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G725" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G730" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G734" t="n">
-        <v>0.804001212120056</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G735" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G736" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391374111176</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G742" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G756" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G757" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G758" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G763" t="n">
-        <v>0.790696263313293</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>0.790696263313293</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G765" t="n">
-        <v>0.790696263313293</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G769" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G770" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G771" t="n">
-        <v>0.790696263313293</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G772" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G773" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G774" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G783" t="n">
-        <v>0.874327659606934</v>
+        <v>0.874327600002289</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G786" t="n">
-        <v>0.868625462055206</v>
+        <v>0.868625521659851</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G789" t="n">
-        <v>0.874327659606934</v>
+        <v>0.874327600002289</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G790" t="n">
-        <v>0.868625462055206</v>
+        <v>0.868625521659851</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G791" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G792" t="n">
-        <v>0.861022651195526</v>
+        <v>0.861022591590881</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G803" t="n">
-        <v>0.887632608413696</v>
+        <v>0.887632548809052</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G807" t="n">
-        <v>0.868625462055206</v>
+        <v>0.868625521659851</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G810" t="n">
-        <v>0.861022651195526</v>
+        <v>0.861022591590881</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>0.853419721126556</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G819" t="n">
-        <v>0.861022651195526</v>
+        <v>0.861022591590881</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G821" t="n">
-        <v>0.861022651195526</v>
+        <v>0.861022591590881</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G825" t="n">
-        <v>0.861022651195526</v>
+        <v>0.861022591590881</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G826" t="n">
-        <v>0.861022651195526</v>
+        <v>0.861022591590881</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G834" t="n">
-        <v>0.885731875896454</v>
+        <v>0.885731816291809</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G837" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G840" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G841" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873723506927</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G844" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G846" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873723506927</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G847" t="n">
-        <v>0.974115014076233</v>
+        <v>0.974114954471588</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G848" t="n">
-        <v>0.96461147069931</v>
+        <v>0.964611530303955</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G852" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753314971924</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G862" t="n">
-        <v>0.897136151790619</v>
+        <v>0.897136211395264</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G868" t="n">
-        <v>0.900937616825104</v>
+        <v>0.900937557220459</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G869" t="n">
-        <v>0.887632608413696</v>
+        <v>0.887632548809052</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G871" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G873" t="n">
-        <v>0.885731875896454</v>
+        <v>0.885731816291809</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G878" t="n">
-        <v>0.881930410861969</v>
+        <v>0.881930470466614</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G880" t="n">
-        <v>0.874327659606934</v>
+        <v>0.874327600002289</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G888" t="n">
-        <v>0.861022651195526</v>
+        <v>0.861022591590881</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G898" t="n">
-        <v>0.868625462055206</v>
+        <v>0.868625521659851</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G902" t="n">
-        <v>0.853419721126556</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>0.853419721126556</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G906" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>0.853419721126556</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G915" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G924" t="n">
-        <v>0.887632608413696</v>
+        <v>0.887632548809052</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G927" t="n">
-        <v>0.908540368080139</v>
+        <v>0.908540427684784</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G928" t="n">
-        <v>0.885731875896454</v>
+        <v>0.885731816291809</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G929" t="n">
-        <v>0.885731875896454</v>
+        <v>0.885731816291809</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G930" t="n">
-        <v>0.921845436096191</v>
+        <v>0.921845495700836</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G932" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753314971924</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G933" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G935" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G937" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753314971924</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G942" t="n">
-        <v>0.908540368080139</v>
+        <v>0.908540427684784</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G943" t="n">
-        <v>0.900937616825104</v>
+        <v>0.900937557220459</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G945" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G947" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G952" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753314971924</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G959" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G962" t="n">
-        <v>0.897136151790619</v>
+        <v>0.897136211395264</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G963" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G964" t="n">
-        <v>0.897136151790619</v>
+        <v>0.897136211395264</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G965" t="n">
-        <v>0.900937616825104</v>
+        <v>0.900937557220459</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G966" t="n">
-        <v>0.897136151790619</v>
+        <v>0.897136211395264</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G967" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G968" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G970" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G972" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G973" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G974" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G975" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G976" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G978" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G979" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G981" t="n">
-        <v>0.993121981620789</v>
+        <v>0.993122100830078</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G983" t="n">
-        <v>0.974115014076233</v>
+        <v>0.974114954471588</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G985" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G988" t="n">
-        <v>0.974115014076233</v>
+        <v>0.974114954471588</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G994" t="n">
-        <v>0.96461147069931</v>
+        <v>0.964611530303955</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G995" t="n">
-        <v>0.96461147069931</v>
+        <v>0.964611530303955</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G997" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G998" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G999" t="n">
-        <v>0.96461147069931</v>
+        <v>0.964611530303955</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.974115014076233</v>
+        <v>0.974114954471588</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873723506927</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.0121294260025</v>
+        <v>1.01212930679321</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.02163279056549</v>
+        <v>1.02163290977478</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.02638471126556</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.0121294260025</v>
+        <v>1.01212930679321</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873723506927</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873723506927</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.993121981620789</v>
+        <v>0.993122100830078</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.993121981620789</v>
+        <v>0.993122100830078</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1030" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.993121981620789</v>
+        <v>0.993122100830078</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716497898102</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873723506927</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.08340585231781</v>
+        <v>1.0834059715271</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873723506927</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.974115014076233</v>
+        <v>0.974114954471588</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.804001212120056</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.804001212120056</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.790696263313293</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.861022651195526</v>
+        <v>0.861022591590881</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>0.906000018119812</v>
       </c>
       <c r="G1116" t="n">
-        <v>0.861022651195526</v>
+        <v>0.861022591590881</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.824909090995789</v>
+        <v>0.824909031391144</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.824909090995789</v>
+        <v>0.824909031391144</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.804001212120056</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.790696263313293</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.811604082584381</v>
+        <v>0.811604022979736</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.811604082584381</v>
+        <v>0.811604022979736</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.804001212120056</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391374111176</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391374111176</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.790696263313293</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391374111176</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.693759977817535</v>
+        <v>0.693759918212891</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391374111176</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.72036999464035</v>
+        <v>0.720369935035706</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.790696263313293</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391374111176</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391374111176</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1381" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G1396" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1405" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391374111176</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1406" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1412" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.72036999464035</v>
+        <v>0.720369935035706</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.710866332054138</v>
+        <v>0.710866391658783</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.710866332054138</v>
+        <v>0.710866391658783</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.710866332054138</v>
+        <v>0.710866391658783</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1521" t="n">
-        <v>0.710866332054138</v>
+        <v>0.710866391658783</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.693759977817535</v>
+        <v>0.693759918212891</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.693759977817535</v>
+        <v>0.693759918212891</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1535" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.693759977817535</v>
+        <v>0.693759918212891</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.693759977817535</v>
+        <v>0.693759918212891</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.693759977817535</v>
+        <v>0.693759918212891</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.684256374835968</v>
+        <v>0.684256434440613</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.684256374835968</v>
+        <v>0.684256434440613</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.684256374835968</v>
+        <v>0.684256434440613</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.684256374835968</v>
+        <v>0.684256434440613</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1551" t="n">
-        <v>0.686157047748566</v>
+        <v>0.68615710735321</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1553" t="n">
-        <v>0.680455029010773</v>
+        <v>0.680454969406128</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.66334855556488</v>
+        <v>0.663348495960236</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1555" t="n">
-        <v>0.680455029010773</v>
+        <v>0.680454969406128</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1556" t="n">
-        <v>0.680455029010773</v>
+        <v>0.680454969406128</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.672852098941803</v>
+        <v>0.672852158546448</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.686157047748566</v>
+        <v>0.68615710735321</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.693759977817535</v>
+        <v>0.693759918212891</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.676653563976288</v>
+        <v>0.676653504371643</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1569" t="n">
-        <v>0.6557457447052</v>
+        <v>0.655745685100555</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.657646358013153</v>
+        <v>0.657646417617798</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1571" t="n">
-        <v>0.650043606758118</v>
+        <v>0.650043547153473</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.617731392383575</v>
+        <v>0.61773145198822</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1579" t="n">
-        <v>0.670951366424561</v>
+        <v>0.670951426029205</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1581" t="n">
-        <v>0.657646358013153</v>
+        <v>0.657646417617798</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1582" t="n">
-        <v>0.650043606758118</v>
+        <v>0.650043547153473</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.650043606758118</v>
+        <v>0.650043547153473</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1586" t="n">
-        <v>0.644341349601746</v>
+        <v>0.64434140920639</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1590" t="n">
-        <v>0.650043606758118</v>
+        <v>0.650043547153473</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.644341349601746</v>
+        <v>0.64434140920639</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1600" t="n">
-        <v>0.63673859834671</v>
+        <v>0.636738538742065</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1603" t="n">
-        <v>0.63673859834671</v>
+        <v>0.636738538742065</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.631036400794983</v>
+        <v>0.631036460399628</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.617731392383575</v>
+        <v>0.61773145198822</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1639" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1643" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1648" t="n">
-        <v>0.566412210464478</v>
+        <v>0.566412270069122</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1649" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1650" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1651" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1654" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.543603718280792</v>
+        <v>0.543603658676147</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.497986555099487</v>
+        <v>0.497986495494843</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1661" t="n">
-        <v>0.541702926158905</v>
+        <v>0.54170298576355</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1666" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1670" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1673" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1676" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220762252808</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1698" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1699" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1705" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220762252808</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220762252808</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220762252808</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1713" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1716" t="n">
-        <v>0.56451153755188</v>
+        <v>0.564511477947235</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1719" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1721" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1722" t="n">
-        <v>0.579717218875885</v>
+        <v>0.57971727848053</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220762252808</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.579717218875885</v>
+        <v>0.57971727848053</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.579717218875885</v>
+        <v>0.57971727848053</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1741" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1743" t="n">
-        <v>0.57591587305069</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.57591587305069</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.56451153755188</v>
+        <v>0.564511477947235</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1759" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220762252808</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1765" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1767" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1768" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220762252808</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1774" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1777" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1779" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220762252808</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1782" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1783" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46753,7 +46753,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1784" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1784" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1785" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220762252808</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1786" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1788" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1789" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1795" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220762252808</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1796" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220762252808</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1797" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1798" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1799" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220762252808</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1805" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220762252808</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1806" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220762252808</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1807" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220762252808</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1811" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1813" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47559,7 +47559,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1815" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1816" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1818" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1821" t="n">
-        <v>0.57591587305069</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1825" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1827" t="n">
-        <v>0.579717218875885</v>
+        <v>0.57971727848053</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.57591587305069</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1837" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1841" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48287,7 +48287,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1843" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.579717218875885</v>
+        <v>0.57971727848053</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48365,7 +48365,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1846" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872442483902</v>
       </c>
       <c r="H1846" t="s">
         <v>8</v>
@@ -48391,7 +48391,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1847" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1847" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1848" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48547,7 +48547,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1853" t="n">
-        <v>0.566412210464478</v>
+        <v>0.566412270069122</v>
       </c>
       <c r="H1853" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1858" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1859" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1860" t="n">
-        <v>0.579717218875885</v>
+        <v>0.57971727848053</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1863" t="n">
-        <v>0.566412210464478</v>
+        <v>0.566412270069122</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1864" t="n">
-        <v>0.579717218875885</v>
+        <v>0.57971727848053</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48859,7 +48859,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1865" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1865" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1866" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1867" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.56451153755188</v>
+        <v>0.564511477947235</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1873" t="n">
-        <v>0.566412210464478</v>
+        <v>0.566412270069122</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1874" t="n">
-        <v>0.566412210464478</v>
+        <v>0.566412270069122</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1875" t="n">
-        <v>0.566412210464478</v>
+        <v>0.566412270069122</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1879" t="n">
-        <v>0.566412210464478</v>
+        <v>0.566412270069122</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.566412210464478</v>
+        <v>0.566412270069122</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49379,7 +49379,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1885" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49483,7 +49483,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1889" t="s">
         <v>8</v>
@@ -49509,7 +49509,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.566412210464478</v>
+        <v>0.566412270069122</v>
       </c>
       <c r="H1890" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1898" t="n">
-        <v>0.56451153755188</v>
+        <v>0.564511477947235</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1900" t="n">
-        <v>0.541702926158905</v>
+        <v>0.54170298576355</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1901" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49847,7 +49847,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1903" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1903" t="s">
         <v>8</v>
@@ -49873,7 +49873,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1904" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1904" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1906" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1907" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1908" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1910" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1911" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50081,7 +50081,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1912" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1912" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1913" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1914" t="n">
-        <v>0.553107261657715</v>
+        <v>0.55310732126236</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1915" t="n">
-        <v>0.541702926158905</v>
+        <v>0.54170298576355</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1916" t="n">
-        <v>0.539802253246307</v>
+        <v>0.539802312850952</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50211,7 +50211,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1917" t="n">
-        <v>0.543603718280792</v>
+        <v>0.543603658676147</v>
       </c>
       <c r="H1917" t="s">
         <v>8</v>
@@ -50237,7 +50237,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1918" t="n">
-        <v>0.539802253246307</v>
+        <v>0.539802312850952</v>
       </c>
       <c r="H1918" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1919" t="n">
-        <v>0.539802253246307</v>
+        <v>0.539802312850952</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1921" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1922" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1925" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1926" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50471,7 +50471,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1927" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1927" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1928" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1929" t="n">
-        <v>0.589220821857452</v>
+        <v>0.589220762252808</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50627,7 +50627,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1933" t="n">
-        <v>0.593022167682648</v>
+        <v>0.593022227287292</v>
       </c>
       <c r="H1933" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1934" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1936" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1938" t="n">
-        <v>0.579717218875885</v>
+        <v>0.57971727848053</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -50835,7 +50835,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1941" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1941" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1947" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1948" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1949" t="n">
-        <v>0.553107261657715</v>
+        <v>0.55310732126236</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1953" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51199,7 +51199,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1955" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1955" t="s">
         <v>8</v>
@@ -51225,7 +51225,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1956" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1956" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1957" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51277,7 +51277,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1958" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1958" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1960" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1961" t="n">
-        <v>0.56451153755188</v>
+        <v>0.564511477947235</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1963" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1965" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1966" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1967" t="n">
-        <v>0.553107261657715</v>
+        <v>0.55310732126236</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1969" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1970" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1971" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1972" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1973" t="n">
-        <v>0.566412210464478</v>
+        <v>0.566412270069122</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>1.22000002861023</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>3144</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>1.22500002384186</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>1.20500004291534</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>1.20500004291534</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>1.23000001907349</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>1.44454109668732</v>
+        <v>1.44454121589661</v>
       </c>
       <c r="H2" t="n">
         <v>5783</v>
@@ -485,7 +485,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G4" t="n">
-        <v>1.56808745861053</v>
+        <v>1.56808757781982</v>
       </c>
       <c r="H4" t="n">
         <v>7639</v>
@@ -601,7 +601,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G8" t="n">
-        <v>1.49205923080444</v>
+        <v>1.49205911159515</v>
       </c>
       <c r="H8" t="n">
         <v>9900</v>
@@ -775,7 +775,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>1.26872539520264</v>
+        <v>1.26872551441193</v>
       </c>
       <c r="H14" t="n">
         <v>17780</v>
@@ -920,7 +920,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G19" t="n">
-        <v>1.36851286888123</v>
+        <v>1.36851274967194</v>
       </c>
       <c r="H19" t="n">
         <v>6521</v>
@@ -1210,7 +1210,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G29" t="n">
-        <v>1.14137768745422</v>
+        <v>1.14137780666351</v>
       </c>
       <c r="H29" t="n">
         <v>1659</v>
@@ -1239,7 +1239,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G30" t="n">
-        <v>1.13662588596344</v>
+        <v>1.13662600517273</v>
       </c>
       <c r="H30" t="n">
         <v>1130</v>
@@ -1384,7 +1384,7 @@
         <v>1.35899996757507</v>
       </c>
       <c r="G35" t="n">
-        <v>1.29153394699097</v>
+        <v>1.29153406620026</v>
       </c>
       <c r="H35" t="n">
         <v>2501</v>
@@ -1471,7 +1471,7 @@
         <v>1.32400000095367</v>
       </c>
       <c r="G38" t="n">
-        <v>1.25827157497406</v>
+        <v>1.25827145576477</v>
       </c>
       <c r="H38" t="n">
         <v>12260</v>
@@ -1500,7 +1500,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G39" t="n">
-        <v>1.31719350814819</v>
+        <v>1.31719362735748</v>
       </c>
       <c r="H39" t="n">
         <v>13555</v>
@@ -1529,7 +1529,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G40" t="n">
-        <v>1.3114914894104</v>
+        <v>1.31149137020111</v>
       </c>
       <c r="H40" t="n">
         <v>13000</v>
@@ -1558,7 +1558,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G41" t="n">
-        <v>1.3114914894104</v>
+        <v>1.31149137020111</v>
       </c>
       <c r="H41" t="n">
         <v>9289</v>
@@ -1616,7 +1616,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G43" t="n">
-        <v>1.3114914894104</v>
+        <v>1.31149137020111</v>
       </c>
       <c r="H43" t="n">
         <v>65</v>
@@ -1645,7 +1645,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G44" t="n">
-        <v>1.32289564609528</v>
+        <v>1.32289552688599</v>
       </c>
       <c r="H44" t="n">
         <v>5423</v>
@@ -1674,7 +1674,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G45" t="n">
-        <v>1.32099497318268</v>
+        <v>1.32099509239197</v>
       </c>
       <c r="H45" t="n">
         <v>1400</v>
@@ -1703,7 +1703,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>1.28773248195648</v>
+        <v>1.28773260116577</v>
       </c>
       <c r="H46" t="n">
         <v>3247</v>
@@ -1877,7 +1877,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G52" t="n">
-        <v>1.32194530963898</v>
+        <v>1.32194542884827</v>
       </c>
       <c r="H52" t="n">
         <v>2834</v>
@@ -1906,7 +1906,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G53" t="n">
-        <v>1.32194530963898</v>
+        <v>1.32194542884827</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G54" t="n">
-        <v>1.32099497318268</v>
+        <v>1.32099509239197</v>
       </c>
       <c r="H54" t="n">
         <v>1500</v>
@@ -1964,7 +1964,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G55" t="n">
-        <v>1.27537786960602</v>
+        <v>1.27537798881531</v>
       </c>
       <c r="H55" t="n">
         <v>10250</v>
@@ -1993,7 +1993,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G56" t="n">
-        <v>1.27537786960602</v>
+        <v>1.27537798881531</v>
       </c>
       <c r="H56" t="n">
         <v>709</v>
@@ -2022,7 +2022,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G57" t="n">
-        <v>1.27537786960602</v>
+        <v>1.27537798881531</v>
       </c>
       <c r="H57" t="n">
         <v>36</v>
@@ -2051,7 +2051,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G58" t="n">
-        <v>1.26967573165894</v>
+        <v>1.26967561244965</v>
       </c>
       <c r="H58" t="n">
         <v>21406</v>
@@ -2080,7 +2080,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>1.32574665546417</v>
+        <v>1.32574677467346</v>
       </c>
       <c r="H59" t="n">
         <v>560</v>
@@ -2109,7 +2109,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G60" t="n">
-        <v>1.27537786960602</v>
+        <v>1.27537798881531</v>
       </c>
       <c r="H60" t="n">
         <v>6529</v>
@@ -2138,7 +2138,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G61" t="n">
-        <v>1.27157640457153</v>
+        <v>1.27157652378082</v>
       </c>
       <c r="H61" t="n">
         <v>1297</v>
@@ -2167,7 +2167,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G62" t="n">
-        <v>1.26207304000854</v>
+        <v>1.26207292079926</v>
       </c>
       <c r="H62" t="n">
         <v>2000</v>
@@ -2283,7 +2283,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G66" t="n">
-        <v>1.23926436901093</v>
+        <v>1.23926448822021</v>
       </c>
       <c r="H66" t="n">
         <v>12363</v>
@@ -2312,7 +2312,7 @@
         <v>1.29200005531311</v>
       </c>
       <c r="G67" t="n">
-        <v>1.22786009311676</v>
+        <v>1.22786021232605</v>
       </c>
       <c r="H67" t="n">
         <v>1650</v>
@@ -2399,7 +2399,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G70" t="n">
-        <v>1.2478175163269</v>
+        <v>1.24781739711761</v>
       </c>
       <c r="H70" t="n">
         <v>3528</v>
@@ -2515,7 +2515,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G74" t="n">
-        <v>1.27537786960602</v>
+        <v>1.27537798881531</v>
       </c>
       <c r="H74" t="n">
         <v>413</v>
@@ -2573,7 +2573,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G76" t="n">
-        <v>1.26967573165894</v>
+        <v>1.26967561244965</v>
       </c>
       <c r="H76" t="n">
         <v>8995</v>
@@ -2631,7 +2631,7 @@
         <v>1.34099996089935</v>
       </c>
       <c r="G78" t="n">
-        <v>1.27442753314972</v>
+        <v>1.27442741394043</v>
       </c>
       <c r="H78" t="n">
         <v>3828</v>
@@ -2660,7 +2660,7 @@
         <v>1.34700000286102</v>
       </c>
       <c r="G79" t="n">
-        <v>1.2801296710968</v>
+        <v>1.28012979030609</v>
       </c>
       <c r="H79" t="n">
         <v>6900</v>
@@ -2776,7 +2776,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G83" t="n">
-        <v>1.26207304000854</v>
+        <v>1.26207292079926</v>
       </c>
       <c r="H83" t="n">
         <v>22657</v>
@@ -2834,7 +2834,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G85" t="n">
-        <v>1.26207304000854</v>
+        <v>1.26207292079926</v>
       </c>
       <c r="H85" t="n">
         <v>4053</v>
@@ -2863,7 +2863,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G86" t="n">
-        <v>1.27537786960602</v>
+        <v>1.27537798881531</v>
       </c>
       <c r="H86" t="n">
         <v>1199</v>
@@ -2921,7 +2921,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G88" t="n">
-        <v>1.26207304000854</v>
+        <v>1.26207292079926</v>
       </c>
       <c r="H88" t="n">
         <v>2439</v>
@@ -3066,7 +3066,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G93" t="n">
-        <v>1.23546278476715</v>
+        <v>1.23546290397644</v>
       </c>
       <c r="H93" t="n">
         <v>7369</v>
@@ -3269,7 +3269,7 @@
         <v>1.25</v>
       </c>
       <c r="G100" t="n">
-        <v>1.18794524669647</v>
+        <v>1.18794512748718</v>
       </c>
       <c r="H100" t="n">
         <v>5981</v>
@@ -3414,7 +3414,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G105" t="n">
-        <v>1.17178916931152</v>
+        <v>1.17178905010223</v>
       </c>
       <c r="H105" t="n">
         <v>3950</v>
@@ -3472,7 +3472,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G107" t="n">
-        <v>1.17749106884003</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H107" t="n">
         <v>2700</v>
@@ -3501,7 +3501,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G108" t="n">
-        <v>1.17749106884003</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H108" t="n">
         <v>500</v>
@@ -3530,7 +3530,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G109" t="n">
-        <v>1.17559051513672</v>
+        <v>1.17559039592743</v>
       </c>
       <c r="H109" t="n">
         <v>2635</v>
@@ -3588,7 +3588,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G111" t="n">
-        <v>1.14803004264832</v>
+        <v>1.1480301618576</v>
       </c>
       <c r="H111" t="n">
         <v>30565</v>
@@ -3617,7 +3617,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G112" t="n">
-        <v>1.18224287033081</v>
+        <v>1.1822429895401</v>
       </c>
       <c r="H112" t="n">
         <v>3100</v>
@@ -3704,7 +3704,7 @@
         <v>1.11199998855591</v>
       </c>
       <c r="G115" t="n">
-        <v>1.056795835495</v>
+        <v>1.05679595470428</v>
       </c>
       <c r="H115" t="n">
         <v>8946</v>
@@ -3791,7 +3791,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G118" t="n">
-        <v>1.17273938655853</v>
+        <v>1.17273950576782</v>
       </c>
       <c r="H118" t="n">
         <v>632</v>
@@ -3936,7 +3936,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G123" t="n">
-        <v>1.13662588596344</v>
+        <v>1.13662600517273</v>
       </c>
       <c r="H123" t="n">
         <v>15822</v>
@@ -4110,7 +4110,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G129" t="n">
-        <v>1.06439888477325</v>
+        <v>1.06439876556396</v>
       </c>
       <c r="H129" t="n">
         <v>33799</v>
@@ -4197,7 +4197,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G132" t="n">
-        <v>0.955107867717743</v>
+        <v>0.955107927322388</v>
       </c>
       <c r="H132" t="n">
         <v>51084</v>
@@ -4255,7 +4255,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G134" t="n">
-        <v>1.02068245410919</v>
+        <v>1.02068257331848</v>
       </c>
       <c r="H134" t="n">
         <v>1695</v>
@@ -4313,7 +4313,7 @@
         <v>1.05200004577637</v>
       </c>
       <c r="G136" t="n">
-        <v>0.999774634838104</v>
+        <v>0.999774575233459</v>
       </c>
       <c r="H136" t="n">
         <v>12850</v>
@@ -4371,7 +4371,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G138" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H138" t="n">
         <v>2668</v>
@@ -4429,7 +4429,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G140" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H140" t="n">
         <v>819</v>
@@ -4458,7 +4458,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G141" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H141" t="n">
         <v>2583</v>
@@ -4487,7 +4487,7 @@
         <v>1.01300001144409</v>
       </c>
       <c r="G142" t="n">
-        <v>0.962710857391357</v>
+        <v>0.962710797786713</v>
       </c>
       <c r="H142" t="n">
         <v>500</v>
@@ -4516,7 +4516,7 @@
         <v>1.01300001144409</v>
       </c>
       <c r="G143" t="n">
-        <v>0.962710857391357</v>
+        <v>0.962710797786713</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>1.01300001144409</v>
       </c>
       <c r="G144" t="n">
-        <v>0.962710857391357</v>
+        <v>0.962710797786713</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G146" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H146" t="n">
         <v>7470</v>
@@ -4748,7 +4748,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G151" t="n">
-        <v>0.98742014169693</v>
+        <v>0.987420082092285</v>
       </c>
       <c r="H151" t="n">
         <v>15266</v>
@@ -4893,7 +4893,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G156" t="n">
-        <v>1.0140300989151</v>
+        <v>1.01402997970581</v>
       </c>
       <c r="H156" t="n">
         <v>4958</v>
@@ -4922,7 +4922,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G157" t="n">
-        <v>1.0140300989151</v>
+        <v>1.01402997970581</v>
       </c>
       <c r="H157" t="n">
         <v>3607</v>
@@ -4951,7 +4951,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G158" t="n">
-        <v>1.0140300989151</v>
+        <v>1.01402997970581</v>
       </c>
       <c r="H158" t="n">
         <v>1536</v>
@@ -4980,7 +4980,7 @@
         <v>1.07700002193451</v>
       </c>
       <c r="G159" t="n">
-        <v>1.02353370189667</v>
+        <v>1.02353358268738</v>
       </c>
       <c r="H159" t="n">
         <v>301</v>
@@ -5009,7 +5009,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G160" t="n">
-        <v>1.02163290977478</v>
+        <v>1.02163279056549</v>
       </c>
       <c r="H160" t="n">
         <v>8000</v>
@@ -5038,7 +5038,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G161" t="n">
-        <v>0.980767488479614</v>
+        <v>0.980767428874969</v>
       </c>
       <c r="H161" t="n">
         <v>9930</v>
@@ -5067,7 +5067,7 @@
         <v>1.03299999237061</v>
       </c>
       <c r="G162" t="n">
-        <v>0.981717765331268</v>
+        <v>0.981717824935913</v>
       </c>
       <c r="H162" t="n">
         <v>7693</v>
@@ -5125,7 +5125,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G164" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H164" t="n">
         <v>250</v>
@@ -5154,7 +5154,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G165" t="n">
-        <v>0.963661134243011</v>
+        <v>0.963661193847656</v>
       </c>
       <c r="H165" t="n">
         <v>3542</v>
@@ -5357,7 +5357,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G172" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H172" t="n">
         <v>10607</v>
@@ -5473,7 +5473,7 @@
         <v>1.1139999628067</v>
       </c>
       <c r="G176" t="n">
-        <v>1.05869662761688</v>
+        <v>1.05869674682617</v>
       </c>
       <c r="H176" t="n">
         <v>20400</v>
@@ -5502,7 +5502,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G177" t="n">
-        <v>1.10241293907166</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H177" t="n">
         <v>19399</v>
@@ -5676,7 +5676,7 @@
         <v>1.12100005149841</v>
       </c>
       <c r="G183" t="n">
-        <v>1.06534922122955</v>
+        <v>1.06534934043884</v>
       </c>
       <c r="H183" t="n">
         <v>1000</v>
@@ -5734,7 +5734,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G185" t="n">
-        <v>1.08910810947418</v>
+        <v>1.08910799026489</v>
       </c>
       <c r="H185" t="n">
         <v>2769</v>
@@ -5879,7 +5879,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G190" t="n">
-        <v>1.00262570381165</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H190" t="n">
         <v>1609</v>
@@ -5937,7 +5937,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G192" t="n">
-        <v>0.98742014169693</v>
+        <v>0.987420082092285</v>
       </c>
       <c r="H192" t="n">
         <v>2600</v>
@@ -5966,7 +5966,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H193" t="n">
         <v>3500</v>
@@ -6024,7 +6024,7 @@
         <v>1.03299999237061</v>
       </c>
       <c r="G195" t="n">
-        <v>0.981717765331268</v>
+        <v>0.981717824935913</v>
       </c>
       <c r="H195" t="n">
         <v>158</v>
@@ -6053,7 +6053,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G196" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H196" t="n">
         <v>305</v>
@@ -6111,7 +6111,7 @@
         <v>1.03299999237061</v>
       </c>
       <c r="G198" t="n">
-        <v>0.981717765331268</v>
+        <v>0.981717824935913</v>
       </c>
       <c r="H198" t="n">
         <v>155</v>
@@ -6169,7 +6169,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G200" t="n">
-        <v>0.984569013118744</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H200" t="n">
         <v>1505</v>
@@ -6227,7 +6227,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G202" t="n">
-        <v>0.963661134243011</v>
+        <v>0.963661193847656</v>
       </c>
       <c r="H202" t="n">
         <v>4000</v>
@@ -6256,7 +6256,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G203" t="n">
-        <v>0.984569013118744</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H203" t="n">
         <v>10950</v>
@@ -6372,7 +6372,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G207" t="n">
-        <v>0.98742014169693</v>
+        <v>0.987420082092285</v>
       </c>
       <c r="H207" t="n">
         <v>9988</v>
@@ -6430,7 +6430,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G209" t="n">
-        <v>1.00357592105865</v>
+        <v>1.00357604026794</v>
       </c>
       <c r="H209" t="n">
         <v>13457</v>
@@ -6459,7 +6459,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G210" t="n">
-        <v>0.971263825893402</v>
+        <v>0.971263885498047</v>
       </c>
       <c r="H210" t="n">
         <v>1000</v>
@@ -6604,7 +6604,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H215" t="n">
         <v>2077</v>
@@ -6662,7 +6662,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G217" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H217" t="n">
         <v>480</v>
@@ -6720,7 +6720,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G219" t="n">
-        <v>0.955107867717743</v>
+        <v>0.955107927322388</v>
       </c>
       <c r="H219" t="n">
         <v>6120</v>
@@ -6749,7 +6749,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G220" t="n">
-        <v>0.955107867717743</v>
+        <v>0.955107927322388</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G222" t="n">
-        <v>0.971263825893402</v>
+        <v>0.971263885498047</v>
       </c>
       <c r="H222" t="n">
         <v>700</v>
@@ -6865,7 +6865,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638447284698</v>
       </c>
       <c r="H224" t="n">
         <v>16296</v>
@@ -6894,7 +6894,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G225" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H225" t="n">
         <v>27306</v>
@@ -6981,7 +6981,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H228" t="n">
         <v>2724</v>
@@ -7010,7 +7010,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H229" t="n">
         <v>11827</v>
@@ -7039,7 +7039,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G230" t="n">
-        <v>0.984569013118744</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H230" t="n">
         <v>302145</v>
@@ -7068,7 +7068,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G231" t="n">
-        <v>0.984569013118744</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>0.982500016689301</v>
       </c>
       <c r="G233" t="n">
-        <v>0.933724939823151</v>
+        <v>0.933724880218506</v>
       </c>
       <c r="H233" t="n">
         <v>2272</v>
@@ -7242,7 +7242,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G237" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7358,7 +7358,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G241" t="n">
-        <v>1.00357592105865</v>
+        <v>1.00357604026794</v>
       </c>
       <c r="H241" t="n">
         <v>19196</v>
@@ -7387,7 +7387,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G242" t="n">
-        <v>1.00262570381165</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H242" t="n">
         <v>340</v>
@@ -7416,7 +7416,7 @@
         <v>1.03299999237061</v>
       </c>
       <c r="G243" t="n">
-        <v>0.981717765331268</v>
+        <v>0.981717824935913</v>
       </c>
       <c r="H243" t="n">
         <v>18267</v>
@@ -7445,7 +7445,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G244" t="n">
-        <v>0.980767488479614</v>
+        <v>0.980767428874969</v>
       </c>
       <c r="H244" t="n">
         <v>10086</v>
@@ -7532,7 +7532,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G247" t="n">
-        <v>0.984569013118744</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H247" t="n">
         <v>11434</v>
@@ -7561,7 +7561,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G248" t="n">
-        <v>0.98742014169693</v>
+        <v>0.987420082092285</v>
       </c>
       <c r="H248" t="n">
         <v>20000</v>
@@ -7648,7 +7648,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G251" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H251" t="n">
         <v>36947</v>
@@ -7677,7 +7677,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G252" t="n">
-        <v>0.963661134243011</v>
+        <v>0.963661193847656</v>
       </c>
       <c r="H252" t="n">
         <v>13025</v>
@@ -7851,7 +7851,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G258" t="n">
-        <v>0.983618497848511</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H258" t="n">
         <v>98439</v>
@@ -7880,7 +7880,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G259" t="n">
-        <v>0.984569013118744</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H259" t="n">
         <v>30635</v>
@@ -7938,7 +7938,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G261" t="n">
-        <v>1.04254066944122</v>
+        <v>1.04254078865051</v>
       </c>
       <c r="H261" t="n">
         <v>183087</v>
@@ -8228,7 +8228,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G271" t="n">
-        <v>1.32289564609528</v>
+        <v>1.32289552688599</v>
       </c>
       <c r="H271" t="n">
         <v>163344</v>
@@ -8315,7 +8315,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>1.26872539520264</v>
+        <v>1.26872551441193</v>
       </c>
       <c r="H274" t="n">
         <v>297056</v>
@@ -8373,7 +8373,7 @@
         <v>1.38100004196167</v>
       </c>
       <c r="G276" t="n">
-        <v>1.31244170665741</v>
+        <v>1.3124418258667</v>
       </c>
       <c r="H276" t="n">
         <v>293645</v>
@@ -8402,7 +8402,7 @@
         <v>1.36099994182587</v>
       </c>
       <c r="G277" t="n">
-        <v>1.29343461990356</v>
+        <v>1.29343450069427</v>
       </c>
       <c r="H277" t="n">
         <v>76933</v>
@@ -8431,7 +8431,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G278" t="n">
-        <v>1.23546278476715</v>
+        <v>1.23546290397644</v>
       </c>
       <c r="H278" t="n">
         <v>119522</v>
@@ -8518,7 +8518,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G281" t="n">
-        <v>1.2478175163269</v>
+        <v>1.24781739711761</v>
       </c>
       <c r="H281" t="n">
         <v>17255</v>
@@ -8547,7 +8547,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G282" t="n">
-        <v>1.26207304000854</v>
+        <v>1.26207292079926</v>
       </c>
       <c r="H282" t="n">
         <v>16948</v>
@@ -8576,7 +8576,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G283" t="n">
-        <v>1.17749106884003</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H283" t="n">
         <v>73831</v>
@@ -8663,7 +8663,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G286" t="n">
-        <v>1.17178916931152</v>
+        <v>1.17178905010223</v>
       </c>
       <c r="H286" t="n">
         <v>51660</v>
@@ -8779,7 +8779,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G290" t="n">
-        <v>1.09671103954315</v>
+        <v>1.09671092033386</v>
       </c>
       <c r="H290" t="n">
         <v>65474</v>
@@ -8953,7 +8953,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G296" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H296" t="n">
         <v>5384</v>
@@ -8982,7 +8982,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G297" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H297" t="n">
         <v>16179</v>
@@ -9011,7 +9011,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G298" t="n">
-        <v>1.06439888477325</v>
+        <v>1.06439876556396</v>
       </c>
       <c r="H298" t="n">
         <v>25146</v>
@@ -9098,7 +9098,7 @@
         <v>1.21899998188019</v>
       </c>
       <c r="G301" t="n">
-        <v>1.15848410129547</v>
+        <v>1.15848398208618</v>
       </c>
       <c r="H301" t="n">
         <v>201854</v>
@@ -9127,7 +9127,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G302" t="n">
-        <v>1.14137768745422</v>
+        <v>1.14137780666351</v>
       </c>
       <c r="H302" t="n">
         <v>82096</v>
@@ -9185,7 +9185,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G304" t="n">
-        <v>1.14137768745422</v>
+        <v>1.14137780666351</v>
       </c>
       <c r="H304" t="n">
         <v>14932</v>
@@ -9359,7 +9359,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G310" t="n">
-        <v>1.13662588596344</v>
+        <v>1.13662600517273</v>
       </c>
       <c r="H310" t="n">
         <v>18377</v>
@@ -9620,7 +9620,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G319" t="n">
-        <v>1.13472533226013</v>
+        <v>1.13472521305084</v>
       </c>
       <c r="H319" t="n">
         <v>11278</v>
@@ -9678,7 +9678,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G321" t="n">
-        <v>1.13377475738525</v>
+        <v>1.13377487659454</v>
       </c>
       <c r="H321" t="n">
         <v>14987</v>
@@ -9707,7 +9707,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G322" t="n">
-        <v>1.16323602199554</v>
+        <v>1.16323590278625</v>
       </c>
       <c r="H322" t="n">
         <v>56748</v>
@@ -9765,7 +9765,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G324" t="n">
-        <v>1.14137768745422</v>
+        <v>1.14137780666351</v>
       </c>
       <c r="H324" t="n">
         <v>6730</v>
@@ -9823,7 +9823,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G326" t="n">
-        <v>1.13377475738525</v>
+        <v>1.13377487659454</v>
       </c>
       <c r="H326" t="n">
         <v>5531</v>
@@ -9852,7 +9852,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G327" t="n">
-        <v>1.13472533226013</v>
+        <v>1.13472521305084</v>
       </c>
       <c r="H327" t="n">
         <v>17355</v>
@@ -9968,7 +9968,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G331" t="n">
-        <v>1.13472533226013</v>
+        <v>1.13472521305084</v>
       </c>
       <c r="H331" t="n">
         <v>38335</v>
@@ -10229,7 +10229,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>1.1128671169281</v>
+        <v>1.11286699771881</v>
       </c>
       <c r="H340" t="n">
         <v>7409</v>
@@ -10258,7 +10258,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G341" t="n">
-        <v>1.11856913566589</v>
+        <v>1.11856925487518</v>
       </c>
       <c r="H341" t="n">
         <v>13730</v>
@@ -10345,7 +10345,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G344" t="n">
-        <v>1.10811531543732</v>
+        <v>1.10811519622803</v>
       </c>
       <c r="H344" t="n">
         <v>19157</v>
@@ -10403,7 +10403,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G346" t="n">
-        <v>1.08910810947418</v>
+        <v>1.08910799026489</v>
       </c>
       <c r="H346" t="n">
         <v>14320</v>
@@ -10751,7 +10751,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H358" t="n">
         <v>39402</v>
@@ -10867,7 +10867,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G362" t="n">
-        <v>1.09956192970276</v>
+        <v>1.09956204891205</v>
       </c>
       <c r="H362" t="n">
         <v>393819</v>
@@ -11041,7 +11041,7 @@
         <v>1.11199998855591</v>
       </c>
       <c r="G368" t="n">
-        <v>1.056795835495</v>
+        <v>1.05679595470428</v>
       </c>
       <c r="H368" t="n">
         <v>32375</v>
@@ -11070,7 +11070,7 @@
         <v>1.10899996757507</v>
       </c>
       <c r="G369" t="n">
-        <v>1.05394494533539</v>
+        <v>1.05394506454468</v>
       </c>
       <c r="H369" t="n">
         <v>12555</v>
@@ -11099,7 +11099,7 @@
         <v>1.12100005149841</v>
       </c>
       <c r="G370" t="n">
-        <v>1.06534922122955</v>
+        <v>1.06534934043884</v>
       </c>
       <c r="H370" t="n">
         <v>20364</v>
@@ -11302,7 +11302,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G377" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H377" t="n">
         <v>31617</v>
@@ -11360,7 +11360,7 @@
         <v>1.15900003910065</v>
       </c>
       <c r="G379" t="n">
-        <v>1.10146284103394</v>
+        <v>1.10146272182465</v>
       </c>
       <c r="H379" t="n">
         <v>21885</v>
@@ -11853,7 +11853,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G396" t="n">
-        <v>1.14232814311981</v>
+        <v>1.14232802391052</v>
       </c>
       <c r="H396" t="n">
         <v>29872</v>
@@ -11969,7 +11969,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G400" t="n">
-        <v>1.11856913566589</v>
+        <v>1.11856925487518</v>
       </c>
       <c r="H400" t="n">
         <v>8359</v>
@@ -12056,7 +12056,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G403" t="n">
-        <v>1.11856913566589</v>
+        <v>1.11856925487518</v>
       </c>
       <c r="H403" t="n">
         <v>15262</v>
@@ -12085,7 +12085,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G404" t="n">
-        <v>1.10241293907166</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H404" t="n">
         <v>22250</v>
@@ -12114,7 +12114,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H405" t="n">
         <v>15760</v>
@@ -12143,7 +12143,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12201,7 +12201,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G408" t="n">
-        <v>1.11761879920959</v>
+        <v>1.11761868000031</v>
       </c>
       <c r="H408" t="n">
         <v>6600</v>
@@ -12230,7 +12230,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G409" t="n">
-        <v>1.11476755142212</v>
+        <v>1.11476767063141</v>
       </c>
       <c r="H409" t="n">
         <v>2481</v>
@@ -12433,7 +12433,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G416" t="n">
-        <v>1.09671103954315</v>
+        <v>1.09671092033386</v>
       </c>
       <c r="H416" t="n">
         <v>5579</v>
@@ -12491,7 +12491,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G418" t="n">
-        <v>1.11096632480621</v>
+        <v>1.1109664440155</v>
       </c>
       <c r="H418" t="n">
         <v>2516</v>
@@ -12868,7 +12868,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G431" t="n">
-        <v>1.13472533226013</v>
+        <v>1.13472521305084</v>
       </c>
       <c r="H431" t="n">
         <v>4925</v>
@@ -13013,7 +13013,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G436" t="n">
-        <v>1.11476755142212</v>
+        <v>1.11476767063141</v>
       </c>
       <c r="H436" t="n">
         <v>4639</v>
@@ -13158,7 +13158,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G441" t="n">
-        <v>1.1128671169281</v>
+        <v>1.11286699771881</v>
       </c>
       <c r="H441" t="n">
         <v>9775</v>
@@ -13216,7 +13216,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G443" t="n">
-        <v>1.11761879920959</v>
+        <v>1.11761868000031</v>
       </c>
       <c r="H443" t="n">
         <v>9327</v>
@@ -13274,7 +13274,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H445" t="n">
         <v>19891</v>
@@ -13390,7 +13390,7 @@
         <v>1.20700001716614</v>
       </c>
       <c r="G449" t="n">
-        <v>1.14707982540131</v>
+        <v>1.14707970619202</v>
       </c>
       <c r="H449" t="n">
         <v>56285</v>
@@ -13506,7 +13506,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G453" t="n">
-        <v>1.20505142211914</v>
+        <v>1.20505154132843</v>
       </c>
       <c r="H453" t="n">
         <v>91082</v>
@@ -13535,7 +13535,7 @@
         <v>1.25</v>
       </c>
       <c r="G454" t="n">
-        <v>1.18794524669647</v>
+        <v>1.18794512748718</v>
       </c>
       <c r="H454" t="n">
         <v>39962</v>
@@ -13593,7 +13593,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G456" t="n">
-        <v>1.17178916931152</v>
+        <v>1.17178905010223</v>
       </c>
       <c r="H456" t="n">
         <v>20072</v>
@@ -13622,7 +13622,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G457" t="n">
-        <v>1.17273938655853</v>
+        <v>1.17273950576782</v>
       </c>
       <c r="H457" t="n">
         <v>21775</v>
@@ -13709,7 +13709,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G460" t="n">
-        <v>1.17749106884003</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H460" t="n">
         <v>19410</v>
@@ -13999,7 +13999,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G470" t="n">
-        <v>1.19079625606537</v>
+        <v>1.19079613685608</v>
       </c>
       <c r="H470" t="n">
         <v>256139</v>
@@ -14028,7 +14028,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G471" t="n">
-        <v>1.19364726543427</v>
+        <v>1.19364738464355</v>
       </c>
       <c r="H471" t="n">
         <v>268871</v>
@@ -14086,7 +14086,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G473" t="n">
-        <v>1.19079625606537</v>
+        <v>1.19079613685608</v>
       </c>
       <c r="H473" t="n">
         <v>23592</v>
@@ -14173,7 +14173,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G476" t="n">
-        <v>1.17749106884003</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H476" t="n">
         <v>127242</v>
@@ -14260,7 +14260,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G479" t="n">
-        <v>1.11476755142212</v>
+        <v>1.11476767063141</v>
       </c>
       <c r="H479" t="n">
         <v>37049</v>
@@ -14405,7 +14405,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G484" t="n">
-        <v>1.155632853508</v>
+        <v>1.15563297271729</v>
       </c>
       <c r="H484" t="n">
         <v>10800</v>
@@ -14492,7 +14492,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G487" t="n">
-        <v>1.13472533226013</v>
+        <v>1.13472521305084</v>
       </c>
       <c r="H487" t="n">
         <v>27842</v>
@@ -14550,7 +14550,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G489" t="n">
-        <v>1.11856913566589</v>
+        <v>1.11856925487518</v>
       </c>
       <c r="H489" t="n">
         <v>10010</v>
@@ -14608,7 +14608,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H491" t="n">
         <v>3613</v>
@@ -14724,7 +14724,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G495" t="n">
-        <v>1.11476755142212</v>
+        <v>1.11476767063141</v>
       </c>
       <c r="H495" t="n">
         <v>2345</v>
@@ -14782,7 +14782,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G497" t="n">
-        <v>1.10241293907166</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H497" t="n">
         <v>13455</v>
@@ -14811,7 +14811,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G498" t="n">
-        <v>1.11096632480621</v>
+        <v>1.1109664440155</v>
       </c>
       <c r="H498" t="n">
         <v>4720</v>
@@ -14840,7 +14840,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G499" t="n">
-        <v>1.11096632480621</v>
+        <v>1.1109664440155</v>
       </c>
       <c r="H499" t="n">
         <v>12294</v>
@@ -14869,7 +14869,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G500" t="n">
-        <v>1.11096632480621</v>
+        <v>1.1109664440155</v>
       </c>
       <c r="H500" t="n">
         <v>20280</v>
@@ -14898,7 +14898,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G501" t="n">
-        <v>1.10241293907166</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H501" t="n">
         <v>2321</v>
@@ -14956,7 +14956,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H503" t="n">
         <v>52184</v>
@@ -14985,7 +14985,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G504" t="n">
-        <v>1.11856913566589</v>
+        <v>1.11856925487518</v>
       </c>
       <c r="H504" t="n">
         <v>15643</v>
@@ -15043,7 +15043,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H506" t="n">
         <v>7586</v>
@@ -15072,7 +15072,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G507" t="n">
-        <v>1.10051238536835</v>
+        <v>1.10051226615906</v>
       </c>
       <c r="H507" t="n">
         <v>2976</v>
@@ -15130,7 +15130,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G509" t="n">
-        <v>1.11096632480621</v>
+        <v>1.1109664440155</v>
       </c>
       <c r="H509" t="n">
         <v>23824</v>
@@ -15420,7 +15420,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H519" t="n">
         <v>26920</v>
@@ -15478,7 +15478,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H521" t="n">
         <v>23513</v>
@@ -15507,7 +15507,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G522" t="n">
-        <v>1.10241293907166</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H522" t="n">
         <v>11085</v>
@@ -15536,7 +15536,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G523" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H523" t="n">
         <v>10943</v>
@@ -15623,7 +15623,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G526" t="n">
-        <v>1.10241293907166</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H526" t="n">
         <v>8087</v>
@@ -15652,7 +15652,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G527" t="n">
-        <v>1.10241293907166</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H527" t="n">
         <v>10437</v>
@@ -15681,7 +15681,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G528" t="n">
-        <v>1.10241293907166</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H528" t="n">
         <v>20786</v>
@@ -15884,7 +15884,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G535" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H535" t="n">
         <v>6800</v>
@@ -15913,7 +15913,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G536" t="n">
-        <v>1.06439888477325</v>
+        <v>1.06439876556396</v>
       </c>
       <c r="H536" t="n">
         <v>8150</v>
@@ -15942,7 +15942,7 @@
         <v>1.125</v>
       </c>
       <c r="G537" t="n">
-        <v>1.06915044784546</v>
+        <v>1.06915056705475</v>
       </c>
       <c r="H537" t="n">
         <v>21910</v>
@@ -16058,7 +16058,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H541" t="n">
         <v>1790</v>
@@ -16435,7 +16435,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G554" t="n">
-        <v>1.02163290977478</v>
+        <v>1.02163279056549</v>
       </c>
       <c r="H554" t="n">
         <v>3821</v>
@@ -16522,7 +16522,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H557" t="n">
         <v>5187</v>
@@ -16551,7 +16551,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G558" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G566" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H566" t="n">
         <v>13910</v>
@@ -16928,7 +16928,7 @@
         <v>1.125</v>
       </c>
       <c r="G571" t="n">
-        <v>1.06915044784546</v>
+        <v>1.06915056705475</v>
       </c>
       <c r="H571" t="n">
         <v>7222</v>
@@ -16957,7 +16957,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G572" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H572" t="n">
         <v>290</v>
@@ -17189,7 +17189,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G580" t="n">
-        <v>1.06439888477325</v>
+        <v>1.06439876556396</v>
       </c>
       <c r="H580" t="n">
         <v>16675</v>
@@ -17392,7 +17392,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G587" t="n">
-        <v>1.06439888477325</v>
+        <v>1.06439876556396</v>
       </c>
       <c r="H587" t="n">
         <v>13671</v>
@@ -17624,7 +17624,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G595" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638447284698</v>
       </c>
       <c r="H595" t="n">
         <v>4500</v>
@@ -17653,7 +17653,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G596" t="n">
-        <v>1.02163290977478</v>
+        <v>1.02163279056549</v>
       </c>
       <c r="H596" t="n">
         <v>9288</v>
@@ -17682,7 +17682,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G597" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638447284698</v>
       </c>
       <c r="H597" t="n">
         <v>17100</v>
@@ -17798,7 +17798,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G601" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H601" t="n">
         <v>7370</v>
@@ -17827,7 +17827,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G602" t="n">
-        <v>1.02163290977478</v>
+        <v>1.02163279056549</v>
       </c>
       <c r="H602" t="n">
         <v>3010</v>
@@ -17856,7 +17856,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G603" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H603" t="n">
         <v>162004</v>
@@ -17885,7 +17885,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G604" t="n">
-        <v>1.06439888477325</v>
+        <v>1.06439876556396</v>
       </c>
       <c r="H604" t="n">
         <v>34087</v>
@@ -17914,7 +17914,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G605" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638447284698</v>
       </c>
       <c r="H605" t="n">
         <v>4449</v>
@@ -18001,7 +18001,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G608" t="n">
-        <v>1.02163290977478</v>
+        <v>1.02163279056549</v>
       </c>
       <c r="H608" t="n">
         <v>7794</v>
@@ -18117,7 +18117,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G612" t="n">
-        <v>1.02163290977478</v>
+        <v>1.02163279056549</v>
       </c>
       <c r="H612" t="n">
         <v>39408</v>
@@ -18146,7 +18146,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H613" t="n">
         <v>16207</v>
@@ -18233,7 +18233,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G616" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H616" t="n">
         <v>10854</v>
@@ -18262,7 +18262,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G617" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H617" t="n">
         <v>22297</v>
@@ -18436,7 +18436,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H623" t="n">
         <v>2010</v>
@@ -18465,7 +18465,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18581,7 +18581,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G628" t="n">
-        <v>0.946554601192474</v>
+        <v>0.946554660797119</v>
       </c>
       <c r="H628" t="n">
         <v>1972</v>
@@ -18697,7 +18697,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G632" t="n">
-        <v>0.919944643974304</v>
+        <v>0.919944703578949</v>
       </c>
       <c r="H632" t="n">
         <v>2053</v>
@@ -18987,7 +18987,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G642" t="n">
-        <v>0.927547633647919</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H642" t="n">
         <v>957</v>
@@ -19074,7 +19074,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G645" t="n">
-        <v>0.937051117420197</v>
+        <v>0.937051177024841</v>
       </c>
       <c r="H645" t="n">
         <v>2898</v>
@@ -19132,7 +19132,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G647" t="n">
-        <v>0.927547633647919</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H647" t="n">
         <v>767</v>
@@ -19161,7 +19161,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G648" t="n">
-        <v>0.927547633647919</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -19393,7 +19393,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G656" t="n">
-        <v>0.904739081859589</v>
+        <v>0.904739022254944</v>
       </c>
       <c r="H656" t="n">
         <v>4776</v>
@@ -19799,7 +19799,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G670" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H670" t="n">
         <v>1010</v>
@@ -20118,7 +20118,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G681" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H681" t="n">
         <v>1709</v>
@@ -20263,7 +20263,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G686" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753314971924</v>
       </c>
       <c r="H686" t="n">
         <v>8065</v>
@@ -20350,7 +20350,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G689" t="n">
-        <v>0.919944643974304</v>
+        <v>0.919944703578949</v>
       </c>
       <c r="H689" t="n">
         <v>38510</v>
@@ -20437,7 +20437,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G692" t="n">
-        <v>0.904739081859589</v>
+        <v>0.904739022254944</v>
       </c>
       <c r="H692" t="n">
         <v>4862</v>
@@ -20466,7 +20466,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G693" t="n">
-        <v>0.904739081859589</v>
+        <v>0.904739022254944</v>
       </c>
       <c r="H693" t="n">
         <v>4465</v>
@@ -20727,7 +20727,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G702" t="n">
-        <v>0.919944643974304</v>
+        <v>0.919944703578949</v>
       </c>
       <c r="H702" t="n">
         <v>712</v>
@@ -20756,7 +20756,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G703" t="n">
-        <v>0.897136151790619</v>
+        <v>0.897136211395264</v>
       </c>
       <c r="H703" t="n">
         <v>5011</v>
@@ -20959,7 +20959,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G710" t="n">
-        <v>0.826809823513031</v>
+        <v>0.826809763908386</v>
       </c>
       <c r="H710" t="n">
         <v>24474</v>
@@ -20988,7 +20988,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G711" t="n">
-        <v>0.828710556030273</v>
+        <v>0.828710496425629</v>
       </c>
       <c r="H711" t="n">
         <v>1614</v>
@@ -21017,7 +21017,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G712" t="n">
-        <v>0.800199866294861</v>
+        <v>0.800199806690216</v>
       </c>
       <c r="H712" t="n">
         <v>300</v>
@@ -21162,7 +21162,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G717" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H717" t="n">
         <v>14233</v>
@@ -21307,7 +21307,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G722" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H722" t="n">
         <v>632</v>
@@ -21365,7 +21365,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G724" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H724" t="n">
         <v>80</v>
@@ -21394,7 +21394,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G725" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H725" t="n">
         <v>1252</v>
@@ -21423,7 +21423,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G726" t="n">
-        <v>0.800199866294861</v>
+        <v>0.800199806690216</v>
       </c>
       <c r="H726" t="n">
         <v>1227</v>
@@ -21481,7 +21481,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G728" t="n">
-        <v>0.800199866294861</v>
+        <v>0.800199806690216</v>
       </c>
       <c r="H728" t="n">
         <v>2265</v>
@@ -21655,7 +21655,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G734" t="n">
-        <v>0.804001331329346</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H734" t="n">
         <v>15413</v>
@@ -21742,7 +21742,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G737" t="n">
-        <v>0.796398401260376</v>
+        <v>0.796398460865021</v>
       </c>
       <c r="H737" t="n">
         <v>1171</v>
@@ -21771,7 +21771,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G738" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185633182526</v>
       </c>
       <c r="H738" t="n">
         <v>1300</v>
@@ -21800,7 +21800,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G739" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185633182526</v>
       </c>
       <c r="H739" t="n">
         <v>879</v>
@@ -21829,7 +21829,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G740" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994184970856</v>
       </c>
       <c r="H740" t="n">
         <v>11723</v>
@@ -21858,7 +21858,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G741" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994184970856</v>
       </c>
       <c r="H741" t="n">
         <v>610</v>
@@ -21887,7 +21887,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G742" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H742" t="n">
         <v>5461</v>
@@ -22003,7 +22003,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G746" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H746" t="n">
         <v>1260</v>
@@ -22032,7 +22032,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G747" t="n">
-        <v>0.796398401260376</v>
+        <v>0.796398460865021</v>
       </c>
       <c r="H747" t="n">
         <v>2094</v>
@@ -22148,7 +22148,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G751" t="n">
-        <v>0.800199866294861</v>
+        <v>0.800199806690216</v>
       </c>
       <c r="H751" t="n">
         <v>3300</v>
@@ -22235,7 +22235,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G754" t="n">
-        <v>0.773589849472046</v>
+        <v>0.773589909076691</v>
       </c>
       <c r="H754" t="n">
         <v>757</v>
@@ -22264,7 +22264,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G755" t="n">
-        <v>0.798299014568329</v>
+        <v>0.798299074172974</v>
       </c>
       <c r="H755" t="n">
         <v>72</v>
@@ -22293,7 +22293,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G756" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H756" t="n">
         <v>3078</v>
@@ -22322,7 +22322,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G757" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H757" t="n">
         <v>2150</v>
@@ -22351,7 +22351,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G758" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H758" t="n">
         <v>0</v>
@@ -22380,7 +22380,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G759" t="n">
-        <v>0.800199866294861</v>
+        <v>0.800199806690216</v>
       </c>
       <c r="H759" t="n">
         <v>11560</v>
@@ -22467,7 +22467,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G762" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H762" t="n">
         <v>10920</v>
@@ -22496,7 +22496,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G763" t="n">
-        <v>0.790696322917938</v>
+        <v>0.790696382522583</v>
       </c>
       <c r="H763" t="n">
         <v>2090</v>
@@ -22525,7 +22525,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>0.790696322917938</v>
+        <v>0.790696382522583</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -22554,7 +22554,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G765" t="n">
-        <v>0.790696322917938</v>
+        <v>0.790696382522583</v>
       </c>
       <c r="H765" t="n">
         <v>1516</v>
@@ -22612,7 +22612,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G767" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H767" t="n">
         <v>2524</v>
@@ -22641,7 +22641,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G768" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994184970856</v>
       </c>
       <c r="H768" t="n">
         <v>10514</v>
@@ -22670,7 +22670,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G769" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H769" t="n">
         <v>16652</v>
@@ -22699,7 +22699,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G770" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H770" t="n">
         <v>9656</v>
@@ -22728,7 +22728,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G771" t="n">
-        <v>0.790696322917938</v>
+        <v>0.790696382522583</v>
       </c>
       <c r="H771" t="n">
         <v>11010</v>
@@ -22757,7 +22757,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G772" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H772" t="n">
         <v>3569</v>
@@ -22786,7 +22786,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G773" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H773" t="n">
         <v>12</v>
@@ -22902,7 +22902,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G777" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H777" t="n">
         <v>20</v>
@@ -22931,7 +22931,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G778" t="n">
-        <v>0.800199866294861</v>
+        <v>0.800199806690216</v>
       </c>
       <c r="H778" t="n">
         <v>2483</v>
@@ -23540,7 +23540,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G799" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H799" t="n">
         <v>38915</v>
@@ -23714,7 +23714,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G805" t="n">
-        <v>0.876228332519531</v>
+        <v>0.876228272914886</v>
       </c>
       <c r="H805" t="n">
         <v>2557</v>
@@ -23888,7 +23888,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G811" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H811" t="n">
         <v>1087</v>
@@ -23917,7 +23917,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>0.853419840335846</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H812" t="n">
         <v>14750</v>
@@ -24033,7 +24033,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G816" t="n">
-        <v>0.832511961460114</v>
+        <v>0.832511901855469</v>
       </c>
       <c r="H816" t="n">
         <v>13272</v>
@@ -24265,7 +24265,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G824" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H824" t="n">
         <v>520</v>
@@ -24381,7 +24381,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G828" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H828" t="n">
         <v>10500</v>
@@ -24497,7 +24497,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G832" t="n">
-        <v>0.876228332519531</v>
+        <v>0.876228272914886</v>
       </c>
       <c r="H832" t="n">
         <v>10810</v>
@@ -24613,7 +24613,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G836" t="n">
-        <v>0.919944643974304</v>
+        <v>0.919944703578949</v>
       </c>
       <c r="H836" t="n">
         <v>93177</v>
@@ -24642,7 +24642,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G837" t="n">
-        <v>1.10241293907166</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H837" t="n">
         <v>521892</v>
@@ -24729,7 +24729,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G840" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H840" t="n">
         <v>199532</v>
@@ -24758,7 +24758,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G841" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H841" t="n">
         <v>56431</v>
@@ -24816,7 +24816,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G843" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H843" t="n">
         <v>10650</v>
@@ -24845,7 +24845,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G844" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H844" t="n">
         <v>6969</v>
@@ -24903,7 +24903,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G846" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H846" t="n">
         <v>6500</v>
@@ -25077,7 +25077,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G852" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753314971924</v>
       </c>
       <c r="H852" t="n">
         <v>18857</v>
@@ -25193,7 +25193,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G856" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H856" t="n">
         <v>23230</v>
@@ -25309,7 +25309,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G860" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H860" t="n">
         <v>74217</v>
@@ -25367,7 +25367,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G862" t="n">
-        <v>0.897136151790619</v>
+        <v>0.897136211395264</v>
       </c>
       <c r="H862" t="n">
         <v>35703</v>
@@ -25831,7 +25831,7 @@
         <v>0.927999973297119</v>
       </c>
       <c r="G878" t="n">
-        <v>0.881930470466614</v>
+        <v>0.881930410861969</v>
       </c>
       <c r="H878" t="n">
         <v>10046</v>
@@ -26034,7 +26034,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G885" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H885" t="n">
         <v>18386</v>
@@ -26092,7 +26092,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G887" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H887" t="n">
         <v>1480</v>
@@ -26150,7 +26150,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G889" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H889" t="n">
         <v>4577</v>
@@ -26179,7 +26179,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G890" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H890" t="n">
         <v>4035</v>
@@ -26237,7 +26237,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G892" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H892" t="n">
         <v>13605</v>
@@ -26324,7 +26324,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G895" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H895" t="n">
         <v>1766</v>
@@ -26498,7 +26498,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G901" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H901" t="n">
         <v>6210</v>
@@ -26527,7 +26527,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G902" t="n">
-        <v>0.853419840335846</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H902" t="n">
         <v>2624</v>
@@ -26585,7 +26585,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>0.853419840335846</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H904" t="n">
         <v>1651</v>
@@ -26672,7 +26672,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>0.853419840335846</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H907" t="n">
         <v>10040</v>
@@ -26846,7 +26846,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G913" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H913" t="n">
         <v>29501</v>
@@ -26875,7 +26875,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G914" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H914" t="n">
         <v>4867</v>
@@ -26933,7 +26933,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G916" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H916" t="n">
         <v>4611</v>
@@ -26962,7 +26962,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G917" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G918" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -27107,7 +27107,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G922" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H922" t="n">
         <v>2714</v>
@@ -27368,7 +27368,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G931" t="n">
-        <v>0.937051117420197</v>
+        <v>0.937051177024841</v>
       </c>
       <c r="H931" t="n">
         <v>302501</v>
@@ -27397,7 +27397,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G932" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753314971924</v>
       </c>
       <c r="H932" t="n">
         <v>68362</v>
@@ -27426,7 +27426,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G933" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H933" t="n">
         <v>30540</v>
@@ -27455,7 +27455,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G934" t="n">
-        <v>0.955107867717743</v>
+        <v>0.955107927322388</v>
       </c>
       <c r="H934" t="n">
         <v>10054</v>
@@ -27484,7 +27484,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G935" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H935" t="n">
         <v>26262</v>
@@ -27542,7 +27542,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G937" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753314971924</v>
       </c>
       <c r="H937" t="n">
         <v>19326</v>
@@ -27571,7 +27571,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G938" t="n">
-        <v>0.927547633647919</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H938" t="n">
         <v>17014</v>
@@ -27658,7 +27658,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G941" t="n">
-        <v>0.927547633647919</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H941" t="n">
         <v>32693</v>
@@ -27832,7 +27832,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G947" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H947" t="n">
         <v>76067</v>
@@ -27861,7 +27861,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G948" t="n">
-        <v>0.927547633647919</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H948" t="n">
         <v>21307</v>
@@ -27890,7 +27890,7 @@
         <v>0.967999994754791</v>
       </c>
       <c r="G949" t="n">
-        <v>0.919944643974304</v>
+        <v>0.919944703578949</v>
       </c>
       <c r="H949" t="n">
         <v>35702</v>
@@ -27919,7 +27919,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G950" t="n">
-        <v>0.937051117420197</v>
+        <v>0.937051177024841</v>
       </c>
       <c r="H950" t="n">
         <v>13708</v>
@@ -27977,7 +27977,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G952" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753314971924</v>
       </c>
       <c r="H952" t="n">
         <v>16989</v>
@@ -28180,7 +28180,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G959" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H959" t="n">
         <v>31567</v>
@@ -28267,7 +28267,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G962" t="n">
-        <v>0.897136151790619</v>
+        <v>0.897136211395264</v>
       </c>
       <c r="H962" t="n">
         <v>28584</v>
@@ -28325,7 +28325,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G964" t="n">
-        <v>0.897136151790619</v>
+        <v>0.897136211395264</v>
       </c>
       <c r="H964" t="n">
         <v>9983</v>
@@ -28383,7 +28383,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G966" t="n">
-        <v>0.897136151790619</v>
+        <v>0.897136211395264</v>
       </c>
       <c r="H966" t="n">
         <v>29220</v>
@@ -28412,7 +28412,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G967" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H967" t="n">
         <v>19223</v>
@@ -28441,7 +28441,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G968" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H968" t="n">
         <v>2280</v>
@@ -28499,7 +28499,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G970" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H970" t="n">
         <v>9218</v>
@@ -28557,7 +28557,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G972" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H972" t="n">
         <v>680</v>
@@ -28644,7 +28644,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G975" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H975" t="n">
         <v>218368</v>
@@ -28673,7 +28673,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G976" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H976" t="n">
         <v>49086</v>
@@ -28702,7 +28702,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G977" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H977" t="n">
         <v>11890</v>
@@ -28731,7 +28731,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G978" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H978" t="n">
         <v>33171</v>
@@ -28760,7 +28760,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G979" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H979" t="n">
         <v>4965</v>
@@ -28789,7 +28789,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G980" t="n">
-        <v>0.955107867717743</v>
+        <v>0.955107927322388</v>
       </c>
       <c r="H980" t="n">
         <v>14510</v>
@@ -28847,7 +28847,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G982" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H982" t="n">
         <v>30123</v>
@@ -28905,7 +28905,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G984" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H984" t="n">
         <v>29319</v>
@@ -28934,7 +28934,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G985" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H985" t="n">
         <v>21774</v>
@@ -28963,7 +28963,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G986" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H986" t="n">
         <v>34613</v>
@@ -28992,7 +28992,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G987" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H987" t="n">
         <v>7153</v>
@@ -29137,7 +29137,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H992" t="n">
         <v>10082</v>
@@ -29166,7 +29166,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G993" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H993" t="n">
         <v>5731</v>
@@ -29253,7 +29253,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G996" t="n">
-        <v>0.983618497848511</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H996" t="n">
         <v>106619</v>
@@ -29282,7 +29282,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G997" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H997" t="n">
         <v>4524</v>
@@ -29311,7 +29311,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G998" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H998" t="n">
         <v>19085</v>
@@ -29369,7 +29369,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H1000" t="n">
         <v>13855</v>
@@ -29427,7 +29427,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.983618497848511</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H1002" t="n">
         <v>25401</v>
@@ -29456,7 +29456,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H1003" t="n">
         <v>87046</v>
@@ -29601,7 +29601,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H1008" t="n">
         <v>70073</v>
@@ -29746,7 +29746,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.02163290977478</v>
+        <v>1.02163279056549</v>
       </c>
       <c r="H1013" t="n">
         <v>15841</v>
@@ -29775,7 +29775,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638447284698</v>
       </c>
       <c r="H1014" t="n">
         <v>4819</v>
@@ -29949,7 +29949,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.00262570381165</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H1020" t="n">
         <v>12764</v>
@@ -30036,7 +30036,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.983618497848511</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H1023" t="n">
         <v>17131</v>
@@ -30065,7 +30065,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H1024" t="n">
         <v>2530</v>
@@ -30094,7 +30094,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H1025" t="n">
         <v>96405</v>
@@ -30123,7 +30123,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H1026" t="n">
         <v>14290</v>
@@ -30210,7 +30210,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H1029" t="n">
         <v>91607</v>
@@ -30239,7 +30239,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1030" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H1030" t="n">
         <v>22283</v>
@@ -30268,7 +30268,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.00262570381165</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H1031" t="n">
         <v>372072</v>
@@ -30326,7 +30326,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H1033" t="n">
         <v>51868</v>
@@ -30413,7 +30413,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.10716474056244</v>
+        <v>1.10716485977173</v>
       </c>
       <c r="H1036" t="n">
         <v>119522</v>
@@ -30471,7 +30471,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H1038" t="n">
         <v>17825</v>
@@ -30500,7 +30500,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.00262570381165</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H1039" t="n">
         <v>32399</v>
@@ -30558,7 +30558,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.06439888477325</v>
+        <v>1.06439876556396</v>
       </c>
       <c r="H1041" t="n">
         <v>42988</v>
@@ -30645,7 +30645,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H1044" t="n">
         <v>40158</v>
@@ -30790,7 +30790,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H1049" t="n">
         <v>122643</v>
@@ -30906,7 +30906,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.983618497848511</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H1053" t="n">
         <v>115588</v>
@@ -30935,7 +30935,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873842716217</v>
       </c>
       <c r="H1054" t="n">
         <v>46940</v>
@@ -30993,7 +30993,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H1056" t="n">
         <v>34580</v>
@@ -31022,7 +31022,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.937051117420197</v>
+        <v>0.937051177024841</v>
       </c>
       <c r="H1057" t="n">
         <v>35665</v>
@@ -31167,7 +31167,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H1062" t="n">
         <v>146893</v>
@@ -31225,7 +31225,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.826809823513031</v>
+        <v>0.826809763908386</v>
       </c>
       <c r="H1064" t="n">
         <v>25040</v>
@@ -31283,7 +31283,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.771689116954803</v>
+        <v>0.771689176559448</v>
       </c>
       <c r="H1066" t="n">
         <v>26733</v>
@@ -31428,7 +31428,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.826809823513031</v>
+        <v>0.826809763908386</v>
       </c>
       <c r="H1071" t="n">
         <v>3693</v>
@@ -31544,7 +31544,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.826809823513031</v>
+        <v>0.826809763908386</v>
       </c>
       <c r="H1075" t="n">
         <v>44457</v>
@@ -32095,7 +32095,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.804001331329346</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H1094" t="n">
         <v>1012</v>
@@ -32124,7 +32124,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.804001331329346</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H1095" t="n">
         <v>271</v>
@@ -32356,7 +32356,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.790696322917938</v>
+        <v>0.790696382522583</v>
       </c>
       <c r="H1103" t="n">
         <v>16565</v>
@@ -32501,7 +32501,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.805902004241943</v>
+        <v>0.805901944637299</v>
       </c>
       <c r="H1108" t="n">
         <v>23576</v>
@@ -32559,7 +32559,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1110" t="n">
         <v>73772</v>
@@ -32588,7 +32588,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H1111" t="n">
         <v>15870</v>
@@ -32617,7 +32617,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H1112" t="n">
         <v>10652</v>
@@ -32762,7 +32762,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.832511961460114</v>
+        <v>0.832511901855469</v>
       </c>
       <c r="H1117" t="n">
         <v>27258</v>
@@ -32791,7 +32791,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.826809823513031</v>
+        <v>0.826809763908386</v>
       </c>
       <c r="H1118" t="n">
         <v>6758</v>
@@ -32936,7 +32936,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H1123" t="n">
         <v>2596</v>
@@ -32965,7 +32965,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H1124" t="n">
         <v>8344</v>
@@ -32994,7 +32994,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H1125" t="n">
         <v>1772</v>
@@ -33110,7 +33110,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H1129" t="n">
         <v>13547</v>
@@ -33197,7 +33197,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H1132" t="n">
         <v>15701</v>
@@ -33226,7 +33226,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1133" t="n">
-        <v>0.828710556030273</v>
+        <v>0.828710496425629</v>
       </c>
       <c r="H1133" t="n">
         <v>12</v>
@@ -33400,7 +33400,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.832511961460114</v>
+        <v>0.832511901855469</v>
       </c>
       <c r="H1139" t="n">
         <v>11115</v>
@@ -33545,7 +33545,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.828710556030273</v>
+        <v>0.828710496425629</v>
       </c>
       <c r="H1144" t="n">
         <v>3310</v>
@@ -33574,7 +33574,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.828710556030273</v>
+        <v>0.828710496425629</v>
       </c>
       <c r="H1145" t="n">
         <v>0</v>
@@ -33603,7 +33603,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.828710556030273</v>
+        <v>0.828710496425629</v>
       </c>
       <c r="H1146" t="n">
         <v>65</v>
@@ -33719,7 +33719,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H1150" t="n">
         <v>1598</v>
@@ -33748,7 +33748,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.832511961460114</v>
+        <v>0.832511901855469</v>
       </c>
       <c r="H1151" t="n">
         <v>7919</v>
@@ -34009,7 +34009,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.800199866294861</v>
+        <v>0.800199806690216</v>
       </c>
       <c r="H1160" t="n">
         <v>7772</v>
@@ -34067,7 +34067,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.804001331329346</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H1162" t="n">
         <v>25013</v>
@@ -34154,7 +34154,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.798299014568329</v>
+        <v>0.798299074172974</v>
       </c>
       <c r="H1165" t="n">
         <v>20</v>
@@ -34183,7 +34183,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.805902004241943</v>
+        <v>0.805901944637299</v>
       </c>
       <c r="H1166" t="n">
         <v>2124</v>
@@ -34270,7 +34270,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1169" t="n">
         <v>1446</v>
@@ -34299,7 +34299,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.790696322917938</v>
+        <v>0.790696382522583</v>
       </c>
       <c r="H1170" t="n">
         <v>3253</v>
@@ -34531,7 +34531,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994184970856</v>
       </c>
       <c r="H1178" t="n">
         <v>1540</v>
@@ -34560,7 +34560,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994184970856</v>
       </c>
       <c r="H1179" t="n">
         <v>0</v>
@@ -34589,7 +34589,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185633182526</v>
       </c>
       <c r="H1180" t="n">
         <v>10010</v>
@@ -34647,7 +34647,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.804001331329346</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H1182" t="n">
         <v>10</v>
@@ -34705,7 +34705,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.773589849472046</v>
+        <v>0.773589909076691</v>
       </c>
       <c r="H1184" t="n">
         <v>3194</v>
@@ -34734,7 +34734,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.773589849472046</v>
+        <v>0.773589909076691</v>
       </c>
       <c r="H1185" t="n">
         <v>0</v>
@@ -34763,7 +34763,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.805902004241943</v>
+        <v>0.805901944637299</v>
       </c>
       <c r="H1186" t="n">
         <v>4330</v>
@@ -34850,7 +34850,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1189" t="n">
         <v>1063</v>
@@ -34879,7 +34879,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1190" t="n">
         <v>4195</v>
@@ -34995,7 +34995,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1194" t="n">
         <v>6350</v>
@@ -35082,7 +35082,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H1197" t="n">
         <v>14658</v>
@@ -35140,7 +35140,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.805902004241943</v>
+        <v>0.805901944637299</v>
       </c>
       <c r="H1199" t="n">
         <v>7747</v>
@@ -35285,7 +35285,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.805902004241943</v>
+        <v>0.805901944637299</v>
       </c>
       <c r="H1204" t="n">
         <v>1326</v>
@@ -35343,7 +35343,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1206" t="n">
         <v>1092</v>
@@ -35372,7 +35372,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.790696322917938</v>
+        <v>0.790696382522583</v>
       </c>
       <c r="H1207" t="n">
         <v>11405</v>
@@ -35401,7 +35401,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1208" t="n">
         <v>1034</v>
@@ -35430,7 +35430,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1209" t="n">
         <v>0</v>
@@ -35459,7 +35459,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.798299014568329</v>
+        <v>0.798299074172974</v>
       </c>
       <c r="H1210" t="n">
         <v>252</v>
@@ -35517,7 +35517,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.796398401260376</v>
+        <v>0.796398460865021</v>
       </c>
       <c r="H1212" t="n">
         <v>45975</v>
@@ -35604,7 +35604,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1215" t="n">
         <v>21716</v>
@@ -35633,7 +35633,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.771689116954803</v>
+        <v>0.771689176559448</v>
       </c>
       <c r="H1216" t="n">
         <v>7137</v>
@@ -35691,7 +35691,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1218" t="n">
         <v>13790</v>
@@ -35720,7 +35720,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1219" t="n">
         <v>12226</v>
@@ -35865,7 +35865,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.716568470001221</v>
+        <v>0.716568529605865</v>
       </c>
       <c r="H1224" t="n">
         <v>20445</v>
@@ -36213,7 +36213,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1236" t="n">
         <v>4134</v>
@@ -36300,7 +36300,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1239" t="n">
         <v>32699</v>
@@ -36329,7 +36329,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1240" t="n">
         <v>9919</v>
@@ -36358,7 +36358,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.750781297683716</v>
+        <v>0.750781357288361</v>
       </c>
       <c r="H1241" t="n">
         <v>5601</v>
@@ -36387,7 +36387,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1242" t="n">
         <v>6749</v>
@@ -36445,7 +36445,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1244" t="n">
         <v>43971</v>
@@ -36474,7 +36474,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1245" t="n">
         <v>5112</v>
@@ -36503,7 +36503,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1246" t="n">
         <v>16700</v>
@@ -36561,7 +36561,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185633182526</v>
       </c>
       <c r="H1248" t="n">
         <v>12890</v>
@@ -36590,7 +36590,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1249" t="n">
         <v>6774</v>
@@ -36706,7 +36706,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185633182526</v>
       </c>
       <c r="H1253" t="n">
         <v>1000</v>
@@ -36793,7 +36793,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1256" t="n">
         <v>2562</v>
@@ -36880,7 +36880,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1259" t="n">
         <v>25666</v>
@@ -36909,7 +36909,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1260" t="n">
         <v>38619</v>
@@ -36938,7 +36938,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1261" t="n">
         <v>1406</v>
@@ -36967,7 +36967,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.771689116954803</v>
+        <v>0.771689176559448</v>
       </c>
       <c r="H1262" t="n">
         <v>2127</v>
@@ -37025,7 +37025,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1264" t="n">
         <v>2413</v>
@@ -37083,7 +37083,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1266" t="n">
         <v>3759</v>
@@ -37112,7 +37112,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1267" t="n">
         <v>0</v>
@@ -37141,7 +37141,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1268" t="n">
         <v>9194</v>
@@ -37170,7 +37170,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1269" t="n">
         <v>14270</v>
@@ -37286,7 +37286,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.750781297683716</v>
+        <v>0.750781357288361</v>
       </c>
       <c r="H1273" t="n">
         <v>2014</v>
@@ -37750,7 +37750,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.726072013378143</v>
+        <v>0.726072072982788</v>
       </c>
       <c r="H1289" t="n">
         <v>1010</v>
@@ -37779,7 +37779,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.726072013378143</v>
+        <v>0.726072072982788</v>
       </c>
       <c r="H1290" t="n">
         <v>0</v>
@@ -37895,7 +37895,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1294" t="n">
         <v>30046</v>
@@ -38011,7 +38011,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.805902004241943</v>
+        <v>0.805901944637299</v>
       </c>
       <c r="H1298" t="n">
         <v>111797</v>
@@ -38040,7 +38040,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1299" t="n">
         <v>73720</v>
@@ -38069,7 +38069,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1300" t="n">
         <v>22782</v>
@@ -38243,7 +38243,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1306" t="n">
         <v>15675</v>
@@ -38272,7 +38272,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.796398401260376</v>
+        <v>0.796398460865021</v>
       </c>
       <c r="H1307" t="n">
         <v>12752</v>
@@ -38301,7 +38301,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1308" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1308" t="n">
         <v>10678</v>
@@ -38330,7 +38330,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.790696322917938</v>
+        <v>0.790696382522583</v>
       </c>
       <c r="H1309" t="n">
         <v>16227</v>
@@ -38446,7 +38446,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1313" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994184970856</v>
       </c>
       <c r="H1313" t="n">
         <v>16652</v>
@@ -38475,7 +38475,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1314" t="n">
         <v>990</v>
@@ -38504,7 +38504,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1315" t="n">
         <v>0</v>
@@ -38533,7 +38533,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185633182526</v>
       </c>
       <c r="H1316" t="n">
         <v>90943</v>
@@ -38707,7 +38707,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1322" t="n">
         <v>6424</v>
@@ -38736,7 +38736,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1323" t="n">
         <v>7011</v>
@@ -38765,7 +38765,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.750781297683716</v>
+        <v>0.750781357288361</v>
       </c>
       <c r="H1324" t="n">
         <v>7016</v>
@@ -38823,7 +38823,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1326" t="n">
         <v>4013</v>
@@ -38852,7 +38852,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1327" t="n">
         <v>2313</v>
@@ -38881,7 +38881,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185633182526</v>
       </c>
       <c r="H1328" t="n">
         <v>52080</v>
@@ -38939,7 +38939,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1330" t="n">
         <v>9538</v>
@@ -39229,7 +39229,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185633182526</v>
       </c>
       <c r="H1340" t="n">
         <v>16027</v>
@@ -39258,7 +39258,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.750781297683716</v>
+        <v>0.750781357288361</v>
       </c>
       <c r="H1341" t="n">
         <v>9119</v>
@@ -39287,7 +39287,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.750781297683716</v>
+        <v>0.750781357288361</v>
       </c>
       <c r="H1342" t="n">
         <v>5538</v>
@@ -39316,7 +39316,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.750781297683716</v>
+        <v>0.750781357288361</v>
       </c>
       <c r="H1343" t="n">
         <v>18336</v>
@@ -39548,7 +39548,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1351" t="n">
         <v>38622</v>
@@ -39577,7 +39577,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1352" t="n">
-        <v>0.750781297683716</v>
+        <v>0.750781357288361</v>
       </c>
       <c r="H1352" t="n">
         <v>16999</v>
@@ -39693,7 +39693,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1356" t="n">
         <v>34806</v>
@@ -39722,7 +39722,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.750781297683716</v>
+        <v>0.750781357288361</v>
       </c>
       <c r="H1357" t="n">
         <v>59428</v>
@@ -39780,7 +39780,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.722270548343658</v>
+        <v>0.722270607948303</v>
       </c>
       <c r="H1359" t="n">
         <v>24873</v>
@@ -39838,7 +39838,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1361" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1361" t="n">
         <v>7927</v>
@@ -39896,7 +39896,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1363" t="n">
         <v>10616</v>
@@ -40186,7 +40186,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1373" t="n">
         <v>84131</v>
@@ -40215,7 +40215,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1374" t="n">
         <v>9611</v>
@@ -40244,7 +40244,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994184970856</v>
       </c>
       <c r="H1375" t="n">
         <v>119857</v>
@@ -40331,7 +40331,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.809703409671783</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1378" t="n">
         <v>69721</v>
@@ -40447,7 +40447,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994184970856</v>
       </c>
       <c r="H1382" t="n">
         <v>47262</v>
@@ -40476,7 +40476,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1383" t="n">
-        <v>0.805902004241943</v>
+        <v>0.805901944637299</v>
       </c>
       <c r="H1383" t="n">
         <v>284246</v>
@@ -40505,7 +40505,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H1384" t="n">
         <v>665882</v>
@@ -40708,7 +40708,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.798299014568329</v>
+        <v>0.798299074172974</v>
       </c>
       <c r="H1391" t="n">
         <v>25564</v>
@@ -40737,7 +40737,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.796398401260376</v>
+        <v>0.796398460865021</v>
       </c>
       <c r="H1392" t="n">
         <v>32493</v>
@@ -40766,7 +40766,7 @@
         <v>0.842000007629395</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.800199866294861</v>
+        <v>0.800199806690216</v>
       </c>
       <c r="H1393" t="n">
         <v>43360</v>
@@ -40795,7 +40795,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.798299014568329</v>
+        <v>0.798299074172974</v>
       </c>
       <c r="H1394" t="n">
         <v>26614</v>
@@ -40824,7 +40824,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994184970856</v>
       </c>
       <c r="H1395" t="n">
         <v>26723</v>
@@ -40853,7 +40853,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G1396" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H1396" t="n">
         <v>29317</v>
@@ -40882,7 +40882,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.796398401260376</v>
+        <v>0.796398460865021</v>
       </c>
       <c r="H1397" t="n">
         <v>49629</v>
@@ -40969,7 +40969,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1400" t="n">
         <v>63141</v>
@@ -41027,7 +41027,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1402" t="n">
         <v>111019</v>
@@ -41201,7 +41201,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185633182526</v>
       </c>
       <c r="H1408" t="n">
         <v>21428</v>
@@ -41433,7 +41433,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.771689116954803</v>
+        <v>0.771689176559448</v>
       </c>
       <c r="H1416" t="n">
         <v>37771</v>
@@ -41520,7 +41520,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185633182526</v>
       </c>
       <c r="H1419" t="n">
         <v>3816</v>
@@ -41578,7 +41578,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1421" t="n">
         <v>20129</v>
@@ -41636,7 +41636,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1423" t="n">
         <v>15016</v>
@@ -41694,7 +41694,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1425" t="n">
-        <v>0.750781297683716</v>
+        <v>0.750781357288361</v>
       </c>
       <c r="H1425" t="n">
         <v>13226</v>
@@ -41810,7 +41810,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1429" t="n">
         <v>777</v>
@@ -41839,7 +41839,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1430" t="n">
         <v>0</v>
@@ -42100,7 +42100,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1439" t="n">
         <v>1167</v>
@@ -42187,7 +42187,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1442" t="n">
-        <v>0.773589849472046</v>
+        <v>0.773589909076691</v>
       </c>
       <c r="H1442" t="n">
         <v>35417</v>
@@ -42332,7 +42332,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.750781297683716</v>
+        <v>0.750781357288361</v>
       </c>
       <c r="H1447" t="n">
         <v>68819</v>
@@ -42680,7 +42680,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185633182526</v>
       </c>
       <c r="H1459" t="n">
         <v>1349</v>
@@ -42941,7 +42941,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.729873538017273</v>
+        <v>0.729873478412628</v>
       </c>
       <c r="H1468" t="n">
         <v>9182</v>
@@ -43086,7 +43086,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1473" t="n">
         <v>35727</v>
@@ -43115,7 +43115,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1474" t="n">
         <v>0</v>
@@ -43260,7 +43260,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.726072013378143</v>
+        <v>0.726072072982788</v>
       </c>
       <c r="H1479" t="n">
         <v>21017</v>
@@ -43289,7 +43289,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.729873538017273</v>
+        <v>0.729873478412628</v>
       </c>
       <c r="H1480" t="n">
         <v>49723</v>
@@ -43318,7 +43318,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1481" t="n">
-        <v>0.726072013378143</v>
+        <v>0.726072072982788</v>
       </c>
       <c r="H1481" t="n">
         <v>9281</v>
@@ -43347,7 +43347,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.726072013378143</v>
+        <v>0.726072072982788</v>
       </c>
       <c r="H1482" t="n">
         <v>0</v>
@@ -43376,7 +43376,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.729873538017273</v>
+        <v>0.729873478412628</v>
       </c>
       <c r="H1483" t="n">
         <v>19545</v>
@@ -43405,7 +43405,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.729873538017273</v>
+        <v>0.729873478412628</v>
       </c>
       <c r="H1484" t="n">
         <v>0</v>
@@ -43434,7 +43434,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.726072013378143</v>
+        <v>0.726072072982788</v>
       </c>
       <c r="H1485" t="n">
         <v>10016</v>
@@ -43463,7 +43463,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1486" t="n">
-        <v>0.716568470001221</v>
+        <v>0.716568529605865</v>
       </c>
       <c r="H1486" t="n">
         <v>3368</v>
@@ -43492,7 +43492,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.716568470001221</v>
+        <v>0.716568529605865</v>
       </c>
       <c r="H1487" t="n">
         <v>6907</v>
@@ -43521,7 +43521,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.722270548343658</v>
+        <v>0.722270607948303</v>
       </c>
       <c r="H1488" t="n">
         <v>24502</v>
@@ -43724,7 +43724,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.729873538017273</v>
+        <v>0.729873478412628</v>
       </c>
       <c r="H1495" t="n">
         <v>11534</v>
@@ -43782,7 +43782,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.726072013378143</v>
+        <v>0.726072072982788</v>
       </c>
       <c r="H1497" t="n">
         <v>27348</v>
@@ -44594,7 +44594,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.699462056159973</v>
+        <v>0.699462115764618</v>
       </c>
       <c r="H1525" t="n">
         <v>7354</v>
@@ -45087,7 +45087,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.684256434440613</v>
+        <v>0.684256374835968</v>
       </c>
       <c r="H1542" t="n">
         <v>22048</v>
@@ -45116,7 +45116,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.684256434440613</v>
+        <v>0.684256374835968</v>
       </c>
       <c r="H1543" t="n">
         <v>3322</v>
@@ -45145,7 +45145,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.699462056159973</v>
+        <v>0.699462115764618</v>
       </c>
       <c r="H1544" t="n">
         <v>4722</v>
@@ -45203,7 +45203,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.684256434440613</v>
+        <v>0.684256374835968</v>
       </c>
       <c r="H1546" t="n">
         <v>450</v>
@@ -45232,7 +45232,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.684256434440613</v>
+        <v>0.684256374835968</v>
       </c>
       <c r="H1547" t="n">
         <v>916</v>
@@ -45406,7 +45406,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1553" t="n">
-        <v>0.680455029010773</v>
+        <v>0.680454969406128</v>
       </c>
       <c r="H1553" t="n">
         <v>21106</v>
@@ -45464,7 +45464,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1555" t="n">
-        <v>0.680455029010773</v>
+        <v>0.680454969406128</v>
       </c>
       <c r="H1555" t="n">
         <v>12414</v>
@@ -45493,7 +45493,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1556" t="n">
-        <v>0.680455029010773</v>
+        <v>0.680454969406128</v>
       </c>
       <c r="H1556" t="n">
         <v>6000</v>
@@ -45580,7 +45580,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1559" t="n">
-        <v>0.729873538017273</v>
+        <v>0.729873478412628</v>
       </c>
       <c r="H1559" t="n">
         <v>105451</v>
@@ -45609,7 +45609,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1560" t="n">
-        <v>0.726072013378143</v>
+        <v>0.726072072982788</v>
       </c>
       <c r="H1560" t="n">
         <v>29042</v>
@@ -45841,7 +45841,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.676653504371643</v>
+        <v>0.676653563976288</v>
       </c>
       <c r="H1568" t="n">
         <v>23252</v>
@@ -45870,7 +45870,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1569" t="n">
-        <v>0.6557457447052</v>
+        <v>0.655745685100555</v>
       </c>
       <c r="H1569" t="n">
         <v>35484</v>
@@ -45899,7 +45899,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.657646477222443</v>
+        <v>0.657646417617798</v>
       </c>
       <c r="H1570" t="n">
         <v>16550</v>
@@ -46044,7 +46044,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.617731392383575</v>
+        <v>0.61773145198822</v>
       </c>
       <c r="H1575" t="n">
         <v>26856</v>
@@ -46218,7 +46218,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1581" t="n">
-        <v>0.657646477222443</v>
+        <v>0.657646417617798</v>
       </c>
       <c r="H1581" t="n">
         <v>43198</v>
@@ -46363,7 +46363,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1586" t="n">
-        <v>0.644341468811035</v>
+        <v>0.64434140920639</v>
       </c>
       <c r="H1586" t="n">
         <v>18130</v>
@@ -46566,7 +46566,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.644341468811035</v>
+        <v>0.64434140920639</v>
       </c>
       <c r="H1593" t="n">
         <v>10012</v>
@@ -46595,7 +46595,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.62913578748703</v>
+        <v>0.629135727882385</v>
       </c>
       <c r="H1594" t="n">
         <v>3425</v>
@@ -46624,7 +46624,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1595" t="n">
-        <v>0.638639330863953</v>
+        <v>0.638639271259308</v>
       </c>
       <c r="H1595" t="n">
         <v>22062</v>
@@ -46653,7 +46653,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.634837865829468</v>
+        <v>0.634837806224823</v>
       </c>
       <c r="H1596" t="n">
         <v>4647</v>
@@ -46682,7 +46682,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.634837865829468</v>
+        <v>0.634837806224823</v>
       </c>
       <c r="H1597" t="n">
         <v>1316</v>
@@ -46798,7 +46798,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1601" t="n">
-        <v>0.632937133312225</v>
+        <v>0.632937073707581</v>
       </c>
       <c r="H1601" t="n">
         <v>3116</v>
@@ -46827,7 +46827,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1602" t="n">
-        <v>0.632937133312225</v>
+        <v>0.632937073707581</v>
       </c>
       <c r="H1602" t="n">
         <v>16383</v>
@@ -46885,7 +46885,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.634837865829468</v>
+        <v>0.634837806224823</v>
       </c>
       <c r="H1604" t="n">
         <v>1929</v>
@@ -47001,7 +47001,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.631036520004272</v>
+        <v>0.631036460399628</v>
       </c>
       <c r="H1608" t="n">
         <v>11497</v>
@@ -47030,7 +47030,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.62913578748703</v>
+        <v>0.629135727882385</v>
       </c>
       <c r="H1609" t="n">
         <v>900</v>
@@ -47117,7 +47117,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1612" t="n">
-        <v>0.62913578748703</v>
+        <v>0.629135727882385</v>
       </c>
       <c r="H1612" t="n">
         <v>1430</v>
@@ -47146,7 +47146,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.62913578748703</v>
+        <v>0.629135727882385</v>
       </c>
       <c r="H1613" t="n">
         <v>0</v>
@@ -47320,7 +47320,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.581618010997772</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1619" t="n">
         <v>103376</v>
@@ -47349,7 +47349,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1620" t="n">
         <v>27183</v>
@@ -47407,7 +47407,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.617731392383575</v>
+        <v>0.61773145198822</v>
       </c>
       <c r="H1622" t="n">
         <v>14108</v>
@@ -47697,7 +47697,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1632" t="n">
-        <v>0.62913578748703</v>
+        <v>0.629135727882385</v>
       </c>
       <c r="H1632" t="n">
         <v>1580</v>
@@ -47726,7 +47726,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1633" t="n">
-        <v>0.61393004655838</v>
+        <v>0.613930106163025</v>
       </c>
       <c r="H1633" t="n">
         <v>28835</v>
@@ -48016,7 +48016,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1643" t="n">
-        <v>0.60252571105957</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1643" t="n">
         <v>500</v>
@@ -48045,7 +48045,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1644" t="n">
         <v>2848</v>
@@ -48103,7 +48103,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1646" t="n">
-        <v>0.581618010997772</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1646" t="n">
         <v>1464</v>
@@ -48132,7 +48132,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1647" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1647" t="n">
         <v>18796</v>
@@ -48277,7 +48277,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1652" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1652" t="n">
         <v>500</v>
@@ -48306,7 +48306,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1653" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1653" t="n">
         <v>0</v>
@@ -48393,7 +48393,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G1656" t="n">
-        <v>0.496085941791534</v>
+        <v>0.49608588218689</v>
       </c>
       <c r="H1656" t="n">
         <v>26936</v>
@@ -48451,7 +48451,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G1658" t="n">
-        <v>0.490383744239807</v>
+        <v>0.490383714437485</v>
       </c>
       <c r="H1658" t="n">
         <v>27018</v>
@@ -48567,7 +48567,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.551206469535828</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1662" t="n">
         <v>291</v>
@@ -48596,7 +48596,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.551206469535828</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1663" t="n">
         <v>1863</v>
@@ -48799,7 +48799,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1670" t="n">
-        <v>0.577816426753998</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1670" t="n">
         <v>16540</v>
@@ -48857,7 +48857,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1672" t="n">
         <v>10972</v>
@@ -48886,7 +48886,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1673" t="n">
-        <v>0.577816426753998</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1673" t="n">
         <v>8763</v>
@@ -48915,7 +48915,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1674" t="n">
         <v>5204</v>
@@ -49060,7 +49060,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1679" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1679" t="n">
         <v>42257</v>
@@ -49089,7 +49089,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1680" t="n">
         <v>5826</v>
@@ -49292,7 +49292,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.60252571105957</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1687" t="n">
         <v>564</v>
@@ -49321,7 +49321,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.60252571105957</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1688" t="n">
         <v>1061</v>
@@ -49350,7 +49350,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.60252571105957</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1689" t="n">
         <v>1</v>
@@ -49379,7 +49379,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1690" t="n">
         <v>1738</v>
@@ -49524,7 +49524,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.60252571105957</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1695" t="n">
         <v>6536</v>
@@ -49727,7 +49727,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1702" t="n">
         <v>502</v>
@@ -49930,7 +49930,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1709" t="n">
         <v>500</v>
@@ -50046,7 +50046,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1713" t="n">
-        <v>0.551206469535828</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1713" t="n">
         <v>3975</v>
@@ -50075,7 +50075,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.536000907421112</v>
+        <v>0.536000847816467</v>
       </c>
       <c r="H1714" t="n">
         <v>6327</v>
@@ -50104,7 +50104,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568313002586365</v>
       </c>
       <c r="H1715" t="n">
         <v>794</v>
@@ -50162,7 +50162,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1717" t="n">
         <v>6642</v>
@@ -50191,7 +50191,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1718" t="n">
         <v>2685</v>
@@ -50278,7 +50278,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1721" t="n">
-        <v>0.577816426753998</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1721" t="n">
         <v>8356</v>
@@ -50452,7 +50452,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1727" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1727" t="n">
         <v>9284</v>
@@ -50771,7 +50771,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1738" t="n">
-        <v>0.581618010997772</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1738" t="n">
         <v>5986</v>
@@ -50800,7 +50800,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.581618010997772</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1739" t="n">
         <v>0</v>
@@ -50829,7 +50829,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1740" t="n">
         <v>3589</v>
@@ -50887,7 +50887,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.577816426753998</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1742" t="n">
         <v>1984</v>
@@ -50945,7 +50945,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1744" t="n">
         <v>500</v>
@@ -51119,7 +51119,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1750" t="n">
         <v>25115</v>
@@ -51148,7 +51148,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1751" t="n">
         <v>5540</v>
@@ -51177,7 +51177,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1752" t="n">
         <v>81</v>
@@ -51206,7 +51206,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1753" t="n">
         <v>194</v>
@@ -51235,7 +51235,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1754" t="n">
-        <v>0.581618010997772</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1754" t="n">
         <v>17</v>
@@ -51264,7 +51264,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.581618010997772</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1755" t="n">
         <v>0</v>
@@ -51322,7 +51322,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1757" t="n">
         <v>9926</v>
@@ -51496,7 +51496,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1763" t="n">
         <v>2731</v>
@@ -51525,7 +51525,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1764" t="n">
         <v>2755</v>
@@ -51583,7 +51583,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1766" t="n">
         <v>11513</v>
@@ -51612,7 +51612,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1767" t="n">
-        <v>0.60252571105957</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1767" t="n">
         <v>624</v>
@@ -51670,7 +51670,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.60252571105957</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1769" t="n">
         <v>8114</v>
@@ -51844,7 +51844,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1775" t="n">
         <v>7172</v>
@@ -51873,7 +51873,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1776" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1776" t="n">
         <v>0</v>
@@ -52018,7 +52018,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1781" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1781" t="n">
         <v>2957</v>
@@ -52192,7 +52192,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1787" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1787" t="n">
         <v>24392</v>
@@ -52337,7 +52337,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1792" t="n">
         <v>1109</v>
@@ -52366,7 +52366,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1793" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823692321777</v>
       </c>
       <c r="H1793" t="n">
         <v>21634</v>
@@ -52569,7 +52569,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1800" t="n">
-        <v>0.581618010997772</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1800" t="n">
         <v>5988</v>
@@ -52598,7 +52598,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1801" t="n">
-        <v>0.581618010997772</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1801" t="n">
         <v>5600</v>
@@ -52656,7 +52656,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1803" t="n">
         <v>4401</v>
@@ -52917,7 +52917,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1812" t="n">
-        <v>0.581618010997772</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1812" t="n">
         <v>676</v>
@@ -53091,7 +53091,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1818" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568313002586365</v>
       </c>
       <c r="H1818" t="n">
         <v>1892</v>
@@ -53207,7 +53207,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.577816426753998</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1822" t="n">
         <v>2670</v>
@@ -53294,7 +53294,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1825" t="n">
-        <v>0.577816426753998</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1825" t="n">
         <v>3608</v>
@@ -53323,7 +53323,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568313002586365</v>
       </c>
       <c r="H1826" t="n">
         <v>73878</v>
@@ -53468,7 +53468,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1831" t="n">
         <v>18113</v>
@@ -53613,7 +53613,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.558809399604797</v>
+        <v>0.558809340000153</v>
       </c>
       <c r="H1836" t="n">
         <v>518</v>
@@ -53816,7 +53816,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568313002586365</v>
       </c>
       <c r="H1843" t="n">
         <v>1246</v>
@@ -53845,7 +53845,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1844" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1844" t="n">
         <v>3137</v>
@@ -53990,7 +53990,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1849" t="n">
         <v>17343</v>
@@ -54019,7 +54019,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568313002586365</v>
       </c>
       <c r="H1850" t="n">
         <v>7024</v>
@@ -54077,7 +54077,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1852" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1852" t="n">
         <v>667</v>
@@ -54135,7 +54135,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1854" t="n">
-        <v>0.581618010997772</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1854" t="n">
         <v>45294</v>
@@ -54164,7 +54164,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1855" t="n">
-        <v>0.581618010997772</v>
+        <v>0.581617951393127</v>
       </c>
       <c r="H1855" t="n">
         <v>18556</v>
@@ -54338,7 +54338,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1861" t="n">
         <v>1513</v>
@@ -54657,7 +54657,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568313002586365</v>
       </c>
       <c r="H1872" t="n">
         <v>11785</v>
@@ -54802,7 +54802,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1877" t="n">
-        <v>0.558809399604797</v>
+        <v>0.558809340000153</v>
       </c>
       <c r="H1877" t="n">
         <v>1202</v>
@@ -55034,7 +55034,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568313002586365</v>
       </c>
       <c r="H1885" t="n">
         <v>10634</v>
@@ -55092,7 +55092,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.558809399604797</v>
+        <v>0.558809340000153</v>
       </c>
       <c r="H1887" t="n">
         <v>2513</v>
@@ -55440,7 +55440,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1899" t="n">
-        <v>0.558809399604797</v>
+        <v>0.558809340000153</v>
       </c>
       <c r="H1899" t="n">
         <v>28638</v>
@@ -55527,7 +55527,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1902" t="n">
-        <v>0.558809399604797</v>
+        <v>0.558809340000153</v>
       </c>
       <c r="H1902" t="n">
         <v>2565</v>
@@ -55556,7 +55556,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1903" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568313002586365</v>
       </c>
       <c r="H1903" t="n">
         <v>8412</v>
@@ -55585,7 +55585,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1904" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568313002586365</v>
       </c>
       <c r="H1904" t="n">
         <v>2017</v>
@@ -55817,7 +55817,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1912" t="n">
-        <v>0.551206469535828</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1912" t="n">
         <v>932</v>
@@ -55846,7 +55846,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1913" t="n">
-        <v>0.551206469535828</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1913" t="n">
         <v>0</v>
@@ -56078,7 +56078,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1921" t="n">
-        <v>0.551206469535828</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1921" t="n">
         <v>3019</v>
@@ -56107,7 +56107,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1922" t="n">
-        <v>0.551206469535828</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1922" t="n">
         <v>4387</v>
@@ -56484,7 +56484,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1935" t="n">
-        <v>0.591121435165405</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1935" t="n">
         <v>12816</v>
@@ -56658,7 +56658,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1941" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568313002586365</v>
       </c>
       <c r="H1941" t="n">
         <v>1989</v>
@@ -56977,7 +56977,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1952" t="n">
-        <v>0.558809399604797</v>
+        <v>0.558809340000153</v>
       </c>
       <c r="H1952" t="n">
         <v>220</v>
@@ -57035,7 +57035,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1954" t="n">
-        <v>0.558809399604797</v>
+        <v>0.558809340000153</v>
       </c>
       <c r="H1954" t="n">
         <v>701</v>
@@ -57296,7 +57296,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1963" t="n">
-        <v>0.551206469535828</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1963" t="n">
         <v>7001</v>
@@ -79965,7 +79965,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="D2745" t="n">
-        <v>1.22500002384186</v>
+        <v>1.23000001907349</v>
       </c>
       <c r="E2745" t="n">
         <v>1.20000004768372</v>
@@ -79980,6 +79980,35 @@
         <v>18600</v>
       </c>
       <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>1.22000002861023</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>1.2150000333786</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>1.2150000333786</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -456,7 +456,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G3" t="n">
-        <v>1.55858409404755</v>
+        <v>1.55858397483826</v>
       </c>
       <c r="H3" t="n">
         <v>10710</v>
@@ -514,7 +514,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G5" t="n">
-        <v>1.46544921398163</v>
+        <v>1.46544909477234</v>
       </c>
       <c r="H5" t="n">
         <v>12095</v>
@@ -543,7 +543,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G6" t="n">
-        <v>1.53482508659363</v>
+        <v>1.53482520580292</v>
       </c>
       <c r="H6" t="n">
         <v>31459</v>
@@ -601,7 +601,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G8" t="n">
-        <v>1.49205911159515</v>
+        <v>1.49205899238586</v>
       </c>
       <c r="H8" t="n">
         <v>9900</v>
@@ -688,7 +688,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G11" t="n">
-        <v>1.34000217914581</v>
+        <v>1.34000205993652</v>
       </c>
       <c r="H11" t="n">
         <v>24720</v>
@@ -717,7 +717,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G12" t="n">
-        <v>1.29248416423798</v>
+        <v>1.29248428344727</v>
       </c>
       <c r="H12" t="n">
         <v>12641</v>
@@ -804,7 +804,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>1.22595942020416</v>
+        <v>1.22595930099487</v>
       </c>
       <c r="H15" t="n">
         <v>10438</v>
@@ -862,7 +862,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G17" t="n">
-        <v>1.30198788642883</v>
+        <v>1.30198800563812</v>
       </c>
       <c r="H17" t="n">
         <v>5838</v>
@@ -891,7 +891,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G18" t="n">
-        <v>1.30198788642883</v>
+        <v>1.30198800563812</v>
       </c>
       <c r="H18" t="n">
         <v>4474</v>
@@ -978,7 +978,7 @@
         <v>1.375</v>
       </c>
       <c r="G21" t="n">
-        <v>1.30673968791962</v>
+        <v>1.30673956871033</v>
       </c>
       <c r="H21" t="n">
         <v>1302</v>
@@ -1065,7 +1065,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G24" t="n">
-        <v>1.33049845695496</v>
+        <v>1.33049857616425</v>
       </c>
       <c r="H24" t="n">
         <v>8036</v>
@@ -1210,7 +1210,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G29" t="n">
-        <v>1.14137780666351</v>
+        <v>1.14137768745422</v>
       </c>
       <c r="H29" t="n">
         <v>1659</v>
@@ -1239,7 +1239,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G30" t="n">
-        <v>1.13662600517273</v>
+        <v>1.13662588596344</v>
       </c>
       <c r="H30" t="n">
         <v>1130</v>
@@ -1268,7 +1268,7 @@
         <v>1.16100001335144</v>
       </c>
       <c r="G31" t="n">
-        <v>1.10336351394653</v>
+        <v>1.10336339473724</v>
       </c>
       <c r="H31" t="n">
         <v>6020</v>
@@ -1297,7 +1297,7 @@
         <v>1.28999996185303</v>
       </c>
       <c r="G32" t="n">
-        <v>1.22595942020416</v>
+        <v>1.22595930099487</v>
       </c>
       <c r="H32" t="n">
         <v>23660</v>
@@ -1326,7 +1326,7 @@
         <v>1.375</v>
       </c>
       <c r="G33" t="n">
-        <v>1.30673968791962</v>
+        <v>1.30673956871033</v>
       </c>
       <c r="H33" t="n">
         <v>9139</v>
@@ -1384,7 +1384,7 @@
         <v>1.35899996757507</v>
       </c>
       <c r="G35" t="n">
-        <v>1.29153406620026</v>
+        <v>1.29153394699097</v>
       </c>
       <c r="H35" t="n">
         <v>2501</v>
@@ -1471,7 +1471,7 @@
         <v>1.32400000095367</v>
       </c>
       <c r="G38" t="n">
-        <v>1.25827145576477</v>
+        <v>1.25827133655548</v>
       </c>
       <c r="H38" t="n">
         <v>12260</v>
@@ -1587,7 +1587,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G42" t="n">
-        <v>1.29723596572876</v>
+        <v>1.29723608493805</v>
       </c>
       <c r="H42" t="n">
         <v>3745</v>
@@ -1674,7 +1674,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G45" t="n">
-        <v>1.32099509239197</v>
+        <v>1.32099497318268</v>
       </c>
       <c r="H45" t="n">
         <v>1400</v>
@@ -1703,7 +1703,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>1.28773260116577</v>
+        <v>1.28773248195648</v>
       </c>
       <c r="H46" t="n">
         <v>3247</v>
@@ -1790,7 +1790,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>1.30103743076324</v>
+        <v>1.30103754997253</v>
       </c>
       <c r="H49" t="n">
         <v>8270</v>
@@ -1819,7 +1819,7 @@
         <v>1.36000001430511</v>
       </c>
       <c r="G50" t="n">
-        <v>1.29248416423798</v>
+        <v>1.29248428344727</v>
       </c>
       <c r="H50" t="n">
         <v>1410</v>
@@ -1848,7 +1848,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G51" t="n">
-        <v>1.33049845695496</v>
+        <v>1.33049857616425</v>
       </c>
       <c r="H51" t="n">
         <v>5788</v>
@@ -1935,7 +1935,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G54" t="n">
-        <v>1.32099509239197</v>
+        <v>1.32099497318268</v>
       </c>
       <c r="H54" t="n">
         <v>1500</v>
@@ -1964,7 +1964,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G55" t="n">
-        <v>1.27537798881531</v>
+        <v>1.27537786960602</v>
       </c>
       <c r="H55" t="n">
         <v>10250</v>
@@ -1993,7 +1993,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G56" t="n">
-        <v>1.27537798881531</v>
+        <v>1.27537786960602</v>
       </c>
       <c r="H56" t="n">
         <v>709</v>
@@ -2022,7 +2022,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G57" t="n">
-        <v>1.27537798881531</v>
+        <v>1.27537786960602</v>
       </c>
       <c r="H57" t="n">
         <v>36</v>
@@ -2051,7 +2051,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G58" t="n">
-        <v>1.26967561244965</v>
+        <v>1.26967573165894</v>
       </c>
       <c r="H58" t="n">
         <v>21406</v>
@@ -2109,7 +2109,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G60" t="n">
-        <v>1.27537798881531</v>
+        <v>1.27537786960602</v>
       </c>
       <c r="H60" t="n">
         <v>6529</v>
@@ -2138,7 +2138,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G61" t="n">
-        <v>1.27157652378082</v>
+        <v>1.27157640457153</v>
       </c>
       <c r="H61" t="n">
         <v>1297</v>
@@ -2167,7 +2167,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G62" t="n">
-        <v>1.26207292079926</v>
+        <v>1.26207280158997</v>
       </c>
       <c r="H62" t="n">
         <v>2000</v>
@@ -2254,7 +2254,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G65" t="n">
-        <v>1.26017224788666</v>
+        <v>1.26017212867737</v>
       </c>
       <c r="H65" t="n">
         <v>13431</v>
@@ -2283,7 +2283,7 @@
         <v>1.30400002002716</v>
       </c>
       <c r="G66" t="n">
-        <v>1.23926448822021</v>
+        <v>1.23926436901093</v>
       </c>
       <c r="H66" t="n">
         <v>12363</v>
@@ -2399,7 +2399,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G70" t="n">
-        <v>1.24781739711761</v>
+        <v>1.2478175163269</v>
       </c>
       <c r="H70" t="n">
         <v>3528</v>
@@ -2428,7 +2428,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G71" t="n">
-        <v>1.24306571483612</v>
+        <v>1.24306583404541</v>
       </c>
       <c r="H71" t="n">
         <v>1224</v>
@@ -2515,7 +2515,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G74" t="n">
-        <v>1.27537798881531</v>
+        <v>1.27537786960602</v>
       </c>
       <c r="H74" t="n">
         <v>413</v>
@@ -2573,7 +2573,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G76" t="n">
-        <v>1.26967561244965</v>
+        <v>1.26967573165894</v>
       </c>
       <c r="H76" t="n">
         <v>8995</v>
@@ -2689,7 +2689,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27917921543121</v>
+        <v>1.2791793346405</v>
       </c>
       <c r="H80" t="n">
         <v>1743</v>
@@ -2718,7 +2718,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G81" t="n">
-        <v>1.27917921543121</v>
+        <v>1.2791793346405</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G83" t="n">
-        <v>1.26207292079926</v>
+        <v>1.26207280158997</v>
       </c>
       <c r="H83" t="n">
         <v>22657</v>
@@ -2834,7 +2834,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G85" t="n">
-        <v>1.26207292079926</v>
+        <v>1.26207280158997</v>
       </c>
       <c r="H85" t="n">
         <v>4053</v>
@@ -2863,7 +2863,7 @@
         <v>1.34200000762939</v>
       </c>
       <c r="G86" t="n">
-        <v>1.27537798881531</v>
+        <v>1.27537786960602</v>
       </c>
       <c r="H86" t="n">
         <v>1199</v>
@@ -2921,7 +2921,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G88" t="n">
-        <v>1.26207292079926</v>
+        <v>1.26207280158997</v>
       </c>
       <c r="H88" t="n">
         <v>2439</v>
@@ -2979,7 +2979,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G90" t="n">
-        <v>1.30103743076324</v>
+        <v>1.30103754997253</v>
       </c>
       <c r="H90" t="n">
         <v>100</v>
@@ -3008,7 +3008,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G91" t="n">
-        <v>1.30103743076324</v>
+        <v>1.30103754997253</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>1.25899994373322</v>
       </c>
       <c r="G102" t="n">
-        <v>1.19649827480316</v>
+        <v>1.19649815559387</v>
       </c>
       <c r="H102" t="n">
         <v>12993</v>
@@ -3356,7 +3356,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G103" t="n">
-        <v>1.16133522987366</v>
+        <v>1.16133499145508</v>
       </c>
       <c r="H103" t="n">
         <v>8484</v>
@@ -3472,7 +3472,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G107" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749106884003</v>
       </c>
       <c r="H107" t="n">
         <v>2700</v>
@@ -3501,7 +3501,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G108" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749106884003</v>
       </c>
       <c r="H108" t="n">
         <v>500</v>
@@ -3530,7 +3530,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G109" t="n">
-        <v>1.17559039592743</v>
+        <v>1.17559051513672</v>
       </c>
       <c r="H109" t="n">
         <v>2635</v>
@@ -3588,7 +3588,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G111" t="n">
-        <v>1.1480301618576</v>
+        <v>1.14803004264832</v>
       </c>
       <c r="H111" t="n">
         <v>30565</v>
@@ -3646,7 +3646,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H113" t="n">
         <v>202</v>
@@ -3675,7 +3675,7 @@
         <v>1.18900001049042</v>
       </c>
       <c r="G114" t="n">
-        <v>1.12997353076935</v>
+        <v>1.12997341156006</v>
       </c>
       <c r="H114" t="n">
         <v>8251</v>
@@ -3733,7 +3733,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G116" t="n">
-        <v>1.09481012821198</v>
+        <v>1.09481024742126</v>
       </c>
       <c r="H116" t="n">
         <v>4584</v>
@@ -3762,7 +3762,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H117" t="n">
         <v>22400</v>
@@ -3791,7 +3791,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G118" t="n">
-        <v>1.17273950576782</v>
+        <v>1.17273938655853</v>
       </c>
       <c r="H118" t="n">
         <v>632</v>
@@ -3878,7 +3878,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G121" t="n">
-        <v>1.13187408447266</v>
+        <v>1.13187396526337</v>
       </c>
       <c r="H121" t="n">
         <v>5919</v>
@@ -3936,7 +3936,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G123" t="n">
-        <v>1.13662600517273</v>
+        <v>1.13662588596344</v>
       </c>
       <c r="H123" t="n">
         <v>15822</v>
@@ -3965,7 +3965,7 @@
         <v>1.02300000190735</v>
       </c>
       <c r="G124" t="n">
-        <v>0.97221428155899</v>
+        <v>0.972214341163635</v>
       </c>
       <c r="H124" t="n">
         <v>9233</v>
@@ -4110,7 +4110,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G129" t="n">
-        <v>1.06439876556396</v>
+        <v>1.06439888477325</v>
       </c>
       <c r="H129" t="n">
         <v>33799</v>
@@ -4197,7 +4197,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G132" t="n">
-        <v>0.955107927322388</v>
+        <v>0.955107867717743</v>
       </c>
       <c r="H132" t="n">
         <v>51084</v>
@@ -4226,7 +4226,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G133" t="n">
-        <v>0.995022833347321</v>
+        <v>0.99502295255661</v>
       </c>
       <c r="H133" t="n">
         <v>5798</v>
@@ -4255,7 +4255,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G134" t="n">
-        <v>1.02068257331848</v>
+        <v>1.02068245410919</v>
       </c>
       <c r="H134" t="n">
         <v>1695</v>
@@ -4284,7 +4284,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G135" t="n">
-        <v>1.00547671318054</v>
+        <v>1.00547683238983</v>
       </c>
       <c r="H135" t="n">
         <v>11813</v>
@@ -4313,7 +4313,7 @@
         <v>1.05200004577637</v>
       </c>
       <c r="G136" t="n">
-        <v>0.999774575233459</v>
+        <v>0.999774694442749</v>
       </c>
       <c r="H136" t="n">
         <v>12850</v>
@@ -4342,7 +4342,7 @@
         <v>1.02699995040894</v>
       </c>
       <c r="G137" t="n">
-        <v>0.976015686988831</v>
+        <v>0.976015567779541</v>
       </c>
       <c r="H137" t="n">
         <v>13243</v>
@@ -4487,7 +4487,7 @@
         <v>1.01300001144409</v>
       </c>
       <c r="G142" t="n">
-        <v>0.962710797786713</v>
+        <v>0.962710738182068</v>
       </c>
       <c r="H142" t="n">
         <v>500</v>
@@ -4516,7 +4516,7 @@
         <v>1.01300001144409</v>
       </c>
       <c r="G143" t="n">
-        <v>0.962710797786713</v>
+        <v>0.962710738182068</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>1.01300001144409</v>
       </c>
       <c r="G144" t="n">
-        <v>0.962710797786713</v>
+        <v>0.962710738182068</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G146" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H146" t="n">
         <v>7470</v>
@@ -4632,7 +4632,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G147" t="n">
-        <v>0.995022833347321</v>
+        <v>0.99502295255661</v>
       </c>
       <c r="H147" t="n">
         <v>10351</v>
@@ -4690,7 +4690,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G149" t="n">
-        <v>1.00927829742432</v>
+        <v>1.00927817821503</v>
       </c>
       <c r="H149" t="n">
         <v>9425</v>
@@ -4719,7 +4719,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G150" t="n">
-        <v>1.03588831424713</v>
+        <v>1.03588819503784</v>
       </c>
       <c r="H150" t="n">
         <v>1564</v>
@@ -4748,7 +4748,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G151" t="n">
-        <v>0.987420082092285</v>
+        <v>0.987419903278351</v>
       </c>
       <c r="H151" t="n">
         <v>15266</v>
@@ -4777,7 +4777,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G152" t="n">
-        <v>0.986469566822052</v>
+        <v>0.986469626426697</v>
       </c>
       <c r="H152" t="n">
         <v>5343</v>
@@ -4806,7 +4806,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G153" t="n">
-        <v>0.986469566822052</v>
+        <v>0.986469626426697</v>
       </c>
       <c r="H153" t="n">
         <v>1577</v>
@@ -5038,7 +5038,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G161" t="n">
-        <v>0.980767428874969</v>
+        <v>0.980767369270325</v>
       </c>
       <c r="H161" t="n">
         <v>9930</v>
@@ -5096,7 +5096,7 @@
         <v>1.02699995040894</v>
       </c>
       <c r="G163" t="n">
-        <v>0.976015686988831</v>
+        <v>0.976015567779541</v>
       </c>
       <c r="H163" t="n">
         <v>1600</v>
@@ -5125,7 +5125,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G164" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H164" t="n">
         <v>250</v>
@@ -5154,7 +5154,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G165" t="n">
-        <v>0.963661193847656</v>
+        <v>0.963661134243011</v>
       </c>
       <c r="H165" t="n">
         <v>3542</v>
@@ -5183,7 +5183,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G166" t="n">
-        <v>0.967462480068207</v>
+        <v>0.967462539672852</v>
       </c>
       <c r="H166" t="n">
         <v>14544</v>
@@ -5212,7 +5212,7 @@
         <v>1.01699995994568</v>
       </c>
       <c r="G167" t="n">
-        <v>0.966512084007263</v>
+        <v>0.966512143611908</v>
       </c>
       <c r="H167" t="n">
         <v>5722</v>
@@ -5241,7 +5241,7 @@
         <v>1.02300000190735</v>
       </c>
       <c r="G168" t="n">
-        <v>0.97221428155899</v>
+        <v>0.972214341163635</v>
       </c>
       <c r="H168" t="n">
         <v>2389</v>
@@ -5270,7 +5270,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G169" t="n">
-        <v>0.986469566822052</v>
+        <v>0.986469626426697</v>
       </c>
       <c r="H169" t="n">
         <v>835</v>
@@ -5299,7 +5299,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G170" t="n">
-        <v>0.973164677619934</v>
+        <v>0.973164737224579</v>
       </c>
       <c r="H170" t="n">
         <v>7003</v>
@@ -5328,7 +5328,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G171" t="n">
-        <v>0.995022833347321</v>
+        <v>0.99502295255661</v>
       </c>
       <c r="H171" t="n">
         <v>2072</v>
@@ -5357,7 +5357,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G172" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H172" t="n">
         <v>10607</v>
@@ -5386,7 +5386,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G173" t="n">
-        <v>1.00547671318054</v>
+        <v>1.00547683238983</v>
       </c>
       <c r="H173" t="n">
         <v>1</v>
@@ -5444,7 +5444,7 @@
         <v>1.10699999332428</v>
       </c>
       <c r="G175" t="n">
-        <v>1.05204427242279</v>
+        <v>1.0520441532135</v>
       </c>
       <c r="H175" t="n">
         <v>96347</v>
@@ -5531,7 +5531,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G178" t="n">
-        <v>1.1518315076828</v>
+        <v>1.15183162689209</v>
       </c>
       <c r="H178" t="n">
         <v>81424</v>
@@ -5560,7 +5560,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G179" t="n">
-        <v>1.12427115440369</v>
+        <v>1.12427127361298</v>
       </c>
       <c r="H179" t="n">
         <v>16527</v>
@@ -5589,7 +5589,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G180" t="n">
-        <v>1.06820023059845</v>
+        <v>1.06820011138916</v>
       </c>
       <c r="H180" t="n">
         <v>18988</v>
@@ -5734,7 +5734,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G185" t="n">
-        <v>1.08910799026489</v>
+        <v>1.08910810947418</v>
       </c>
       <c r="H185" t="n">
         <v>2769</v>
@@ -5821,7 +5821,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G188" t="n">
-        <v>1.03588831424713</v>
+        <v>1.03588819503784</v>
       </c>
       <c r="H188" t="n">
         <v>4450</v>
@@ -5850,7 +5850,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G189" t="n">
-        <v>1.00072491168976</v>
+        <v>1.00072503089905</v>
       </c>
       <c r="H189" t="n">
         <v>8629</v>
@@ -5879,7 +5879,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G190" t="n">
-        <v>1.00262558460236</v>
+        <v>1.00262546539307</v>
       </c>
       <c r="H190" t="n">
         <v>1609</v>
@@ -5908,7 +5908,7 @@
         <v>1.04299998283386</v>
       </c>
       <c r="G191" t="n">
-        <v>0.991221487522125</v>
+        <v>0.991221368312836</v>
       </c>
       <c r="H191" t="n">
         <v>16155</v>
@@ -5937,7 +5937,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G192" t="n">
-        <v>0.987420082092285</v>
+        <v>0.987419903278351</v>
       </c>
       <c r="H192" t="n">
         <v>2600</v>
@@ -6053,7 +6053,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G196" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H196" t="n">
         <v>305</v>
@@ -6140,7 +6140,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G199" t="n">
-        <v>0.986469566822052</v>
+        <v>0.986469626426697</v>
       </c>
       <c r="H199" t="n">
         <v>1462</v>
@@ -6227,7 +6227,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G202" t="n">
-        <v>0.963661193847656</v>
+        <v>0.963661134243011</v>
       </c>
       <c r="H202" t="n">
         <v>4000</v>
@@ -6372,7 +6372,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G207" t="n">
-        <v>0.987420082092285</v>
+        <v>0.987419903278351</v>
       </c>
       <c r="H207" t="n">
         <v>9988</v>
@@ -6401,7 +6401,7 @@
         <v>1.02699995040894</v>
       </c>
       <c r="G208" t="n">
-        <v>0.976015686988831</v>
+        <v>0.976015567779541</v>
       </c>
       <c r="H208" t="n">
         <v>10816</v>
@@ -6430,7 +6430,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G209" t="n">
-        <v>1.00357604026794</v>
+        <v>1.00357592105865</v>
       </c>
       <c r="H209" t="n">
         <v>13457</v>
@@ -6459,7 +6459,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G210" t="n">
-        <v>0.971263885498047</v>
+        <v>0.971263945102692</v>
       </c>
       <c r="H210" t="n">
         <v>1000</v>
@@ -6488,7 +6488,7 @@
         <v>1.02699995040894</v>
       </c>
       <c r="G211" t="n">
-        <v>0.976015686988831</v>
+        <v>0.976015567779541</v>
       </c>
       <c r="H211" t="n">
         <v>5254</v>
@@ -6517,7 +6517,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G212" t="n">
-        <v>0.973164677619934</v>
+        <v>0.973164737224579</v>
       </c>
       <c r="H212" t="n">
         <v>900</v>
@@ -6604,7 +6604,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H215" t="n">
         <v>2077</v>
@@ -6662,7 +6662,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G217" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H217" t="n">
         <v>480</v>
@@ -6720,7 +6720,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G219" t="n">
-        <v>0.955107927322388</v>
+        <v>0.955107867717743</v>
       </c>
       <c r="H219" t="n">
         <v>6120</v>
@@ -6749,7 +6749,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G220" t="n">
-        <v>0.955107927322388</v>
+        <v>0.955107867717743</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G222" t="n">
-        <v>0.971263885498047</v>
+        <v>0.971263945102692</v>
       </c>
       <c r="H222" t="n">
         <v>700</v>
@@ -6836,7 +6836,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G223" t="n">
-        <v>0.973164677619934</v>
+        <v>0.973164737224579</v>
       </c>
       <c r="H223" t="n">
         <v>5403</v>
@@ -6865,7 +6865,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>1.02638447284698</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H224" t="n">
         <v>16296</v>
@@ -6894,7 +6894,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G225" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H225" t="n">
         <v>27306</v>
@@ -6923,7 +6923,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G226" t="n">
-        <v>0.961760401725769</v>
+        <v>0.961760342121124</v>
       </c>
       <c r="H226" t="n">
         <v>6335</v>
@@ -6952,7 +6952,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G227" t="n">
-        <v>0.967462480068207</v>
+        <v>0.967462539672852</v>
       </c>
       <c r="H227" t="n">
         <v>15742</v>
@@ -6981,7 +6981,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H228" t="n">
         <v>2724</v>
@@ -7010,7 +7010,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H229" t="n">
         <v>11827</v>
@@ -7097,7 +7097,7 @@
         <v>0.998499989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>0.948930501937866</v>
+        <v>0.948930561542511</v>
       </c>
       <c r="H232" t="n">
         <v>17878</v>
@@ -7155,7 +7155,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G234" t="n">
-        <v>0.957958936691284</v>
+        <v>0.957959055900574</v>
       </c>
       <c r="H234" t="n">
         <v>2310</v>
@@ -7213,7 +7213,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G236" t="n">
-        <v>0.973164677619934</v>
+        <v>0.973164737224579</v>
       </c>
       <c r="H236" t="n">
         <v>261</v>
@@ -7242,7 +7242,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G237" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7300,7 +7300,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G239" t="n">
-        <v>0.961760401725769</v>
+        <v>0.961760342121124</v>
       </c>
       <c r="H239" t="n">
         <v>2678</v>
@@ -7358,7 +7358,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G241" t="n">
-        <v>1.00357604026794</v>
+        <v>1.00357592105865</v>
       </c>
       <c r="H241" t="n">
         <v>19196</v>
@@ -7387,7 +7387,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G242" t="n">
-        <v>1.00262558460236</v>
+        <v>1.00262546539307</v>
       </c>
       <c r="H242" t="n">
         <v>340</v>
@@ -7445,7 +7445,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G244" t="n">
-        <v>0.980767428874969</v>
+        <v>0.980767369270325</v>
       </c>
       <c r="H244" t="n">
         <v>10086</v>
@@ -7561,7 +7561,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G248" t="n">
-        <v>0.987420082092285</v>
+        <v>0.987419903278351</v>
       </c>
       <c r="H248" t="n">
         <v>20000</v>
@@ -7619,7 +7619,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G250" t="n">
-        <v>0.973164677619934</v>
+        <v>0.973164737224579</v>
       </c>
       <c r="H250" t="n">
         <v>51760</v>
@@ -7648,7 +7648,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G251" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H251" t="n">
         <v>36947</v>
@@ -7677,7 +7677,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G252" t="n">
-        <v>0.963661193847656</v>
+        <v>0.963661134243011</v>
       </c>
       <c r="H252" t="n">
         <v>13025</v>
@@ -7851,7 +7851,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G258" t="n">
-        <v>0.983618557453156</v>
+        <v>0.9836186170578</v>
       </c>
       <c r="H258" t="n">
         <v>98439</v>
@@ -7938,7 +7938,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G261" t="n">
-        <v>1.04254078865051</v>
+        <v>1.04254066944122</v>
       </c>
       <c r="H261" t="n">
         <v>183087</v>
@@ -7967,7 +7967,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G262" t="n">
-        <v>1.17654073238373</v>
+        <v>1.17654085159302</v>
       </c>
       <c r="H262" t="n">
         <v>297642</v>
@@ -8141,7 +8141,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G268" t="n">
-        <v>1.33049845695496</v>
+        <v>1.33049857616425</v>
       </c>
       <c r="H268" t="n">
         <v>188065</v>
@@ -8170,7 +8170,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G269" t="n">
-        <v>1.34000217914581</v>
+        <v>1.34000205993652</v>
       </c>
       <c r="H269" t="n">
         <v>298958</v>
@@ -8257,7 +8257,7 @@
         <v>1.33399999141693</v>
       </c>
       <c r="G272" t="n">
-        <v>1.26777493953705</v>
+        <v>1.26777505874634</v>
       </c>
       <c r="H272" t="n">
         <v>118198</v>
@@ -8286,7 +8286,7 @@
         <v>1.29499995708466</v>
       </c>
       <c r="G273" t="n">
-        <v>1.23071122169495</v>
+        <v>1.23071110248566</v>
       </c>
       <c r="H273" t="n">
         <v>105663</v>
@@ -8489,7 +8489,7 @@
         <v>1.31099998950958</v>
       </c>
       <c r="G280" t="n">
-        <v>1.2459169626236</v>
+        <v>1.24591684341431</v>
       </c>
       <c r="H280" t="n">
         <v>14708</v>
@@ -8518,7 +8518,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G281" t="n">
-        <v>1.24781739711761</v>
+        <v>1.2478175163269</v>
       </c>
       <c r="H281" t="n">
         <v>17255</v>
@@ -8547,7 +8547,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G282" t="n">
-        <v>1.26207292079926</v>
+        <v>1.26207280158997</v>
       </c>
       <c r="H282" t="n">
         <v>16948</v>
@@ -8576,7 +8576,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G283" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749106884003</v>
       </c>
       <c r="H283" t="n">
         <v>73831</v>
@@ -8605,7 +8605,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H284" t="n">
         <v>55023</v>
@@ -8721,7 +8721,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G288" t="n">
-        <v>1.12142014503479</v>
+        <v>1.12142026424408</v>
       </c>
       <c r="H288" t="n">
         <v>46988</v>
@@ -8837,7 +8837,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>1.09766125679016</v>
+        <v>1.09766113758087</v>
       </c>
       <c r="H292" t="n">
         <v>16347</v>
@@ -8982,7 +8982,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G297" t="n">
-        <v>1.05964696407318</v>
+        <v>1.05964708328247</v>
       </c>
       <c r="H297" t="n">
         <v>16179</v>
@@ -9011,7 +9011,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G298" t="n">
-        <v>1.06439876556396</v>
+        <v>1.06439888477325</v>
       </c>
       <c r="H298" t="n">
         <v>25146</v>
@@ -9098,7 +9098,7 @@
         <v>1.21899998188019</v>
       </c>
       <c r="G301" t="n">
-        <v>1.15848398208618</v>
+        <v>1.15848410129547</v>
       </c>
       <c r="H301" t="n">
         <v>201854</v>
@@ -9127,7 +9127,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G302" t="n">
-        <v>1.14137780666351</v>
+        <v>1.14137768745422</v>
       </c>
       <c r="H302" t="n">
         <v>82096</v>
@@ -9185,7 +9185,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G304" t="n">
-        <v>1.14137780666351</v>
+        <v>1.14137768745422</v>
       </c>
       <c r="H304" t="n">
         <v>14932</v>
@@ -9272,7 +9272,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G307" t="n">
-        <v>1.1508811712265</v>
+        <v>1.15088129043579</v>
       </c>
       <c r="H307" t="n">
         <v>26808</v>
@@ -9330,7 +9330,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G309" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H309" t="n">
         <v>25871</v>
@@ -9359,7 +9359,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G310" t="n">
-        <v>1.13662600517273</v>
+        <v>1.13662588596344</v>
       </c>
       <c r="H310" t="n">
         <v>18377</v>
@@ -9388,7 +9388,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G311" t="n">
-        <v>1.1518315076828</v>
+        <v>1.15183162689209</v>
       </c>
       <c r="H311" t="n">
         <v>17084</v>
@@ -9446,7 +9446,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>1.14042735099792</v>
+        <v>1.14042747020721</v>
       </c>
       <c r="H313" t="n">
         <v>17880</v>
@@ -9504,7 +9504,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G315" t="n">
-        <v>1.13282454013824</v>
+        <v>1.13282442092896</v>
       </c>
       <c r="H315" t="n">
         <v>19395</v>
@@ -9533,7 +9533,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H316" t="n">
         <v>17705</v>
@@ -9562,7 +9562,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G317" t="n">
-        <v>1.12522172927856</v>
+        <v>1.12522161006927</v>
       </c>
       <c r="H317" t="n">
         <v>18494</v>
@@ -9765,7 +9765,7 @@
         <v>1.20099997520447</v>
       </c>
       <c r="G324" t="n">
-        <v>1.14137780666351</v>
+        <v>1.14137768745422</v>
       </c>
       <c r="H324" t="n">
         <v>6730</v>
@@ -9881,7 +9881,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G328" t="n">
-        <v>1.12807273864746</v>
+        <v>1.12807285785675</v>
       </c>
       <c r="H328" t="n">
         <v>9540</v>
@@ -10200,7 +10200,7 @@
         <v>1.18900001049042</v>
       </c>
       <c r="G339" t="n">
-        <v>1.12997353076935</v>
+        <v>1.12997341156006</v>
       </c>
       <c r="H339" t="n">
         <v>5820</v>
@@ -10229,7 +10229,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>1.11286699771881</v>
+        <v>1.11286687850952</v>
       </c>
       <c r="H340" t="n">
         <v>7409</v>
@@ -10287,7 +10287,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G342" t="n">
-        <v>1.12142014503479</v>
+        <v>1.12142026424408</v>
       </c>
       <c r="H342" t="n">
         <v>14737</v>
@@ -10403,7 +10403,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G346" t="n">
-        <v>1.08910799026489</v>
+        <v>1.08910810947418</v>
       </c>
       <c r="H346" t="n">
         <v>14320</v>
@@ -10490,7 +10490,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G349" t="n">
-        <v>1.12522172927856</v>
+        <v>1.12522161006927</v>
       </c>
       <c r="H349" t="n">
         <v>11135</v>
@@ -10519,7 +10519,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G350" t="n">
-        <v>1.12142014503479</v>
+        <v>1.12142026424408</v>
       </c>
       <c r="H350" t="n">
         <v>2609</v>
@@ -10693,7 +10693,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G356" t="n">
-        <v>1.09385979175568</v>
+        <v>1.09385991096497</v>
       </c>
       <c r="H356" t="n">
         <v>510</v>
@@ -10780,7 +10780,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G359" t="n">
-        <v>1.06249809265137</v>
+        <v>1.06249821186066</v>
       </c>
       <c r="H359" t="n">
         <v>87083</v>
@@ -10809,7 +10809,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G360" t="n">
-        <v>1.04919302463531</v>
+        <v>1.0491931438446</v>
       </c>
       <c r="H360" t="n">
         <v>10968</v>
@@ -10867,7 +10867,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G362" t="n">
-        <v>1.09956204891205</v>
+        <v>1.09956192970276</v>
       </c>
       <c r="H362" t="n">
         <v>393819</v>
@@ -10983,7 +10983,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G366" t="n">
-        <v>1.04919302463531</v>
+        <v>1.0491931438446</v>
       </c>
       <c r="H366" t="n">
         <v>56985</v>
@@ -11012,7 +11012,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G367" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H367" t="n">
         <v>43857</v>
@@ -11070,7 +11070,7 @@
         <v>1.10899996757507</v>
       </c>
       <c r="G369" t="n">
-        <v>1.05394506454468</v>
+        <v>1.05394494533539</v>
       </c>
       <c r="H369" t="n">
         <v>12555</v>
@@ -11128,7 +11128,7 @@
         <v>1.10099995136261</v>
       </c>
       <c r="G371" t="n">
-        <v>1.04634201526642</v>
+        <v>1.04634213447571</v>
       </c>
       <c r="H371" t="n">
         <v>16691</v>
@@ -11157,7 +11157,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G372" t="n">
-        <v>1.0510938167572</v>
+        <v>1.05109369754791</v>
       </c>
       <c r="H372" t="n">
         <v>1157</v>
@@ -11186,7 +11186,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G373" t="n">
-        <v>1.0510938167572</v>
+        <v>1.05109369754791</v>
       </c>
       <c r="H373" t="n">
         <v>12141</v>
@@ -11215,7 +11215,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G374" t="n">
-        <v>1.09385979175568</v>
+        <v>1.09385991096497</v>
       </c>
       <c r="H374" t="n">
         <v>270010</v>
@@ -11476,7 +11476,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G383" t="n">
-        <v>1.0834059715271</v>
+        <v>1.08340585231781</v>
       </c>
       <c r="H383" t="n">
         <v>60477</v>
@@ -11505,7 +11505,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G384" t="n">
-        <v>1.09290945529938</v>
+        <v>1.09290957450867</v>
       </c>
       <c r="H384" t="n">
         <v>8937</v>
@@ -11621,7 +11621,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G388" t="n">
-        <v>1.14042735099792</v>
+        <v>1.14042747020721</v>
       </c>
       <c r="H388" t="n">
         <v>38769</v>
@@ -11737,7 +11737,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G392" t="n">
-        <v>1.17464005947113</v>
+        <v>1.17464017868042</v>
       </c>
       <c r="H392" t="n">
         <v>75009</v>
@@ -11766,7 +11766,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G393" t="n">
-        <v>1.14042735099792</v>
+        <v>1.14042747020721</v>
       </c>
       <c r="H393" t="n">
         <v>24599</v>
@@ -11795,7 +11795,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G394" t="n">
-        <v>1.12427115440369</v>
+        <v>1.12427127361298</v>
       </c>
       <c r="H394" t="n">
         <v>33424</v>
@@ -11998,7 +11998,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>1.14042735099792</v>
+        <v>1.14042747020721</v>
       </c>
       <c r="H401" t="n">
         <v>11690</v>
@@ -12027,7 +12027,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G402" t="n">
-        <v>1.14042735099792</v>
+        <v>1.14042747020721</v>
       </c>
       <c r="H402" t="n">
         <v>13119</v>
@@ -12201,7 +12201,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G408" t="n">
-        <v>1.11761868000031</v>
+        <v>1.11761879920959</v>
       </c>
       <c r="H408" t="n">
         <v>6600</v>
@@ -12259,7 +12259,7 @@
         <v>1.15299999713898</v>
       </c>
       <c r="G410" t="n">
-        <v>1.09576058387756</v>
+        <v>1.09576070308685</v>
       </c>
       <c r="H410" t="n">
         <v>2558</v>
@@ -12665,7 +12665,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G424" t="n">
-        <v>1.16133522987366</v>
+        <v>1.16133499145508</v>
       </c>
       <c r="H424" t="n">
         <v>64353</v>
@@ -12694,7 +12694,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H425" t="n">
         <v>23167</v>
@@ -12810,7 +12810,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G429" t="n">
-        <v>1.12427115440369</v>
+        <v>1.12427127361298</v>
       </c>
       <c r="H429" t="n">
         <v>17930</v>
@@ -12955,7 +12955,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G434" t="n">
-        <v>1.12142014503479</v>
+        <v>1.12142026424408</v>
       </c>
       <c r="H434" t="n">
         <v>31340</v>
@@ -12984,7 +12984,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G435" t="n">
-        <v>1.12142014503479</v>
+        <v>1.12142026424408</v>
       </c>
       <c r="H435" t="n">
         <v>7381</v>
@@ -13042,7 +13042,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G437" t="n">
-        <v>1.12522172927856</v>
+        <v>1.12522161006927</v>
       </c>
       <c r="H437" t="n">
         <v>13177</v>
@@ -13071,7 +13071,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G438" t="n">
-        <v>1.12142014503479</v>
+        <v>1.12142026424408</v>
       </c>
       <c r="H438" t="n">
         <v>706</v>
@@ -13100,7 +13100,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>1.12522172927856</v>
+        <v>1.12522161006927</v>
       </c>
       <c r="H439" t="n">
         <v>55175</v>
@@ -13158,7 +13158,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G441" t="n">
-        <v>1.11286699771881</v>
+        <v>1.11286687850952</v>
       </c>
       <c r="H441" t="n">
         <v>9775</v>
@@ -13216,7 +13216,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G443" t="n">
-        <v>1.11761868000031</v>
+        <v>1.11761879920959</v>
       </c>
       <c r="H443" t="n">
         <v>9327</v>
@@ -13332,7 +13332,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G447" t="n">
-        <v>1.18604445457458</v>
+        <v>1.18604457378387</v>
       </c>
       <c r="H447" t="n">
         <v>202560</v>
@@ -13390,7 +13390,7 @@
         <v>1.20700001716614</v>
       </c>
       <c r="G449" t="n">
-        <v>1.14707970619202</v>
+        <v>1.14707982540131</v>
       </c>
       <c r="H449" t="n">
         <v>56285</v>
@@ -13419,7 +13419,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G450" t="n">
-        <v>1.1508811712265</v>
+        <v>1.15088129043579</v>
       </c>
       <c r="H450" t="n">
         <v>8668</v>
@@ -13448,7 +13448,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G451" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H451" t="n">
         <v>11298</v>
@@ -13477,7 +13477,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G452" t="n">
-        <v>1.22025728225708</v>
+        <v>1.22025740146637</v>
       </c>
       <c r="H452" t="n">
         <v>307038</v>
@@ -13506,7 +13506,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G453" t="n">
-        <v>1.20505154132843</v>
+        <v>1.20505166053772</v>
       </c>
       <c r="H453" t="n">
         <v>91082</v>
@@ -13564,7 +13564,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G455" t="n">
-        <v>1.16133522987366</v>
+        <v>1.16133499145508</v>
       </c>
       <c r="H455" t="n">
         <v>67397</v>
@@ -13622,7 +13622,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G457" t="n">
-        <v>1.17273950576782</v>
+        <v>1.17273938655853</v>
       </c>
       <c r="H457" t="n">
         <v>21775</v>
@@ -13680,7 +13680,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G459" t="n">
-        <v>1.17654073238373</v>
+        <v>1.17654085159302</v>
       </c>
       <c r="H459" t="n">
         <v>19287</v>
@@ -13709,7 +13709,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G460" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749106884003</v>
       </c>
       <c r="H460" t="n">
         <v>19410</v>
@@ -13738,7 +13738,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G461" t="n">
-        <v>1.17464005947113</v>
+        <v>1.17464017868042</v>
       </c>
       <c r="H461" t="n">
         <v>4453</v>
@@ -13767,7 +13767,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H462" t="n">
         <v>20101</v>
@@ -13883,7 +13883,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G466" t="n">
-        <v>1.15468275547028</v>
+        <v>1.15468263626099</v>
       </c>
       <c r="H466" t="n">
         <v>60422</v>
@@ -13912,7 +13912,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G467" t="n">
-        <v>1.15468275547028</v>
+        <v>1.15468263626099</v>
       </c>
       <c r="H467" t="n">
         <v>20882</v>
@@ -14028,7 +14028,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G471" t="n">
-        <v>1.19364738464355</v>
+        <v>1.19364726543427</v>
       </c>
       <c r="H471" t="n">
         <v>268871</v>
@@ -14057,7 +14057,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G472" t="n">
-        <v>1.18604445457458</v>
+        <v>1.18604457378387</v>
       </c>
       <c r="H472" t="n">
         <v>66425</v>
@@ -14173,7 +14173,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G476" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749106884003</v>
       </c>
       <c r="H476" t="n">
         <v>127242</v>
@@ -14202,7 +14202,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H477" t="n">
         <v>41948</v>
@@ -14289,7 +14289,7 @@
         <v>1.19200003147125</v>
       </c>
       <c r="G480" t="n">
-        <v>1.13282454013824</v>
+        <v>1.13282442092896</v>
       </c>
       <c r="H480" t="n">
         <v>68717</v>
@@ -14579,7 +14579,7 @@
         <v>1.18900001049042</v>
       </c>
       <c r="G490" t="n">
-        <v>1.12997353076935</v>
+        <v>1.12997341156006</v>
       </c>
       <c r="H490" t="n">
         <v>24742</v>
@@ -14927,7 +14927,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G502" t="n">
-        <v>1.09481012821198</v>
+        <v>1.09481024742126</v>
       </c>
       <c r="H502" t="n">
         <v>4212</v>
@@ -15014,7 +15014,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G505" t="n">
-        <v>1.12142014503479</v>
+        <v>1.12142026424408</v>
       </c>
       <c r="H505" t="n">
         <v>4635</v>
@@ -15159,7 +15159,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G510" t="n">
-        <v>1.12427115440369</v>
+        <v>1.12427127361298</v>
       </c>
       <c r="H510" t="n">
         <v>3049</v>
@@ -15188,7 +15188,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G511" t="n">
-        <v>1.13187408447266</v>
+        <v>1.13187396526337</v>
       </c>
       <c r="H511" t="n">
         <v>3108</v>
@@ -15449,7 +15449,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G520" t="n">
-        <v>1.09766125679016</v>
+        <v>1.09766113758087</v>
       </c>
       <c r="H520" t="n">
         <v>20364</v>
@@ -15710,7 +15710,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G529" t="n">
-        <v>1.09290945529938</v>
+        <v>1.09290957450867</v>
       </c>
       <c r="H529" t="n">
         <v>9700</v>
@@ -15768,7 +15768,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G531" t="n">
-        <v>1.12142014503479</v>
+        <v>1.12142026424408</v>
       </c>
       <c r="H531" t="n">
         <v>8000</v>
@@ -15797,7 +15797,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G532" t="n">
-        <v>1.09290945529938</v>
+        <v>1.09290957450867</v>
       </c>
       <c r="H532" t="n">
         <v>3262</v>
@@ -15826,7 +15826,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G533" t="n">
-        <v>1.09290945529938</v>
+        <v>1.09290957450867</v>
       </c>
       <c r="H533" t="n">
         <v>18204</v>
@@ -15855,7 +15855,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G534" t="n">
-        <v>1.09290945529938</v>
+        <v>1.09290957450867</v>
       </c>
       <c r="H534" t="n">
         <v>10012</v>
@@ -15913,7 +15913,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G536" t="n">
-        <v>1.06439876556396</v>
+        <v>1.06439888477325</v>
       </c>
       <c r="H536" t="n">
         <v>8150</v>
@@ -15942,7 +15942,7 @@
         <v>1.125</v>
       </c>
       <c r="G537" t="n">
-        <v>1.06915056705475</v>
+        <v>1.06915068626404</v>
       </c>
       <c r="H537" t="n">
         <v>21910</v>
@@ -15971,7 +15971,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G538" t="n">
-        <v>1.0834059715271</v>
+        <v>1.08340585231781</v>
       </c>
       <c r="H538" t="n">
         <v>4582</v>
@@ -16000,7 +16000,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.0834059715271</v>
+        <v>1.08340585231781</v>
       </c>
       <c r="H539" t="n">
         <v>29</v>
@@ -16029,7 +16029,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G540" t="n">
-        <v>1.07390236854553</v>
+        <v>1.07390224933624</v>
       </c>
       <c r="H540" t="n">
         <v>16999</v>
@@ -16087,7 +16087,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G542" t="n">
-        <v>1.07390236854553</v>
+        <v>1.07390224933624</v>
       </c>
       <c r="H542" t="n">
         <v>6521</v>
@@ -16116,7 +16116,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G543" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H543" t="n">
         <v>1293</v>
@@ -16174,7 +16174,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G545" t="n">
-        <v>1.07390236854553</v>
+        <v>1.07390224933624</v>
       </c>
       <c r="H545" t="n">
         <v>3680</v>
@@ -16203,7 +16203,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G546" t="n">
-        <v>1.07390236854553</v>
+        <v>1.07390224933624</v>
       </c>
       <c r="H546" t="n">
         <v>5525</v>
@@ -16232,7 +16232,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G547" t="n">
-        <v>1.07390236854553</v>
+        <v>1.07390224933624</v>
       </c>
       <c r="H547" t="n">
         <v>2500</v>
@@ -16290,7 +16290,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G549" t="n">
-        <v>1.04539179801941</v>
+        <v>1.04539167881012</v>
       </c>
       <c r="H549" t="n">
         <v>3739</v>
@@ -16406,7 +16406,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G553" t="n">
-        <v>1.04539179801941</v>
+        <v>1.04539167881012</v>
       </c>
       <c r="H553" t="n">
         <v>10964</v>
@@ -16493,7 +16493,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>1.03113639354706</v>
+        <v>1.03113651275635</v>
       </c>
       <c r="H556" t="n">
         <v>3690</v>
@@ -16522,7 +16522,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>1.05964696407318</v>
+        <v>1.05964708328247</v>
       </c>
       <c r="H557" t="n">
         <v>5187</v>
@@ -16551,7 +16551,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G558" t="n">
-        <v>1.05964696407318</v>
+        <v>1.05964708328247</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G560" t="n">
-        <v>1.04539179801941</v>
+        <v>1.04539167881012</v>
       </c>
       <c r="H560" t="n">
         <v>7000</v>
@@ -16638,7 +16638,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G561" t="n">
-        <v>1.04539179801941</v>
+        <v>1.04539167881012</v>
       </c>
       <c r="H561" t="n">
         <v>389</v>
@@ -16696,7 +16696,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G563" t="n">
-        <v>1.03588831424713</v>
+        <v>1.03588819503784</v>
       </c>
       <c r="H563" t="n">
         <v>2600</v>
@@ -16754,7 +16754,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G565" t="n">
-        <v>1.04539179801941</v>
+        <v>1.04539167881012</v>
       </c>
       <c r="H565" t="n">
         <v>3022</v>
@@ -16783,7 +16783,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G566" t="n">
-        <v>1.05964696407318</v>
+        <v>1.05964708328247</v>
       </c>
       <c r="H566" t="n">
         <v>13910</v>
@@ -16870,7 +16870,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G569" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H569" t="n">
         <v>6375</v>
@@ -16899,7 +16899,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G570" t="n">
-        <v>1.0834059715271</v>
+        <v>1.08340585231781</v>
       </c>
       <c r="H570" t="n">
         <v>4666</v>
@@ -16928,7 +16928,7 @@
         <v>1.125</v>
       </c>
       <c r="G571" t="n">
-        <v>1.06915056705475</v>
+        <v>1.06915068626404</v>
       </c>
       <c r="H571" t="n">
         <v>7222</v>
@@ -16957,7 +16957,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G572" t="n">
-        <v>1.05964696407318</v>
+        <v>1.05964708328247</v>
       </c>
       <c r="H572" t="n">
         <v>290</v>
@@ -16986,7 +16986,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G573" t="n">
-        <v>1.03113639354706</v>
+        <v>1.03113651275635</v>
       </c>
       <c r="H573" t="n">
         <v>13912</v>
@@ -17189,7 +17189,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G580" t="n">
-        <v>1.06439876556396</v>
+        <v>1.06439888477325</v>
       </c>
       <c r="H580" t="n">
         <v>16675</v>
@@ -17305,7 +17305,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G584" t="n">
-        <v>1.07390236854553</v>
+        <v>1.07390224933624</v>
       </c>
       <c r="H584" t="n">
         <v>31167</v>
@@ -17392,7 +17392,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G587" t="n">
-        <v>1.06439876556396</v>
+        <v>1.06439888477325</v>
       </c>
       <c r="H587" t="n">
         <v>13671</v>
@@ -17479,7 +17479,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>1.03113639354706</v>
+        <v>1.03113651275635</v>
       </c>
       <c r="H590" t="n">
         <v>31548</v>
@@ -17508,7 +17508,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G591" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H591" t="n">
         <v>4775</v>
@@ -17537,7 +17537,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G592" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H592" t="n">
         <v>834</v>
@@ -17566,7 +17566,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G593" t="n">
-        <v>1.04539179801941</v>
+        <v>1.04539167881012</v>
       </c>
       <c r="H593" t="n">
         <v>5693</v>
@@ -17595,7 +17595,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>1.03113639354706</v>
+        <v>1.03113651275635</v>
       </c>
       <c r="H594" t="n">
         <v>8390</v>
@@ -17624,7 +17624,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G595" t="n">
-        <v>1.02638447284698</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H595" t="n">
         <v>4500</v>
@@ -17682,7 +17682,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G597" t="n">
-        <v>1.02638447284698</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H597" t="n">
         <v>17100</v>
@@ -17740,7 +17740,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G599" t="n">
-        <v>1.03588831424713</v>
+        <v>1.03588819503784</v>
       </c>
       <c r="H599" t="n">
         <v>17301</v>
@@ -17798,7 +17798,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G601" t="n">
-        <v>1.05964696407318</v>
+        <v>1.05964708328247</v>
       </c>
       <c r="H601" t="n">
         <v>7370</v>
@@ -17856,7 +17856,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G603" t="n">
-        <v>1.05964696407318</v>
+        <v>1.05964708328247</v>
       </c>
       <c r="H603" t="n">
         <v>162004</v>
@@ -17885,7 +17885,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G604" t="n">
-        <v>1.06439876556396</v>
+        <v>1.06439888477325</v>
       </c>
       <c r="H604" t="n">
         <v>34087</v>
@@ -17914,7 +17914,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G605" t="n">
-        <v>1.02638447284698</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H605" t="n">
         <v>4449</v>
@@ -18030,7 +18030,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G609" t="n">
-        <v>1.04539179801941</v>
+        <v>1.04539167881012</v>
       </c>
       <c r="H609" t="n">
         <v>12761</v>
@@ -18059,7 +18059,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G610" t="n">
-        <v>1.01212930679321</v>
+        <v>1.0121294260025</v>
       </c>
       <c r="H610" t="n">
         <v>4398</v>
@@ -18146,7 +18146,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H613" t="n">
         <v>16207</v>
@@ -18175,7 +18175,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G614" t="n">
-        <v>0.931349039077759</v>
+        <v>0.931348979473114</v>
       </c>
       <c r="H614" t="n">
         <v>50700</v>
@@ -18233,7 +18233,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G616" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H616" t="n">
         <v>10854</v>
@@ -18262,7 +18262,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G617" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H617" t="n">
         <v>22297</v>
@@ -18320,7 +18320,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G619" t="n">
-        <v>0.974114954471588</v>
+        <v>0.974115014076233</v>
       </c>
       <c r="H619" t="n">
         <v>1495</v>
@@ -18349,7 +18349,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G620" t="n">
-        <v>0.974114954471588</v>
+        <v>0.974115014076233</v>
       </c>
       <c r="H620" t="n">
         <v>6029</v>
@@ -18407,7 +18407,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G622" t="n">
-        <v>0.948455452919006</v>
+        <v>0.948455393314362</v>
       </c>
       <c r="H622" t="n">
         <v>10698</v>
@@ -18436,7 +18436,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H623" t="n">
         <v>2010</v>
@@ -18465,7 +18465,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18581,7 +18581,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G628" t="n">
-        <v>0.946554660797119</v>
+        <v>0.946554720401764</v>
       </c>
       <c r="H628" t="n">
         <v>1972</v>
@@ -18639,7 +18639,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G630" t="n">
-        <v>0.948455452919006</v>
+        <v>0.948455393314362</v>
       </c>
       <c r="H630" t="n">
         <v>5204</v>
@@ -18668,7 +18668,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G631" t="n">
-        <v>0.944653928279877</v>
+        <v>0.944653987884521</v>
       </c>
       <c r="H631" t="n">
         <v>2000</v>
@@ -18755,7 +18755,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G634" t="n">
-        <v>0.933249652385712</v>
+        <v>0.933249711990356</v>
       </c>
       <c r="H634" t="n">
         <v>2877</v>
@@ -18784,7 +18784,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G635" t="n">
-        <v>0.933249652385712</v>
+        <v>0.933249711990356</v>
       </c>
       <c r="H635" t="n">
         <v>0</v>
@@ -18813,7 +18813,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G636" t="n">
-        <v>0.931349039077759</v>
+        <v>0.931348979473114</v>
       </c>
       <c r="H636" t="n">
         <v>16795</v>
@@ -18871,7 +18871,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G638" t="n">
-        <v>0.916143238544464</v>
+        <v>0.916143298149109</v>
       </c>
       <c r="H638" t="n">
         <v>15119</v>
@@ -18900,7 +18900,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G639" t="n">
-        <v>0.935150444507599</v>
+        <v>0.935150504112244</v>
       </c>
       <c r="H639" t="n">
         <v>12673</v>
@@ -18987,7 +18987,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G642" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H642" t="n">
         <v>957</v>
@@ -19074,7 +19074,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G645" t="n">
-        <v>0.937051177024841</v>
+        <v>0.937051117420197</v>
       </c>
       <c r="H645" t="n">
         <v>2898</v>
@@ -19132,7 +19132,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G647" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H647" t="n">
         <v>767</v>
@@ -19161,7 +19161,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G648" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -19190,7 +19190,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G649" t="n">
-        <v>0.931349039077759</v>
+        <v>0.931348979473114</v>
       </c>
       <c r="H649" t="n">
         <v>5129</v>
@@ -19306,7 +19306,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G653" t="n">
-        <v>0.931349039077759</v>
+        <v>0.931348979473114</v>
       </c>
       <c r="H653" t="n">
         <v>12344</v>
@@ -19364,7 +19364,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G655" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H655" t="n">
         <v>4810</v>
@@ -19422,7 +19422,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G657" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H657" t="n">
         <v>2580</v>
@@ -19451,7 +19451,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G658" t="n">
-        <v>0.900937557220459</v>
+        <v>0.900937616825104</v>
       </c>
       <c r="H658" t="n">
         <v>7561</v>
@@ -19480,7 +19480,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G659" t="n">
-        <v>0.893334686756134</v>
+        <v>0.893334746360779</v>
       </c>
       <c r="H659" t="n">
         <v>5198</v>
@@ -19596,7 +19596,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G663" t="n">
-        <v>0.916143238544464</v>
+        <v>0.916143298149109</v>
       </c>
       <c r="H663" t="n">
         <v>3108</v>
@@ -19625,7 +19625,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G664" t="n">
-        <v>0.916143238544464</v>
+        <v>0.916143298149109</v>
       </c>
       <c r="H664" t="n">
         <v>17813</v>
@@ -19712,7 +19712,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G667" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H667" t="n">
         <v>3010</v>
@@ -19741,7 +19741,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G668" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H668" t="n">
         <v>1315</v>
@@ -19770,7 +19770,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G669" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H669" t="n">
         <v>0</v>
@@ -19886,7 +19886,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G673" t="n">
-        <v>0.893334686756134</v>
+        <v>0.893334746360779</v>
       </c>
       <c r="H673" t="n">
         <v>2230</v>
@@ -20031,7 +20031,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G678" t="n">
-        <v>0.880029797554016</v>
+        <v>0.880029737949371</v>
       </c>
       <c r="H678" t="n">
         <v>6164</v>
@@ -20060,7 +20060,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G679" t="n">
-        <v>0.880029797554016</v>
+        <v>0.880029737949371</v>
       </c>
       <c r="H679" t="n">
         <v>0</v>
@@ -20089,7 +20089,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G680" t="n">
-        <v>0.883831143379211</v>
+        <v>0.883831202983856</v>
       </c>
       <c r="H680" t="n">
         <v>2527</v>
@@ -20118,7 +20118,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G681" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H681" t="n">
         <v>1709</v>
@@ -20147,7 +20147,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G682" t="n">
-        <v>0.866724789142609</v>
+        <v>0.866724729537964</v>
       </c>
       <c r="H682" t="n">
         <v>1730</v>
@@ -20205,7 +20205,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G684" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H684" t="n">
         <v>35108</v>
@@ -20234,7 +20234,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G685" t="n">
-        <v>0.935150444507599</v>
+        <v>0.935150504112244</v>
       </c>
       <c r="H685" t="n">
         <v>13058</v>
@@ -20263,7 +20263,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G686" t="n">
-        <v>0.942753314971924</v>
+        <v>0.942753255367279</v>
       </c>
       <c r="H686" t="n">
         <v>8065</v>
@@ -20756,7 +20756,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G703" t="n">
-        <v>0.897136211395264</v>
+        <v>0.897136151790619</v>
       </c>
       <c r="H703" t="n">
         <v>5011</v>
@@ -20843,7 +20843,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G706" t="n">
-        <v>0.864824056625366</v>
+        <v>0.864823997020721</v>
       </c>
       <c r="H706" t="n">
         <v>23727</v>
@@ -20930,7 +20930,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G709" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114831924438</v>
       </c>
       <c r="H709" t="n">
         <v>4372</v>
@@ -21104,7 +21104,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G715" t="n">
-        <v>0.821107685565948</v>
+        <v>0.821107625961304</v>
       </c>
       <c r="H715" t="n">
         <v>4186</v>
@@ -21133,7 +21133,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G716" t="n">
-        <v>0.792596995830536</v>
+        <v>0.792597055435181</v>
       </c>
       <c r="H716" t="n">
         <v>12077</v>
@@ -21162,7 +21162,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G717" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H717" t="n">
         <v>14233</v>
@@ -21220,7 +21220,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G719" t="n">
-        <v>0.802100539207458</v>
+        <v>0.802100479602814</v>
       </c>
       <c r="H719" t="n">
         <v>4618</v>
@@ -21249,7 +21249,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G720" t="n">
-        <v>0.802100539207458</v>
+        <v>0.802100479602814</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21278,7 +21278,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G721" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H721" t="n">
         <v>770</v>
@@ -21307,7 +21307,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G722" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H722" t="n">
         <v>632</v>
@@ -21336,7 +21336,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G723" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H723" t="n">
         <v>6360</v>
@@ -21365,7 +21365,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G724" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H724" t="n">
         <v>80</v>
@@ -21539,7 +21539,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G730" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H730" t="n">
         <v>3578</v>
@@ -21568,7 +21568,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G731" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H731" t="n">
         <v>6117</v>
@@ -21597,7 +21597,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G732" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H732" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G734" t="n">
-        <v>0.804001271724701</v>
+        <v>0.804001212120056</v>
       </c>
       <c r="H734" t="n">
         <v>15413</v>
@@ -21684,7 +21684,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G735" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H735" t="n">
         <v>10721</v>
@@ -21713,7 +21713,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G736" t="n">
-        <v>0.777391374111176</v>
+        <v>0.777391314506531</v>
       </c>
       <c r="H736" t="n">
         <v>1019</v>
@@ -21771,7 +21771,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G738" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H738" t="n">
         <v>1300</v>
@@ -21800,7 +21800,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G739" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H739" t="n">
         <v>879</v>
@@ -21916,7 +21916,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G743" t="n">
-        <v>0.802100539207458</v>
+        <v>0.802100479602814</v>
       </c>
       <c r="H743" t="n">
         <v>134</v>
@@ -21945,7 +21945,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G744" t="n">
-        <v>0.792596995830536</v>
+        <v>0.792597055435181</v>
       </c>
       <c r="H744" t="n">
         <v>622</v>
@@ -21974,7 +21974,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G745" t="n">
-        <v>0.792596995830536</v>
+        <v>0.792597055435181</v>
       </c>
       <c r="H745" t="n">
         <v>11</v>
@@ -22003,7 +22003,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G746" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H746" t="n">
         <v>1260</v>
@@ -22061,7 +22061,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G748" t="n">
-        <v>0.802100539207458</v>
+        <v>0.802100479602814</v>
       </c>
       <c r="H748" t="n">
         <v>3958</v>
@@ -22090,7 +22090,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G749" t="n">
-        <v>0.802100539207458</v>
+        <v>0.802100479602814</v>
       </c>
       <c r="H749" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G750" t="n">
-        <v>0.792596995830536</v>
+        <v>0.792597055435181</v>
       </c>
       <c r="H750" t="n">
         <v>1370</v>
@@ -22177,7 +22177,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G752" t="n">
-        <v>0.792596995830536</v>
+        <v>0.792597055435181</v>
       </c>
       <c r="H752" t="n">
         <v>164</v>
@@ -22206,7 +22206,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G753" t="n">
-        <v>0.792596995830536</v>
+        <v>0.792597055435181</v>
       </c>
       <c r="H753" t="n">
         <v>2035</v>
@@ -22264,7 +22264,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G755" t="n">
-        <v>0.798299074172974</v>
+        <v>0.798299133777618</v>
       </c>
       <c r="H755" t="n">
         <v>72</v>
@@ -22409,7 +22409,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G760" t="n">
-        <v>0.792596995830536</v>
+        <v>0.792597055435181</v>
       </c>
       <c r="H760" t="n">
         <v>6813</v>
@@ -22438,7 +22438,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G761" t="n">
-        <v>0.792596995830536</v>
+        <v>0.792597055435181</v>
       </c>
       <c r="H761" t="n">
         <v>0</v>
@@ -22467,7 +22467,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G762" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H762" t="n">
         <v>10920</v>
@@ -22496,7 +22496,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G763" t="n">
-        <v>0.790696382522583</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H763" t="n">
         <v>2090</v>
@@ -22525,7 +22525,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>0.790696382522583</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -22554,7 +22554,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G765" t="n">
-        <v>0.790696382522583</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H765" t="n">
         <v>1516</v>
@@ -22583,7 +22583,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G766" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H766" t="n">
         <v>1790</v>
@@ -22612,7 +22612,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G767" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H767" t="n">
         <v>2524</v>
@@ -22728,7 +22728,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G771" t="n">
-        <v>0.790696382522583</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H771" t="n">
         <v>11010</v>
@@ -22815,7 +22815,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G774" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H774" t="n">
         <v>1400</v>
@@ -22902,7 +22902,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G777" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H777" t="n">
         <v>20</v>
@@ -22989,7 +22989,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G780" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H780" t="n">
         <v>20726</v>
@@ -23047,7 +23047,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G782" t="n">
-        <v>0.893334686756134</v>
+        <v>0.893334746360779</v>
       </c>
       <c r="H782" t="n">
         <v>14782</v>
@@ -23134,7 +23134,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G785" t="n">
-        <v>0.883831143379211</v>
+        <v>0.883831202983856</v>
       </c>
       <c r="H785" t="n">
         <v>9369</v>
@@ -23221,7 +23221,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G788" t="n">
-        <v>0.880029797554016</v>
+        <v>0.880029737949371</v>
       </c>
       <c r="H788" t="n">
         <v>384</v>
@@ -23540,7 +23540,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G799" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H799" t="n">
         <v>38915</v>
@@ -23598,7 +23598,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G801" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H801" t="n">
         <v>16877</v>
@@ -23656,7 +23656,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G803" t="n">
-        <v>0.887632548809052</v>
+        <v>0.887632608413696</v>
       </c>
       <c r="H803" t="n">
         <v>44684</v>
@@ -23685,7 +23685,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G804" t="n">
-        <v>0.866724789142609</v>
+        <v>0.866724729537964</v>
       </c>
       <c r="H804" t="n">
         <v>682</v>
@@ -23888,7 +23888,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G811" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H811" t="n">
         <v>1087</v>
@@ -24004,7 +24004,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G815" t="n">
-        <v>0.864824056625366</v>
+        <v>0.864823997020721</v>
       </c>
       <c r="H815" t="n">
         <v>8465</v>
@@ -24062,7 +24062,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G817" t="n">
-        <v>0.864824056625366</v>
+        <v>0.864823997020721</v>
       </c>
       <c r="H817" t="n">
         <v>8692</v>
@@ -24236,7 +24236,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G823" t="n">
-        <v>0.847717642784119</v>
+        <v>0.847717702388763</v>
       </c>
       <c r="H823" t="n">
         <v>12285</v>
@@ -24265,7 +24265,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G824" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H824" t="n">
         <v>520</v>
@@ -24381,7 +24381,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G828" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H828" t="n">
         <v>10500</v>
@@ -24410,7 +24410,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G829" t="n">
-        <v>0.866724789142609</v>
+        <v>0.866724729537964</v>
       </c>
       <c r="H829" t="n">
         <v>22573</v>
@@ -24468,7 +24468,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G831" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H831" t="n">
         <v>22651</v>
@@ -24671,7 +24671,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G838" t="n">
-        <v>1.03588831424713</v>
+        <v>1.03588819503784</v>
       </c>
       <c r="H838" t="n">
         <v>778664</v>
@@ -24729,7 +24729,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G840" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H840" t="n">
         <v>199532</v>
@@ -24845,7 +24845,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G844" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H844" t="n">
         <v>6969</v>
@@ -24932,7 +24932,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G847" t="n">
-        <v>0.974114954471588</v>
+        <v>0.974115014076233</v>
       </c>
       <c r="H847" t="n">
         <v>18414</v>
@@ -24961,7 +24961,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G848" t="n">
-        <v>0.96461147069931</v>
+        <v>0.964611351490021</v>
       </c>
       <c r="H848" t="n">
         <v>8252</v>
@@ -25048,7 +25048,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G851" t="n">
-        <v>0.931349039077759</v>
+        <v>0.931348979473114</v>
       </c>
       <c r="H851" t="n">
         <v>9589</v>
@@ -25077,7 +25077,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G852" t="n">
-        <v>0.942753314971924</v>
+        <v>0.942753255367279</v>
       </c>
       <c r="H852" t="n">
         <v>18857</v>
@@ -25106,7 +25106,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G853" t="n">
-        <v>0.931349039077759</v>
+        <v>0.931348979473114</v>
       </c>
       <c r="H853" t="n">
         <v>8467</v>
@@ -25193,7 +25193,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G856" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H856" t="n">
         <v>23230</v>
@@ -25222,7 +25222,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G857" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H857" t="n">
         <v>20242</v>
@@ -25251,7 +25251,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G858" t="n">
-        <v>0.893334686756134</v>
+        <v>0.893334746360779</v>
       </c>
       <c r="H858" t="n">
         <v>21338</v>
@@ -25280,7 +25280,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>0.931349039077759</v>
+        <v>0.931348979473114</v>
       </c>
       <c r="H859" t="n">
         <v>27930</v>
@@ -25338,7 +25338,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G861" t="n">
-        <v>0.948455452919006</v>
+        <v>0.948455393314362</v>
       </c>
       <c r="H861" t="n">
         <v>21200</v>
@@ -25367,7 +25367,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G862" t="n">
-        <v>0.897136211395264</v>
+        <v>0.897136151790619</v>
       </c>
       <c r="H862" t="n">
         <v>35703</v>
@@ -25425,7 +25425,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G864" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H864" t="n">
         <v>58709</v>
@@ -25454,7 +25454,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G865" t="n">
-        <v>0.883831143379211</v>
+        <v>0.883831202983856</v>
       </c>
       <c r="H865" t="n">
         <v>12395</v>
@@ -25483,7 +25483,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G866" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H866" t="n">
         <v>19486</v>
@@ -25541,7 +25541,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G868" t="n">
-        <v>0.900937557220459</v>
+        <v>0.900937616825104</v>
       </c>
       <c r="H868" t="n">
         <v>17359</v>
@@ -25570,7 +25570,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G869" t="n">
-        <v>0.887632548809052</v>
+        <v>0.887632608413696</v>
       </c>
       <c r="H869" t="n">
         <v>6207</v>
@@ -25657,7 +25657,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G872" t="n">
-        <v>0.893334686756134</v>
+        <v>0.893334746360779</v>
       </c>
       <c r="H872" t="n">
         <v>30045</v>
@@ -25860,7 +25860,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G879" t="n">
-        <v>0.880029797554016</v>
+        <v>0.880029737949371</v>
       </c>
       <c r="H879" t="n">
         <v>2292</v>
@@ -25976,7 +25976,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G883" t="n">
-        <v>0.893334686756134</v>
+        <v>0.893334746360779</v>
       </c>
       <c r="H883" t="n">
         <v>20510</v>
@@ -26005,7 +26005,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G884" t="n">
-        <v>0.880029797554016</v>
+        <v>0.880029737949371</v>
       </c>
       <c r="H884" t="n">
         <v>34609</v>
@@ -26034,7 +26034,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G885" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H885" t="n">
         <v>18386</v>
@@ -26063,7 +26063,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G886" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H886" t="n">
         <v>11911</v>
@@ -26092,7 +26092,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G887" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H887" t="n">
         <v>1480</v>
@@ -26150,7 +26150,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G889" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H889" t="n">
         <v>4577</v>
@@ -26179,7 +26179,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G890" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H890" t="n">
         <v>4035</v>
@@ -26237,7 +26237,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G892" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H892" t="n">
         <v>13605</v>
@@ -26295,7 +26295,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G894" t="n">
-        <v>0.864824056625366</v>
+        <v>0.864823997020721</v>
       </c>
       <c r="H894" t="n">
         <v>10061</v>
@@ -26353,7 +26353,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G896" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H896" t="n">
         <v>2121</v>
@@ -26382,7 +26382,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G897" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H897" t="n">
         <v>5200</v>
@@ -26498,7 +26498,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G901" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H901" t="n">
         <v>6210</v>
@@ -26759,7 +26759,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G910" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114831924438</v>
       </c>
       <c r="H910" t="n">
         <v>5000</v>
@@ -26817,7 +26817,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G912" t="n">
-        <v>0.847717642784119</v>
+        <v>0.847717702388763</v>
       </c>
       <c r="H912" t="n">
         <v>3225</v>
@@ -26846,7 +26846,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G913" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H913" t="n">
         <v>29501</v>
@@ -26875,7 +26875,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G914" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H914" t="n">
         <v>4867</v>
@@ -27107,7 +27107,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G922" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H922" t="n">
         <v>2714</v>
@@ -27136,7 +27136,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G923" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114831924438</v>
       </c>
       <c r="H923" t="n">
         <v>99</v>
@@ -27165,7 +27165,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G924" t="n">
-        <v>0.887632548809052</v>
+        <v>0.887632608413696</v>
       </c>
       <c r="H924" t="n">
         <v>33700</v>
@@ -27194,7 +27194,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G925" t="n">
-        <v>0.883831143379211</v>
+        <v>0.883831202983856</v>
       </c>
       <c r="H925" t="n">
         <v>9196</v>
@@ -27368,7 +27368,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G931" t="n">
-        <v>0.937051177024841</v>
+        <v>0.937051117420197</v>
       </c>
       <c r="H931" t="n">
         <v>302501</v>
@@ -27397,7 +27397,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G932" t="n">
-        <v>0.942753314971924</v>
+        <v>0.942753255367279</v>
       </c>
       <c r="H932" t="n">
         <v>68362</v>
@@ -27426,7 +27426,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G933" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H933" t="n">
         <v>30540</v>
@@ -27455,7 +27455,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G934" t="n">
-        <v>0.955107927322388</v>
+        <v>0.955107867717743</v>
       </c>
       <c r="H934" t="n">
         <v>10054</v>
@@ -27484,7 +27484,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G935" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H935" t="n">
         <v>26262</v>
@@ -27542,7 +27542,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G937" t="n">
-        <v>0.942753314971924</v>
+        <v>0.942753255367279</v>
       </c>
       <c r="H937" t="n">
         <v>19326</v>
@@ -27571,7 +27571,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G938" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H938" t="n">
         <v>17014</v>
@@ -27629,7 +27629,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G940" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H940" t="n">
         <v>11547</v>
@@ -27658,7 +27658,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G941" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H941" t="n">
         <v>32693</v>
@@ -27716,7 +27716,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G943" t="n">
-        <v>0.900937557220459</v>
+        <v>0.900937616825104</v>
       </c>
       <c r="H943" t="n">
         <v>3624</v>
@@ -27832,7 +27832,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G947" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H947" t="n">
         <v>76067</v>
@@ -27861,7 +27861,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G948" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H948" t="n">
         <v>21307</v>
@@ -27919,7 +27919,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G950" t="n">
-        <v>0.937051177024841</v>
+        <v>0.937051117420197</v>
       </c>
       <c r="H950" t="n">
         <v>13708</v>
@@ -27977,7 +27977,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G952" t="n">
-        <v>0.942753314971924</v>
+        <v>0.942753255367279</v>
       </c>
       <c r="H952" t="n">
         <v>16989</v>
@@ -28006,7 +28006,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G953" t="n">
-        <v>0.935150444507599</v>
+        <v>0.935150504112244</v>
       </c>
       <c r="H953" t="n">
         <v>4957</v>
@@ -28093,7 +28093,7 @@
         <v>0.96399998664856</v>
       </c>
       <c r="G956" t="n">
-        <v>0.916143238544464</v>
+        <v>0.916143298149109</v>
       </c>
       <c r="H956" t="n">
         <v>11514</v>
@@ -28151,7 +28151,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G958" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H958" t="n">
         <v>15725</v>
@@ -28209,7 +28209,7 @@
         <v>0.939999997615814</v>
       </c>
       <c r="G960" t="n">
-        <v>0.893334686756134</v>
+        <v>0.893334746360779</v>
       </c>
       <c r="H960" t="n">
         <v>21548</v>
@@ -28238,7 +28238,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G961" t="n">
-        <v>0.883831143379211</v>
+        <v>0.883831202983856</v>
       </c>
       <c r="H961" t="n">
         <v>17086</v>
@@ -28267,7 +28267,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G962" t="n">
-        <v>0.897136211395264</v>
+        <v>0.897136151790619</v>
       </c>
       <c r="H962" t="n">
         <v>28584</v>
@@ -28325,7 +28325,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G964" t="n">
-        <v>0.897136211395264</v>
+        <v>0.897136151790619</v>
       </c>
       <c r="H964" t="n">
         <v>9983</v>
@@ -28354,7 +28354,7 @@
         <v>0.948000013828278</v>
       </c>
       <c r="G965" t="n">
-        <v>0.900937557220459</v>
+        <v>0.900937616825104</v>
       </c>
       <c r="H965" t="n">
         <v>50591</v>
@@ -28383,7 +28383,7 @@
         <v>0.944000005722046</v>
       </c>
       <c r="G966" t="n">
-        <v>0.897136211395264</v>
+        <v>0.897136151790619</v>
       </c>
       <c r="H966" t="n">
         <v>29220</v>
@@ -28470,7 +28470,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G969" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H969" t="n">
         <v>16831</v>
@@ -28644,7 +28644,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G975" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H975" t="n">
         <v>218368</v>
@@ -28673,7 +28673,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G976" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H976" t="n">
         <v>49086</v>
@@ -28731,7 +28731,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G978" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H978" t="n">
         <v>33171</v>
@@ -28760,7 +28760,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G979" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H979" t="n">
         <v>4965</v>
@@ -28789,7 +28789,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G980" t="n">
-        <v>0.955107927322388</v>
+        <v>0.955107867717743</v>
       </c>
       <c r="H980" t="n">
         <v>14510</v>
@@ -28818,7 +28818,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G981" t="n">
-        <v>0.993122100830078</v>
+        <v>0.993121981620789</v>
       </c>
       <c r="H981" t="n">
         <v>192780</v>
@@ -28876,7 +28876,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G983" t="n">
-        <v>0.974114954471588</v>
+        <v>0.974115014076233</v>
       </c>
       <c r="H983" t="n">
         <v>7760</v>
@@ -28934,7 +28934,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G985" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H985" t="n">
         <v>21774</v>
@@ -29021,7 +29021,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G988" t="n">
-        <v>0.974114954471588</v>
+        <v>0.974115014076233</v>
       </c>
       <c r="H988" t="n">
         <v>10066</v>
@@ -29079,7 +29079,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G990" t="n">
-        <v>0.935150444507599</v>
+        <v>0.935150504112244</v>
       </c>
       <c r="H990" t="n">
         <v>13913</v>
@@ -29108,7 +29108,7 @@
         <v>0.980000019073486</v>
       </c>
       <c r="G991" t="n">
-        <v>0.931349039077759</v>
+        <v>0.931348979473114</v>
       </c>
       <c r="H991" t="n">
         <v>9311</v>
@@ -29195,7 +29195,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G994" t="n">
-        <v>0.96461147069931</v>
+        <v>0.964611351490021</v>
       </c>
       <c r="H994" t="n">
         <v>2711</v>
@@ -29224,7 +29224,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G995" t="n">
-        <v>0.96461147069931</v>
+        <v>0.964611351490021</v>
       </c>
       <c r="H995" t="n">
         <v>16059</v>
@@ -29253,7 +29253,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G996" t="n">
-        <v>0.983618557453156</v>
+        <v>0.9836186170578</v>
       </c>
       <c r="H996" t="n">
         <v>106619</v>
@@ -29282,7 +29282,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G997" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H997" t="n">
         <v>4524</v>
@@ -29311,7 +29311,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G998" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H998" t="n">
         <v>19085</v>
@@ -29340,7 +29340,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G999" t="n">
-        <v>0.96461147069931</v>
+        <v>0.964611351490021</v>
       </c>
       <c r="H999" t="n">
         <v>93021</v>
@@ -29398,7 +29398,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.974114954471588</v>
+        <v>0.974115014076233</v>
       </c>
       <c r="H1001" t="n">
         <v>8205</v>
@@ -29427,7 +29427,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.983618557453156</v>
+        <v>0.9836186170578</v>
       </c>
       <c r="H1002" t="n">
         <v>25401</v>
@@ -29485,7 +29485,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.01212930679321</v>
+        <v>1.0121294260025</v>
       </c>
       <c r="H1004" t="n">
         <v>32111</v>
@@ -29514,7 +29514,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H1005" t="n">
         <v>59119</v>
@@ -29543,7 +29543,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.04539179801941</v>
+        <v>1.04539167881012</v>
       </c>
       <c r="H1006" t="n">
         <v>32120</v>
@@ -29601,7 +29601,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.05964696407318</v>
+        <v>1.05964708328247</v>
       </c>
       <c r="H1008" t="n">
         <v>70073</v>
@@ -29630,7 +29630,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.03588831424713</v>
+        <v>1.03588819503784</v>
       </c>
       <c r="H1009" t="n">
         <v>7010</v>
@@ -29659,7 +29659,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.04539179801941</v>
+        <v>1.04539167881012</v>
       </c>
       <c r="H1010" t="n">
         <v>13449</v>
@@ -29688,7 +29688,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.04539179801941</v>
+        <v>1.04539167881012</v>
       </c>
       <c r="H1011" t="n">
         <v>7455</v>
@@ -29717,7 +29717,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H1012" t="n">
         <v>19076</v>
@@ -29775,7 +29775,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.02638447284698</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H1014" t="n">
         <v>4819</v>
@@ -29804,7 +29804,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.03113639354706</v>
+        <v>1.03113651275635</v>
       </c>
       <c r="H1015" t="n">
         <v>10656</v>
@@ -29833,7 +29833,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.03113639354706</v>
+        <v>1.03113651275635</v>
       </c>
       <c r="H1016" t="n">
         <v>37152</v>
@@ -29862,7 +29862,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.03113639354706</v>
+        <v>1.03113651275635</v>
       </c>
       <c r="H1017" t="n">
         <v>12949</v>
@@ -29949,7 +29949,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.00262558460236</v>
+        <v>1.00262546539307</v>
       </c>
       <c r="H1020" t="n">
         <v>12764</v>
@@ -29978,7 +29978,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.01212930679321</v>
+        <v>1.0121294260025</v>
       </c>
       <c r="H1021" t="n">
         <v>113267</v>
@@ -30036,7 +30036,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.983618557453156</v>
+        <v>0.9836186170578</v>
       </c>
       <c r="H1023" t="n">
         <v>17131</v>
@@ -30123,7 +30123,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H1026" t="n">
         <v>14290</v>
@@ -30152,7 +30152,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.993122100830078</v>
+        <v>0.993121981620789</v>
       </c>
       <c r="H1027" t="n">
         <v>28649</v>
@@ -30181,7 +30181,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.993122100830078</v>
+        <v>0.993121981620789</v>
       </c>
       <c r="H1028" t="n">
         <v>20606</v>
@@ -30210,7 +30210,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H1029" t="n">
         <v>91607</v>
@@ -30239,7 +30239,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1030" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H1030" t="n">
         <v>22283</v>
@@ -30268,7 +30268,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.00262558460236</v>
+        <v>1.00262546539307</v>
       </c>
       <c r="H1031" t="n">
         <v>372072</v>
@@ -30297,7 +30297,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.993122100830078</v>
+        <v>0.993121981620789</v>
       </c>
       <c r="H1032" t="n">
         <v>93979</v>
@@ -30500,7 +30500,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.00262558460236</v>
+        <v>1.00262546539307</v>
       </c>
       <c r="H1039" t="n">
         <v>32399</v>
@@ -30529,7 +30529,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.03588831424713</v>
+        <v>1.03588819503784</v>
       </c>
       <c r="H1040" t="n">
         <v>28777</v>
@@ -30558,7 +30558,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.06439876556396</v>
+        <v>1.06439888477325</v>
       </c>
       <c r="H1041" t="n">
         <v>42988</v>
@@ -30587,7 +30587,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.04539179801941</v>
+        <v>1.04539167881012</v>
       </c>
       <c r="H1042" t="n">
         <v>11404</v>
@@ -30616,7 +30616,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.0834059715271</v>
+        <v>1.08340585231781</v>
       </c>
       <c r="H1043" t="n">
         <v>139130</v>
@@ -30674,7 +30674,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.09766125679016</v>
+        <v>1.09766113758087</v>
       </c>
       <c r="H1045" t="n">
         <v>470152</v>
@@ -30703,7 +30703,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.07390236854553</v>
+        <v>1.07390224933624</v>
       </c>
       <c r="H1046" t="n">
         <v>138069</v>
@@ -30732,7 +30732,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.07390236854553</v>
+        <v>1.07390224933624</v>
       </c>
       <c r="H1047" t="n">
         <v>23538</v>
@@ -30877,7 +30877,7 @@
         <v>1.0900000333786</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.03588831424713</v>
+        <v>1.03588819503784</v>
       </c>
       <c r="H1052" t="n">
         <v>82556</v>
@@ -30906,7 +30906,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.983618557453156</v>
+        <v>0.9836186170578</v>
       </c>
       <c r="H1053" t="n">
         <v>115588</v>
@@ -30964,7 +30964,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.974114954471588</v>
+        <v>0.974115014076233</v>
       </c>
       <c r="H1055" t="n">
         <v>11641</v>
@@ -30993,7 +30993,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866755962372</v>
       </c>
       <c r="H1056" t="n">
         <v>34580</v>
@@ -31022,7 +31022,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.937051177024841</v>
+        <v>0.937051117420197</v>
       </c>
       <c r="H1057" t="n">
         <v>35665</v>
@@ -31167,7 +31167,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H1062" t="n">
         <v>146893</v>
@@ -31196,7 +31196,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1063" t="n">
         <v>26146</v>
@@ -31283,7 +31283,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.771689176559448</v>
+        <v>0.771689116954803</v>
       </c>
       <c r="H1066" t="n">
         <v>26733</v>
@@ -31573,7 +31573,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.842015504837036</v>
+        <v>0.842015445232391</v>
       </c>
       <c r="H1076" t="n">
         <v>2628</v>
@@ -31602,7 +31602,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114831924438</v>
       </c>
       <c r="H1077" t="n">
         <v>7972</v>
@@ -31718,7 +31718,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114831924438</v>
       </c>
       <c r="H1081" t="n">
         <v>12204</v>
@@ -31747,7 +31747,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114831924438</v>
       </c>
       <c r="H1082" t="n">
         <v>1150</v>
@@ -31805,7 +31805,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H1084" t="n">
         <v>14829</v>
@@ -31863,7 +31863,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.834412693977356</v>
+        <v>0.834412634372711</v>
       </c>
       <c r="H1086" t="n">
         <v>31057</v>
@@ -31921,7 +31921,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.842015504837036</v>
+        <v>0.842015445232391</v>
       </c>
       <c r="H1088" t="n">
         <v>12131</v>
@@ -31950,7 +31950,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.834412693977356</v>
+        <v>0.834412634372711</v>
       </c>
       <c r="H1089" t="n">
         <v>14709</v>
@@ -32037,7 +32037,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1092" t="n">
         <v>52209</v>
@@ -32095,7 +32095,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.804001271724701</v>
+        <v>0.804001212120056</v>
       </c>
       <c r="H1094" t="n">
         <v>1012</v>
@@ -32124,7 +32124,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.804001271724701</v>
+        <v>0.804001212120056</v>
       </c>
       <c r="H1095" t="n">
         <v>271</v>
@@ -32356,7 +32356,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.790696382522583</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H1103" t="n">
         <v>16565</v>
@@ -32472,7 +32472,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.821107685565948</v>
+        <v>0.821107625961304</v>
       </c>
       <c r="H1107" t="n">
         <v>8572</v>
@@ -32559,7 +32559,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.809703350067139</v>
+        <v>0.809703290462494</v>
       </c>
       <c r="H1110" t="n">
         <v>73772</v>
@@ -32588,7 +32588,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H1111" t="n">
         <v>15870</v>
@@ -32617,7 +32617,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H1112" t="n">
         <v>10652</v>
@@ -32675,7 +32675,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.864824056625366</v>
+        <v>0.864823997020721</v>
       </c>
       <c r="H1114" t="n">
         <v>485</v>
@@ -32936,7 +32936,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H1123" t="n">
         <v>2596</v>
@@ -32994,7 +32994,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H1125" t="n">
         <v>1772</v>
@@ -33023,7 +33023,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.842015504837036</v>
+        <v>0.842015445232391</v>
       </c>
       <c r="H1126" t="n">
         <v>646</v>
@@ -33052,7 +33052,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.842015504837036</v>
+        <v>0.842015445232391</v>
       </c>
       <c r="H1127" t="n">
         <v>3377</v>
@@ -33255,7 +33255,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114831924438</v>
       </c>
       <c r="H1134" t="n">
         <v>13934</v>
@@ -33284,7 +33284,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.840114772319794</v>
+        <v>0.840114831924438</v>
       </c>
       <c r="H1135" t="n">
         <v>2707</v>
@@ -33487,7 +33487,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1142" t="n">
-        <v>0.834412693977356</v>
+        <v>0.834412634372711</v>
       </c>
       <c r="H1142" t="n">
         <v>2048</v>
@@ -33951,7 +33951,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.821107685565948</v>
+        <v>0.821107625961304</v>
       </c>
       <c r="H1158" t="n">
         <v>17399</v>
@@ -33980,7 +33980,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1159" t="n">
         <v>57439</v>
@@ -34067,7 +34067,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.804001271724701</v>
+        <v>0.804001212120056</v>
       </c>
       <c r="H1162" t="n">
         <v>25013</v>
@@ -34125,7 +34125,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1164" t="n">
         <v>154</v>
@@ -34154,7 +34154,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.798299074172974</v>
+        <v>0.798299133777618</v>
       </c>
       <c r="H1165" t="n">
         <v>20</v>
@@ -34212,7 +34212,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1167" t="n">
         <v>5059</v>
@@ -34241,7 +34241,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H1168" t="n">
         <v>2588</v>
@@ -34270,7 +34270,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1169" t="n">
         <v>1446</v>
@@ -34299,7 +34299,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.790696382522583</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H1170" t="n">
         <v>3253</v>
@@ -34589,7 +34589,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1180" t="n">
         <v>10010</v>
@@ -34647,7 +34647,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.804001271724701</v>
+        <v>0.804001212120056</v>
       </c>
       <c r="H1182" t="n">
         <v>10</v>
@@ -34676,7 +34676,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.775490581989288</v>
+        <v>0.775490641593933</v>
       </c>
       <c r="H1183" t="n">
         <v>3161</v>
@@ -34850,7 +34850,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1189" t="n">
         <v>1063</v>
@@ -34879,7 +34879,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1190" t="n">
         <v>4195</v>
@@ -34908,7 +34908,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1191" t="n">
         <v>10276</v>
@@ -34937,7 +34937,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.777391374111176</v>
+        <v>0.777391314506531</v>
       </c>
       <c r="H1192" t="n">
         <v>11693</v>
@@ -34966,7 +34966,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.777391374111176</v>
+        <v>0.777391314506531</v>
       </c>
       <c r="H1193" t="n">
         <v>0</v>
@@ -34995,7 +34995,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1194" t="n">
         <v>6350</v>
@@ -35024,7 +35024,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1195" t="n">
         <v>2689</v>
@@ -35111,7 +35111,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.802100539207458</v>
+        <v>0.802100479602814</v>
       </c>
       <c r="H1198" t="n">
         <v>6267</v>
@@ -35169,7 +35169,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1200" t="n">
         <v>4016</v>
@@ -35198,7 +35198,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.792596995830536</v>
+        <v>0.792597055435181</v>
       </c>
       <c r="H1201" t="n">
         <v>3357</v>
@@ -35314,7 +35314,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.792596995830536</v>
+        <v>0.792597055435181</v>
       </c>
       <c r="H1205" t="n">
         <v>6916</v>
@@ -35343,7 +35343,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.809703350067139</v>
+        <v>0.809703290462494</v>
       </c>
       <c r="H1206" t="n">
         <v>1092</v>
@@ -35372,7 +35372,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.790696382522583</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H1207" t="n">
         <v>11405</v>
@@ -35401,7 +35401,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1208" t="n">
         <v>1034</v>
@@ -35430,7 +35430,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1209" t="n">
         <v>0</v>
@@ -35459,7 +35459,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.798299074172974</v>
+        <v>0.798299133777618</v>
       </c>
       <c r="H1210" t="n">
         <v>252</v>
@@ -35546,7 +35546,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.777391374111176</v>
+        <v>0.777391314506531</v>
       </c>
       <c r="H1213" t="n">
         <v>19225</v>
@@ -35633,7 +35633,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.771689176559448</v>
+        <v>0.771689116954803</v>
       </c>
       <c r="H1216" t="n">
         <v>7137</v>
@@ -35749,7 +35749,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752682089805603</v>
       </c>
       <c r="H1220" t="n">
         <v>18729</v>
@@ -35778,7 +35778,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752682089805603</v>
       </c>
       <c r="H1221" t="n">
         <v>5763</v>
@@ -35836,7 +35836,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1223" t="n">
         <v>29179</v>
@@ -35865,7 +35865,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1224" t="n">
-        <v>0.716568529605865</v>
+        <v>0.716568470001221</v>
       </c>
       <c r="H1224" t="n">
         <v>20445</v>
@@ -35923,7 +35923,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.665249228477478</v>
+        <v>0.665249288082123</v>
       </c>
       <c r="H1226" t="n">
         <v>2220</v>
@@ -35952,7 +35952,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.693759977817535</v>
+        <v>0.693759918212891</v>
       </c>
       <c r="H1227" t="n">
         <v>10514</v>
@@ -35981,7 +35981,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1228" t="n">
         <v>3123</v>
@@ -36010,7 +36010,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.689958512783051</v>
+        <v>0.689958572387695</v>
       </c>
       <c r="H1229" t="n">
         <v>1200</v>
@@ -36039,7 +36039,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1230" t="n">
         <v>2138</v>
@@ -36068,7 +36068,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1231" t="n">
         <v>5454</v>
@@ -36155,7 +36155,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.7051642537117</v>
+        <v>0.705164194107056</v>
       </c>
       <c r="H1234" t="n">
         <v>4544</v>
@@ -36213,7 +36213,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1236" t="n">
         <v>4134</v>
@@ -36242,7 +36242,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1237" t="n">
         <v>16304</v>
@@ -36271,7 +36271,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.777391374111176</v>
+        <v>0.777391314506531</v>
       </c>
       <c r="H1238" t="n">
         <v>13935</v>
@@ -36561,7 +36561,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1248" t="n">
         <v>12890</v>
@@ -36706,7 +36706,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1253" t="n">
         <v>1000</v>
@@ -36764,7 +36764,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1255" t="n">
         <v>8859</v>
@@ -36793,7 +36793,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1256" t="n">
         <v>2562</v>
@@ -36822,7 +36822,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.775490581989288</v>
+        <v>0.775490641593933</v>
       </c>
       <c r="H1257" t="n">
         <v>15595</v>
@@ -36967,7 +36967,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.771689176559448</v>
+        <v>0.771689116954803</v>
       </c>
       <c r="H1262" t="n">
         <v>2127</v>
@@ -37170,7 +37170,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.745079219341278</v>
+        <v>0.745079159736633</v>
       </c>
       <c r="H1269" t="n">
         <v>14270</v>
@@ -37228,7 +37228,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1271" t="n">
         <v>11039</v>
@@ -37257,7 +37257,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1272" t="n">
         <v>360</v>
@@ -37344,7 +37344,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1275" t="n">
         <v>27068</v>
@@ -37402,7 +37402,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1277" t="n">
         <v>7772</v>
@@ -37460,7 +37460,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1279" t="n">
         <v>6732</v>
@@ -37489,7 +37489,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1280" t="n">
         <v>48413</v>
@@ -37518,7 +37518,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1281" t="n">
         <v>0</v>
@@ -37547,7 +37547,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1282" t="n">
         <v>0</v>
@@ -37576,7 +37576,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.733675003051758</v>
+        <v>0.733674943447113</v>
       </c>
       <c r="H1283" t="n">
         <v>1224</v>
@@ -37605,7 +37605,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1284" t="n">
         <v>513</v>
@@ -37663,7 +37663,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1286" t="n">
-        <v>0.733675003051758</v>
+        <v>0.733674943447113</v>
       </c>
       <c r="H1286" t="n">
         <v>7484</v>
@@ -37692,7 +37692,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1287" t="n">
         <v>1796</v>
@@ -37721,7 +37721,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.733675003051758</v>
+        <v>0.733674943447113</v>
       </c>
       <c r="H1288" t="n">
         <v>18076</v>
@@ -37837,7 +37837,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.720369935035706</v>
+        <v>0.72036999464035</v>
       </c>
       <c r="H1292" t="n">
         <v>33828</v>
@@ -37895,7 +37895,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.745079219341278</v>
+        <v>0.745079159736633</v>
       </c>
       <c r="H1294" t="n">
         <v>30046</v>
@@ -37924,7 +37924,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1295" t="n">
         <v>52781</v>
@@ -38040,7 +38040,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.809703350067139</v>
+        <v>0.809703290462494</v>
       </c>
       <c r="H1299" t="n">
         <v>73720</v>
@@ -38069,7 +38069,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.809703350067139</v>
+        <v>0.809703290462494</v>
       </c>
       <c r="H1300" t="n">
         <v>22782</v>
@@ -38214,7 +38214,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1305" t="n">
         <v>13544</v>
@@ -38243,7 +38243,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.809703350067139</v>
+        <v>0.809703290462494</v>
       </c>
       <c r="H1306" t="n">
         <v>15675</v>
@@ -38301,7 +38301,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1308" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1308" t="n">
         <v>10678</v>
@@ -38330,7 +38330,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.790696382522583</v>
+        <v>0.790696322917938</v>
       </c>
       <c r="H1309" t="n">
         <v>16227</v>
@@ -38388,7 +38388,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H1311" t="n">
         <v>3023</v>
@@ -38417,7 +38417,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1312" t="n">
         <v>5581</v>
@@ -38475,7 +38475,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1314" t="n">
         <v>990</v>
@@ -38504,7 +38504,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1315" t="n">
         <v>0</v>
@@ -38533,7 +38533,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1316" t="n">
         <v>90943</v>
@@ -38620,7 +38620,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1319" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752682089805603</v>
       </c>
       <c r="H1319" t="n">
         <v>44851</v>
@@ -38707,7 +38707,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.745079219341278</v>
+        <v>0.745079159736633</v>
       </c>
       <c r="H1322" t="n">
         <v>6424</v>
@@ -38736,7 +38736,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.745079219341278</v>
+        <v>0.745079159736633</v>
       </c>
       <c r="H1323" t="n">
         <v>7011</v>
@@ -38794,7 +38794,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1325" t="n">
         <v>21172</v>
@@ -38823,7 +38823,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.745079219341278</v>
+        <v>0.745079159736633</v>
       </c>
       <c r="H1326" t="n">
         <v>4013</v>
@@ -38852,7 +38852,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1327" t="n">
         <v>2313</v>
@@ -38881,7 +38881,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1328" t="n">
         <v>52080</v>
@@ -38939,7 +38939,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1330" t="n">
         <v>9538</v>
@@ -38997,7 +38997,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.777391374111176</v>
+        <v>0.777391314506531</v>
       </c>
       <c r="H1332" t="n">
         <v>36760</v>
@@ -39026,7 +39026,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.777391374111176</v>
+        <v>0.777391314506531</v>
       </c>
       <c r="H1333" t="n">
         <v>3523</v>
@@ -39055,7 +39055,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1334" t="n">
         <v>5578</v>
@@ -39142,7 +39142,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.775490581989288</v>
+        <v>0.775490641593933</v>
       </c>
       <c r="H1337" t="n">
         <v>36262</v>
@@ -39229,7 +39229,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1340" t="n">
         <v>16027</v>
@@ -39403,7 +39403,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1346" t="n">
         <v>6014</v>
@@ -39432,7 +39432,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1347" t="n">
-        <v>0.737476348876953</v>
+        <v>0.737476408481598</v>
       </c>
       <c r="H1347" t="n">
         <v>5814</v>
@@ -39461,7 +39461,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1348" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1348" t="n">
         <v>169972</v>
@@ -39519,7 +39519,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1350" t="n">
         <v>30168</v>
@@ -39548,7 +39548,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1351" t="n">
         <v>38622</v>
@@ -39635,7 +39635,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752682089805603</v>
       </c>
       <c r="H1354" t="n">
         <v>45133</v>
@@ -39693,7 +39693,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1356" t="n">
         <v>34806</v>
@@ -39809,7 +39809,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.737476348876953</v>
+        <v>0.737476408481598</v>
       </c>
       <c r="H1360" t="n">
         <v>8724</v>
@@ -39838,7 +39838,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1361" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1361" t="n">
         <v>7927</v>
@@ -39867,7 +39867,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1362" t="n">
         <v>12523</v>
@@ -39896,7 +39896,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1363" t="n">
         <v>10616</v>
@@ -39954,7 +39954,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1365" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1365" t="n">
         <v>15186</v>
@@ -39983,7 +39983,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1366" t="n">
         <v>7755</v>
@@ -40012,7 +40012,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1367" t="n">
         <v>22120</v>
@@ -40041,7 +40041,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.737476348876953</v>
+        <v>0.737476408481598</v>
       </c>
       <c r="H1368" t="n">
         <v>1053</v>
@@ -40070,7 +40070,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1369" t="n">
         <v>13174</v>
@@ -40157,7 +40157,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1372" t="n">
-        <v>0.737476348876953</v>
+        <v>0.737476408481598</v>
       </c>
       <c r="H1372" t="n">
         <v>19032</v>
@@ -40186,7 +40186,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1373" t="n">
         <v>84131</v>
@@ -40215,7 +40215,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.745079219341278</v>
+        <v>0.745079159736633</v>
       </c>
       <c r="H1374" t="n">
         <v>9611</v>
@@ -40273,7 +40273,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1376" t="n">
         <v>151700</v>
@@ -40331,7 +40331,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.809703350067139</v>
+        <v>0.809703290462494</v>
       </c>
       <c r="H1378" t="n">
         <v>69721</v>
@@ -40389,7 +40389,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1380" t="n">
         <v>85030</v>
@@ -40418,7 +40418,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1381" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1381" t="n">
         <v>85408</v>
@@ -40505,7 +40505,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H1384" t="n">
         <v>665882</v>
@@ -40534,7 +40534,7 @@
         <v>0.878000020980835</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.834412693977356</v>
+        <v>0.834412634372711</v>
       </c>
       <c r="H1385" t="n">
         <v>193295</v>
@@ -40592,7 +40592,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.842015504837036</v>
+        <v>0.842015445232391</v>
       </c>
       <c r="H1387" t="n">
         <v>396763</v>
@@ -40708,7 +40708,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.798299074172974</v>
+        <v>0.798299133777618</v>
       </c>
       <c r="H1391" t="n">
         <v>25564</v>
@@ -40795,7 +40795,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.798299074172974</v>
+        <v>0.798299133777618</v>
       </c>
       <c r="H1394" t="n">
         <v>26614</v>
@@ -40911,7 +40911,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1398" t="n">
-        <v>0.792596995830536</v>
+        <v>0.792597055435181</v>
       </c>
       <c r="H1398" t="n">
         <v>7277</v>
@@ -40969,7 +40969,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1400" t="n">
         <v>63141</v>
@@ -40998,7 +40998,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1401" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1401" t="n">
         <v>55616</v>
@@ -41056,7 +41056,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H1403" t="n">
         <v>21218</v>
@@ -41114,7 +41114,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1405" t="n">
-        <v>0.777391374111176</v>
+        <v>0.777391314506531</v>
       </c>
       <c r="H1405" t="n">
         <v>14851</v>
@@ -41143,7 +41143,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1406" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1406" t="n">
         <v>7404</v>
@@ -41201,7 +41201,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1408" t="n">
         <v>21428</v>
@@ -41259,7 +41259,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1410" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1410" t="n">
         <v>45925</v>
@@ -41346,7 +41346,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1413" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752682089805603</v>
       </c>
       <c r="H1413" t="n">
         <v>861</v>
@@ -41404,7 +41404,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1415" t="n">
         <v>5994</v>
@@ -41433,7 +41433,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.771689176559448</v>
+        <v>0.771689116954803</v>
       </c>
       <c r="H1416" t="n">
         <v>37771</v>
@@ -41462,7 +41462,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752682089805603</v>
       </c>
       <c r="H1417" t="n">
         <v>6109</v>
@@ -41520,7 +41520,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1419" t="n">
         <v>3816</v>
@@ -41578,7 +41578,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1421" t="n">
         <v>20129</v>
@@ -41810,7 +41810,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.745079219341278</v>
+        <v>0.745079159736633</v>
       </c>
       <c r="H1429" t="n">
         <v>777</v>
@@ -41839,7 +41839,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.745079219341278</v>
+        <v>0.745079159736633</v>
       </c>
       <c r="H1430" t="n">
         <v>0</v>
@@ -41897,7 +41897,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1432" t="n">
         <v>4312</v>
@@ -41955,7 +41955,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1434" t="n">
-        <v>0.741277694702148</v>
+        <v>0.741277754306793</v>
       </c>
       <c r="H1434" t="n">
         <v>62963</v>
@@ -42129,7 +42129,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1440" t="n">
         <v>11075</v>
@@ -42274,7 +42274,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.775490581989288</v>
+        <v>0.775490641593933</v>
       </c>
       <c r="H1445" t="n">
         <v>16945</v>
@@ -42390,7 +42390,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1449" t="n">
         <v>6766</v>
@@ -42680,7 +42680,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.762185633182526</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1459" t="n">
         <v>1349</v>
@@ -42738,7 +42738,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1461" t="n">
         <v>1500</v>
@@ -42767,7 +42767,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.737476348876953</v>
+        <v>0.737476408481598</v>
       </c>
       <c r="H1462" t="n">
         <v>106579</v>
@@ -42941,7 +42941,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.729873478412628</v>
+        <v>0.729873538017273</v>
       </c>
       <c r="H1468" t="n">
         <v>9182</v>
@@ -42970,7 +42970,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.737476348876953</v>
+        <v>0.737476408481598</v>
       </c>
       <c r="H1469" t="n">
         <v>19553</v>
@@ -43057,7 +43057,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1472" t="n">
-        <v>0.737476348876953</v>
+        <v>0.737476408481598</v>
       </c>
       <c r="H1472" t="n">
         <v>15367</v>
@@ -43086,7 +43086,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1473" t="n">
         <v>35727</v>
@@ -43115,7 +43115,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1474" t="n">
         <v>0</v>
@@ -43144,7 +43144,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1475" t="n">
         <v>1100</v>
@@ -43173,7 +43173,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1476" t="n">
         <v>1113</v>
@@ -43202,7 +43202,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1477" t="n">
         <v>11896</v>
@@ -43231,7 +43231,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.733675003051758</v>
+        <v>0.733674943447113</v>
       </c>
       <c r="H1478" t="n">
         <v>10920</v>
@@ -43289,7 +43289,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1480" t="n">
-        <v>0.729873478412628</v>
+        <v>0.729873538017273</v>
       </c>
       <c r="H1480" t="n">
         <v>49723</v>
@@ -43376,7 +43376,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1483" t="n">
-        <v>0.729873478412628</v>
+        <v>0.729873538017273</v>
       </c>
       <c r="H1483" t="n">
         <v>19545</v>
@@ -43405,7 +43405,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.729873478412628</v>
+        <v>0.729873538017273</v>
       </c>
       <c r="H1484" t="n">
         <v>0</v>
@@ -43463,7 +43463,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1486" t="n">
-        <v>0.716568529605865</v>
+        <v>0.716568470001221</v>
       </c>
       <c r="H1486" t="n">
         <v>3368</v>
@@ -43492,7 +43492,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.716568529605865</v>
+        <v>0.716568470001221</v>
       </c>
       <c r="H1487" t="n">
         <v>6907</v>
@@ -43550,7 +43550,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.733675003051758</v>
+        <v>0.733674943447113</v>
       </c>
       <c r="H1489" t="n">
         <v>2166</v>
@@ -43579,7 +43579,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1490" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1490" t="n">
         <v>4543</v>
@@ -43724,7 +43724,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.729873478412628</v>
+        <v>0.729873538017273</v>
       </c>
       <c r="H1495" t="n">
         <v>11534</v>
@@ -43811,7 +43811,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.720369935035706</v>
+        <v>0.72036999464035</v>
       </c>
       <c r="H1498" t="n">
         <v>96906</v>
@@ -43869,7 +43869,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.708965599536896</v>
+        <v>0.708965659141541</v>
       </c>
       <c r="H1500" t="n">
         <v>36772</v>
@@ -43985,7 +43985,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1504" t="n">
-        <v>0.714667797088623</v>
+        <v>0.714667737483978</v>
       </c>
       <c r="H1504" t="n">
         <v>11995</v>
@@ -44014,7 +44014,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.7051642537117</v>
+        <v>0.705164194107056</v>
       </c>
       <c r="H1505" t="n">
         <v>10102</v>
@@ -44130,7 +44130,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.7051642537117</v>
+        <v>0.705164194107056</v>
       </c>
       <c r="H1509" t="n">
         <v>1101</v>
@@ -44159,7 +44159,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1510" t="n">
-        <v>0.689958512783051</v>
+        <v>0.689958572387695</v>
       </c>
       <c r="H1510" t="n">
         <v>1716</v>
@@ -44188,7 +44188,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.7051642537117</v>
+        <v>0.705164194107056</v>
       </c>
       <c r="H1511" t="n">
         <v>12243</v>
@@ -44217,7 +44217,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.7051642537117</v>
+        <v>0.705164194107056</v>
       </c>
       <c r="H1512" t="n">
         <v>1400</v>
@@ -44246,7 +44246,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.714667797088623</v>
+        <v>0.714667737483978</v>
       </c>
       <c r="H1513" t="n">
         <v>4895</v>
@@ -44333,7 +44333,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.708965599536896</v>
+        <v>0.708965659141541</v>
       </c>
       <c r="H1516" t="n">
         <v>28188</v>
@@ -44420,7 +44420,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.708965599536896</v>
+        <v>0.708965659141541</v>
       </c>
       <c r="H1519" t="n">
         <v>3267</v>
@@ -44449,7 +44449,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.708965599536896</v>
+        <v>0.708965659141541</v>
       </c>
       <c r="H1520" t="n">
         <v>0</v>
@@ -44536,7 +44536,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1523" t="n">
-        <v>0.688057839870453</v>
+        <v>0.688057780265808</v>
       </c>
       <c r="H1523" t="n">
         <v>48</v>
@@ -44565,7 +44565,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.7051642537117</v>
+        <v>0.705164194107056</v>
       </c>
       <c r="H1524" t="n">
         <v>11569</v>
@@ -44594,7 +44594,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.699462115764618</v>
+        <v>0.699462056159973</v>
       </c>
       <c r="H1525" t="n">
         <v>7354</v>
@@ -44623,7 +44623,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1526" t="n">
-        <v>0.7051642537117</v>
+        <v>0.705164194107056</v>
       </c>
       <c r="H1526" t="n">
         <v>12617</v>
@@ -44681,7 +44681,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1528" t="n">
-        <v>0.7051642537117</v>
+        <v>0.705164194107056</v>
       </c>
       <c r="H1528" t="n">
         <v>13687</v>
@@ -44710,7 +44710,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.693759977817535</v>
+        <v>0.693759918212891</v>
       </c>
       <c r="H1529" t="n">
         <v>31255</v>
@@ -44739,7 +44739,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1530" t="n">
-        <v>0.688057839870453</v>
+        <v>0.688057780265808</v>
       </c>
       <c r="H1530" t="n">
         <v>17959</v>
@@ -44768,7 +44768,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.688057839870453</v>
+        <v>0.688057780265808</v>
       </c>
       <c r="H1531" t="n">
         <v>9620</v>
@@ -44797,7 +44797,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.693759977817535</v>
+        <v>0.693759918212891</v>
       </c>
       <c r="H1532" t="n">
         <v>2091</v>
@@ -44884,7 +44884,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1535" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1535" t="n">
         <v>3000</v>
@@ -44913,7 +44913,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1536" t="n">
         <v>2001</v>
@@ -44942,7 +44942,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1537" t="n">
         <v>1094</v>
@@ -44971,7 +44971,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.693759977817535</v>
+        <v>0.693759918212891</v>
       </c>
       <c r="H1538" t="n">
         <v>1647</v>
@@ -45000,7 +45000,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.693759977817535</v>
+        <v>0.693759918212891</v>
       </c>
       <c r="H1539" t="n">
         <v>0</v>
@@ -45029,7 +45029,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.693759977817535</v>
+        <v>0.693759918212891</v>
       </c>
       <c r="H1540" t="n">
         <v>18889</v>
@@ -45058,7 +45058,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1541" t="n">
-        <v>0.688057839870453</v>
+        <v>0.688057780265808</v>
       </c>
       <c r="H1541" t="n">
         <v>5040</v>
@@ -45145,7 +45145,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.699462115764618</v>
+        <v>0.699462056159973</v>
       </c>
       <c r="H1544" t="n">
         <v>4722</v>
@@ -45174,7 +45174,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.689958512783051</v>
+        <v>0.689958572387695</v>
       </c>
       <c r="H1545" t="n">
         <v>4900</v>
@@ -45261,7 +45261,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1548" t="n">
         <v>116</v>
@@ -45319,7 +45319,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.689958512783051</v>
+        <v>0.689958572387695</v>
       </c>
       <c r="H1550" t="n">
         <v>10800</v>
@@ -45377,7 +45377,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1552" t="n">
-        <v>0.688057839870453</v>
+        <v>0.688057780265808</v>
       </c>
       <c r="H1552" t="n">
         <v>16300</v>
@@ -45522,7 +45522,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.665249228477478</v>
+        <v>0.665249288082123</v>
       </c>
       <c r="H1557" t="n">
         <v>20167</v>
@@ -45580,7 +45580,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1559" t="n">
-        <v>0.729873478412628</v>
+        <v>0.729873538017273</v>
       </c>
       <c r="H1559" t="n">
         <v>105451</v>
@@ -45638,7 +45638,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.708965599536896</v>
+        <v>0.708965659141541</v>
       </c>
       <c r="H1561" t="n">
         <v>42743</v>
@@ -45754,7 +45754,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.665249228477478</v>
+        <v>0.665249288082123</v>
       </c>
       <c r="H1565" t="n">
         <v>39792</v>
@@ -45783,7 +45783,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.693759977817535</v>
+        <v>0.693759918212891</v>
       </c>
       <c r="H1566" t="n">
         <v>7267</v>
@@ -45986,7 +45986,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.62153285741806</v>
+        <v>0.621532917022705</v>
       </c>
       <c r="H1573" t="n">
         <v>17448</v>
@@ -46015,7 +46015,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.62153285741806</v>
+        <v>0.621532917022705</v>
       </c>
       <c r="H1574" t="n">
         <v>7498</v>
@@ -46363,7 +46363,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1586" t="n">
-        <v>0.64434140920639</v>
+        <v>0.644341349601746</v>
       </c>
       <c r="H1586" t="n">
         <v>18130</v>
@@ -46421,7 +46421,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1588" t="n">
-        <v>0.646242082118988</v>
+        <v>0.646242141723633</v>
       </c>
       <c r="H1588" t="n">
         <v>9357</v>
@@ -46450,7 +46450,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1589" t="n">
-        <v>0.646242082118988</v>
+        <v>0.646242141723633</v>
       </c>
       <c r="H1589" t="n">
         <v>4463</v>
@@ -46508,7 +46508,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1591" t="n">
-        <v>0.64814281463623</v>
+        <v>0.648142874240875</v>
       </c>
       <c r="H1591" t="n">
         <v>1075</v>
@@ -46537,7 +46537,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1592" t="n">
-        <v>0.64814281463623</v>
+        <v>0.648142874240875</v>
       </c>
       <c r="H1592" t="n">
         <v>5713</v>
@@ -46566,7 +46566,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.64434140920639</v>
+        <v>0.644341349601746</v>
       </c>
       <c r="H1593" t="n">
         <v>10012</v>
@@ -46595,7 +46595,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.629135727882385</v>
+        <v>0.62913566827774</v>
       </c>
       <c r="H1594" t="n">
         <v>3425</v>
@@ -46624,7 +46624,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1595" t="n">
-        <v>0.638639271259308</v>
+        <v>0.638639211654663</v>
       </c>
       <c r="H1595" t="n">
         <v>22062</v>
@@ -46653,7 +46653,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.634837806224823</v>
+        <v>0.634837865829468</v>
       </c>
       <c r="H1596" t="n">
         <v>4647</v>
@@ -46682,7 +46682,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.634837806224823</v>
+        <v>0.634837865829468</v>
       </c>
       <c r="H1597" t="n">
         <v>1316</v>
@@ -46798,7 +46798,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1601" t="n">
-        <v>0.632937073707581</v>
+        <v>0.632937133312225</v>
       </c>
       <c r="H1601" t="n">
         <v>3116</v>
@@ -46827,7 +46827,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1602" t="n">
-        <v>0.632937073707581</v>
+        <v>0.632937133312225</v>
       </c>
       <c r="H1602" t="n">
         <v>16383</v>
@@ -46885,7 +46885,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.634837806224823</v>
+        <v>0.634837865829468</v>
       </c>
       <c r="H1604" t="n">
         <v>1929</v>
@@ -46943,7 +46943,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1606" t="n">
         <v>18179</v>
@@ -47001,7 +47001,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.631036460399628</v>
+        <v>0.631036400794983</v>
       </c>
       <c r="H1608" t="n">
         <v>11497</v>
@@ -47030,7 +47030,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.629135727882385</v>
+        <v>0.62913566827774</v>
       </c>
       <c r="H1609" t="n">
         <v>900</v>
@@ -47117,7 +47117,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1612" t="n">
-        <v>0.629135727882385</v>
+        <v>0.62913566827774</v>
       </c>
       <c r="H1612" t="n">
         <v>1430</v>
@@ -47146,7 +47146,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.629135727882385</v>
+        <v>0.62913566827774</v>
       </c>
       <c r="H1613" t="n">
         <v>0</v>
@@ -47175,7 +47175,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1614" t="n">
         <v>5966</v>
@@ -47204,7 +47204,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.612029373645782</v>
+        <v>0.612029314041138</v>
       </c>
       <c r="H1615" t="n">
         <v>2932</v>
@@ -47349,7 +47349,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1620" t="n">
         <v>27183</v>
@@ -47378,7 +47378,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1621" t="n">
         <v>7627</v>
@@ -47610,7 +47610,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1629" t="n">
         <v>42986</v>
@@ -47697,7 +47697,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1632" t="n">
-        <v>0.629135727882385</v>
+        <v>0.62913566827774</v>
       </c>
       <c r="H1632" t="n">
         <v>1580</v>
@@ -47755,7 +47755,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.61012864112854</v>
+        <v>0.610128700733185</v>
       </c>
       <c r="H1634" t="n">
         <v>4677</v>
@@ -47784,7 +47784,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1635" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1635" t="n">
         <v>9129</v>
@@ -47813,7 +47813,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1636" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1636" t="n">
         <v>4863</v>
@@ -47842,7 +47842,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1637" t="n">
         <v>0</v>
@@ -47929,7 +47929,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1640" t="n">
         <v>23258</v>
@@ -47958,7 +47958,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1641" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1641" t="n">
         <v>0</v>
@@ -47987,7 +47987,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1642" t="n">
         <v>0</v>
@@ -48016,7 +48016,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1643" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252583026886</v>
       </c>
       <c r="H1643" t="n">
         <v>500</v>
@@ -48045,7 +48045,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1644" t="n">
         <v>2848</v>
@@ -48132,7 +48132,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1647" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1647" t="n">
         <v>18796</v>
@@ -48161,7 +48161,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1648" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1648" t="n">
         <v>4996</v>
@@ -48277,7 +48277,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1652" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1652" t="n">
         <v>500</v>
@@ -48306,7 +48306,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1653" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1653" t="n">
         <v>0</v>
@@ -48335,7 +48335,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1654" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1654" t="n">
         <v>1001</v>
@@ -48364,7 +48364,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.543603658676147</v>
+        <v>0.543603718280792</v>
       </c>
       <c r="H1655" t="n">
         <v>74811</v>
@@ -48422,7 +48422,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.497986555099487</v>
+        <v>0.497986614704132</v>
       </c>
       <c r="H1657" t="n">
         <v>15248</v>
@@ -48451,7 +48451,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G1658" t="n">
-        <v>0.490383714437485</v>
+        <v>0.490383684635162</v>
       </c>
       <c r="H1658" t="n">
         <v>27018</v>
@@ -48509,7 +48509,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.524596512317657</v>
+        <v>0.524596571922302</v>
       </c>
       <c r="H1660" t="n">
         <v>17827</v>
@@ -48538,7 +48538,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1661" t="n">
-        <v>0.54170298576355</v>
+        <v>0.541702926158905</v>
       </c>
       <c r="H1661" t="n">
         <v>8896</v>
@@ -48741,7 +48741,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1668" t="n">
         <v>39945</v>
@@ -48770,7 +48770,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.61012864112854</v>
+        <v>0.610128700733185</v>
       </c>
       <c r="H1669" t="n">
         <v>3016</v>
@@ -48828,7 +48828,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.604426443576813</v>
+        <v>0.604426503181458</v>
       </c>
       <c r="H1671" t="n">
         <v>3877</v>
@@ -48857,7 +48857,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1672" t="n">
         <v>10972</v>
@@ -48915,7 +48915,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1674" t="n">
         <v>5204</v>
@@ -49031,7 +49031,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1678" t="n">
-        <v>0.57211434841156</v>
+        <v>0.572114408016205</v>
       </c>
       <c r="H1678" t="n">
         <v>16692</v>
@@ -49060,7 +49060,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1679" t="n">
-        <v>0.574015080928802</v>
+        <v>0.574015021324158</v>
       </c>
       <c r="H1679" t="n">
         <v>42257</v>
@@ -49089,7 +49089,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1680" t="n">
         <v>5826</v>
@@ -49118,7 +49118,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1681" t="n">
-        <v>0.604426443576813</v>
+        <v>0.604426503181458</v>
       </c>
       <c r="H1681" t="n">
         <v>5420</v>
@@ -49147,7 +49147,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.612029373645782</v>
+        <v>0.612029314041138</v>
       </c>
       <c r="H1682" t="n">
         <v>9272</v>
@@ -49176,7 +49176,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.61012864112854</v>
+        <v>0.610128700733185</v>
       </c>
       <c r="H1683" t="n">
         <v>13294</v>
@@ -49205,7 +49205,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.593022227287292</v>
+        <v>0.593022286891937</v>
       </c>
       <c r="H1684" t="n">
         <v>17009</v>
@@ -49292,7 +49292,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252583026886</v>
       </c>
       <c r="H1687" t="n">
         <v>564</v>
@@ -49321,7 +49321,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252583026886</v>
       </c>
       <c r="H1688" t="n">
         <v>1061</v>
@@ -49350,7 +49350,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252583026886</v>
       </c>
       <c r="H1689" t="n">
         <v>1</v>
@@ -49408,7 +49408,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.604426443576813</v>
+        <v>0.604426503181458</v>
       </c>
       <c r="H1691" t="n">
         <v>677</v>
@@ -49466,7 +49466,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1693" t="n">
-        <v>0.604426443576813</v>
+        <v>0.604426503181458</v>
       </c>
       <c r="H1693" t="n">
         <v>832</v>
@@ -49495,7 +49495,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1694" t="n">
-        <v>0.604426443576813</v>
+        <v>0.604426503181458</v>
       </c>
       <c r="H1694" t="n">
         <v>950</v>
@@ -49524,7 +49524,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252583026886</v>
       </c>
       <c r="H1695" t="n">
         <v>6536</v>
@@ -49553,7 +49553,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1696" t="n">
         <v>1080</v>
@@ -49582,7 +49582,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1697" t="n">
         <v>0</v>
@@ -49698,7 +49698,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1701" t="n">
         <v>16</v>
@@ -49727,7 +49727,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1702" t="n">
         <v>502</v>
@@ -49756,7 +49756,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1703" t="n">
         <v>8574</v>
@@ -49785,7 +49785,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.593022227287292</v>
+        <v>0.593022286891937</v>
       </c>
       <c r="H1704" t="n">
         <v>5848</v>
@@ -49901,7 +49901,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1708" t="n">
         <v>6016</v>
@@ -49959,7 +49959,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.57211434841156</v>
+        <v>0.572114408016205</v>
       </c>
       <c r="H1710" t="n">
         <v>520</v>
@@ -49988,7 +49988,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1711" t="n">
         <v>63</v>
@@ -50017,7 +50017,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1712" t="n">
         <v>10927</v>
@@ -50104,7 +50104,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.568313002586365</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1715" t="n">
         <v>794</v>
@@ -50191,7 +50191,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1718" t="n">
         <v>2685</v>
@@ -50365,7 +50365,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.593022227287292</v>
+        <v>0.593022286891937</v>
       </c>
       <c r="H1724" t="n">
         <v>3416</v>
@@ -50481,7 +50481,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.593022227287292</v>
+        <v>0.593022286891937</v>
       </c>
       <c r="H1728" t="n">
         <v>3098</v>
@@ -50510,7 +50510,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.593022227287292</v>
+        <v>0.593022286891937</v>
       </c>
       <c r="H1729" t="n">
         <v>5901</v>
@@ -50626,7 +50626,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1733" t="n">
         <v>33</v>
@@ -50713,7 +50713,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1736" t="n">
         <v>347</v>
@@ -50742,7 +50742,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1737" t="n">
         <v>148</v>
@@ -50829,7 +50829,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.574015080928802</v>
+        <v>0.574015021324158</v>
       </c>
       <c r="H1740" t="n">
         <v>3589</v>
@@ -50858,7 +50858,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1741" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1741" t="n">
         <v>2611</v>
@@ -50916,7 +50916,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1743" t="n">
-        <v>0.5759157538414</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1743" t="n">
         <v>1000</v>
@@ -50945,7 +50945,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.574015080928802</v>
+        <v>0.574015021324158</v>
       </c>
       <c r="H1744" t="n">
         <v>500</v>
@@ -50974,7 +50974,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1745" t="n">
         <v>32626</v>
@@ -51003,7 +51003,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1746" t="n">
         <v>0</v>
@@ -51032,7 +51032,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.5759157538414</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1747" t="n">
         <v>8200</v>
@@ -51148,7 +51148,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1751" t="n">
         <v>5540</v>
@@ -51177,7 +51177,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.574015080928802</v>
+        <v>0.574015021324158</v>
       </c>
       <c r="H1752" t="n">
         <v>81</v>
@@ -51351,7 +51351,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1758" t="n">
         <v>2396</v>
@@ -51380,7 +51380,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1759" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1759" t="n">
         <v>0</v>
@@ -51409,7 +51409,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.57211434841156</v>
+        <v>0.572114408016205</v>
       </c>
       <c r="H1760" t="n">
         <v>5263</v>
@@ -51467,7 +51467,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1762" t="n">
         <v>615</v>
@@ -51496,7 +51496,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1763" t="n">
         <v>2731</v>
@@ -51525,7 +51525,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1764" t="n">
         <v>2755</v>
@@ -51583,7 +51583,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1766" t="n">
         <v>11513</v>
@@ -51612,7 +51612,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1767" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252583026886</v>
       </c>
       <c r="H1767" t="n">
         <v>624</v>
@@ -51670,7 +51670,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252583026886</v>
       </c>
       <c r="H1769" t="n">
         <v>8114</v>
@@ -51699,7 +51699,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.604426443576813</v>
+        <v>0.604426503181458</v>
       </c>
       <c r="H1770" t="n">
         <v>19269</v>
@@ -51728,7 +51728,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1771" t="n">
-        <v>0.604426443576813</v>
+        <v>0.604426503181458</v>
       </c>
       <c r="H1771" t="n">
         <v>15200</v>
@@ -51815,7 +51815,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1774" t="n">
-        <v>0.593022227287292</v>
+        <v>0.593022286891937</v>
       </c>
       <c r="H1774" t="n">
         <v>5550</v>
@@ -51844,7 +51844,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1775" t="n">
         <v>7172</v>
@@ -51873,7 +51873,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1776" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1776" t="n">
         <v>0</v>
@@ -51902,7 +51902,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1777" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1777" t="n">
         <v>6313</v>
@@ -51931,7 +51931,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1778" t="n">
         <v>516</v>
@@ -51989,7 +51989,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1780" t="n">
         <v>20280</v>
@@ -52163,7 +52163,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1786" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1786" t="n">
         <v>5365</v>
@@ -52192,7 +52192,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1787" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1787" t="n">
         <v>24392</v>
@@ -52221,7 +52221,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1788" t="n">
-        <v>0.593022227287292</v>
+        <v>0.593022286891937</v>
       </c>
       <c r="H1788" t="n">
         <v>1723</v>
@@ -52337,7 +52337,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1792" t="n">
         <v>1109</v>
@@ -52366,7 +52366,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1793" t="n">
-        <v>0.596823692321777</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1793" t="n">
         <v>21634</v>
@@ -52395,7 +52395,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1794" t="n">
-        <v>0.604426443576813</v>
+        <v>0.604426503181458</v>
       </c>
       <c r="H1794" t="n">
         <v>1836</v>
@@ -52482,7 +52482,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1797" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1797" t="n">
         <v>1834</v>
@@ -52511,7 +52511,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1798" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1798" t="n">
         <v>0</v>
@@ -52540,7 +52540,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1799" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1799" t="n">
         <v>0</v>
@@ -52772,7 +52772,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1807" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1807" t="n">
         <v>7034</v>
@@ -52830,7 +52830,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.593022227287292</v>
+        <v>0.593022286891937</v>
       </c>
       <c r="H1809" t="n">
         <v>10097</v>
@@ -52888,7 +52888,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1811" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1811" t="n">
         <v>4998</v>
@@ -52946,7 +52946,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1813" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1813" t="n">
         <v>32</v>
@@ -52975,7 +52975,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1814" t="n">
         <v>2582</v>
@@ -53004,7 +53004,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1815" t="n">
         <v>0</v>
@@ -53033,7 +53033,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1816" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1816" t="n">
         <v>3535</v>
@@ -53062,7 +53062,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1817" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1817" t="n">
         <v>22549</v>
@@ -53091,7 +53091,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1818" t="n">
-        <v>0.568313002586365</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1818" t="n">
         <v>1892</v>
@@ -53120,7 +53120,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1819" t="n">
-        <v>0.57211434841156</v>
+        <v>0.572114408016205</v>
       </c>
       <c r="H1819" t="n">
         <v>1215</v>
@@ -53149,7 +53149,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1820" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1820" t="n">
         <v>7922</v>
@@ -53178,7 +53178,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1821" t="n">
-        <v>0.5759157538414</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1821" t="n">
         <v>9490</v>
@@ -53265,7 +53265,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1824" t="n">
         <v>2687</v>
@@ -53323,7 +53323,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.568313002586365</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1826" t="n">
         <v>73878</v>
@@ -53381,7 +53381,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1828" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1828" t="n">
         <v>5044</v>
@@ -53410,7 +53410,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1829" t="n">
         <v>1562</v>
@@ -53468,7 +53468,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1831" t="n">
         <v>18113</v>
@@ -53497,7 +53497,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.5759157538414</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1832" t="n">
         <v>2559</v>
@@ -53526,7 +53526,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1833" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1833" t="n">
         <v>26592</v>
@@ -53555,7 +53555,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1834" t="n">
         <v>661</v>
@@ -53584,7 +53584,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1835" t="n">
         <v>2647</v>
@@ -53613,7 +53613,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.558809340000153</v>
+        <v>0.558809399604797</v>
       </c>
       <c r="H1836" t="n">
         <v>518</v>
@@ -53729,7 +53729,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1840" t="n">
         <v>5059</v>
@@ -53787,7 +53787,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1842" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1842" t="n">
         <v>9717</v>
@@ -53816,7 +53816,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.568313002586365</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1843" t="n">
         <v>1246</v>
@@ -53845,7 +53845,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1844" t="n">
-        <v>0.574015080928802</v>
+        <v>0.574015021324158</v>
       </c>
       <c r="H1844" t="n">
         <v>3137</v>
@@ -53932,7 +53932,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1847" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1847" t="n">
         <v>7661</v>
@@ -53961,7 +53961,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1848" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1848" t="n">
         <v>1162</v>
@@ -53990,7 +53990,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.574015080928802</v>
+        <v>0.574015021324158</v>
       </c>
       <c r="H1849" t="n">
         <v>17343</v>
@@ -54019,7 +54019,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.568313002586365</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1850" t="n">
         <v>7024</v>
@@ -54048,7 +54048,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1851" t="n">
         <v>7619</v>
@@ -54077,7 +54077,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1852" t="n">
-        <v>0.574015080928802</v>
+        <v>0.574015021324158</v>
       </c>
       <c r="H1852" t="n">
         <v>667</v>
@@ -54106,7 +54106,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1853" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1853" t="n">
         <v>5890</v>
@@ -54193,7 +54193,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1856" t="n">
         <v>12642</v>
@@ -54222,7 +54222,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1857" t="n">
-        <v>0.57211434841156</v>
+        <v>0.572114408016205</v>
       </c>
       <c r="H1857" t="n">
         <v>3125</v>
@@ -54251,7 +54251,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1858" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1858" t="n">
         <v>13779</v>
@@ -54280,7 +54280,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1859" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1859" t="n">
         <v>0</v>
@@ -54338,7 +54338,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.574015080928802</v>
+        <v>0.574015021324158</v>
       </c>
       <c r="H1861" t="n">
         <v>1513</v>
@@ -54367,7 +54367,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1862" t="n">
         <v>921</v>
@@ -54396,7 +54396,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1863" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1863" t="n">
         <v>10404</v>
@@ -54454,7 +54454,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1865" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1865" t="n">
         <v>817</v>
@@ -54483,7 +54483,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1866" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1866" t="n">
         <v>8439</v>
@@ -54512,7 +54512,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1867" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1867" t="n">
         <v>0</v>
@@ -54541,7 +54541,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1868" t="n">
         <v>235</v>
@@ -54657,7 +54657,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.568313002586365</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1872" t="n">
         <v>11785</v>
@@ -54686,7 +54686,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1873" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1873" t="n">
         <v>2469</v>
@@ -54715,7 +54715,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1874" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1874" t="n">
         <v>19</v>
@@ -54744,7 +54744,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1875" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1875" t="n">
         <v>2017</v>
@@ -54802,7 +54802,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1877" t="n">
-        <v>0.558809340000153</v>
+        <v>0.558809399604797</v>
       </c>
       <c r="H1877" t="n">
         <v>1202</v>
@@ -54831,7 +54831,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1878" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1878" t="n">
         <v>345</v>
@@ -54860,7 +54860,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1879" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1879" t="n">
         <v>1515</v>
@@ -54889,7 +54889,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1880" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1880" t="n">
         <v>18</v>
@@ -54918,7 +54918,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1881" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1881" t="n">
         <v>1</v>
@@ -54947,7 +54947,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1882" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1882" t="n">
         <v>3117</v>
@@ -54976,7 +54976,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1883" t="n">
         <v>69</v>
@@ -55005,7 +55005,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1884" t="n">
         <v>12818</v>
@@ -55034,7 +55034,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.568313002586365</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1885" t="n">
         <v>10634</v>
@@ -55063,7 +55063,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1886" t="n">
         <v>7962</v>
@@ -55092,7 +55092,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.558809340000153</v>
+        <v>0.558809399604797</v>
       </c>
       <c r="H1887" t="n">
         <v>2513</v>
@@ -55121,7 +55121,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1888" t="n">
         <v>1701</v>
@@ -55150,7 +55150,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1889" t="n">
         <v>0</v>
@@ -55179,7 +55179,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1890" t="n">
         <v>616</v>
@@ -55208,7 +55208,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1891" t="n">
         <v>4328</v>
@@ -55237,7 +55237,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1892" t="n">
         <v>4045</v>
@@ -55266,7 +55266,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1893" t="n">
         <v>0</v>
@@ -55295,7 +55295,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1894" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1894" t="n">
         <v>500</v>
@@ -55324,7 +55324,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1895" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1895" t="n">
         <v>1600</v>
@@ -55353,7 +55353,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1896" t="n">
         <v>0</v>
@@ -55382,7 +55382,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1897" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1897" t="n">
         <v>3982</v>
@@ -55440,7 +55440,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1899" t="n">
-        <v>0.558809340000153</v>
+        <v>0.558809399604797</v>
       </c>
       <c r="H1899" t="n">
         <v>28638</v>
@@ -55469,7 +55469,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1900" t="n">
-        <v>0.54170298576355</v>
+        <v>0.541702926158905</v>
       </c>
       <c r="H1900" t="n">
         <v>3769</v>
@@ -55527,7 +55527,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1902" t="n">
-        <v>0.558809340000153</v>
+        <v>0.558809399604797</v>
       </c>
       <c r="H1902" t="n">
         <v>2565</v>
@@ -55556,7 +55556,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1903" t="n">
-        <v>0.568313002586365</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1903" t="n">
         <v>8412</v>
@@ -55585,7 +55585,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1904" t="n">
-        <v>0.568313002586365</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1904" t="n">
         <v>2017</v>
@@ -55643,7 +55643,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1906" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1906" t="n">
         <v>1018</v>
@@ -55672,7 +55672,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1907" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1907" t="n">
         <v>0</v>
@@ -55701,7 +55701,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1908" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1908" t="n">
         <v>0</v>
@@ -55730,7 +55730,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1909" t="n">
         <v>1000</v>
@@ -55904,7 +55904,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1915" t="n">
-        <v>0.54170298576355</v>
+        <v>0.541702926158905</v>
       </c>
       <c r="H1915" t="n">
         <v>2626</v>
@@ -55962,7 +55962,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1917" t="n">
-        <v>0.543603658676147</v>
+        <v>0.543603718280792</v>
       </c>
       <c r="H1917" t="n">
         <v>5021</v>
@@ -56165,7 +56165,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G1924" t="n">
-        <v>0.547405064105988</v>
+        <v>0.547405123710632</v>
       </c>
       <c r="H1924" t="n">
         <v>2872</v>
@@ -56368,7 +56368,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1931" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327176094055</v>
       </c>
       <c r="H1931" t="n">
         <v>5238</v>
@@ -56397,7 +56397,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1932" t="n">
-        <v>0.612029373645782</v>
+        <v>0.612029314041138</v>
       </c>
       <c r="H1932" t="n">
         <v>18087</v>
@@ -56426,7 +56426,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1933" t="n">
-        <v>0.593022227287292</v>
+        <v>0.593022286891937</v>
       </c>
       <c r="H1933" t="n">
         <v>8534</v>
@@ -56455,7 +56455,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1934" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1934" t="n">
         <v>3890</v>
@@ -56513,7 +56513,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1936" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1936" t="n">
         <v>2748</v>
@@ -56542,7 +56542,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1937" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1937" t="n">
         <v>4073</v>
@@ -56629,7 +56629,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1940" t="n">
-        <v>0.57211434841156</v>
+        <v>0.572114408016205</v>
       </c>
       <c r="H1940" t="n">
         <v>10044</v>
@@ -56658,7 +56658,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1941" t="n">
-        <v>0.568313002586365</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1941" t="n">
         <v>1989</v>
@@ -56687,7 +56687,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1942" t="n">
-        <v>0.57211434841156</v>
+        <v>0.572114408016205</v>
       </c>
       <c r="H1942" t="n">
         <v>1706</v>
@@ -56716,7 +56716,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1943" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1943" t="n">
         <v>8017</v>
@@ -56745,7 +56745,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1944" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1944" t="n">
         <v>0</v>
@@ -56774,7 +56774,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1945" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1945" t="n">
         <v>0</v>
@@ -56803,7 +56803,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1946" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1946" t="n">
         <v>11246</v>
@@ -56919,7 +56919,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1950" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1950" t="n">
         <v>500</v>
@@ -56948,7 +56948,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1951" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1951" t="n">
         <v>8549</v>
@@ -56977,7 +56977,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1952" t="n">
-        <v>0.558809340000153</v>
+        <v>0.558809399604797</v>
       </c>
       <c r="H1952" t="n">
         <v>220</v>
@@ -57035,7 +57035,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1954" t="n">
-        <v>0.558809340000153</v>
+        <v>0.558809399604797</v>
       </c>
       <c r="H1954" t="n">
         <v>701</v>
@@ -57180,7 +57180,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1959" t="n">
         <v>52634</v>
@@ -57267,7 +57267,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1962" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071013212204</v>
       </c>
       <c r="H1962" t="n">
         <v>6069</v>
@@ -57586,7 +57586,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G1973" t="n">
-        <v>0.566412270069122</v>
+        <v>0.566412210464478</v>
       </c>
       <c r="H1973" t="n">
         <v>26871</v>
@@ -57644,7 +57644,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1975" t="n">
-        <v>0.565447270870209</v>
+        <v>0.565447330474854</v>
       </c>
       <c r="H1975" t="n">
         <v>35084</v>
@@ -57702,7 +57702,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1977" t="n">
-        <v>0.584745824337006</v>
+        <v>0.58474588394165</v>
       </c>
       <c r="H1977" t="n">
         <v>68759</v>
@@ -57789,7 +57789,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1980" t="n">
-        <v>0.550008475780487</v>
+        <v>0.550008416175842</v>
       </c>
       <c r="H1980" t="n">
         <v>8925</v>
@@ -57963,7 +57963,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1986" t="n">
-        <v>0.521060645580292</v>
+        <v>0.521060705184937</v>
       </c>
       <c r="H1986" t="n">
         <v>44064</v>
@@ -58050,7 +58050,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1989" t="n">
-        <v>0.521060645580292</v>
+        <v>0.521060705184937</v>
       </c>
       <c r="H1989" t="n">
         <v>10515</v>
@@ -58137,7 +58137,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1992" t="n">
-        <v>0.522990465164185</v>
+        <v>0.522990524768829</v>
       </c>
       <c r="H1992" t="n">
         <v>2</v>
@@ -58195,7 +58195,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1994" t="n">
-        <v>0.521060645580292</v>
+        <v>0.521060705184937</v>
       </c>
       <c r="H1994" t="n">
         <v>1448</v>
@@ -58224,7 +58224,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1995" t="n">
-        <v>0.521060645580292</v>
+        <v>0.521060705184937</v>
       </c>
       <c r="H1995" t="n">
         <v>31063</v>
@@ -58253,7 +58253,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1996" t="n">
-        <v>0.521060645580292</v>
+        <v>0.521060705184937</v>
       </c>
       <c r="H1996" t="n">
         <v>2633</v>
@@ -58311,7 +58311,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1998" t="n">
-        <v>0.522990465164185</v>
+        <v>0.522990524768829</v>
       </c>
       <c r="H1998" t="n">
         <v>3143</v>
@@ -58340,7 +58340,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1999" t="n">
-        <v>0.519130825996399</v>
+        <v>0.519130766391754</v>
       </c>
       <c r="H1999" t="n">
         <v>6157</v>
@@ -58369,7 +58369,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2000" t="n">
-        <v>0.524920403957367</v>
+        <v>0.524920344352722</v>
       </c>
       <c r="H2000" t="n">
         <v>19211</v>
@@ -58427,7 +58427,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2002" t="n">
-        <v>0.507551670074463</v>
+        <v>0.507551729679108</v>
       </c>
       <c r="H2002" t="n">
         <v>37821</v>
@@ -58572,7 +58572,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2007" t="n">
-        <v>0.524920403957367</v>
+        <v>0.524920344352722</v>
       </c>
       <c r="H2007" t="n">
         <v>8019</v>
@@ -58659,7 +58659,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G2010" t="n">
-        <v>0.503692030906677</v>
+        <v>0.503691971302032</v>
       </c>
       <c r="H2010" t="n">
         <v>2802</v>
@@ -58688,7 +58688,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2011" t="n">
-        <v>0.521060645580292</v>
+        <v>0.521060705184937</v>
       </c>
       <c r="H2011" t="n">
         <v>29644</v>
@@ -58717,7 +58717,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G2012" t="n">
-        <v>0.519130825996399</v>
+        <v>0.519130766391754</v>
       </c>
       <c r="H2012" t="n">
         <v>581</v>
@@ -59007,7 +59007,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G2022" t="n">
-        <v>0.503692030906677</v>
+        <v>0.503691971302032</v>
       </c>
       <c r="H2022" t="n">
         <v>2249</v>
@@ -59065,7 +59065,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2024" t="n">
-        <v>0.507551670074463</v>
+        <v>0.507551729679108</v>
       </c>
       <c r="H2024" t="n">
         <v>18265</v>
@@ -59268,7 +59268,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2031" t="n">
-        <v>0.495972543954849</v>
+        <v>0.495972573757172</v>
       </c>
       <c r="H2031" t="n">
         <v>4847</v>
@@ -59326,7 +59326,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2033" t="n">
-        <v>0.490182965993881</v>
+        <v>0.490183025598526</v>
       </c>
       <c r="H2033" t="n">
         <v>2502</v>
@@ -59471,7 +59471,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2038" t="n">
-        <v>0.488253146409988</v>
+        <v>0.488253116607666</v>
       </c>
       <c r="H2038" t="n">
         <v>1700</v>
@@ -59500,7 +59500,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2039" t="n">
-        <v>0.495972543954849</v>
+        <v>0.495972573757172</v>
       </c>
       <c r="H2039" t="n">
         <v>17700</v>
@@ -59645,7 +59645,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2044" t="n">
-        <v>0.495972543954849</v>
+        <v>0.495972573757172</v>
       </c>
       <c r="H2044" t="n">
         <v>12503</v>
@@ -59674,7 +59674,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2045" t="n">
-        <v>0.484393417835236</v>
+        <v>0.484393388032913</v>
       </c>
       <c r="H2045" t="n">
         <v>5704</v>
@@ -59732,7 +59732,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2047" t="n">
-        <v>0.490182965993881</v>
+        <v>0.490183025598526</v>
       </c>
       <c r="H2047" t="n">
         <v>1308</v>
@@ -59761,7 +59761,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2048" t="n">
-        <v>0.490182965993881</v>
+        <v>0.490183025598526</v>
       </c>
       <c r="H2048" t="n">
         <v>0</v>
@@ -60022,7 +60022,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2057" t="n">
-        <v>0.46412992477417</v>
+        <v>0.464129954576492</v>
       </c>
       <c r="H2057" t="n">
         <v>4024</v>
@@ -60573,7 +60573,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G2076" t="n">
-        <v>0.462200105190277</v>
+        <v>0.462200075387955</v>
       </c>
       <c r="H2076" t="n">
         <v>3818</v>
@@ -60718,7 +60718,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2081" t="n">
-        <v>0.443866461515427</v>
+        <v>0.443866491317749</v>
       </c>
       <c r="H2081" t="n">
         <v>160</v>
@@ -60805,7 +60805,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2084" t="n">
-        <v>0.434217184782028</v>
+        <v>0.434217214584351</v>
       </c>
       <c r="H2084" t="n">
         <v>18625</v>
@@ -60921,7 +60921,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2088" t="n">
-        <v>0.394655227661133</v>
+        <v>0.39465519785881</v>
       </c>
       <c r="H2088" t="n">
         <v>47151</v>
@@ -60950,7 +60950,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2089" t="n">
-        <v>0.401409715414047</v>
+        <v>0.401409685611725</v>
       </c>
       <c r="H2089" t="n">
         <v>15614</v>
@@ -61037,7 +61037,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2092" t="n">
-        <v>0.37632155418396</v>
+        <v>0.376321583986282</v>
       </c>
       <c r="H2092" t="n">
         <v>16216</v>
@@ -61298,7 +61298,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2101" t="n">
-        <v>0.378251433372498</v>
+        <v>0.378251403570175</v>
       </c>
       <c r="H2101" t="n">
         <v>31991</v>
@@ -61559,7 +61559,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2110" t="n">
-        <v>0.380181282758713</v>
+        <v>0.38018125295639</v>
       </c>
       <c r="H2110" t="n">
         <v>7881</v>
@@ -61646,7 +61646,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2113" t="n">
-        <v>0.37632155418396</v>
+        <v>0.376321583986282</v>
       </c>
       <c r="H2113" t="n">
         <v>8562</v>
@@ -61675,7 +61675,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G2114" t="n">
-        <v>0.35509318113327</v>
+        <v>0.355093151330948</v>
       </c>
       <c r="H2114" t="n">
         <v>32113</v>
@@ -61762,7 +61762,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G2117" t="n">
-        <v>0.356058120727539</v>
+        <v>0.356058090925217</v>
       </c>
       <c r="H2117" t="n">
         <v>4033</v>
@@ -61849,7 +61849,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2120" t="n">
-        <v>0.373426765203476</v>
+        <v>0.373426795005798</v>
       </c>
       <c r="H2120" t="n">
         <v>13582</v>
@@ -61878,7 +61878,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2121" t="n">
-        <v>0.434217184782028</v>
+        <v>0.434217214584351</v>
       </c>
       <c r="H2121" t="n">
         <v>286699</v>
@@ -61936,7 +61936,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2123" t="n">
-        <v>0.416848540306091</v>
+        <v>0.416848510503769</v>
       </c>
       <c r="H2123" t="n">
         <v>68404</v>
@@ -61965,7 +61965,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2124" t="n">
-        <v>0.401409715414047</v>
+        <v>0.401409685611725</v>
       </c>
       <c r="H2124" t="n">
         <v>97328</v>
@@ -62052,7 +62052,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2127" t="n">
-        <v>0.405269354581833</v>
+        <v>0.405269384384155</v>
       </c>
       <c r="H2127" t="n">
         <v>52451</v>
@@ -62284,7 +62284,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2135" t="n">
-        <v>0.394655227661133</v>
+        <v>0.39465519785881</v>
       </c>
       <c r="H2135" t="n">
         <v>7804</v>
@@ -62313,7 +62313,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2136" t="n">
-        <v>0.378251433372498</v>
+        <v>0.378251403570175</v>
       </c>
       <c r="H2136" t="n">
         <v>1237</v>
@@ -62458,7 +62458,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2141" t="n">
-        <v>0.394655227661133</v>
+        <v>0.39465519785881</v>
       </c>
       <c r="H2141" t="n">
         <v>28880</v>
@@ -62487,7 +62487,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2142" t="n">
-        <v>0.394655227661133</v>
+        <v>0.39465519785881</v>
       </c>
       <c r="H2142" t="n">
         <v>0</v>
@@ -62516,7 +62516,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2143" t="n">
-        <v>0.391760408878326</v>
+        <v>0.391760379076004</v>
       </c>
       <c r="H2143" t="n">
         <v>2955</v>
@@ -62545,7 +62545,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2144" t="n">
-        <v>0.391760408878326</v>
+        <v>0.391760379076004</v>
       </c>
       <c r="H2144" t="n">
         <v>28728</v>
@@ -63067,7 +63067,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2162" t="n">
-        <v>0.39947983622551</v>
+        <v>0.399479866027832</v>
       </c>
       <c r="H2162" t="n">
         <v>20849</v>
@@ -63096,7 +63096,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2163" t="n">
-        <v>0.401409715414047</v>
+        <v>0.401409685611725</v>
       </c>
       <c r="H2163" t="n">
         <v>11659</v>
@@ -63212,7 +63212,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2167" t="n">
-        <v>0.412023842334747</v>
+        <v>0.41202387213707</v>
       </c>
       <c r="H2167" t="n">
         <v>33001</v>
@@ -63270,7 +63270,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2169" t="n">
-        <v>0.408164203166962</v>
+        <v>0.408164173364639</v>
       </c>
       <c r="H2169" t="n">
         <v>55582</v>
@@ -63299,7 +63299,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2170" t="n">
-        <v>0.401409715414047</v>
+        <v>0.401409685611725</v>
       </c>
       <c r="H2170" t="n">
         <v>21037</v>
@@ -63328,7 +63328,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2171" t="n">
-        <v>0.401409715414047</v>
+        <v>0.401409685611725</v>
       </c>
       <c r="H2171" t="n">
         <v>31998</v>
@@ -63386,7 +63386,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2173" t="n">
-        <v>0.401409715414047</v>
+        <v>0.401409685611725</v>
       </c>
       <c r="H2173" t="n">
         <v>2007</v>
@@ -63502,7 +63502,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2177" t="n">
-        <v>0.396585047245026</v>
+        <v>0.396585077047348</v>
       </c>
       <c r="H2177" t="n">
         <v>533</v>
@@ -63531,7 +63531,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2178" t="n">
-        <v>0.399024099111557</v>
+        <v>0.399024069309235</v>
       </c>
       <c r="H2178" t="n">
         <v>19001</v>
@@ -63676,7 +63676,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2183" t="n">
-        <v>0.403902113437653</v>
+        <v>0.403902143239975</v>
       </c>
       <c r="H2183" t="n">
         <v>6543</v>
@@ -63734,7 +63734,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2185" t="n">
-        <v>0.403902113437653</v>
+        <v>0.403902143239975</v>
       </c>
       <c r="H2185" t="n">
         <v>25</v>
@@ -63966,7 +63966,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G2193" t="n">
-        <v>0.376585096120834</v>
+        <v>0.376585066318512</v>
       </c>
       <c r="H2193" t="n">
         <v>479</v>
@@ -64140,7 +64140,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2199" t="n">
-        <v>0.380487471818924</v>
+        <v>0.380487501621246</v>
       </c>
       <c r="H2199" t="n">
         <v>18500</v>
@@ -64343,7 +64343,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G2206" t="n">
-        <v>0.378536283969879</v>
+        <v>0.378536313772202</v>
       </c>
       <c r="H2206" t="n">
         <v>17820</v>
@@ -64372,7 +64372,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G2207" t="n">
-        <v>0.378536283969879</v>
+        <v>0.378536313772202</v>
       </c>
       <c r="H2207" t="n">
         <v>0</v>
@@ -64430,7 +64430,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2209" t="n">
-        <v>0.380487471818924</v>
+        <v>0.380487501621246</v>
       </c>
       <c r="H2209" t="n">
         <v>12610</v>
@@ -64604,7 +64604,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2215" t="n">
-        <v>0.377560645341873</v>
+        <v>0.377560675144196</v>
       </c>
       <c r="H2215" t="n">
         <v>10440</v>
@@ -64633,7 +64633,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G2216" t="n">
-        <v>0.376585096120834</v>
+        <v>0.376585066318512</v>
       </c>
       <c r="H2216" t="n">
         <v>1600</v>
@@ -64749,7 +64749,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2220" t="n">
-        <v>0.377560645341873</v>
+        <v>0.377560675144196</v>
       </c>
       <c r="H2220" t="n">
         <v>500</v>
@@ -64778,7 +64778,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G2221" t="n">
-        <v>0.376585096120834</v>
+        <v>0.376585066318512</v>
       </c>
       <c r="H2221" t="n">
         <v>9168</v>
@@ -64952,7 +64952,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2227" t="n">
-        <v>0.418536245822906</v>
+        <v>0.418536216020584</v>
       </c>
       <c r="H2227" t="n">
         <v>97027</v>
@@ -65097,7 +65097,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2232" t="n">
-        <v>0.396097242832184</v>
+        <v>0.396097213029861</v>
       </c>
       <c r="H2232" t="n">
         <v>32431</v>
@@ -65184,7 +65184,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2235" t="n">
-        <v>0.399024099111557</v>
+        <v>0.399024069309235</v>
       </c>
       <c r="H2235" t="n">
         <v>2415</v>
@@ -65213,7 +65213,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2236" t="n">
-        <v>0.400975286960602</v>
+        <v>0.400975316762924</v>
       </c>
       <c r="H2236" t="n">
         <v>34547</v>
@@ -65329,7 +65329,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2240" t="n">
-        <v>0.400975286960602</v>
+        <v>0.400975316762924</v>
       </c>
       <c r="H2240" t="n">
         <v>8875</v>
@@ -65387,7 +65387,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2242" t="n">
-        <v>0.399024099111557</v>
+        <v>0.399024069309235</v>
       </c>
       <c r="H2242" t="n">
         <v>5683</v>
@@ -65503,7 +65503,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2246" t="n">
-        <v>0.384389936923981</v>
+        <v>0.384389907121658</v>
       </c>
       <c r="H2246" t="n">
         <v>1</v>
@@ -65619,7 +65619,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G2250" t="n">
-        <v>0.376585096120834</v>
+        <v>0.376585066318512</v>
       </c>
       <c r="H2250" t="n">
         <v>23292</v>
@@ -65648,7 +65648,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2251" t="n">
-        <v>0.380487471818924</v>
+        <v>0.380487501621246</v>
       </c>
       <c r="H2251" t="n">
         <v>6568</v>
@@ -65677,7 +65677,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2252" t="n">
-        <v>0.380487471818924</v>
+        <v>0.380487501621246</v>
       </c>
       <c r="H2252" t="n">
         <v>0</v>
@@ -65706,7 +65706,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2253" t="n">
-        <v>0.396097242832184</v>
+        <v>0.396097213029861</v>
       </c>
       <c r="H2253" t="n">
         <v>1000</v>
@@ -65793,7 +65793,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2256" t="n">
-        <v>0.380487471818924</v>
+        <v>0.380487501621246</v>
       </c>
       <c r="H2256" t="n">
         <v>2783</v>
@@ -66025,7 +66025,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2264" t="n">
-        <v>0.396097242832184</v>
+        <v>0.396097213029861</v>
       </c>
       <c r="H2264" t="n">
         <v>17013</v>
@@ -66083,7 +66083,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2266" t="n">
-        <v>0.384389936923981</v>
+        <v>0.384389907121658</v>
       </c>
       <c r="H2266" t="n">
         <v>20680</v>
@@ -66170,7 +66170,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G2269" t="n">
-        <v>0.378536283969879</v>
+        <v>0.378536313772202</v>
       </c>
       <c r="H2269" t="n">
         <v>263</v>
@@ -66431,7 +66431,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2278" t="n">
-        <v>0.418536245822906</v>
+        <v>0.418536216020584</v>
       </c>
       <c r="H2278" t="n">
         <v>172855</v>
@@ -66489,7 +66489,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G2280" t="n">
-        <v>0.478048413991928</v>
+        <v>0.478048384189606</v>
       </c>
       <c r="H2280" t="n">
         <v>278829</v>
@@ -66605,7 +66605,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G2284" t="n">
-        <v>0.48390206694603</v>
+        <v>0.483902037143707</v>
       </c>
       <c r="H2284" t="n">
         <v>48623</v>
@@ -66634,7 +66634,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2285" t="n">
-        <v>0.469267904758453</v>
+        <v>0.469267934560776</v>
       </c>
       <c r="H2285" t="n">
         <v>35599</v>
@@ -66663,7 +66663,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G2286" t="n">
-        <v>0.478048413991928</v>
+        <v>0.478048384189606</v>
       </c>
       <c r="H2286" t="n">
         <v>29506</v>
@@ -66895,7 +66895,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G2294" t="n">
-        <v>0.467316716909409</v>
+        <v>0.467316687107086</v>
       </c>
       <c r="H2294" t="n">
         <v>68672</v>
@@ -66953,7 +66953,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G2296" t="n">
-        <v>0.463414251804352</v>
+        <v>0.463414281606674</v>
       </c>
       <c r="H2296" t="n">
         <v>16299</v>
@@ -67040,7 +67040,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2299" t="n">
-        <v>0.43902400135994</v>
+        <v>0.439024031162262</v>
       </c>
       <c r="H2299" t="n">
         <v>9929</v>
@@ -67243,7 +67243,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2306" t="n">
-        <v>0.448780119419098</v>
+        <v>0.44878014922142</v>
       </c>
       <c r="H2306" t="n">
         <v>20358</v>
@@ -67446,7 +67446,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2313" t="n">
-        <v>0.493658155202866</v>
+        <v>0.493658125400543</v>
       </c>
       <c r="H2313" t="n">
         <v>307123</v>
@@ -67475,7 +67475,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2314" t="n">
-        <v>0.491706907749176</v>
+        <v>0.491706937551498</v>
       </c>
       <c r="H2314" t="n">
         <v>87078</v>
@@ -67504,7 +67504,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2315" t="n">
-        <v>0.491706907749176</v>
+        <v>0.491706937551498</v>
       </c>
       <c r="H2315" t="n">
         <v>2346</v>
@@ -67562,7 +67562,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2317" t="n">
-        <v>0.49560934305191</v>
+        <v>0.495609402656555</v>
       </c>
       <c r="H2317" t="n">
         <v>129371</v>
@@ -67649,7 +67649,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2320" t="n">
-        <v>0.513170301914215</v>
+        <v>0.51317036151886</v>
       </c>
       <c r="H2320" t="n">
         <v>65607</v>
@@ -67678,7 +67678,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2321" t="n">
-        <v>0.581462979316711</v>
+        <v>0.581462919712067</v>
       </c>
       <c r="H2321" t="n">
         <v>185258</v>
@@ -67736,7 +67736,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2323" t="n">
-        <v>0.727804243564606</v>
+        <v>0.72780430316925</v>
       </c>
       <c r="H2323" t="n">
         <v>511007</v>
@@ -67823,7 +67823,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2326" t="n">
-        <v>0.68292623758316</v>
+        <v>0.682926297187805</v>
       </c>
       <c r="H2326" t="n">
         <v>110593</v>
@@ -68055,7 +68055,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G2334" t="n">
-        <v>0.647804379463196</v>
+        <v>0.647804319858551</v>
       </c>
       <c r="H2334" t="n">
         <v>64268</v>
@@ -68084,7 +68084,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2335" t="n">
-        <v>0.66926771402359</v>
+        <v>0.669267773628235</v>
       </c>
       <c r="H2335" t="n">
         <v>7106</v>
@@ -68229,7 +68229,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G2340" t="n">
-        <v>0.710243284702301</v>
+        <v>0.710243344306946</v>
       </c>
       <c r="H2340" t="n">
         <v>378919</v>
@@ -68258,7 +68258,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G2341" t="n">
-        <v>0.710243284702301</v>
+        <v>0.710243344306946</v>
       </c>
       <c r="H2341" t="n">
         <v>297783</v>
@@ -68287,7 +68287,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G2342" t="n">
-        <v>0.706340909004211</v>
+        <v>0.706340849399567</v>
       </c>
       <c r="H2342" t="n">
         <v>127644</v>
@@ -68316,7 +68316,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2343" t="n">
-        <v>0.68292623758316</v>
+        <v>0.682926297187805</v>
       </c>
       <c r="H2343" t="n">
         <v>51783</v>
@@ -68374,7 +68374,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2345" t="n">
-        <v>0.68292623758316</v>
+        <v>0.682926297187805</v>
       </c>
       <c r="H2345" t="n">
         <v>33898</v>
@@ -68432,7 +68432,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G2347" t="n">
-        <v>0.688779890537262</v>
+        <v>0.688779950141907</v>
       </c>
       <c r="H2347" t="n">
         <v>38891</v>
@@ -68548,7 +68548,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2351" t="n">
-        <v>0.675121426582336</v>
+        <v>0.675121366977692</v>
       </c>
       <c r="H2351" t="n">
         <v>2020</v>
@@ -68577,7 +68577,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2352" t="n">
-        <v>0.571706831455231</v>
+        <v>0.571706891059875</v>
       </c>
       <c r="H2352" t="n">
         <v>262615</v>
@@ -68606,7 +68606,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2353" t="n">
-        <v>0.575609266757965</v>
+        <v>0.57560932636261</v>
       </c>
       <c r="H2353" t="n">
         <v>38367</v>
@@ -68664,7 +68664,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2355" t="n">
-        <v>0.536584973335266</v>
+        <v>0.536584913730621</v>
       </c>
       <c r="H2355" t="n">
         <v>160119</v>
@@ -68867,7 +68867,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2362" t="n">
-        <v>0.575609266757965</v>
+        <v>0.57560932636261</v>
       </c>
       <c r="H2362" t="n">
         <v>81915</v>
@@ -68983,7 +68983,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2366" t="n">
-        <v>0.675121426582336</v>
+        <v>0.675121366977692</v>
       </c>
       <c r="H2366" t="n">
         <v>134358</v>
@@ -69012,7 +69012,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2367" t="n">
-        <v>0.66926771402359</v>
+        <v>0.669267773628235</v>
       </c>
       <c r="H2367" t="n">
         <v>126530</v>
@@ -69041,7 +69041,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2368" t="n">
-        <v>0.663414061069489</v>
+        <v>0.663414120674133</v>
       </c>
       <c r="H2368" t="n">
         <v>18106</v>
@@ -69128,7 +69128,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2371" t="n">
-        <v>0.638048231601715</v>
+        <v>0.63804829120636</v>
       </c>
       <c r="H2371" t="n">
         <v>84922</v>
@@ -69186,7 +69186,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2373" t="n">
-        <v>0.655609250068665</v>
+        <v>0.65560919046402</v>
       </c>
       <c r="H2373" t="n">
         <v>43588</v>
@@ -69215,7 +69215,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2374" t="n">
-        <v>0.616584956645966</v>
+        <v>0.616584897041321</v>
       </c>
       <c r="H2374" t="n">
         <v>235030</v>
@@ -69273,7 +69273,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2376" t="n">
-        <v>0.616584956645966</v>
+        <v>0.616584897041321</v>
       </c>
       <c r="H2376" t="n">
         <v>18713</v>
@@ -69418,7 +69418,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2381" t="n">
-        <v>0.616584956645966</v>
+        <v>0.616584897041321</v>
       </c>
       <c r="H2381" t="n">
         <v>44210</v>
@@ -69476,7 +69476,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2383" t="n">
-        <v>0.616584956645966</v>
+        <v>0.616584897041321</v>
       </c>
       <c r="H2383" t="n">
         <v>177203</v>
@@ -69766,7 +69766,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2393" t="n">
-        <v>0.663414061069489</v>
+        <v>0.663414120674133</v>
       </c>
       <c r="H2393" t="n">
         <v>110879</v>
@@ -69795,7 +69795,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2394" t="n">
-        <v>0.673170208930969</v>
+        <v>0.673170149326324</v>
       </c>
       <c r="H2394" t="n">
         <v>49142</v>
@@ -69853,7 +69853,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2396" t="n">
-        <v>0.66926771402359</v>
+        <v>0.669267773628235</v>
       </c>
       <c r="H2396" t="n">
         <v>92823</v>
@@ -69911,7 +69911,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2398" t="n">
-        <v>0.675121426582336</v>
+        <v>0.675121366977692</v>
       </c>
       <c r="H2398" t="n">
         <v>9840</v>
@@ -70085,7 +70085,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2404" t="n">
-        <v>0.663414061069489</v>
+        <v>0.663414120674133</v>
       </c>
       <c r="H2404" t="n">
         <v>166415</v>
@@ -70172,7 +70172,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G2407" t="n">
-        <v>0.647804379463196</v>
+        <v>0.647804319858551</v>
       </c>
       <c r="H2407" t="n">
         <v>324</v>
@@ -70230,7 +70230,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2409" t="n">
-        <v>0.628292202949524</v>
+        <v>0.628292143344879</v>
       </c>
       <c r="H2409" t="n">
         <v>7797</v>
@@ -70259,7 +70259,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2410" t="n">
-        <v>0.638048231601715</v>
+        <v>0.63804829120636</v>
       </c>
       <c r="H2410" t="n">
         <v>2707</v>
@@ -70288,7 +70288,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2411" t="n">
-        <v>0.638048231601715</v>
+        <v>0.63804829120636</v>
       </c>
       <c r="H2411" t="n">
         <v>2255</v>
@@ -70346,7 +70346,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G2413" t="n">
-        <v>0.647804379463196</v>
+        <v>0.647804319858551</v>
       </c>
       <c r="H2413" t="n">
         <v>17</v>
@@ -70375,7 +70375,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2414" t="n">
-        <v>0.628292202949524</v>
+        <v>0.628292143344879</v>
       </c>
       <c r="H2414" t="n">
         <v>42392</v>
@@ -70549,7 +70549,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2420" t="n">
-        <v>0.62048727273941</v>
+        <v>0.620487332344055</v>
       </c>
       <c r="H2420" t="n">
         <v>12474</v>
@@ -70607,7 +70607,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2422" t="n">
-        <v>0.628292202949524</v>
+        <v>0.628292143344879</v>
       </c>
       <c r="H2422" t="n">
         <v>1650</v>
@@ -70636,7 +70636,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G2423" t="n">
-        <v>0.618536055088043</v>
+        <v>0.618536114692688</v>
       </c>
       <c r="H2423" t="n">
         <v>8750</v>
@@ -70723,7 +70723,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2426" t="n">
-        <v>0.628292202949524</v>
+        <v>0.628292143344879</v>
       </c>
       <c r="H2426" t="n">
         <v>2088</v>
@@ -79997,7 +79997,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="E2746" t="n">
-        <v>1.22000002861023</v>
+        <v>1.2150000333786</v>
       </c>
       <c r="F2746" t="n">
         <v>1.2150000333786</v>
@@ -80009,6 +80009,35 @@
         <v>5</v>
       </c>
       <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>1.21000003814697</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>17782</v>
+      </c>
+      <c r="I2747" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -543,7 +543,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G6" t="n">
-        <v>1.53482520580292</v>
+        <v>1.53482508659363</v>
       </c>
       <c r="H6" t="n">
         <v>31459</v>
@@ -601,7 +601,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G8" t="n">
-        <v>1.49205899238586</v>
+        <v>1.49205923080444</v>
       </c>
       <c r="H8" t="n">
         <v>9900</v>
@@ -862,7 +862,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G17" t="n">
-        <v>1.30198800563812</v>
+        <v>1.30198788642883</v>
       </c>
       <c r="H17" t="n">
         <v>5838</v>
@@ -891,7 +891,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G18" t="n">
-        <v>1.30198800563812</v>
+        <v>1.30198788642883</v>
       </c>
       <c r="H18" t="n">
         <v>4474</v>
@@ -949,7 +949,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G20" t="n">
-        <v>1.30388844013214</v>
+        <v>1.30388855934143</v>
       </c>
       <c r="H20" t="n">
         <v>7254</v>
@@ -978,7 +978,7 @@
         <v>1.375</v>
       </c>
       <c r="G21" t="n">
-        <v>1.30673956871033</v>
+        <v>1.30673968791962</v>
       </c>
       <c r="H21" t="n">
         <v>1302</v>
@@ -1065,7 +1065,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G24" t="n">
-        <v>1.33049857616425</v>
+        <v>1.33049845695496</v>
       </c>
       <c r="H24" t="n">
         <v>8036</v>
@@ -1123,7 +1123,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G26" t="n">
-        <v>1.25446999073029</v>
+        <v>1.25447010993958</v>
       </c>
       <c r="H26" t="n">
         <v>11901</v>
@@ -1181,7 +1181,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G28" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H28" t="n">
         <v>6283</v>
@@ -1239,7 +1239,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G30" t="n">
-        <v>1.13662588596344</v>
+        <v>1.13662576675415</v>
       </c>
       <c r="H30" t="n">
         <v>1130</v>
@@ -1268,7 +1268,7 @@
         <v>1.16100001335144</v>
       </c>
       <c r="G31" t="n">
-        <v>1.10336339473724</v>
+        <v>1.10336351394653</v>
       </c>
       <c r="H31" t="n">
         <v>6020</v>
@@ -1326,7 +1326,7 @@
         <v>1.375</v>
       </c>
       <c r="G33" t="n">
-        <v>1.30673956871033</v>
+        <v>1.30673968791962</v>
       </c>
       <c r="H33" t="n">
         <v>9139</v>
@@ -1355,7 +1355,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G34" t="n">
-        <v>1.24496638774872</v>
+        <v>1.24496650695801</v>
       </c>
       <c r="H34" t="n">
         <v>11697</v>
@@ -1384,7 +1384,7 @@
         <v>1.35899996757507</v>
       </c>
       <c r="G35" t="n">
-        <v>1.29153394699097</v>
+        <v>1.29153406620026</v>
       </c>
       <c r="H35" t="n">
         <v>2501</v>
@@ -1413,7 +1413,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G36" t="n">
-        <v>1.25922179222107</v>
+        <v>1.25922191143036</v>
       </c>
       <c r="H36" t="n">
         <v>4117</v>
@@ -1471,7 +1471,7 @@
         <v>1.32400000095367</v>
       </c>
       <c r="G38" t="n">
-        <v>1.25827133655548</v>
+        <v>1.25827145576477</v>
       </c>
       <c r="H38" t="n">
         <v>12260</v>
@@ -1529,7 +1529,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G40" t="n">
-        <v>1.31149137020111</v>
+        <v>1.3114914894104</v>
       </c>
       <c r="H40" t="n">
         <v>13000</v>
@@ -1558,7 +1558,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G41" t="n">
-        <v>1.31149137020111</v>
+        <v>1.3114914894104</v>
       </c>
       <c r="H41" t="n">
         <v>9289</v>
@@ -1587,7 +1587,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G42" t="n">
-        <v>1.29723608493805</v>
+        <v>1.29723620414734</v>
       </c>
       <c r="H42" t="n">
         <v>3745</v>
@@ -1616,7 +1616,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G43" t="n">
-        <v>1.31149137020111</v>
+        <v>1.3114914894104</v>
       </c>
       <c r="H43" t="n">
         <v>65</v>
@@ -1790,7 +1790,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>1.30103754997253</v>
+        <v>1.30103743076324</v>
       </c>
       <c r="H49" t="n">
         <v>8270</v>
@@ -1848,7 +1848,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G51" t="n">
-        <v>1.33049857616425</v>
+        <v>1.33049845695496</v>
       </c>
       <c r="H51" t="n">
         <v>5788</v>
@@ -2051,7 +2051,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G58" t="n">
-        <v>1.26967573165894</v>
+        <v>1.26967561244965</v>
       </c>
       <c r="H58" t="n">
         <v>21406</v>
@@ -2138,7 +2138,7 @@
         <v>1.33800005912781</v>
       </c>
       <c r="G61" t="n">
-        <v>1.27157640457153</v>
+        <v>1.27157652378082</v>
       </c>
       <c r="H61" t="n">
         <v>1297</v>
@@ -2196,7 +2196,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G63" t="n">
-        <v>1.24496638774872</v>
+        <v>1.24496650695801</v>
       </c>
       <c r="H63" t="n">
         <v>3282</v>
@@ -2225,7 +2225,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G64" t="n">
-        <v>1.24116504192352</v>
+        <v>1.24116492271423</v>
       </c>
       <c r="H64" t="n">
         <v>6820</v>
@@ -2254,7 +2254,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G65" t="n">
-        <v>1.26017212867737</v>
+        <v>1.26017224788666</v>
       </c>
       <c r="H65" t="n">
         <v>13431</v>
@@ -2341,7 +2341,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G68" t="n">
-        <v>1.30578923225403</v>
+        <v>1.30578935146332</v>
       </c>
       <c r="H68" t="n">
         <v>119</v>
@@ -2370,7 +2370,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G69" t="n">
-        <v>1.30578923225403</v>
+        <v>1.30578935146332</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G70" t="n">
-        <v>1.2478175163269</v>
+        <v>1.24781763553619</v>
       </c>
       <c r="H70" t="n">
         <v>3528</v>
@@ -2486,7 +2486,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G73" t="n">
-        <v>1.29058361053467</v>
+        <v>1.29058349132538</v>
       </c>
       <c r="H73" t="n">
         <v>5869</v>
@@ -2573,7 +2573,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G76" t="n">
-        <v>1.26967573165894</v>
+        <v>1.26967561244965</v>
       </c>
       <c r="H76" t="n">
         <v>8995</v>
@@ -2660,7 +2660,7 @@
         <v>1.34700000286102</v>
       </c>
       <c r="G79" t="n">
-        <v>1.28012979030609</v>
+        <v>1.2801296710968</v>
       </c>
       <c r="H79" t="n">
         <v>6900</v>
@@ -2689,7 +2689,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G80" t="n">
-        <v>1.2791793346405</v>
+        <v>1.27917921543121</v>
       </c>
       <c r="H80" t="n">
         <v>1743</v>
@@ -2718,7 +2718,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G81" t="n">
-        <v>1.2791793346405</v>
+        <v>1.27917921543121</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>1.37199997901917</v>
       </c>
       <c r="G82" t="n">
-        <v>1.30388844013214</v>
+        <v>1.30388855934143</v>
       </c>
       <c r="H82" t="n">
         <v>4227</v>
@@ -2892,7 +2892,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G87" t="n">
-        <v>1.28488147258759</v>
+        <v>1.2848813533783</v>
       </c>
       <c r="H87" t="n">
         <v>1240</v>
@@ -2979,7 +2979,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G90" t="n">
-        <v>1.30103754997253</v>
+        <v>1.30103743076324</v>
       </c>
       <c r="H90" t="n">
         <v>100</v>
@@ -3008,7 +3008,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G91" t="n">
-        <v>1.30103754997253</v>
+        <v>1.30103743076324</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G92" t="n">
-        <v>1.25922179222107</v>
+        <v>1.25922191143036</v>
       </c>
       <c r="H92" t="n">
         <v>1792</v>
@@ -3066,7 +3066,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G93" t="n">
-        <v>1.23546290397644</v>
+        <v>1.23546278476715</v>
       </c>
       <c r="H93" t="n">
         <v>7369</v>
@@ -3095,7 +3095,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G94" t="n">
-        <v>1.25446999073029</v>
+        <v>1.25447010993958</v>
       </c>
       <c r="H94" t="n">
         <v>6526</v>
@@ -3211,7 +3211,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G98" t="n">
-        <v>1.18034219741821</v>
+        <v>1.1803423166275</v>
       </c>
       <c r="H98" t="n">
         <v>765</v>
@@ -3240,7 +3240,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G99" t="n">
-        <v>1.18034219741821</v>
+        <v>1.1803423166275</v>
       </c>
       <c r="H99" t="n">
         <v>10250</v>
@@ -3269,7 +3269,7 @@
         <v>1.25</v>
       </c>
       <c r="G100" t="n">
-        <v>1.18794512748718</v>
+        <v>1.18794500827789</v>
       </c>
       <c r="H100" t="n">
         <v>5981</v>
@@ -3327,7 +3327,7 @@
         <v>1.25899994373322</v>
       </c>
       <c r="G102" t="n">
-        <v>1.19649815559387</v>
+        <v>1.19649827480316</v>
       </c>
       <c r="H102" t="n">
         <v>12993</v>
@@ -3356,7 +3356,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G103" t="n">
-        <v>1.16133499145508</v>
+        <v>1.16133511066437</v>
       </c>
       <c r="H103" t="n">
         <v>8484</v>
@@ -3385,7 +3385,7 @@
         <v>1.22099995613098</v>
       </c>
       <c r="G104" t="n">
-        <v>1.16038465499878</v>
+        <v>1.16038477420807</v>
       </c>
       <c r="H104" t="n">
         <v>2759</v>
@@ -3443,7 +3443,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G106" t="n">
-        <v>1.17844152450562</v>
+        <v>1.1784416437149</v>
       </c>
       <c r="H106" t="n">
         <v>2020</v>
@@ -3472,7 +3472,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G107" t="n">
-        <v>1.17749106884003</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H107" t="n">
         <v>2700</v>
@@ -3501,7 +3501,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G108" t="n">
-        <v>1.17749106884003</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H108" t="n">
         <v>500</v>
@@ -3530,7 +3530,7 @@
         <v>1.23699998855591</v>
       </c>
       <c r="G109" t="n">
-        <v>1.17559051513672</v>
+        <v>1.17559039592743</v>
       </c>
       <c r="H109" t="n">
         <v>2635</v>
@@ -3588,7 +3588,7 @@
         <v>1.20799994468689</v>
       </c>
       <c r="G111" t="n">
-        <v>1.14803004264832</v>
+        <v>1.1480301618576</v>
       </c>
       <c r="H111" t="n">
         <v>30565</v>
@@ -3646,7 +3646,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H113" t="n">
         <v>202</v>
@@ -3733,7 +3733,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G116" t="n">
-        <v>1.09481024742126</v>
+        <v>1.09481012821198</v>
       </c>
       <c r="H116" t="n">
         <v>4584</v>
@@ -3762,7 +3762,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H117" t="n">
         <v>22400</v>
@@ -3878,7 +3878,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G121" t="n">
-        <v>1.13187396526337</v>
+        <v>1.13187408447266</v>
       </c>
       <c r="H121" t="n">
         <v>5919</v>
@@ -3936,7 +3936,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G123" t="n">
-        <v>1.13662588596344</v>
+        <v>1.13662576675415</v>
       </c>
       <c r="H123" t="n">
         <v>15822</v>
@@ -3965,7 +3965,7 @@
         <v>1.02300000190735</v>
       </c>
       <c r="G124" t="n">
-        <v>0.972214341163635</v>
+        <v>0.97221428155899</v>
       </c>
       <c r="H124" t="n">
         <v>9233</v>
@@ -4023,7 +4023,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G126" t="n">
-        <v>0.975065350532532</v>
+        <v>0.975065410137177</v>
       </c>
       <c r="H126" t="n">
         <v>15762</v>
@@ -4139,7 +4139,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G130" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H130" t="n">
         <v>9949</v>
@@ -4168,7 +4168,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G131" t="n">
-        <v>1.09005832672119</v>
+        <v>1.09005844593048</v>
       </c>
       <c r="H131" t="n">
         <v>4789</v>
@@ -4226,7 +4226,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G133" t="n">
-        <v>0.99502295255661</v>
+        <v>0.995022833347321</v>
       </c>
       <c r="H133" t="n">
         <v>5798</v>
@@ -4255,7 +4255,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G134" t="n">
-        <v>1.02068245410919</v>
+        <v>1.02068257331848</v>
       </c>
       <c r="H134" t="n">
         <v>1695</v>
@@ -4284,7 +4284,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G135" t="n">
-        <v>1.00547683238983</v>
+        <v>1.00547671318054</v>
       </c>
       <c r="H135" t="n">
         <v>11813</v>
@@ -4342,7 +4342,7 @@
         <v>1.02699995040894</v>
       </c>
       <c r="G137" t="n">
-        <v>0.976015567779541</v>
+        <v>0.976015627384186</v>
       </c>
       <c r="H137" t="n">
         <v>13243</v>
@@ -4400,7 +4400,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G139" t="n">
-        <v>0.996923565864563</v>
+        <v>0.996923446655273</v>
       </c>
       <c r="H139" t="n">
         <v>1497</v>
@@ -4574,7 +4574,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G145" t="n">
-        <v>0.975065350532532</v>
+        <v>0.975065410137177</v>
       </c>
       <c r="H145" t="n">
         <v>6955</v>
@@ -4603,7 +4603,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G146" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H146" t="n">
         <v>7470</v>
@@ -4632,7 +4632,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G147" t="n">
-        <v>0.99502295255661</v>
+        <v>0.995022833347321</v>
       </c>
       <c r="H147" t="n">
         <v>10351</v>
@@ -4661,7 +4661,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>0.988370299339294</v>
+        <v>0.988370358943939</v>
       </c>
       <c r="H148" t="n">
         <v>13390</v>
@@ -4690,7 +4690,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G149" t="n">
-        <v>1.00927817821503</v>
+        <v>1.00927829742432</v>
       </c>
       <c r="H149" t="n">
         <v>9425</v>
@@ -4748,7 +4748,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G151" t="n">
-        <v>0.987419903278351</v>
+        <v>0.987420082092285</v>
       </c>
       <c r="H151" t="n">
         <v>15266</v>
@@ -4777,7 +4777,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G152" t="n">
-        <v>0.986469626426697</v>
+        <v>0.986469566822052</v>
       </c>
       <c r="H152" t="n">
         <v>5343</v>
@@ -4806,7 +4806,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G153" t="n">
-        <v>0.986469626426697</v>
+        <v>0.986469566822052</v>
       </c>
       <c r="H153" t="n">
         <v>1577</v>
@@ -5096,7 +5096,7 @@
         <v>1.02699995040894</v>
       </c>
       <c r="G163" t="n">
-        <v>0.976015567779541</v>
+        <v>0.976015627384186</v>
       </c>
       <c r="H163" t="n">
         <v>1600</v>
@@ -5125,7 +5125,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G164" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H164" t="n">
         <v>250</v>
@@ -5154,7 +5154,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G165" t="n">
-        <v>0.963661134243011</v>
+        <v>0.963661193847656</v>
       </c>
       <c r="H165" t="n">
         <v>3542</v>
@@ -5241,7 +5241,7 @@
         <v>1.02300000190735</v>
       </c>
       <c r="G168" t="n">
-        <v>0.972214341163635</v>
+        <v>0.97221428155899</v>
       </c>
       <c r="H168" t="n">
         <v>2389</v>
@@ -5270,7 +5270,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G169" t="n">
-        <v>0.986469626426697</v>
+        <v>0.986469566822052</v>
       </c>
       <c r="H169" t="n">
         <v>835</v>
@@ -5299,7 +5299,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G170" t="n">
-        <v>0.973164737224579</v>
+        <v>0.973164677619934</v>
       </c>
       <c r="H170" t="n">
         <v>7003</v>
@@ -5328,7 +5328,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G171" t="n">
-        <v>0.99502295255661</v>
+        <v>0.995022833347321</v>
       </c>
       <c r="H171" t="n">
         <v>2072</v>
@@ -5357,7 +5357,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G172" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H172" t="n">
         <v>10607</v>
@@ -5386,7 +5386,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G173" t="n">
-        <v>1.00547683238983</v>
+        <v>1.00547671318054</v>
       </c>
       <c r="H173" t="n">
         <v>1</v>
@@ -5415,7 +5415,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G174" t="n">
-        <v>0.996923565864563</v>
+        <v>0.996923446655273</v>
       </c>
       <c r="H174" t="n">
         <v>500</v>
@@ -5502,7 +5502,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G177" t="n">
-        <v>1.10241305828094</v>
+        <v>1.10241317749023</v>
       </c>
       <c r="H177" t="n">
         <v>19399</v>
@@ -5531,7 +5531,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G178" t="n">
-        <v>1.15183162689209</v>
+        <v>1.15183174610138</v>
       </c>
       <c r="H178" t="n">
         <v>81424</v>
@@ -5560,7 +5560,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G179" t="n">
-        <v>1.12427127361298</v>
+        <v>1.12427115440369</v>
       </c>
       <c r="H179" t="n">
         <v>16527</v>
@@ -5589,7 +5589,7 @@
         <v>1.12399995326996</v>
       </c>
       <c r="G180" t="n">
-        <v>1.06820011138916</v>
+        <v>1.06820023059845</v>
       </c>
       <c r="H180" t="n">
         <v>18988</v>
@@ -5705,7 +5705,7 @@
         <v>1.14900004863739</v>
       </c>
       <c r="G184" t="n">
-        <v>1.09195923805237</v>
+        <v>1.09195911884308</v>
       </c>
       <c r="H184" t="n">
         <v>10097</v>
@@ -5734,7 +5734,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G185" t="n">
-        <v>1.08910810947418</v>
+        <v>1.08910799026489</v>
       </c>
       <c r="H185" t="n">
         <v>2769</v>
@@ -5879,7 +5879,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G190" t="n">
-        <v>1.00262546539307</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H190" t="n">
         <v>1609</v>
@@ -5937,7 +5937,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G192" t="n">
-        <v>0.987419903278351</v>
+        <v>0.987420082092285</v>
       </c>
       <c r="H192" t="n">
         <v>2600</v>
@@ -5995,7 +5995,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G194" t="n">
-        <v>0.996923565864563</v>
+        <v>0.996923446655273</v>
       </c>
       <c r="H194" t="n">
         <v>3572</v>
@@ -6053,7 +6053,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G196" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H196" t="n">
         <v>305</v>
@@ -6082,7 +6082,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G197" t="n">
-        <v>0.989320755004883</v>
+        <v>0.989320635795593</v>
       </c>
       <c r="H197" t="n">
         <v>16909</v>
@@ -6140,7 +6140,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G199" t="n">
-        <v>0.986469626426697</v>
+        <v>0.986469566822052</v>
       </c>
       <c r="H199" t="n">
         <v>1462</v>
@@ -6169,7 +6169,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G200" t="n">
-        <v>0.984568953514099</v>
+        <v>0.98456883430481</v>
       </c>
       <c r="H200" t="n">
         <v>1505</v>
@@ -6198,7 +6198,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>0.988370299339294</v>
+        <v>0.988370358943939</v>
       </c>
       <c r="H201" t="n">
         <v>500</v>
@@ -6227,7 +6227,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G202" t="n">
-        <v>0.963661134243011</v>
+        <v>0.963661193847656</v>
       </c>
       <c r="H202" t="n">
         <v>4000</v>
@@ -6256,7 +6256,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G203" t="n">
-        <v>0.984568953514099</v>
+        <v>0.98456883430481</v>
       </c>
       <c r="H203" t="n">
         <v>10950</v>
@@ -6372,7 +6372,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G207" t="n">
-        <v>0.987419903278351</v>
+        <v>0.987420082092285</v>
       </c>
       <c r="H207" t="n">
         <v>9988</v>
@@ -6401,7 +6401,7 @@
         <v>1.02699995040894</v>
       </c>
       <c r="G208" t="n">
-        <v>0.976015567779541</v>
+        <v>0.976015627384186</v>
       </c>
       <c r="H208" t="n">
         <v>10816</v>
@@ -6430,7 +6430,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G209" t="n">
-        <v>1.00357592105865</v>
+        <v>1.00357604026794</v>
       </c>
       <c r="H209" t="n">
         <v>13457</v>
@@ -6488,7 +6488,7 @@
         <v>1.02699995040894</v>
       </c>
       <c r="G211" t="n">
-        <v>0.976015567779541</v>
+        <v>0.976015627384186</v>
       </c>
       <c r="H211" t="n">
         <v>5254</v>
@@ -6517,7 +6517,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G212" t="n">
-        <v>0.973164737224579</v>
+        <v>0.973164677619934</v>
       </c>
       <c r="H212" t="n">
         <v>900</v>
@@ -6546,7 +6546,7 @@
         <v>1.01900005340576</v>
       </c>
       <c r="G213" t="n">
-        <v>0.96841287612915</v>
+        <v>0.968412935733795</v>
       </c>
       <c r="H213" t="n">
         <v>1800</v>
@@ -6575,7 +6575,7 @@
         <v>1.01900005340576</v>
       </c>
       <c r="G214" t="n">
-        <v>0.96841287612915</v>
+        <v>0.968412935733795</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H215" t="n">
         <v>2077</v>
@@ -6633,7 +6633,7 @@
         <v>1.01900005340576</v>
       </c>
       <c r="G216" t="n">
-        <v>0.96841287612915</v>
+        <v>0.968412935733795</v>
       </c>
       <c r="H216" t="n">
         <v>9286</v>
@@ -6662,7 +6662,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G217" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H217" t="n">
         <v>480</v>
@@ -6836,7 +6836,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G223" t="n">
-        <v>0.973164737224579</v>
+        <v>0.973164677619934</v>
       </c>
       <c r="H223" t="n">
         <v>5403</v>
@@ -6865,7 +6865,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638471126556</v>
       </c>
       <c r="H224" t="n">
         <v>16296</v>
@@ -6894,7 +6894,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G225" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H225" t="n">
         <v>27306</v>
@@ -6981,7 +6981,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H228" t="n">
         <v>2724</v>
@@ -7010,7 +7010,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H229" t="n">
         <v>11827</v>
@@ -7039,7 +7039,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G230" t="n">
-        <v>0.984568953514099</v>
+        <v>0.98456883430481</v>
       </c>
       <c r="H230" t="n">
         <v>302145</v>
@@ -7068,7 +7068,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G231" t="n">
-        <v>0.984568953514099</v>
+        <v>0.98456883430481</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G234" t="n">
-        <v>0.957959055900574</v>
+        <v>0.957958936691284</v>
       </c>
       <c r="H234" t="n">
         <v>2310</v>
@@ -7184,7 +7184,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G235" t="n">
-        <v>0.989320755004883</v>
+        <v>0.989320635795593</v>
       </c>
       <c r="H235" t="n">
         <v>10528</v>
@@ -7213,7 +7213,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G236" t="n">
-        <v>0.973164737224579</v>
+        <v>0.973164677619934</v>
       </c>
       <c r="H236" t="n">
         <v>261</v>
@@ -7242,7 +7242,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G237" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7358,7 +7358,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G241" t="n">
-        <v>1.00357592105865</v>
+        <v>1.00357604026794</v>
       </c>
       <c r="H241" t="n">
         <v>19196</v>
@@ -7387,7 +7387,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G242" t="n">
-        <v>1.00262546539307</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H242" t="n">
         <v>340</v>
@@ -7474,7 +7474,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G245" t="n">
-        <v>0.975065350532532</v>
+        <v>0.975065410137177</v>
       </c>
       <c r="H245" t="n">
         <v>2093</v>
@@ -7503,7 +7503,7 @@
         <v>1.00100004673004</v>
       </c>
       <c r="G246" t="n">
-        <v>0.951306462287903</v>
+        <v>0.951306521892548</v>
       </c>
       <c r="H246" t="n">
         <v>37497</v>
@@ -7532,7 +7532,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G247" t="n">
-        <v>0.984568953514099</v>
+        <v>0.98456883430481</v>
       </c>
       <c r="H247" t="n">
         <v>11434</v>
@@ -7561,7 +7561,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G248" t="n">
-        <v>0.987419903278351</v>
+        <v>0.987420082092285</v>
       </c>
       <c r="H248" t="n">
         <v>20000</v>
@@ -7590,7 +7590,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G249" t="n">
-        <v>0.982668280601501</v>
+        <v>0.982668220996857</v>
       </c>
       <c r="H249" t="n">
         <v>204848</v>
@@ -7619,7 +7619,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G250" t="n">
-        <v>0.973164737224579</v>
+        <v>0.973164677619934</v>
       </c>
       <c r="H250" t="n">
         <v>51760</v>
@@ -7648,7 +7648,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G251" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H251" t="n">
         <v>36947</v>
@@ -7677,7 +7677,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G252" t="n">
-        <v>0.963661134243011</v>
+        <v>0.963661193847656</v>
       </c>
       <c r="H252" t="n">
         <v>13025</v>
@@ -7706,7 +7706,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G253" t="n">
-        <v>0.956058323383331</v>
+        <v>0.956058263778687</v>
       </c>
       <c r="H253" t="n">
         <v>4366</v>
@@ -7735,7 +7735,7 @@
         <v>1.00600004196167</v>
       </c>
       <c r="G254" t="n">
-        <v>0.956058323383331</v>
+        <v>0.956058263778687</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>1.13300001621246</v>
       </c>
       <c r="G255" t="n">
-        <v>1.07675361633301</v>
+        <v>1.07675349712372</v>
       </c>
       <c r="H255" t="n">
         <v>230084</v>
@@ -7822,7 +7822,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G257" t="n">
-        <v>0.989320755004883</v>
+        <v>0.989320635795593</v>
       </c>
       <c r="H257" t="n">
         <v>97577</v>
@@ -7851,7 +7851,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G258" t="n">
-        <v>0.9836186170578</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H258" t="n">
         <v>98439</v>
@@ -7880,7 +7880,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G259" t="n">
-        <v>0.984568953514099</v>
+        <v>0.98456883430481</v>
       </c>
       <c r="H259" t="n">
         <v>30635</v>
@@ -7909,7 +7909,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>0.988370299339294</v>
+        <v>0.988370358943939</v>
       </c>
       <c r="H260" t="n">
         <v>96748</v>
@@ -7938,7 +7938,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G261" t="n">
-        <v>1.04254066944122</v>
+        <v>1.04254055023193</v>
       </c>
       <c r="H261" t="n">
         <v>183087</v>
@@ -8141,7 +8141,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G268" t="n">
-        <v>1.33049857616425</v>
+        <v>1.33049845695496</v>
       </c>
       <c r="H268" t="n">
         <v>188065</v>
@@ -8199,7 +8199,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G270" t="n">
-        <v>1.30008709430695</v>
+        <v>1.30008721351624</v>
       </c>
       <c r="H270" t="n">
         <v>145039</v>
@@ -8402,7 +8402,7 @@
         <v>1.36099994182587</v>
       </c>
       <c r="G277" t="n">
-        <v>1.29343450069427</v>
+        <v>1.29343461990356</v>
       </c>
       <c r="H277" t="n">
         <v>76933</v>
@@ -8431,7 +8431,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G278" t="n">
-        <v>1.23546290397644</v>
+        <v>1.23546278476715</v>
       </c>
       <c r="H278" t="n">
         <v>119522</v>
@@ -8460,7 +8460,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G279" t="n">
-        <v>1.24496638774872</v>
+        <v>1.24496650695801</v>
       </c>
       <c r="H279" t="n">
         <v>21788</v>
@@ -8489,7 +8489,7 @@
         <v>1.31099998950958</v>
       </c>
       <c r="G280" t="n">
-        <v>1.24591684341431</v>
+        <v>1.2459169626236</v>
       </c>
       <c r="H280" t="n">
         <v>14708</v>
@@ -8518,7 +8518,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G281" t="n">
-        <v>1.2478175163269</v>
+        <v>1.24781763553619</v>
       </c>
       <c r="H281" t="n">
         <v>17255</v>
@@ -8576,7 +8576,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G283" t="n">
-        <v>1.17749106884003</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H283" t="n">
         <v>73831</v>
@@ -8605,7 +8605,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H284" t="n">
         <v>55023</v>
@@ -8634,7 +8634,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G285" t="n">
-        <v>1.13947701454163</v>
+        <v>1.13947689533234</v>
       </c>
       <c r="H285" t="n">
         <v>47058</v>
@@ -8721,7 +8721,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G288" t="n">
-        <v>1.12142026424408</v>
+        <v>1.12142014503479</v>
       </c>
       <c r="H288" t="n">
         <v>46988</v>
@@ -8750,7 +8750,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G289" t="n">
-        <v>1.09005832672119</v>
+        <v>1.09005844593048</v>
       </c>
       <c r="H289" t="n">
         <v>64492</v>
@@ -8808,7 +8808,7 @@
         <v>1.14100003242493</v>
       </c>
       <c r="G291" t="n">
-        <v>1.0843563079834</v>
+        <v>1.08435642719269</v>
       </c>
       <c r="H291" t="n">
         <v>36646</v>
@@ -8837,7 +8837,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>1.09766113758087</v>
+        <v>1.09766125679016</v>
       </c>
       <c r="H292" t="n">
         <v>16347</v>
@@ -8866,7 +8866,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G293" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H293" t="n">
         <v>4906</v>
@@ -9040,7 +9040,7 @@
         <v>1.30999994277954</v>
       </c>
       <c r="G299" t="n">
-        <v>1.24496638774872</v>
+        <v>1.24496650695801</v>
       </c>
       <c r="H299" t="n">
         <v>246224</v>
@@ -9069,7 +9069,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>1.20695221424103</v>
+        <v>1.20695233345032</v>
       </c>
       <c r="H300" t="n">
         <v>416286</v>
@@ -9272,7 +9272,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G307" t="n">
-        <v>1.15088129043579</v>
+        <v>1.1508811712265</v>
       </c>
       <c r="H307" t="n">
         <v>26808</v>
@@ -9301,7 +9301,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G308" t="n">
-        <v>1.15943455696106</v>
+        <v>1.15943443775177</v>
       </c>
       <c r="H308" t="n">
         <v>50763</v>
@@ -9330,7 +9330,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G309" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H309" t="n">
         <v>25871</v>
@@ -9359,7 +9359,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G310" t="n">
-        <v>1.13662588596344</v>
+        <v>1.13662576675415</v>
       </c>
       <c r="H310" t="n">
         <v>18377</v>
@@ -9388,7 +9388,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G311" t="n">
-        <v>1.15183162689209</v>
+        <v>1.15183174610138</v>
       </c>
       <c r="H311" t="n">
         <v>17084</v>
@@ -9446,7 +9446,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>1.14042747020721</v>
+        <v>1.14042735099792</v>
       </c>
       <c r="H313" t="n">
         <v>17880</v>
@@ -9533,7 +9533,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H316" t="n">
         <v>17705</v>
@@ -9562,7 +9562,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G317" t="n">
-        <v>1.12522161006927</v>
+        <v>1.12522172927856</v>
       </c>
       <c r="H317" t="n">
         <v>18494</v>
@@ -9591,7 +9591,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G318" t="n">
-        <v>1.12902295589447</v>
+        <v>1.12902307510376</v>
       </c>
       <c r="H318" t="n">
         <v>25882</v>
@@ -9620,7 +9620,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G319" t="n">
-        <v>1.13472521305084</v>
+        <v>1.13472509384155</v>
       </c>
       <c r="H319" t="n">
         <v>11278</v>
@@ -9852,7 +9852,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G327" t="n">
-        <v>1.13472521305084</v>
+        <v>1.13472509384155</v>
       </c>
       <c r="H327" t="n">
         <v>17355</v>
@@ -9881,7 +9881,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G328" t="n">
-        <v>1.12807285785675</v>
+        <v>1.12807273864746</v>
       </c>
       <c r="H328" t="n">
         <v>9540</v>
@@ -9910,7 +9910,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G329" t="n">
-        <v>1.12902295589447</v>
+        <v>1.12902307510376</v>
       </c>
       <c r="H329" t="n">
         <v>11046</v>
@@ -9939,7 +9939,7 @@
         <v>1.2059999704361</v>
       </c>
       <c r="G330" t="n">
-        <v>1.14612936973572</v>
+        <v>1.14612948894501</v>
       </c>
       <c r="H330" t="n">
         <v>19046</v>
@@ -9968,7 +9968,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G331" t="n">
-        <v>1.13472521305084</v>
+        <v>1.13472509384155</v>
       </c>
       <c r="H331" t="n">
         <v>38335</v>
@@ -10113,7 +10113,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G336" t="n">
-        <v>1.11666834354401</v>
+        <v>1.1166684627533</v>
       </c>
       <c r="H336" t="n">
         <v>13081</v>
@@ -10229,7 +10229,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>1.11286687850952</v>
+        <v>1.11286699771881</v>
       </c>
       <c r="H340" t="n">
         <v>7409</v>
@@ -10258,7 +10258,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G341" t="n">
-        <v>1.11856925487518</v>
+        <v>1.11856913566589</v>
       </c>
       <c r="H341" t="n">
         <v>13730</v>
@@ -10287,7 +10287,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G342" t="n">
-        <v>1.12142026424408</v>
+        <v>1.12142014503479</v>
       </c>
       <c r="H342" t="n">
         <v>14737</v>
@@ -10316,7 +10316,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G343" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H343" t="n">
         <v>13913</v>
@@ -10374,7 +10374,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G345" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H345" t="n">
         <v>6925</v>
@@ -10403,7 +10403,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G346" t="n">
-        <v>1.08910810947418</v>
+        <v>1.08910799026489</v>
       </c>
       <c r="H346" t="n">
         <v>14320</v>
@@ -10490,7 +10490,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G349" t="n">
-        <v>1.12522161006927</v>
+        <v>1.12522172927856</v>
       </c>
       <c r="H349" t="n">
         <v>11135</v>
@@ -10519,7 +10519,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G350" t="n">
-        <v>1.12142026424408</v>
+        <v>1.12142014503479</v>
       </c>
       <c r="H350" t="n">
         <v>2609</v>
@@ -10577,7 +10577,7 @@
         <v>1.13300001621246</v>
       </c>
       <c r="G352" t="n">
-        <v>1.07675361633301</v>
+        <v>1.07675349712372</v>
       </c>
       <c r="H352" t="n">
         <v>56977</v>
@@ -10693,7 +10693,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G356" t="n">
-        <v>1.09385991096497</v>
+        <v>1.09385979175568</v>
       </c>
       <c r="H356" t="n">
         <v>510</v>
@@ -10867,7 +10867,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G362" t="n">
-        <v>1.09956192970276</v>
+        <v>1.09956204891205</v>
       </c>
       <c r="H362" t="n">
         <v>393819</v>
@@ -10954,7 +10954,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G365" t="n">
-        <v>1.0796046257019</v>
+        <v>1.07960450649261</v>
       </c>
       <c r="H365" t="n">
         <v>33258</v>
@@ -11012,7 +11012,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G367" t="n">
-        <v>1.0501434803009</v>
+        <v>1.05014359951019</v>
       </c>
       <c r="H367" t="n">
         <v>43857</v>
@@ -11128,7 +11128,7 @@
         <v>1.10099995136261</v>
       </c>
       <c r="G371" t="n">
-        <v>1.04634213447571</v>
+        <v>1.04634189605713</v>
       </c>
       <c r="H371" t="n">
         <v>16691</v>
@@ -11157,7 +11157,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G372" t="n">
-        <v>1.05109369754791</v>
+        <v>1.05109393596649</v>
       </c>
       <c r="H372" t="n">
         <v>1157</v>
@@ -11186,7 +11186,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G373" t="n">
-        <v>1.05109369754791</v>
+        <v>1.05109393596649</v>
       </c>
       <c r="H373" t="n">
         <v>12141</v>
@@ -11215,7 +11215,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G374" t="n">
-        <v>1.09385991096497</v>
+        <v>1.09385979175568</v>
       </c>
       <c r="H374" t="n">
         <v>270010</v>
@@ -11244,7 +11244,7 @@
         <v>1.14900004863739</v>
       </c>
       <c r="G375" t="n">
-        <v>1.09195923805237</v>
+        <v>1.09195911884308</v>
       </c>
       <c r="H375" t="n">
         <v>91832</v>
@@ -11273,7 +11273,7 @@
         <v>1.14100003242493</v>
       </c>
       <c r="G376" t="n">
-        <v>1.0843563079834</v>
+        <v>1.08435642719269</v>
       </c>
       <c r="H376" t="n">
         <v>26349</v>
@@ -11331,7 +11331,7 @@
         <v>1.13300001621246</v>
       </c>
       <c r="G378" t="n">
-        <v>1.07675361633301</v>
+        <v>1.07675349712372</v>
       </c>
       <c r="H378" t="n">
         <v>8636</v>
@@ -11389,7 +11389,7 @@
         <v>1.14900004863739</v>
       </c>
       <c r="G380" t="n">
-        <v>1.09195923805237</v>
+        <v>1.09195911884308</v>
       </c>
       <c r="H380" t="n">
         <v>3130</v>
@@ -11447,7 +11447,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G382" t="n">
-        <v>1.09005832672119</v>
+        <v>1.09005844593048</v>
       </c>
       <c r="H382" t="n">
         <v>16300</v>
@@ -11505,7 +11505,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G384" t="n">
-        <v>1.09290957450867</v>
+        <v>1.09290933609009</v>
       </c>
       <c r="H384" t="n">
         <v>8937</v>
@@ -11563,7 +11563,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G386" t="n">
-        <v>1.12902295589447</v>
+        <v>1.12902307510376</v>
       </c>
       <c r="H386" t="n">
         <v>23772</v>
@@ -11592,7 +11592,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G387" t="n">
-        <v>1.11001598834991</v>
+        <v>1.11001586914062</v>
       </c>
       <c r="H387" t="n">
         <v>40810</v>
@@ -11621,7 +11621,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G388" t="n">
-        <v>1.14042747020721</v>
+        <v>1.14042735099792</v>
       </c>
       <c r="H388" t="n">
         <v>38769</v>
@@ -11650,7 +11650,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G389" t="n">
-        <v>1.13947701454163</v>
+        <v>1.13947689533234</v>
       </c>
       <c r="H389" t="n">
         <v>14550</v>
@@ -11679,7 +11679,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G390" t="n">
-        <v>1.13947701454163</v>
+        <v>1.13947689533234</v>
       </c>
       <c r="H390" t="n">
         <v>6972</v>
@@ -11766,7 +11766,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G393" t="n">
-        <v>1.14042747020721</v>
+        <v>1.14042735099792</v>
       </c>
       <c r="H393" t="n">
         <v>24599</v>
@@ -11795,7 +11795,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G394" t="n">
-        <v>1.12427127361298</v>
+        <v>1.12427115440369</v>
       </c>
       <c r="H394" t="n">
         <v>33424</v>
@@ -11853,7 +11853,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G396" t="n">
-        <v>1.14232802391052</v>
+        <v>1.14232790470123</v>
       </c>
       <c r="H396" t="n">
         <v>29872</v>
@@ -11882,7 +11882,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G397" t="n">
-        <v>1.1489804983139</v>
+        <v>1.14898061752319</v>
       </c>
       <c r="H397" t="n">
         <v>985</v>
@@ -11911,7 +11911,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G398" t="n">
-        <v>1.13947701454163</v>
+        <v>1.13947689533234</v>
       </c>
       <c r="H398" t="n">
         <v>13357</v>
@@ -11969,7 +11969,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G400" t="n">
-        <v>1.11856925487518</v>
+        <v>1.11856913566589</v>
       </c>
       <c r="H400" t="n">
         <v>8359</v>
@@ -11998,7 +11998,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>1.14042747020721</v>
+        <v>1.14042735099792</v>
       </c>
       <c r="H401" t="n">
         <v>11690</v>
@@ -12027,7 +12027,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G402" t="n">
-        <v>1.14042747020721</v>
+        <v>1.14042735099792</v>
       </c>
       <c r="H402" t="n">
         <v>13119</v>
@@ -12056,7 +12056,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G403" t="n">
-        <v>1.11856925487518</v>
+        <v>1.11856913566589</v>
       </c>
       <c r="H403" t="n">
         <v>15262</v>
@@ -12085,7 +12085,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G404" t="n">
-        <v>1.10241305828094</v>
+        <v>1.10241317749023</v>
       </c>
       <c r="H404" t="n">
         <v>22250</v>
@@ -12230,7 +12230,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G409" t="n">
-        <v>1.11476767063141</v>
+        <v>1.1147677898407</v>
       </c>
       <c r="H409" t="n">
         <v>2481</v>
@@ -12259,7 +12259,7 @@
         <v>1.15299999713898</v>
       </c>
       <c r="G410" t="n">
-        <v>1.09576070308685</v>
+        <v>1.09576046466827</v>
       </c>
       <c r="H410" t="n">
         <v>2558</v>
@@ -12317,7 +12317,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G412" t="n">
-        <v>1.1195193529129</v>
+        <v>1.11951947212219</v>
       </c>
       <c r="H412" t="n">
         <v>16500</v>
@@ -12346,7 +12346,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G413" t="n">
-        <v>1.11381733417511</v>
+        <v>1.1138174533844</v>
       </c>
       <c r="H413" t="n">
         <v>2500</v>
@@ -12404,7 +12404,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G415" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H415" t="n">
         <v>1660</v>
@@ -12549,7 +12549,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G420" t="n">
-        <v>1.1195193529129</v>
+        <v>1.11951947212219</v>
       </c>
       <c r="H420" t="n">
         <v>29208</v>
@@ -12578,7 +12578,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G421" t="n">
-        <v>1.1489804983139</v>
+        <v>1.14898061752319</v>
       </c>
       <c r="H421" t="n">
         <v>132162</v>
@@ -12665,7 +12665,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G424" t="n">
-        <v>1.16133499145508</v>
+        <v>1.16133511066437</v>
       </c>
       <c r="H424" t="n">
         <v>64353</v>
@@ -12694,7 +12694,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H425" t="n">
         <v>23167</v>
@@ -12781,7 +12781,7 @@
         <v>1.18799996376038</v>
       </c>
       <c r="G428" t="n">
-        <v>1.12902295589447</v>
+        <v>1.12902307510376</v>
       </c>
       <c r="H428" t="n">
         <v>33132</v>
@@ -12810,7 +12810,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G429" t="n">
-        <v>1.12427127361298</v>
+        <v>1.12427115440369</v>
       </c>
       <c r="H429" t="n">
         <v>17930</v>
@@ -12868,7 +12868,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G431" t="n">
-        <v>1.13472521305084</v>
+        <v>1.13472509384155</v>
       </c>
       <c r="H431" t="n">
         <v>4925</v>
@@ -12955,7 +12955,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G434" t="n">
-        <v>1.12142026424408</v>
+        <v>1.12142014503479</v>
       </c>
       <c r="H434" t="n">
         <v>31340</v>
@@ -12984,7 +12984,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G435" t="n">
-        <v>1.12142026424408</v>
+        <v>1.12142014503479</v>
       </c>
       <c r="H435" t="n">
         <v>7381</v>
@@ -13013,7 +13013,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G436" t="n">
-        <v>1.11476767063141</v>
+        <v>1.1147677898407</v>
       </c>
       <c r="H436" t="n">
         <v>4639</v>
@@ -13042,7 +13042,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G437" t="n">
-        <v>1.12522161006927</v>
+        <v>1.12522172927856</v>
       </c>
       <c r="H437" t="n">
         <v>13177</v>
@@ -13071,7 +13071,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G438" t="n">
-        <v>1.12142026424408</v>
+        <v>1.12142014503479</v>
       </c>
       <c r="H438" t="n">
         <v>706</v>
@@ -13100,7 +13100,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>1.12522161006927</v>
+        <v>1.12522172927856</v>
       </c>
       <c r="H439" t="n">
         <v>55175</v>
@@ -13158,7 +13158,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G441" t="n">
-        <v>1.11286687850952</v>
+        <v>1.11286699771881</v>
       </c>
       <c r="H441" t="n">
         <v>9775</v>
@@ -13245,7 +13245,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G444" t="n">
-        <v>1.11001598834991</v>
+        <v>1.11001586914062</v>
       </c>
       <c r="H444" t="n">
         <v>1482</v>
@@ -13332,7 +13332,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G447" t="n">
-        <v>1.18604457378387</v>
+        <v>1.1860443353653</v>
       </c>
       <c r="H447" t="n">
         <v>202560</v>
@@ -13419,7 +13419,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G450" t="n">
-        <v>1.15088129043579</v>
+        <v>1.1508811712265</v>
       </c>
       <c r="H450" t="n">
         <v>8668</v>
@@ -13448,7 +13448,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G451" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H451" t="n">
         <v>11298</v>
@@ -13477,7 +13477,7 @@
         <v>1.28400003910065</v>
       </c>
       <c r="G452" t="n">
-        <v>1.22025740146637</v>
+        <v>1.22025728225708</v>
       </c>
       <c r="H452" t="n">
         <v>307038</v>
@@ -13535,7 +13535,7 @@
         <v>1.25</v>
       </c>
       <c r="G454" t="n">
-        <v>1.18794512748718</v>
+        <v>1.18794500827789</v>
       </c>
       <c r="H454" t="n">
         <v>39962</v>
@@ -13564,7 +13564,7 @@
         <v>1.22200000286102</v>
       </c>
       <c r="G455" t="n">
-        <v>1.16133499145508</v>
+        <v>1.16133511066437</v>
       </c>
       <c r="H455" t="n">
         <v>67397</v>
@@ -13651,7 +13651,7 @@
         <v>1.22099995613098</v>
       </c>
       <c r="G458" t="n">
-        <v>1.16038465499878</v>
+        <v>1.16038477420807</v>
       </c>
       <c r="H458" t="n">
         <v>21799</v>
@@ -13709,7 +13709,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G460" t="n">
-        <v>1.17749106884003</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H460" t="n">
         <v>19410</v>
@@ -13767,7 +13767,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H462" t="n">
         <v>20101</v>
@@ -13796,7 +13796,7 @@
         <v>1.22099995613098</v>
       </c>
       <c r="G463" t="n">
-        <v>1.16038465499878</v>
+        <v>1.16038477420807</v>
       </c>
       <c r="H463" t="n">
         <v>22236</v>
@@ -13854,7 +13854,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G465" t="n">
-        <v>1.17844152450562</v>
+        <v>1.1784416437149</v>
       </c>
       <c r="H465" t="n">
         <v>45904</v>
@@ -13883,7 +13883,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G466" t="n">
-        <v>1.15468263626099</v>
+        <v>1.15468275547028</v>
       </c>
       <c r="H466" t="n">
         <v>60422</v>
@@ -13912,7 +13912,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G467" t="n">
-        <v>1.15468263626099</v>
+        <v>1.15468275547028</v>
       </c>
       <c r="H467" t="n">
         <v>20882</v>
@@ -13970,7 +13970,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G469" t="n">
-        <v>1.17844152450562</v>
+        <v>1.1784416437149</v>
       </c>
       <c r="H469" t="n">
         <v>105071</v>
@@ -14057,7 +14057,7 @@
         <v>1.24800002574921</v>
       </c>
       <c r="G472" t="n">
-        <v>1.18604457378387</v>
+        <v>1.1860443353653</v>
       </c>
       <c r="H472" t="n">
         <v>66425</v>
@@ -14115,7 +14115,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>1.20695221424103</v>
+        <v>1.20695233345032</v>
       </c>
       <c r="H474" t="n">
         <v>221096</v>
@@ -14173,7 +14173,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G476" t="n">
-        <v>1.17749106884003</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H476" t="n">
         <v>127242</v>
@@ -14202,7 +14202,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H477" t="n">
         <v>41948</v>
@@ -14260,7 +14260,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G479" t="n">
-        <v>1.11476767063141</v>
+        <v>1.1147677898407</v>
       </c>
       <c r="H479" t="n">
         <v>37049</v>
@@ -14318,7 +14318,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G481" t="n">
-        <v>1.1195193529129</v>
+        <v>1.11951947212219</v>
       </c>
       <c r="H481" t="n">
         <v>25391</v>
@@ -14405,7 +14405,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G484" t="n">
-        <v>1.15563297271729</v>
+        <v>1.15563309192657</v>
       </c>
       <c r="H484" t="n">
         <v>10800</v>
@@ -14463,7 +14463,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G486" t="n">
-        <v>1.11381733417511</v>
+        <v>1.1138174533844</v>
       </c>
       <c r="H486" t="n">
         <v>6100</v>
@@ -14492,7 +14492,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G487" t="n">
-        <v>1.13472521305084</v>
+        <v>1.13472509384155</v>
       </c>
       <c r="H487" t="n">
         <v>27842</v>
@@ -14550,7 +14550,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G489" t="n">
-        <v>1.11856925487518</v>
+        <v>1.11856913566589</v>
       </c>
       <c r="H489" t="n">
         <v>10010</v>
@@ -14724,7 +14724,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G495" t="n">
-        <v>1.11476767063141</v>
+        <v>1.1147677898407</v>
       </c>
       <c r="H495" t="n">
         <v>2345</v>
@@ -14753,7 +14753,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G496" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H496" t="n">
         <v>2297</v>
@@ -14782,7 +14782,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G497" t="n">
-        <v>1.10241305828094</v>
+        <v>1.10241317749023</v>
       </c>
       <c r="H497" t="n">
         <v>13455</v>
@@ -14898,7 +14898,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G501" t="n">
-        <v>1.10241305828094</v>
+        <v>1.10241317749023</v>
       </c>
       <c r="H501" t="n">
         <v>2321</v>
@@ -14927,7 +14927,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G502" t="n">
-        <v>1.09481024742126</v>
+        <v>1.09481012821198</v>
       </c>
       <c r="H502" t="n">
         <v>4212</v>
@@ -14985,7 +14985,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G504" t="n">
-        <v>1.11856925487518</v>
+        <v>1.11856913566589</v>
       </c>
       <c r="H504" t="n">
         <v>15643</v>
@@ -15014,7 +15014,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G505" t="n">
-        <v>1.12142026424408</v>
+        <v>1.12142014503479</v>
       </c>
       <c r="H505" t="n">
         <v>4635</v>
@@ -15072,7 +15072,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G507" t="n">
-        <v>1.10051226615906</v>
+        <v>1.10051238536835</v>
       </c>
       <c r="H507" t="n">
         <v>2976</v>
@@ -15159,7 +15159,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G510" t="n">
-        <v>1.12427127361298</v>
+        <v>1.12427115440369</v>
       </c>
       <c r="H510" t="n">
         <v>3049</v>
@@ -15188,7 +15188,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G511" t="n">
-        <v>1.13187396526337</v>
+        <v>1.13187408447266</v>
       </c>
       <c r="H511" t="n">
         <v>3108</v>
@@ -15217,7 +15217,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G512" t="n">
-        <v>1.11666834354401</v>
+        <v>1.1166684627533</v>
       </c>
       <c r="H512" t="n">
         <v>19476</v>
@@ -15362,7 +15362,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G517" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H517" t="n">
         <v>37428</v>
@@ -15391,7 +15391,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G518" t="n">
-        <v>1.11666834354401</v>
+        <v>1.1166684627533</v>
       </c>
       <c r="H518" t="n">
         <v>40844</v>
@@ -15449,7 +15449,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G520" t="n">
-        <v>1.09766113758087</v>
+        <v>1.09766125679016</v>
       </c>
       <c r="H520" t="n">
         <v>20364</v>
@@ -15507,7 +15507,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G522" t="n">
-        <v>1.10241305828094</v>
+        <v>1.10241317749023</v>
       </c>
       <c r="H522" t="n">
         <v>11085</v>
@@ -15623,7 +15623,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G526" t="n">
-        <v>1.10241305828094</v>
+        <v>1.10241317749023</v>
       </c>
       <c r="H526" t="n">
         <v>8087</v>
@@ -15652,7 +15652,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G527" t="n">
-        <v>1.10241305828094</v>
+        <v>1.10241317749023</v>
       </c>
       <c r="H527" t="n">
         <v>10437</v>
@@ -15681,7 +15681,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G528" t="n">
-        <v>1.10241305828094</v>
+        <v>1.10241317749023</v>
       </c>
       <c r="H528" t="n">
         <v>20786</v>
@@ -15710,7 +15710,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G529" t="n">
-        <v>1.09290957450867</v>
+        <v>1.09290933609009</v>
       </c>
       <c r="H529" t="n">
         <v>9700</v>
@@ -15739,7 +15739,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G530" t="n">
-        <v>1.11666834354401</v>
+        <v>1.1166684627533</v>
       </c>
       <c r="H530" t="n">
         <v>32447</v>
@@ -15768,7 +15768,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G531" t="n">
-        <v>1.12142026424408</v>
+        <v>1.12142014503479</v>
       </c>
       <c r="H531" t="n">
         <v>8000</v>
@@ -15797,7 +15797,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G532" t="n">
-        <v>1.09290957450867</v>
+        <v>1.09290933609009</v>
       </c>
       <c r="H532" t="n">
         <v>3262</v>
@@ -15826,7 +15826,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G533" t="n">
-        <v>1.09290957450867</v>
+        <v>1.09290933609009</v>
       </c>
       <c r="H533" t="n">
         <v>18204</v>
@@ -15855,7 +15855,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G534" t="n">
-        <v>1.09290957450867</v>
+        <v>1.09290933609009</v>
       </c>
       <c r="H534" t="n">
         <v>10012</v>
@@ -15942,7 +15942,7 @@
         <v>1.125</v>
       </c>
       <c r="G537" t="n">
-        <v>1.06915068626404</v>
+        <v>1.06915056705475</v>
       </c>
       <c r="H537" t="n">
         <v>21910</v>
@@ -16029,7 +16029,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G540" t="n">
-        <v>1.07390224933624</v>
+        <v>1.07390236854553</v>
       </c>
       <c r="H540" t="n">
         <v>16999</v>
@@ -16087,7 +16087,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G542" t="n">
-        <v>1.07390224933624</v>
+        <v>1.07390236854553</v>
       </c>
       <c r="H542" t="n">
         <v>6521</v>
@@ -16116,7 +16116,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G543" t="n">
-        <v>1.0501434803009</v>
+        <v>1.05014359951019</v>
       </c>
       <c r="H543" t="n">
         <v>1293</v>
@@ -16174,7 +16174,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G545" t="n">
-        <v>1.07390224933624</v>
+        <v>1.07390236854553</v>
       </c>
       <c r="H545" t="n">
         <v>3680</v>
@@ -16203,7 +16203,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G546" t="n">
-        <v>1.07390224933624</v>
+        <v>1.07390236854553</v>
       </c>
       <c r="H546" t="n">
         <v>5525</v>
@@ -16232,7 +16232,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G547" t="n">
-        <v>1.07390224933624</v>
+        <v>1.07390236854553</v>
       </c>
       <c r="H547" t="n">
         <v>2500</v>
@@ -16319,7 +16319,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G550" t="n">
-        <v>1.04063999652863</v>
+        <v>1.04063987731934</v>
       </c>
       <c r="H550" t="n">
         <v>1925</v>
@@ -16493,7 +16493,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>1.03113651275635</v>
+        <v>1.03113639354706</v>
       </c>
       <c r="H556" t="n">
         <v>3690</v>
@@ -16667,7 +16667,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G562" t="n">
-        <v>1.04063999652863</v>
+        <v>1.04063987731934</v>
       </c>
       <c r="H562" t="n">
         <v>7020</v>
@@ -16725,7 +16725,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G564" t="n">
-        <v>1.04063999652863</v>
+        <v>1.04063987731934</v>
       </c>
       <c r="H564" t="n">
         <v>531</v>
@@ -16870,7 +16870,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G569" t="n">
-        <v>1.0501434803009</v>
+        <v>1.05014359951019</v>
       </c>
       <c r="H569" t="n">
         <v>6375</v>
@@ -16928,7 +16928,7 @@
         <v>1.125</v>
       </c>
       <c r="G571" t="n">
-        <v>1.06915068626404</v>
+        <v>1.06915056705475</v>
       </c>
       <c r="H571" t="n">
         <v>7222</v>
@@ -16986,7 +16986,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G573" t="n">
-        <v>1.03113651275635</v>
+        <v>1.03113639354706</v>
       </c>
       <c r="H573" t="n">
         <v>13912</v>
@@ -17102,7 +17102,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G577" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H577" t="n">
         <v>67253</v>
@@ -17305,7 +17305,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G584" t="n">
-        <v>1.07390224933624</v>
+        <v>1.07390236854553</v>
       </c>
       <c r="H584" t="n">
         <v>31167</v>
@@ -17421,7 +17421,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G588" t="n">
-        <v>1.04063999652863</v>
+        <v>1.04063987731934</v>
       </c>
       <c r="H588" t="n">
         <v>18593</v>
@@ -17479,7 +17479,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>1.03113651275635</v>
+        <v>1.03113639354706</v>
       </c>
       <c r="H590" t="n">
         <v>31548</v>
@@ -17508,7 +17508,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G591" t="n">
-        <v>1.0501434803009</v>
+        <v>1.05014359951019</v>
       </c>
       <c r="H591" t="n">
         <v>4775</v>
@@ -17537,7 +17537,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G592" t="n">
-        <v>1.0501434803009</v>
+        <v>1.05014359951019</v>
       </c>
       <c r="H592" t="n">
         <v>834</v>
@@ -17595,7 +17595,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>1.03113651275635</v>
+        <v>1.03113639354706</v>
       </c>
       <c r="H594" t="n">
         <v>8390</v>
@@ -17624,7 +17624,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G595" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638471126556</v>
       </c>
       <c r="H595" t="n">
         <v>4500</v>
@@ -17682,7 +17682,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G597" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638471126556</v>
       </c>
       <c r="H597" t="n">
         <v>17100</v>
@@ -17914,7 +17914,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G605" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638471126556</v>
       </c>
       <c r="H605" t="n">
         <v>4449</v>
@@ -17943,7 +17943,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G606" t="n">
-        <v>1.04063999652863</v>
+        <v>1.04063987731934</v>
       </c>
       <c r="H606" t="n">
         <v>5902</v>
@@ -18088,7 +18088,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G611" t="n">
-        <v>1.04063999652863</v>
+        <v>1.04063987731934</v>
       </c>
       <c r="H611" t="n">
         <v>11268</v>
@@ -18146,7 +18146,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H613" t="n">
         <v>16207</v>
@@ -18233,7 +18233,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G616" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H616" t="n">
         <v>10854</v>
@@ -18262,7 +18262,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G617" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H617" t="n">
         <v>22297</v>
@@ -18407,7 +18407,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G622" t="n">
-        <v>0.948455393314362</v>
+        <v>0.948455452919006</v>
       </c>
       <c r="H622" t="n">
         <v>10698</v>
@@ -18436,7 +18436,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H623" t="n">
         <v>2010</v>
@@ -18465,7 +18465,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18581,7 +18581,7 @@
         <v>0.995999991893768</v>
       </c>
       <c r="G628" t="n">
-        <v>0.946554720401764</v>
+        <v>0.946554660797119</v>
       </c>
       <c r="H628" t="n">
         <v>1972</v>
@@ -18639,7 +18639,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G630" t="n">
-        <v>0.948455393314362</v>
+        <v>0.948455452919006</v>
       </c>
       <c r="H630" t="n">
         <v>5204</v>
@@ -18755,7 +18755,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G634" t="n">
-        <v>0.933249711990356</v>
+        <v>0.933249652385712</v>
       </c>
       <c r="H634" t="n">
         <v>2877</v>
@@ -18784,7 +18784,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G635" t="n">
-        <v>0.933249711990356</v>
+        <v>0.933249652385712</v>
       </c>
       <c r="H635" t="n">
         <v>0</v>
@@ -18900,7 +18900,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G639" t="n">
-        <v>0.935150504112244</v>
+        <v>0.935150444507599</v>
       </c>
       <c r="H639" t="n">
         <v>12673</v>
@@ -18929,7 +18929,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G640" t="n">
-        <v>0.929448246955872</v>
+        <v>0.929448306560516</v>
       </c>
       <c r="H640" t="n">
         <v>7994</v>
@@ -18958,7 +18958,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G641" t="n">
-        <v>0.929448246955872</v>
+        <v>0.929448306560516</v>
       </c>
       <c r="H641" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G642" t="n">
-        <v>0.927547514438629</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H642" t="n">
         <v>957</v>
@@ -19045,7 +19045,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G644" t="n">
-        <v>0.938951790332794</v>
+        <v>0.938951849937439</v>
       </c>
       <c r="H644" t="n">
         <v>822</v>
@@ -19132,7 +19132,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G647" t="n">
-        <v>0.927547514438629</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H647" t="n">
         <v>767</v>
@@ -19161,7 +19161,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G648" t="n">
-        <v>0.927547514438629</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -19364,7 +19364,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G655" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H655" t="n">
         <v>4810</v>
@@ -19422,7 +19422,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G657" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H657" t="n">
         <v>2580</v>
@@ -19509,7 +19509,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G660" t="n">
-        <v>0.908540427684784</v>
+        <v>0.908540368080139</v>
       </c>
       <c r="H660" t="n">
         <v>1277</v>
@@ -19683,7 +19683,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G666" t="n">
-        <v>0.908540427684784</v>
+        <v>0.908540368080139</v>
       </c>
       <c r="H666" t="n">
         <v>9122</v>
@@ -19712,7 +19712,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G667" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H667" t="n">
         <v>3010</v>
@@ -19741,7 +19741,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G668" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H668" t="n">
         <v>1315</v>
@@ -19770,7 +19770,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G669" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H669" t="n">
         <v>0</v>
@@ -19799,7 +19799,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G670" t="n">
-        <v>0.899036824703217</v>
+        <v>0.899036884307861</v>
       </c>
       <c r="H670" t="n">
         <v>1010</v>
@@ -20089,7 +20089,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G680" t="n">
-        <v>0.883831202983856</v>
+        <v>0.883831143379211</v>
       </c>
       <c r="H680" t="n">
         <v>2527</v>
@@ -20147,7 +20147,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G682" t="n">
-        <v>0.866724729537964</v>
+        <v>0.866724789142609</v>
       </c>
       <c r="H682" t="n">
         <v>1730</v>
@@ -20205,7 +20205,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G684" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H684" t="n">
         <v>35108</v>
@@ -20234,7 +20234,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G685" t="n">
-        <v>0.935150504112244</v>
+        <v>0.935150444507599</v>
       </c>
       <c r="H685" t="n">
         <v>13058</v>
@@ -20379,7 +20379,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H690" t="n">
         <v>17802</v>
@@ -20495,7 +20495,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G694" t="n">
-        <v>0.929448246955872</v>
+        <v>0.929448306560516</v>
       </c>
       <c r="H694" t="n">
         <v>5765</v>
@@ -20669,7 +20669,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G700" t="n">
-        <v>0.929448246955872</v>
+        <v>0.929448306560516</v>
       </c>
       <c r="H700" t="n">
         <v>89315</v>
@@ -20785,7 +20785,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H704" t="n">
         <v>10874</v>
@@ -20814,7 +20814,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G705" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H705" t="n">
         <v>4170</v>
@@ -20843,7 +20843,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G706" t="n">
-        <v>0.864823997020721</v>
+        <v>0.864824056625366</v>
       </c>
       <c r="H706" t="n">
         <v>23727</v>
@@ -20872,7 +20872,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G707" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H707" t="n">
         <v>7325</v>
@@ -20930,7 +20930,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G709" t="n">
-        <v>0.840114831924438</v>
+        <v>0.840114712715149</v>
       </c>
       <c r="H709" t="n">
         <v>4372</v>
@@ -20988,7 +20988,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G711" t="n">
-        <v>0.828710496425629</v>
+        <v>0.828710436820984</v>
       </c>
       <c r="H711" t="n">
         <v>1614</v>
@@ -21104,7 +21104,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G715" t="n">
-        <v>0.821107625961304</v>
+        <v>0.821107685565948</v>
       </c>
       <c r="H715" t="n">
         <v>4186</v>
@@ -21191,7 +21191,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G718" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H718" t="n">
         <v>44205</v>
@@ -21278,7 +21278,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G721" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H721" t="n">
         <v>770</v>
@@ -21394,7 +21394,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G725" t="n">
-        <v>0.794497728347778</v>
+        <v>0.794497787952423</v>
       </c>
       <c r="H725" t="n">
         <v>1252</v>
@@ -21452,7 +21452,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G727" t="n">
-        <v>0.807802736759186</v>
+        <v>0.807802677154541</v>
       </c>
       <c r="H727" t="n">
         <v>699</v>
@@ -21510,7 +21510,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G729" t="n">
-        <v>0.807802736759186</v>
+        <v>0.807802677154541</v>
       </c>
       <c r="H729" t="n">
         <v>1837</v>
@@ -21568,7 +21568,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G731" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H731" t="n">
         <v>6117</v>
@@ -21597,7 +21597,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G732" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H732" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G740" t="n">
-        <v>0.784994184970856</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H740" t="n">
         <v>11723</v>
@@ -21858,7 +21858,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G741" t="n">
-        <v>0.784994184970856</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H741" t="n">
         <v>610</v>
@@ -21887,7 +21887,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G742" t="n">
-        <v>0.794497728347778</v>
+        <v>0.794497787952423</v>
       </c>
       <c r="H742" t="n">
         <v>5461</v>
@@ -22293,7 +22293,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G756" t="n">
-        <v>0.794497728347778</v>
+        <v>0.794497787952423</v>
       </c>
       <c r="H756" t="n">
         <v>3078</v>
@@ -22322,7 +22322,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G757" t="n">
-        <v>0.794497728347778</v>
+        <v>0.794497787952423</v>
       </c>
       <c r="H757" t="n">
         <v>2150</v>
@@ -22351,7 +22351,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G758" t="n">
-        <v>0.794497728347778</v>
+        <v>0.794497787952423</v>
       </c>
       <c r="H758" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G763" t="n">
-        <v>0.790696322917938</v>
+        <v>0.790696263313293</v>
       </c>
       <c r="H763" t="n">
         <v>2090</v>
@@ -22525,7 +22525,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G764" t="n">
-        <v>0.790696322917938</v>
+        <v>0.790696263313293</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -22554,7 +22554,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G765" t="n">
-        <v>0.790696322917938</v>
+        <v>0.790696263313293</v>
       </c>
       <c r="H765" t="n">
         <v>1516</v>
@@ -22583,7 +22583,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G766" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H766" t="n">
         <v>1790</v>
@@ -22641,7 +22641,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G768" t="n">
-        <v>0.784994184970856</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H768" t="n">
         <v>10514</v>
@@ -22670,7 +22670,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G769" t="n">
-        <v>0.794497728347778</v>
+        <v>0.794497787952423</v>
       </c>
       <c r="H769" t="n">
         <v>16652</v>
@@ -22699,7 +22699,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G770" t="n">
-        <v>0.794497728347778</v>
+        <v>0.794497787952423</v>
       </c>
       <c r="H770" t="n">
         <v>9656</v>
@@ -22728,7 +22728,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G771" t="n">
-        <v>0.790696322917938</v>
+        <v>0.790696263313293</v>
       </c>
       <c r="H771" t="n">
         <v>11010</v>
@@ -22757,7 +22757,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G772" t="n">
-        <v>0.794497728347778</v>
+        <v>0.794497787952423</v>
       </c>
       <c r="H772" t="n">
         <v>3569</v>
@@ -22786,7 +22786,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G773" t="n">
-        <v>0.794497728347778</v>
+        <v>0.794497787952423</v>
       </c>
       <c r="H773" t="n">
         <v>12</v>
@@ -22873,7 +22873,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G776" t="n">
-        <v>0.807802736759186</v>
+        <v>0.807802677154541</v>
       </c>
       <c r="H776" t="n">
         <v>24392</v>
@@ -23076,7 +23076,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G783" t="n">
-        <v>0.874327600002289</v>
+        <v>0.874327659606934</v>
       </c>
       <c r="H783" t="n">
         <v>8033</v>
@@ -23134,7 +23134,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G785" t="n">
-        <v>0.883831202983856</v>
+        <v>0.883831143379211</v>
       </c>
       <c r="H785" t="n">
         <v>9369</v>
@@ -23250,7 +23250,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G789" t="n">
-        <v>0.874327600002289</v>
+        <v>0.874327659606934</v>
       </c>
       <c r="H789" t="n">
         <v>7232</v>
@@ -23308,7 +23308,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G791" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H791" t="n">
         <v>46594</v>
@@ -23366,7 +23366,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G793" t="n">
-        <v>0.843916177749634</v>
+        <v>0.843916237354279</v>
       </c>
       <c r="H793" t="n">
         <v>4060</v>
@@ -23540,7 +23540,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G799" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H799" t="n">
         <v>38915</v>
@@ -23685,7 +23685,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G804" t="n">
-        <v>0.866724729537964</v>
+        <v>0.866724789142609</v>
       </c>
       <c r="H804" t="n">
         <v>682</v>
@@ -23714,7 +23714,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G805" t="n">
-        <v>0.876228272914886</v>
+        <v>0.876228332519531</v>
       </c>
       <c r="H805" t="n">
         <v>2557</v>
@@ -23917,7 +23917,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>0.853419780731201</v>
+        <v>0.853419721126556</v>
       </c>
       <c r="H812" t="n">
         <v>14750</v>
@@ -24004,7 +24004,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G815" t="n">
-        <v>0.864823997020721</v>
+        <v>0.864824056625366</v>
       </c>
       <c r="H815" t="n">
         <v>8465</v>
@@ -24062,7 +24062,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G817" t="n">
-        <v>0.864823997020721</v>
+        <v>0.864824056625366</v>
       </c>
       <c r="H817" t="n">
         <v>8692</v>
@@ -24207,7 +24207,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>0.843916177749634</v>
+        <v>0.843916237354279</v>
       </c>
       <c r="H822" t="n">
         <v>11961</v>
@@ -24236,7 +24236,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G823" t="n">
-        <v>0.847717702388763</v>
+        <v>0.847717642784119</v>
       </c>
       <c r="H823" t="n">
         <v>12285</v>
@@ -24265,7 +24265,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G824" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H824" t="n">
         <v>520</v>
@@ -24381,7 +24381,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G828" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H828" t="n">
         <v>10500</v>
@@ -24410,7 +24410,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G829" t="n">
-        <v>0.866724729537964</v>
+        <v>0.866724789142609</v>
       </c>
       <c r="H829" t="n">
         <v>22573</v>
@@ -24497,7 +24497,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G832" t="n">
-        <v>0.876228272914886</v>
+        <v>0.876228332519531</v>
       </c>
       <c r="H832" t="n">
         <v>10810</v>
@@ -24642,7 +24642,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G837" t="n">
-        <v>1.10241305828094</v>
+        <v>1.10241317749023</v>
       </c>
       <c r="H837" t="n">
         <v>521892</v>
@@ -24729,7 +24729,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G840" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H840" t="n">
         <v>199532</v>
@@ -24845,7 +24845,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G844" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H844" t="n">
         <v>6969</v>
@@ -24874,7 +24874,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G845" t="n">
-        <v>0.988370299339294</v>
+        <v>0.988370358943939</v>
       </c>
       <c r="H845" t="n">
         <v>40133</v>
@@ -24961,7 +24961,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G848" t="n">
-        <v>0.964611351490021</v>
+        <v>0.96461147069931</v>
       </c>
       <c r="H848" t="n">
         <v>8252</v>
@@ -25019,7 +25019,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G850" t="n">
-        <v>0.938951790332794</v>
+        <v>0.938951849937439</v>
       </c>
       <c r="H850" t="n">
         <v>45709</v>
@@ -25193,7 +25193,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G856" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H856" t="n">
         <v>23230</v>
@@ -25222,7 +25222,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G857" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H857" t="n">
         <v>20242</v>
@@ -25338,7 +25338,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G861" t="n">
-        <v>0.948455393314362</v>
+        <v>0.948455452919006</v>
       </c>
       <c r="H861" t="n">
         <v>21200</v>
@@ -25425,7 +25425,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G864" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H864" t="n">
         <v>58709</v>
@@ -25454,7 +25454,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G865" t="n">
-        <v>0.883831202983856</v>
+        <v>0.883831143379211</v>
       </c>
       <c r="H865" t="n">
         <v>12395</v>
@@ -25599,7 +25599,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G870" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H870" t="n">
         <v>11502</v>
@@ -25715,7 +25715,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G874" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H874" t="n">
         <v>1274</v>
@@ -25744,7 +25744,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G875" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H875" t="n">
         <v>2508</v>
@@ -25773,7 +25773,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G876" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H876" t="n">
         <v>2701</v>
@@ -25802,7 +25802,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G877" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H877" t="n">
         <v>5064</v>
@@ -25889,7 +25889,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G880" t="n">
-        <v>0.874327600002289</v>
+        <v>0.874327659606934</v>
       </c>
       <c r="H880" t="n">
         <v>27077</v>
@@ -26034,7 +26034,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G885" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H885" t="n">
         <v>18386</v>
@@ -26237,7 +26237,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G892" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H892" t="n">
         <v>13605</v>
@@ -26295,7 +26295,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G894" t="n">
-        <v>0.864823997020721</v>
+        <v>0.864824056625366</v>
       </c>
       <c r="H894" t="n">
         <v>10061</v>
@@ -26324,7 +26324,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G895" t="n">
-        <v>0.849618315696716</v>
+        <v>0.849618375301361</v>
       </c>
       <c r="H895" t="n">
         <v>1766</v>
@@ -26498,7 +26498,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G901" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H901" t="n">
         <v>6210</v>
@@ -26527,7 +26527,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G902" t="n">
-        <v>0.853419780731201</v>
+        <v>0.853419721126556</v>
       </c>
       <c r="H902" t="n">
         <v>2624</v>
@@ -26585,7 +26585,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>0.853419780731201</v>
+        <v>0.853419721126556</v>
       </c>
       <c r="H904" t="n">
         <v>1651</v>
@@ -26643,7 +26643,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G906" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H906" t="n">
         <v>10749</v>
@@ -26672,7 +26672,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>0.853419780731201</v>
+        <v>0.853419721126556</v>
       </c>
       <c r="H907" t="n">
         <v>10040</v>
@@ -26759,7 +26759,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G910" t="n">
-        <v>0.840114831924438</v>
+        <v>0.840114712715149</v>
       </c>
       <c r="H910" t="n">
         <v>5000</v>
@@ -26817,7 +26817,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G912" t="n">
-        <v>0.847717702388763</v>
+        <v>0.847717642784119</v>
       </c>
       <c r="H912" t="n">
         <v>3225</v>
@@ -26846,7 +26846,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G913" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H913" t="n">
         <v>29501</v>
@@ -26875,7 +26875,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G914" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H914" t="n">
         <v>4867</v>
@@ -26904,7 +26904,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G915" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H915" t="n">
         <v>201</v>
@@ -26933,7 +26933,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G916" t="n">
-        <v>0.849618315696716</v>
+        <v>0.849618375301361</v>
       </c>
       <c r="H916" t="n">
         <v>4611</v>
@@ -26962,7 +26962,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G917" t="n">
-        <v>0.849618315696716</v>
+        <v>0.849618375301361</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G918" t="n">
-        <v>0.849618315696716</v>
+        <v>0.849618375301361</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -27136,7 +27136,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G923" t="n">
-        <v>0.840114831924438</v>
+        <v>0.840114712715149</v>
       </c>
       <c r="H923" t="n">
         <v>99</v>
@@ -27194,7 +27194,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G925" t="n">
-        <v>0.883831202983856</v>
+        <v>0.883831143379211</v>
       </c>
       <c r="H925" t="n">
         <v>9196</v>
@@ -27223,7 +27223,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G926" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H926" t="n">
         <v>260416</v>
@@ -27252,7 +27252,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G927" t="n">
-        <v>0.908540427684784</v>
+        <v>0.908540368080139</v>
       </c>
       <c r="H927" t="n">
         <v>121461</v>
@@ -27426,7 +27426,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G933" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H933" t="n">
         <v>30540</v>
@@ -27484,7 +27484,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G935" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H935" t="n">
         <v>26262</v>
@@ -27571,7 +27571,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G938" t="n">
-        <v>0.927547514438629</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H938" t="n">
         <v>17014</v>
@@ -27629,7 +27629,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G940" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H940" t="n">
         <v>11547</v>
@@ -27658,7 +27658,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G941" t="n">
-        <v>0.927547514438629</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H941" t="n">
         <v>32693</v>
@@ -27687,7 +27687,7 @@
         <v>0.955999970436096</v>
       </c>
       <c r="G942" t="n">
-        <v>0.908540427684784</v>
+        <v>0.908540368080139</v>
       </c>
       <c r="H942" t="n">
         <v>40773</v>
@@ -27803,7 +27803,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>0.988370299339294</v>
+        <v>0.988370358943939</v>
       </c>
       <c r="H946" t="n">
         <v>175676</v>
@@ -27832,7 +27832,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G947" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H947" t="n">
         <v>76067</v>
@@ -27861,7 +27861,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G948" t="n">
-        <v>0.927547514438629</v>
+        <v>0.927547574043274</v>
       </c>
       <c r="H948" t="n">
         <v>21307</v>
@@ -28006,7 +28006,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G953" t="n">
-        <v>0.935150504112244</v>
+        <v>0.935150444507599</v>
       </c>
       <c r="H953" t="n">
         <v>4957</v>
@@ -28151,7 +28151,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G958" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H958" t="n">
         <v>15725</v>
@@ -28180,7 +28180,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G959" t="n">
-        <v>0.899036824703217</v>
+        <v>0.899036884307861</v>
       </c>
       <c r="H959" t="n">
         <v>31567</v>
@@ -28238,7 +28238,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G961" t="n">
-        <v>0.883831202983856</v>
+        <v>0.883831143379211</v>
       </c>
       <c r="H961" t="n">
         <v>17086</v>
@@ -28412,7 +28412,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G967" t="n">
-        <v>0.899036824703217</v>
+        <v>0.899036884307861</v>
       </c>
       <c r="H967" t="n">
         <v>19223</v>
@@ -28441,7 +28441,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G968" t="n">
-        <v>0.899036824703217</v>
+        <v>0.899036884307861</v>
       </c>
       <c r="H968" t="n">
         <v>2280</v>
@@ -28470,7 +28470,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G969" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H969" t="n">
         <v>16831</v>
@@ -28499,7 +28499,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G970" t="n">
-        <v>0.899036824703217</v>
+        <v>0.899036884307861</v>
       </c>
       <c r="H970" t="n">
         <v>9218</v>
@@ -28528,7 +28528,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G971" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H971" t="n">
         <v>3011</v>
@@ -28557,7 +28557,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G972" t="n">
-        <v>0.899036824703217</v>
+        <v>0.899036884307861</v>
       </c>
       <c r="H972" t="n">
         <v>680</v>
@@ -28644,7 +28644,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G975" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H975" t="n">
         <v>218368</v>
@@ -28673,7 +28673,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G976" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H976" t="n">
         <v>49086</v>
@@ -28731,7 +28731,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G978" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H978" t="n">
         <v>33171</v>
@@ -28760,7 +28760,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G979" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H979" t="n">
         <v>4965</v>
@@ -28934,7 +28934,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G985" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H985" t="n">
         <v>21774</v>
@@ -29079,7 +29079,7 @@
         <v>0.984000027179718</v>
       </c>
       <c r="G990" t="n">
-        <v>0.935150504112244</v>
+        <v>0.935150444507599</v>
       </c>
       <c r="H990" t="n">
         <v>13913</v>
@@ -29195,7 +29195,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G994" t="n">
-        <v>0.964611351490021</v>
+        <v>0.96461147069931</v>
       </c>
       <c r="H994" t="n">
         <v>2711</v>
@@ -29224,7 +29224,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G995" t="n">
-        <v>0.964611351490021</v>
+        <v>0.96461147069931</v>
       </c>
       <c r="H995" t="n">
         <v>16059</v>
@@ -29253,7 +29253,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G996" t="n">
-        <v>0.9836186170578</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H996" t="n">
         <v>106619</v>
@@ -29282,7 +29282,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G997" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H997" t="n">
         <v>4524</v>
@@ -29311,7 +29311,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G998" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H998" t="n">
         <v>19085</v>
@@ -29340,7 +29340,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G999" t="n">
-        <v>0.964611351490021</v>
+        <v>0.96461147069931</v>
       </c>
       <c r="H999" t="n">
         <v>93021</v>
@@ -29427,7 +29427,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.9836186170578</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H1002" t="n">
         <v>25401</v>
@@ -29514,7 +29514,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.0501434803009</v>
+        <v>1.05014359951019</v>
       </c>
       <c r="H1005" t="n">
         <v>59119</v>
@@ -29717,7 +29717,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.0501434803009</v>
+        <v>1.05014359951019</v>
       </c>
       <c r="H1012" t="n">
         <v>19076</v>
@@ -29775,7 +29775,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638471126556</v>
       </c>
       <c r="H1014" t="n">
         <v>4819</v>
@@ -29804,7 +29804,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.03113651275635</v>
+        <v>1.03113639354706</v>
       </c>
       <c r="H1015" t="n">
         <v>10656</v>
@@ -29833,7 +29833,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.03113651275635</v>
+        <v>1.03113639354706</v>
       </c>
       <c r="H1016" t="n">
         <v>37152</v>
@@ -29862,7 +29862,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.03113651275635</v>
+        <v>1.03113639354706</v>
       </c>
       <c r="H1017" t="n">
         <v>12949</v>
@@ -29949,7 +29949,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.00262546539307</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H1020" t="n">
         <v>12764</v>
@@ -30007,7 +30007,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.988370299339294</v>
+        <v>0.988370358943939</v>
       </c>
       <c r="H1022" t="n">
         <v>30056</v>
@@ -30036,7 +30036,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.9836186170578</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H1023" t="n">
         <v>17131</v>
@@ -30123,7 +30123,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H1026" t="n">
         <v>14290</v>
@@ -30210,7 +30210,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H1029" t="n">
         <v>91607</v>
@@ -30239,7 +30239,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1030" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H1030" t="n">
         <v>22283</v>
@@ -30268,7 +30268,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.00262546539307</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H1031" t="n">
         <v>372072</v>
@@ -30355,7 +30355,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>0.988370299339294</v>
+        <v>0.988370358943939</v>
       </c>
       <c r="H1034" t="n">
         <v>57336</v>
@@ -30500,7 +30500,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.00262546539307</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H1039" t="n">
         <v>32399</v>
@@ -30674,7 +30674,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.09766113758087</v>
+        <v>1.09766125679016</v>
       </c>
       <c r="H1045" t="n">
         <v>470152</v>
@@ -30703,7 +30703,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.07390224933624</v>
+        <v>1.07390236854553</v>
       </c>
       <c r="H1046" t="n">
         <v>138069</v>
@@ -30732,7 +30732,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.07390224933624</v>
+        <v>1.07390236854553</v>
       </c>
       <c r="H1047" t="n">
         <v>23538</v>
@@ -30761,7 +30761,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H1048" t="n">
         <v>82375</v>
@@ -30906,7 +30906,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.9836186170578</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H1053" t="n">
         <v>115588</v>
@@ -30993,7 +30993,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.978866755962372</v>
+        <v>0.978866696357727</v>
       </c>
       <c r="H1056" t="n">
         <v>34580</v>
@@ -31080,7 +31080,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.938951790332794</v>
+        <v>0.938951849937439</v>
       </c>
       <c r="H1059" t="n">
         <v>19870</v>
@@ -31196,7 +31196,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1063" t="n">
         <v>26146</v>
@@ -31254,7 +31254,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H1065" t="n">
         <v>8706</v>
@@ -31283,7 +31283,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1066" t="n">
-        <v>0.771689116954803</v>
+        <v>0.771689176559448</v>
       </c>
       <c r="H1066" t="n">
         <v>26733</v>
@@ -31341,7 +31341,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.807802736759186</v>
+        <v>0.807802677154541</v>
       </c>
       <c r="H1068" t="n">
         <v>2554</v>
@@ -31370,7 +31370,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.807802736759186</v>
+        <v>0.807802677154541</v>
       </c>
       <c r="H1069" t="n">
         <v>503</v>
@@ -31399,7 +31399,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.817306220531464</v>
+        <v>0.817306280136108</v>
       </c>
       <c r="H1070" t="n">
         <v>5000</v>
@@ -31486,7 +31486,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H1073" t="n">
         <v>22248</v>
@@ -31573,7 +31573,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1076" t="n">
-        <v>0.842015445232391</v>
+        <v>0.842015504837036</v>
       </c>
       <c r="H1076" t="n">
         <v>2628</v>
@@ -31602,7 +31602,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1077" t="n">
-        <v>0.840114831924438</v>
+        <v>0.840114712715149</v>
       </c>
       <c r="H1077" t="n">
         <v>7972</v>
@@ -31631,7 +31631,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1078" t="n">
-        <v>0.817306220531464</v>
+        <v>0.817306280136108</v>
       </c>
       <c r="H1078" t="n">
         <v>6753</v>
@@ -31718,7 +31718,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.840114831924438</v>
+        <v>0.840114712715149</v>
       </c>
       <c r="H1081" t="n">
         <v>12204</v>
@@ -31747,7 +31747,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1082" t="n">
-        <v>0.840114831924438</v>
+        <v>0.840114712715149</v>
       </c>
       <c r="H1082" t="n">
         <v>1150</v>
@@ -31834,7 +31834,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H1085" t="n">
         <v>17000</v>
@@ -31921,7 +31921,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.842015445232391</v>
+        <v>0.842015504837036</v>
       </c>
       <c r="H1088" t="n">
         <v>12131</v>
@@ -32066,7 +32066,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.807802736759186</v>
+        <v>0.807802677154541</v>
       </c>
       <c r="H1093" t="n">
         <v>5640</v>
@@ -32153,7 +32153,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.815405488014221</v>
+        <v>0.815405428409576</v>
       </c>
       <c r="H1096" t="n">
         <v>5889</v>
@@ -32182,7 +32182,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.815405488014221</v>
+        <v>0.815405428409576</v>
       </c>
       <c r="H1097" t="n">
         <v>0</v>
@@ -32211,7 +32211,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.817306220531464</v>
+        <v>0.817306280136108</v>
       </c>
       <c r="H1098" t="n">
         <v>612</v>
@@ -32240,7 +32240,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1099" t="n">
-        <v>0.817306220531464</v>
+        <v>0.817306280136108</v>
       </c>
       <c r="H1099" t="n">
         <v>22424</v>
@@ -32298,7 +32298,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.815405488014221</v>
+        <v>0.815405428409576</v>
       </c>
       <c r="H1101" t="n">
         <v>7786</v>
@@ -32327,7 +32327,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.807802736759186</v>
+        <v>0.807802677154541</v>
       </c>
       <c r="H1102" t="n">
         <v>16688</v>
@@ -32356,7 +32356,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.790696322917938</v>
+        <v>0.790696263313293</v>
       </c>
       <c r="H1103" t="n">
         <v>16565</v>
@@ -32385,7 +32385,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1104" t="n">
         <v>5636</v>
@@ -32414,7 +32414,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.815405488014221</v>
+        <v>0.815405428409576</v>
       </c>
       <c r="H1105" t="n">
         <v>20026</v>
@@ -32443,7 +32443,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.817306220531464</v>
+        <v>0.817306280136108</v>
       </c>
       <c r="H1106" t="n">
         <v>3660</v>
@@ -32472,7 +32472,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.821107625961304</v>
+        <v>0.821107685565948</v>
       </c>
       <c r="H1107" t="n">
         <v>8572</v>
@@ -32559,7 +32559,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.809703290462494</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1110" t="n">
         <v>73772</v>
@@ -32588,7 +32588,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H1111" t="n">
         <v>15870</v>
@@ -32675,7 +32675,7 @@
         <v>0.910000026226044</v>
       </c>
       <c r="G1114" t="n">
-        <v>0.864823997020721</v>
+        <v>0.864824056625366</v>
       </c>
       <c r="H1114" t="n">
         <v>485</v>
@@ -32907,7 +32907,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H1122" t="n">
         <v>28335</v>
@@ -32936,7 +32936,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H1123" t="n">
         <v>2596</v>
@@ -32965,7 +32965,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.849618315696716</v>
+        <v>0.849618375301361</v>
       </c>
       <c r="H1124" t="n">
         <v>8344</v>
@@ -32994,7 +32994,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.859121918678284</v>
+        <v>0.859121859073639</v>
       </c>
       <c r="H1125" t="n">
         <v>1772</v>
@@ -33023,7 +33023,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1126" t="n">
-        <v>0.842015445232391</v>
+        <v>0.842015504837036</v>
       </c>
       <c r="H1126" t="n">
         <v>646</v>
@@ -33052,7 +33052,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.842015445232391</v>
+        <v>0.842015504837036</v>
       </c>
       <c r="H1127" t="n">
         <v>3377</v>
@@ -33110,7 +33110,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.849618315696716</v>
+        <v>0.849618375301361</v>
       </c>
       <c r="H1129" t="n">
         <v>13547</v>
@@ -33139,7 +33139,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1130" t="n">
-        <v>0.843916177749634</v>
+        <v>0.843916237354279</v>
       </c>
       <c r="H1130" t="n">
         <v>1300</v>
@@ -33168,7 +33168,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H1131" t="n">
         <v>54987</v>
@@ -33197,7 +33197,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.849618315696716</v>
+        <v>0.849618375301361</v>
       </c>
       <c r="H1132" t="n">
         <v>15701</v>
@@ -33226,7 +33226,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1133" t="n">
-        <v>0.828710496425629</v>
+        <v>0.828710436820984</v>
       </c>
       <c r="H1133" t="n">
         <v>12</v>
@@ -33255,7 +33255,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.840114831924438</v>
+        <v>0.840114712715149</v>
       </c>
       <c r="H1134" t="n">
         <v>13934</v>
@@ -33284,7 +33284,7 @@
         <v>0.88400000333786</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.840114831924438</v>
+        <v>0.840114712715149</v>
       </c>
       <c r="H1135" t="n">
         <v>2707</v>
@@ -33545,7 +33545,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.828710496425629</v>
+        <v>0.828710436820984</v>
       </c>
       <c r="H1144" t="n">
         <v>3310</v>
@@ -33574,7 +33574,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.828710496425629</v>
+        <v>0.828710436820984</v>
       </c>
       <c r="H1145" t="n">
         <v>0</v>
@@ -33603,7 +33603,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.828710496425629</v>
+        <v>0.828710436820984</v>
       </c>
       <c r="H1146" t="n">
         <v>65</v>
@@ -33719,7 +33719,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.849618315696716</v>
+        <v>0.849618375301361</v>
       </c>
       <c r="H1150" t="n">
         <v>1598</v>
@@ -33864,7 +33864,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.824909031391144</v>
+        <v>0.824909090995789</v>
       </c>
       <c r="H1155" t="n">
         <v>805</v>
@@ -33893,7 +33893,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.824909031391144</v>
+        <v>0.824909090995789</v>
       </c>
       <c r="H1156" t="n">
         <v>52496</v>
@@ -33922,7 +33922,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1157" t="n">
         <v>1157</v>
@@ -33951,7 +33951,7 @@
         <v>0.864000022411346</v>
       </c>
       <c r="G1158" t="n">
-        <v>0.821107625961304</v>
+        <v>0.821107685565948</v>
       </c>
       <c r="H1158" t="n">
         <v>17399</v>
@@ -33980,7 +33980,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1159" t="n">
         <v>57439</v>
@@ -34096,7 +34096,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.807802736759186</v>
+        <v>0.807802677154541</v>
       </c>
       <c r="H1163" t="n">
         <v>6755</v>
@@ -34125,7 +34125,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1164" t="n">
         <v>154</v>
@@ -34299,7 +34299,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1170" t="n">
-        <v>0.790696322917938</v>
+        <v>0.790696263313293</v>
       </c>
       <c r="H1170" t="n">
         <v>3253</v>
@@ -34328,7 +34328,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.815405488014221</v>
+        <v>0.815405428409576</v>
       </c>
       <c r="H1171" t="n">
         <v>7751</v>
@@ -34357,7 +34357,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1172" t="n">
         <v>1500</v>
@@ -34386,7 +34386,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1173" t="n">
         <v>0</v>
@@ -34415,7 +34415,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1174" t="n">
         <v>0</v>
@@ -34444,7 +34444,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1175" t="n">
         <v>0</v>
@@ -34473,7 +34473,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.811604022979736</v>
+        <v>0.811604082584381</v>
       </c>
       <c r="H1176" t="n">
         <v>1005</v>
@@ -34502,7 +34502,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.811604022979736</v>
+        <v>0.811604082584381</v>
       </c>
       <c r="H1177" t="n">
         <v>0</v>
@@ -34531,7 +34531,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.784994184970856</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1178" t="n">
         <v>1540</v>
@@ -34560,7 +34560,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.784994184970856</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1179" t="n">
         <v>0</v>
@@ -34676,7 +34676,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.775490641593933</v>
+        <v>0.775490581989288</v>
       </c>
       <c r="H1183" t="n">
         <v>3161</v>
@@ -34792,7 +34792,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1187" t="n">
         <v>4602</v>
@@ -35053,7 +35053,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1196" t="n">
         <v>1048</v>
@@ -35082,7 +35082,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.794497728347778</v>
+        <v>0.794497787952423</v>
       </c>
       <c r="H1197" t="n">
         <v>14658</v>
@@ -35169,7 +35169,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1200" t="n">
         <v>4016</v>
@@ -35227,7 +35227,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.807802736759186</v>
+        <v>0.807802677154541</v>
       </c>
       <c r="H1202" t="n">
         <v>13459</v>
@@ -35256,7 +35256,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.807802736759186</v>
+        <v>0.807802677154541</v>
       </c>
       <c r="H1203" t="n">
         <v>5351</v>
@@ -35343,7 +35343,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.809703290462494</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1206" t="n">
         <v>1092</v>
@@ -35372,7 +35372,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.790696322917938</v>
+        <v>0.790696263313293</v>
       </c>
       <c r="H1207" t="n">
         <v>11405</v>
@@ -35575,7 +35575,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1214" t="n">
         <v>11574</v>
@@ -35604,7 +35604,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1215" t="n">
         <v>21716</v>
@@ -35633,7 +35633,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1216" t="n">
-        <v>0.771689116954803</v>
+        <v>0.771689176559448</v>
       </c>
       <c r="H1216" t="n">
         <v>7137</v>
@@ -35691,7 +35691,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1218" t="n">
         <v>13790</v>
@@ -35720,7 +35720,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1219" t="n">
         <v>12226</v>
@@ -35749,7 +35749,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.752682089805603</v>
+        <v>0.752682030200958</v>
       </c>
       <c r="H1220" t="n">
         <v>18729</v>
@@ -35778,7 +35778,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.752682089805603</v>
+        <v>0.752682030200958</v>
       </c>
       <c r="H1221" t="n">
         <v>5763</v>
@@ -35836,7 +35836,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1223" t="n">
         <v>29179</v>
@@ -35923,7 +35923,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.665249288082123</v>
+        <v>0.665249228477478</v>
       </c>
       <c r="H1226" t="n">
         <v>2220</v>
@@ -35952,7 +35952,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.693759918212891</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1227" t="n">
         <v>10514</v>
@@ -35981,7 +35981,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.69756144285202</v>
+        <v>0.697561383247375</v>
       </c>
       <c r="H1228" t="n">
         <v>3123</v>
@@ -36010,7 +36010,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.689958572387695</v>
+        <v>0.689958512783051</v>
       </c>
       <c r="H1229" t="n">
         <v>1200</v>
@@ -36039,7 +36039,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.69756144285202</v>
+        <v>0.697561383247375</v>
       </c>
       <c r="H1230" t="n">
         <v>2138</v>
@@ -36068,7 +36068,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.69756144285202</v>
+        <v>0.697561383247375</v>
       </c>
       <c r="H1231" t="n">
         <v>5454</v>
@@ -36155,7 +36155,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1234" t="n">
-        <v>0.705164194107056</v>
+        <v>0.7051642537117</v>
       </c>
       <c r="H1234" t="n">
         <v>4544</v>
@@ -36242,7 +36242,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.756483435630798</v>
+        <v>0.756483495235443</v>
       </c>
       <c r="H1237" t="n">
         <v>16304</v>
@@ -36300,7 +36300,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1239" t="n">
         <v>32699</v>
@@ -36329,7 +36329,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1240" t="n">
         <v>9919</v>
@@ -36387,7 +36387,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1242" t="n">
         <v>6749</v>
@@ -36445,7 +36445,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1244" t="n">
         <v>43971</v>
@@ -36474,7 +36474,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1245" t="n">
         <v>5112</v>
@@ -36503,7 +36503,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1246" t="n">
         <v>16700</v>
@@ -36590,7 +36590,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1249" t="n">
         <v>6774</v>
@@ -36764,7 +36764,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.756483435630798</v>
+        <v>0.756483495235443</v>
       </c>
       <c r="H1255" t="n">
         <v>8859</v>
@@ -36793,7 +36793,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1256" t="n">
         <v>2562</v>
@@ -36822,7 +36822,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.775490641593933</v>
+        <v>0.775490581989288</v>
       </c>
       <c r="H1257" t="n">
         <v>15595</v>
@@ -36851,7 +36851,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1258" t="n">
         <v>913</v>
@@ -36880,7 +36880,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1259" t="n">
         <v>25666</v>
@@ -36909,7 +36909,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1260" t="n">
         <v>38619</v>
@@ -36938,7 +36938,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1261" t="n">
         <v>1406</v>
@@ -36967,7 +36967,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1262" t="n">
-        <v>0.771689116954803</v>
+        <v>0.771689176559448</v>
       </c>
       <c r="H1262" t="n">
         <v>2127</v>
@@ -36996,7 +36996,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1263" t="n">
         <v>2463</v>
@@ -37025,7 +37025,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1264" t="n">
         <v>2413</v>
@@ -37054,7 +37054,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1265" t="n">
         <v>12191</v>
@@ -37083,7 +37083,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1266" t="n">
         <v>3759</v>
@@ -37112,7 +37112,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1267" t="n">
         <v>0</v>
@@ -37141,7 +37141,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1268" t="n">
         <v>9194</v>
@@ -37170,7 +37170,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1269" t="n">
         <v>14270</v>
@@ -37228,7 +37228,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1271" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1271" t="n">
         <v>11039</v>
@@ -37257,7 +37257,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.756483435630798</v>
+        <v>0.756483495235443</v>
       </c>
       <c r="H1272" t="n">
         <v>360</v>
@@ -37344,7 +37344,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1275" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1275" t="n">
         <v>27068</v>
@@ -37402,7 +37402,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1277" t="n">
         <v>7772</v>
@@ -37431,7 +37431,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.724171340465546</v>
+        <v>0.72417140007019</v>
       </c>
       <c r="H1278" t="n">
         <v>25501</v>
@@ -37460,7 +37460,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.735575616359711</v>
+        <v>0.735575556755066</v>
       </c>
       <c r="H1279" t="n">
         <v>6732</v>
@@ -37489,7 +37489,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.735575616359711</v>
+        <v>0.735575556755066</v>
       </c>
       <c r="H1280" t="n">
         <v>48413</v>
@@ -37518,7 +37518,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.735575616359711</v>
+        <v>0.735575556755066</v>
       </c>
       <c r="H1281" t="n">
         <v>0</v>
@@ -37547,7 +37547,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.735575616359711</v>
+        <v>0.735575556755066</v>
       </c>
       <c r="H1282" t="n">
         <v>0</v>
@@ -37605,7 +37605,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.735575616359711</v>
+        <v>0.735575556755066</v>
       </c>
       <c r="H1284" t="n">
         <v>513</v>
@@ -37692,7 +37692,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.735575616359711</v>
+        <v>0.735575556755066</v>
       </c>
       <c r="H1287" t="n">
         <v>1796</v>
@@ -37895,7 +37895,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1294" t="n">
         <v>30046</v>
@@ -37924,7 +37924,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1295" t="n">
         <v>52781</v>
@@ -37982,7 +37982,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1297" t="n">
         <v>20882</v>
@@ -38040,7 +38040,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>0.809703290462494</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1299" t="n">
         <v>73720</v>
@@ -38069,7 +38069,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.809703290462494</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1300" t="n">
         <v>22782</v>
@@ -38098,7 +38098,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.807802736759186</v>
+        <v>0.807802677154541</v>
       </c>
       <c r="H1301" t="n">
         <v>5660</v>
@@ -38127,7 +38127,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.807802736759186</v>
+        <v>0.807802677154541</v>
       </c>
       <c r="H1302" t="n">
         <v>53740</v>
@@ -38185,7 +38185,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1304" t="n">
         <v>5839</v>
@@ -38214,7 +38214,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1305" t="n">
         <v>13544</v>
@@ -38243,7 +38243,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.809703290462494</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1306" t="n">
         <v>15675</v>
@@ -38330,7 +38330,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.790696322917938</v>
+        <v>0.790696263313293</v>
       </c>
       <c r="H1309" t="n">
         <v>16227</v>
@@ -38359,7 +38359,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1310" t="n">
         <v>77093</v>
@@ -38446,7 +38446,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1313" t="n">
-        <v>0.784994184970856</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1313" t="n">
         <v>16652</v>
@@ -38562,7 +38562,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1317" t="n">
         <v>10278</v>
@@ -38620,7 +38620,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1319" t="n">
-        <v>0.752682089805603</v>
+        <v>0.752682030200958</v>
       </c>
       <c r="H1319" t="n">
         <v>44851</v>
@@ -38707,7 +38707,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1322" t="n">
         <v>6424</v>
@@ -38736,7 +38736,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1323" t="n">
         <v>7011</v>
@@ -38794,7 +38794,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1325" t="n">
         <v>21172</v>
@@ -38823,7 +38823,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1326" t="n">
         <v>4013</v>
@@ -38852,7 +38852,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1327" t="n">
         <v>2313</v>
@@ -38939,7 +38939,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1330" t="n">
         <v>9538</v>
@@ -38968,7 +38968,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1331" t="n">
         <v>69317</v>
@@ -39084,7 +39084,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1335" t="n">
         <v>38397</v>
@@ -39113,7 +39113,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1336" t="n">
         <v>31378</v>
@@ -39142,7 +39142,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.775490641593933</v>
+        <v>0.775490581989288</v>
       </c>
       <c r="H1337" t="n">
         <v>36262</v>
@@ -39345,7 +39345,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1344" t="n">
         <v>16127</v>
@@ -39403,7 +39403,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1346" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1346" t="n">
         <v>6014</v>
@@ -39432,7 +39432,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1347" t="n">
-        <v>0.737476408481598</v>
+        <v>0.737476348876953</v>
       </c>
       <c r="H1347" t="n">
         <v>5814</v>
@@ -39461,7 +39461,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1348" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1348" t="n">
         <v>169972</v>
@@ -39490,7 +39490,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1349" t="n">
         <v>16898</v>
@@ -39519,7 +39519,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.756483435630798</v>
+        <v>0.756483495235443</v>
       </c>
       <c r="H1350" t="n">
         <v>30168</v>
@@ -39548,7 +39548,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1351" t="n">
         <v>38622</v>
@@ -39635,7 +39635,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.752682089805603</v>
+        <v>0.752682030200958</v>
       </c>
       <c r="H1354" t="n">
         <v>45133</v>
@@ -39693,7 +39693,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1356" t="n">
         <v>34806</v>
@@ -39751,7 +39751,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.746979892253876</v>
+        <v>0.746979951858521</v>
       </c>
       <c r="H1358" t="n">
         <v>5644</v>
@@ -39809,7 +39809,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1360" t="n">
-        <v>0.737476408481598</v>
+        <v>0.737476348876953</v>
       </c>
       <c r="H1360" t="n">
         <v>8724</v>
@@ -39867,7 +39867,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1362" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1362" t="n">
         <v>12523</v>
@@ -39925,7 +39925,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.746979892253876</v>
+        <v>0.746979951858521</v>
       </c>
       <c r="H1364" t="n">
         <v>15021</v>
@@ -39954,7 +39954,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1365" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1365" t="n">
         <v>15186</v>
@@ -39983,7 +39983,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1366" t="n">
         <v>7755</v>
@@ -40012,7 +40012,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1367" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1367" t="n">
         <v>22120</v>
@@ -40041,7 +40041,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.737476408481598</v>
+        <v>0.737476348876953</v>
       </c>
       <c r="H1368" t="n">
         <v>1053</v>
@@ -40070,7 +40070,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1369" t="n">
         <v>13174</v>
@@ -40157,7 +40157,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1372" t="n">
-        <v>0.737476408481598</v>
+        <v>0.737476348876953</v>
       </c>
       <c r="H1372" t="n">
         <v>19032</v>
@@ -40215,7 +40215,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1374" t="n">
         <v>9611</v>
@@ -40244,7 +40244,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.784994184970856</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1375" t="n">
         <v>119857</v>
@@ -40331,7 +40331,7 @@
         <v>0.851999998092651</v>
       </c>
       <c r="G1378" t="n">
-        <v>0.809703290462494</v>
+        <v>0.809703350067139</v>
       </c>
       <c r="H1378" t="n">
         <v>69721</v>
@@ -40360,7 +40360,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.807802736759186</v>
+        <v>0.807802677154541</v>
       </c>
       <c r="H1379" t="n">
         <v>70925</v>
@@ -40389,7 +40389,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1380" t="n">
         <v>85030</v>
@@ -40447,7 +40447,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.784994184970856</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1382" t="n">
         <v>47262</v>
@@ -40563,7 +40563,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1386" t="n">
-        <v>0.817306220531464</v>
+        <v>0.817306280136108</v>
       </c>
       <c r="H1386" t="n">
         <v>127054</v>
@@ -40592,7 +40592,7 @@
         <v>0.885999977588654</v>
       </c>
       <c r="G1387" t="n">
-        <v>0.842015445232391</v>
+        <v>0.842015504837036</v>
       </c>
       <c r="H1387" t="n">
         <v>396763</v>
@@ -40621,7 +40621,7 @@
         <v>0.860000014305115</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.817306220531464</v>
+        <v>0.817306280136108</v>
       </c>
       <c r="H1388" t="n">
         <v>68548</v>
@@ -40650,7 +40650,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1389" t="n">
         <v>86617</v>
@@ -40679,7 +40679,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1390" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1390" t="n">
         <v>44133</v>
@@ -40824,7 +40824,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.784994184970856</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1395" t="n">
         <v>26723</v>
@@ -40853,7 +40853,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G1396" t="n">
-        <v>0.794497728347778</v>
+        <v>0.794497787952423</v>
       </c>
       <c r="H1396" t="n">
         <v>29317</v>
@@ -40940,7 +40940,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.807802736759186</v>
+        <v>0.807802677154541</v>
       </c>
       <c r="H1399" t="n">
         <v>10008</v>
@@ -40998,7 +40998,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1401" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1401" t="n">
         <v>55616</v>
@@ -41027,7 +41027,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1402" t="n">
         <v>111019</v>
@@ -41085,7 +41085,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1404" t="n">
         <v>6420</v>
@@ -41172,7 +41172,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1407" t="n">
         <v>2400</v>
@@ -41259,7 +41259,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1410" t="n">
-        <v>0.735575616359711</v>
+        <v>0.735575556755066</v>
       </c>
       <c r="H1410" t="n">
         <v>45925</v>
@@ -41317,7 +41317,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1412" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1412" t="n">
         <v>53142</v>
@@ -41346,7 +41346,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1413" t="n">
-        <v>0.752682089805603</v>
+        <v>0.752682030200958</v>
       </c>
       <c r="H1413" t="n">
         <v>861</v>
@@ -41404,7 +41404,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1415" t="n">
         <v>5994</v>
@@ -41433,7 +41433,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.771689116954803</v>
+        <v>0.771689176559448</v>
       </c>
       <c r="H1416" t="n">
         <v>37771</v>
@@ -41462,7 +41462,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.752682089805603</v>
+        <v>0.752682030200958</v>
       </c>
       <c r="H1417" t="n">
         <v>6109</v>
@@ -41491,7 +41491,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.746979892253876</v>
+        <v>0.746979951858521</v>
       </c>
       <c r="H1418" t="n">
         <v>5839</v>
@@ -41578,7 +41578,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1421" t="n">
         <v>20129</v>
@@ -41636,7 +41636,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1423" t="n">
         <v>15016</v>
@@ -41810,7 +41810,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1429" t="n">
         <v>777</v>
@@ -41839,7 +41839,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1430" t="n">
         <v>0</v>
@@ -41897,7 +41897,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.756483435630798</v>
+        <v>0.756483495235443</v>
       </c>
       <c r="H1432" t="n">
         <v>4312</v>
@@ -41955,7 +41955,7 @@
         <v>0.779999971389771</v>
       </c>
       <c r="G1434" t="n">
-        <v>0.741277754306793</v>
+        <v>0.741277694702148</v>
       </c>
       <c r="H1434" t="n">
         <v>62963</v>
@@ -42013,7 +42013,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.746979892253876</v>
+        <v>0.746979951858521</v>
       </c>
       <c r="H1436" t="n">
         <v>53665</v>
@@ -42100,7 +42100,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887830734253</v>
       </c>
       <c r="H1439" t="n">
         <v>1167</v>
@@ -42129,7 +42129,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.756483435630798</v>
+        <v>0.756483495235443</v>
       </c>
       <c r="H1440" t="n">
         <v>11075</v>
@@ -42245,7 +42245,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.769788444042206</v>
+        <v>0.769788503646851</v>
       </c>
       <c r="H1444" t="n">
         <v>52488</v>
@@ -42274,7 +42274,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.775490641593933</v>
+        <v>0.775490581989288</v>
       </c>
       <c r="H1445" t="n">
         <v>16945</v>
@@ -42361,7 +42361,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.746979892253876</v>
+        <v>0.746979951858521</v>
       </c>
       <c r="H1448" t="n">
         <v>35514</v>
@@ -42390,7 +42390,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.756483435630798</v>
+        <v>0.756483495235443</v>
       </c>
       <c r="H1449" t="n">
         <v>6766</v>
@@ -42506,7 +42506,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1453" t="n">
         <v>21018</v>
@@ -42651,7 +42651,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.746979892253876</v>
+        <v>0.746979951858521</v>
       </c>
       <c r="H1458" t="n">
         <v>30564</v>
@@ -42738,7 +42738,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.756483435630798</v>
+        <v>0.756483495235443</v>
       </c>
       <c r="H1461" t="n">
         <v>1500</v>
@@ -42767,7 +42767,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.737476408481598</v>
+        <v>0.737476348876953</v>
       </c>
       <c r="H1462" t="n">
         <v>106579</v>
@@ -42970,7 +42970,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1469" t="n">
-        <v>0.737476408481598</v>
+        <v>0.737476348876953</v>
       </c>
       <c r="H1469" t="n">
         <v>19553</v>
@@ -43057,7 +43057,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1472" t="n">
-        <v>0.737476408481598</v>
+        <v>0.737476348876953</v>
       </c>
       <c r="H1472" t="n">
         <v>15367</v>
@@ -43144,7 +43144,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.735575616359711</v>
+        <v>0.735575556755066</v>
       </c>
       <c r="H1475" t="n">
         <v>1100</v>
@@ -43173,7 +43173,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.735575616359711</v>
+        <v>0.735575556755066</v>
       </c>
       <c r="H1476" t="n">
         <v>1113</v>
@@ -43202,7 +43202,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.735575616359711</v>
+        <v>0.735575556755066</v>
       </c>
       <c r="H1477" t="n">
         <v>11896</v>
@@ -43579,7 +43579,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1490" t="n">
-        <v>0.735575616359711</v>
+        <v>0.735575556755066</v>
       </c>
       <c r="H1490" t="n">
         <v>4543</v>
@@ -43695,7 +43695,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.724171340465546</v>
+        <v>0.72417140007019</v>
       </c>
       <c r="H1494" t="n">
         <v>5164</v>
@@ -43840,7 +43840,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1499" t="n">
-        <v>0.710866391658783</v>
+        <v>0.710866332054138</v>
       </c>
       <c r="H1499" t="n">
         <v>10051</v>
@@ -43869,7 +43869,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.708965659141541</v>
+        <v>0.708965599536896</v>
       </c>
       <c r="H1500" t="n">
         <v>36772</v>
@@ -43956,7 +43956,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1503" t="n">
-        <v>0.710866391658783</v>
+        <v>0.710866332054138</v>
       </c>
       <c r="H1503" t="n">
         <v>16164</v>
@@ -44014,7 +44014,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.705164194107056</v>
+        <v>0.7051642537117</v>
       </c>
       <c r="H1505" t="n">
         <v>10102</v>
@@ -44130,7 +44130,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1509" t="n">
-        <v>0.705164194107056</v>
+        <v>0.7051642537117</v>
       </c>
       <c r="H1509" t="n">
         <v>1101</v>
@@ -44159,7 +44159,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1510" t="n">
-        <v>0.689958572387695</v>
+        <v>0.689958512783051</v>
       </c>
       <c r="H1510" t="n">
         <v>1716</v>
@@ -44188,7 +44188,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1511" t="n">
-        <v>0.705164194107056</v>
+        <v>0.7051642537117</v>
       </c>
       <c r="H1511" t="n">
         <v>12243</v>
@@ -44217,7 +44217,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1512" t="n">
-        <v>0.705164194107056</v>
+        <v>0.7051642537117</v>
       </c>
       <c r="H1512" t="n">
         <v>1400</v>
@@ -44275,7 +44275,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1514" t="n">
-        <v>0.710866391658783</v>
+        <v>0.710866332054138</v>
       </c>
       <c r="H1514" t="n">
         <v>2519</v>
@@ -44333,7 +44333,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.708965659141541</v>
+        <v>0.708965599536896</v>
       </c>
       <c r="H1516" t="n">
         <v>28188</v>
@@ -44420,7 +44420,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.708965659141541</v>
+        <v>0.708965599536896</v>
       </c>
       <c r="H1519" t="n">
         <v>3267</v>
@@ -44449,7 +44449,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.708965659141541</v>
+        <v>0.708965599536896</v>
       </c>
       <c r="H1520" t="n">
         <v>0</v>
@@ -44478,7 +44478,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1521" t="n">
-        <v>0.710866391658783</v>
+        <v>0.710866332054138</v>
       </c>
       <c r="H1521" t="n">
         <v>4401</v>
@@ -44565,7 +44565,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.705164194107056</v>
+        <v>0.7051642537117</v>
       </c>
       <c r="H1524" t="n">
         <v>11569</v>
@@ -44594,7 +44594,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.699462056159973</v>
+        <v>0.699462115764618</v>
       </c>
       <c r="H1525" t="n">
         <v>7354</v>
@@ -44623,7 +44623,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1526" t="n">
-        <v>0.705164194107056</v>
+        <v>0.7051642537117</v>
       </c>
       <c r="H1526" t="n">
         <v>12617</v>
@@ -44681,7 +44681,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1528" t="n">
-        <v>0.705164194107056</v>
+        <v>0.7051642537117</v>
       </c>
       <c r="H1528" t="n">
         <v>13687</v>
@@ -44710,7 +44710,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.693759918212891</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1529" t="n">
         <v>31255</v>
@@ -44797,7 +44797,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.693759918212891</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1532" t="n">
         <v>2091</v>
@@ -44884,7 +44884,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1535" t="n">
-        <v>0.69756144285202</v>
+        <v>0.697561383247375</v>
       </c>
       <c r="H1535" t="n">
         <v>3000</v>
@@ -44913,7 +44913,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.69756144285202</v>
+        <v>0.697561383247375</v>
       </c>
       <c r="H1536" t="n">
         <v>2001</v>
@@ -44942,7 +44942,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.69756144285202</v>
+        <v>0.697561383247375</v>
       </c>
       <c r="H1537" t="n">
         <v>1094</v>
@@ -44971,7 +44971,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.693759918212891</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1538" t="n">
         <v>1647</v>
@@ -45000,7 +45000,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.693759918212891</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1539" t="n">
         <v>0</v>
@@ -45029,7 +45029,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.693759918212891</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1540" t="n">
         <v>18889</v>
@@ -45145,7 +45145,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1544" t="n">
-        <v>0.699462056159973</v>
+        <v>0.699462115764618</v>
       </c>
       <c r="H1544" t="n">
         <v>4722</v>
@@ -45174,7 +45174,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.689958572387695</v>
+        <v>0.689958512783051</v>
       </c>
       <c r="H1545" t="n">
         <v>4900</v>
@@ -45261,7 +45261,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.69756144285202</v>
+        <v>0.697561383247375</v>
       </c>
       <c r="H1548" t="n">
         <v>116</v>
@@ -45319,7 +45319,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.689958572387695</v>
+        <v>0.689958512783051</v>
       </c>
       <c r="H1550" t="n">
         <v>10800</v>
@@ -45348,7 +45348,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1551" t="n">
-        <v>0.68615710735321</v>
+        <v>0.686157047748566</v>
       </c>
       <c r="H1551" t="n">
         <v>16</v>
@@ -45406,7 +45406,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1553" t="n">
-        <v>0.680454969406128</v>
+        <v>0.680455029010773</v>
       </c>
       <c r="H1553" t="n">
         <v>21106</v>
@@ -45464,7 +45464,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1555" t="n">
-        <v>0.680454969406128</v>
+        <v>0.680455029010773</v>
       </c>
       <c r="H1555" t="n">
         <v>12414</v>
@@ -45493,7 +45493,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1556" t="n">
-        <v>0.680454969406128</v>
+        <v>0.680455029010773</v>
       </c>
       <c r="H1556" t="n">
         <v>6000</v>
@@ -45522,7 +45522,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.665249288082123</v>
+        <v>0.665249228477478</v>
       </c>
       <c r="H1557" t="n">
         <v>20167</v>
@@ -45638,7 +45638,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.708965659141541</v>
+        <v>0.708965599536896</v>
       </c>
       <c r="H1561" t="n">
         <v>42743</v>
@@ -45725,7 +45725,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.68615710735321</v>
+        <v>0.686157047748566</v>
       </c>
       <c r="H1564" t="n">
         <v>10278</v>
@@ -45754,7 +45754,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.665249288082123</v>
+        <v>0.665249228477478</v>
       </c>
       <c r="H1565" t="n">
         <v>39792</v>
@@ -45783,7 +45783,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.693759918212891</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1566" t="n">
         <v>7267</v>
@@ -45870,7 +45870,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1569" t="n">
-        <v>0.655745685100555</v>
+        <v>0.6557457447052</v>
       </c>
       <c r="H1569" t="n">
         <v>35484</v>
@@ -45899,7 +45899,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.657646417617798</v>
+        <v>0.657646358013153</v>
       </c>
       <c r="H1570" t="n">
         <v>16550</v>
@@ -45928,7 +45928,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1571" t="n">
-        <v>0.650043547153473</v>
+        <v>0.650043606758118</v>
       </c>
       <c r="H1571" t="n">
         <v>4462</v>
@@ -46044,7 +46044,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.61773145198822</v>
+        <v>0.617731392383575</v>
       </c>
       <c r="H1575" t="n">
         <v>26856</v>
@@ -46073,7 +46073,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.627234995365143</v>
+        <v>0.627235054969788</v>
       </c>
       <c r="H1576" t="n">
         <v>32785</v>
@@ -46218,7 +46218,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1581" t="n">
-        <v>0.657646417617798</v>
+        <v>0.657646358013153</v>
       </c>
       <c r="H1581" t="n">
         <v>43198</v>
@@ -46247,7 +46247,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1582" t="n">
-        <v>0.650043547153473</v>
+        <v>0.650043606758118</v>
       </c>
       <c r="H1582" t="n">
         <v>28095</v>
@@ -46276,7 +46276,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.650043547153473</v>
+        <v>0.650043606758118</v>
       </c>
       <c r="H1583" t="n">
         <v>8899</v>
@@ -46392,7 +46392,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.642440736293793</v>
+        <v>0.642440676689148</v>
       </c>
       <c r="H1587" t="n">
         <v>11421</v>
@@ -46479,7 +46479,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1590" t="n">
-        <v>0.650043547153473</v>
+        <v>0.650043606758118</v>
       </c>
       <c r="H1590" t="n">
         <v>9986</v>
@@ -46508,7 +46508,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1591" t="n">
-        <v>0.648142874240875</v>
+        <v>0.64814281463623</v>
       </c>
       <c r="H1591" t="n">
         <v>1075</v>
@@ -46537,7 +46537,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1592" t="n">
-        <v>0.648142874240875</v>
+        <v>0.64814281463623</v>
       </c>
       <c r="H1592" t="n">
         <v>5713</v>
@@ -46595,7 +46595,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.62913566827774</v>
+        <v>0.629135727882385</v>
       </c>
       <c r="H1594" t="n">
         <v>3425</v>
@@ -46624,7 +46624,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1595" t="n">
-        <v>0.638639211654663</v>
+        <v>0.638639271259308</v>
       </c>
       <c r="H1595" t="n">
         <v>22062</v>
@@ -46653,7 +46653,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.634837865829468</v>
+        <v>0.634837806224823</v>
       </c>
       <c r="H1596" t="n">
         <v>4647</v>
@@ -46682,7 +46682,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.634837865829468</v>
+        <v>0.634837806224823</v>
       </c>
       <c r="H1597" t="n">
         <v>1316</v>
@@ -46711,7 +46711,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.627234995365143</v>
+        <v>0.627235054969788</v>
       </c>
       <c r="H1598" t="n">
         <v>2717</v>
@@ -46740,7 +46740,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1599" t="n">
-        <v>0.627234995365143</v>
+        <v>0.627235054969788</v>
       </c>
       <c r="H1599" t="n">
         <v>0</v>
@@ -46885,7 +46885,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.634837865829468</v>
+        <v>0.634837806224823</v>
       </c>
       <c r="H1604" t="n">
         <v>1929</v>
@@ -46914,7 +46914,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.627234995365143</v>
+        <v>0.627235054969788</v>
       </c>
       <c r="H1605" t="n">
         <v>1703</v>
@@ -46943,7 +46943,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1606" t="n">
         <v>18179</v>
@@ -47030,7 +47030,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.62913566827774</v>
+        <v>0.629135727882385</v>
       </c>
       <c r="H1609" t="n">
         <v>900</v>
@@ -47117,7 +47117,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1612" t="n">
-        <v>0.62913566827774</v>
+        <v>0.629135727882385</v>
       </c>
       <c r="H1612" t="n">
         <v>1430</v>
@@ -47146,7 +47146,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.62913566827774</v>
+        <v>0.629135727882385</v>
       </c>
       <c r="H1613" t="n">
         <v>0</v>
@@ -47175,7 +47175,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.606327176094055</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1614" t="n">
         <v>5966</v>
@@ -47204,7 +47204,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.612029314041138</v>
+        <v>0.612029373645782</v>
       </c>
       <c r="H1615" t="n">
         <v>2932</v>
@@ -47349,7 +47349,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1620" t="n">
         <v>27183</v>
@@ -47378,7 +47378,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1621" t="n">
         <v>7627</v>
@@ -47407,7 +47407,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.61773145198822</v>
+        <v>0.617731392383575</v>
       </c>
       <c r="H1622" t="n">
         <v>14108</v>
@@ -47581,7 +47581,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1628" t="n">
-        <v>0.627234995365143</v>
+        <v>0.627235054969788</v>
       </c>
       <c r="H1628" t="n">
         <v>11217</v>
@@ -47610,7 +47610,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1629" t="n">
         <v>42986</v>
@@ -47697,7 +47697,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1632" t="n">
-        <v>0.62913566827774</v>
+        <v>0.629135727882385</v>
       </c>
       <c r="H1632" t="n">
         <v>1580</v>
@@ -47755,7 +47755,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.610128700733185</v>
+        <v>0.61012864112854</v>
       </c>
       <c r="H1634" t="n">
         <v>4677</v>
@@ -47784,7 +47784,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1635" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1635" t="n">
         <v>9129</v>
@@ -47813,7 +47813,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1636" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1636" t="n">
         <v>4863</v>
@@ -47842,7 +47842,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1637" t="n">
         <v>0</v>
@@ -47929,7 +47929,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.606327176094055</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1640" t="n">
         <v>23258</v>
@@ -47958,7 +47958,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1641" t="n">
-        <v>0.606327176094055</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1641" t="n">
         <v>0</v>
@@ -47987,7 +47987,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.606327176094055</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1642" t="n">
         <v>0</v>
@@ -48422,7 +48422,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.497986614704132</v>
+        <v>0.497986555099487</v>
       </c>
       <c r="H1657" t="n">
         <v>15248</v>
@@ -48480,7 +48480,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1659" t="n">
-        <v>0.494185149669647</v>
+        <v>0.49418517947197</v>
       </c>
       <c r="H1659" t="n">
         <v>111650</v>
@@ -48567,7 +48567,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.551206529140472</v>
+        <v>0.551206588745117</v>
       </c>
       <c r="H1662" t="n">
         <v>291</v>
@@ -48596,7 +48596,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.551206529140472</v>
+        <v>0.551206588745117</v>
       </c>
       <c r="H1663" t="n">
         <v>1863</v>
@@ -48654,7 +48654,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1665" t="n">
         <v>288</v>
@@ -48683,7 +48683,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1666" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1666" t="n">
         <v>15</v>
@@ -48712,7 +48712,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1667" t="n">
         <v>2000</v>
@@ -48770,7 +48770,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1669" t="n">
-        <v>0.610128700733185</v>
+        <v>0.61012864112854</v>
       </c>
       <c r="H1669" t="n">
         <v>3016</v>
@@ -48799,7 +48799,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1670" t="n">
-        <v>0.577816486358643</v>
+        <v>0.577816545963287</v>
       </c>
       <c r="H1670" t="n">
         <v>16540</v>
@@ -48886,7 +48886,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1673" t="n">
-        <v>0.577816486358643</v>
+        <v>0.577816545963287</v>
       </c>
       <c r="H1673" t="n">
         <v>8763</v>
@@ -48915,7 +48915,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1674" t="n">
         <v>5204</v>
@@ -48973,7 +48973,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1676" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1676" t="n">
         <v>13169</v>
@@ -49031,7 +49031,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1678" t="n">
-        <v>0.572114408016205</v>
+        <v>0.57211434841156</v>
       </c>
       <c r="H1678" t="n">
         <v>16692</v>
@@ -49060,7 +49060,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1679" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1679" t="n">
         <v>42257</v>
@@ -49089,7 +49089,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1680" t="n">
         <v>5826</v>
@@ -49147,7 +49147,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.612029314041138</v>
+        <v>0.612029373645782</v>
       </c>
       <c r="H1682" t="n">
         <v>9272</v>
@@ -49176,7 +49176,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.610128700733185</v>
+        <v>0.61012864112854</v>
       </c>
       <c r="H1683" t="n">
         <v>13294</v>
@@ -49205,7 +49205,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1684" t="n">
-        <v>0.593022286891937</v>
+        <v>0.593022167682648</v>
       </c>
       <c r="H1684" t="n">
         <v>17009</v>
@@ -49553,7 +49553,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.606327176094055</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1696" t="n">
         <v>1080</v>
@@ -49582,7 +49582,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.606327176094055</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1697" t="n">
         <v>0</v>
@@ -49698,7 +49698,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.606327176094055</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1701" t="n">
         <v>16</v>
@@ -49785,7 +49785,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1704" t="n">
-        <v>0.593022286891937</v>
+        <v>0.593022167682648</v>
       </c>
       <c r="H1704" t="n">
         <v>5848</v>
@@ -49814,7 +49814,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1705" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1705" t="n">
         <v>1462</v>
@@ -49843,7 +49843,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1706" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1706" t="n">
         <v>500</v>
@@ -49872,7 +49872,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1707" t="n">
         <v>2499</v>
@@ -49959,7 +49959,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1710" t="n">
-        <v>0.572114408016205</v>
+        <v>0.57211434841156</v>
       </c>
       <c r="H1710" t="n">
         <v>520</v>
@@ -50046,7 +50046,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1713" t="n">
-        <v>0.551206529140472</v>
+        <v>0.551206588745117</v>
       </c>
       <c r="H1713" t="n">
         <v>3975</v>
@@ -50104,7 +50104,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1715" t="n">
         <v>794</v>
@@ -50133,7 +50133,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1716" t="n">
-        <v>0.564511477947235</v>
+        <v>0.56451153755188</v>
       </c>
       <c r="H1716" t="n">
         <v>1532</v>
@@ -50220,7 +50220,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1719" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1719" t="n">
         <v>12381</v>
@@ -50249,7 +50249,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1720" t="n">
         <v>4551</v>
@@ -50278,7 +50278,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1721" t="n">
-        <v>0.577816486358643</v>
+        <v>0.577816545963287</v>
       </c>
       <c r="H1721" t="n">
         <v>8356</v>
@@ -50307,7 +50307,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1722" t="n">
-        <v>0.57971727848053</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1722" t="n">
         <v>4854</v>
@@ -50336,7 +50336,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1723" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1723" t="n">
         <v>16</v>
@@ -50365,7 +50365,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1724" t="n">
-        <v>0.593022286891937</v>
+        <v>0.593022167682648</v>
       </c>
       <c r="H1724" t="n">
         <v>3416</v>
@@ -50394,7 +50394,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.57971727848053</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1725" t="n">
         <v>7417</v>
@@ -50481,7 +50481,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.593022286891937</v>
+        <v>0.593022167682648</v>
       </c>
       <c r="H1728" t="n">
         <v>3098</v>
@@ -50510,7 +50510,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.593022286891937</v>
+        <v>0.593022167682648</v>
       </c>
       <c r="H1729" t="n">
         <v>5901</v>
@@ -50597,7 +50597,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.57971727848053</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1732" t="n">
         <v>3355</v>
@@ -50829,7 +50829,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1740" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1740" t="n">
         <v>3589</v>
@@ -50887,7 +50887,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.577816486358643</v>
+        <v>0.577816545963287</v>
       </c>
       <c r="H1742" t="n">
         <v>1984</v>
@@ -50916,7 +50916,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1743" t="n">
-        <v>0.575915813446045</v>
+        <v>0.57591587305069</v>
       </c>
       <c r="H1743" t="n">
         <v>1000</v>
@@ -50945,7 +50945,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1744" t="n">
         <v>500</v>
@@ -50974,7 +50974,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1745" t="n">
         <v>32626</v>
@@ -51003,7 +51003,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1746" t="n">
         <v>0</v>
@@ -51032,7 +51032,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.575915813446045</v>
+        <v>0.57591587305069</v>
       </c>
       <c r="H1747" t="n">
         <v>8200</v>
@@ -51061,7 +51061,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1748" t="n">
-        <v>0.564511477947235</v>
+        <v>0.56451153755188</v>
       </c>
       <c r="H1748" t="n">
         <v>300</v>
@@ -51148,7 +51148,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1751" t="n">
         <v>5540</v>
@@ -51177,7 +51177,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1752" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1752" t="n">
         <v>81</v>
@@ -51409,7 +51409,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1760" t="n">
-        <v>0.572114408016205</v>
+        <v>0.57211434841156</v>
       </c>
       <c r="H1760" t="n">
         <v>5263</v>
@@ -51438,7 +51438,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1761" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1761" t="n">
         <v>6016</v>
@@ -51496,7 +51496,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1763" t="n">
         <v>2731</v>
@@ -51525,7 +51525,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1764" t="n">
         <v>2755</v>
@@ -51583,7 +51583,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1766" t="n">
         <v>11513</v>
@@ -51641,7 +51641,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1768" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1768" t="n">
         <v>2208</v>
@@ -51815,7 +51815,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1774" t="n">
-        <v>0.593022286891937</v>
+        <v>0.593022167682648</v>
       </c>
       <c r="H1774" t="n">
         <v>5550</v>
@@ -51960,7 +51960,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1779" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1779" t="n">
         <v>26656</v>
@@ -51989,7 +51989,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.606327176094055</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1780" t="n">
         <v>20280</v>
@@ -52134,7 +52134,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1785" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1785" t="n">
         <v>15057</v>
@@ -52221,7 +52221,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1788" t="n">
-        <v>0.593022286891937</v>
+        <v>0.593022167682648</v>
       </c>
       <c r="H1788" t="n">
         <v>1723</v>
@@ -52337,7 +52337,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1792" t="n">
         <v>1109</v>
@@ -52424,7 +52424,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1795" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1795" t="n">
         <v>2534</v>
@@ -52453,7 +52453,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1796" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1796" t="n">
         <v>7774</v>
@@ -52685,7 +52685,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1804" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1804" t="n">
         <v>4098</v>
@@ -52714,7 +52714,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1805" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1805" t="n">
         <v>3602</v>
@@ -52743,7 +52743,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1806" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1806" t="n">
         <v>450</v>
@@ -52830,7 +52830,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.593022286891937</v>
+        <v>0.593022167682648</v>
       </c>
       <c r="H1809" t="n">
         <v>10097</v>
@@ -52859,7 +52859,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1810" t="n">
         <v>3351</v>
@@ -53062,7 +53062,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1817" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1817" t="n">
         <v>22549</v>
@@ -53091,7 +53091,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1818" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1818" t="n">
         <v>1892</v>
@@ -53120,7 +53120,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1819" t="n">
-        <v>0.572114408016205</v>
+        <v>0.57211434841156</v>
       </c>
       <c r="H1819" t="n">
         <v>1215</v>
@@ -53149,7 +53149,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1820" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1820" t="n">
         <v>7922</v>
@@ -53178,7 +53178,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1821" t="n">
-        <v>0.575915813446045</v>
+        <v>0.57591587305069</v>
       </c>
       <c r="H1821" t="n">
         <v>9490</v>
@@ -53207,7 +53207,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.577816486358643</v>
+        <v>0.577816545963287</v>
       </c>
       <c r="H1822" t="n">
         <v>2670</v>
@@ -53265,7 +53265,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1824" t="n">
         <v>2687</v>
@@ -53294,7 +53294,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1825" t="n">
-        <v>0.577816486358643</v>
+        <v>0.577816545963287</v>
       </c>
       <c r="H1825" t="n">
         <v>3608</v>
@@ -53323,7 +53323,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1826" t="n">
         <v>73878</v>
@@ -53352,7 +53352,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1827" t="n">
-        <v>0.57971727848053</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1827" t="n">
         <v>12465</v>
@@ -53381,7 +53381,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1828" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1828" t="n">
         <v>5044</v>
@@ -53410,7 +53410,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1829" t="n">
         <v>1562</v>
@@ -53468,7 +53468,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1831" t="n">
         <v>18113</v>
@@ -53497,7 +53497,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.575915813446045</v>
+        <v>0.57591587305069</v>
       </c>
       <c r="H1832" t="n">
         <v>2559</v>
@@ -53526,7 +53526,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1833" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1833" t="n">
         <v>26592</v>
@@ -53555,7 +53555,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1834" t="n">
         <v>661</v>
@@ -53584,7 +53584,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1835" t="n">
         <v>2647</v>
@@ -53642,7 +53642,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1837" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1837" t="n">
         <v>31108</v>
@@ -53729,7 +53729,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1840" t="n">
         <v>5059</v>
@@ -53758,7 +53758,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1841" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1841" t="n">
         <v>353</v>
@@ -53787,7 +53787,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1842" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1842" t="n">
         <v>9717</v>
@@ -53816,7 +53816,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1843" t="n">
         <v>1246</v>
@@ -53845,7 +53845,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1844" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1844" t="n">
         <v>3137</v>
@@ -53874,7 +53874,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.57971727848053</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1845" t="n">
         <v>4050</v>
@@ -53990,7 +53990,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1849" t="n">
         <v>17343</v>
@@ -54019,7 +54019,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1850" t="n">
         <v>7024</v>
@@ -54048,7 +54048,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1851" t="n">
         <v>7619</v>
@@ -54077,7 +54077,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1852" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1852" t="n">
         <v>667</v>
@@ -54193,7 +54193,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1856" t="n">
         <v>12642</v>
@@ -54222,7 +54222,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1857" t="n">
-        <v>0.572114408016205</v>
+        <v>0.57211434841156</v>
       </c>
       <c r="H1857" t="n">
         <v>3125</v>
@@ -54309,7 +54309,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1860" t="n">
-        <v>0.57971727848053</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1860" t="n">
         <v>4000</v>
@@ -54338,7 +54338,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1861" t="n">
-        <v>0.574015021324158</v>
+        <v>0.574015080928802</v>
       </c>
       <c r="H1861" t="n">
         <v>1513</v>
@@ -54367,7 +54367,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1862" t="n">
         <v>921</v>
@@ -54425,7 +54425,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1864" t="n">
-        <v>0.57971727848053</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1864" t="n">
         <v>2015</v>
@@ -54628,7 +54628,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1871" t="n">
-        <v>0.564511477947235</v>
+        <v>0.56451153755188</v>
       </c>
       <c r="H1871" t="n">
         <v>7114</v>
@@ -54657,7 +54657,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1872" t="n">
         <v>11785</v>
@@ -54773,7 +54773,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1876" t="n">
         <v>32101</v>
@@ -54831,7 +54831,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1878" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1878" t="n">
         <v>345</v>
@@ -54889,7 +54889,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1880" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1880" t="n">
         <v>18</v>
@@ -54918,7 +54918,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1881" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1881" t="n">
         <v>1</v>
@@ -54947,7 +54947,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1882" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1882" t="n">
         <v>3117</v>
@@ -55005,7 +55005,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1884" t="n">
         <v>12818</v>
@@ -55034,7 +55034,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1885" t="n">
         <v>10634</v>
@@ -55063,7 +55063,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1886" t="n">
         <v>7962</v>
@@ -55121,7 +55121,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1888" t="n">
         <v>1701</v>
@@ -55150,7 +55150,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1889" t="n">
         <v>0</v>
@@ -55208,7 +55208,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1891" t="n">
         <v>4328</v>
@@ -55237,7 +55237,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1892" t="n">
         <v>4045</v>
@@ -55266,7 +55266,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1893" t="n">
         <v>0</v>
@@ -55295,7 +55295,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1894" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1894" t="n">
         <v>500</v>
@@ -55324,7 +55324,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1895" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1895" t="n">
         <v>1600</v>
@@ -55353,7 +55353,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1896" t="n">
         <v>0</v>
@@ -55382,7 +55382,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1897" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1897" t="n">
         <v>3982</v>
@@ -55411,7 +55411,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1898" t="n">
-        <v>0.564511477947235</v>
+        <v>0.56451153755188</v>
       </c>
       <c r="H1898" t="n">
         <v>4260</v>
@@ -55498,7 +55498,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1901" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1901" t="n">
         <v>517</v>
@@ -55556,7 +55556,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1903" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1903" t="n">
         <v>8412</v>
@@ -55585,7 +55585,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1904" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1904" t="n">
         <v>2017</v>
@@ -55643,7 +55643,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1906" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1906" t="n">
         <v>1018</v>
@@ -55672,7 +55672,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1907" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1907" t="n">
         <v>0</v>
@@ -55701,7 +55701,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1908" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1908" t="n">
         <v>0</v>
@@ -55730,7 +55730,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1909" t="n">
         <v>1000</v>
@@ -55759,7 +55759,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1910" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1910" t="n">
         <v>3519</v>
@@ -55788,7 +55788,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1911" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1911" t="n">
         <v>10376</v>
@@ -55817,7 +55817,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1912" t="n">
-        <v>0.551206529140472</v>
+        <v>0.551206588745117</v>
       </c>
       <c r="H1912" t="n">
         <v>932</v>
@@ -55846,7 +55846,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1913" t="n">
-        <v>0.551206529140472</v>
+        <v>0.551206588745117</v>
       </c>
       <c r="H1913" t="n">
         <v>0</v>
@@ -55933,7 +55933,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1916" t="n">
-        <v>0.539802312850952</v>
+        <v>0.539802253246307</v>
       </c>
       <c r="H1916" t="n">
         <v>6504</v>
@@ -55991,7 +55991,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1918" t="n">
-        <v>0.539802312850952</v>
+        <v>0.539802253246307</v>
       </c>
       <c r="H1918" t="n">
         <v>10300</v>
@@ -56020,7 +56020,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1919" t="n">
-        <v>0.539802312850952</v>
+        <v>0.539802253246307</v>
       </c>
       <c r="H1919" t="n">
         <v>23641</v>
@@ -56078,7 +56078,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1921" t="n">
-        <v>0.551206529140472</v>
+        <v>0.551206588745117</v>
       </c>
       <c r="H1921" t="n">
         <v>3019</v>
@@ -56107,7 +56107,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1922" t="n">
-        <v>0.551206529140472</v>
+        <v>0.551206588745117</v>
       </c>
       <c r="H1922" t="n">
         <v>4387</v>
@@ -56165,7 +56165,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G1924" t="n">
-        <v>0.547405123710632</v>
+        <v>0.547405064105988</v>
       </c>
       <c r="H1924" t="n">
         <v>2872</v>
@@ -56194,7 +56194,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1925" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1925" t="n">
         <v>27392</v>
@@ -56223,7 +56223,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1926" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1926" t="n">
         <v>2000</v>
@@ -56252,7 +56252,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1927" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1927" t="n">
         <v>1725</v>
@@ -56281,7 +56281,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1928" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1928" t="n">
         <v>18560</v>
@@ -56310,7 +56310,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1929" t="n">
-        <v>0.589220762252808</v>
+        <v>0.589220821857452</v>
       </c>
       <c r="H1929" t="n">
         <v>64767</v>
@@ -56368,7 +56368,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1931" t="n">
-        <v>0.606327176094055</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1931" t="n">
         <v>5238</v>
@@ -56397,7 +56397,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1932" t="n">
-        <v>0.612029314041138</v>
+        <v>0.612029373645782</v>
       </c>
       <c r="H1932" t="n">
         <v>18087</v>
@@ -56426,7 +56426,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1933" t="n">
-        <v>0.593022286891937</v>
+        <v>0.593022167682648</v>
       </c>
       <c r="H1933" t="n">
         <v>8534</v>
@@ -56542,7 +56542,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1937" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1937" t="n">
         <v>4073</v>
@@ -56571,7 +56571,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1938" t="n">
-        <v>0.57971727848053</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1938" t="n">
         <v>3888</v>
@@ -56629,7 +56629,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1940" t="n">
-        <v>0.572114408016205</v>
+        <v>0.57211434841156</v>
       </c>
       <c r="H1940" t="n">
         <v>10044</v>
@@ -56658,7 +56658,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1941" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1941" t="n">
         <v>1989</v>
@@ -56687,7 +56687,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1942" t="n">
-        <v>0.572114408016205</v>
+        <v>0.57211434841156</v>
       </c>
       <c r="H1942" t="n">
         <v>1706</v>
@@ -56716,7 +56716,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1943" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1943" t="n">
         <v>8017</v>
@@ -56745,7 +56745,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1944" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1944" t="n">
         <v>0</v>
@@ -56774,7 +56774,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1945" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1945" t="n">
         <v>0</v>
@@ -56803,7 +56803,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1946" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1946" t="n">
         <v>11246</v>
@@ -56832,7 +56832,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1947" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1947" t="n">
         <v>525</v>
@@ -56861,7 +56861,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1948" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1948" t="n">
         <v>4089</v>
@@ -56919,7 +56919,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1950" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1950" t="n">
         <v>500</v>
@@ -56948,7 +56948,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1951" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1951" t="n">
         <v>8549</v>
@@ -57006,7 +57006,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1953" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1953" t="n">
         <v>2398</v>
@@ -57064,7 +57064,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1955" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1955" t="n">
         <v>1419</v>
@@ -57093,7 +57093,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1956" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1956" t="n">
         <v>4</v>
@@ -57122,7 +57122,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1957" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1957" t="n">
         <v>978</v>
@@ -57151,7 +57151,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1958" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1958" t="n">
         <v>817</v>
@@ -57180,7 +57180,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.570213735103607</v>
+        <v>0.570213675498962</v>
       </c>
       <c r="H1959" t="n">
         <v>52634</v>
@@ -57209,7 +57209,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1960" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1960" t="n">
         <v>15378</v>
@@ -57238,7 +57238,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G1961" t="n">
-        <v>0.564511477947235</v>
+        <v>0.56451153755188</v>
       </c>
       <c r="H1961" t="n">
         <v>5114</v>
@@ -57267,7 +57267,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1962" t="n">
-        <v>0.56071013212204</v>
+        <v>0.560710072517395</v>
       </c>
       <c r="H1962" t="n">
         <v>6069</v>
@@ -57296,7 +57296,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1963" t="n">
-        <v>0.551206529140472</v>
+        <v>0.551206588745117</v>
       </c>
       <c r="H1963" t="n">
         <v>7001</v>
@@ -57354,7 +57354,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1965" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1965" t="n">
         <v>7</v>
@@ -57383,7 +57383,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1966" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1966" t="n">
         <v>1200</v>
@@ -57470,7 +57470,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1969" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1969" t="n">
         <v>8365</v>
@@ -57499,7 +57499,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1970" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1970" t="n">
         <v>0</v>
@@ -57528,7 +57528,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1971" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1971" t="n">
         <v>4333</v>
@@ -57557,7 +57557,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1972" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1972" t="n">
         <v>1258</v>
@@ -57644,7 +57644,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1975" t="n">
-        <v>0.565447330474854</v>
+        <v>0.565447270870209</v>
       </c>
       <c r="H1975" t="n">
         <v>35084</v>
@@ -57702,7 +57702,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1977" t="n">
-        <v>0.58474588394165</v>
+        <v>0.584745824337006</v>
       </c>
       <c r="H1977" t="n">
         <v>68759</v>
@@ -57789,7 +57789,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1980" t="n">
-        <v>0.550008416175842</v>
+        <v>0.550008475780487</v>
       </c>
       <c r="H1980" t="n">
         <v>8925</v>
@@ -57963,7 +57963,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1986" t="n">
-        <v>0.521060705184937</v>
+        <v>0.521060645580292</v>
       </c>
       <c r="H1986" t="n">
         <v>44064</v>
@@ -58050,7 +58050,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1989" t="n">
-        <v>0.521060705184937</v>
+        <v>0.521060645580292</v>
       </c>
       <c r="H1989" t="n">
         <v>10515</v>
@@ -58137,7 +58137,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1992" t="n">
-        <v>0.522990524768829</v>
+        <v>0.522990465164185</v>
       </c>
       <c r="H1992" t="n">
         <v>2</v>
@@ -58195,7 +58195,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1994" t="n">
-        <v>0.521060705184937</v>
+        <v>0.521060645580292</v>
       </c>
       <c r="H1994" t="n">
         <v>1448</v>
@@ -58224,7 +58224,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1995" t="n">
-        <v>0.521060705184937</v>
+        <v>0.521060645580292</v>
       </c>
       <c r="H1995" t="n">
         <v>31063</v>
@@ -58253,7 +58253,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G1996" t="n">
-        <v>0.521060705184937</v>
+        <v>0.521060645580292</v>
       </c>
       <c r="H1996" t="n">
         <v>2633</v>
@@ -58311,7 +58311,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1998" t="n">
-        <v>0.522990524768829</v>
+        <v>0.522990465164185</v>
       </c>
       <c r="H1998" t="n">
         <v>3143</v>
@@ -58340,7 +58340,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1999" t="n">
-        <v>0.519130766391754</v>
+        <v>0.519130825996399</v>
       </c>
       <c r="H1999" t="n">
         <v>6157</v>
@@ -58369,7 +58369,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2000" t="n">
-        <v>0.524920344352722</v>
+        <v>0.524920403957367</v>
       </c>
       <c r="H2000" t="n">
         <v>19211</v>
@@ -58427,7 +58427,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2002" t="n">
-        <v>0.507551729679108</v>
+        <v>0.507551670074463</v>
       </c>
       <c r="H2002" t="n">
         <v>37821</v>
@@ -58572,7 +58572,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2007" t="n">
-        <v>0.524920344352722</v>
+        <v>0.524920403957367</v>
       </c>
       <c r="H2007" t="n">
         <v>8019</v>
@@ -58659,7 +58659,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G2010" t="n">
-        <v>0.503691971302032</v>
+        <v>0.503692030906677</v>
       </c>
       <c r="H2010" t="n">
         <v>2802</v>
@@ -58688,7 +58688,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2011" t="n">
-        <v>0.521060705184937</v>
+        <v>0.521060645580292</v>
       </c>
       <c r="H2011" t="n">
         <v>29644</v>
@@ -58717,7 +58717,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G2012" t="n">
-        <v>0.519130766391754</v>
+        <v>0.519130825996399</v>
       </c>
       <c r="H2012" t="n">
         <v>581</v>
@@ -59007,7 +59007,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G2022" t="n">
-        <v>0.503691971302032</v>
+        <v>0.503692030906677</v>
       </c>
       <c r="H2022" t="n">
         <v>2249</v>
@@ -59065,7 +59065,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2024" t="n">
-        <v>0.507551729679108</v>
+        <v>0.507551670074463</v>
       </c>
       <c r="H2024" t="n">
         <v>18265</v>
@@ -59268,7 +59268,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2031" t="n">
-        <v>0.495972573757172</v>
+        <v>0.495972543954849</v>
       </c>
       <c r="H2031" t="n">
         <v>4847</v>
@@ -59326,7 +59326,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2033" t="n">
-        <v>0.490183025598526</v>
+        <v>0.490182965993881</v>
       </c>
       <c r="H2033" t="n">
         <v>2502</v>
@@ -59471,7 +59471,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2038" t="n">
-        <v>0.488253116607666</v>
+        <v>0.488253146409988</v>
       </c>
       <c r="H2038" t="n">
         <v>1700</v>
@@ -59500,7 +59500,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2039" t="n">
-        <v>0.495972573757172</v>
+        <v>0.495972543954849</v>
       </c>
       <c r="H2039" t="n">
         <v>17700</v>
@@ -59645,7 +59645,7 @@
         <v>0.513999998569489</v>
       </c>
       <c r="G2044" t="n">
-        <v>0.495972573757172</v>
+        <v>0.495972543954849</v>
       </c>
       <c r="H2044" t="n">
         <v>12503</v>
@@ -59674,7 +59674,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2045" t="n">
-        <v>0.484393388032913</v>
+        <v>0.484393417835236</v>
       </c>
       <c r="H2045" t="n">
         <v>5704</v>
@@ -59732,7 +59732,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2047" t="n">
-        <v>0.490183025598526</v>
+        <v>0.490182965993881</v>
       </c>
       <c r="H2047" t="n">
         <v>1308</v>
@@ -59761,7 +59761,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2048" t="n">
-        <v>0.490183025598526</v>
+        <v>0.490182965993881</v>
       </c>
       <c r="H2048" t="n">
         <v>0</v>
@@ -60022,7 +60022,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2057" t="n">
-        <v>0.464129954576492</v>
+        <v>0.46412992477417</v>
       </c>
       <c r="H2057" t="n">
         <v>4024</v>
@@ -60573,7 +60573,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G2076" t="n">
-        <v>0.462200075387955</v>
+        <v>0.462200105190277</v>
       </c>
       <c r="H2076" t="n">
         <v>3818</v>
@@ -60718,7 +60718,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2081" t="n">
-        <v>0.443866491317749</v>
+        <v>0.443866461515427</v>
       </c>
       <c r="H2081" t="n">
         <v>160</v>
@@ -60805,7 +60805,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2084" t="n">
-        <v>0.434217214584351</v>
+        <v>0.434217184782028</v>
       </c>
       <c r="H2084" t="n">
         <v>18625</v>
@@ -60921,7 +60921,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2088" t="n">
-        <v>0.39465519785881</v>
+        <v>0.394655227661133</v>
       </c>
       <c r="H2088" t="n">
         <v>47151</v>
@@ -60950,7 +60950,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2089" t="n">
-        <v>0.401409685611725</v>
+        <v>0.401409715414047</v>
       </c>
       <c r="H2089" t="n">
         <v>15614</v>
@@ -61037,7 +61037,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2092" t="n">
-        <v>0.376321583986282</v>
+        <v>0.37632155418396</v>
       </c>
       <c r="H2092" t="n">
         <v>16216</v>
@@ -61298,7 +61298,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2101" t="n">
-        <v>0.378251403570175</v>
+        <v>0.378251433372498</v>
       </c>
       <c r="H2101" t="n">
         <v>31991</v>
@@ -61559,7 +61559,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2110" t="n">
-        <v>0.38018125295639</v>
+        <v>0.380181282758713</v>
       </c>
       <c r="H2110" t="n">
         <v>7881</v>
@@ -61646,7 +61646,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2113" t="n">
-        <v>0.376321583986282</v>
+        <v>0.37632155418396</v>
       </c>
       <c r="H2113" t="n">
         <v>8562</v>
@@ -61675,7 +61675,7 @@
         <v>0.368000000715256</v>
       </c>
       <c r="G2114" t="n">
-        <v>0.355093151330948</v>
+        <v>0.35509318113327</v>
       </c>
       <c r="H2114" t="n">
         <v>32113</v>
@@ -61762,7 +61762,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G2117" t="n">
-        <v>0.356058090925217</v>
+        <v>0.356058120727539</v>
       </c>
       <c r="H2117" t="n">
         <v>4033</v>
@@ -61849,7 +61849,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2120" t="n">
-        <v>0.373426795005798</v>
+        <v>0.373426765203476</v>
       </c>
       <c r="H2120" t="n">
         <v>13582</v>
@@ -61878,7 +61878,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2121" t="n">
-        <v>0.434217214584351</v>
+        <v>0.434217184782028</v>
       </c>
       <c r="H2121" t="n">
         <v>286699</v>
@@ -61936,7 +61936,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2123" t="n">
-        <v>0.416848510503769</v>
+        <v>0.416848540306091</v>
       </c>
       <c r="H2123" t="n">
         <v>68404</v>
@@ -61965,7 +61965,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2124" t="n">
-        <v>0.401409685611725</v>
+        <v>0.401409715414047</v>
       </c>
       <c r="H2124" t="n">
         <v>97328</v>
@@ -62052,7 +62052,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2127" t="n">
-        <v>0.405269384384155</v>
+        <v>0.405269354581833</v>
       </c>
       <c r="H2127" t="n">
         <v>52451</v>
@@ -62284,7 +62284,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2135" t="n">
-        <v>0.39465519785881</v>
+        <v>0.394655227661133</v>
       </c>
       <c r="H2135" t="n">
         <v>7804</v>
@@ -62313,7 +62313,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2136" t="n">
-        <v>0.378251403570175</v>
+        <v>0.378251433372498</v>
       </c>
       <c r="H2136" t="n">
         <v>1237</v>
@@ -62458,7 +62458,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2141" t="n">
-        <v>0.39465519785881</v>
+        <v>0.394655227661133</v>
       </c>
       <c r="H2141" t="n">
         <v>28880</v>
@@ -62487,7 +62487,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2142" t="n">
-        <v>0.39465519785881</v>
+        <v>0.394655227661133</v>
       </c>
       <c r="H2142" t="n">
         <v>0</v>
@@ -62516,7 +62516,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2143" t="n">
-        <v>0.391760379076004</v>
+        <v>0.391760408878326</v>
       </c>
       <c r="H2143" t="n">
         <v>2955</v>
@@ -62545,7 +62545,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2144" t="n">
-        <v>0.391760379076004</v>
+        <v>0.391760408878326</v>
       </c>
       <c r="H2144" t="n">
         <v>28728</v>
@@ -63067,7 +63067,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2162" t="n">
-        <v>0.399479866027832</v>
+        <v>0.39947983622551</v>
       </c>
       <c r="H2162" t="n">
         <v>20849</v>
@@ -63096,7 +63096,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2163" t="n">
-        <v>0.401409685611725</v>
+        <v>0.401409715414047</v>
       </c>
       <c r="H2163" t="n">
         <v>11659</v>
@@ -63212,7 +63212,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2167" t="n">
-        <v>0.41202387213707</v>
+        <v>0.412023842334747</v>
       </c>
       <c r="H2167" t="n">
         <v>33001</v>
@@ -63270,7 +63270,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2169" t="n">
-        <v>0.408164173364639</v>
+        <v>0.408164203166962</v>
       </c>
       <c r="H2169" t="n">
         <v>55582</v>
@@ -63299,7 +63299,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2170" t="n">
-        <v>0.401409685611725</v>
+        <v>0.401409715414047</v>
       </c>
       <c r="H2170" t="n">
         <v>21037</v>
@@ -63328,7 +63328,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2171" t="n">
-        <v>0.401409685611725</v>
+        <v>0.401409715414047</v>
       </c>
       <c r="H2171" t="n">
         <v>31998</v>
@@ -63386,7 +63386,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2173" t="n">
-        <v>0.401409685611725</v>
+        <v>0.401409715414047</v>
       </c>
       <c r="H2173" t="n">
         <v>2007</v>
@@ -63502,7 +63502,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2177" t="n">
-        <v>0.396585077047348</v>
+        <v>0.396585047245026</v>
       </c>
       <c r="H2177" t="n">
         <v>533</v>
@@ -63531,7 +63531,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2178" t="n">
-        <v>0.399024069309235</v>
+        <v>0.399024099111557</v>
       </c>
       <c r="H2178" t="n">
         <v>19001</v>
@@ -63676,7 +63676,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2183" t="n">
-        <v>0.403902143239975</v>
+        <v>0.403902113437653</v>
       </c>
       <c r="H2183" t="n">
         <v>6543</v>
@@ -63734,7 +63734,7 @@
         <v>0.414000004529953</v>
       </c>
       <c r="G2185" t="n">
-        <v>0.403902143239975</v>
+        <v>0.403902113437653</v>
       </c>
       <c r="H2185" t="n">
         <v>25</v>
@@ -63966,7 +63966,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G2193" t="n">
-        <v>0.376585066318512</v>
+        <v>0.376585096120834</v>
       </c>
       <c r="H2193" t="n">
         <v>479</v>
@@ -64140,7 +64140,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2199" t="n">
-        <v>0.380487501621246</v>
+        <v>0.380487471818924</v>
       </c>
       <c r="H2199" t="n">
         <v>18500</v>
@@ -64343,7 +64343,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G2206" t="n">
-        <v>0.378536313772202</v>
+        <v>0.378536283969879</v>
       </c>
       <c r="H2206" t="n">
         <v>17820</v>
@@ -64372,7 +64372,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G2207" t="n">
-        <v>0.378536313772202</v>
+        <v>0.378536283969879</v>
       </c>
       <c r="H2207" t="n">
         <v>0</v>
@@ -64430,7 +64430,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2209" t="n">
-        <v>0.380487501621246</v>
+        <v>0.380487471818924</v>
       </c>
       <c r="H2209" t="n">
         <v>12610</v>
@@ -64604,7 +64604,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2215" t="n">
-        <v>0.377560675144196</v>
+        <v>0.377560645341873</v>
       </c>
       <c r="H2215" t="n">
         <v>10440</v>
@@ -64633,7 +64633,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G2216" t="n">
-        <v>0.376585066318512</v>
+        <v>0.376585096120834</v>
       </c>
       <c r="H2216" t="n">
         <v>1600</v>
@@ -64749,7 +64749,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2220" t="n">
-        <v>0.377560675144196</v>
+        <v>0.377560645341873</v>
       </c>
       <c r="H2220" t="n">
         <v>500</v>
@@ -64778,7 +64778,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G2221" t="n">
-        <v>0.376585066318512</v>
+        <v>0.376585096120834</v>
       </c>
       <c r="H2221" t="n">
         <v>9168</v>
@@ -64952,7 +64952,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2227" t="n">
-        <v>0.418536216020584</v>
+        <v>0.418536245822906</v>
       </c>
       <c r="H2227" t="n">
         <v>97027</v>
@@ -65097,7 +65097,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2232" t="n">
-        <v>0.396097213029861</v>
+        <v>0.396097242832184</v>
       </c>
       <c r="H2232" t="n">
         <v>32431</v>
@@ -65184,7 +65184,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2235" t="n">
-        <v>0.399024069309235</v>
+        <v>0.399024099111557</v>
       </c>
       <c r="H2235" t="n">
         <v>2415</v>
@@ -65213,7 +65213,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2236" t="n">
-        <v>0.400975316762924</v>
+        <v>0.400975286960602</v>
       </c>
       <c r="H2236" t="n">
         <v>34547</v>
@@ -65329,7 +65329,7 @@
         <v>0.41100001335144</v>
       </c>
       <c r="G2240" t="n">
-        <v>0.400975316762924</v>
+        <v>0.400975286960602</v>
       </c>
       <c r="H2240" t="n">
         <v>8875</v>
@@ -65387,7 +65387,7 @@
         <v>0.409000009298325</v>
       </c>
       <c r="G2242" t="n">
-        <v>0.399024069309235</v>
+        <v>0.399024099111557</v>
       </c>
       <c r="H2242" t="n">
         <v>5683</v>
@@ -65503,7 +65503,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2246" t="n">
-        <v>0.384389907121658</v>
+        <v>0.384389936923981</v>
       </c>
       <c r="H2246" t="n">
         <v>1</v>
@@ -65619,7 +65619,7 @@
         <v>0.386000007390976</v>
       </c>
       <c r="G2250" t="n">
-        <v>0.376585066318512</v>
+        <v>0.376585096120834</v>
       </c>
       <c r="H2250" t="n">
         <v>23292</v>
@@ -65648,7 +65648,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2251" t="n">
-        <v>0.380487501621246</v>
+        <v>0.380487471818924</v>
       </c>
       <c r="H2251" t="n">
         <v>6568</v>
@@ -65677,7 +65677,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2252" t="n">
-        <v>0.380487501621246</v>
+        <v>0.380487471818924</v>
       </c>
       <c r="H2252" t="n">
         <v>0</v>
@@ -65706,7 +65706,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2253" t="n">
-        <v>0.396097213029861</v>
+        <v>0.396097242832184</v>
       </c>
       <c r="H2253" t="n">
         <v>1000</v>
@@ -65793,7 +65793,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2256" t="n">
-        <v>0.380487501621246</v>
+        <v>0.380487471818924</v>
       </c>
       <c r="H2256" t="n">
         <v>2783</v>
@@ -66025,7 +66025,7 @@
         <v>0.40599998831749</v>
       </c>
       <c r="G2264" t="n">
-        <v>0.396097213029861</v>
+        <v>0.396097242832184</v>
       </c>
       <c r="H2264" t="n">
         <v>17013</v>
@@ -66083,7 +66083,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2266" t="n">
-        <v>0.384389907121658</v>
+        <v>0.384389936923981</v>
       </c>
       <c r="H2266" t="n">
         <v>20680</v>
@@ -66170,7 +66170,7 @@
         <v>0.388000011444092</v>
       </c>
       <c r="G2269" t="n">
-        <v>0.378536313772202</v>
+        <v>0.378536283969879</v>
       </c>
       <c r="H2269" t="n">
         <v>263</v>
@@ -66431,7 +66431,7 @@
         <v>0.428999990224838</v>
       </c>
       <c r="G2278" t="n">
-        <v>0.418536216020584</v>
+        <v>0.418536245822906</v>
       </c>
       <c r="H2278" t="n">
         <v>172855</v>
@@ -66489,7 +66489,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G2280" t="n">
-        <v>0.478048384189606</v>
+        <v>0.478048413991928</v>
       </c>
       <c r="H2280" t="n">
         <v>278829</v>
@@ -66605,7 +66605,7 @@
         <v>0.495999991893768</v>
       </c>
       <c r="G2284" t="n">
-        <v>0.483902037143707</v>
+        <v>0.48390206694603</v>
       </c>
       <c r="H2284" t="n">
         <v>48623</v>
@@ -66634,7 +66634,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2285" t="n">
-        <v>0.469267934560776</v>
+        <v>0.469267904758453</v>
       </c>
       <c r="H2285" t="n">
         <v>35599</v>
@@ -66663,7 +66663,7 @@
         <v>0.490000009536743</v>
       </c>
       <c r="G2286" t="n">
-        <v>0.478048384189606</v>
+        <v>0.478048413991928</v>
       </c>
       <c r="H2286" t="n">
         <v>29506</v>
@@ -66895,7 +66895,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G2294" t="n">
-        <v>0.467316687107086</v>
+        <v>0.467316716909409</v>
       </c>
       <c r="H2294" t="n">
         <v>68672</v>
@@ -66953,7 +66953,7 @@
         <v>0.474999994039536</v>
       </c>
       <c r="G2296" t="n">
-        <v>0.463414281606674</v>
+        <v>0.463414251804352</v>
       </c>
       <c r="H2296" t="n">
         <v>16299</v>
@@ -67040,7 +67040,7 @@
         <v>0.449999988079071</v>
       </c>
       <c r="G2299" t="n">
-        <v>0.439024031162262</v>
+        <v>0.43902400135994</v>
       </c>
       <c r="H2299" t="n">
         <v>9929</v>
@@ -67243,7 +67243,7 @@
         <v>0.46000000834465</v>
       </c>
       <c r="G2306" t="n">
-        <v>0.44878014922142</v>
+        <v>0.448780119419098</v>
       </c>
       <c r="H2306" t="n">
         <v>20358</v>
@@ -67446,7 +67446,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2313" t="n">
-        <v>0.493658125400543</v>
+        <v>0.493658155202866</v>
       </c>
       <c r="H2313" t="n">
         <v>307123</v>
@@ -67475,7 +67475,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2314" t="n">
-        <v>0.491706937551498</v>
+        <v>0.491706907749176</v>
       </c>
       <c r="H2314" t="n">
         <v>87078</v>
@@ -67504,7 +67504,7 @@
         <v>0.504000008106232</v>
       </c>
       <c r="G2315" t="n">
-        <v>0.491706937551498</v>
+        <v>0.491706907749176</v>
       </c>
       <c r="H2315" t="n">
         <v>2346</v>
@@ -67562,7 +67562,7 @@
         <v>0.508000016212463</v>
       </c>
       <c r="G2317" t="n">
-        <v>0.495609402656555</v>
+        <v>0.49560934305191</v>
       </c>
       <c r="H2317" t="n">
         <v>129371</v>
@@ -67649,7 +67649,7 @@
         <v>0.526000022888184</v>
       </c>
       <c r="G2320" t="n">
-        <v>0.51317036151886</v>
+        <v>0.513170301914215</v>
       </c>
       <c r="H2320" t="n">
         <v>65607</v>
@@ -67678,7 +67678,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2321" t="n">
-        <v>0.581462919712067</v>
+        <v>0.581462979316711</v>
       </c>
       <c r="H2321" t="n">
         <v>185258</v>
@@ -67736,7 +67736,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G2323" t="n">
-        <v>0.72780430316925</v>
+        <v>0.727804243564606</v>
       </c>
       <c r="H2323" t="n">
         <v>511007</v>
@@ -67823,7 +67823,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2326" t="n">
-        <v>0.682926297187805</v>
+        <v>0.68292623758316</v>
       </c>
       <c r="H2326" t="n">
         <v>110593</v>
@@ -68055,7 +68055,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G2334" t="n">
-        <v>0.647804319858551</v>
+        <v>0.647804379463196</v>
       </c>
       <c r="H2334" t="n">
         <v>64268</v>
@@ -68084,7 +68084,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2335" t="n">
-        <v>0.669267773628235</v>
+        <v>0.66926771402359</v>
       </c>
       <c r="H2335" t="n">
         <v>7106</v>
@@ -68229,7 +68229,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G2340" t="n">
-        <v>0.710243344306946</v>
+        <v>0.710243284702301</v>
       </c>
       <c r="H2340" t="n">
         <v>378919</v>
@@ -68258,7 +68258,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G2341" t="n">
-        <v>0.710243344306946</v>
+        <v>0.710243284702301</v>
       </c>
       <c r="H2341" t="n">
         <v>297783</v>
@@ -68287,7 +68287,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G2342" t="n">
-        <v>0.706340849399567</v>
+        <v>0.706340909004211</v>
       </c>
       <c r="H2342" t="n">
         <v>127644</v>
@@ -68316,7 +68316,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2343" t="n">
-        <v>0.682926297187805</v>
+        <v>0.68292623758316</v>
       </c>
       <c r="H2343" t="n">
         <v>51783</v>
@@ -68374,7 +68374,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2345" t="n">
-        <v>0.682926297187805</v>
+        <v>0.68292623758316</v>
       </c>
       <c r="H2345" t="n">
         <v>33898</v>
@@ -68432,7 +68432,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G2347" t="n">
-        <v>0.688779950141907</v>
+        <v>0.688779890537262</v>
       </c>
       <c r="H2347" t="n">
         <v>38891</v>
@@ -68548,7 +68548,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2351" t="n">
-        <v>0.675121366977692</v>
+        <v>0.675121426582336</v>
       </c>
       <c r="H2351" t="n">
         <v>2020</v>
@@ -68577,7 +68577,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2352" t="n">
-        <v>0.571706891059875</v>
+        <v>0.571706831455231</v>
       </c>
       <c r="H2352" t="n">
         <v>262615</v>
@@ -68606,7 +68606,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2353" t="n">
-        <v>0.57560932636261</v>
+        <v>0.575609266757965</v>
       </c>
       <c r="H2353" t="n">
         <v>38367</v>
@@ -68664,7 +68664,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2355" t="n">
-        <v>0.536584913730621</v>
+        <v>0.536584973335266</v>
       </c>
       <c r="H2355" t="n">
         <v>160119</v>
@@ -68867,7 +68867,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2362" t="n">
-        <v>0.57560932636261</v>
+        <v>0.575609266757965</v>
       </c>
       <c r="H2362" t="n">
         <v>81915</v>
@@ -68983,7 +68983,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2366" t="n">
-        <v>0.675121366977692</v>
+        <v>0.675121426582336</v>
       </c>
       <c r="H2366" t="n">
         <v>134358</v>
@@ -69012,7 +69012,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2367" t="n">
-        <v>0.669267773628235</v>
+        <v>0.66926771402359</v>
       </c>
       <c r="H2367" t="n">
         <v>126530</v>
@@ -69041,7 +69041,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2368" t="n">
-        <v>0.663414120674133</v>
+        <v>0.663414061069489</v>
       </c>
       <c r="H2368" t="n">
         <v>18106</v>
@@ -69128,7 +69128,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2371" t="n">
-        <v>0.63804829120636</v>
+        <v>0.638048231601715</v>
       </c>
       <c r="H2371" t="n">
         <v>84922</v>
@@ -69186,7 +69186,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2373" t="n">
-        <v>0.65560919046402</v>
+        <v>0.655609250068665</v>
       </c>
       <c r="H2373" t="n">
         <v>43588</v>
@@ -69215,7 +69215,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2374" t="n">
-        <v>0.616584897041321</v>
+        <v>0.616584956645966</v>
       </c>
       <c r="H2374" t="n">
         <v>235030</v>
@@ -69273,7 +69273,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2376" t="n">
-        <v>0.616584897041321</v>
+        <v>0.616584956645966</v>
       </c>
       <c r="H2376" t="n">
         <v>18713</v>
@@ -69418,7 +69418,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2381" t="n">
-        <v>0.616584897041321</v>
+        <v>0.616584956645966</v>
       </c>
       <c r="H2381" t="n">
         <v>44210</v>
@@ -69476,7 +69476,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2383" t="n">
-        <v>0.616584897041321</v>
+        <v>0.616584956645966</v>
       </c>
       <c r="H2383" t="n">
         <v>177203</v>
@@ -69766,7 +69766,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2393" t="n">
-        <v>0.663414120674133</v>
+        <v>0.663414061069489</v>
       </c>
       <c r="H2393" t="n">
         <v>110879</v>
@@ -69795,7 +69795,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2394" t="n">
-        <v>0.673170149326324</v>
+        <v>0.673170208930969</v>
       </c>
       <c r="H2394" t="n">
         <v>49142</v>
@@ -69853,7 +69853,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2396" t="n">
-        <v>0.669267773628235</v>
+        <v>0.66926771402359</v>
       </c>
       <c r="H2396" t="n">
         <v>92823</v>
@@ -69911,7 +69911,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2398" t="n">
-        <v>0.675121366977692</v>
+        <v>0.675121426582336</v>
       </c>
       <c r="H2398" t="n">
         <v>9840</v>
@@ -70085,7 +70085,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2404" t="n">
-        <v>0.663414120674133</v>
+        <v>0.663414061069489</v>
       </c>
       <c r="H2404" t="n">
         <v>166415</v>
@@ -70172,7 +70172,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G2407" t="n">
-        <v>0.647804319858551</v>
+        <v>0.647804379463196</v>
       </c>
       <c r="H2407" t="n">
         <v>324</v>
@@ -70230,7 +70230,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2409" t="n">
-        <v>0.628292143344879</v>
+        <v>0.628292202949524</v>
       </c>
       <c r="H2409" t="n">
         <v>7797</v>
@@ -70259,7 +70259,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2410" t="n">
-        <v>0.63804829120636</v>
+        <v>0.638048231601715</v>
       </c>
       <c r="H2410" t="n">
         <v>2707</v>
@@ -70288,7 +70288,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2411" t="n">
-        <v>0.63804829120636</v>
+        <v>0.638048231601715</v>
       </c>
       <c r="H2411" t="n">
         <v>2255</v>
@@ -70346,7 +70346,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G2413" t="n">
-        <v>0.647804319858551</v>
+        <v>0.647804379463196</v>
       </c>
       <c r="H2413" t="n">
         <v>17</v>
@@ -70375,7 +70375,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2414" t="n">
-        <v>0.628292143344879</v>
+        <v>0.628292202949524</v>
       </c>
       <c r="H2414" t="n">
         <v>42392</v>
@@ -70549,7 +70549,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2420" t="n">
-        <v>0.620487332344055</v>
+        <v>0.62048727273941</v>
       </c>
       <c r="H2420" t="n">
         <v>12474</v>
@@ -70607,7 +70607,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2422" t="n">
-        <v>0.628292143344879</v>
+        <v>0.628292202949524</v>
       </c>
       <c r="H2422" t="n">
         <v>1650</v>
@@ -70636,7 +70636,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G2423" t="n">
-        <v>0.618536114692688</v>
+        <v>0.618536055088043</v>
       </c>
       <c r="H2423" t="n">
         <v>8750</v>
@@ -70723,7 +70723,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2426" t="n">
-        <v>0.628292143344879</v>
+        <v>0.628292202949524</v>
       </c>
       <c r="H2426" t="n">
         <v>2088</v>
@@ -80038,6 +80038,35 @@
         <v>17782</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>1.18499994277954</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>1.16999995708466</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>1.18499994277954</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>1.18499994277954</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>551</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -572,7 +572,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>1.46354842185974</v>
+        <v>1.46354830265045</v>
       </c>
       <c r="H7" t="n">
         <v>39904</v>
@@ -601,7 +601,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G8" t="n">
-        <v>1.49205923080444</v>
+        <v>1.49205911159515</v>
       </c>
       <c r="H8" t="n">
         <v>9900</v>
@@ -775,7 +775,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>1.26872551441193</v>
+        <v>1.26872539520264</v>
       </c>
       <c r="H14" t="n">
         <v>17780</v>
@@ -862,7 +862,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G17" t="n">
-        <v>1.30198788642883</v>
+        <v>1.30198776721954</v>
       </c>
       <c r="H17" t="n">
         <v>5838</v>
@@ -891,7 +891,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G18" t="n">
-        <v>1.30198788642883</v>
+        <v>1.30198776721954</v>
       </c>
       <c r="H18" t="n">
         <v>4474</v>
@@ -1007,7 +1007,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G22" t="n">
-        <v>1.32669711112976</v>
+        <v>1.32669723033905</v>
       </c>
       <c r="H22" t="n">
         <v>7549</v>
@@ -1036,7 +1036,7 @@
         <v>1.40699994564056</v>
       </c>
       <c r="G23" t="n">
-        <v>1.33715093135834</v>
+        <v>1.33715105056763</v>
       </c>
       <c r="H23" t="n">
         <v>2689</v>
@@ -1065,7 +1065,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G24" t="n">
-        <v>1.33049845695496</v>
+        <v>1.33049857616425</v>
       </c>
       <c r="H24" t="n">
         <v>8036</v>
@@ -1094,7 +1094,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G25" t="n">
-        <v>1.28298079967499</v>
+        <v>1.2829806804657</v>
       </c>
       <c r="H25" t="n">
         <v>21414</v>
@@ -1181,7 +1181,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G28" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H28" t="n">
         <v>6283</v>
@@ -1239,7 +1239,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G30" t="n">
-        <v>1.13662576675415</v>
+        <v>1.13662588596344</v>
       </c>
       <c r="H30" t="n">
         <v>1130</v>
@@ -1268,7 +1268,7 @@
         <v>1.16100001335144</v>
       </c>
       <c r="G31" t="n">
-        <v>1.10336351394653</v>
+        <v>1.10336339473724</v>
       </c>
       <c r="H31" t="n">
         <v>6020</v>
@@ -1384,7 +1384,7 @@
         <v>1.35899996757507</v>
       </c>
       <c r="G35" t="n">
-        <v>1.29153406620026</v>
+        <v>1.29153394699097</v>
       </c>
       <c r="H35" t="n">
         <v>2501</v>
@@ -1413,7 +1413,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G36" t="n">
-        <v>1.25922191143036</v>
+        <v>1.25922179222107</v>
       </c>
       <c r="H36" t="n">
         <v>4117</v>
@@ -1442,7 +1442,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G37" t="n">
-        <v>1.33905172348022</v>
+        <v>1.33905184268951</v>
       </c>
       <c r="H37" t="n">
         <v>9441</v>
@@ -1471,7 +1471,7 @@
         <v>1.32400000095367</v>
       </c>
       <c r="G38" t="n">
-        <v>1.25827145576477</v>
+        <v>1.25827157497406</v>
       </c>
       <c r="H38" t="n">
         <v>12260</v>
@@ -1500,7 +1500,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G39" t="n">
-        <v>1.31719362735748</v>
+        <v>1.31719350814819</v>
       </c>
       <c r="H39" t="n">
         <v>13555</v>
@@ -1587,7 +1587,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G42" t="n">
-        <v>1.29723620414734</v>
+        <v>1.29723608493805</v>
       </c>
       <c r="H42" t="n">
         <v>3745</v>
@@ -1645,7 +1645,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G44" t="n">
-        <v>1.32289552688599</v>
+        <v>1.32289564609528</v>
       </c>
       <c r="H44" t="n">
         <v>5423</v>
@@ -1674,7 +1674,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G45" t="n">
-        <v>1.32099497318268</v>
+        <v>1.32099509239197</v>
       </c>
       <c r="H45" t="n">
         <v>1400</v>
@@ -1703,7 +1703,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>1.28773248195648</v>
+        <v>1.28773260116577</v>
       </c>
       <c r="H46" t="n">
         <v>3247</v>
@@ -1732,7 +1732,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G47" t="n">
-        <v>1.2810800075531</v>
+        <v>1.28108012676239</v>
       </c>
       <c r="H47" t="n">
         <v>4298</v>
@@ -1761,7 +1761,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G48" t="n">
-        <v>1.2810800075531</v>
+        <v>1.28108012676239</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G51" t="n">
-        <v>1.33049845695496</v>
+        <v>1.33049857616425</v>
       </c>
       <c r="H51" t="n">
         <v>5788</v>
@@ -1877,7 +1877,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G52" t="n">
-        <v>1.32194542884827</v>
+        <v>1.32194530963898</v>
       </c>
       <c r="H52" t="n">
         <v>2834</v>
@@ -1906,7 +1906,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G53" t="n">
-        <v>1.32194542884827</v>
+        <v>1.32194530963898</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G54" t="n">
-        <v>1.32099497318268</v>
+        <v>1.32099509239197</v>
       </c>
       <c r="H54" t="n">
         <v>1500</v>
@@ -2051,7 +2051,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G58" t="n">
-        <v>1.26967561244965</v>
+        <v>1.26967573165894</v>
       </c>
       <c r="H58" t="n">
         <v>21406</v>
@@ -2080,7 +2080,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>1.32574677467346</v>
+        <v>1.32574665546417</v>
       </c>
       <c r="H59" t="n">
         <v>560</v>
@@ -2167,7 +2167,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G62" t="n">
-        <v>1.26207280158997</v>
+        <v>1.26207292079926</v>
       </c>
       <c r="H62" t="n">
         <v>2000</v>
@@ -2225,7 +2225,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G64" t="n">
-        <v>1.24116492271423</v>
+        <v>1.24116504192352</v>
       </c>
       <c r="H64" t="n">
         <v>6820</v>
@@ -2254,7 +2254,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G65" t="n">
-        <v>1.26017224788666</v>
+        <v>1.26017212867737</v>
       </c>
       <c r="H65" t="n">
         <v>13431</v>
@@ -2341,7 +2341,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G68" t="n">
-        <v>1.30578935146332</v>
+        <v>1.30578923225403</v>
       </c>
       <c r="H68" t="n">
         <v>119</v>
@@ -2370,7 +2370,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G69" t="n">
-        <v>1.30578935146332</v>
+        <v>1.30578923225403</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G70" t="n">
-        <v>1.24781763553619</v>
+        <v>1.2478175163269</v>
       </c>
       <c r="H70" t="n">
         <v>3528</v>
@@ -2428,7 +2428,7 @@
         <v>1.30799996852875</v>
       </c>
       <c r="G71" t="n">
-        <v>1.24306583404541</v>
+        <v>1.24306571483612</v>
       </c>
       <c r="H71" t="n">
         <v>1224</v>
@@ -2457,7 +2457,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G72" t="n">
-        <v>1.30483889579773</v>
+        <v>1.30483901500702</v>
       </c>
       <c r="H72" t="n">
         <v>14416</v>
@@ -2486,7 +2486,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G73" t="n">
-        <v>1.29058349132538</v>
+        <v>1.29058372974396</v>
       </c>
       <c r="H73" t="n">
         <v>5869</v>
@@ -2573,7 +2573,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G76" t="n">
-        <v>1.26967561244965</v>
+        <v>1.26967573165894</v>
       </c>
       <c r="H76" t="n">
         <v>8995</v>
@@ -2631,7 +2631,7 @@
         <v>1.34099996089935</v>
       </c>
       <c r="G78" t="n">
-        <v>1.27442741394043</v>
+        <v>1.27442765235901</v>
       </c>
       <c r="H78" t="n">
         <v>3828</v>
@@ -2776,7 +2776,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G83" t="n">
-        <v>1.26207280158997</v>
+        <v>1.26207292079926</v>
       </c>
       <c r="H83" t="n">
         <v>22657</v>
@@ -2834,7 +2834,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G85" t="n">
-        <v>1.26207280158997</v>
+        <v>1.26207292079926</v>
       </c>
       <c r="H85" t="n">
         <v>4053</v>
@@ -2892,7 +2892,7 @@
         <v>1.35199999809265</v>
       </c>
       <c r="G87" t="n">
-        <v>1.2848813533783</v>
+        <v>1.28488147258759</v>
       </c>
       <c r="H87" t="n">
         <v>1240</v>
@@ -2921,7 +2921,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G88" t="n">
-        <v>1.26207280158997</v>
+        <v>1.26207292079926</v>
       </c>
       <c r="H88" t="n">
         <v>2439</v>
@@ -2950,7 +2950,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G89" t="n">
-        <v>1.30483889579773</v>
+        <v>1.30483901500702</v>
       </c>
       <c r="H89" t="n">
         <v>852</v>
@@ -3037,7 +3037,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G92" t="n">
-        <v>1.25922191143036</v>
+        <v>1.25922179222107</v>
       </c>
       <c r="H92" t="n">
         <v>1792</v>
@@ -3124,7 +3124,7 @@
         <v>1.27999997138977</v>
       </c>
       <c r="G95" t="n">
-        <v>1.2164558172226</v>
+        <v>1.21645569801331</v>
       </c>
       <c r="H95" t="n">
         <v>9477</v>
@@ -3182,7 +3182,7 @@
         <v>1.26900005340576</v>
       </c>
       <c r="G97" t="n">
-        <v>1.20600187778473</v>
+        <v>1.20600175857544</v>
       </c>
       <c r="H97" t="n">
         <v>1181</v>
@@ -3211,7 +3211,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G98" t="n">
-        <v>1.1803423166275</v>
+        <v>1.18034219741821</v>
       </c>
       <c r="H98" t="n">
         <v>765</v>
@@ -3240,7 +3240,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G99" t="n">
-        <v>1.1803423166275</v>
+        <v>1.18034219741821</v>
       </c>
       <c r="H99" t="n">
         <v>10250</v>
@@ -3414,7 +3414,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G105" t="n">
-        <v>1.17178905010223</v>
+        <v>1.17178916931152</v>
       </c>
       <c r="H105" t="n">
         <v>3950</v>
@@ -3617,7 +3617,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G112" t="n">
-        <v>1.1822429895401</v>
+        <v>1.18224310874939</v>
       </c>
       <c r="H112" t="n">
         <v>3100</v>
@@ -3646,7 +3646,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H113" t="n">
         <v>202</v>
@@ -3762,7 +3762,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H117" t="n">
         <v>22400</v>
@@ -3936,7 +3936,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G123" t="n">
-        <v>1.13662576675415</v>
+        <v>1.13662588596344</v>
       </c>
       <c r="H123" t="n">
         <v>15822</v>
@@ -3965,7 +3965,7 @@
         <v>1.02300000190735</v>
       </c>
       <c r="G124" t="n">
-        <v>0.97221428155899</v>
+        <v>0.972214341163635</v>
       </c>
       <c r="H124" t="n">
         <v>9233</v>
@@ -4023,7 +4023,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G126" t="n">
-        <v>0.975065410137177</v>
+        <v>0.975065350532532</v>
       </c>
       <c r="H126" t="n">
         <v>15762</v>
@@ -4052,7 +4052,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G127" t="n">
-        <v>1.00737738609314</v>
+        <v>1.00737726688385</v>
       </c>
       <c r="H127" t="n">
         <v>1550</v>
@@ -4110,7 +4110,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G129" t="n">
-        <v>1.06439888477325</v>
+        <v>1.06439876556396</v>
       </c>
       <c r="H129" t="n">
         <v>33799</v>
@@ -4139,7 +4139,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G130" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H130" t="n">
         <v>9949</v>
@@ -4168,7 +4168,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G131" t="n">
-        <v>1.09005844593048</v>
+        <v>1.09005832672119</v>
       </c>
       <c r="H131" t="n">
         <v>4789</v>
@@ -4197,7 +4197,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G132" t="n">
-        <v>0.955107867717743</v>
+        <v>0.955107927322388</v>
       </c>
       <c r="H132" t="n">
         <v>51084</v>
@@ -4255,7 +4255,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G134" t="n">
-        <v>1.02068257331848</v>
+        <v>1.02068245410919</v>
       </c>
       <c r="H134" t="n">
         <v>1695</v>
@@ -4371,7 +4371,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G138" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H138" t="n">
         <v>2668</v>
@@ -4400,7 +4400,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G139" t="n">
-        <v>0.996923446655273</v>
+        <v>0.996923506259918</v>
       </c>
       <c r="H139" t="n">
         <v>1497</v>
@@ -4429,7 +4429,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G140" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H140" t="n">
         <v>819</v>
@@ -4458,7 +4458,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G141" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H141" t="n">
         <v>2583</v>
@@ -4574,7 +4574,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G145" t="n">
-        <v>0.975065410137177</v>
+        <v>0.975065350532532</v>
       </c>
       <c r="H145" t="n">
         <v>6955</v>
@@ -4603,7 +4603,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G146" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H146" t="n">
         <v>7470</v>
@@ -4748,7 +4748,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G151" t="n">
-        <v>0.987420082092285</v>
+        <v>0.987419962882996</v>
       </c>
       <c r="H151" t="n">
         <v>15266</v>
@@ -4777,7 +4777,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G152" t="n">
-        <v>0.986469566822052</v>
+        <v>0.986469686031342</v>
       </c>
       <c r="H152" t="n">
         <v>5343</v>
@@ -4806,7 +4806,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G153" t="n">
-        <v>0.986469566822052</v>
+        <v>0.986469686031342</v>
       </c>
       <c r="H153" t="n">
         <v>1577</v>
@@ -4835,7 +4835,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G154" t="n">
-        <v>1.00737738609314</v>
+        <v>1.00737726688385</v>
       </c>
       <c r="H154" t="n">
         <v>2200</v>
@@ -4864,7 +4864,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G155" t="n">
-        <v>1.00737738609314</v>
+        <v>1.00737726688385</v>
       </c>
       <c r="H155" t="n">
         <v>2862</v>
@@ -4980,7 +4980,7 @@
         <v>1.07700002193451</v>
       </c>
       <c r="G159" t="n">
-        <v>1.02353358268738</v>
+        <v>1.02353346347809</v>
       </c>
       <c r="H159" t="n">
         <v>301</v>
@@ -5009,7 +5009,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G160" t="n">
-        <v>1.02163279056549</v>
+        <v>1.02163290977478</v>
       </c>
       <c r="H160" t="n">
         <v>8000</v>
@@ -5038,7 +5038,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G161" t="n">
-        <v>0.980767369270325</v>
+        <v>0.980767428874969</v>
       </c>
       <c r="H161" t="n">
         <v>9930</v>
@@ -5125,7 +5125,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G164" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H164" t="n">
         <v>250</v>
@@ -5154,7 +5154,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G165" t="n">
-        <v>0.963661193847656</v>
+        <v>0.963661134243011</v>
       </c>
       <c r="H165" t="n">
         <v>3542</v>
@@ -5183,7 +5183,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G166" t="n">
-        <v>0.967462539672852</v>
+        <v>0.967462599277496</v>
       </c>
       <c r="H166" t="n">
         <v>14544</v>
@@ -5241,7 +5241,7 @@
         <v>1.02300000190735</v>
       </c>
       <c r="G168" t="n">
-        <v>0.97221428155899</v>
+        <v>0.972214341163635</v>
       </c>
       <c r="H168" t="n">
         <v>2389</v>
@@ -5270,7 +5270,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G169" t="n">
-        <v>0.986469566822052</v>
+        <v>0.986469686031342</v>
       </c>
       <c r="H169" t="n">
         <v>835</v>
@@ -5299,7 +5299,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G170" t="n">
-        <v>0.973164677619934</v>
+        <v>0.973164737224579</v>
       </c>
       <c r="H170" t="n">
         <v>7003</v>
@@ -5357,7 +5357,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G172" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H172" t="n">
         <v>10607</v>
@@ -5415,7 +5415,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G174" t="n">
-        <v>0.996923446655273</v>
+        <v>0.996923506259918</v>
       </c>
       <c r="H174" t="n">
         <v>500</v>
@@ -5502,7 +5502,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G177" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H177" t="n">
         <v>19399</v>
@@ -5531,7 +5531,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G178" t="n">
-        <v>1.15183174610138</v>
+        <v>1.15183162689209</v>
       </c>
       <c r="H178" t="n">
         <v>81424</v>
@@ -5560,7 +5560,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G179" t="n">
-        <v>1.12427115440369</v>
+        <v>1.12427127361298</v>
       </c>
       <c r="H179" t="n">
         <v>16527</v>
@@ -5618,7 +5618,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G181" t="n">
-        <v>1.07295203208923</v>
+        <v>1.07295191287994</v>
       </c>
       <c r="H181" t="n">
         <v>7705</v>
@@ -5647,7 +5647,7 @@
         <v>1.12899994850159</v>
       </c>
       <c r="G182" t="n">
-        <v>1.07295203208923</v>
+        <v>1.07295191287994</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>1.14900004863739</v>
       </c>
       <c r="G184" t="n">
-        <v>1.09195911884308</v>
+        <v>1.09195923805237</v>
       </c>
       <c r="H184" t="n">
         <v>10097</v>
@@ -5734,7 +5734,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G185" t="n">
-        <v>1.08910799026489</v>
+        <v>1.08910810947418</v>
       </c>
       <c r="H185" t="n">
         <v>2769</v>
@@ -5792,7 +5792,7 @@
         <v>1.12699997425079</v>
       </c>
       <c r="G187" t="n">
-        <v>1.07105123996735</v>
+        <v>1.07105135917664</v>
       </c>
       <c r="H187" t="n">
         <v>100</v>
@@ -5850,7 +5850,7 @@
         <v>1.05299997329712</v>
       </c>
       <c r="G189" t="n">
-        <v>1.00072503089905</v>
+        <v>1.00072491168976</v>
       </c>
       <c r="H189" t="n">
         <v>8629</v>
@@ -5879,7 +5879,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G190" t="n">
-        <v>1.00262558460236</v>
+        <v>1.00262570381165</v>
       </c>
       <c r="H190" t="n">
         <v>1609</v>
@@ -5908,7 +5908,7 @@
         <v>1.04299998283386</v>
       </c>
       <c r="G191" t="n">
-        <v>0.991221368312836</v>
+        <v>0.99122142791748</v>
       </c>
       <c r="H191" t="n">
         <v>16155</v>
@@ -5937,7 +5937,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G192" t="n">
-        <v>0.987420082092285</v>
+        <v>0.987419962882996</v>
       </c>
       <c r="H192" t="n">
         <v>2600</v>
@@ -5966,7 +5966,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H193" t="n">
         <v>3500</v>
@@ -5995,7 +5995,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G194" t="n">
-        <v>0.996923446655273</v>
+        <v>0.996923506259918</v>
       </c>
       <c r="H194" t="n">
         <v>3572</v>
@@ -6053,7 +6053,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G196" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H196" t="n">
         <v>305</v>
@@ -6082,7 +6082,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G197" t="n">
-        <v>0.989320635795593</v>
+        <v>0.989320695400238</v>
       </c>
       <c r="H197" t="n">
         <v>16909</v>
@@ -6140,7 +6140,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G199" t="n">
-        <v>0.986469566822052</v>
+        <v>0.986469686031342</v>
       </c>
       <c r="H199" t="n">
         <v>1462</v>
@@ -6169,7 +6169,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G200" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H200" t="n">
         <v>1505</v>
@@ -6227,7 +6227,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G202" t="n">
-        <v>0.963661193847656</v>
+        <v>0.963661134243011</v>
       </c>
       <c r="H202" t="n">
         <v>4000</v>
@@ -6256,7 +6256,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G203" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H203" t="n">
         <v>10950</v>
@@ -6285,7 +6285,7 @@
         <v>1.02100002765656</v>
       </c>
       <c r="G204" t="n">
-        <v>0.970313549041748</v>
+        <v>0.970313608646393</v>
       </c>
       <c r="H204" t="n">
         <v>4160</v>
@@ -6314,7 +6314,7 @@
         <v>1.02100002765656</v>
       </c>
       <c r="G205" t="n">
-        <v>0.970313549041748</v>
+        <v>0.970313608646393</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>1.02100002765656</v>
       </c>
       <c r="G206" t="n">
-        <v>0.970313549041748</v>
+        <v>0.970313608646393</v>
       </c>
       <c r="H206" t="n">
         <v>1966</v>
@@ -6372,7 +6372,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G207" t="n">
-        <v>0.987420082092285</v>
+        <v>0.987419962882996</v>
       </c>
       <c r="H207" t="n">
         <v>9988</v>
@@ -6459,7 +6459,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G210" t="n">
-        <v>0.971263945102692</v>
+        <v>0.971263825893402</v>
       </c>
       <c r="H210" t="n">
         <v>1000</v>
@@ -6517,7 +6517,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G212" t="n">
-        <v>0.973164677619934</v>
+        <v>0.973164737224579</v>
       </c>
       <c r="H212" t="n">
         <v>900</v>
@@ -6604,7 +6604,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H215" t="n">
         <v>2077</v>
@@ -6662,7 +6662,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G217" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H217" t="n">
         <v>480</v>
@@ -6720,7 +6720,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G219" t="n">
-        <v>0.955107867717743</v>
+        <v>0.955107927322388</v>
       </c>
       <c r="H219" t="n">
         <v>6120</v>
@@ -6749,7 +6749,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G220" t="n">
-        <v>0.955107867717743</v>
+        <v>0.955107927322388</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G221" t="n">
-        <v>0.947504997253418</v>
+        <v>0.947505056858063</v>
       </c>
       <c r="H221" t="n">
         <v>16472</v>
@@ -6807,7 +6807,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G222" t="n">
-        <v>0.971263945102692</v>
+        <v>0.971263825893402</v>
       </c>
       <c r="H222" t="n">
         <v>700</v>
@@ -6836,7 +6836,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G223" t="n">
-        <v>0.973164677619934</v>
+        <v>0.973164737224579</v>
       </c>
       <c r="H223" t="n">
         <v>5403</v>
@@ -6894,7 +6894,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G225" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H225" t="n">
         <v>27306</v>
@@ -6952,7 +6952,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G227" t="n">
-        <v>0.967462539672852</v>
+        <v>0.967462599277496</v>
       </c>
       <c r="H227" t="n">
         <v>15742</v>
@@ -6981,7 +6981,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H228" t="n">
         <v>2724</v>
@@ -7010,7 +7010,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H229" t="n">
         <v>11827</v>
@@ -7039,7 +7039,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G230" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H230" t="n">
         <v>302145</v>
@@ -7068,7 +7068,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G231" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>1.00800001621246</v>
       </c>
       <c r="G234" t="n">
-        <v>0.957958936691284</v>
+        <v>0.957958877086639</v>
       </c>
       <c r="H234" t="n">
         <v>2310</v>
@@ -7184,7 +7184,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G235" t="n">
-        <v>0.989320635795593</v>
+        <v>0.989320695400238</v>
       </c>
       <c r="H235" t="n">
         <v>10528</v>
@@ -7213,7 +7213,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G236" t="n">
-        <v>0.973164677619934</v>
+        <v>0.973164737224579</v>
       </c>
       <c r="H236" t="n">
         <v>261</v>
@@ -7242,7 +7242,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G237" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7387,7 +7387,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G242" t="n">
-        <v>1.00262558460236</v>
+        <v>1.00262570381165</v>
       </c>
       <c r="H242" t="n">
         <v>340</v>
@@ -7445,7 +7445,7 @@
         <v>1.03199994564056</v>
       </c>
       <c r="G244" t="n">
-        <v>0.980767369270325</v>
+        <v>0.980767428874969</v>
       </c>
       <c r="H244" t="n">
         <v>10086</v>
@@ -7474,7 +7474,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G245" t="n">
-        <v>0.975065410137177</v>
+        <v>0.975065350532532</v>
       </c>
       <c r="H245" t="n">
         <v>2093</v>
@@ -7503,7 +7503,7 @@
         <v>1.00100004673004</v>
       </c>
       <c r="G246" t="n">
-        <v>0.951306521892548</v>
+        <v>0.951306462287903</v>
       </c>
       <c r="H246" t="n">
         <v>37497</v>
@@ -7532,7 +7532,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G247" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H247" t="n">
         <v>11434</v>
@@ -7561,7 +7561,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G248" t="n">
-        <v>0.987420082092285</v>
+        <v>0.987419962882996</v>
       </c>
       <c r="H248" t="n">
         <v>20000</v>
@@ -7590,7 +7590,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G249" t="n">
-        <v>0.982668220996857</v>
+        <v>0.982668280601501</v>
       </c>
       <c r="H249" t="n">
         <v>204848</v>
@@ -7619,7 +7619,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G250" t="n">
-        <v>0.973164677619934</v>
+        <v>0.973164737224579</v>
       </c>
       <c r="H250" t="n">
         <v>51760</v>
@@ -7648,7 +7648,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G251" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H251" t="n">
         <v>36947</v>
@@ -7677,7 +7677,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G252" t="n">
-        <v>0.963661193847656</v>
+        <v>0.963661134243011</v>
       </c>
       <c r="H252" t="n">
         <v>13025</v>
@@ -7764,7 +7764,7 @@
         <v>1.13300001621246</v>
       </c>
       <c r="G255" t="n">
-        <v>1.07675349712372</v>
+        <v>1.07675337791443</v>
       </c>
       <c r="H255" t="n">
         <v>230084</v>
@@ -7822,7 +7822,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G257" t="n">
-        <v>0.989320635795593</v>
+        <v>0.989320695400238</v>
       </c>
       <c r="H257" t="n">
         <v>97577</v>
@@ -7851,7 +7851,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G258" t="n">
-        <v>0.983618557453156</v>
+        <v>0.983618438243866</v>
       </c>
       <c r="H258" t="n">
         <v>98439</v>
@@ -7880,7 +7880,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G259" t="n">
-        <v>0.98456883430481</v>
+        <v>0.984568953514099</v>
       </c>
       <c r="H259" t="n">
         <v>30635</v>
@@ -7938,7 +7938,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G261" t="n">
-        <v>1.04254055023193</v>
+        <v>1.04254066944122</v>
       </c>
       <c r="H261" t="n">
         <v>183087</v>
@@ -7967,7 +7967,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G262" t="n">
-        <v>1.17654085159302</v>
+        <v>1.17654097080231</v>
       </c>
       <c r="H262" t="n">
         <v>297642</v>
@@ -8025,7 +8025,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G264" t="n">
-        <v>1.45404481887817</v>
+        <v>1.45404493808746</v>
       </c>
       <c r="H264" t="n">
         <v>866479</v>
@@ -8083,7 +8083,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G266" t="n">
-        <v>1.39227175712585</v>
+        <v>1.39227163791656</v>
       </c>
       <c r="H266" t="n">
         <v>81832</v>
@@ -8141,7 +8141,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G268" t="n">
-        <v>1.33049845695496</v>
+        <v>1.33049857616425</v>
       </c>
       <c r="H268" t="n">
         <v>188065</v>
@@ -8228,7 +8228,7 @@
         <v>1.39199995994568</v>
       </c>
       <c r="G271" t="n">
-        <v>1.32289552688599</v>
+        <v>1.32289564609528</v>
       </c>
       <c r="H271" t="n">
         <v>163344</v>
@@ -8315,7 +8315,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>1.26872551441193</v>
+        <v>1.26872539520264</v>
       </c>
       <c r="H274" t="n">
         <v>297056</v>
@@ -8344,7 +8344,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G275" t="n">
-        <v>1.3837183713913</v>
+        <v>1.38371849060059</v>
       </c>
       <c r="H275" t="n">
         <v>660972</v>
@@ -8489,7 +8489,7 @@
         <v>1.31099998950958</v>
       </c>
       <c r="G280" t="n">
-        <v>1.2459169626236</v>
+        <v>1.24591684341431</v>
       </c>
       <c r="H280" t="n">
         <v>14708</v>
@@ -8518,7 +8518,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G281" t="n">
-        <v>1.24781763553619</v>
+        <v>1.2478175163269</v>
       </c>
       <c r="H281" t="n">
         <v>17255</v>
@@ -8547,7 +8547,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G282" t="n">
-        <v>1.26207280158997</v>
+        <v>1.26207292079926</v>
       </c>
       <c r="H282" t="n">
         <v>16948</v>
@@ -8605,7 +8605,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H284" t="n">
         <v>55023</v>
@@ -8663,7 +8663,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G286" t="n">
-        <v>1.17178905010223</v>
+        <v>1.17178916931152</v>
       </c>
       <c r="H286" t="n">
         <v>51660</v>
@@ -8692,7 +8692,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G287" t="n">
-        <v>1.12617194652557</v>
+        <v>1.12617182731628</v>
       </c>
       <c r="H287" t="n">
         <v>23104</v>
@@ -8750,7 +8750,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G289" t="n">
-        <v>1.09005844593048</v>
+        <v>1.09005832672119</v>
       </c>
       <c r="H289" t="n">
         <v>64492</v>
@@ -8808,7 +8808,7 @@
         <v>1.14100003242493</v>
       </c>
       <c r="G291" t="n">
-        <v>1.08435642719269</v>
+        <v>1.0843563079834</v>
       </c>
       <c r="H291" t="n">
         <v>36646</v>
@@ -8866,7 +8866,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G293" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H293" t="n">
         <v>4906</v>
@@ -8953,7 +8953,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G296" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H296" t="n">
         <v>5384</v>
@@ -8982,7 +8982,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G297" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H297" t="n">
         <v>16179</v>
@@ -9011,7 +9011,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G298" t="n">
-        <v>1.06439888477325</v>
+        <v>1.06439876556396</v>
       </c>
       <c r="H298" t="n">
         <v>25146</v>
@@ -9098,7 +9098,7 @@
         <v>1.21899998188019</v>
       </c>
       <c r="G301" t="n">
-        <v>1.15848410129547</v>
+        <v>1.15848422050476</v>
       </c>
       <c r="H301" t="n">
         <v>201854</v>
@@ -9272,7 +9272,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G307" t="n">
-        <v>1.1508811712265</v>
+        <v>1.15088105201721</v>
       </c>
       <c r="H307" t="n">
         <v>26808</v>
@@ -9330,7 +9330,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G309" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H309" t="n">
         <v>25871</v>
@@ -9359,7 +9359,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G310" t="n">
-        <v>1.13662576675415</v>
+        <v>1.13662588596344</v>
       </c>
       <c r="H310" t="n">
         <v>18377</v>
@@ -9388,7 +9388,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G311" t="n">
-        <v>1.15183174610138</v>
+        <v>1.15183162689209</v>
       </c>
       <c r="H311" t="n">
         <v>17084</v>
@@ -9417,7 +9417,7 @@
         <v>1.19700002670288</v>
       </c>
       <c r="G312" t="n">
-        <v>1.13757634162903</v>
+        <v>1.13757622241974</v>
       </c>
       <c r="H312" t="n">
         <v>23203</v>
@@ -9446,7 +9446,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G313" t="n">
-        <v>1.14042735099792</v>
+        <v>1.14042747020721</v>
       </c>
       <c r="H313" t="n">
         <v>17880</v>
@@ -9475,7 +9475,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G314" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H314" t="n">
         <v>30226</v>
@@ -9533,7 +9533,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H316" t="n">
         <v>17705</v>
@@ -9562,7 +9562,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G317" t="n">
-        <v>1.12522172927856</v>
+        <v>1.12522161006927</v>
       </c>
       <c r="H317" t="n">
         <v>18494</v>
@@ -9620,7 +9620,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G319" t="n">
-        <v>1.13472509384155</v>
+        <v>1.13472521305084</v>
       </c>
       <c r="H319" t="n">
         <v>11278</v>
@@ -9649,7 +9649,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G320" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H320" t="n">
         <v>15262</v>
@@ -9678,7 +9678,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G321" t="n">
-        <v>1.13377487659454</v>
+        <v>1.13377475738525</v>
       </c>
       <c r="H321" t="n">
         <v>14987</v>
@@ -9707,7 +9707,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G322" t="n">
-        <v>1.16323590278625</v>
+        <v>1.16323566436768</v>
       </c>
       <c r="H322" t="n">
         <v>56748</v>
@@ -9823,7 +9823,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G326" t="n">
-        <v>1.13377487659454</v>
+        <v>1.13377475738525</v>
       </c>
       <c r="H326" t="n">
         <v>5531</v>
@@ -9852,7 +9852,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G327" t="n">
-        <v>1.13472509384155</v>
+        <v>1.13472521305084</v>
       </c>
       <c r="H327" t="n">
         <v>17355</v>
@@ -9881,7 +9881,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G328" t="n">
-        <v>1.12807273864746</v>
+        <v>1.12807285785675</v>
       </c>
       <c r="H328" t="n">
         <v>9540</v>
@@ -9968,7 +9968,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G331" t="n">
-        <v>1.13472509384155</v>
+        <v>1.13472521305084</v>
       </c>
       <c r="H331" t="n">
         <v>38335</v>
@@ -10113,7 +10113,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G336" t="n">
-        <v>1.1166684627533</v>
+        <v>1.11666834354401</v>
       </c>
       <c r="H336" t="n">
         <v>13081</v>
@@ -10142,7 +10142,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G337" t="n">
-        <v>1.11571800708771</v>
+        <v>1.115718126297</v>
       </c>
       <c r="H337" t="n">
         <v>2860</v>
@@ -10229,7 +10229,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>1.11286699771881</v>
+        <v>1.11286687850952</v>
       </c>
       <c r="H340" t="n">
         <v>7409</v>
@@ -10316,7 +10316,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G343" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H343" t="n">
         <v>13913</v>
@@ -10345,7 +10345,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G344" t="n">
-        <v>1.10811519622803</v>
+        <v>1.10811531543732</v>
       </c>
       <c r="H344" t="n">
         <v>19157</v>
@@ -10374,7 +10374,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G345" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H345" t="n">
         <v>6925</v>
@@ -10403,7 +10403,7 @@
         <v>1.14600002765656</v>
       </c>
       <c r="G346" t="n">
-        <v>1.08910799026489</v>
+        <v>1.08910810947418</v>
       </c>
       <c r="H346" t="n">
         <v>14320</v>
@@ -10461,7 +10461,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G348" t="n">
-        <v>1.11571800708771</v>
+        <v>1.115718126297</v>
       </c>
       <c r="H348" t="n">
         <v>15070</v>
@@ -10490,7 +10490,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G349" t="n">
-        <v>1.12522172927856</v>
+        <v>1.12522161006927</v>
       </c>
       <c r="H349" t="n">
         <v>11135</v>
@@ -10577,7 +10577,7 @@
         <v>1.13300001621246</v>
       </c>
       <c r="G352" t="n">
-        <v>1.07675349712372</v>
+        <v>1.07675337791443</v>
       </c>
       <c r="H352" t="n">
         <v>56977</v>
@@ -10606,7 +10606,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G353" t="n">
-        <v>1.07770371437073</v>
+        <v>1.07770383358002</v>
       </c>
       <c r="H353" t="n">
         <v>33956</v>
@@ -10693,7 +10693,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G356" t="n">
-        <v>1.09385979175568</v>
+        <v>1.09385991096497</v>
       </c>
       <c r="H356" t="n">
         <v>510</v>
@@ -10722,7 +10722,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G357" t="n">
-        <v>1.07010102272034</v>
+        <v>1.07010090351105</v>
       </c>
       <c r="H357" t="n">
         <v>20350</v>
@@ -10751,7 +10751,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H358" t="n">
         <v>39402</v>
@@ -10867,7 +10867,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G362" t="n">
-        <v>1.09956204891205</v>
+        <v>1.09956192970276</v>
       </c>
       <c r="H362" t="n">
         <v>393819</v>
@@ -10925,7 +10925,7 @@
         <v>1.12699997425079</v>
       </c>
       <c r="G364" t="n">
-        <v>1.07105123996735</v>
+        <v>1.07105135917664</v>
       </c>
       <c r="H364" t="n">
         <v>27841</v>
@@ -11012,7 +11012,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G367" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H367" t="n">
         <v>43857</v>
@@ -11070,7 +11070,7 @@
         <v>1.10899996757507</v>
       </c>
       <c r="G369" t="n">
-        <v>1.05394494533539</v>
+        <v>1.0539448261261</v>
       </c>
       <c r="H369" t="n">
         <v>12555</v>
@@ -11128,7 +11128,7 @@
         <v>1.10099995136261</v>
       </c>
       <c r="G371" t="n">
-        <v>1.04634189605713</v>
+        <v>1.04634201526642</v>
       </c>
       <c r="H371" t="n">
         <v>16691</v>
@@ -11157,7 +11157,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G372" t="n">
-        <v>1.05109393596649</v>
+        <v>1.0510938167572</v>
       </c>
       <c r="H372" t="n">
         <v>1157</v>
@@ -11186,7 +11186,7 @@
         <v>1.10599994659424</v>
       </c>
       <c r="G373" t="n">
-        <v>1.05109393596649</v>
+        <v>1.0510938167572</v>
       </c>
       <c r="H373" t="n">
         <v>12141</v>
@@ -11215,7 +11215,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G374" t="n">
-        <v>1.09385979175568</v>
+        <v>1.09385991096497</v>
       </c>
       <c r="H374" t="n">
         <v>270010</v>
@@ -11244,7 +11244,7 @@
         <v>1.14900004863739</v>
       </c>
       <c r="G375" t="n">
-        <v>1.09195911884308</v>
+        <v>1.09195923805237</v>
       </c>
       <c r="H375" t="n">
         <v>91832</v>
@@ -11273,7 +11273,7 @@
         <v>1.14100003242493</v>
       </c>
       <c r="G376" t="n">
-        <v>1.08435642719269</v>
+        <v>1.0843563079834</v>
       </c>
       <c r="H376" t="n">
         <v>26349</v>
@@ -11302,7 +11302,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G377" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H377" t="n">
         <v>31617</v>
@@ -11331,7 +11331,7 @@
         <v>1.13300001621246</v>
       </c>
       <c r="G378" t="n">
-        <v>1.07675349712372</v>
+        <v>1.07675337791443</v>
       </c>
       <c r="H378" t="n">
         <v>8636</v>
@@ -11389,7 +11389,7 @@
         <v>1.14900004863739</v>
       </c>
       <c r="G380" t="n">
-        <v>1.09195911884308</v>
+        <v>1.09195923805237</v>
       </c>
       <c r="H380" t="n">
         <v>3130</v>
@@ -11447,7 +11447,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G382" t="n">
-        <v>1.09005844593048</v>
+        <v>1.09005832672119</v>
       </c>
       <c r="H382" t="n">
         <v>16300</v>
@@ -11476,7 +11476,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G383" t="n">
-        <v>1.08340585231781</v>
+        <v>1.0834059715271</v>
       </c>
       <c r="H383" t="n">
         <v>60477</v>
@@ -11505,7 +11505,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G384" t="n">
-        <v>1.09290933609009</v>
+        <v>1.09290945529938</v>
       </c>
       <c r="H384" t="n">
         <v>8937</v>
@@ -11534,7 +11534,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G385" t="n">
-        <v>1.12617194652557</v>
+        <v>1.12617182731628</v>
       </c>
       <c r="H385" t="n">
         <v>18124</v>
@@ -11592,7 +11592,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G387" t="n">
-        <v>1.11001586914062</v>
+        <v>1.11001598834991</v>
       </c>
       <c r="H387" t="n">
         <v>40810</v>
@@ -11621,7 +11621,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G388" t="n">
-        <v>1.14042735099792</v>
+        <v>1.14042747020721</v>
       </c>
       <c r="H388" t="n">
         <v>38769</v>
@@ -11737,7 +11737,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G392" t="n">
-        <v>1.17464017868042</v>
+        <v>1.17464005947113</v>
       </c>
       <c r="H392" t="n">
         <v>75009</v>
@@ -11766,7 +11766,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G393" t="n">
-        <v>1.14042735099792</v>
+        <v>1.14042747020721</v>
       </c>
       <c r="H393" t="n">
         <v>24599</v>
@@ -11795,7 +11795,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G394" t="n">
-        <v>1.12427115440369</v>
+        <v>1.12427127361298</v>
       </c>
       <c r="H394" t="n">
         <v>33424</v>
@@ -11853,7 +11853,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G396" t="n">
-        <v>1.14232790470123</v>
+        <v>1.14232814311981</v>
       </c>
       <c r="H396" t="n">
         <v>29872</v>
@@ -11882,7 +11882,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G397" t="n">
-        <v>1.14898061752319</v>
+        <v>1.1489804983139</v>
       </c>
       <c r="H397" t="n">
         <v>985</v>
@@ -11998,7 +11998,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G401" t="n">
-        <v>1.14042735099792</v>
+        <v>1.14042747020721</v>
       </c>
       <c r="H401" t="n">
         <v>11690</v>
@@ -12027,7 +12027,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G402" t="n">
-        <v>1.14042735099792</v>
+        <v>1.14042747020721</v>
       </c>
       <c r="H402" t="n">
         <v>13119</v>
@@ -12085,7 +12085,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G404" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H404" t="n">
         <v>22250</v>
@@ -12114,7 +12114,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H405" t="n">
         <v>15760</v>
@@ -12143,7 +12143,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G406" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G407" t="n">
-        <v>1.11571800708771</v>
+        <v>1.115718126297</v>
       </c>
       <c r="H407" t="n">
         <v>7147</v>
@@ -12230,7 +12230,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G409" t="n">
-        <v>1.1147677898407</v>
+        <v>1.11476767063141</v>
       </c>
       <c r="H409" t="n">
         <v>2481</v>
@@ -12259,7 +12259,7 @@
         <v>1.15299999713898</v>
       </c>
       <c r="G410" t="n">
-        <v>1.09576046466827</v>
+        <v>1.09576070308685</v>
       </c>
       <c r="H410" t="n">
         <v>2558</v>
@@ -12288,7 +12288,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G411" t="n">
-        <v>1.12617194652557</v>
+        <v>1.12617182731628</v>
       </c>
       <c r="H411" t="n">
         <v>7071</v>
@@ -12317,7 +12317,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G412" t="n">
-        <v>1.11951947212219</v>
+        <v>1.1195193529129</v>
       </c>
       <c r="H412" t="n">
         <v>16500</v>
@@ -12346,7 +12346,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G413" t="n">
-        <v>1.1138174533844</v>
+        <v>1.11381733417511</v>
       </c>
       <c r="H413" t="n">
         <v>2500</v>
@@ -12404,7 +12404,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G415" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H415" t="n">
         <v>1660</v>
@@ -12491,7 +12491,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G418" t="n">
-        <v>1.1109664440155</v>
+        <v>1.11096632480621</v>
       </c>
       <c r="H418" t="n">
         <v>2516</v>
@@ -12549,7 +12549,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G420" t="n">
-        <v>1.11951947212219</v>
+        <v>1.1195193529129</v>
       </c>
       <c r="H420" t="n">
         <v>29208</v>
@@ -12578,7 +12578,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G421" t="n">
-        <v>1.14898061752319</v>
+        <v>1.1489804983139</v>
       </c>
       <c r="H421" t="n">
         <v>132162</v>
@@ -12694,7 +12694,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H425" t="n">
         <v>23167</v>
@@ -12723,7 +12723,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G426" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H426" t="n">
         <v>2930</v>
@@ -12752,7 +12752,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G427" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H427" t="n">
         <v>23775</v>
@@ -12810,7 +12810,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G429" t="n">
-        <v>1.12427115440369</v>
+        <v>1.12427127361298</v>
       </c>
       <c r="H429" t="n">
         <v>17930</v>
@@ -12839,7 +12839,7 @@
         <v>1.18099999427795</v>
       </c>
       <c r="G430" t="n">
-        <v>1.12237060070038</v>
+        <v>1.12237071990967</v>
       </c>
       <c r="H430" t="n">
         <v>13326</v>
@@ -12868,7 +12868,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G431" t="n">
-        <v>1.13472509384155</v>
+        <v>1.13472521305084</v>
       </c>
       <c r="H431" t="n">
         <v>4925</v>
@@ -12897,7 +12897,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G432" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H432" t="n">
         <v>23557</v>
@@ -13013,7 +13013,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G436" t="n">
-        <v>1.1147677898407</v>
+        <v>1.11476767063141</v>
       </c>
       <c r="H436" t="n">
         <v>4639</v>
@@ -13042,7 +13042,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G437" t="n">
-        <v>1.12522172927856</v>
+        <v>1.12522161006927</v>
       </c>
       <c r="H437" t="n">
         <v>13177</v>
@@ -13100,7 +13100,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>1.12522172927856</v>
+        <v>1.12522161006927</v>
       </c>
       <c r="H439" t="n">
         <v>55175</v>
@@ -13129,7 +13129,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G440" t="n">
-        <v>1.11571800708771</v>
+        <v>1.115718126297</v>
       </c>
       <c r="H440" t="n">
         <v>9872</v>
@@ -13158,7 +13158,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G441" t="n">
-        <v>1.11286699771881</v>
+        <v>1.11286687850952</v>
       </c>
       <c r="H441" t="n">
         <v>9775</v>
@@ -13245,7 +13245,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G444" t="n">
-        <v>1.11001586914062</v>
+        <v>1.11001598834991</v>
       </c>
       <c r="H444" t="n">
         <v>1482</v>
@@ -13274,7 +13274,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H445" t="n">
         <v>19891</v>
@@ -13303,7 +13303,7 @@
         <v>1.18099999427795</v>
       </c>
       <c r="G446" t="n">
-        <v>1.12237060070038</v>
+        <v>1.12237071990967</v>
       </c>
       <c r="H446" t="n">
         <v>45363</v>
@@ -13419,7 +13419,7 @@
         <v>1.21099996566772</v>
       </c>
       <c r="G450" t="n">
-        <v>1.1508811712265</v>
+        <v>1.15088105201721</v>
       </c>
       <c r="H450" t="n">
         <v>8668</v>
@@ -13448,7 +13448,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G451" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H451" t="n">
         <v>11298</v>
@@ -13506,7 +13506,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G453" t="n">
-        <v>1.20505166053772</v>
+        <v>1.20505154132843</v>
       </c>
       <c r="H453" t="n">
         <v>91082</v>
@@ -13593,7 +13593,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G456" t="n">
-        <v>1.17178905010223</v>
+        <v>1.17178916931152</v>
       </c>
       <c r="H456" t="n">
         <v>20072</v>
@@ -13680,7 +13680,7 @@
         <v>1.23800003528595</v>
       </c>
       <c r="G459" t="n">
-        <v>1.17654085159302</v>
+        <v>1.17654097080231</v>
       </c>
       <c r="H459" t="n">
         <v>19287</v>
@@ -13738,7 +13738,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G461" t="n">
-        <v>1.17464017868042</v>
+        <v>1.17464005947113</v>
       </c>
       <c r="H461" t="n">
         <v>4453</v>
@@ -13767,7 +13767,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H462" t="n">
         <v>20101</v>
@@ -13999,7 +13999,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G470" t="n">
-        <v>1.19079613685608</v>
+        <v>1.19079625606537</v>
       </c>
       <c r="H470" t="n">
         <v>256139</v>
@@ -14028,7 +14028,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G471" t="n">
-        <v>1.19364726543427</v>
+        <v>1.19364714622498</v>
       </c>
       <c r="H471" t="n">
         <v>268871</v>
@@ -14086,7 +14086,7 @@
         <v>1.25300002098083</v>
       </c>
       <c r="G473" t="n">
-        <v>1.19079613685608</v>
+        <v>1.19079625606537</v>
       </c>
       <c r="H473" t="n">
         <v>23592</v>
@@ -14144,7 +14144,7 @@
         <v>1.26199996471405</v>
       </c>
       <c r="G475" t="n">
-        <v>1.19934940338135</v>
+        <v>1.19934928417206</v>
       </c>
       <c r="H475" t="n">
         <v>62864</v>
@@ -14202,7 +14202,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>1.14993095397949</v>
+        <v>1.1499308347702</v>
       </c>
       <c r="H477" t="n">
         <v>41948</v>
@@ -14260,7 +14260,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G479" t="n">
-        <v>1.1147677898407</v>
+        <v>1.11476767063141</v>
       </c>
       <c r="H479" t="n">
         <v>37049</v>
@@ -14318,7 +14318,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G481" t="n">
-        <v>1.11951947212219</v>
+        <v>1.1195193529129</v>
       </c>
       <c r="H481" t="n">
         <v>25391</v>
@@ -14376,7 +14376,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G483" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H483" t="n">
         <v>4602</v>
@@ -14405,7 +14405,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G484" t="n">
-        <v>1.15563309192657</v>
+        <v>1.15563297271729</v>
       </c>
       <c r="H484" t="n">
         <v>10800</v>
@@ -14434,7 +14434,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G485" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H485" t="n">
         <v>5311</v>
@@ -14463,7 +14463,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G486" t="n">
-        <v>1.1138174533844</v>
+        <v>1.11381733417511</v>
       </c>
       <c r="H486" t="n">
         <v>6100</v>
@@ -14492,7 +14492,7 @@
         <v>1.19400000572205</v>
       </c>
       <c r="G487" t="n">
-        <v>1.13472509384155</v>
+        <v>1.13472521305084</v>
       </c>
       <c r="H487" t="n">
         <v>27842</v>
@@ -14521,7 +14521,7 @@
         <v>1.19700002670288</v>
       </c>
       <c r="G488" t="n">
-        <v>1.13757634162903</v>
+        <v>1.13757622241974</v>
       </c>
       <c r="H488" t="n">
         <v>13286</v>
@@ -14608,7 +14608,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G491" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H491" t="n">
         <v>3613</v>
@@ -14724,7 +14724,7 @@
         <v>1.17299997806549</v>
       </c>
       <c r="G495" t="n">
-        <v>1.1147677898407</v>
+        <v>1.11476767063141</v>
       </c>
       <c r="H495" t="n">
         <v>2345</v>
@@ -14753,7 +14753,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G496" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H496" t="n">
         <v>2297</v>
@@ -14782,7 +14782,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G497" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H497" t="n">
         <v>13455</v>
@@ -14811,7 +14811,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G498" t="n">
-        <v>1.1109664440155</v>
+        <v>1.11096632480621</v>
       </c>
       <c r="H498" t="n">
         <v>4720</v>
@@ -14840,7 +14840,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G499" t="n">
-        <v>1.1109664440155</v>
+        <v>1.11096632480621</v>
       </c>
       <c r="H499" t="n">
         <v>12294</v>
@@ -14869,7 +14869,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G500" t="n">
-        <v>1.1109664440155</v>
+        <v>1.11096632480621</v>
       </c>
       <c r="H500" t="n">
         <v>20280</v>
@@ -14898,7 +14898,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G501" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H501" t="n">
         <v>2321</v>
@@ -14956,7 +14956,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H503" t="n">
         <v>52184</v>
@@ -15043,7 +15043,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H506" t="n">
         <v>7586</v>
@@ -15072,7 +15072,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G507" t="n">
-        <v>1.10051238536835</v>
+        <v>1.10051226615906</v>
       </c>
       <c r="H507" t="n">
         <v>2976</v>
@@ -15130,7 +15130,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G509" t="n">
-        <v>1.1109664440155</v>
+        <v>1.11096632480621</v>
       </c>
       <c r="H509" t="n">
         <v>23824</v>
@@ -15159,7 +15159,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G510" t="n">
-        <v>1.12427115440369</v>
+        <v>1.12427127361298</v>
       </c>
       <c r="H510" t="n">
         <v>3049</v>
@@ -15217,7 +15217,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G512" t="n">
-        <v>1.1166684627533</v>
+        <v>1.11666834354401</v>
       </c>
       <c r="H512" t="n">
         <v>19476</v>
@@ -15304,7 +15304,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G515" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H515" t="n">
         <v>9430</v>
@@ -15333,7 +15333,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G516" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H516" t="n">
         <v>47735</v>
@@ -15362,7 +15362,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G517" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H517" t="n">
         <v>37428</v>
@@ -15391,7 +15391,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G518" t="n">
-        <v>1.1166684627533</v>
+        <v>1.11666834354401</v>
       </c>
       <c r="H518" t="n">
         <v>40844</v>
@@ -15420,7 +15420,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H519" t="n">
         <v>26920</v>
@@ -15478,7 +15478,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G521" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H521" t="n">
         <v>23513</v>
@@ -15507,7 +15507,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G522" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H522" t="n">
         <v>11085</v>
@@ -15536,7 +15536,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G523" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H523" t="n">
         <v>10943</v>
@@ -15565,7 +15565,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G524" t="n">
-        <v>1.12617194652557</v>
+        <v>1.12617182731628</v>
       </c>
       <c r="H524" t="n">
         <v>49480</v>
@@ -15594,7 +15594,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G525" t="n">
-        <v>1.12617194652557</v>
+        <v>1.12617182731628</v>
       </c>
       <c r="H525" t="n">
         <v>39363</v>
@@ -15623,7 +15623,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G526" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H526" t="n">
         <v>8087</v>
@@ -15652,7 +15652,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G527" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H527" t="n">
         <v>10437</v>
@@ -15681,7 +15681,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G528" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H528" t="n">
         <v>20786</v>
@@ -15710,7 +15710,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G529" t="n">
-        <v>1.09290933609009</v>
+        <v>1.09290945529938</v>
       </c>
       <c r="H529" t="n">
         <v>9700</v>
@@ -15739,7 +15739,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G530" t="n">
-        <v>1.1166684627533</v>
+        <v>1.11666834354401</v>
       </c>
       <c r="H530" t="n">
         <v>32447</v>
@@ -15797,7 +15797,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G532" t="n">
-        <v>1.09290933609009</v>
+        <v>1.09290945529938</v>
       </c>
       <c r="H532" t="n">
         <v>3262</v>
@@ -15826,7 +15826,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G533" t="n">
-        <v>1.09290933609009</v>
+        <v>1.09290945529938</v>
       </c>
       <c r="H533" t="n">
         <v>18204</v>
@@ -15855,7 +15855,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G534" t="n">
-        <v>1.09290933609009</v>
+        <v>1.09290945529938</v>
       </c>
       <c r="H534" t="n">
         <v>10012</v>
@@ -15884,7 +15884,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G535" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H535" t="n">
         <v>6800</v>
@@ -15913,7 +15913,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G536" t="n">
-        <v>1.06439888477325</v>
+        <v>1.06439876556396</v>
       </c>
       <c r="H536" t="n">
         <v>8150</v>
@@ -15942,7 +15942,7 @@
         <v>1.125</v>
       </c>
       <c r="G537" t="n">
-        <v>1.06915056705475</v>
+        <v>1.06915068626404</v>
       </c>
       <c r="H537" t="n">
         <v>21910</v>
@@ -15971,7 +15971,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G538" t="n">
-        <v>1.08340585231781</v>
+        <v>1.0834059715271</v>
       </c>
       <c r="H538" t="n">
         <v>4582</v>
@@ -16000,7 +16000,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.08340585231781</v>
+        <v>1.0834059715271</v>
       </c>
       <c r="H539" t="n">
         <v>29</v>
@@ -16058,7 +16058,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H541" t="n">
         <v>1790</v>
@@ -16116,7 +16116,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G543" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H543" t="n">
         <v>1293</v>
@@ -16290,7 +16290,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G549" t="n">
-        <v>1.04539167881012</v>
+        <v>1.04539179801941</v>
       </c>
       <c r="H549" t="n">
         <v>3739</v>
@@ -16319,7 +16319,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G550" t="n">
-        <v>1.04063987731934</v>
+        <v>1.04063999652863</v>
       </c>
       <c r="H550" t="n">
         <v>1925</v>
@@ -16406,7 +16406,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G553" t="n">
-        <v>1.04539167881012</v>
+        <v>1.04539179801941</v>
       </c>
       <c r="H553" t="n">
         <v>10964</v>
@@ -16435,7 +16435,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G554" t="n">
-        <v>1.02163279056549</v>
+        <v>1.02163290977478</v>
       </c>
       <c r="H554" t="n">
         <v>3821</v>
@@ -16522,7 +16522,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H557" t="n">
         <v>5187</v>
@@ -16551,7 +16551,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G558" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -16609,7 +16609,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G560" t="n">
-        <v>1.04539167881012</v>
+        <v>1.04539179801941</v>
       </c>
       <c r="H560" t="n">
         <v>7000</v>
@@ -16638,7 +16638,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G561" t="n">
-        <v>1.04539167881012</v>
+        <v>1.04539179801941</v>
       </c>
       <c r="H561" t="n">
         <v>389</v>
@@ -16667,7 +16667,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G562" t="n">
-        <v>1.04063987731934</v>
+        <v>1.04063999652863</v>
       </c>
       <c r="H562" t="n">
         <v>7020</v>
@@ -16725,7 +16725,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G564" t="n">
-        <v>1.04063987731934</v>
+        <v>1.04063999652863</v>
       </c>
       <c r="H564" t="n">
         <v>531</v>
@@ -16754,7 +16754,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G565" t="n">
-        <v>1.04539167881012</v>
+        <v>1.04539179801941</v>
       </c>
       <c r="H565" t="n">
         <v>3022</v>
@@ -16783,7 +16783,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G566" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H566" t="n">
         <v>13910</v>
@@ -16870,7 +16870,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G569" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H569" t="n">
         <v>6375</v>
@@ -16899,7 +16899,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G570" t="n">
-        <v>1.08340585231781</v>
+        <v>1.0834059715271</v>
       </c>
       <c r="H570" t="n">
         <v>4666</v>
@@ -16928,7 +16928,7 @@
         <v>1.125</v>
       </c>
       <c r="G571" t="n">
-        <v>1.06915056705475</v>
+        <v>1.06915068626404</v>
       </c>
       <c r="H571" t="n">
         <v>7222</v>
@@ -16957,7 +16957,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G572" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H572" t="n">
         <v>290</v>
@@ -17102,7 +17102,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G577" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H577" t="n">
         <v>67253</v>
@@ -17189,7 +17189,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G580" t="n">
-        <v>1.06439888477325</v>
+        <v>1.06439876556396</v>
       </c>
       <c r="H580" t="n">
         <v>16675</v>
@@ -17392,7 +17392,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G587" t="n">
-        <v>1.06439888477325</v>
+        <v>1.06439876556396</v>
       </c>
       <c r="H587" t="n">
         <v>13671</v>
@@ -17421,7 +17421,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G588" t="n">
-        <v>1.04063987731934</v>
+        <v>1.04063999652863</v>
       </c>
       <c r="H588" t="n">
         <v>18593</v>
@@ -17508,7 +17508,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G591" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H591" t="n">
         <v>4775</v>
@@ -17537,7 +17537,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G592" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H592" t="n">
         <v>834</v>
@@ -17566,7 +17566,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G593" t="n">
-        <v>1.04539167881012</v>
+        <v>1.04539179801941</v>
       </c>
       <c r="H593" t="n">
         <v>5693</v>
@@ -17653,7 +17653,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G596" t="n">
-        <v>1.02163279056549</v>
+        <v>1.02163290977478</v>
       </c>
       <c r="H596" t="n">
         <v>9288</v>
@@ -17798,7 +17798,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G601" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H601" t="n">
         <v>7370</v>
@@ -17827,7 +17827,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G602" t="n">
-        <v>1.02163279056549</v>
+        <v>1.02163290977478</v>
       </c>
       <c r="H602" t="n">
         <v>3010</v>
@@ -17856,7 +17856,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G603" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H603" t="n">
         <v>162004</v>
@@ -17885,7 +17885,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G604" t="n">
-        <v>1.06439888477325</v>
+        <v>1.06439876556396</v>
       </c>
       <c r="H604" t="n">
         <v>34087</v>
@@ -17943,7 +17943,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G606" t="n">
-        <v>1.04063987731934</v>
+        <v>1.04063999652863</v>
       </c>
       <c r="H606" t="n">
         <v>5902</v>
@@ -17972,7 +17972,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G607" t="n">
-        <v>1.00737738609314</v>
+        <v>1.00737726688385</v>
       </c>
       <c r="H607" t="n">
         <v>24997</v>
@@ -18001,7 +18001,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G608" t="n">
-        <v>1.02163279056549</v>
+        <v>1.02163290977478</v>
       </c>
       <c r="H608" t="n">
         <v>7794</v>
@@ -18030,7 +18030,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G609" t="n">
-        <v>1.04539167881012</v>
+        <v>1.04539179801941</v>
       </c>
       <c r="H609" t="n">
         <v>12761</v>
@@ -18059,7 +18059,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G610" t="n">
-        <v>1.0121294260025</v>
+        <v>1.01212930679321</v>
       </c>
       <c r="H610" t="n">
         <v>4398</v>
@@ -18088,7 +18088,7 @@
         <v>1.09500002861023</v>
       </c>
       <c r="G611" t="n">
-        <v>1.04063987731934</v>
+        <v>1.04063999652863</v>
       </c>
       <c r="H611" t="n">
         <v>11268</v>
@@ -18117,7 +18117,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G612" t="n">
-        <v>1.02163279056549</v>
+        <v>1.02163290977478</v>
       </c>
       <c r="H612" t="n">
         <v>39408</v>
@@ -18146,7 +18146,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H613" t="n">
         <v>16207</v>
@@ -18233,7 +18233,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G616" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H616" t="n">
         <v>10854</v>
@@ -18262,7 +18262,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G617" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H617" t="n">
         <v>22297</v>
@@ -18407,7 +18407,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G622" t="n">
-        <v>0.948455452919006</v>
+        <v>0.948455393314362</v>
       </c>
       <c r="H622" t="n">
         <v>10698</v>
@@ -18436,7 +18436,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H623" t="n">
         <v>2010</v>
@@ -18465,7 +18465,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18639,7 +18639,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G630" t="n">
-        <v>0.948455452919006</v>
+        <v>0.948455393314362</v>
       </c>
       <c r="H630" t="n">
         <v>5204</v>
@@ -18668,7 +18668,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G631" t="n">
-        <v>0.944653987884521</v>
+        <v>0.944653928279877</v>
       </c>
       <c r="H631" t="n">
         <v>2000</v>
@@ -18929,7 +18929,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G640" t="n">
-        <v>0.929448306560516</v>
+        <v>0.929448187351227</v>
       </c>
       <c r="H640" t="n">
         <v>7994</v>
@@ -18958,7 +18958,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G641" t="n">
-        <v>0.929448306560516</v>
+        <v>0.929448187351227</v>
       </c>
       <c r="H641" t="n">
         <v>0</v>
@@ -19045,7 +19045,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G644" t="n">
-        <v>0.938951849937439</v>
+        <v>0.938951790332794</v>
       </c>
       <c r="H644" t="n">
         <v>822</v>
@@ -19074,7 +19074,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G645" t="n">
-        <v>0.937051117420197</v>
+        <v>0.937051177024841</v>
       </c>
       <c r="H645" t="n">
         <v>2898</v>
@@ -19277,7 +19277,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G652" t="n">
-        <v>0.923746168613434</v>
+        <v>0.923746109008789</v>
       </c>
       <c r="H652" t="n">
         <v>3847</v>
@@ -19364,7 +19364,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G655" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H655" t="n">
         <v>4810</v>
@@ -19422,7 +19422,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G657" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H657" t="n">
         <v>2580</v>
@@ -19712,7 +19712,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G667" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H667" t="n">
         <v>3010</v>
@@ -19741,7 +19741,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G668" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H668" t="n">
         <v>1315</v>
@@ -19770,7 +19770,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G669" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H669" t="n">
         <v>0</v>
@@ -19799,7 +19799,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G670" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H670" t="n">
         <v>1010</v>
@@ -19828,7 +19828,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G671" t="n">
-        <v>0.891434073448181</v>
+        <v>0.891434013843536</v>
       </c>
       <c r="H671" t="n">
         <v>960</v>
@@ -19857,7 +19857,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G672" t="n">
-        <v>0.891434073448181</v>
+        <v>0.891434013843536</v>
       </c>
       <c r="H672" t="n">
         <v>10828</v>
@@ -19915,7 +19915,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G674" t="n">
-        <v>0.891434073448181</v>
+        <v>0.891434013843536</v>
       </c>
       <c r="H674" t="n">
         <v>8328</v>
@@ -19944,7 +19944,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G675" t="n">
-        <v>0.891434073448181</v>
+        <v>0.891434013843536</v>
       </c>
       <c r="H675" t="n">
         <v>524</v>
@@ -19973,7 +19973,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G676" t="n">
-        <v>0.891434073448181</v>
+        <v>0.891434013843536</v>
       </c>
       <c r="H676" t="n">
         <v>0</v>
@@ -20002,7 +20002,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G677" t="n">
-        <v>0.891434073448181</v>
+        <v>0.891434013843536</v>
       </c>
       <c r="H677" t="n">
         <v>2001</v>
@@ -20118,7 +20118,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G681" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H681" t="n">
         <v>1709</v>
@@ -20147,7 +20147,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G682" t="n">
-        <v>0.866724789142609</v>
+        <v>0.866724729537964</v>
       </c>
       <c r="H682" t="n">
         <v>1730</v>
@@ -20205,7 +20205,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G684" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H684" t="n">
         <v>35108</v>
@@ -20263,7 +20263,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G686" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753195762634</v>
       </c>
       <c r="H686" t="n">
         <v>8065</v>
@@ -20495,7 +20495,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G694" t="n">
-        <v>0.929448306560516</v>
+        <v>0.929448187351227</v>
       </c>
       <c r="H694" t="n">
         <v>5765</v>
@@ -20669,7 +20669,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G700" t="n">
-        <v>0.929448306560516</v>
+        <v>0.929448187351227</v>
       </c>
       <c r="H700" t="n">
         <v>89315</v>
@@ -20959,7 +20959,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G710" t="n">
-        <v>0.826809763908386</v>
+        <v>0.826809823513031</v>
       </c>
       <c r="H710" t="n">
         <v>24474</v>
@@ -20988,7 +20988,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G711" t="n">
-        <v>0.828710436820984</v>
+        <v>0.828710556030273</v>
       </c>
       <c r="H711" t="n">
         <v>1614</v>
@@ -21133,7 +21133,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G716" t="n">
-        <v>0.792597055435181</v>
+        <v>0.792596995830536</v>
       </c>
       <c r="H716" t="n">
         <v>12077</v>
@@ -21191,7 +21191,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G718" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H718" t="n">
         <v>44205</v>
@@ -21220,7 +21220,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G719" t="n">
-        <v>0.802100479602814</v>
+        <v>0.802100539207458</v>
       </c>
       <c r="H719" t="n">
         <v>4618</v>
@@ -21249,7 +21249,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G720" t="n">
-        <v>0.802100479602814</v>
+        <v>0.802100539207458</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21394,7 +21394,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G725" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497668743134</v>
       </c>
       <c r="H725" t="n">
         <v>1252</v>
@@ -21452,7 +21452,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G727" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H727" t="n">
         <v>699</v>
@@ -21510,7 +21510,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G729" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H729" t="n">
         <v>1837</v>
@@ -21655,7 +21655,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G734" t="n">
-        <v>0.804001212120056</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H734" t="n">
         <v>15413</v>
@@ -21713,7 +21713,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G736" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391254901886</v>
       </c>
       <c r="H736" t="n">
         <v>1019</v>
@@ -21771,7 +21771,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G738" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185513973236</v>
       </c>
       <c r="H738" t="n">
         <v>1300</v>
@@ -21800,7 +21800,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G739" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185513973236</v>
       </c>
       <c r="H739" t="n">
         <v>879</v>
@@ -21887,7 +21887,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G742" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497668743134</v>
       </c>
       <c r="H742" t="n">
         <v>5461</v>
@@ -21916,7 +21916,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G743" t="n">
-        <v>0.802100479602814</v>
+        <v>0.802100539207458</v>
       </c>
       <c r="H743" t="n">
         <v>134</v>
@@ -21945,7 +21945,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G744" t="n">
-        <v>0.792597055435181</v>
+        <v>0.792596995830536</v>
       </c>
       <c r="H744" t="n">
         <v>622</v>
@@ -21974,7 +21974,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G745" t="n">
-        <v>0.792597055435181</v>
+        <v>0.792596995830536</v>
       </c>
       <c r="H745" t="n">
         <v>11</v>
@@ -22061,7 +22061,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G748" t="n">
-        <v>0.802100479602814</v>
+        <v>0.802100539207458</v>
       </c>
       <c r="H748" t="n">
         <v>3958</v>
@@ -22090,7 +22090,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G749" t="n">
-        <v>0.802100479602814</v>
+        <v>0.802100539207458</v>
       </c>
       <c r="H749" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G750" t="n">
-        <v>0.792597055435181</v>
+        <v>0.792596995830536</v>
       </c>
       <c r="H750" t="n">
         <v>1370</v>
@@ -22177,7 +22177,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G752" t="n">
-        <v>0.792597055435181</v>
+        <v>0.792596995830536</v>
       </c>
       <c r="H752" t="n">
         <v>164</v>
@@ -22206,7 +22206,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G753" t="n">
-        <v>0.792597055435181</v>
+        <v>0.792596995830536</v>
       </c>
       <c r="H753" t="n">
         <v>2035</v>
@@ -22235,7 +22235,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G754" t="n">
-        <v>0.773589909076691</v>
+        <v>0.773589849472046</v>
       </c>
       <c r="H754" t="n">
         <v>757</v>
@@ -22293,7 +22293,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G756" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497668743134</v>
       </c>
       <c r="H756" t="n">
         <v>3078</v>
@@ -22322,7 +22322,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G757" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497668743134</v>
       </c>
       <c r="H757" t="n">
         <v>2150</v>
@@ -22351,7 +22351,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G758" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497668743134</v>
       </c>
       <c r="H758" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G760" t="n">
-        <v>0.792597055435181</v>
+        <v>0.792596995830536</v>
       </c>
       <c r="H760" t="n">
         <v>6813</v>
@@ -22438,7 +22438,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G761" t="n">
-        <v>0.792597055435181</v>
+        <v>0.792596995830536</v>
       </c>
       <c r="H761" t="n">
         <v>0</v>
@@ -22670,7 +22670,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G769" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497668743134</v>
       </c>
       <c r="H769" t="n">
         <v>16652</v>
@@ -22699,7 +22699,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G770" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497668743134</v>
       </c>
       <c r="H770" t="n">
         <v>9656</v>
@@ -22757,7 +22757,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G772" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497668743134</v>
       </c>
       <c r="H772" t="n">
         <v>3569</v>
@@ -22786,7 +22786,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G773" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497668743134</v>
       </c>
       <c r="H773" t="n">
         <v>12</v>
@@ -22873,7 +22873,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G776" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H776" t="n">
         <v>24392</v>
@@ -22960,7 +22960,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G779" t="n">
-        <v>0.872426867485046</v>
+        <v>0.872426927089691</v>
       </c>
       <c r="H779" t="n">
         <v>86606</v>
@@ -22989,7 +22989,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G780" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H780" t="n">
         <v>20726</v>
@@ -23105,7 +23105,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G784" t="n">
-        <v>0.862923324108124</v>
+        <v>0.862923383712769</v>
       </c>
       <c r="H784" t="n">
         <v>7352</v>
@@ -23192,7 +23192,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>0.862923324108124</v>
+        <v>0.862923383712769</v>
       </c>
       <c r="H787" t="n">
         <v>5312</v>
@@ -23366,7 +23366,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G793" t="n">
-        <v>0.843916237354279</v>
+        <v>0.843916296958923</v>
       </c>
       <c r="H793" t="n">
         <v>4060</v>
@@ -23453,7 +23453,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G796" t="n">
-        <v>0.819206953048706</v>
+        <v>0.819206893444061</v>
       </c>
       <c r="H796" t="n">
         <v>11904</v>
@@ -23511,7 +23511,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G798" t="n">
-        <v>0.862923324108124</v>
+        <v>0.862923383712769</v>
       </c>
       <c r="H798" t="n">
         <v>140001</v>
@@ -23540,7 +23540,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G799" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H799" t="n">
         <v>38915</v>
@@ -23598,7 +23598,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G801" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H801" t="n">
         <v>16877</v>
@@ -23627,7 +23627,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G802" t="n">
-        <v>0.862923324108124</v>
+        <v>0.862923383712769</v>
       </c>
       <c r="H802" t="n">
         <v>7726</v>
@@ -23656,7 +23656,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G803" t="n">
-        <v>0.887632608413696</v>
+        <v>0.887632668018341</v>
       </c>
       <c r="H803" t="n">
         <v>44684</v>
@@ -23685,7 +23685,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G804" t="n">
-        <v>0.866724789142609</v>
+        <v>0.866724729537964</v>
       </c>
       <c r="H804" t="n">
         <v>682</v>
@@ -23743,7 +23743,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>0.862923324108124</v>
+        <v>0.862923383712769</v>
       </c>
       <c r="H806" t="n">
         <v>13866</v>
@@ -23801,7 +23801,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G808" t="n">
-        <v>0.862923324108124</v>
+        <v>0.862923383712769</v>
       </c>
       <c r="H808" t="n">
         <v>2296</v>
@@ -23830,7 +23830,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G809" t="n">
-        <v>0.862923324108124</v>
+        <v>0.862923383712769</v>
       </c>
       <c r="H809" t="n">
         <v>4956</v>
@@ -23888,7 +23888,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G811" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H811" t="n">
         <v>1087</v>
@@ -23917,7 +23917,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>0.853419721126556</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H812" t="n">
         <v>14750</v>
@@ -23946,7 +23946,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G813" t="n">
-        <v>0.857221186161041</v>
+        <v>0.857221245765686</v>
       </c>
       <c r="H813" t="n">
         <v>14</v>
@@ -23975,7 +23975,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G814" t="n">
-        <v>0.857221186161041</v>
+        <v>0.857221245765686</v>
       </c>
       <c r="H814" t="n">
         <v>274</v>
@@ -24033,7 +24033,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G816" t="n">
-        <v>0.832511901855469</v>
+        <v>0.832511961460114</v>
       </c>
       <c r="H816" t="n">
         <v>13272</v>
@@ -24091,7 +24091,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>0.862923324108124</v>
+        <v>0.862923383712769</v>
       </c>
       <c r="H818" t="n">
         <v>6661</v>
@@ -24149,7 +24149,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G820" t="n">
-        <v>0.857221186161041</v>
+        <v>0.857221245765686</v>
       </c>
       <c r="H820" t="n">
         <v>4811</v>
@@ -24207,7 +24207,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>0.843916237354279</v>
+        <v>0.843916296958923</v>
       </c>
       <c r="H822" t="n">
         <v>11961</v>
@@ -24236,7 +24236,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G823" t="n">
-        <v>0.847717642784119</v>
+        <v>0.847717702388763</v>
       </c>
       <c r="H823" t="n">
         <v>12285</v>
@@ -24265,7 +24265,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G824" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H824" t="n">
         <v>520</v>
@@ -24352,7 +24352,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>0.862923324108124</v>
+        <v>0.862923383712769</v>
       </c>
       <c r="H827" t="n">
         <v>690</v>
@@ -24381,7 +24381,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G828" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H828" t="n">
         <v>10500</v>
@@ -24410,7 +24410,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G829" t="n">
-        <v>0.866724789142609</v>
+        <v>0.866724729537964</v>
       </c>
       <c r="H829" t="n">
         <v>22573</v>
@@ -24439,7 +24439,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G830" t="n">
-        <v>0.862923324108124</v>
+        <v>0.862923383712769</v>
       </c>
       <c r="H830" t="n">
         <v>10583</v>
@@ -24468,7 +24468,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G831" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H831" t="n">
         <v>22651</v>
@@ -24526,7 +24526,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G833" t="n">
-        <v>0.872426867485046</v>
+        <v>0.872426927089691</v>
       </c>
       <c r="H833" t="n">
         <v>16115</v>
@@ -24555,7 +24555,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G834" t="n">
-        <v>0.885731875896454</v>
+        <v>0.885731816291809</v>
       </c>
       <c r="H834" t="n">
         <v>3610</v>
@@ -24584,7 +24584,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G835" t="n">
-        <v>0.891434073448181</v>
+        <v>0.891434013843536</v>
       </c>
       <c r="H835" t="n">
         <v>15076</v>
@@ -24642,7 +24642,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G837" t="n">
-        <v>1.10241317749023</v>
+        <v>1.10241305828094</v>
       </c>
       <c r="H837" t="n">
         <v>521892</v>
@@ -24700,7 +24700,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G839" t="n">
-        <v>1.00737738609314</v>
+        <v>1.00737726688385</v>
       </c>
       <c r="H839" t="n">
         <v>135704</v>
@@ -24729,7 +24729,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G840" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H840" t="n">
         <v>199532</v>
@@ -24758,7 +24758,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G841" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H841" t="n">
         <v>56431</v>
@@ -24816,7 +24816,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G843" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H843" t="n">
         <v>10650</v>
@@ -24845,7 +24845,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G844" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H844" t="n">
         <v>6969</v>
@@ -24903,7 +24903,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G846" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H846" t="n">
         <v>6500</v>
@@ -24961,7 +24961,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G848" t="n">
-        <v>0.96461147069931</v>
+        <v>0.964611411094666</v>
       </c>
       <c r="H848" t="n">
         <v>8252</v>
@@ -25019,7 +25019,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G850" t="n">
-        <v>0.938951849937439</v>
+        <v>0.938951790332794</v>
       </c>
       <c r="H850" t="n">
         <v>45709</v>
@@ -25077,7 +25077,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G852" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753195762634</v>
       </c>
       <c r="H852" t="n">
         <v>18857</v>
@@ -25135,7 +25135,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G854" t="n">
-        <v>0.923746168613434</v>
+        <v>0.923746109008789</v>
       </c>
       <c r="H854" t="n">
         <v>5073</v>
@@ -25193,7 +25193,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G856" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H856" t="n">
         <v>23230</v>
@@ -25222,7 +25222,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G857" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H857" t="n">
         <v>20242</v>
@@ -25309,7 +25309,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G860" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H860" t="n">
         <v>74217</v>
@@ -25338,7 +25338,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G861" t="n">
-        <v>0.948455452919006</v>
+        <v>0.948455393314362</v>
       </c>
       <c r="H861" t="n">
         <v>21200</v>
@@ -25425,7 +25425,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G864" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H864" t="n">
         <v>58709</v>
@@ -25483,7 +25483,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G866" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H866" t="n">
         <v>19486</v>
@@ -25512,7 +25512,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G867" t="n">
-        <v>0.891434073448181</v>
+        <v>0.891434013843536</v>
       </c>
       <c r="H867" t="n">
         <v>26756</v>
@@ -25570,7 +25570,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G869" t="n">
-        <v>0.887632608413696</v>
+        <v>0.887632668018341</v>
       </c>
       <c r="H869" t="n">
         <v>6207</v>
@@ -25686,7 +25686,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G873" t="n">
-        <v>0.885731875896454</v>
+        <v>0.885731816291809</v>
       </c>
       <c r="H873" t="n">
         <v>2011</v>
@@ -25918,7 +25918,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G881" t="n">
-        <v>0.891434073448181</v>
+        <v>0.891434013843536</v>
       </c>
       <c r="H881" t="n">
         <v>5840</v>
@@ -25947,7 +25947,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G882" t="n">
-        <v>0.891434073448181</v>
+        <v>0.891434013843536</v>
       </c>
       <c r="H882" t="n">
         <v>0</v>
@@ -26034,7 +26034,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G885" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H885" t="n">
         <v>18386</v>
@@ -26063,7 +26063,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G886" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H886" t="n">
         <v>11911</v>
@@ -26092,7 +26092,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G887" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H887" t="n">
         <v>1480</v>
@@ -26150,7 +26150,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G889" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H889" t="n">
         <v>4577</v>
@@ -26179,7 +26179,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G890" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H890" t="n">
         <v>4035</v>
@@ -26208,7 +26208,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G891" t="n">
-        <v>0.857221186161041</v>
+        <v>0.857221245765686</v>
       </c>
       <c r="H891" t="n">
         <v>7770</v>
@@ -26237,7 +26237,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G892" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H892" t="n">
         <v>13605</v>
@@ -26266,7 +26266,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G893" t="n">
-        <v>0.862923324108124</v>
+        <v>0.862923383712769</v>
       </c>
       <c r="H893" t="n">
         <v>4770</v>
@@ -26324,7 +26324,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G895" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H895" t="n">
         <v>1766</v>
@@ -26353,7 +26353,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G896" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H896" t="n">
         <v>2121</v>
@@ -26382,7 +26382,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G897" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H897" t="n">
         <v>5200</v>
@@ -26440,7 +26440,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G899" t="n">
-        <v>0.862923324108124</v>
+        <v>0.862923383712769</v>
       </c>
       <c r="H899" t="n">
         <v>1400</v>
@@ -26469,7 +26469,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G900" t="n">
-        <v>0.862923324108124</v>
+        <v>0.862923383712769</v>
       </c>
       <c r="H900" t="n">
         <v>13973</v>
@@ -26498,7 +26498,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G901" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H901" t="n">
         <v>6210</v>
@@ -26527,7 +26527,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G902" t="n">
-        <v>0.853419721126556</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H902" t="n">
         <v>2624</v>
@@ -26585,7 +26585,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>0.853419721126556</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H904" t="n">
         <v>1651</v>
@@ -26672,7 +26672,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>0.853419721126556</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H907" t="n">
         <v>10040</v>
@@ -26788,7 +26788,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G911" t="n">
-        <v>0.862923324108124</v>
+        <v>0.862923383712769</v>
       </c>
       <c r="H911" t="n">
         <v>28764</v>
@@ -26817,7 +26817,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G912" t="n">
-        <v>0.847717642784119</v>
+        <v>0.847717702388763</v>
       </c>
       <c r="H912" t="n">
         <v>3225</v>
@@ -26846,7 +26846,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G913" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H913" t="n">
         <v>29501</v>
@@ -26875,7 +26875,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G914" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H914" t="n">
         <v>4867</v>
@@ -26933,7 +26933,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G916" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H916" t="n">
         <v>4611</v>
@@ -26962,7 +26962,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G917" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G918" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -27107,7 +27107,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G922" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H922" t="n">
         <v>2714</v>
@@ -27165,7 +27165,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G924" t="n">
-        <v>0.887632608413696</v>
+        <v>0.887632668018341</v>
       </c>
       <c r="H924" t="n">
         <v>33700</v>
@@ -27281,7 +27281,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G928" t="n">
-        <v>0.885731875896454</v>
+        <v>0.885731816291809</v>
       </c>
       <c r="H928" t="n">
         <v>6532</v>
@@ -27310,7 +27310,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G929" t="n">
-        <v>0.885731875896454</v>
+        <v>0.885731816291809</v>
       </c>
       <c r="H929" t="n">
         <v>13529</v>
@@ -27368,7 +27368,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G931" t="n">
-        <v>0.937051117420197</v>
+        <v>0.937051177024841</v>
       </c>
       <c r="H931" t="n">
         <v>302501</v>
@@ -27397,7 +27397,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G932" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753195762634</v>
       </c>
       <c r="H932" t="n">
         <v>68362</v>
@@ -27426,7 +27426,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G933" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H933" t="n">
         <v>30540</v>
@@ -27455,7 +27455,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G934" t="n">
-        <v>0.955107867717743</v>
+        <v>0.955107927322388</v>
       </c>
       <c r="H934" t="n">
         <v>10054</v>
@@ -27484,7 +27484,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G935" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H935" t="n">
         <v>26262</v>
@@ -27542,7 +27542,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G937" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753195762634</v>
       </c>
       <c r="H937" t="n">
         <v>19326</v>
@@ -27629,7 +27629,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G940" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H940" t="n">
         <v>11547</v>
@@ -27745,7 +27745,7 @@
         <v>0.938000023365021</v>
       </c>
       <c r="G944" t="n">
-        <v>0.891434073448181</v>
+        <v>0.891434013843536</v>
       </c>
       <c r="H944" t="n">
         <v>14374</v>
@@ -27832,7 +27832,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G947" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H947" t="n">
         <v>76067</v>
@@ -27919,7 +27919,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G950" t="n">
-        <v>0.937051117420197</v>
+        <v>0.937051177024841</v>
       </c>
       <c r="H950" t="n">
         <v>13708</v>
@@ -27977,7 +27977,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G952" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753195762634</v>
       </c>
       <c r="H952" t="n">
         <v>16989</v>
@@ -28151,7 +28151,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G958" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H958" t="n">
         <v>15725</v>
@@ -28180,7 +28180,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G959" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H959" t="n">
         <v>31567</v>
@@ -28412,7 +28412,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G967" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H967" t="n">
         <v>19223</v>
@@ -28441,7 +28441,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G968" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H968" t="n">
         <v>2280</v>
@@ -28470,7 +28470,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G969" t="n">
-        <v>0.902838289737701</v>
+        <v>0.902838349342346</v>
       </c>
       <c r="H969" t="n">
         <v>16831</v>
@@ -28499,7 +28499,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G970" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H970" t="n">
         <v>9218</v>
@@ -28557,7 +28557,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G972" t="n">
-        <v>0.899036884307861</v>
+        <v>0.899036824703217</v>
       </c>
       <c r="H972" t="n">
         <v>680</v>
@@ -28644,7 +28644,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G975" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H975" t="n">
         <v>218368</v>
@@ -28673,7 +28673,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G976" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H976" t="n">
         <v>49086</v>
@@ -28702,7 +28702,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G977" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H977" t="n">
         <v>11890</v>
@@ -28731,7 +28731,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G978" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H978" t="n">
         <v>33171</v>
@@ -28760,7 +28760,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G979" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H979" t="n">
         <v>4965</v>
@@ -28789,7 +28789,7 @@
         <v>1.00499999523163</v>
       </c>
       <c r="G980" t="n">
-        <v>0.955107867717743</v>
+        <v>0.955107927322388</v>
       </c>
       <c r="H980" t="n">
         <v>14510</v>
@@ -28818,7 +28818,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G981" t="n">
-        <v>0.993121981620789</v>
+        <v>0.993122100830078</v>
       </c>
       <c r="H981" t="n">
         <v>192780</v>
@@ -28847,7 +28847,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G982" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H982" t="n">
         <v>30123</v>
@@ -28905,7 +28905,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G984" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H984" t="n">
         <v>29319</v>
@@ -28934,7 +28934,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G985" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H985" t="n">
         <v>21774</v>
@@ -28963,7 +28963,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G986" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H986" t="n">
         <v>34613</v>
@@ -28992,7 +28992,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G987" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H987" t="n">
         <v>7153</v>
@@ -29137,7 +29137,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H992" t="n">
         <v>10082</v>
@@ -29166,7 +29166,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G993" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H993" t="n">
         <v>5731</v>
@@ -29195,7 +29195,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G994" t="n">
-        <v>0.96461147069931</v>
+        <v>0.964611411094666</v>
       </c>
       <c r="H994" t="n">
         <v>2711</v>
@@ -29224,7 +29224,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G995" t="n">
-        <v>0.96461147069931</v>
+        <v>0.964611411094666</v>
       </c>
       <c r="H995" t="n">
         <v>16059</v>
@@ -29253,7 +29253,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G996" t="n">
-        <v>0.983618557453156</v>
+        <v>0.983618438243866</v>
       </c>
       <c r="H996" t="n">
         <v>106619</v>
@@ -29282,7 +29282,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G997" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H997" t="n">
         <v>4524</v>
@@ -29311,7 +29311,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G998" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H998" t="n">
         <v>19085</v>
@@ -29340,7 +29340,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G999" t="n">
-        <v>0.96461147069931</v>
+        <v>0.964611411094666</v>
       </c>
       <c r="H999" t="n">
         <v>93021</v>
@@ -29369,7 +29369,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H1000" t="n">
         <v>13855</v>
@@ -29427,7 +29427,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.983618557453156</v>
+        <v>0.983618438243866</v>
       </c>
       <c r="H1002" t="n">
         <v>25401</v>
@@ -29456,7 +29456,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1003" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H1003" t="n">
         <v>87046</v>
@@ -29485,7 +29485,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.0121294260025</v>
+        <v>1.01212930679321</v>
       </c>
       <c r="H1004" t="n">
         <v>32111</v>
@@ -29514,7 +29514,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H1005" t="n">
         <v>59119</v>
@@ -29543,7 +29543,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.04539167881012</v>
+        <v>1.04539179801941</v>
       </c>
       <c r="H1006" t="n">
         <v>32120</v>
@@ -29601,7 +29601,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.05964708328247</v>
+        <v>1.05964696407318</v>
       </c>
       <c r="H1008" t="n">
         <v>70073</v>
@@ -29659,7 +29659,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.04539167881012</v>
+        <v>1.04539179801941</v>
       </c>
       <c r="H1010" t="n">
         <v>13449</v>
@@ -29688,7 +29688,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.04539167881012</v>
+        <v>1.04539179801941</v>
       </c>
       <c r="H1011" t="n">
         <v>7455</v>
@@ -29717,7 +29717,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.05014359951019</v>
+        <v>1.0501434803009</v>
       </c>
       <c r="H1012" t="n">
         <v>19076</v>
@@ -29746,7 +29746,7 @@
         <v>1.07500004768372</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.02163279056549</v>
+        <v>1.02163290977478</v>
       </c>
       <c r="H1013" t="n">
         <v>15841</v>
@@ -29920,7 +29920,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1019" t="n">
-        <v>1.00737738609314</v>
+        <v>1.00737726688385</v>
       </c>
       <c r="H1019" t="n">
         <v>28015</v>
@@ -29949,7 +29949,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.00262558460236</v>
+        <v>1.00262570381165</v>
       </c>
       <c r="H1020" t="n">
         <v>12764</v>
@@ -29978,7 +29978,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.0121294260025</v>
+        <v>1.01212930679321</v>
       </c>
       <c r="H1021" t="n">
         <v>113267</v>
@@ -30036,7 +30036,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.983618557453156</v>
+        <v>0.983618438243866</v>
       </c>
       <c r="H1023" t="n">
         <v>17131</v>
@@ -30065,7 +30065,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1024" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H1024" t="n">
         <v>2530</v>
@@ -30094,7 +30094,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H1025" t="n">
         <v>96405</v>
@@ -30123,7 +30123,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H1026" t="n">
         <v>14290</v>
@@ -30152,7 +30152,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.993121981620789</v>
+        <v>0.993122100830078</v>
       </c>
       <c r="H1027" t="n">
         <v>28649</v>
@@ -30181,7 +30181,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.993121981620789</v>
+        <v>0.993122100830078</v>
       </c>
       <c r="H1028" t="n">
         <v>20606</v>
@@ -30210,7 +30210,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H1029" t="n">
         <v>91607</v>
@@ -30239,7 +30239,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1030" t="n">
-        <v>0.959859669208527</v>
+        <v>0.959859609603882</v>
       </c>
       <c r="H1030" t="n">
         <v>22283</v>
@@ -30268,7 +30268,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.00262558460236</v>
+        <v>1.00262570381165</v>
       </c>
       <c r="H1031" t="n">
         <v>372072</v>
@@ -30297,7 +30297,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.993121981620789</v>
+        <v>0.993122100830078</v>
       </c>
       <c r="H1032" t="n">
         <v>93979</v>
@@ -30326,7 +30326,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H1033" t="n">
         <v>51868</v>
@@ -30384,7 +30384,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.00737738609314</v>
+        <v>1.00737726688385</v>
       </c>
       <c r="H1035" t="n">
         <v>23532</v>
@@ -30413,7 +30413,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.10716485977173</v>
+        <v>1.10716474056244</v>
       </c>
       <c r="H1036" t="n">
         <v>119522</v>
@@ -30471,7 +30471,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H1038" t="n">
         <v>17825</v>
@@ -30500,7 +30500,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.00262558460236</v>
+        <v>1.00262570381165</v>
       </c>
       <c r="H1039" t="n">
         <v>32399</v>
@@ -30558,7 +30558,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.06439888477325</v>
+        <v>1.06439876556396</v>
       </c>
       <c r="H1041" t="n">
         <v>42988</v>
@@ -30587,7 +30587,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.04539167881012</v>
+        <v>1.04539179801941</v>
       </c>
       <c r="H1042" t="n">
         <v>11404</v>
@@ -30616,7 +30616,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.08340585231781</v>
+        <v>1.0834059715271</v>
       </c>
       <c r="H1043" t="n">
         <v>139130</v>
@@ -30645,7 +30645,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H1044" t="n">
         <v>40158</v>
@@ -30761,7 +30761,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H1048" t="n">
         <v>82375</v>
@@ -30790,7 +30790,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.08815777301788</v>
+        <v>1.08815765380859</v>
       </c>
       <c r="H1049" t="n">
         <v>122643</v>
@@ -30906,7 +30906,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.983618557453156</v>
+        <v>0.983618438243866</v>
       </c>
       <c r="H1053" t="n">
         <v>115588</v>
@@ -30935,7 +30935,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.997873842716217</v>
+        <v>0.997873902320862</v>
       </c>
       <c r="H1054" t="n">
         <v>46940</v>
@@ -30993,7 +30993,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.978866696357727</v>
+        <v>0.978866815567017</v>
       </c>
       <c r="H1056" t="n">
         <v>34580</v>
@@ -31022,7 +31022,7 @@
         <v>0.986000001430511</v>
       </c>
       <c r="G1057" t="n">
-        <v>0.937051117420197</v>
+        <v>0.937051177024841</v>
       </c>
       <c r="H1057" t="n">
         <v>35665</v>
@@ -31080,7 +31080,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.938951849937439</v>
+        <v>0.938951790332794</v>
       </c>
       <c r="H1059" t="n">
         <v>19870</v>
@@ -31167,7 +31167,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H1062" t="n">
         <v>146893</v>
@@ -31225,7 +31225,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.826809763908386</v>
+        <v>0.826809823513031</v>
       </c>
       <c r="H1064" t="n">
         <v>25040</v>
@@ -31312,7 +31312,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.819206953048706</v>
+        <v>0.819206893444061</v>
       </c>
       <c r="H1067" t="n">
         <v>22955</v>
@@ -31341,7 +31341,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1068" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1068" t="n">
         <v>2554</v>
@@ -31370,7 +31370,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1069" t="n">
         <v>503</v>
@@ -31428,7 +31428,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.826809763908386</v>
+        <v>0.826809823513031</v>
       </c>
       <c r="H1071" t="n">
         <v>3693</v>
@@ -31515,7 +31515,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.872426867485046</v>
+        <v>0.872426927089691</v>
       </c>
       <c r="H1074" t="n">
         <v>2011</v>
@@ -31544,7 +31544,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.826809763908386</v>
+        <v>0.826809823513031</v>
       </c>
       <c r="H1075" t="n">
         <v>44457</v>
@@ -31776,7 +31776,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.872426867485046</v>
+        <v>0.872426927089691</v>
       </c>
       <c r="H1083" t="n">
         <v>23349</v>
@@ -31805,7 +31805,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H1084" t="n">
         <v>14829</v>
@@ -32066,7 +32066,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1093" t="n">
         <v>5640</v>
@@ -32095,7 +32095,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.804001212120056</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H1094" t="n">
         <v>1012</v>
@@ -32124,7 +32124,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.804001212120056</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H1095" t="n">
         <v>271</v>
@@ -32153,7 +32153,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1096" t="n">
-        <v>0.815405428409576</v>
+        <v>0.815405488014221</v>
       </c>
       <c r="H1096" t="n">
         <v>5889</v>
@@ -32182,7 +32182,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.815405428409576</v>
+        <v>0.815405488014221</v>
       </c>
       <c r="H1097" t="n">
         <v>0</v>
@@ -32269,7 +32269,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.819206953048706</v>
+        <v>0.819206893444061</v>
       </c>
       <c r="H1100" t="n">
         <v>28856</v>
@@ -32298,7 +32298,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.815405428409576</v>
+        <v>0.815405488014221</v>
       </c>
       <c r="H1101" t="n">
         <v>7786</v>
@@ -32327,7 +32327,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1102" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1102" t="n">
         <v>16688</v>
@@ -32385,7 +32385,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.813504755496979</v>
+        <v>0.813504815101624</v>
       </c>
       <c r="H1104" t="n">
         <v>5636</v>
@@ -32414,7 +32414,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.815405428409576</v>
+        <v>0.815405488014221</v>
       </c>
       <c r="H1105" t="n">
         <v>20026</v>
@@ -32530,7 +32530,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.819206953048706</v>
+        <v>0.819206893444061</v>
       </c>
       <c r="H1109" t="n">
         <v>7100</v>
@@ -32588,7 +32588,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1111" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H1111" t="n">
         <v>15870</v>
@@ -32617,7 +32617,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H1112" t="n">
         <v>10652</v>
@@ -32646,7 +32646,7 @@
         <v>0.907999992370605</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.862923324108124</v>
+        <v>0.862923383712769</v>
       </c>
       <c r="H1113" t="n">
         <v>5872</v>
@@ -32762,7 +32762,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1117" t="n">
-        <v>0.832511901855469</v>
+        <v>0.832511961460114</v>
       </c>
       <c r="H1117" t="n">
         <v>27258</v>
@@ -32791,7 +32791,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.826809763908386</v>
+        <v>0.826809823513031</v>
       </c>
       <c r="H1118" t="n">
         <v>6758</v>
@@ -32936,7 +32936,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1123" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H1123" t="n">
         <v>2596</v>
@@ -32965,7 +32965,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H1124" t="n">
         <v>8344</v>
@@ -32994,7 +32994,7 @@
         <v>0.903999984264374</v>
       </c>
       <c r="G1125" t="n">
-        <v>0.859121859073639</v>
+        <v>0.859121918678284</v>
       </c>
       <c r="H1125" t="n">
         <v>1772</v>
@@ -33081,7 +33081,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1128" t="n">
-        <v>0.819206953048706</v>
+        <v>0.819206893444061</v>
       </c>
       <c r="H1128" t="n">
         <v>3729</v>
@@ -33110,7 +33110,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H1129" t="n">
         <v>13547</v>
@@ -33139,7 +33139,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1130" t="n">
-        <v>0.843916237354279</v>
+        <v>0.843916296958923</v>
       </c>
       <c r="H1130" t="n">
         <v>1300</v>
@@ -33197,7 +33197,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H1132" t="n">
         <v>15701</v>
@@ -33226,7 +33226,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1133" t="n">
-        <v>0.828710436820984</v>
+        <v>0.828710556030273</v>
       </c>
       <c r="H1133" t="n">
         <v>12</v>
@@ -33400,7 +33400,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.832511901855469</v>
+        <v>0.832511961460114</v>
       </c>
       <c r="H1139" t="n">
         <v>11115</v>
@@ -33545,7 +33545,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.828710436820984</v>
+        <v>0.828710556030273</v>
       </c>
       <c r="H1144" t="n">
         <v>3310</v>
@@ -33574,7 +33574,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.828710436820984</v>
+        <v>0.828710556030273</v>
       </c>
       <c r="H1145" t="n">
         <v>0</v>
@@ -33603,7 +33603,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.828710436820984</v>
+        <v>0.828710556030273</v>
       </c>
       <c r="H1146" t="n">
         <v>65</v>
@@ -33632,7 +33632,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.857221186161041</v>
+        <v>0.857221245765686</v>
       </c>
       <c r="H1147" t="n">
         <v>6492</v>
@@ -33719,7 +33719,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.849618375301361</v>
+        <v>0.849618315696716</v>
       </c>
       <c r="H1150" t="n">
         <v>1598</v>
@@ -33748,7 +33748,7 @@
         <v>0.875999987125397</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.832511901855469</v>
+        <v>0.832511961460114</v>
       </c>
       <c r="H1151" t="n">
         <v>7919</v>
@@ -33864,7 +33864,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.824909090995789</v>
+        <v>0.824909031391144</v>
       </c>
       <c r="H1155" t="n">
         <v>805</v>
@@ -33893,7 +33893,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.824909090995789</v>
+        <v>0.824909031391144</v>
       </c>
       <c r="H1156" t="n">
         <v>52496</v>
@@ -33922,7 +33922,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.813504755496979</v>
+        <v>0.813504815101624</v>
       </c>
       <c r="H1157" t="n">
         <v>1157</v>
@@ -34038,7 +34038,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.819206953048706</v>
+        <v>0.819206893444061</v>
       </c>
       <c r="H1161" t="n">
         <v>20870</v>
@@ -34067,7 +34067,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.804001212120056</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H1162" t="n">
         <v>25013</v>
@@ -34096,7 +34096,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1163" t="n">
         <v>6755</v>
@@ -34328,7 +34328,7 @@
         <v>0.857999980449677</v>
       </c>
       <c r="G1171" t="n">
-        <v>0.815405428409576</v>
+        <v>0.815405488014221</v>
       </c>
       <c r="H1171" t="n">
         <v>7751</v>
@@ -34357,7 +34357,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.813504755496979</v>
+        <v>0.813504815101624</v>
       </c>
       <c r="H1172" t="n">
         <v>1500</v>
@@ -34386,7 +34386,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.813504755496979</v>
+        <v>0.813504815101624</v>
       </c>
       <c r="H1173" t="n">
         <v>0</v>
@@ -34415,7 +34415,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.813504755496979</v>
+        <v>0.813504815101624</v>
       </c>
       <c r="H1174" t="n">
         <v>0</v>
@@ -34444,7 +34444,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.813504755496979</v>
+        <v>0.813504815101624</v>
       </c>
       <c r="H1175" t="n">
         <v>0</v>
@@ -34473,7 +34473,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.811604082584381</v>
+        <v>0.811604142189026</v>
       </c>
       <c r="H1176" t="n">
         <v>1005</v>
@@ -34502,7 +34502,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.811604082584381</v>
+        <v>0.811604142189026</v>
       </c>
       <c r="H1177" t="n">
         <v>0</v>
@@ -34589,7 +34589,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185513973236</v>
       </c>
       <c r="H1180" t="n">
         <v>10010</v>
@@ -34647,7 +34647,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.804001212120056</v>
+        <v>0.804001271724701</v>
       </c>
       <c r="H1182" t="n">
         <v>10</v>
@@ -34676,7 +34676,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.775490581989288</v>
+        <v>0.775490522384644</v>
       </c>
       <c r="H1183" t="n">
         <v>3161</v>
@@ -34705,7 +34705,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1184" t="n">
-        <v>0.773589909076691</v>
+        <v>0.773589849472046</v>
       </c>
       <c r="H1184" t="n">
         <v>3194</v>
@@ -34734,7 +34734,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.773589909076691</v>
+        <v>0.773589849472046</v>
       </c>
       <c r="H1185" t="n">
         <v>0</v>
@@ -34792,7 +34792,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1187" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1187" t="n">
         <v>4602</v>
@@ -34937,7 +34937,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391254901886</v>
       </c>
       <c r="H1192" t="n">
         <v>11693</v>
@@ -34966,7 +34966,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391254901886</v>
       </c>
       <c r="H1193" t="n">
         <v>0</v>
@@ -35053,7 +35053,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1196" t="n">
         <v>1048</v>
@@ -35082,7 +35082,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497668743134</v>
       </c>
       <c r="H1197" t="n">
         <v>14658</v>
@@ -35111,7 +35111,7 @@
         <v>0.843999981880188</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.802100479602814</v>
+        <v>0.802100539207458</v>
       </c>
       <c r="H1198" t="n">
         <v>6267</v>
@@ -35198,7 +35198,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1201" t="n">
-        <v>0.792597055435181</v>
+        <v>0.792596995830536</v>
       </c>
       <c r="H1201" t="n">
         <v>3357</v>
@@ -35227,7 +35227,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1202" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1202" t="n">
         <v>13459</v>
@@ -35256,7 +35256,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1203" t="n">
         <v>5351</v>
@@ -35314,7 +35314,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.792597055435181</v>
+        <v>0.792596995830536</v>
       </c>
       <c r="H1205" t="n">
         <v>6916</v>
@@ -35546,7 +35546,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391254901886</v>
       </c>
       <c r="H1213" t="n">
         <v>19225</v>
@@ -35575,7 +35575,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1214" t="n">
         <v>11574</v>
@@ -35604,7 +35604,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1215" t="n">
         <v>21716</v>
@@ -35662,7 +35662,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.760284900665283</v>
+        <v>0.760284841060638</v>
       </c>
       <c r="H1217" t="n">
         <v>3825</v>
@@ -35691,7 +35691,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1218" t="n">
         <v>13790</v>
@@ -35720,7 +35720,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1219" t="n">
         <v>12226</v>
@@ -35807,7 +35807,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1222" t="n">
         <v>9255</v>
@@ -35923,7 +35923,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.665249228477478</v>
+        <v>0.665249288082123</v>
       </c>
       <c r="H1226" t="n">
         <v>2220</v>
@@ -35952,7 +35952,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.693759977817535</v>
+        <v>0.69376003742218</v>
       </c>
       <c r="H1227" t="n">
         <v>10514</v>
@@ -36010,7 +36010,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.689958512783051</v>
+        <v>0.689958572387695</v>
       </c>
       <c r="H1229" t="n">
         <v>1200</v>
@@ -36126,7 +36126,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.701362788677216</v>
+        <v>0.701362729072571</v>
       </c>
       <c r="H1233" t="n">
         <v>2151</v>
@@ -36184,7 +36184,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.760284900665283</v>
+        <v>0.760284841060638</v>
       </c>
       <c r="H1235" t="n">
         <v>25366</v>
@@ -36213,7 +36213,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1236" t="n">
         <v>4134</v>
@@ -36242,7 +36242,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1237" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1237" t="n">
         <v>16304</v>
@@ -36271,7 +36271,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391254901886</v>
       </c>
       <c r="H1238" t="n">
         <v>13935</v>
@@ -36300,7 +36300,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1239" t="n">
         <v>32699</v>
@@ -36329,7 +36329,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1240" t="n">
         <v>9919</v>
@@ -36387,7 +36387,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1242" t="n">
         <v>6749</v>
@@ -36445,7 +36445,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1244" t="n">
         <v>43971</v>
@@ -36474,7 +36474,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1245" t="n">
         <v>5112</v>
@@ -36503,7 +36503,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1246" t="n">
         <v>16700</v>
@@ -36532,7 +36532,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.760284900665283</v>
+        <v>0.760284841060638</v>
       </c>
       <c r="H1247" t="n">
         <v>18577</v>
@@ -36561,7 +36561,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185513973236</v>
       </c>
       <c r="H1248" t="n">
         <v>12890</v>
@@ -36590,7 +36590,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1249" t="n">
         <v>6774</v>
@@ -36648,7 +36648,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582822322845</v>
       </c>
       <c r="H1251" t="n">
         <v>2313</v>
@@ -36706,7 +36706,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185513973236</v>
       </c>
       <c r="H1253" t="n">
         <v>1000</v>
@@ -36735,7 +36735,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582822322845</v>
       </c>
       <c r="H1254" t="n">
         <v>2276</v>
@@ -36764,7 +36764,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1255" t="n">
         <v>8859</v>
@@ -36793,7 +36793,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1256" t="n">
         <v>2562</v>
@@ -36822,7 +36822,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.775490581989288</v>
+        <v>0.775490522384644</v>
       </c>
       <c r="H1257" t="n">
         <v>15595</v>
@@ -36880,7 +36880,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1259" t="n">
         <v>25666</v>
@@ -36909,7 +36909,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1260" t="n">
         <v>38619</v>
@@ -36938,7 +36938,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1261" t="n">
         <v>1406</v>
@@ -37025,7 +37025,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1264" t="n">
         <v>2413</v>
@@ -37054,7 +37054,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1265" t="n">
         <v>12191</v>
@@ -37083,7 +37083,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1266" t="n">
         <v>3759</v>
@@ -37112,7 +37112,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1267" t="n">
         <v>0</v>
@@ -37141,7 +37141,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1268" t="n">
         <v>9194</v>
@@ -37170,7 +37170,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.745079219341278</v>
+        <v>0.745079159736633</v>
       </c>
       <c r="H1269" t="n">
         <v>14270</v>
@@ -37257,7 +37257,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1272" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1272" t="n">
         <v>360</v>
@@ -37373,7 +37373,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1276" t="n">
         <v>26285</v>
@@ -37460,7 +37460,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1279" t="n">
         <v>6732</v>
@@ -37489,7 +37489,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1280" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1280" t="n">
         <v>48413</v>
@@ -37518,7 +37518,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1281" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1281" t="n">
         <v>0</v>
@@ -37547,7 +37547,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1282" t="n">
         <v>0</v>
@@ -37605,7 +37605,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1284" t="n">
         <v>513</v>
@@ -37692,7 +37692,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1287" t="n">
         <v>1796</v>
@@ -37750,7 +37750,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1289" t="n">
-        <v>0.726072072982788</v>
+        <v>0.726072013378143</v>
       </c>
       <c r="H1289" t="n">
         <v>1010</v>
@@ -37779,7 +37779,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1290" t="n">
-        <v>0.726072072982788</v>
+        <v>0.726072013378143</v>
       </c>
       <c r="H1290" t="n">
         <v>0</v>
@@ -37808,7 +37808,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1291" t="n">
         <v>10</v>
@@ -37837,7 +37837,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.72036999464035</v>
+        <v>0.720369935035706</v>
       </c>
       <c r="H1292" t="n">
         <v>33828</v>
@@ -37895,7 +37895,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.745079219341278</v>
+        <v>0.745079159736633</v>
       </c>
       <c r="H1294" t="n">
         <v>30046</v>
@@ -37982,7 +37982,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1297" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1297" t="n">
         <v>20882</v>
@@ -38098,7 +38098,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1301" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1301" t="n">
         <v>5660</v>
@@ -38127,7 +38127,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1302" t="n">
         <v>53740</v>
@@ -38185,7 +38185,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1304" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1304" t="n">
         <v>5839</v>
@@ -38533,7 +38533,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185513973236</v>
       </c>
       <c r="H1316" t="n">
         <v>90943</v>
@@ -38649,7 +38649,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582822322845</v>
       </c>
       <c r="H1320" t="n">
         <v>37453</v>
@@ -38678,7 +38678,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.760284900665283</v>
+        <v>0.760284841060638</v>
       </c>
       <c r="H1321" t="n">
         <v>31626</v>
@@ -38707,7 +38707,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.745079219341278</v>
+        <v>0.745079159736633</v>
       </c>
       <c r="H1322" t="n">
         <v>6424</v>
@@ -38736,7 +38736,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.745079219341278</v>
+        <v>0.745079159736633</v>
       </c>
       <c r="H1323" t="n">
         <v>7011</v>
@@ -38823,7 +38823,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.745079219341278</v>
+        <v>0.745079159736633</v>
       </c>
       <c r="H1326" t="n">
         <v>4013</v>
@@ -38852,7 +38852,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1327" t="n">
         <v>2313</v>
@@ -38881,7 +38881,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185513973236</v>
       </c>
       <c r="H1328" t="n">
         <v>52080</v>
@@ -38910,7 +38910,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582822322845</v>
       </c>
       <c r="H1329" t="n">
         <v>143</v>
@@ -38939,7 +38939,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1330" t="n">
         <v>9538</v>
@@ -38968,7 +38968,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1331" t="n">
         <v>69317</v>
@@ -38997,7 +38997,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391254901886</v>
       </c>
       <c r="H1332" t="n">
         <v>36760</v>
@@ -39026,7 +39026,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391254901886</v>
       </c>
       <c r="H1333" t="n">
         <v>3523</v>
@@ -39084,7 +39084,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1335" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1335" t="n">
         <v>38397</v>
@@ -39142,7 +39142,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.775490581989288</v>
+        <v>0.775490522384644</v>
       </c>
       <c r="H1337" t="n">
         <v>36262</v>
@@ -39171,7 +39171,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.760284900665283</v>
+        <v>0.760284841060638</v>
       </c>
       <c r="H1338" t="n">
         <v>5829</v>
@@ -39200,7 +39200,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582822322845</v>
       </c>
       <c r="H1339" t="n">
         <v>5953</v>
@@ -39229,7 +39229,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185513973236</v>
       </c>
       <c r="H1340" t="n">
         <v>16027</v>
@@ -39519,7 +39519,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1350" t="n">
         <v>30168</v>
@@ -39548,7 +39548,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1351" t="n">
         <v>38622</v>
@@ -39606,7 +39606,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.760284900665283</v>
+        <v>0.760284841060638</v>
       </c>
       <c r="H1353" t="n">
         <v>12165</v>
@@ -39664,7 +39664,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582822322845</v>
       </c>
       <c r="H1355" t="n">
         <v>24882</v>
@@ -39693,7 +39693,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1356" t="n">
         <v>34806</v>
@@ -39751,7 +39751,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1358" t="n">
-        <v>0.746979951858521</v>
+        <v>0.746979892253876</v>
       </c>
       <c r="H1358" t="n">
         <v>5644</v>
@@ -39838,7 +39838,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1361" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1361" t="n">
         <v>7927</v>
@@ -39896,7 +39896,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1363" t="n">
         <v>10616</v>
@@ -39925,7 +39925,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1364" t="n">
-        <v>0.746979951858521</v>
+        <v>0.746979892253876</v>
       </c>
       <c r="H1364" t="n">
         <v>15021</v>
@@ -40099,7 +40099,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1370" t="n">
         <v>7560</v>
@@ -40128,7 +40128,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1371" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1371" t="n">
         <v>16407</v>
@@ -40186,7 +40186,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1373" t="n">
         <v>84131</v>
@@ -40215,7 +40215,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.745079219341278</v>
+        <v>0.745079159736633</v>
       </c>
       <c r="H1374" t="n">
         <v>9611</v>
@@ -40360,7 +40360,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1379" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1379" t="n">
         <v>70925</v>
@@ -40505,7 +40505,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.855320453643799</v>
+        <v>0.855320394039154</v>
       </c>
       <c r="H1384" t="n">
         <v>665882</v>
@@ -40650,7 +40650,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.813504755496979</v>
+        <v>0.813504815101624</v>
       </c>
       <c r="H1389" t="n">
         <v>86617</v>
@@ -40679,7 +40679,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1390" t="n">
-        <v>0.813504755496979</v>
+        <v>0.813504815101624</v>
       </c>
       <c r="H1390" t="n">
         <v>44133</v>
@@ -40853,7 +40853,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G1396" t="n">
-        <v>0.794497787952423</v>
+        <v>0.794497668743134</v>
       </c>
       <c r="H1396" t="n">
         <v>29317</v>
@@ -40911,7 +40911,7 @@
         <v>0.833999991416931</v>
       </c>
       <c r="G1398" t="n">
-        <v>0.792597055435181</v>
+        <v>0.792596995830536</v>
       </c>
       <c r="H1398" t="n">
         <v>7277</v>
@@ -40940,7 +40940,7 @@
         <v>0.850000023841858</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.807802677154541</v>
+        <v>0.807802736759186</v>
       </c>
       <c r="H1399" t="n">
         <v>10008</v>
@@ -41027,7 +41027,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1402" t="n">
         <v>111019</v>
@@ -41085,7 +41085,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1404" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1404" t="n">
         <v>6420</v>
@@ -41114,7 +41114,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1405" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391254901886</v>
       </c>
       <c r="H1405" t="n">
         <v>14851</v>
@@ -41172,7 +41172,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1407" t="n">
         <v>2400</v>
@@ -41201,7 +41201,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185513973236</v>
       </c>
       <c r="H1408" t="n">
         <v>21428</v>
@@ -41230,7 +41230,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1409" t="n">
         <v>43653</v>
@@ -41259,7 +41259,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1410" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1410" t="n">
         <v>45925</v>
@@ -41288,7 +41288,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582822322845</v>
       </c>
       <c r="H1411" t="n">
         <v>49753</v>
@@ -41491,7 +41491,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.746979951858521</v>
+        <v>0.746979892253876</v>
       </c>
       <c r="H1418" t="n">
         <v>5839</v>
@@ -41520,7 +41520,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185513973236</v>
       </c>
       <c r="H1419" t="n">
         <v>3816</v>
@@ -41549,7 +41549,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1420" t="n">
-        <v>0.760284900665283</v>
+        <v>0.760284841060638</v>
       </c>
       <c r="H1420" t="n">
         <v>394</v>
@@ -41578,7 +41578,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.748880624771118</v>
+        <v>0.748880565166473</v>
       </c>
       <c r="H1421" t="n">
         <v>20129</v>
@@ -41607,7 +41607,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.760284900665283</v>
+        <v>0.760284841060638</v>
       </c>
       <c r="H1422" t="n">
         <v>1016</v>
@@ -41636,7 +41636,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.765986979007721</v>
+        <v>0.765987038612366</v>
       </c>
       <c r="H1423" t="n">
         <v>15016</v>
@@ -41665,7 +41665,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582822322845</v>
       </c>
       <c r="H1424" t="n">
         <v>13463</v>
@@ -41752,7 +41752,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.760284900665283</v>
+        <v>0.760284841060638</v>
       </c>
       <c r="H1427" t="n">
         <v>33992</v>
@@ -41810,7 +41810,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.745079219341278</v>
+        <v>0.745079159736633</v>
       </c>
       <c r="H1429" t="n">
         <v>777</v>
@@ -41839,7 +41839,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.745079219341278</v>
+        <v>0.745079159736633</v>
       </c>
       <c r="H1430" t="n">
         <v>0</v>
@@ -41868,7 +41868,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.760284900665283</v>
+        <v>0.760284841060638</v>
       </c>
       <c r="H1431" t="n">
         <v>6918</v>
@@ -41897,7 +41897,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1432" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1432" t="n">
         <v>4312</v>
@@ -41984,7 +41984,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1435" t="n">
         <v>50781</v>
@@ -42013,7 +42013,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.746979951858521</v>
+        <v>0.746979892253876</v>
       </c>
       <c r="H1436" t="n">
         <v>53665</v>
@@ -42100,7 +42100,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.767887830734253</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1439" t="n">
         <v>1167</v>
@@ -42129,7 +42129,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1440" t="n">
         <v>11075</v>
@@ -42158,7 +42158,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.760284900665283</v>
+        <v>0.760284841060638</v>
       </c>
       <c r="H1441" t="n">
         <v>2013</v>
@@ -42187,7 +42187,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1442" t="n">
-        <v>0.773589909076691</v>
+        <v>0.773589849472046</v>
       </c>
       <c r="H1442" t="n">
         <v>35417</v>
@@ -42216,7 +42216,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.760284900665283</v>
+        <v>0.760284841060638</v>
       </c>
       <c r="H1443" t="n">
         <v>21576</v>
@@ -42245,7 +42245,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1444" t="n">
-        <v>0.769788503646851</v>
+        <v>0.769788444042206</v>
       </c>
       <c r="H1444" t="n">
         <v>52488</v>
@@ -42274,7 +42274,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.775490581989288</v>
+        <v>0.775490522384644</v>
       </c>
       <c r="H1445" t="n">
         <v>16945</v>
@@ -42303,7 +42303,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.760284900665283</v>
+        <v>0.760284841060638</v>
       </c>
       <c r="H1446" t="n">
         <v>49512</v>
@@ -42361,7 +42361,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.746979951858521</v>
+        <v>0.746979892253876</v>
       </c>
       <c r="H1448" t="n">
         <v>35514</v>
@@ -42390,7 +42390,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1449" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1449" t="n">
         <v>6766</v>
@@ -42419,7 +42419,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.760284900665283</v>
+        <v>0.760284841060638</v>
       </c>
       <c r="H1450" t="n">
         <v>19978</v>
@@ -42448,7 +42448,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.760284900665283</v>
+        <v>0.760284841060638</v>
       </c>
       <c r="H1451" t="n">
         <v>26</v>
@@ -42564,7 +42564,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1455" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582822322845</v>
       </c>
       <c r="H1455" t="n">
         <v>3339</v>
@@ -42593,7 +42593,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582822322845</v>
       </c>
       <c r="H1456" t="n">
         <v>0</v>
@@ -42622,7 +42622,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1457" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582822322845</v>
       </c>
       <c r="H1457" t="n">
         <v>1282</v>
@@ -42651,7 +42651,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1458" t="n">
-        <v>0.746979951858521</v>
+        <v>0.746979892253876</v>
       </c>
       <c r="H1458" t="n">
         <v>30564</v>
@@ -42680,7 +42680,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.762185573577881</v>
+        <v>0.762185513973236</v>
       </c>
       <c r="H1459" t="n">
         <v>1349</v>
@@ -42709,7 +42709,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.754582762718201</v>
+        <v>0.754582822322845</v>
       </c>
       <c r="H1460" t="n">
         <v>4863</v>
@@ -42738,7 +42738,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1461" t="n">
-        <v>0.756483495235443</v>
+        <v>0.756483435630798</v>
       </c>
       <c r="H1461" t="n">
         <v>1500</v>
@@ -42854,7 +42854,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1465" t="n">
         <v>63301</v>
@@ -42912,7 +42912,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1467" t="n">
         <v>35377</v>
@@ -43086,7 +43086,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1473" t="n">
         <v>35727</v>
@@ -43115,7 +43115,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.739377021789551</v>
+        <v>0.739377081394196</v>
       </c>
       <c r="H1474" t="n">
         <v>0</v>
@@ -43144,7 +43144,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1475" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1475" t="n">
         <v>1100</v>
@@ -43173,7 +43173,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1476" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1476" t="n">
         <v>1113</v>
@@ -43202,7 +43202,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1477" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1477" t="n">
         <v>11896</v>
@@ -43260,7 +43260,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.726072072982788</v>
+        <v>0.726072013378143</v>
       </c>
       <c r="H1479" t="n">
         <v>21017</v>
@@ -43318,7 +43318,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1481" t="n">
-        <v>0.726072072982788</v>
+        <v>0.726072013378143</v>
       </c>
       <c r="H1481" t="n">
         <v>9281</v>
@@ -43347,7 +43347,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1482" t="n">
-        <v>0.726072072982788</v>
+        <v>0.726072013378143</v>
       </c>
       <c r="H1482" t="n">
         <v>0</v>
@@ -43434,7 +43434,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.726072072982788</v>
+        <v>0.726072013378143</v>
       </c>
       <c r="H1485" t="n">
         <v>10016</v>
@@ -43579,7 +43579,7 @@
         <v>0.773999989032745</v>
       </c>
       <c r="G1490" t="n">
-        <v>0.735575556755066</v>
+        <v>0.735575616359711</v>
       </c>
       <c r="H1490" t="n">
         <v>4543</v>
@@ -43608,7 +43608,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1491" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1491" t="n">
         <v>8016</v>
@@ -43637,7 +43637,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1492" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1492" t="n">
         <v>3065</v>
@@ -43666,7 +43666,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.731774210929871</v>
+        <v>0.731774151325226</v>
       </c>
       <c r="H1493" t="n">
         <v>3253</v>
@@ -43782,7 +43782,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1497" t="n">
-        <v>0.726072072982788</v>
+        <v>0.726072013378143</v>
       </c>
       <c r="H1497" t="n">
         <v>27348</v>
@@ -43811,7 +43811,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.72036999464035</v>
+        <v>0.720369935035706</v>
       </c>
       <c r="H1498" t="n">
         <v>96906</v>
@@ -43869,7 +43869,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.708965599536896</v>
+        <v>0.708965659141541</v>
       </c>
       <c r="H1500" t="n">
         <v>36772</v>
@@ -43985,7 +43985,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1504" t="n">
-        <v>0.714667737483978</v>
+        <v>0.714667797088623</v>
       </c>
       <c r="H1504" t="n">
         <v>11995</v>
@@ -44159,7 +44159,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1510" t="n">
-        <v>0.689958512783051</v>
+        <v>0.689958572387695</v>
       </c>
       <c r="H1510" t="n">
         <v>1716</v>
@@ -44246,7 +44246,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.714667737483978</v>
+        <v>0.714667797088623</v>
       </c>
       <c r="H1513" t="n">
         <v>4895</v>
@@ -44304,7 +44304,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.701362788677216</v>
+        <v>0.701362729072571</v>
       </c>
       <c r="H1515" t="n">
         <v>3000</v>
@@ -44333,7 +44333,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.708965599536896</v>
+        <v>0.708965659141541</v>
       </c>
       <c r="H1516" t="n">
         <v>28188</v>
@@ -44362,7 +44362,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.701362788677216</v>
+        <v>0.701362729072571</v>
       </c>
       <c r="H1517" t="n">
         <v>2916</v>
@@ -44420,7 +44420,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.708965599536896</v>
+        <v>0.708965659141541</v>
       </c>
       <c r="H1519" t="n">
         <v>3267</v>
@@ -44449,7 +44449,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.708965599536896</v>
+        <v>0.708965659141541</v>
       </c>
       <c r="H1520" t="n">
         <v>0</v>
@@ -44507,7 +44507,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.691859185695648</v>
+        <v>0.691859245300293</v>
       </c>
       <c r="H1522" t="n">
         <v>4220</v>
@@ -44652,7 +44652,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1527" t="n">
-        <v>0.691859185695648</v>
+        <v>0.691859245300293</v>
       </c>
       <c r="H1527" t="n">
         <v>7816</v>
@@ -44710,7 +44710,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.693759977817535</v>
+        <v>0.69376003742218</v>
       </c>
       <c r="H1529" t="n">
         <v>31255</v>
@@ -44797,7 +44797,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.693759977817535</v>
+        <v>0.69376003742218</v>
       </c>
       <c r="H1532" t="n">
         <v>2091</v>
@@ -44826,7 +44826,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1533" t="n">
-        <v>0.691859185695648</v>
+        <v>0.691859245300293</v>
       </c>
       <c r="H1533" t="n">
         <v>2683</v>
@@ -44855,7 +44855,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1534" t="n">
-        <v>0.701362788677216</v>
+        <v>0.701362729072571</v>
       </c>
       <c r="H1534" t="n">
         <v>13975</v>
@@ -44971,7 +44971,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.693759977817535</v>
+        <v>0.69376003742218</v>
       </c>
       <c r="H1538" t="n">
         <v>1647</v>
@@ -45000,7 +45000,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.693759977817535</v>
+        <v>0.69376003742218</v>
       </c>
       <c r="H1539" t="n">
         <v>0</v>
@@ -45029,7 +45029,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.693759977817535</v>
+        <v>0.69376003742218</v>
       </c>
       <c r="H1540" t="n">
         <v>18889</v>
@@ -45174,7 +45174,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.689958512783051</v>
+        <v>0.689958572387695</v>
       </c>
       <c r="H1545" t="n">
         <v>4900</v>
@@ -45290,7 +45290,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.695660650730133</v>
+        <v>0.695660591125488</v>
       </c>
       <c r="H1549" t="n">
         <v>2218</v>
@@ -45319,7 +45319,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.689958512783051</v>
+        <v>0.689958572387695</v>
       </c>
       <c r="H1550" t="n">
         <v>10800</v>
@@ -45435,7 +45435,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1554" t="n">
-        <v>0.66334855556488</v>
+        <v>0.663348615169525</v>
       </c>
       <c r="H1554" t="n">
         <v>21016</v>
@@ -45522,7 +45522,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.665249228477478</v>
+        <v>0.665249288082123</v>
       </c>
       <c r="H1557" t="n">
         <v>20167</v>
@@ -45551,7 +45551,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.701362788677216</v>
+        <v>0.701362729072571</v>
       </c>
       <c r="H1558" t="n">
         <v>45922</v>
@@ -45609,7 +45609,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1560" t="n">
-        <v>0.726072072982788</v>
+        <v>0.726072013378143</v>
       </c>
       <c r="H1560" t="n">
         <v>29042</v>
@@ -45638,7 +45638,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.708965599536896</v>
+        <v>0.708965659141541</v>
       </c>
       <c r="H1561" t="n">
         <v>42743</v>
@@ -45754,7 +45754,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.665249228477478</v>
+        <v>0.665249288082123</v>
       </c>
       <c r="H1565" t="n">
         <v>39792</v>
@@ -45783,7 +45783,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.693759977817535</v>
+        <v>0.69376003742218</v>
       </c>
       <c r="H1566" t="n">
         <v>7267</v>
@@ -45986,7 +45986,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1573" t="n">
-        <v>0.621532917022705</v>
+        <v>0.62153285741806</v>
       </c>
       <c r="H1573" t="n">
         <v>17448</v>
@@ -46015,7 +46015,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.621532917022705</v>
+        <v>0.62153285741806</v>
       </c>
       <c r="H1574" t="n">
         <v>7498</v>
@@ -46160,7 +46160,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1579" t="n">
-        <v>0.670951366424561</v>
+        <v>0.670951306819916</v>
       </c>
       <c r="H1579" t="n">
         <v>117601</v>
@@ -46305,7 +46305,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.64054000377655</v>
+        <v>0.640540063381195</v>
       </c>
       <c r="H1584" t="n">
         <v>1100</v>
@@ -46363,7 +46363,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1586" t="n">
-        <v>0.644341349601746</v>
+        <v>0.64434140920639</v>
       </c>
       <c r="H1586" t="n">
         <v>18130</v>
@@ -46392,7 +46392,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.642440676689148</v>
+        <v>0.642440736293793</v>
       </c>
       <c r="H1587" t="n">
         <v>11421</v>
@@ -46566,7 +46566,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1593" t="n">
-        <v>0.644341349601746</v>
+        <v>0.64434140920639</v>
       </c>
       <c r="H1593" t="n">
         <v>10012</v>
@@ -46595,7 +46595,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.629135727882385</v>
+        <v>0.62913578748703</v>
       </c>
       <c r="H1594" t="n">
         <v>3425</v>
@@ -46653,7 +46653,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.634837806224823</v>
+        <v>0.634837865829468</v>
       </c>
       <c r="H1596" t="n">
         <v>4647</v>
@@ -46682,7 +46682,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.634837806224823</v>
+        <v>0.634837865829468</v>
       </c>
       <c r="H1597" t="n">
         <v>1316</v>
@@ -46885,7 +46885,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.634837806224823</v>
+        <v>0.634837865829468</v>
       </c>
       <c r="H1604" t="n">
         <v>1929</v>
@@ -46943,7 +46943,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1606" t="n">
         <v>18179</v>
@@ -47001,7 +47001,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1608" t="n">
-        <v>0.631036400794983</v>
+        <v>0.631036460399628</v>
       </c>
       <c r="H1608" t="n">
         <v>11497</v>
@@ -47030,7 +47030,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.629135727882385</v>
+        <v>0.62913578748703</v>
       </c>
       <c r="H1609" t="n">
         <v>900</v>
@@ -47117,7 +47117,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1612" t="n">
-        <v>0.629135727882385</v>
+        <v>0.62913578748703</v>
       </c>
       <c r="H1612" t="n">
         <v>1430</v>
@@ -47146,7 +47146,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.629135727882385</v>
+        <v>0.62913578748703</v>
       </c>
       <c r="H1613" t="n">
         <v>0</v>
@@ -47204,7 +47204,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.612029373645782</v>
+        <v>0.612029254436493</v>
       </c>
       <c r="H1615" t="n">
         <v>2932</v>
@@ -47320,7 +47320,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617832183838</v>
       </c>
       <c r="H1619" t="n">
         <v>103376</v>
@@ -47378,7 +47378,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1621" t="n">
         <v>7627</v>
@@ -47610,7 +47610,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1629" t="n">
         <v>42986</v>
@@ -47697,7 +47697,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1632" t="n">
-        <v>0.629135727882385</v>
+        <v>0.62913578748703</v>
       </c>
       <c r="H1632" t="n">
         <v>1580</v>
@@ -47784,7 +47784,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1635" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1635" t="n">
         <v>9129</v>
@@ -47813,7 +47813,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1636" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1636" t="n">
         <v>4863</v>
@@ -47842,7 +47842,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.615830779075623</v>
+        <v>0.615830838680267</v>
       </c>
       <c r="H1637" t="n">
         <v>0</v>
@@ -48016,7 +48016,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1643" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1643" t="n">
         <v>500</v>
@@ -48045,7 +48045,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823573112488</v>
       </c>
       <c r="H1644" t="n">
         <v>2848</v>
@@ -48103,7 +48103,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1646" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617832183838</v>
       </c>
       <c r="H1646" t="n">
         <v>1464</v>
@@ -48132,7 +48132,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1647" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823573112488</v>
       </c>
       <c r="H1647" t="n">
         <v>18796</v>
@@ -48277,7 +48277,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1652" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823573112488</v>
       </c>
       <c r="H1652" t="n">
         <v>500</v>
@@ -48306,7 +48306,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1653" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823573112488</v>
       </c>
       <c r="H1653" t="n">
         <v>0</v>
@@ -48335,7 +48335,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1654" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1654" t="n">
         <v>1001</v>
@@ -48393,7 +48393,7 @@
         <v>0.522000014781952</v>
       </c>
       <c r="G1656" t="n">
-        <v>0.49608588218689</v>
+        <v>0.496085941791534</v>
       </c>
       <c r="H1656" t="n">
         <v>26936</v>
@@ -48422,7 +48422,7 @@
         <v>0.523999989032745</v>
       </c>
       <c r="G1657" t="n">
-        <v>0.497986555099487</v>
+        <v>0.49798658490181</v>
       </c>
       <c r="H1657" t="n">
         <v>15248</v>
@@ -48451,7 +48451,7 @@
         <v>0.515999972820282</v>
       </c>
       <c r="G1658" t="n">
-        <v>0.490383684635162</v>
+        <v>0.490383714437485</v>
       </c>
       <c r="H1658" t="n">
         <v>27018</v>
@@ -48538,7 +48538,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1661" t="n">
-        <v>0.541702926158905</v>
+        <v>0.54170298576355</v>
       </c>
       <c r="H1661" t="n">
         <v>8896</v>
@@ -48567,7 +48567,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1662" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1662" t="n">
         <v>291</v>
@@ -48596,7 +48596,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1663" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1663" t="n">
         <v>1863</v>
@@ -48654,7 +48654,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1665" t="n">
         <v>288</v>
@@ -48683,7 +48683,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1666" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1666" t="n">
         <v>15</v>
@@ -48712,7 +48712,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1667" t="n">
         <v>2000</v>
@@ -48741,7 +48741,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1668" t="n">
         <v>39945</v>
@@ -48799,7 +48799,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1670" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1670" t="n">
         <v>16540</v>
@@ -48828,7 +48828,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.604426503181458</v>
+        <v>0.604426443576813</v>
       </c>
       <c r="H1671" t="n">
         <v>3877</v>
@@ -48857,7 +48857,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823573112488</v>
       </c>
       <c r="H1672" t="n">
         <v>10972</v>
@@ -48886,7 +48886,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1673" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1673" t="n">
         <v>8763</v>
@@ -49002,7 +49002,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1677" t="n">
-        <v>0.608227908611298</v>
+        <v>0.608227849006653</v>
       </c>
       <c r="H1677" t="n">
         <v>25134</v>
@@ -49118,7 +49118,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1681" t="n">
-        <v>0.604426503181458</v>
+        <v>0.604426443576813</v>
       </c>
       <c r="H1681" t="n">
         <v>5420</v>
@@ -49147,7 +49147,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.612029373645782</v>
+        <v>0.612029254436493</v>
       </c>
       <c r="H1682" t="n">
         <v>9272</v>
@@ -49292,7 +49292,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1687" t="n">
         <v>564</v>
@@ -49321,7 +49321,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1688" t="n">
         <v>1061</v>
@@ -49350,7 +49350,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1689" t="n">
         <v>1</v>
@@ -49379,7 +49379,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121554374695</v>
       </c>
       <c r="H1690" t="n">
         <v>1738</v>
@@ -49408,7 +49408,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.604426503181458</v>
+        <v>0.604426443576813</v>
       </c>
       <c r="H1691" t="n">
         <v>677</v>
@@ -49466,7 +49466,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1693" t="n">
-        <v>0.604426503181458</v>
+        <v>0.604426443576813</v>
       </c>
       <c r="H1693" t="n">
         <v>832</v>
@@ -49495,7 +49495,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1694" t="n">
-        <v>0.604426503181458</v>
+        <v>0.604426443576813</v>
       </c>
       <c r="H1694" t="n">
         <v>950</v>
@@ -49524,7 +49524,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1695" t="n">
         <v>6536</v>
@@ -49727,7 +49727,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823573112488</v>
       </c>
       <c r="H1702" t="n">
         <v>502</v>
@@ -49756,7 +49756,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1703" t="n">
         <v>8574</v>
@@ -49901,7 +49901,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1708" t="n">
         <v>6016</v>
@@ -49930,7 +49930,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121554374695</v>
       </c>
       <c r="H1709" t="n">
         <v>500</v>
@@ -49988,7 +49988,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1711" t="n">
         <v>63</v>
@@ -50017,7 +50017,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1712" t="n">
         <v>10927</v>
@@ -50046,7 +50046,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1713" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1713" t="n">
         <v>3975</v>
@@ -50104,7 +50104,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1715" t="n">
         <v>794</v>
@@ -50162,7 +50162,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121554374695</v>
       </c>
       <c r="H1717" t="n">
         <v>6642</v>
@@ -50191,7 +50191,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823573112488</v>
       </c>
       <c r="H1718" t="n">
         <v>2685</v>
@@ -50220,7 +50220,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1719" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1719" t="n">
         <v>12381</v>
@@ -50249,7 +50249,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1720" t="n">
         <v>4551</v>
@@ -50278,7 +50278,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1721" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1721" t="n">
         <v>8356</v>
@@ -50423,7 +50423,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.608227908611298</v>
+        <v>0.608227849006653</v>
       </c>
       <c r="H1726" t="n">
         <v>10016</v>
@@ -50452,7 +50452,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1727" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121554374695</v>
       </c>
       <c r="H1727" t="n">
         <v>9284</v>
@@ -50626,7 +50626,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1733" t="n">
         <v>33</v>
@@ -50713,7 +50713,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1736" t="n">
         <v>347</v>
@@ -50742,7 +50742,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1737" t="n">
         <v>148</v>
@@ -50771,7 +50771,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1738" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617832183838</v>
       </c>
       <c r="H1738" t="n">
         <v>5986</v>
@@ -50800,7 +50800,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617832183838</v>
       </c>
       <c r="H1739" t="n">
         <v>0</v>
@@ -50858,7 +50858,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1741" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1741" t="n">
         <v>2611</v>
@@ -50887,7 +50887,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1742" t="n">
         <v>1984</v>
@@ -50916,7 +50916,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1743" t="n">
-        <v>0.57591587305069</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1743" t="n">
         <v>1000</v>
@@ -50974,7 +50974,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1745" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1745" t="n">
         <v>32626</v>
@@ -51003,7 +51003,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1746" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1746" t="n">
         <v>0</v>
@@ -51032,7 +51032,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.57591587305069</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1747" t="n">
         <v>8200</v>
@@ -51090,7 +51090,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1749" t="n">
-        <v>0.608227908611298</v>
+        <v>0.608227849006653</v>
       </c>
       <c r="H1749" t="n">
         <v>30401</v>
@@ -51119,7 +51119,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121554374695</v>
       </c>
       <c r="H1750" t="n">
         <v>25115</v>
@@ -51206,7 +51206,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121554374695</v>
       </c>
       <c r="H1753" t="n">
         <v>194</v>
@@ -51235,7 +51235,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1754" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617832183838</v>
       </c>
       <c r="H1754" t="n">
         <v>17</v>
@@ -51264,7 +51264,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617832183838</v>
       </c>
       <c r="H1755" t="n">
         <v>0</v>
@@ -51322,7 +51322,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121554374695</v>
       </c>
       <c r="H1757" t="n">
         <v>9926</v>
@@ -51351,7 +51351,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1758" t="n">
         <v>2396</v>
@@ -51380,7 +51380,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1759" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1759" t="n">
         <v>0</v>
@@ -51467,7 +51467,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1762" t="n">
         <v>615</v>
@@ -51612,7 +51612,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1767" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1767" t="n">
         <v>624</v>
@@ -51670,7 +51670,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.60252583026886</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1769" t="n">
         <v>8114</v>
@@ -51699,7 +51699,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.604426503181458</v>
+        <v>0.604426443576813</v>
       </c>
       <c r="H1770" t="n">
         <v>19269</v>
@@ -51728,7 +51728,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1771" t="n">
-        <v>0.604426503181458</v>
+        <v>0.604426443576813</v>
       </c>
       <c r="H1771" t="n">
         <v>15200</v>
@@ -51757,7 +51757,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1772" t="n">
-        <v>0.608227908611298</v>
+        <v>0.608227849006653</v>
       </c>
       <c r="H1772" t="n">
         <v>4017</v>
@@ -51844,7 +51844,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823573112488</v>
       </c>
       <c r="H1775" t="n">
         <v>7172</v>
@@ -51873,7 +51873,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1776" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823573112488</v>
       </c>
       <c r="H1776" t="n">
         <v>0</v>
@@ -51902,7 +51902,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1777" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1777" t="n">
         <v>6313</v>
@@ -51931,7 +51931,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1778" t="n">
         <v>516</v>
@@ -52018,7 +52018,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1781" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121554374695</v>
       </c>
       <c r="H1781" t="n">
         <v>2957</v>
@@ -52163,7 +52163,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1786" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1786" t="n">
         <v>5365</v>
@@ -52192,7 +52192,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1787" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823573112488</v>
       </c>
       <c r="H1787" t="n">
         <v>24392</v>
@@ -52366,7 +52366,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1793" t="n">
-        <v>0.596823632717133</v>
+        <v>0.596823573112488</v>
       </c>
       <c r="H1793" t="n">
         <v>21634</v>
@@ -52395,7 +52395,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1794" t="n">
-        <v>0.604426503181458</v>
+        <v>0.604426443576813</v>
       </c>
       <c r="H1794" t="n">
         <v>1836</v>
@@ -52482,7 +52482,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1797" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1797" t="n">
         <v>1834</v>
@@ -52511,7 +52511,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1798" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1798" t="n">
         <v>0</v>
@@ -52540,7 +52540,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1799" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1799" t="n">
         <v>0</v>
@@ -52569,7 +52569,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1800" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617832183838</v>
       </c>
       <c r="H1800" t="n">
         <v>5988</v>
@@ -52598,7 +52598,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1801" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617832183838</v>
       </c>
       <c r="H1801" t="n">
         <v>5600</v>
@@ -52656,7 +52656,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121554374695</v>
       </c>
       <c r="H1803" t="n">
         <v>4401</v>
@@ -52772,7 +52772,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1807" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1807" t="n">
         <v>7034</v>
@@ -52888,7 +52888,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1811" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1811" t="n">
         <v>4998</v>
@@ -52917,7 +52917,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1812" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617832183838</v>
       </c>
       <c r="H1812" t="n">
         <v>676</v>
@@ -52946,7 +52946,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1813" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1813" t="n">
         <v>32</v>
@@ -52975,7 +52975,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1814" t="n">
         <v>2582</v>
@@ -53004,7 +53004,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1815" t="n">
         <v>0</v>
@@ -53033,7 +53033,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1816" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1816" t="n">
         <v>3535</v>
@@ -53062,7 +53062,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1817" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1817" t="n">
         <v>22549</v>
@@ -53091,7 +53091,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1818" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1818" t="n">
         <v>1892</v>
@@ -53149,7 +53149,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1820" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1820" t="n">
         <v>7922</v>
@@ -53178,7 +53178,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1821" t="n">
-        <v>0.57591587305069</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1821" t="n">
         <v>9490</v>
@@ -53207,7 +53207,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1822" t="n">
         <v>2670</v>
@@ -53265,7 +53265,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1824" t="n">
         <v>2687</v>
@@ -53294,7 +53294,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1825" t="n">
-        <v>0.577816545963287</v>
+        <v>0.577816486358643</v>
       </c>
       <c r="H1825" t="n">
         <v>3608</v>
@@ -53323,7 +53323,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1826" t="n">
         <v>73878</v>
@@ -53381,7 +53381,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1828" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1828" t="n">
         <v>5044</v>
@@ -53410,7 +53410,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1829" t="n">
         <v>1562</v>
@@ -53497,7 +53497,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.57591587305069</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1832" t="n">
         <v>2559</v>
@@ -53555,7 +53555,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1834" t="n">
         <v>661</v>
@@ -53642,7 +53642,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1837" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1837" t="n">
         <v>31108</v>
@@ -53729,7 +53729,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1840" t="n">
         <v>5059</v>
@@ -53758,7 +53758,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1841" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1841" t="n">
         <v>353</v>
@@ -53787,7 +53787,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1842" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1842" t="n">
         <v>9717</v>
@@ -53816,7 +53816,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1843" t="n">
         <v>1246</v>
@@ -53932,7 +53932,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1847" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1847" t="n">
         <v>7661</v>
@@ -53961,7 +53961,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1848" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1848" t="n">
         <v>1162</v>
@@ -54019,7 +54019,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1850" t="n">
         <v>7024</v>
@@ -54048,7 +54048,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1851" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1851" t="n">
         <v>7619</v>
@@ -54135,7 +54135,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1854" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617832183838</v>
       </c>
       <c r="H1854" t="n">
         <v>45294</v>
@@ -54164,7 +54164,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1855" t="n">
-        <v>0.581617951393127</v>
+        <v>0.581617832183838</v>
       </c>
       <c r="H1855" t="n">
         <v>18556</v>
@@ -54193,7 +54193,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1856" t="n">
         <v>12642</v>
@@ -54251,7 +54251,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1858" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1858" t="n">
         <v>13779</v>
@@ -54280,7 +54280,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1859" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1859" t="n">
         <v>0</v>
@@ -54367,7 +54367,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1862" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1862" t="n">
         <v>921</v>
@@ -54454,7 +54454,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1865" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1865" t="n">
         <v>817</v>
@@ -54483,7 +54483,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1866" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1866" t="n">
         <v>8439</v>
@@ -54512,7 +54512,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1867" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1867" t="n">
         <v>0</v>
@@ -54541,7 +54541,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1868" t="n">
         <v>235</v>
@@ -54657,7 +54657,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1872" t="n">
         <v>11785</v>
@@ -54773,7 +54773,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1876" t="n">
         <v>32101</v>
@@ -54889,7 +54889,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1880" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1880" t="n">
         <v>18</v>
@@ -54918,7 +54918,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1881" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1881" t="n">
         <v>1</v>
@@ -54947,7 +54947,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1882" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1882" t="n">
         <v>3117</v>
@@ -55005,7 +55005,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1884" t="n">
         <v>12818</v>
@@ -55034,7 +55034,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1885" t="n">
         <v>10634</v>
@@ -55121,7 +55121,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1888" t="n">
         <v>1701</v>
@@ -55150,7 +55150,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1889" t="n">
         <v>0</v>
@@ -55469,7 +55469,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1900" t="n">
-        <v>0.541702926158905</v>
+        <v>0.54170298576355</v>
       </c>
       <c r="H1900" t="n">
         <v>3769</v>
@@ -55498,7 +55498,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1901" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1901" t="n">
         <v>517</v>
@@ -55556,7 +55556,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1903" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1903" t="n">
         <v>8412</v>
@@ -55585,7 +55585,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1904" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1904" t="n">
         <v>2017</v>
@@ -55643,7 +55643,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1906" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1906" t="n">
         <v>1018</v>
@@ -55672,7 +55672,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1907" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1907" t="n">
         <v>0</v>
@@ -55701,7 +55701,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1908" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1908" t="n">
         <v>0</v>
@@ -55730,7 +55730,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.562610864639282</v>
+        <v>0.562610805034637</v>
       </c>
       <c r="H1909" t="n">
         <v>1000</v>
@@ -55759,7 +55759,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1910" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1910" t="n">
         <v>3519</v>
@@ -55788,7 +55788,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1911" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1911" t="n">
         <v>10376</v>
@@ -55817,7 +55817,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1912" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1912" t="n">
         <v>932</v>
@@ -55846,7 +55846,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1913" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1913" t="n">
         <v>0</v>
@@ -55904,7 +55904,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1915" t="n">
-        <v>0.541702926158905</v>
+        <v>0.54170298576355</v>
       </c>
       <c r="H1915" t="n">
         <v>2626</v>
@@ -56078,7 +56078,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1921" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1921" t="n">
         <v>3019</v>
@@ -56107,7 +56107,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1922" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1922" t="n">
         <v>4387</v>
@@ -56194,7 +56194,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1925" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1925" t="n">
         <v>27392</v>
@@ -56223,7 +56223,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1926" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1926" t="n">
         <v>2000</v>
@@ -56252,7 +56252,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1927" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1927" t="n">
         <v>1725</v>
@@ -56281,7 +56281,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1928" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1928" t="n">
         <v>18560</v>
@@ -56397,7 +56397,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1932" t="n">
-        <v>0.612029373645782</v>
+        <v>0.612029254436493</v>
       </c>
       <c r="H1932" t="n">
         <v>18087</v>
@@ -56455,7 +56455,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1934" t="n">
-        <v>0.58732008934021</v>
+        <v>0.587320029735565</v>
       </c>
       <c r="H1934" t="n">
         <v>3890</v>
@@ -56484,7 +56484,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1935" t="n">
-        <v>0.59112149477005</v>
+        <v>0.591121554374695</v>
       </c>
       <c r="H1935" t="n">
         <v>12816</v>
@@ -56513,7 +56513,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1936" t="n">
-        <v>0.585419356822968</v>
+        <v>0.585419416427612</v>
       </c>
       <c r="H1936" t="n">
         <v>2748</v>
@@ -56542,7 +56542,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1937" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1937" t="n">
         <v>4073</v>
@@ -56658,7 +56658,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1941" t="n">
-        <v>0.568312883377075</v>
+        <v>0.56831294298172</v>
       </c>
       <c r="H1941" t="n">
         <v>1989</v>
@@ -56832,7 +56832,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1947" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1947" t="n">
         <v>525</v>
@@ -56861,7 +56861,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1948" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1948" t="n">
         <v>4089</v>
@@ -57006,7 +57006,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1953" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1953" t="n">
         <v>2398</v>
@@ -57064,7 +57064,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1955" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1955" t="n">
         <v>1419</v>
@@ -57093,7 +57093,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1956" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1956" t="n">
         <v>4</v>
@@ -57122,7 +57122,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1957" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1957" t="n">
         <v>978</v>
@@ -57151,7 +57151,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1958" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1958" t="n">
         <v>817</v>
@@ -57180,7 +57180,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1959" t="n">
-        <v>0.570213675498962</v>
+        <v>0.570213735103607</v>
       </c>
       <c r="H1959" t="n">
         <v>52634</v>
@@ -57209,7 +57209,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1960" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1960" t="n">
         <v>15378</v>
@@ -57296,7 +57296,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1963" t="n">
-        <v>0.551206588745117</v>
+        <v>0.551206529140472</v>
       </c>
       <c r="H1963" t="n">
         <v>7001</v>
@@ -57354,7 +57354,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1965" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1965" t="n">
         <v>7</v>
@@ -57383,7 +57383,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1966" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1966" t="n">
         <v>1200</v>
@@ -57470,7 +57470,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1969" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1969" t="n">
         <v>8365</v>
@@ -57499,7 +57499,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1970" t="n">
-        <v>0.555007934570312</v>
+        <v>0.555007994174957</v>
       </c>
       <c r="H1970" t="n">
         <v>0</v>
@@ -57528,7 +57528,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1971" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1971" t="n">
         <v>4333</v>
@@ -57557,7 +57557,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1972" t="n">
-        <v>0.5569087266922</v>
+        <v>0.556908667087555</v>
       </c>
       <c r="H1972" t="n">
         <v>1258</v>
@@ -57615,7 +57615,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1974" t="n">
-        <v>0.561587631702423</v>
+        <v>0.561587572097778</v>
       </c>
       <c r="H1974" t="n">
         <v>12430</v>
@@ -57760,7 +57760,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G1979" t="n">
-        <v>0.557727932929993</v>
+        <v>0.557727873325348</v>
       </c>
       <c r="H1979" t="n">
         <v>16329</v>
@@ -57789,7 +57789,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1980" t="n">
-        <v>0.550008475780487</v>
+        <v>0.550008535385132</v>
       </c>
       <c r="H1980" t="n">
         <v>8925</v>
@@ -58137,7 +58137,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1992" t="n">
-        <v>0.522990465164185</v>
+        <v>0.522990524768829</v>
       </c>
       <c r="H1992" t="n">
         <v>2</v>
@@ -58166,7 +58166,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1993" t="n">
-        <v>0.511411368846893</v>
+        <v>0.511411309242249</v>
       </c>
       <c r="H1993" t="n">
         <v>5405</v>
@@ -58282,7 +58282,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G1997" t="n">
-        <v>0.513341188430786</v>
+        <v>0.513341248035431</v>
       </c>
       <c r="H1997" t="n">
         <v>5938</v>
@@ -58311,7 +58311,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1998" t="n">
-        <v>0.522990465164185</v>
+        <v>0.522990524768829</v>
       </c>
       <c r="H1998" t="n">
         <v>3143</v>
@@ -58340,7 +58340,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G1999" t="n">
-        <v>0.519130825996399</v>
+        <v>0.519130766391754</v>
       </c>
       <c r="H1999" t="n">
         <v>6157</v>
@@ -58398,7 +58398,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2001" t="n">
-        <v>0.513341188430786</v>
+        <v>0.513341248035431</v>
       </c>
       <c r="H2001" t="n">
         <v>1783</v>
@@ -58456,7 +58456,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2003" t="n">
-        <v>0.511411368846893</v>
+        <v>0.511411309242249</v>
       </c>
       <c r="H2003" t="n">
         <v>3405</v>
@@ -58485,7 +58485,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2004" t="n">
-        <v>0.501762092113495</v>
+        <v>0.50176203250885</v>
       </c>
       <c r="H2004" t="n">
         <v>94494</v>
@@ -58543,7 +58543,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2006" t="n">
-        <v>0.513341188430786</v>
+        <v>0.513341248035431</v>
       </c>
       <c r="H2006" t="n">
         <v>10470</v>
@@ -58630,7 +58630,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2009" t="n">
-        <v>0.513341188430786</v>
+        <v>0.513341248035431</v>
       </c>
       <c r="H2009" t="n">
         <v>101</v>
@@ -58717,7 +58717,7 @@
         <v>0.537999987602234</v>
       </c>
       <c r="G2012" t="n">
-        <v>0.519130825996399</v>
+        <v>0.519130766391754</v>
       </c>
       <c r="H2012" t="n">
         <v>581</v>
@@ -58746,7 +58746,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2013" t="n">
-        <v>0.517201006412506</v>
+        <v>0.517200946807861</v>
       </c>
       <c r="H2013" t="n">
         <v>2500</v>
@@ -58804,7 +58804,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2015" t="n">
-        <v>0.501762092113495</v>
+        <v>0.50176203250885</v>
       </c>
       <c r="H2015" t="n">
         <v>6429</v>
@@ -58833,7 +58833,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2016" t="n">
-        <v>0.517201006412506</v>
+        <v>0.517200946807861</v>
       </c>
       <c r="H2016" t="n">
         <v>8577</v>
@@ -58862,7 +58862,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2017" t="n">
-        <v>0.517201006412506</v>
+        <v>0.517200946807861</v>
       </c>
       <c r="H2017" t="n">
         <v>0</v>
@@ -58891,7 +58891,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2018" t="n">
-        <v>0.509481489658356</v>
+        <v>0.509481549263</v>
       </c>
       <c r="H2018" t="n">
         <v>11268</v>
@@ -58920,7 +58920,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2019" t="n">
-        <v>0.509481489658356</v>
+        <v>0.509481549263</v>
       </c>
       <c r="H2019" t="n">
         <v>0</v>
@@ -59094,7 +59094,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2025" t="n">
-        <v>0.509481489658356</v>
+        <v>0.509481549263</v>
       </c>
       <c r="H2025" t="n">
         <v>2000</v>
@@ -59123,7 +59123,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2026" t="n">
-        <v>0.509481489658356</v>
+        <v>0.509481549263</v>
       </c>
       <c r="H2026" t="n">
         <v>464</v>
@@ -59239,7 +59239,7 @@
         <v>0.51800000667572</v>
       </c>
       <c r="G2030" t="n">
-        <v>0.499832302331924</v>
+        <v>0.499832272529602</v>
       </c>
       <c r="H2030" t="n">
         <v>18004</v>
@@ -59413,7 +59413,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2036" t="n">
-        <v>0.492112815380096</v>
+        <v>0.492112845182419</v>
       </c>
       <c r="H2036" t="n">
         <v>5940</v>
@@ -59471,7 +59471,7 @@
         <v>0.505999982357025</v>
       </c>
       <c r="G2038" t="n">
-        <v>0.488253146409988</v>
+        <v>0.488253116607666</v>
       </c>
       <c r="H2038" t="n">
         <v>1700</v>
@@ -59529,7 +59529,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2040" t="n">
-        <v>0.492112815380096</v>
+        <v>0.492112845182419</v>
       </c>
       <c r="H2040" t="n">
         <v>14595</v>
@@ -59558,7 +59558,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2041" t="n">
-        <v>0.492112815380096</v>
+        <v>0.492112845182419</v>
       </c>
       <c r="H2041" t="n">
         <v>4739</v>
@@ -59587,7 +59587,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2042" t="n">
-        <v>0.492112815380096</v>
+        <v>0.492112845182419</v>
       </c>
       <c r="H2042" t="n">
         <v>6416</v>
@@ -59674,7 +59674,7 @@
         <v>0.501999974250793</v>
       </c>
       <c r="G2045" t="n">
-        <v>0.484393417835236</v>
+        <v>0.484393388032913</v>
       </c>
       <c r="H2045" t="n">
         <v>5704</v>
@@ -59790,7 +59790,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2049" t="n">
-        <v>0.492112815380096</v>
+        <v>0.492112845182419</v>
       </c>
       <c r="H2049" t="n">
         <v>9800</v>
@@ -59819,7 +59819,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2050" t="n">
-        <v>0.492112815380096</v>
+        <v>0.492112845182419</v>
       </c>
       <c r="H2050" t="n">
         <v>1000</v>
@@ -59848,7 +59848,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2051" t="n">
-        <v>0.492112815380096</v>
+        <v>0.492112845182419</v>
       </c>
       <c r="H2051" t="n">
         <v>14972</v>
@@ -59906,7 +59906,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2053" t="n">
-        <v>0.467989683151245</v>
+        <v>0.467989653348923</v>
       </c>
       <c r="H2053" t="n">
         <v>15320</v>
@@ -59935,7 +59935,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G2054" t="n">
-        <v>0.470884472131729</v>
+        <v>0.470884442329407</v>
       </c>
       <c r="H2054" t="n">
         <v>10529</v>
@@ -59964,7 +59964,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G2055" t="n">
-        <v>0.470884472131729</v>
+        <v>0.470884442329407</v>
       </c>
       <c r="H2055" t="n">
         <v>0</v>
@@ -59993,7 +59993,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2056" t="n">
-        <v>0.46027022600174</v>
+        <v>0.460270255804062</v>
       </c>
       <c r="H2056" t="n">
         <v>28839</v>
@@ -60022,7 +60022,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2057" t="n">
-        <v>0.46412992477417</v>
+        <v>0.464129954576492</v>
       </c>
       <c r="H2057" t="n">
         <v>4024</v>
@@ -60051,7 +60051,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2058" t="n">
-        <v>0.46027022600174</v>
+        <v>0.460270255804062</v>
       </c>
       <c r="H2058" t="n">
         <v>7830</v>
@@ -60109,7 +60109,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2060" t="n">
-        <v>0.46027022600174</v>
+        <v>0.460270255804062</v>
       </c>
       <c r="H2060" t="n">
         <v>18433</v>
@@ -60138,7 +60138,7 @@
         <v>0.488000005483627</v>
       </c>
       <c r="G2061" t="n">
-        <v>0.470884472131729</v>
+        <v>0.470884442329407</v>
       </c>
       <c r="H2061" t="n">
         <v>11780</v>
@@ -60254,7 +60254,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2065" t="n">
-        <v>0.467989683151245</v>
+        <v>0.467989653348923</v>
       </c>
       <c r="H2065" t="n">
         <v>2600</v>
@@ -60283,7 +60283,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2066" t="n">
-        <v>0.467989683151245</v>
+        <v>0.467989653348923</v>
       </c>
       <c r="H2066" t="n">
         <v>0</v>
@@ -60312,7 +60312,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2067" t="n">
-        <v>0.467989683151245</v>
+        <v>0.467989653348923</v>
       </c>
       <c r="H2067" t="n">
         <v>6112</v>
@@ -60341,7 +60341,7 @@
         <v>0.485000014305115</v>
       </c>
       <c r="G2068" t="n">
-        <v>0.467989683151245</v>
+        <v>0.467989653348923</v>
       </c>
       <c r="H2068" t="n">
         <v>0</v>
@@ -60486,7 +60486,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2073" t="n">
-        <v>0.46027022600174</v>
+        <v>0.460270255804062</v>
       </c>
       <c r="H2073" t="n">
         <v>24576</v>
@@ -60515,7 +60515,7 @@
         <v>0.476999998092651</v>
       </c>
       <c r="G2074" t="n">
-        <v>0.46027022600174</v>
+        <v>0.460270255804062</v>
       </c>
       <c r="H2074" t="n">
         <v>0</v>
@@ -60602,7 +60602,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2077" t="n">
-        <v>0.450620949268341</v>
+        <v>0.450621008872986</v>
       </c>
       <c r="H2077" t="n">
         <v>3943</v>
@@ -60776,7 +60776,7 @@
         <v>0.46900001168251</v>
       </c>
       <c r="G2083" t="n">
-        <v>0.452550858259201</v>
+        <v>0.452550828456879</v>
       </c>
       <c r="H2083" t="n">
         <v>15830</v>
@@ -60950,7 +60950,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2089" t="n">
-        <v>0.401409715414047</v>
+        <v>0.401409685611725</v>
       </c>
       <c r="H2089" t="n">
         <v>15614</v>
@@ -61008,7 +61008,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2091" t="n">
-        <v>0.383076071739197</v>
+        <v>0.383076101541519</v>
       </c>
       <c r="H2091" t="n">
         <v>12738</v>
@@ -61037,7 +61037,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2092" t="n">
-        <v>0.37632155418396</v>
+        <v>0.376321583986282</v>
       </c>
       <c r="H2092" t="n">
         <v>16216</v>
@@ -61182,7 +61182,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2097" t="n">
-        <v>0.383076071739197</v>
+        <v>0.383076101541519</v>
       </c>
       <c r="H2097" t="n">
         <v>5500</v>
@@ -61298,7 +61298,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2101" t="n">
-        <v>0.378251433372498</v>
+        <v>0.378251403570175</v>
       </c>
       <c r="H2101" t="n">
         <v>31991</v>
@@ -61327,7 +61327,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2102" t="n">
-        <v>0.382111132144928</v>
+        <v>0.38211116194725</v>
       </c>
       <c r="H2102" t="n">
         <v>17631</v>
@@ -61414,7 +61414,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2105" t="n">
-        <v>0.382111132144928</v>
+        <v>0.38211116194725</v>
       </c>
       <c r="H2105" t="n">
         <v>27697</v>
@@ -61443,7 +61443,7 @@
         <v>0.374000012874603</v>
       </c>
       <c r="G2106" t="n">
-        <v>0.360882759094238</v>
+        <v>0.360882729291916</v>
       </c>
       <c r="H2106" t="n">
         <v>24811</v>
@@ -61617,7 +61617,7 @@
         <v>0.398000001907349</v>
       </c>
       <c r="G2112" t="n">
-        <v>0.384041011333466</v>
+        <v>0.384040981531143</v>
       </c>
       <c r="H2112" t="n">
         <v>100</v>
@@ -61646,7 +61646,7 @@
         <v>0.389999985694885</v>
       </c>
       <c r="G2113" t="n">
-        <v>0.37632155418396</v>
+        <v>0.376321583986282</v>
       </c>
       <c r="H2113" t="n">
         <v>8562</v>
@@ -61762,7 +61762,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G2117" t="n">
-        <v>0.356058120727539</v>
+        <v>0.356058090925217</v>
       </c>
       <c r="H2117" t="n">
         <v>4033</v>
@@ -61849,7 +61849,7 @@
         <v>0.386999994516373</v>
       </c>
       <c r="G2120" t="n">
-        <v>0.373426765203476</v>
+        <v>0.373426795005798</v>
       </c>
       <c r="H2120" t="n">
         <v>13582</v>
@@ -61936,7 +61936,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2123" t="n">
-        <v>0.416848540306091</v>
+        <v>0.416848510503769</v>
       </c>
       <c r="H2123" t="n">
         <v>68404</v>
@@ -61965,7 +61965,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2124" t="n">
-        <v>0.401409715414047</v>
+        <v>0.401409685611725</v>
       </c>
       <c r="H2124" t="n">
         <v>97328</v>
@@ -62023,7 +62023,7 @@
         <v>0.416999995708466</v>
       </c>
       <c r="G2126" t="n">
-        <v>0.402374625205994</v>
+        <v>0.402374595403671</v>
       </c>
       <c r="H2126" t="n">
         <v>22877</v>
@@ -62052,7 +62052,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2127" t="n">
-        <v>0.405269354581833</v>
+        <v>0.405269384384155</v>
       </c>
       <c r="H2127" t="n">
         <v>52451</v>
@@ -62313,7 +62313,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2136" t="n">
-        <v>0.378251433372498</v>
+        <v>0.378251403570175</v>
       </c>
       <c r="H2136" t="n">
         <v>1237</v>
@@ -62806,7 +62806,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2153" t="n">
-        <v>0.398514896631241</v>
+        <v>0.398514866828918</v>
       </c>
       <c r="H2153" t="n">
         <v>7378</v>
@@ -62835,7 +62835,7 @@
         <v>0.430000007152557</v>
       </c>
       <c r="G2154" t="n">
-        <v>0.414918661117554</v>
+        <v>0.414918690919876</v>
       </c>
       <c r="H2154" t="n">
         <v>44165</v>
@@ -63096,7 +63096,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2163" t="n">
-        <v>0.401409715414047</v>
+        <v>0.401409685611725</v>
       </c>
       <c r="H2163" t="n">
         <v>11659</v>
@@ -63212,7 +63212,7 @@
         <v>0.426999986171722</v>
       </c>
       <c r="G2167" t="n">
-        <v>0.412023842334747</v>
+        <v>0.41202387213707</v>
       </c>
       <c r="H2167" t="n">
         <v>33001</v>
@@ -63270,7 +63270,7 @@
         <v>0.423000007867813</v>
       </c>
       <c r="G2169" t="n">
-        <v>0.408164203166962</v>
+        <v>0.408164173364639</v>
       </c>
       <c r="H2169" t="n">
         <v>55582</v>
@@ -63299,7 +63299,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2170" t="n">
-        <v>0.401409715414047</v>
+        <v>0.401409685611725</v>
       </c>
       <c r="H2170" t="n">
         <v>21037</v>
@@ -63328,7 +63328,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2171" t="n">
-        <v>0.401409715414047</v>
+        <v>0.401409685611725</v>
       </c>
       <c r="H2171" t="n">
         <v>31998</v>
@@ -63357,7 +63357,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G2172" t="n">
-        <v>0.400444746017456</v>
+        <v>0.400444775819778</v>
       </c>
       <c r="H2172" t="n">
         <v>12152</v>
@@ -63386,7 +63386,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2173" t="n">
-        <v>0.401409715414047</v>
+        <v>0.401409685611725</v>
       </c>
       <c r="H2173" t="n">
         <v>2007</v>
@@ -63415,7 +63415,7 @@
         <v>0.41499999165535</v>
       </c>
       <c r="G2174" t="n">
-        <v>0.400444746017456</v>
+        <v>0.400444775819778</v>
       </c>
       <c r="H2174" t="n">
         <v>1000</v>
@@ -80067,6 +80067,35 @@
         <v>551</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>1.16499996185303</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>1.18499994277954</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>1.15499997138977</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>1525</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -456,7 +456,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G3" t="n">
-        <v>1.55858397483826</v>
+        <v>1.55858409404755</v>
       </c>
       <c r="H3" t="n">
         <v>10710</v>
@@ -514,7 +514,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G5" t="n">
-        <v>1.46544909477234</v>
+        <v>1.46544921398163</v>
       </c>
       <c r="H5" t="n">
         <v>12095</v>
@@ -746,7 +746,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G13" t="n">
-        <v>1.34950566291809</v>
+        <v>1.3495055437088</v>
       </c>
       <c r="H13" t="n">
         <v>6400</v>
@@ -775,7 +775,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>1.26872539520264</v>
+        <v>1.26872551441193</v>
       </c>
       <c r="H14" t="n">
         <v>17780</v>
@@ -833,7 +833,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G16" t="n">
-        <v>1.34950566291809</v>
+        <v>1.3495055437088</v>
       </c>
       <c r="H16" t="n">
         <v>17034</v>
@@ -862,7 +862,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G17" t="n">
-        <v>1.30198776721954</v>
+        <v>1.30198788642883</v>
       </c>
       <c r="H17" t="n">
         <v>5838</v>
@@ -891,7 +891,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G18" t="n">
-        <v>1.30198776721954</v>
+        <v>1.30198788642883</v>
       </c>
       <c r="H18" t="n">
         <v>4474</v>
@@ -1094,7 +1094,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G25" t="n">
-        <v>1.2829806804657</v>
+        <v>1.28298079967499</v>
       </c>
       <c r="H25" t="n">
         <v>21414</v>
@@ -1181,7 +1181,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G28" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H28" t="n">
         <v>6283</v>
@@ -1471,7 +1471,7 @@
         <v>1.32400000095367</v>
       </c>
       <c r="G38" t="n">
-        <v>1.25827157497406</v>
+        <v>1.25827145576477</v>
       </c>
       <c r="H38" t="n">
         <v>12260</v>
@@ -1732,7 +1732,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G47" t="n">
-        <v>1.28108012676239</v>
+        <v>1.2810800075531</v>
       </c>
       <c r="H47" t="n">
         <v>4298</v>
@@ -1761,7 +1761,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G48" t="n">
-        <v>1.28108012676239</v>
+        <v>1.2810800075531</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>1.30103743076324</v>
+        <v>1.30103754997253</v>
       </c>
       <c r="H49" t="n">
         <v>8270</v>
@@ -1877,7 +1877,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G52" t="n">
-        <v>1.32194530963898</v>
+        <v>1.32194542884827</v>
       </c>
       <c r="H52" t="n">
         <v>2834</v>
@@ -1906,7 +1906,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G53" t="n">
-        <v>1.32194530963898</v>
+        <v>1.32194542884827</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>1.32574665546417</v>
+        <v>1.32574677467346</v>
       </c>
       <c r="H59" t="n">
         <v>560</v>
@@ -2225,7 +2225,7 @@
         <v>1.30599999427795</v>
       </c>
       <c r="G64" t="n">
-        <v>1.24116504192352</v>
+        <v>1.24116492271423</v>
       </c>
       <c r="H64" t="n">
         <v>6820</v>
@@ -2254,7 +2254,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G65" t="n">
-        <v>1.26017212867737</v>
+        <v>1.26017200946808</v>
       </c>
       <c r="H65" t="n">
         <v>13431</v>
@@ -2341,7 +2341,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G68" t="n">
-        <v>1.30578923225403</v>
+        <v>1.30578935146332</v>
       </c>
       <c r="H68" t="n">
         <v>119</v>
@@ -2370,7 +2370,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G69" t="n">
-        <v>1.30578923225403</v>
+        <v>1.30578935146332</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G72" t="n">
-        <v>1.30483901500702</v>
+        <v>1.30483889579773</v>
       </c>
       <c r="H72" t="n">
         <v>14416</v>
@@ -2486,7 +2486,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G73" t="n">
-        <v>1.29058372974396</v>
+        <v>1.29058361053467</v>
       </c>
       <c r="H73" t="n">
         <v>5869</v>
@@ -2544,7 +2544,7 @@
         <v>1.31200003623962</v>
       </c>
       <c r="G75" t="n">
-        <v>1.24686717987061</v>
+        <v>1.2468672990799</v>
       </c>
       <c r="H75" t="n">
         <v>4961</v>
@@ -2602,7 +2602,7 @@
         <v>1.32700002193451</v>
       </c>
       <c r="G77" t="n">
-        <v>1.26112258434296</v>
+        <v>1.26112246513367</v>
       </c>
       <c r="H77" t="n">
         <v>14946</v>
@@ -2631,7 +2631,7 @@
         <v>1.34099996089935</v>
       </c>
       <c r="G78" t="n">
-        <v>1.27442765235901</v>
+        <v>1.27442753314972</v>
       </c>
       <c r="H78" t="n">
         <v>3828</v>
@@ -2660,7 +2660,7 @@
         <v>1.34700000286102</v>
       </c>
       <c r="G79" t="n">
-        <v>1.2801296710968</v>
+        <v>1.28012955188751</v>
       </c>
       <c r="H79" t="n">
         <v>6900</v>
@@ -2950,7 +2950,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G89" t="n">
-        <v>1.30483901500702</v>
+        <v>1.30483889579773</v>
       </c>
       <c r="H89" t="n">
         <v>852</v>
@@ -2979,7 +2979,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G90" t="n">
-        <v>1.30103743076324</v>
+        <v>1.30103754997253</v>
       </c>
       <c r="H90" t="n">
         <v>100</v>
@@ -3008,7 +3008,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G91" t="n">
-        <v>1.30103743076324</v>
+        <v>1.30103754997253</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G105" t="n">
-        <v>1.17178916931152</v>
+        <v>1.17178905010223</v>
       </c>
       <c r="H105" t="n">
         <v>3950</v>
@@ -3472,7 +3472,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G107" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749130725861</v>
       </c>
       <c r="H107" t="n">
         <v>2700</v>
@@ -3501,7 +3501,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G108" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749130725861</v>
       </c>
       <c r="H108" t="n">
         <v>500</v>
@@ -3559,7 +3559,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>1.16893804073334</v>
+        <v>1.16893792152405</v>
       </c>
       <c r="H110" t="n">
         <v>3500</v>
@@ -3617,7 +3617,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G112" t="n">
-        <v>1.18224310874939</v>
+        <v>1.1822429895401</v>
       </c>
       <c r="H112" t="n">
         <v>3100</v>
@@ -3791,7 +3791,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G118" t="n">
-        <v>1.17273938655853</v>
+        <v>1.17273950576782</v>
       </c>
       <c r="H118" t="n">
         <v>632</v>
@@ -3820,7 +3820,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G119" t="n">
-        <v>1.18699467182159</v>
+        <v>1.1869945526123</v>
       </c>
       <c r="H119" t="n">
         <v>7654</v>
@@ -3878,7 +3878,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G121" t="n">
-        <v>1.13187408447266</v>
+        <v>1.13187396526337</v>
       </c>
       <c r="H121" t="n">
         <v>5919</v>
@@ -4023,7 +4023,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G126" t="n">
-        <v>0.975065350532532</v>
+        <v>0.975065410137177</v>
       </c>
       <c r="H126" t="n">
         <v>15762</v>
@@ -4081,7 +4081,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G128" t="n">
-        <v>1.12046980857849</v>
+        <v>1.12046992778778</v>
       </c>
       <c r="H128" t="n">
         <v>34445</v>
@@ -4110,7 +4110,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G129" t="n">
-        <v>1.06439876556396</v>
+        <v>1.06439888477325</v>
       </c>
       <c r="H129" t="n">
         <v>33799</v>
@@ -4139,7 +4139,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G130" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H130" t="n">
         <v>9949</v>
@@ -4168,7 +4168,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G131" t="n">
-        <v>1.09005832672119</v>
+        <v>1.09005844593048</v>
       </c>
       <c r="H131" t="n">
         <v>4789</v>
@@ -4226,7 +4226,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G133" t="n">
-        <v>0.995022833347321</v>
+        <v>0.99502295255661</v>
       </c>
       <c r="H133" t="n">
         <v>5798</v>
@@ -4400,7 +4400,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G139" t="n">
-        <v>0.996923506259918</v>
+        <v>0.996923625469208</v>
       </c>
       <c r="H139" t="n">
         <v>1497</v>
@@ -4574,7 +4574,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G145" t="n">
-        <v>0.975065350532532</v>
+        <v>0.975065410137177</v>
       </c>
       <c r="H145" t="n">
         <v>6955</v>
@@ -4603,7 +4603,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G146" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H146" t="n">
         <v>7470</v>
@@ -4632,7 +4632,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G147" t="n">
-        <v>0.995022833347321</v>
+        <v>0.99502295255661</v>
       </c>
       <c r="H147" t="n">
         <v>10351</v>
@@ -4661,7 +4661,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>0.988370358943939</v>
+        <v>0.98837023973465</v>
       </c>
       <c r="H148" t="n">
         <v>13390</v>
@@ -4777,7 +4777,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G152" t="n">
-        <v>0.986469686031342</v>
+        <v>0.986469626426697</v>
       </c>
       <c r="H152" t="n">
         <v>5343</v>
@@ -4806,7 +4806,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G153" t="n">
-        <v>0.986469686031342</v>
+        <v>0.986469626426697</v>
       </c>
       <c r="H153" t="n">
         <v>1577</v>
@@ -5154,7 +5154,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G165" t="n">
-        <v>0.963661134243011</v>
+        <v>0.963661074638367</v>
       </c>
       <c r="H165" t="n">
         <v>3542</v>
@@ -5183,7 +5183,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G166" t="n">
-        <v>0.967462599277496</v>
+        <v>0.967462539672852</v>
       </c>
       <c r="H166" t="n">
         <v>14544</v>
@@ -5270,7 +5270,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G169" t="n">
-        <v>0.986469686031342</v>
+        <v>0.986469626426697</v>
       </c>
       <c r="H169" t="n">
         <v>835</v>
@@ -5299,7 +5299,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G170" t="n">
-        <v>0.973164737224579</v>
+        <v>0.973164796829224</v>
       </c>
       <c r="H170" t="n">
         <v>7003</v>
@@ -5328,7 +5328,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G171" t="n">
-        <v>0.995022833347321</v>
+        <v>0.99502295255661</v>
       </c>
       <c r="H171" t="n">
         <v>2072</v>
@@ -5415,7 +5415,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G174" t="n">
-        <v>0.996923506259918</v>
+        <v>0.996923625469208</v>
       </c>
       <c r="H174" t="n">
         <v>500</v>
@@ -5473,7 +5473,7 @@
         <v>1.1139999628067</v>
       </c>
       <c r="G176" t="n">
-        <v>1.05869674682617</v>
+        <v>1.05869662761688</v>
       </c>
       <c r="H176" t="n">
         <v>20400</v>
@@ -5531,7 +5531,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G178" t="n">
-        <v>1.15183162689209</v>
+        <v>1.1518315076828</v>
       </c>
       <c r="H178" t="n">
         <v>81424</v>
@@ -5879,7 +5879,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G190" t="n">
-        <v>1.00262570381165</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H190" t="n">
         <v>1609</v>
@@ -5908,7 +5908,7 @@
         <v>1.04299998283386</v>
       </c>
       <c r="G191" t="n">
-        <v>0.99122142791748</v>
+        <v>0.99122154712677</v>
       </c>
       <c r="H191" t="n">
         <v>16155</v>
@@ -5966,7 +5966,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H193" t="n">
         <v>3500</v>
@@ -5995,7 +5995,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G194" t="n">
-        <v>0.996923506259918</v>
+        <v>0.996923625469208</v>
       </c>
       <c r="H194" t="n">
         <v>3572</v>
@@ -6082,7 +6082,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G197" t="n">
-        <v>0.989320695400238</v>
+        <v>0.989320576190948</v>
       </c>
       <c r="H197" t="n">
         <v>16909</v>
@@ -6140,7 +6140,7 @@
         <v>1.03799998760223</v>
       </c>
       <c r="G199" t="n">
-        <v>0.986469686031342</v>
+        <v>0.986469626426697</v>
       </c>
       <c r="H199" t="n">
         <v>1462</v>
@@ -6198,7 +6198,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>0.988370358943939</v>
+        <v>0.98837023973465</v>
       </c>
       <c r="H201" t="n">
         <v>500</v>
@@ -6227,7 +6227,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G202" t="n">
-        <v>0.963661134243011</v>
+        <v>0.963661074638367</v>
       </c>
       <c r="H202" t="n">
         <v>4000</v>
@@ -6459,7 +6459,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G210" t="n">
-        <v>0.971263825893402</v>
+        <v>0.971263885498047</v>
       </c>
       <c r="H210" t="n">
         <v>1000</v>
@@ -6517,7 +6517,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G212" t="n">
-        <v>0.973164737224579</v>
+        <v>0.973164796829224</v>
       </c>
       <c r="H212" t="n">
         <v>900</v>
@@ -6604,7 +6604,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G215" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H215" t="n">
         <v>2077</v>
@@ -6662,7 +6662,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G217" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H217" t="n">
         <v>480</v>
@@ -6778,7 +6778,7 @@
         <v>0.996999979019165</v>
       </c>
       <c r="G221" t="n">
-        <v>0.947505056858063</v>
+        <v>0.947504997253418</v>
       </c>
       <c r="H221" t="n">
         <v>16472</v>
@@ -6807,7 +6807,7 @@
         <v>1.02199995517731</v>
       </c>
       <c r="G222" t="n">
-        <v>0.971263825893402</v>
+        <v>0.971263885498047</v>
       </c>
       <c r="H222" t="n">
         <v>700</v>
@@ -6836,7 +6836,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G223" t="n">
-        <v>0.973164737224579</v>
+        <v>0.973164796829224</v>
       </c>
       <c r="H223" t="n">
         <v>5403</v>
@@ -6865,7 +6865,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>1.02638471126556</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H224" t="n">
         <v>16296</v>
@@ -6894,7 +6894,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G225" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H225" t="n">
         <v>27306</v>
@@ -6923,7 +6923,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G226" t="n">
-        <v>0.961760342121124</v>
+        <v>0.961760401725769</v>
       </c>
       <c r="H226" t="n">
         <v>6335</v>
@@ -6952,7 +6952,7 @@
         <v>1.01800000667572</v>
       </c>
       <c r="G227" t="n">
-        <v>0.967462599277496</v>
+        <v>0.967462539672852</v>
       </c>
       <c r="H227" t="n">
         <v>15742</v>
@@ -7097,7 +7097,7 @@
         <v>0.998499989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>0.948930561542511</v>
+        <v>0.948930501937866</v>
       </c>
       <c r="H232" t="n">
         <v>17878</v>
@@ -7184,7 +7184,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G235" t="n">
-        <v>0.989320695400238</v>
+        <v>0.989320576190948</v>
       </c>
       <c r="H235" t="n">
         <v>10528</v>
@@ -7213,7 +7213,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G236" t="n">
-        <v>0.973164737224579</v>
+        <v>0.973164796829224</v>
       </c>
       <c r="H236" t="n">
         <v>261</v>
@@ -7242,7 +7242,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G237" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H237" t="n">
         <v>10000</v>
@@ -7300,7 +7300,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G239" t="n">
-        <v>0.961760342121124</v>
+        <v>0.961760401725769</v>
       </c>
       <c r="H239" t="n">
         <v>2678</v>
@@ -7387,7 +7387,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G242" t="n">
-        <v>1.00262570381165</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H242" t="n">
         <v>340</v>
@@ -7474,7 +7474,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G245" t="n">
-        <v>0.975065350532532</v>
+        <v>0.975065410137177</v>
       </c>
       <c r="H245" t="n">
         <v>2093</v>
@@ -7590,7 +7590,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G249" t="n">
-        <v>0.982668280601501</v>
+        <v>0.982668220996857</v>
       </c>
       <c r="H249" t="n">
         <v>204848</v>
@@ -7619,7 +7619,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G250" t="n">
-        <v>0.973164737224579</v>
+        <v>0.973164796829224</v>
       </c>
       <c r="H250" t="n">
         <v>51760</v>
@@ -7648,7 +7648,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G251" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H251" t="n">
         <v>36947</v>
@@ -7677,7 +7677,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G252" t="n">
-        <v>0.963661134243011</v>
+        <v>0.963661074638367</v>
       </c>
       <c r="H252" t="n">
         <v>13025</v>
@@ -7822,7 +7822,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G257" t="n">
-        <v>0.989320695400238</v>
+        <v>0.989320576190948</v>
       </c>
       <c r="H257" t="n">
         <v>97577</v>
@@ -7851,7 +7851,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G258" t="n">
-        <v>0.983618438243866</v>
+        <v>0.983618497848511</v>
       </c>
       <c r="H258" t="n">
         <v>98439</v>
@@ -7909,7 +7909,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>0.988370358943939</v>
+        <v>0.98837023973465</v>
       </c>
       <c r="H260" t="n">
         <v>96748</v>
@@ -7938,7 +7938,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G261" t="n">
-        <v>1.04254066944122</v>
+        <v>1.04254055023193</v>
       </c>
       <c r="H261" t="n">
         <v>183087</v>
@@ -8083,7 +8083,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G266" t="n">
-        <v>1.39227163791656</v>
+        <v>1.39227175712585</v>
       </c>
       <c r="H266" t="n">
         <v>81832</v>
@@ -8315,7 +8315,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G274" t="n">
-        <v>1.26872539520264</v>
+        <v>1.26872551441193</v>
       </c>
       <c r="H274" t="n">
         <v>297056</v>
@@ -8344,7 +8344,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G275" t="n">
-        <v>1.38371849060059</v>
+        <v>1.3837183713913</v>
       </c>
       <c r="H275" t="n">
         <v>660972</v>
@@ -8576,7 +8576,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G283" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749130725861</v>
       </c>
       <c r="H283" t="n">
         <v>73831</v>
@@ -8634,7 +8634,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G285" t="n">
-        <v>1.13947689533234</v>
+        <v>1.13947701454163</v>
       </c>
       <c r="H285" t="n">
         <v>47058</v>
@@ -8663,7 +8663,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G286" t="n">
-        <v>1.17178916931152</v>
+        <v>1.17178905010223</v>
       </c>
       <c r="H286" t="n">
         <v>51660</v>
@@ -8750,7 +8750,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G289" t="n">
-        <v>1.09005832672119</v>
+        <v>1.09005844593048</v>
       </c>
       <c r="H289" t="n">
         <v>64492</v>
@@ -8808,7 +8808,7 @@
         <v>1.14100003242493</v>
       </c>
       <c r="G291" t="n">
-        <v>1.0843563079834</v>
+        <v>1.08435642719269</v>
       </c>
       <c r="H291" t="n">
         <v>36646</v>
@@ -8837,7 +8837,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G292" t="n">
-        <v>1.09766125679016</v>
+        <v>1.09766113758087</v>
       </c>
       <c r="H292" t="n">
         <v>16347</v>
@@ -8866,7 +8866,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G293" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H293" t="n">
         <v>4906</v>
@@ -8982,7 +8982,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G297" t="n">
-        <v>1.05964696407318</v>
+        <v>1.05964708328247</v>
       </c>
       <c r="H297" t="n">
         <v>16179</v>
@@ -9011,7 +9011,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G298" t="n">
-        <v>1.06439876556396</v>
+        <v>1.06439888477325</v>
       </c>
       <c r="H298" t="n">
         <v>25146</v>
@@ -9069,7 +9069,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>1.20695233345032</v>
+        <v>1.20695221424103</v>
       </c>
       <c r="H300" t="n">
         <v>416286</v>
@@ -9156,7 +9156,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>1.16893804073334</v>
+        <v>1.16893792152405</v>
       </c>
       <c r="H303" t="n">
         <v>24748</v>
@@ -9301,7 +9301,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G308" t="n">
-        <v>1.15943443775177</v>
+        <v>1.15943455696106</v>
       </c>
       <c r="H308" t="n">
         <v>50763</v>
@@ -9388,7 +9388,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G311" t="n">
-        <v>1.15183162689209</v>
+        <v>1.1518315076828</v>
       </c>
       <c r="H311" t="n">
         <v>17084</v>
@@ -9475,7 +9475,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G314" t="n">
-        <v>1.13567566871643</v>
+        <v>1.13567554950714</v>
       </c>
       <c r="H314" t="n">
         <v>30226</v>
@@ -9649,7 +9649,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G320" t="n">
-        <v>1.13567566871643</v>
+        <v>1.13567554950714</v>
       </c>
       <c r="H320" t="n">
         <v>15262</v>
@@ -9707,7 +9707,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G322" t="n">
-        <v>1.16323566436768</v>
+        <v>1.16323578357697</v>
       </c>
       <c r="H322" t="n">
         <v>56748</v>
@@ -9736,7 +9736,7 @@
         <v>1.22300004959106</v>
       </c>
       <c r="G323" t="n">
-        <v>1.16228556632996</v>
+        <v>1.16228544712067</v>
       </c>
       <c r="H323" t="n">
         <v>12953</v>
@@ -9997,7 +9997,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G332" t="n">
-        <v>1.12046980857849</v>
+        <v>1.12046992778778</v>
       </c>
       <c r="H332" t="n">
         <v>29437</v>
@@ -10026,7 +10026,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G333" t="n">
-        <v>1.12332093715668</v>
+        <v>1.12332105636597</v>
       </c>
       <c r="H333" t="n">
         <v>15092</v>
@@ -10142,7 +10142,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G337" t="n">
-        <v>1.115718126297</v>
+        <v>1.11571800708771</v>
       </c>
       <c r="H337" t="n">
         <v>2860</v>
@@ -10171,7 +10171,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G338" t="n">
-        <v>1.12046980857849</v>
+        <v>1.12046992778778</v>
       </c>
       <c r="H338" t="n">
         <v>12735</v>
@@ -10258,7 +10258,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G341" t="n">
-        <v>1.11856913566589</v>
+        <v>1.11856925487518</v>
       </c>
       <c r="H341" t="n">
         <v>13730</v>
@@ -10316,7 +10316,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G343" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H343" t="n">
         <v>13913</v>
@@ -10345,7 +10345,7 @@
         <v>1.16600000858307</v>
       </c>
       <c r="G344" t="n">
-        <v>1.10811531543732</v>
+        <v>1.10811519622803</v>
       </c>
       <c r="H344" t="n">
         <v>19157</v>
@@ -10374,7 +10374,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G345" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H345" t="n">
         <v>6925</v>
@@ -10461,7 +10461,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G348" t="n">
-        <v>1.115718126297</v>
+        <v>1.11571800708771</v>
       </c>
       <c r="H348" t="n">
         <v>15070</v>
@@ -10606,7 +10606,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G353" t="n">
-        <v>1.07770383358002</v>
+        <v>1.07770371437073</v>
       </c>
       <c r="H353" t="n">
         <v>33956</v>
@@ -10722,7 +10722,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G357" t="n">
-        <v>1.07010090351105</v>
+        <v>1.07010102272034</v>
       </c>
       <c r="H357" t="n">
         <v>20350</v>
@@ -10780,7 +10780,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G359" t="n">
-        <v>1.06249821186066</v>
+        <v>1.06249809265137</v>
       </c>
       <c r="H359" t="n">
         <v>87083</v>
@@ -10867,7 +10867,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G362" t="n">
-        <v>1.09956192970276</v>
+        <v>1.09956204891205</v>
       </c>
       <c r="H362" t="n">
         <v>393819</v>
@@ -11012,7 +11012,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G367" t="n">
-        <v>1.0501434803009</v>
+        <v>1.05014359951019</v>
       </c>
       <c r="H367" t="n">
         <v>43857</v>
@@ -11128,7 +11128,7 @@
         <v>1.10099995136261</v>
       </c>
       <c r="G371" t="n">
-        <v>1.04634201526642</v>
+        <v>1.04634213447571</v>
       </c>
       <c r="H371" t="n">
         <v>16691</v>
@@ -11273,7 +11273,7 @@
         <v>1.14100003242493</v>
       </c>
       <c r="G376" t="n">
-        <v>1.0843563079834</v>
+        <v>1.08435642719269</v>
       </c>
       <c r="H376" t="n">
         <v>26349</v>
@@ -11447,7 +11447,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G382" t="n">
-        <v>1.09005832672119</v>
+        <v>1.09005844593048</v>
       </c>
       <c r="H382" t="n">
         <v>16300</v>
@@ -11650,7 +11650,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G389" t="n">
-        <v>1.13947689533234</v>
+        <v>1.13947701454163</v>
       </c>
       <c r="H389" t="n">
         <v>14550</v>
@@ -11679,7 +11679,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G390" t="n">
-        <v>1.13947689533234</v>
+        <v>1.13947701454163</v>
       </c>
       <c r="H390" t="n">
         <v>6972</v>
@@ -11853,7 +11853,7 @@
         <v>1.20200002193451</v>
       </c>
       <c r="G396" t="n">
-        <v>1.14232814311981</v>
+        <v>1.14232802391052</v>
       </c>
       <c r="H396" t="n">
         <v>29872</v>
@@ -11911,7 +11911,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G398" t="n">
-        <v>1.13947689533234</v>
+        <v>1.13947701454163</v>
       </c>
       <c r="H398" t="n">
         <v>13357</v>
@@ -11940,7 +11940,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G399" t="n">
-        <v>1.12332093715668</v>
+        <v>1.12332105636597</v>
       </c>
       <c r="H399" t="n">
         <v>13610</v>
@@ -11969,7 +11969,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G400" t="n">
-        <v>1.11856913566589</v>
+        <v>1.11856925487518</v>
       </c>
       <c r="H400" t="n">
         <v>8359</v>
@@ -12056,7 +12056,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G403" t="n">
-        <v>1.11856913566589</v>
+        <v>1.11856925487518</v>
       </c>
       <c r="H403" t="n">
         <v>15262</v>
@@ -12172,7 +12172,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G407" t="n">
-        <v>1.115718126297</v>
+        <v>1.11571800708771</v>
       </c>
       <c r="H407" t="n">
         <v>7147</v>
@@ -12201,7 +12201,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G408" t="n">
-        <v>1.11761879920959</v>
+        <v>1.11761868000031</v>
       </c>
       <c r="H408" t="n">
         <v>6600</v>
@@ -12259,7 +12259,7 @@
         <v>1.15299999713898</v>
       </c>
       <c r="G410" t="n">
-        <v>1.09576070308685</v>
+        <v>1.09576058387756</v>
       </c>
       <c r="H410" t="n">
         <v>2558</v>
@@ -12317,7 +12317,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G412" t="n">
-        <v>1.1195193529129</v>
+        <v>1.11951947212219</v>
       </c>
       <c r="H412" t="n">
         <v>16500</v>
@@ -12404,7 +12404,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G415" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H415" t="n">
         <v>1660</v>
@@ -12549,7 +12549,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G420" t="n">
-        <v>1.1195193529129</v>
+        <v>1.11951947212219</v>
       </c>
       <c r="H420" t="n">
         <v>29208</v>
@@ -12636,7 +12636,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G423" t="n">
-        <v>1.16893804073334</v>
+        <v>1.16893792152405</v>
       </c>
       <c r="H423" t="n">
         <v>227097</v>
@@ -12723,7 +12723,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G426" t="n">
-        <v>1.13567566871643</v>
+        <v>1.13567554950714</v>
       </c>
       <c r="H426" t="n">
         <v>2930</v>
@@ -12752,7 +12752,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G427" t="n">
-        <v>1.13567566871643</v>
+        <v>1.13567554950714</v>
       </c>
       <c r="H427" t="n">
         <v>23775</v>
@@ -12839,7 +12839,7 @@
         <v>1.18099999427795</v>
       </c>
       <c r="G430" t="n">
-        <v>1.12237071990967</v>
+        <v>1.12237060070038</v>
       </c>
       <c r="H430" t="n">
         <v>13326</v>
@@ -12897,7 +12897,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G432" t="n">
-        <v>1.13567566871643</v>
+        <v>1.13567554950714</v>
       </c>
       <c r="H432" t="n">
         <v>23557</v>
@@ -12926,7 +12926,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G433" t="n">
-        <v>1.12332093715668</v>
+        <v>1.12332105636597</v>
       </c>
       <c r="H433" t="n">
         <v>7710</v>
@@ -13129,7 +13129,7 @@
         <v>1.17400002479553</v>
       </c>
       <c r="G440" t="n">
-        <v>1.115718126297</v>
+        <v>1.11571800708771</v>
       </c>
       <c r="H440" t="n">
         <v>9872</v>
@@ -13187,7 +13187,7 @@
         <v>1.182000041008</v>
       </c>
       <c r="G442" t="n">
-        <v>1.12332093715668</v>
+        <v>1.12332105636597</v>
       </c>
       <c r="H442" t="n">
         <v>19435</v>
@@ -13216,7 +13216,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G443" t="n">
-        <v>1.11761879920959</v>
+        <v>1.11761868000031</v>
       </c>
       <c r="H443" t="n">
         <v>9327</v>
@@ -13303,7 +13303,7 @@
         <v>1.18099999427795</v>
       </c>
       <c r="G446" t="n">
-        <v>1.12237071990967</v>
+        <v>1.12237060070038</v>
       </c>
       <c r="H446" t="n">
         <v>45363</v>
@@ -13361,7 +13361,7 @@
         <v>1.22300004959106</v>
       </c>
       <c r="G448" t="n">
-        <v>1.16228556632996</v>
+        <v>1.16228544712067</v>
       </c>
       <c r="H448" t="n">
         <v>136567</v>
@@ -13506,7 +13506,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G453" t="n">
-        <v>1.20505154132843</v>
+        <v>1.20505142211914</v>
       </c>
       <c r="H453" t="n">
         <v>91082</v>
@@ -13593,7 +13593,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G456" t="n">
-        <v>1.17178916931152</v>
+        <v>1.17178905010223</v>
       </c>
       <c r="H456" t="n">
         <v>20072</v>
@@ -13622,7 +13622,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G457" t="n">
-        <v>1.17273938655853</v>
+        <v>1.17273950576782</v>
       </c>
       <c r="H457" t="n">
         <v>21775</v>
@@ -13709,7 +13709,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G460" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749130725861</v>
       </c>
       <c r="H460" t="n">
         <v>19410</v>
@@ -13941,7 +13941,7 @@
         <v>1.22300004959106</v>
       </c>
       <c r="G468" t="n">
-        <v>1.16228556632996</v>
+        <v>1.16228544712067</v>
       </c>
       <c r="H468" t="n">
         <v>5718</v>
@@ -14028,7 +14028,7 @@
         <v>1.25600004196167</v>
       </c>
       <c r="G471" t="n">
-        <v>1.19364714622498</v>
+        <v>1.19364726543427</v>
       </c>
       <c r="H471" t="n">
         <v>268871</v>
@@ -14115,7 +14115,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>1.20695233345032</v>
+        <v>1.20695221424103</v>
       </c>
       <c r="H474" t="n">
         <v>221096</v>
@@ -14173,7 +14173,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G476" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749130725861</v>
       </c>
       <c r="H476" t="n">
         <v>127242</v>
@@ -14231,7 +14231,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G478" t="n">
-        <v>1.16703736782074</v>
+        <v>1.16703724861145</v>
       </c>
       <c r="H478" t="n">
         <v>11110</v>
@@ -14318,7 +14318,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G481" t="n">
-        <v>1.1195193529129</v>
+        <v>1.11951947212219</v>
       </c>
       <c r="H481" t="n">
         <v>25391</v>
@@ -14347,7 +14347,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G482" t="n">
-        <v>1.12046980857849</v>
+        <v>1.12046992778778</v>
       </c>
       <c r="H482" t="n">
         <v>3732</v>
@@ -14376,7 +14376,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G483" t="n">
-        <v>1.13567566871643</v>
+        <v>1.13567554950714</v>
       </c>
       <c r="H483" t="n">
         <v>4602</v>
@@ -14434,7 +14434,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G485" t="n">
-        <v>1.13567566871643</v>
+        <v>1.13567554950714</v>
       </c>
       <c r="H485" t="n">
         <v>5311</v>
@@ -14550,7 +14550,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G489" t="n">
-        <v>1.11856913566589</v>
+        <v>1.11856925487518</v>
       </c>
       <c r="H489" t="n">
         <v>10010</v>
@@ -14637,7 +14637,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G492" t="n">
-        <v>1.12046980857849</v>
+        <v>1.12046992778778</v>
       </c>
       <c r="H492" t="n">
         <v>5587</v>
@@ -14666,7 +14666,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G493" t="n">
-        <v>1.12046980857849</v>
+        <v>1.12046992778778</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G496" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H496" t="n">
         <v>2297</v>
@@ -14985,7 +14985,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G504" t="n">
-        <v>1.11856913566589</v>
+        <v>1.11856925487518</v>
       </c>
       <c r="H504" t="n">
         <v>15643</v>
@@ -15072,7 +15072,7 @@
         <v>1.15799999237061</v>
       </c>
       <c r="G507" t="n">
-        <v>1.10051226615906</v>
+        <v>1.10051238536835</v>
       </c>
       <c r="H507" t="n">
         <v>2976</v>
@@ -15101,7 +15101,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G508" t="n">
-        <v>1.10431373119354</v>
+        <v>1.10431385040283</v>
       </c>
       <c r="H508" t="n">
         <v>5415</v>
@@ -15188,7 +15188,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G511" t="n">
-        <v>1.13187408447266</v>
+        <v>1.13187396526337</v>
       </c>
       <c r="H511" t="n">
         <v>3108</v>
@@ -15304,7 +15304,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G515" t="n">
-        <v>1.13567566871643</v>
+        <v>1.13567554950714</v>
       </c>
       <c r="H515" t="n">
         <v>9430</v>
@@ -15333,7 +15333,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G516" t="n">
-        <v>1.13567566871643</v>
+        <v>1.13567554950714</v>
       </c>
       <c r="H516" t="n">
         <v>47735</v>
@@ -15362,7 +15362,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G517" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H517" t="n">
         <v>37428</v>
@@ -15449,7 +15449,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G520" t="n">
-        <v>1.09766125679016</v>
+        <v>1.09766113758087</v>
       </c>
       <c r="H520" t="n">
         <v>20364</v>
@@ -15913,7 +15913,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G536" t="n">
-        <v>1.06439876556396</v>
+        <v>1.06439888477325</v>
       </c>
       <c r="H536" t="n">
         <v>8150</v>
@@ -16029,7 +16029,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G540" t="n">
-        <v>1.07390236854553</v>
+        <v>1.07390248775482</v>
       </c>
       <c r="H540" t="n">
         <v>16999</v>
@@ -16087,7 +16087,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G542" t="n">
-        <v>1.07390236854553</v>
+        <v>1.07390248775482</v>
       </c>
       <c r="H542" t="n">
         <v>6521</v>
@@ -16116,7 +16116,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G543" t="n">
-        <v>1.0501434803009</v>
+        <v>1.05014359951019</v>
       </c>
       <c r="H543" t="n">
         <v>1293</v>
@@ -16174,7 +16174,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G545" t="n">
-        <v>1.07390236854553</v>
+        <v>1.07390248775482</v>
       </c>
       <c r="H545" t="n">
         <v>3680</v>
@@ -16203,7 +16203,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G546" t="n">
-        <v>1.07390236854553</v>
+        <v>1.07390248775482</v>
       </c>
       <c r="H546" t="n">
         <v>5525</v>
@@ -16232,7 +16232,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G547" t="n">
-        <v>1.07390236854553</v>
+        <v>1.07390248775482</v>
       </c>
       <c r="H547" t="n">
         <v>2500</v>
@@ -16522,7 +16522,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G557" t="n">
-        <v>1.05964696407318</v>
+        <v>1.05964708328247</v>
       </c>
       <c r="H557" t="n">
         <v>5187</v>
@@ -16551,7 +16551,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G558" t="n">
-        <v>1.05964696407318</v>
+        <v>1.05964708328247</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -16783,7 +16783,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G566" t="n">
-        <v>1.05964696407318</v>
+        <v>1.05964708328247</v>
       </c>
       <c r="H566" t="n">
         <v>13910</v>
@@ -16870,7 +16870,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G569" t="n">
-        <v>1.0501434803009</v>
+        <v>1.05014359951019</v>
       </c>
       <c r="H569" t="n">
         <v>6375</v>
@@ -16957,7 +16957,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G572" t="n">
-        <v>1.05964696407318</v>
+        <v>1.05964708328247</v>
       </c>
       <c r="H572" t="n">
         <v>290</v>
@@ -17102,7 +17102,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G577" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H577" t="n">
         <v>67253</v>
@@ -17189,7 +17189,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G580" t="n">
-        <v>1.06439876556396</v>
+        <v>1.06439888477325</v>
       </c>
       <c r="H580" t="n">
         <v>16675</v>
@@ -17305,7 +17305,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G584" t="n">
-        <v>1.07390236854553</v>
+        <v>1.07390248775482</v>
       </c>
       <c r="H584" t="n">
         <v>31167</v>
@@ -17392,7 +17392,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G587" t="n">
-        <v>1.06439876556396</v>
+        <v>1.06439888477325</v>
       </c>
       <c r="H587" t="n">
         <v>13671</v>
@@ -17508,7 +17508,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G591" t="n">
-        <v>1.0501434803009</v>
+        <v>1.05014359951019</v>
       </c>
       <c r="H591" t="n">
         <v>4775</v>
@@ -17537,7 +17537,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G592" t="n">
-        <v>1.0501434803009</v>
+        <v>1.05014359951019</v>
       </c>
       <c r="H592" t="n">
         <v>834</v>
@@ -17624,7 +17624,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G595" t="n">
-        <v>1.02638471126556</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H595" t="n">
         <v>4500</v>
@@ -17682,7 +17682,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G597" t="n">
-        <v>1.02638471126556</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H597" t="n">
         <v>17100</v>
@@ -17798,7 +17798,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G601" t="n">
-        <v>1.05964696407318</v>
+        <v>1.05964708328247</v>
       </c>
       <c r="H601" t="n">
         <v>7370</v>
@@ -17856,7 +17856,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G603" t="n">
-        <v>1.05964696407318</v>
+        <v>1.05964708328247</v>
       </c>
       <c r="H603" t="n">
         <v>162004</v>
@@ -17885,7 +17885,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G604" t="n">
-        <v>1.06439876556396</v>
+        <v>1.06439888477325</v>
       </c>
       <c r="H604" t="n">
         <v>34087</v>
@@ -17914,7 +17914,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G605" t="n">
-        <v>1.02638471126556</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H605" t="n">
         <v>4449</v>
@@ -18262,7 +18262,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G617" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H617" t="n">
         <v>22297</v>
@@ -18320,7 +18320,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G619" t="n">
-        <v>0.974115014076233</v>
+        <v>0.974115073680878</v>
       </c>
       <c r="H619" t="n">
         <v>1495</v>
@@ -18349,7 +18349,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G620" t="n">
-        <v>0.974115014076233</v>
+        <v>0.974115073680878</v>
       </c>
       <c r="H620" t="n">
         <v>6029</v>
@@ -18407,7 +18407,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G622" t="n">
-        <v>0.948455393314362</v>
+        <v>0.948455333709717</v>
       </c>
       <c r="H622" t="n">
         <v>10698</v>
@@ -18436,7 +18436,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H623" t="n">
         <v>2010</v>
@@ -18465,7 +18465,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18639,7 +18639,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G630" t="n">
-        <v>0.948455393314362</v>
+        <v>0.948455333709717</v>
       </c>
       <c r="H630" t="n">
         <v>5204</v>
@@ -18668,7 +18668,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G631" t="n">
-        <v>0.944653928279877</v>
+        <v>0.944653987884521</v>
       </c>
       <c r="H631" t="n">
         <v>2000</v>
@@ -18929,7 +18929,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G640" t="n">
-        <v>0.929448187351227</v>
+        <v>0.929448246955872</v>
       </c>
       <c r="H640" t="n">
         <v>7994</v>
@@ -18958,7 +18958,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G641" t="n">
-        <v>0.929448187351227</v>
+        <v>0.929448246955872</v>
       </c>
       <c r="H641" t="n">
         <v>0</v>
@@ -19045,7 +19045,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G644" t="n">
-        <v>0.938951790332794</v>
+        <v>0.938951730728149</v>
       </c>
       <c r="H644" t="n">
         <v>822</v>
@@ -19219,7 +19219,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G650" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H650" t="n">
         <v>5923</v>
@@ -19364,7 +19364,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G655" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H655" t="n">
         <v>4810</v>
@@ -19393,7 +19393,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G656" t="n">
-        <v>0.904739022254944</v>
+        <v>0.904739081859589</v>
       </c>
       <c r="H656" t="n">
         <v>4776</v>
@@ -19422,7 +19422,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G657" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H657" t="n">
         <v>2580</v>
@@ -19712,7 +19712,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G667" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H667" t="n">
         <v>3010</v>
@@ -19741,7 +19741,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G668" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H668" t="n">
         <v>1315</v>
@@ -19770,7 +19770,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G669" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H669" t="n">
         <v>0</v>
@@ -20031,7 +20031,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G678" t="n">
-        <v>0.880029737949371</v>
+        <v>0.880029797554016</v>
       </c>
       <c r="H678" t="n">
         <v>6164</v>
@@ -20060,7 +20060,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G679" t="n">
-        <v>0.880029737949371</v>
+        <v>0.880029797554016</v>
       </c>
       <c r="H679" t="n">
         <v>0</v>
@@ -20118,7 +20118,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G681" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H681" t="n">
         <v>1709</v>
@@ -20176,7 +20176,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G683" t="n">
-        <v>0.868625462055206</v>
+        <v>0.868625521659851</v>
       </c>
       <c r="H683" t="n">
         <v>12885</v>
@@ -20205,7 +20205,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G684" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H684" t="n">
         <v>35108</v>
@@ -20263,7 +20263,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G686" t="n">
-        <v>0.942753195762634</v>
+        <v>0.942753255367279</v>
       </c>
       <c r="H686" t="n">
         <v>8065</v>
@@ -20379,7 +20379,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H690" t="n">
         <v>17802</v>
@@ -20437,7 +20437,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G692" t="n">
-        <v>0.904739022254944</v>
+        <v>0.904739081859589</v>
       </c>
       <c r="H692" t="n">
         <v>4862</v>
@@ -20466,7 +20466,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G693" t="n">
-        <v>0.904739022254944</v>
+        <v>0.904739081859589</v>
       </c>
       <c r="H693" t="n">
         <v>4465</v>
@@ -20495,7 +20495,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G694" t="n">
-        <v>0.929448187351227</v>
+        <v>0.929448246955872</v>
       </c>
       <c r="H694" t="n">
         <v>5765</v>
@@ -20524,7 +20524,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G695" t="n">
-        <v>0.921845436096191</v>
+        <v>0.921845376491547</v>
       </c>
       <c r="H695" t="n">
         <v>12680</v>
@@ -20669,7 +20669,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G700" t="n">
-        <v>0.929448187351227</v>
+        <v>0.929448246955872</v>
       </c>
       <c r="H700" t="n">
         <v>89315</v>
@@ -20698,7 +20698,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G701" t="n">
-        <v>0.921845436096191</v>
+        <v>0.921845376491547</v>
       </c>
       <c r="H701" t="n">
         <v>16266</v>
@@ -20785,7 +20785,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H704" t="n">
         <v>10874</v>
@@ -20814,7 +20814,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G705" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H705" t="n">
         <v>4170</v>
@@ -20872,7 +20872,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G707" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H707" t="n">
         <v>7325</v>
@@ -21162,7 +21162,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G717" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H717" t="n">
         <v>14233</v>
@@ -21278,7 +21278,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G721" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H721" t="n">
         <v>770</v>
@@ -21307,7 +21307,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G722" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H722" t="n">
         <v>632</v>
@@ -21336,7 +21336,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G723" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H723" t="n">
         <v>6360</v>
@@ -21365,7 +21365,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G724" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H724" t="n">
         <v>80</v>
@@ -21539,7 +21539,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G730" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H730" t="n">
         <v>3578</v>
@@ -21568,7 +21568,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G731" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H731" t="n">
         <v>6117</v>
@@ -21597,7 +21597,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G732" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H732" t="n">
         <v>0</v>
@@ -21626,7 +21626,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G733" t="n">
-        <v>0.783093452453613</v>
+        <v>0.783093392848969</v>
       </c>
       <c r="H733" t="n">
         <v>4768</v>
@@ -21684,7 +21684,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G735" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H735" t="n">
         <v>10721</v>
@@ -21713,7 +21713,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G736" t="n">
-        <v>0.777391254901886</v>
+        <v>0.777391314506531</v>
       </c>
       <c r="H736" t="n">
         <v>1019</v>
@@ -21771,7 +21771,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G738" t="n">
-        <v>0.762185513973236</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H738" t="n">
         <v>1300</v>
@@ -21800,7 +21800,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G739" t="n">
-        <v>0.762185513973236</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H739" t="n">
         <v>879</v>
@@ -21829,7 +21829,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G740" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994065761566</v>
       </c>
       <c r="H740" t="n">
         <v>11723</v>
@@ -21858,7 +21858,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G741" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994065761566</v>
       </c>
       <c r="H741" t="n">
         <v>610</v>
@@ -22003,7 +22003,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G746" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H746" t="n">
         <v>1260</v>
@@ -22264,7 +22264,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G755" t="n">
-        <v>0.798299133777618</v>
+        <v>0.798299074172974</v>
       </c>
       <c r="H755" t="n">
         <v>72</v>
@@ -22467,7 +22467,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G762" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H762" t="n">
         <v>10920</v>
@@ -22583,7 +22583,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G766" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H766" t="n">
         <v>1790</v>
@@ -22612,7 +22612,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G767" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H767" t="n">
         <v>2524</v>
@@ -22641,7 +22641,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G768" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994065761566</v>
       </c>
       <c r="H768" t="n">
         <v>10514</v>
@@ -22815,7 +22815,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G774" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H774" t="n">
         <v>1400</v>
@@ -22902,7 +22902,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G777" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H777" t="n">
         <v>20</v>
@@ -22960,7 +22960,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G779" t="n">
-        <v>0.872426927089691</v>
+        <v>0.872426867485046</v>
       </c>
       <c r="H779" t="n">
         <v>86606</v>
@@ -22989,7 +22989,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G780" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H780" t="n">
         <v>20726</v>
@@ -23076,7 +23076,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G783" t="n">
-        <v>0.874327659606934</v>
+        <v>0.874327600002289</v>
       </c>
       <c r="H783" t="n">
         <v>8033</v>
@@ -23163,7 +23163,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G786" t="n">
-        <v>0.868625462055206</v>
+        <v>0.868625521659851</v>
       </c>
       <c r="H786" t="n">
         <v>14022</v>
@@ -23221,7 +23221,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G788" t="n">
-        <v>0.880029737949371</v>
+        <v>0.880029797554016</v>
       </c>
       <c r="H788" t="n">
         <v>384</v>
@@ -23250,7 +23250,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G789" t="n">
-        <v>0.874327659606934</v>
+        <v>0.874327600002289</v>
       </c>
       <c r="H789" t="n">
         <v>7232</v>
@@ -23279,7 +23279,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G790" t="n">
-        <v>0.868625462055206</v>
+        <v>0.868625521659851</v>
       </c>
       <c r="H790" t="n">
         <v>14705</v>
@@ -23308,7 +23308,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G791" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H791" t="n">
         <v>46594</v>
@@ -23395,7 +23395,7 @@
         <v>0.882000029087067</v>
       </c>
       <c r="G794" t="n">
-        <v>0.838214099407196</v>
+        <v>0.838214159011841</v>
       </c>
       <c r="H794" t="n">
         <v>1159</v>
@@ -23598,7 +23598,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G801" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H801" t="n">
         <v>16877</v>
@@ -23714,7 +23714,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G805" t="n">
-        <v>0.876228332519531</v>
+        <v>0.876228272914886</v>
       </c>
       <c r="H805" t="n">
         <v>2557</v>
@@ -23772,7 +23772,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G807" t="n">
-        <v>0.868625462055206</v>
+        <v>0.868625521659851</v>
       </c>
       <c r="H807" t="n">
         <v>16010</v>
@@ -23888,7 +23888,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G811" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H811" t="n">
         <v>1087</v>
@@ -23917,7 +23917,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>0.853419780731201</v>
+        <v>0.853419840335846</v>
       </c>
       <c r="H812" t="n">
         <v>14750</v>
@@ -23946,7 +23946,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G813" t="n">
-        <v>0.857221245765686</v>
+        <v>0.857221186161041</v>
       </c>
       <c r="H813" t="n">
         <v>14</v>
@@ -23975,7 +23975,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G814" t="n">
-        <v>0.857221245765686</v>
+        <v>0.857221186161041</v>
       </c>
       <c r="H814" t="n">
         <v>274</v>
@@ -24149,7 +24149,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G820" t="n">
-        <v>0.857221245765686</v>
+        <v>0.857221186161041</v>
       </c>
       <c r="H820" t="n">
         <v>4811</v>
@@ -24236,7 +24236,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G823" t="n">
-        <v>0.847717702388763</v>
+        <v>0.847717642784119</v>
       </c>
       <c r="H823" t="n">
         <v>12285</v>
@@ -24468,7 +24468,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G831" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H831" t="n">
         <v>22651</v>
@@ -24497,7 +24497,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G832" t="n">
-        <v>0.876228332519531</v>
+        <v>0.876228272914886</v>
       </c>
       <c r="H832" t="n">
         <v>10810</v>
@@ -24526,7 +24526,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G833" t="n">
-        <v>0.872426927089691</v>
+        <v>0.872426867485046</v>
       </c>
       <c r="H833" t="n">
         <v>16115</v>
@@ -24816,7 +24816,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G843" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H843" t="n">
         <v>10650</v>
@@ -24845,7 +24845,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G844" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H844" t="n">
         <v>6969</v>
@@ -24874,7 +24874,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G845" t="n">
-        <v>0.988370358943939</v>
+        <v>0.98837023973465</v>
       </c>
       <c r="H845" t="n">
         <v>40133</v>
@@ -24932,7 +24932,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G847" t="n">
-        <v>0.974115014076233</v>
+        <v>0.974115073680878</v>
       </c>
       <c r="H847" t="n">
         <v>18414</v>
@@ -25019,7 +25019,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G850" t="n">
-        <v>0.938951790332794</v>
+        <v>0.938951730728149</v>
       </c>
       <c r="H850" t="n">
         <v>45709</v>
@@ -25077,7 +25077,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G852" t="n">
-        <v>0.942753195762634</v>
+        <v>0.942753255367279</v>
       </c>
       <c r="H852" t="n">
         <v>18857</v>
@@ -25222,7 +25222,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G857" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H857" t="n">
         <v>20242</v>
@@ -25309,7 +25309,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G860" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H860" t="n">
         <v>74217</v>
@@ -25338,7 +25338,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G861" t="n">
-        <v>0.948455393314362</v>
+        <v>0.948455333709717</v>
       </c>
       <c r="H861" t="n">
         <v>21200</v>
@@ -25425,7 +25425,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G864" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H864" t="n">
         <v>58709</v>
@@ -25483,7 +25483,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G866" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H866" t="n">
         <v>19486</v>
@@ -25599,7 +25599,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G870" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H870" t="n">
         <v>11502</v>
@@ -25628,7 +25628,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G871" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H871" t="n">
         <v>11</v>
@@ -25715,7 +25715,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G874" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H874" t="n">
         <v>1274</v>
@@ -25744,7 +25744,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G875" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H875" t="n">
         <v>2508</v>
@@ -25773,7 +25773,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G876" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H876" t="n">
         <v>2701</v>
@@ -25802,7 +25802,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G877" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H877" t="n">
         <v>5064</v>
@@ -25860,7 +25860,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G879" t="n">
-        <v>0.880029737949371</v>
+        <v>0.880029797554016</v>
       </c>
       <c r="H879" t="n">
         <v>2292</v>
@@ -25889,7 +25889,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G880" t="n">
-        <v>0.874327659606934</v>
+        <v>0.874327600002289</v>
       </c>
       <c r="H880" t="n">
         <v>27077</v>
@@ -26005,7 +26005,7 @@
         <v>0.925999999046326</v>
       </c>
       <c r="G884" t="n">
-        <v>0.880029737949371</v>
+        <v>0.880029797554016</v>
       </c>
       <c r="H884" t="n">
         <v>34609</v>
@@ -26063,7 +26063,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G886" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H886" t="n">
         <v>11911</v>
@@ -26092,7 +26092,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G887" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H887" t="n">
         <v>1480</v>
@@ -26150,7 +26150,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G889" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H889" t="n">
         <v>4577</v>
@@ -26179,7 +26179,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G890" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H890" t="n">
         <v>4035</v>
@@ -26208,7 +26208,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G891" t="n">
-        <v>0.857221245765686</v>
+        <v>0.857221186161041</v>
       </c>
       <c r="H891" t="n">
         <v>7770</v>
@@ -26353,7 +26353,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G896" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H896" t="n">
         <v>2121</v>
@@ -26382,7 +26382,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G897" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H897" t="n">
         <v>5200</v>
@@ -26411,7 +26411,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G898" t="n">
-        <v>0.868625462055206</v>
+        <v>0.868625521659851</v>
       </c>
       <c r="H898" t="n">
         <v>30729</v>
@@ -26527,7 +26527,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G902" t="n">
-        <v>0.853419780731201</v>
+        <v>0.853419840335846</v>
       </c>
       <c r="H902" t="n">
         <v>2624</v>
@@ -26585,7 +26585,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>0.853419780731201</v>
+        <v>0.853419840335846</v>
       </c>
       <c r="H904" t="n">
         <v>1651</v>
@@ -26643,7 +26643,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G906" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H906" t="n">
         <v>10749</v>
@@ -26672,7 +26672,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>0.853419780731201</v>
+        <v>0.853419840335846</v>
       </c>
       <c r="H907" t="n">
         <v>10040</v>
@@ -26817,7 +26817,7 @@
         <v>0.892000019550323</v>
       </c>
       <c r="G912" t="n">
-        <v>0.847717702388763</v>
+        <v>0.847717642784119</v>
       </c>
       <c r="H912" t="n">
         <v>3225</v>
@@ -26904,7 +26904,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G915" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H915" t="n">
         <v>201</v>
@@ -27107,7 +27107,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G922" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H922" t="n">
         <v>2714</v>
@@ -27223,7 +27223,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G926" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H926" t="n">
         <v>260416</v>
@@ -27339,7 +27339,7 @@
         <v>0.970000028610229</v>
       </c>
       <c r="G930" t="n">
-        <v>0.921845436096191</v>
+        <v>0.921845376491547</v>
       </c>
       <c r="H930" t="n">
         <v>72047</v>
@@ -27397,7 +27397,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G932" t="n">
-        <v>0.942753195762634</v>
+        <v>0.942753255367279</v>
       </c>
       <c r="H932" t="n">
         <v>68362</v>
@@ -27426,7 +27426,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G933" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H933" t="n">
         <v>30540</v>
@@ -27484,7 +27484,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G935" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H935" t="n">
         <v>26262</v>
@@ -27542,7 +27542,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G937" t="n">
-        <v>0.942753195762634</v>
+        <v>0.942753255367279</v>
       </c>
       <c r="H937" t="n">
         <v>19326</v>
@@ -27629,7 +27629,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G940" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H940" t="n">
         <v>11547</v>
@@ -27774,7 +27774,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G945" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H945" t="n">
         <v>2460</v>
@@ -27803,7 +27803,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>0.988370358943939</v>
+        <v>0.98837023973465</v>
       </c>
       <c r="H946" t="n">
         <v>175676</v>
@@ -27832,7 +27832,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G947" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H947" t="n">
         <v>76067</v>
@@ -27977,7 +27977,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G952" t="n">
-        <v>0.942753195762634</v>
+        <v>0.942753255367279</v>
       </c>
       <c r="H952" t="n">
         <v>16989</v>
@@ -28151,7 +28151,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G958" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H958" t="n">
         <v>15725</v>
@@ -28296,7 +28296,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G963" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H963" t="n">
         <v>34081</v>
@@ -28470,7 +28470,7 @@
         <v>0.949999988079071</v>
       </c>
       <c r="G969" t="n">
-        <v>0.902838349342346</v>
+        <v>0.902838289737701</v>
       </c>
       <c r="H969" t="n">
         <v>16831</v>
@@ -28528,7 +28528,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G971" t="n">
-        <v>0.889533340930939</v>
+        <v>0.889533281326294</v>
       </c>
       <c r="H971" t="n">
         <v>3011</v>
@@ -28586,7 +28586,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G973" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H973" t="n">
         <v>8924</v>
@@ -28615,7 +28615,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G974" t="n">
-        <v>0.895235419273376</v>
+        <v>0.895235478878021</v>
       </c>
       <c r="H974" t="n">
         <v>5067</v>
@@ -28673,7 +28673,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G976" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H976" t="n">
         <v>49086</v>
@@ -28702,7 +28702,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G977" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H977" t="n">
         <v>11890</v>
@@ -28760,7 +28760,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G979" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H979" t="n">
         <v>4965</v>
@@ -28847,7 +28847,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G982" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H982" t="n">
         <v>30123</v>
@@ -28876,7 +28876,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G983" t="n">
-        <v>0.974115014076233</v>
+        <v>0.974115073680878</v>
       </c>
       <c r="H983" t="n">
         <v>7760</v>
@@ -28905,7 +28905,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G984" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H984" t="n">
         <v>29319</v>
@@ -28934,7 +28934,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G985" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H985" t="n">
         <v>21774</v>
@@ -28963,7 +28963,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G986" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H986" t="n">
         <v>34613</v>
@@ -28992,7 +28992,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G987" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H987" t="n">
         <v>7153</v>
@@ -29021,7 +29021,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G988" t="n">
-        <v>0.974115014076233</v>
+        <v>0.974115073680878</v>
       </c>
       <c r="H988" t="n">
         <v>10066</v>
@@ -29137,7 +29137,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H992" t="n">
         <v>10082</v>
@@ -29166,7 +29166,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G993" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H993" t="n">
         <v>5731</v>
@@ -29253,7 +29253,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G996" t="n">
-        <v>0.983618438243866</v>
+        <v>0.983618497848511</v>
       </c>
       <c r="H996" t="n">
         <v>106619</v>
@@ -29369,7 +29369,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H1000" t="n">
         <v>13855</v>
@@ -29398,7 +29398,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.974115014076233</v>
+        <v>0.974115073680878</v>
       </c>
       <c r="H1001" t="n">
         <v>8205</v>
@@ -29427,7 +29427,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.983618438243866</v>
+        <v>0.983618497848511</v>
       </c>
       <c r="H1002" t="n">
         <v>25401</v>
@@ -29514,7 +29514,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.0501434803009</v>
+        <v>1.05014359951019</v>
       </c>
       <c r="H1005" t="n">
         <v>59119</v>
@@ -29601,7 +29601,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.05964696407318</v>
+        <v>1.05964708328247</v>
       </c>
       <c r="H1008" t="n">
         <v>70073</v>
@@ -29717,7 +29717,7 @@
         <v>1.10500001907349</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.0501434803009</v>
+        <v>1.05014359951019</v>
       </c>
       <c r="H1012" t="n">
         <v>19076</v>
@@ -29775,7 +29775,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.02638471126556</v>
+        <v>1.02638459205627</v>
       </c>
       <c r="H1014" t="n">
         <v>4819</v>
@@ -29949,7 +29949,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.00262570381165</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H1020" t="n">
         <v>12764</v>
@@ -30007,7 +30007,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.988370358943939</v>
+        <v>0.98837023973465</v>
       </c>
       <c r="H1022" t="n">
         <v>30056</v>
@@ -30036,7 +30036,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.983618438243866</v>
+        <v>0.983618497848511</v>
       </c>
       <c r="H1023" t="n">
         <v>17131</v>
@@ -30210,7 +30210,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1029" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H1029" t="n">
         <v>91607</v>
@@ -30239,7 +30239,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G1030" t="n">
-        <v>0.959859609603882</v>
+        <v>0.959859669208527</v>
       </c>
       <c r="H1030" t="n">
         <v>22283</v>
@@ -30268,7 +30268,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.00262570381165</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H1031" t="n">
         <v>372072</v>
@@ -30326,7 +30326,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.969363152980804</v>
+        <v>0.969363212585449</v>
       </c>
       <c r="H1033" t="n">
         <v>51868</v>
@@ -30355,7 +30355,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>0.988370358943939</v>
+        <v>0.98837023973465</v>
       </c>
       <c r="H1034" t="n">
         <v>57336</v>
@@ -30500,7 +30500,7 @@
         <v>1.05499994754791</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.00262570381165</v>
+        <v>1.00262558460236</v>
       </c>
       <c r="H1039" t="n">
         <v>32399</v>
@@ -30558,7 +30558,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.06439876556396</v>
+        <v>1.06439888477325</v>
       </c>
       <c r="H1041" t="n">
         <v>42988</v>
@@ -30674,7 +30674,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.09766125679016</v>
+        <v>1.09766113758087</v>
       </c>
       <c r="H1045" t="n">
         <v>470152</v>
@@ -30703,7 +30703,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.07390236854553</v>
+        <v>1.07390248775482</v>
       </c>
       <c r="H1046" t="n">
         <v>138069</v>
@@ -30732,7 +30732,7 @@
         <v>1.12999999523163</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.07390236854553</v>
+        <v>1.07390248775482</v>
       </c>
       <c r="H1047" t="n">
         <v>23538</v>
@@ -30761,7 +30761,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.11191666126251</v>
+        <v>1.11191654205322</v>
       </c>
       <c r="H1048" t="n">
         <v>82375</v>
@@ -30906,7 +30906,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.983618438243866</v>
+        <v>0.983618497848511</v>
       </c>
       <c r="H1053" t="n">
         <v>115588</v>
@@ -30964,7 +30964,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.974115014076233</v>
+        <v>0.974115073680878</v>
       </c>
       <c r="H1055" t="n">
         <v>11641</v>
@@ -31080,7 +31080,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.938951790332794</v>
+        <v>0.938951730728149</v>
       </c>
       <c r="H1059" t="n">
         <v>19870</v>
@@ -31167,7 +31167,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H1062" t="n">
         <v>146893</v>
@@ -31196,7 +31196,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1063" t="n">
         <v>26146</v>
@@ -31254,7 +31254,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H1065" t="n">
         <v>8706</v>
@@ -31486,7 +31486,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H1073" t="n">
         <v>22248</v>
@@ -31515,7 +31515,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.872426927089691</v>
+        <v>0.872426867485046</v>
       </c>
       <c r="H1074" t="n">
         <v>2011</v>
@@ -31776,7 +31776,7 @@
         <v>0.917999982833862</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.872426927089691</v>
+        <v>0.872426867485046</v>
       </c>
       <c r="H1083" t="n">
         <v>23349</v>
@@ -31805,7 +31805,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.870526134967804</v>
+        <v>0.870526194572449</v>
       </c>
       <c r="H1084" t="n">
         <v>14829</v>
@@ -31834,7 +31834,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H1085" t="n">
         <v>17000</v>
@@ -31979,7 +31979,7 @@
         <v>0.882000029087067</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.838214099407196</v>
+        <v>0.838214159011841</v>
       </c>
       <c r="H1090" t="n">
         <v>15501</v>
@@ -32008,7 +32008,7 @@
         <v>0.882000029087067</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.838214099407196</v>
+        <v>0.838214159011841</v>
       </c>
       <c r="H1091" t="n">
         <v>0</v>
@@ -32037,7 +32037,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1092" t="n">
         <v>52209</v>
@@ -32385,7 +32385,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504874706268</v>
       </c>
       <c r="H1104" t="n">
         <v>5636</v>
@@ -32617,7 +32617,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H1112" t="n">
         <v>10652</v>
@@ -32907,7 +32907,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H1122" t="n">
         <v>28335</v>
@@ -33168,7 +33168,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.851519048213959</v>
+        <v>0.851519107818604</v>
       </c>
       <c r="H1131" t="n">
         <v>54987</v>
@@ -33632,7 +33632,7 @@
         <v>0.90200001001358</v>
       </c>
       <c r="G1147" t="n">
-        <v>0.857221245765686</v>
+        <v>0.857221186161041</v>
       </c>
       <c r="H1147" t="n">
         <v>6492</v>
@@ -33922,7 +33922,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504874706268</v>
       </c>
       <c r="H1157" t="n">
         <v>1157</v>
@@ -33980,7 +33980,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1159" t="n">
         <v>57439</v>
@@ -34125,7 +34125,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1164" t="n">
         <v>154</v>
@@ -34154,7 +34154,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.798299133777618</v>
+        <v>0.798299074172974</v>
       </c>
       <c r="H1165" t="n">
         <v>20</v>
@@ -34212,7 +34212,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1167" t="n">
         <v>5059</v>
@@ -34241,7 +34241,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H1168" t="n">
         <v>2588</v>
@@ -34270,7 +34270,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1169" t="n">
         <v>1446</v>
@@ -34357,7 +34357,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504874706268</v>
       </c>
       <c r="H1172" t="n">
         <v>1500</v>
@@ -34386,7 +34386,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504874706268</v>
       </c>
       <c r="H1173" t="n">
         <v>0</v>
@@ -34415,7 +34415,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504874706268</v>
       </c>
       <c r="H1174" t="n">
         <v>0</v>
@@ -34444,7 +34444,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504874706268</v>
       </c>
       <c r="H1175" t="n">
         <v>0</v>
@@ -34473,7 +34473,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.811604142189026</v>
+        <v>0.811604082584381</v>
       </c>
       <c r="H1176" t="n">
         <v>1005</v>
@@ -34502,7 +34502,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.811604142189026</v>
+        <v>0.811604082584381</v>
       </c>
       <c r="H1177" t="n">
         <v>0</v>
@@ -34531,7 +34531,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994065761566</v>
       </c>
       <c r="H1178" t="n">
         <v>1540</v>
@@ -34560,7 +34560,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994065761566</v>
       </c>
       <c r="H1179" t="n">
         <v>0</v>
@@ -34589,7 +34589,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.762185513973236</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1180" t="n">
         <v>10010</v>
@@ -34618,7 +34618,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1181" t="n">
-        <v>0.783093452453613</v>
+        <v>0.783093392848969</v>
       </c>
       <c r="H1181" t="n">
         <v>1658</v>
@@ -34821,7 +34821,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1188" t="n">
-        <v>0.783093452453613</v>
+        <v>0.783093392848969</v>
       </c>
       <c r="H1188" t="n">
         <v>1716</v>
@@ -34850,7 +34850,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1189" t="n">
         <v>1063</v>
@@ -34879,7 +34879,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1190" t="n">
         <v>4195</v>
@@ -34908,7 +34908,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1191" t="n">
         <v>10276</v>
@@ -34937,7 +34937,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.777391254901886</v>
+        <v>0.777391314506531</v>
       </c>
       <c r="H1192" t="n">
         <v>11693</v>
@@ -34966,7 +34966,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.777391254901886</v>
+        <v>0.777391314506531</v>
       </c>
       <c r="H1193" t="n">
         <v>0</v>
@@ -34995,7 +34995,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1194" t="n">
         <v>6350</v>
@@ -35024,7 +35024,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1195" t="n">
         <v>2689</v>
@@ -35169,7 +35169,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1200" t="n">
         <v>4016</v>
@@ -35401,7 +35401,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1208" t="n">
         <v>1034</v>
@@ -35430,7 +35430,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1209" t="n">
         <v>0</v>
@@ -35459,7 +35459,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.798299133777618</v>
+        <v>0.798299074172974</v>
       </c>
       <c r="H1210" t="n">
         <v>252</v>
@@ -35488,7 +35488,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.783093452453613</v>
+        <v>0.783093392848969</v>
       </c>
       <c r="H1211" t="n">
         <v>21916</v>
@@ -35546,7 +35546,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.777391254901886</v>
+        <v>0.777391314506531</v>
       </c>
       <c r="H1213" t="n">
         <v>19225</v>
@@ -35604,7 +35604,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1215" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1215" t="n">
         <v>21716</v>
@@ -35662,7 +35662,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1217" t="n">
-        <v>0.760284841060638</v>
+        <v>0.760284900665283</v>
       </c>
       <c r="H1217" t="n">
         <v>3825</v>
@@ -35691,7 +35691,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1218" t="n">
         <v>13790</v>
@@ -35720,7 +35720,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1219" t="n">
         <v>12226</v>
@@ -35952,7 +35952,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.69376003742218</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1227" t="n">
         <v>10514</v>
@@ -35981,7 +35981,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1228" t="n">
         <v>3123</v>
@@ -36039,7 +36039,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1230" t="n">
         <v>2138</v>
@@ -36068,7 +36068,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1231" t="n">
         <v>5454</v>
@@ -36184,7 +36184,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.760284841060638</v>
+        <v>0.760284900665283</v>
       </c>
       <c r="H1235" t="n">
         <v>25366</v>
@@ -36271,7 +36271,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.777391254901886</v>
+        <v>0.777391314506531</v>
       </c>
       <c r="H1238" t="n">
         <v>13935</v>
@@ -36300,7 +36300,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1239" t="n">
         <v>32699</v>
@@ -36329,7 +36329,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1240" t="n">
         <v>9919</v>
@@ -36387,7 +36387,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1242" t="n">
         <v>6749</v>
@@ -36416,7 +36416,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.783093452453613</v>
+        <v>0.783093392848969</v>
       </c>
       <c r="H1243" t="n">
         <v>64591</v>
@@ -36445,7 +36445,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1244" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1244" t="n">
         <v>43971</v>
@@ -36474,7 +36474,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1245" t="n">
         <v>5112</v>
@@ -36503,7 +36503,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1246" t="n">
         <v>16700</v>
@@ -36532,7 +36532,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1247" t="n">
-        <v>0.760284841060638</v>
+        <v>0.760284900665283</v>
       </c>
       <c r="H1247" t="n">
         <v>18577</v>
@@ -36561,7 +36561,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.762185513973236</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1248" t="n">
         <v>12890</v>
@@ -36590,7 +36590,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1249" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1249" t="n">
         <v>6774</v>
@@ -36619,7 +36619,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.758384168148041</v>
+        <v>0.758384108543396</v>
       </c>
       <c r="H1250" t="n">
         <v>6647</v>
@@ -36677,7 +36677,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.758384168148041</v>
+        <v>0.758384108543396</v>
       </c>
       <c r="H1252" t="n">
         <v>7654</v>
@@ -36706,7 +36706,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.762185513973236</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1253" t="n">
         <v>1000</v>
@@ -36851,7 +36851,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1258" t="n">
         <v>913</v>
@@ -36880,7 +36880,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1259" t="n">
         <v>25666</v>
@@ -36909,7 +36909,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1260" t="n">
         <v>38619</v>
@@ -36938,7 +36938,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1261" t="n">
         <v>1406</v>
@@ -36996,7 +36996,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1263" t="n">
         <v>2463</v>
@@ -37025,7 +37025,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1264" t="n">
         <v>2413</v>
@@ -37083,7 +37083,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1266" t="n">
         <v>3759</v>
@@ -37112,7 +37112,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1267" t="n">
         <v>0</v>
@@ -37141,7 +37141,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1268" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1268" t="n">
         <v>9194</v>
@@ -37199,7 +37199,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.758384168148041</v>
+        <v>0.758384108543396</v>
       </c>
       <c r="H1270" t="n">
         <v>8817</v>
@@ -37837,7 +37837,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.720369935035706</v>
+        <v>0.720369875431061</v>
       </c>
       <c r="H1292" t="n">
         <v>33828</v>
@@ -38156,7 +38156,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.783093452453613</v>
+        <v>0.783093392848969</v>
       </c>
       <c r="H1303" t="n">
         <v>21005</v>
@@ -38214,7 +38214,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1305" t="n">
         <v>13544</v>
@@ -38301,7 +38301,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1308" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1308" t="n">
         <v>10678</v>
@@ -38359,7 +38359,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1310" t="n">
         <v>77093</v>
@@ -38388,7 +38388,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H1311" t="n">
         <v>3023</v>
@@ -38417,7 +38417,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1312" t="n">
         <v>5581</v>
@@ -38446,7 +38446,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1313" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994065761566</v>
       </c>
       <c r="H1313" t="n">
         <v>16652</v>
@@ -38475,7 +38475,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1314" t="n">
         <v>990</v>
@@ -38504,7 +38504,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1315" t="n">
         <v>0</v>
@@ -38533,7 +38533,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.762185513973236</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1316" t="n">
         <v>90943</v>
@@ -38562,7 +38562,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1317" t="n">
         <v>10278</v>
@@ -38591,7 +38591,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.758384168148041</v>
+        <v>0.758384108543396</v>
       </c>
       <c r="H1318" t="n">
         <v>14877</v>
@@ -38678,7 +38678,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1321" t="n">
-        <v>0.760284841060638</v>
+        <v>0.760284900665283</v>
       </c>
       <c r="H1321" t="n">
         <v>31626</v>
@@ -38881,7 +38881,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1328" t="n">
-        <v>0.762185513973236</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1328" t="n">
         <v>52080</v>
@@ -38997,7 +38997,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.777391254901886</v>
+        <v>0.777391314506531</v>
       </c>
       <c r="H1332" t="n">
         <v>36760</v>
@@ -39026,7 +39026,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.777391254901886</v>
+        <v>0.777391314506531</v>
       </c>
       <c r="H1333" t="n">
         <v>3523</v>
@@ -39055,7 +39055,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1334" t="n">
         <v>5578</v>
@@ -39113,7 +39113,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1336" t="n">
         <v>31378</v>
@@ -39171,7 +39171,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1338" t="n">
-        <v>0.760284841060638</v>
+        <v>0.760284900665283</v>
       </c>
       <c r="H1338" t="n">
         <v>5829</v>
@@ -39229,7 +39229,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1340" t="n">
-        <v>0.762185513973236</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1340" t="n">
         <v>16027</v>
@@ -39345,7 +39345,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1344" t="n">
         <v>16127</v>
@@ -39461,7 +39461,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1348" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1348" t="n">
         <v>169972</v>
@@ -39490,7 +39490,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1349" t="n">
         <v>16898</v>
@@ -39606,7 +39606,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.760284841060638</v>
+        <v>0.760284900665283</v>
       </c>
       <c r="H1353" t="n">
         <v>12165</v>
@@ -40244,7 +40244,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994065761566</v>
       </c>
       <c r="H1375" t="n">
         <v>119857</v>
@@ -40273,7 +40273,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1376" t="n">
         <v>151700</v>
@@ -40302,7 +40302,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.783093452453613</v>
+        <v>0.783093392848969</v>
       </c>
       <c r="H1377" t="n">
         <v>193535</v>
@@ -40389,7 +40389,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1380" t="n">
         <v>85030</v>
@@ -40418,7 +40418,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1381" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1381" t="n">
         <v>85408</v>
@@ -40447,7 +40447,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994065761566</v>
       </c>
       <c r="H1382" t="n">
         <v>47262</v>
@@ -40505,7 +40505,7 @@
         <v>0.899999976158142</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.855320394039154</v>
+        <v>0.855320453643799</v>
       </c>
       <c r="H1384" t="n">
         <v>665882</v>
@@ -40650,7 +40650,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504874706268</v>
       </c>
       <c r="H1389" t="n">
         <v>86617</v>
@@ -40679,7 +40679,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1390" t="n">
-        <v>0.813504815101624</v>
+        <v>0.813504874706268</v>
       </c>
       <c r="H1390" t="n">
         <v>44133</v>
@@ -40708,7 +40708,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.798299133777618</v>
+        <v>0.798299074172974</v>
       </c>
       <c r="H1391" t="n">
         <v>25564</v>
@@ -40795,7 +40795,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.798299133777618</v>
+        <v>0.798299074172974</v>
       </c>
       <c r="H1394" t="n">
         <v>26614</v>
@@ -40824,7 +40824,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.784994125366211</v>
+        <v>0.784994065761566</v>
       </c>
       <c r="H1395" t="n">
         <v>26723</v>
@@ -40969,7 +40969,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.788795530796051</v>
+        <v>0.788795590400696</v>
       </c>
       <c r="H1400" t="n">
         <v>63141</v>
@@ -40998,7 +40998,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1401" t="n">
-        <v>0.786894857883453</v>
+        <v>0.786894917488098</v>
       </c>
       <c r="H1401" t="n">
         <v>55616</v>
@@ -41027,7 +41027,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1402" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1402" t="n">
         <v>111019</v>
@@ -41056,7 +41056,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.781192779541016</v>
+        <v>0.781192719936371</v>
       </c>
       <c r="H1403" t="n">
         <v>21218</v>
@@ -41114,7 +41114,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1405" t="n">
-        <v>0.777391254901886</v>
+        <v>0.777391314506531</v>
       </c>
       <c r="H1405" t="n">
         <v>14851</v>
@@ -41143,7 +41143,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1406" t="n">
-        <v>0.779291987419128</v>
+        <v>0.779292047023773</v>
       </c>
       <c r="H1406" t="n">
         <v>7404</v>
@@ -41201,7 +41201,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.762185513973236</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1408" t="n">
         <v>21428</v>
@@ -41317,7 +41317,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1412" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1412" t="n">
         <v>53142</v>
@@ -41520,7 +41520,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1419" t="n">
-        <v>0.762185513973236</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1419" t="n">
         <v>3816</v>
@@ -41549,7 +41549,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1420" t="n">
-        <v>0.760284841060638</v>
+        <v>0.760284900665283</v>
       </c>
       <c r="H1420" t="n">
         <v>394</v>
@@ -41607,7 +41607,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1422" t="n">
-        <v>0.760284841060638</v>
+        <v>0.760284900665283</v>
       </c>
       <c r="H1422" t="n">
         <v>1016</v>
@@ -41636,7 +41636,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1423" t="n">
-        <v>0.765987038612366</v>
+        <v>0.765986979007721</v>
       </c>
       <c r="H1423" t="n">
         <v>15016</v>
@@ -41723,7 +41723,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.758384168148041</v>
+        <v>0.758384108543396</v>
       </c>
       <c r="H1426" t="n">
         <v>4889</v>
@@ -41752,7 +41752,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.760284841060638</v>
+        <v>0.760284900665283</v>
       </c>
       <c r="H1427" t="n">
         <v>33992</v>
@@ -41868,7 +41868,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1431" t="n">
-        <v>0.760284841060638</v>
+        <v>0.760284900665283</v>
       </c>
       <c r="H1431" t="n">
         <v>6918</v>
@@ -41926,7 +41926,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1433" t="n">
-        <v>0.758384168148041</v>
+        <v>0.758384108543396</v>
       </c>
       <c r="H1433" t="n">
         <v>4016</v>
@@ -42042,7 +42042,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.758384168148041</v>
+        <v>0.758384108543396</v>
       </c>
       <c r="H1437" t="n">
         <v>25753</v>
@@ -42071,7 +42071,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.758384168148041</v>
+        <v>0.758384108543396</v>
       </c>
       <c r="H1438" t="n">
         <v>2223</v>
@@ -42100,7 +42100,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.767887771129608</v>
+        <v>0.767887711524963</v>
       </c>
       <c r="H1439" t="n">
         <v>1167</v>
@@ -42158,7 +42158,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1441" t="n">
-        <v>0.760284841060638</v>
+        <v>0.760284900665283</v>
       </c>
       <c r="H1441" t="n">
         <v>2013</v>
@@ -42216,7 +42216,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1443" t="n">
-        <v>0.760284841060638</v>
+        <v>0.760284900665283</v>
       </c>
       <c r="H1443" t="n">
         <v>21576</v>
@@ -42303,7 +42303,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1446" t="n">
-        <v>0.760284841060638</v>
+        <v>0.760284900665283</v>
       </c>
       <c r="H1446" t="n">
         <v>49512</v>
@@ -42419,7 +42419,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.760284841060638</v>
+        <v>0.760284900665283</v>
       </c>
       <c r="H1450" t="n">
         <v>19978</v>
@@ -42448,7 +42448,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.760284841060638</v>
+        <v>0.760284900665283</v>
       </c>
       <c r="H1451" t="n">
         <v>26</v>
@@ -42477,7 +42477,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1452" t="n">
-        <v>0.758384168148041</v>
+        <v>0.758384108543396</v>
       </c>
       <c r="H1452" t="n">
         <v>3313</v>
@@ -42506,7 +42506,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.764086306095123</v>
+        <v>0.764086365699768</v>
       </c>
       <c r="H1453" t="n">
         <v>21018</v>
@@ -42680,7 +42680,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.762185513973236</v>
+        <v>0.762185573577881</v>
       </c>
       <c r="H1459" t="n">
         <v>1349</v>
@@ -43811,7 +43811,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.720369935035706</v>
+        <v>0.720369875431061</v>
       </c>
       <c r="H1498" t="n">
         <v>96906</v>
@@ -43985,7 +43985,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1504" t="n">
-        <v>0.714667797088623</v>
+        <v>0.714667856693268</v>
       </c>
       <c r="H1504" t="n">
         <v>11995</v>
@@ -44246,7 +44246,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.714667797088623</v>
+        <v>0.714667856693268</v>
       </c>
       <c r="H1513" t="n">
         <v>4895</v>
@@ -44507,7 +44507,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1522" t="n">
-        <v>0.691859245300293</v>
+        <v>0.691859185695648</v>
       </c>
       <c r="H1522" t="n">
         <v>4220</v>
@@ -44536,7 +44536,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1523" t="n">
-        <v>0.688057780265808</v>
+        <v>0.688057839870453</v>
       </c>
       <c r="H1523" t="n">
         <v>48</v>
@@ -44652,7 +44652,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1527" t="n">
-        <v>0.691859245300293</v>
+        <v>0.691859185695648</v>
       </c>
       <c r="H1527" t="n">
         <v>7816</v>
@@ -44710,7 +44710,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.69376003742218</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1529" t="n">
         <v>31255</v>
@@ -44739,7 +44739,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1530" t="n">
-        <v>0.688057780265808</v>
+        <v>0.688057839870453</v>
       </c>
       <c r="H1530" t="n">
         <v>17959</v>
@@ -44768,7 +44768,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.688057780265808</v>
+        <v>0.688057839870453</v>
       </c>
       <c r="H1531" t="n">
         <v>9620</v>
@@ -44797,7 +44797,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.69376003742218</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1532" t="n">
         <v>2091</v>
@@ -44826,7 +44826,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1533" t="n">
-        <v>0.691859245300293</v>
+        <v>0.691859185695648</v>
       </c>
       <c r="H1533" t="n">
         <v>2683</v>
@@ -44884,7 +44884,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1535" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1535" t="n">
         <v>3000</v>
@@ -44913,7 +44913,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1536" t="n">
         <v>2001</v>
@@ -44942,7 +44942,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1537" t="n">
         <v>1094</v>
@@ -44971,7 +44971,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.69376003742218</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1538" t="n">
         <v>1647</v>
@@ -45000,7 +45000,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.69376003742218</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1539" t="n">
         <v>0</v>
@@ -45029,7 +45029,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.69376003742218</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1540" t="n">
         <v>18889</v>
@@ -45058,7 +45058,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1541" t="n">
-        <v>0.688057780265808</v>
+        <v>0.688057839870453</v>
       </c>
       <c r="H1541" t="n">
         <v>5040</v>
@@ -45261,7 +45261,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.697561383247375</v>
+        <v>0.69756144285202</v>
       </c>
       <c r="H1548" t="n">
         <v>116</v>
@@ -45290,7 +45290,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.695660591125488</v>
+        <v>0.695660650730133</v>
       </c>
       <c r="H1549" t="n">
         <v>2218</v>
@@ -45348,7 +45348,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1551" t="n">
-        <v>0.686157047748566</v>
+        <v>0.68615710735321</v>
       </c>
       <c r="H1551" t="n">
         <v>16</v>
@@ -45377,7 +45377,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1552" t="n">
-        <v>0.688057780265808</v>
+        <v>0.688057839870453</v>
       </c>
       <c r="H1552" t="n">
         <v>16300</v>
@@ -45696,7 +45696,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.672852098941803</v>
+        <v>0.672852158546448</v>
       </c>
       <c r="H1563" t="n">
         <v>2697</v>
@@ -45725,7 +45725,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.686157047748566</v>
+        <v>0.68615710735321</v>
       </c>
       <c r="H1564" t="n">
         <v>10278</v>
@@ -45783,7 +45783,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.69376003742218</v>
+        <v>0.693759977817535</v>
       </c>
       <c r="H1566" t="n">
         <v>7267</v>
@@ -45841,7 +45841,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.676653563976288</v>
+        <v>0.676653504371643</v>
       </c>
       <c r="H1568" t="n">
         <v>23252</v>
@@ -46102,7 +46102,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1577" t="n">
-        <v>0.623433589935303</v>
+        <v>0.623433649539948</v>
       </c>
       <c r="H1577" t="n">
         <v>8418</v>
@@ -46160,7 +46160,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1579" t="n">
-        <v>0.670951306819916</v>
+        <v>0.670951366424561</v>
       </c>
       <c r="H1579" t="n">
         <v>117601</v>
@@ -46189,7 +46189,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1580" t="n">
-        <v>0.674752831459045</v>
+        <v>0.674752771854401</v>
       </c>
       <c r="H1580" t="n">
         <v>7398</v>
@@ -46305,7 +46305,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.640540063381195</v>
+        <v>0.64054000377655</v>
       </c>
       <c r="H1584" t="n">
         <v>1100</v>
@@ -46334,7 +46334,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1585" t="n">
-        <v>0.623433589935303</v>
+        <v>0.623433649539948</v>
       </c>
       <c r="H1585" t="n">
         <v>31781</v>
@@ -46595,7 +46595,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.62913578748703</v>
+        <v>0.629135727882385</v>
       </c>
       <c r="H1594" t="n">
         <v>3425</v>
@@ -46943,7 +46943,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1606" t="n">
         <v>18179</v>
@@ -46972,7 +46972,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.623433589935303</v>
+        <v>0.623433649539948</v>
       </c>
       <c r="H1607" t="n">
         <v>1695</v>
@@ -47030,7 +47030,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1609" t="n">
-        <v>0.62913578748703</v>
+        <v>0.629135727882385</v>
       </c>
       <c r="H1609" t="n">
         <v>900</v>
@@ -47117,7 +47117,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1612" t="n">
-        <v>0.62913578748703</v>
+        <v>0.629135727882385</v>
       </c>
       <c r="H1612" t="n">
         <v>1430</v>
@@ -47146,7 +47146,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.62913578748703</v>
+        <v>0.629135727882385</v>
       </c>
       <c r="H1613" t="n">
         <v>0</v>
@@ -47175,7 +47175,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327295303345</v>
       </c>
       <c r="H1614" t="n">
         <v>5966</v>
@@ -47233,7 +47233,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1616" t="n">
-        <v>0.623433589935303</v>
+        <v>0.623433649539948</v>
       </c>
       <c r="H1616" t="n">
         <v>1329</v>
@@ -47262,7 +47262,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.623433589935303</v>
+        <v>0.623433649539948</v>
       </c>
       <c r="H1617" t="n">
         <v>0</v>
@@ -47291,7 +47291,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1618" t="n">
-        <v>0.623433589935303</v>
+        <v>0.623433649539948</v>
       </c>
       <c r="H1618" t="n">
         <v>0</v>
@@ -47320,7 +47320,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.581617832183838</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1619" t="n">
         <v>103376</v>
@@ -47349,7 +47349,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1620" t="n">
         <v>27183</v>
@@ -47378,7 +47378,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1621" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1621" t="n">
         <v>7627</v>
@@ -47436,7 +47436,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1623" t="n">
-        <v>0.623433589935303</v>
+        <v>0.623433649539948</v>
       </c>
       <c r="H1623" t="n">
         <v>28945</v>
@@ -47465,7 +47465,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1624" t="n">
-        <v>0.623433589935303</v>
+        <v>0.623433649539948</v>
       </c>
       <c r="H1624" t="n">
         <v>0</v>
@@ -47494,7 +47494,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1625" t="n">
-        <v>0.623433589935303</v>
+        <v>0.623433649539948</v>
       </c>
       <c r="H1625" t="n">
         <v>3239</v>
@@ -47523,7 +47523,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1626" t="n">
-        <v>0.623433589935303</v>
+        <v>0.623433649539948</v>
       </c>
       <c r="H1626" t="n">
         <v>5923</v>
@@ -47552,7 +47552,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1627" t="n">
-        <v>0.623433589935303</v>
+        <v>0.623433649539948</v>
       </c>
       <c r="H1627" t="n">
         <v>1050</v>
@@ -47610,7 +47610,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1629" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1629" t="n">
         <v>42986</v>
@@ -47697,7 +47697,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1632" t="n">
-        <v>0.62913578748703</v>
+        <v>0.629135727882385</v>
       </c>
       <c r="H1632" t="n">
         <v>1580</v>
@@ -47784,7 +47784,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1635" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1635" t="n">
         <v>9129</v>
@@ -47813,7 +47813,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1636" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1636" t="n">
         <v>4863</v>
@@ -47842,7 +47842,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1637" t="n">
-        <v>0.615830838680267</v>
+        <v>0.615830779075623</v>
       </c>
       <c r="H1637" t="n">
         <v>0</v>
@@ -47929,7 +47929,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327295303345</v>
       </c>
       <c r="H1640" t="n">
         <v>23258</v>
@@ -47958,7 +47958,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1641" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327295303345</v>
       </c>
       <c r="H1641" t="n">
         <v>0</v>
@@ -47987,7 +47987,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327295303345</v>
       </c>
       <c r="H1642" t="n">
         <v>0</v>
@@ -48016,7 +48016,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1643" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252571105957</v>
       </c>
       <c r="H1643" t="n">
         <v>500</v>
@@ -48045,7 +48045,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.596823573112488</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1644" t="n">
         <v>2848</v>
@@ -48103,7 +48103,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1646" t="n">
-        <v>0.581617832183838</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1646" t="n">
         <v>1464</v>
@@ -48132,7 +48132,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1647" t="n">
-        <v>0.596823573112488</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1647" t="n">
         <v>18796</v>
@@ -48277,7 +48277,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1652" t="n">
-        <v>0.596823573112488</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1652" t="n">
         <v>500</v>
@@ -48306,7 +48306,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1653" t="n">
-        <v>0.596823573112488</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1653" t="n">
         <v>0</v>
@@ -48480,7 +48480,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1659" t="n">
-        <v>0.49418517947197</v>
+        <v>0.494185119867325</v>
       </c>
       <c r="H1659" t="n">
         <v>111650</v>
@@ -48828,7 +48828,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.604426443576813</v>
+        <v>0.604426503181458</v>
       </c>
       <c r="H1671" t="n">
         <v>3877</v>
@@ -48857,7 +48857,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.596823573112488</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1672" t="n">
         <v>10972</v>
@@ -48915,7 +48915,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1674" t="n">
         <v>5204</v>
@@ -49089,7 +49089,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1680" t="n">
         <v>5826</v>
@@ -49118,7 +49118,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1681" t="n">
-        <v>0.604426443576813</v>
+        <v>0.604426503181458</v>
       </c>
       <c r="H1681" t="n">
         <v>5420</v>
@@ -49292,7 +49292,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252571105957</v>
       </c>
       <c r="H1687" t="n">
         <v>564</v>
@@ -49321,7 +49321,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252571105957</v>
       </c>
       <c r="H1688" t="n">
         <v>1061</v>
@@ -49350,7 +49350,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252571105957</v>
       </c>
       <c r="H1689" t="n">
         <v>1</v>
@@ -49379,7 +49379,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1690" t="n">
-        <v>0.591121554374695</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1690" t="n">
         <v>1738</v>
@@ -49408,7 +49408,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.604426443576813</v>
+        <v>0.604426503181458</v>
       </c>
       <c r="H1691" t="n">
         <v>677</v>
@@ -49466,7 +49466,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1693" t="n">
-        <v>0.604426443576813</v>
+        <v>0.604426503181458</v>
       </c>
       <c r="H1693" t="n">
         <v>832</v>
@@ -49495,7 +49495,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1694" t="n">
-        <v>0.604426443576813</v>
+        <v>0.604426503181458</v>
       </c>
       <c r="H1694" t="n">
         <v>950</v>
@@ -49524,7 +49524,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252571105957</v>
       </c>
       <c r="H1695" t="n">
         <v>6536</v>
@@ -49553,7 +49553,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327295303345</v>
       </c>
       <c r="H1696" t="n">
         <v>1080</v>
@@ -49582,7 +49582,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327295303345</v>
       </c>
       <c r="H1697" t="n">
         <v>0</v>
@@ -49698,7 +49698,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327295303345</v>
       </c>
       <c r="H1701" t="n">
         <v>16</v>
@@ -49727,7 +49727,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.596823573112488</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1702" t="n">
         <v>502</v>
@@ -49930,7 +49930,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1709" t="n">
-        <v>0.591121554374695</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1709" t="n">
         <v>500</v>
@@ -50162,7 +50162,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.591121554374695</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1717" t="n">
         <v>6642</v>
@@ -50191,7 +50191,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1718" t="n">
-        <v>0.596823573112488</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1718" t="n">
         <v>2685</v>
@@ -50307,7 +50307,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1722" t="n">
-        <v>0.579717218875885</v>
+        <v>0.57971727848053</v>
       </c>
       <c r="H1722" t="n">
         <v>4854</v>
@@ -50394,7 +50394,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.579717218875885</v>
+        <v>0.57971727848053</v>
       </c>
       <c r="H1725" t="n">
         <v>7417</v>
@@ -50452,7 +50452,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1727" t="n">
-        <v>0.591121554374695</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1727" t="n">
         <v>9284</v>
@@ -50597,7 +50597,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.579717218875885</v>
+        <v>0.57971727848053</v>
       </c>
       <c r="H1732" t="n">
         <v>3355</v>
@@ -50626,7 +50626,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1733" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1733" t="n">
         <v>33</v>
@@ -50713,7 +50713,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1736" t="n">
         <v>347</v>
@@ -50742,7 +50742,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1737" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1737" t="n">
         <v>148</v>
@@ -50771,7 +50771,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1738" t="n">
-        <v>0.581617832183838</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1738" t="n">
         <v>5986</v>
@@ -50800,7 +50800,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.581617832183838</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1739" t="n">
         <v>0</v>
@@ -50916,7 +50916,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1743" t="n">
-        <v>0.575915813446045</v>
+        <v>0.5759157538414</v>
       </c>
       <c r="H1743" t="n">
         <v>1000</v>
@@ -51032,7 +51032,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.575915813446045</v>
+        <v>0.5759157538414</v>
       </c>
       <c r="H1747" t="n">
         <v>8200</v>
@@ -51119,7 +51119,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.591121554374695</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1750" t="n">
         <v>25115</v>
@@ -51148,7 +51148,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1751" t="n">
         <v>5540</v>
@@ -51206,7 +51206,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1753" t="n">
-        <v>0.591121554374695</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1753" t="n">
         <v>194</v>
@@ -51235,7 +51235,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1754" t="n">
-        <v>0.581617832183838</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1754" t="n">
         <v>17</v>
@@ -51264,7 +51264,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.581617832183838</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1755" t="n">
         <v>0</v>
@@ -51293,7 +51293,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1756" t="n">
-        <v>0.58351868391037</v>
+        <v>0.583518624305725</v>
       </c>
       <c r="H1756" t="n">
         <v>209</v>
@@ -51322,7 +51322,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1757" t="n">
-        <v>0.591121554374695</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1757" t="n">
         <v>9926</v>
@@ -51496,7 +51496,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1763" t="n">
         <v>2731</v>
@@ -51525,7 +51525,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1764" t="n">
         <v>2755</v>
@@ -51583,7 +51583,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1766" t="n">
         <v>11513</v>
@@ -51612,7 +51612,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1767" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252571105957</v>
       </c>
       <c r="H1767" t="n">
         <v>624</v>
@@ -51670,7 +51670,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.602525770664215</v>
+        <v>0.60252571105957</v>
       </c>
       <c r="H1769" t="n">
         <v>8114</v>
@@ -51699,7 +51699,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.604426443576813</v>
+        <v>0.604426503181458</v>
       </c>
       <c r="H1770" t="n">
         <v>19269</v>
@@ -51728,7 +51728,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1771" t="n">
-        <v>0.604426443576813</v>
+        <v>0.604426503181458</v>
       </c>
       <c r="H1771" t="n">
         <v>15200</v>
@@ -51844,7 +51844,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1775" t="n">
-        <v>0.596823573112488</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1775" t="n">
         <v>7172</v>
@@ -51873,7 +51873,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1776" t="n">
-        <v>0.596823573112488</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1776" t="n">
         <v>0</v>
@@ -51902,7 +51902,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1777" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1777" t="n">
         <v>6313</v>
@@ -51989,7 +51989,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327295303345</v>
       </c>
       <c r="H1780" t="n">
         <v>20280</v>
@@ -52018,7 +52018,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1781" t="n">
-        <v>0.591121554374695</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1781" t="n">
         <v>2957</v>
@@ -52192,7 +52192,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1787" t="n">
-        <v>0.596823573112488</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1787" t="n">
         <v>24392</v>
@@ -52308,7 +52308,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1791" t="n">
-        <v>0.58351868391037</v>
+        <v>0.583518624305725</v>
       </c>
       <c r="H1791" t="n">
         <v>5017</v>
@@ -52337,7 +52337,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1792" t="n">
         <v>1109</v>
@@ -52366,7 +52366,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1793" t="n">
-        <v>0.596823573112488</v>
+        <v>0.596823632717133</v>
       </c>
       <c r="H1793" t="n">
         <v>21634</v>
@@ -52395,7 +52395,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1794" t="n">
-        <v>0.604426443576813</v>
+        <v>0.604426503181458</v>
       </c>
       <c r="H1794" t="n">
         <v>1836</v>
@@ -52482,7 +52482,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1797" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1797" t="n">
         <v>1834</v>
@@ -52511,7 +52511,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1798" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1798" t="n">
         <v>0</v>
@@ -52540,7 +52540,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1799" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1799" t="n">
         <v>0</v>
@@ -52569,7 +52569,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1800" t="n">
-        <v>0.581617832183838</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1800" t="n">
         <v>5988</v>
@@ -52598,7 +52598,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1801" t="n">
-        <v>0.581617832183838</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1801" t="n">
         <v>5600</v>
@@ -52656,7 +52656,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.591121554374695</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1803" t="n">
         <v>4401</v>
@@ -52801,7 +52801,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1808" t="n">
-        <v>0.58351868391037</v>
+        <v>0.583518624305725</v>
       </c>
       <c r="H1808" t="n">
         <v>6391</v>
@@ -52888,7 +52888,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1811" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1811" t="n">
         <v>4998</v>
@@ -52917,7 +52917,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1812" t="n">
-        <v>0.581617832183838</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1812" t="n">
         <v>676</v>
@@ -52946,7 +52946,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1813" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1813" t="n">
         <v>32</v>
@@ -52975,7 +52975,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1814" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1814" t="n">
         <v>2582</v>
@@ -53004,7 +53004,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1815" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1815" t="n">
         <v>0</v>
@@ -53033,7 +53033,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1816" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1816" t="n">
         <v>3535</v>
@@ -53178,7 +53178,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1821" t="n">
-        <v>0.575915813446045</v>
+        <v>0.5759157538414</v>
       </c>
       <c r="H1821" t="n">
         <v>9490</v>
@@ -53236,7 +53236,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1823" t="n">
-        <v>0.58351868391037</v>
+        <v>0.583518624305725</v>
       </c>
       <c r="H1823" t="n">
         <v>4868</v>
@@ -53352,7 +53352,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1827" t="n">
-        <v>0.579717218875885</v>
+        <v>0.57971727848053</v>
       </c>
       <c r="H1827" t="n">
         <v>12465</v>
@@ -53439,7 +53439,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1830" t="n">
-        <v>0.58351868391037</v>
+        <v>0.583518624305725</v>
       </c>
       <c r="H1830" t="n">
         <v>37386</v>
@@ -53468,7 +53468,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.600625157356262</v>
+        <v>0.600625097751617</v>
       </c>
       <c r="H1831" t="n">
         <v>18113</v>
@@ -53497,7 +53497,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.575915813446045</v>
+        <v>0.5759157538414</v>
       </c>
       <c r="H1832" t="n">
         <v>2559</v>
@@ -53613,7 +53613,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.558809399604797</v>
+        <v>0.558809340000153</v>
       </c>
       <c r="H1836" t="n">
         <v>518</v>
@@ -53874,7 +53874,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.579717218875885</v>
+        <v>0.57971727848053</v>
       </c>
       <c r="H1845" t="n">
         <v>4050</v>
@@ -54135,7 +54135,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1854" t="n">
-        <v>0.581617832183838</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1854" t="n">
         <v>45294</v>
@@ -54164,7 +54164,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1855" t="n">
-        <v>0.581617832183838</v>
+        <v>0.581617891788483</v>
       </c>
       <c r="H1855" t="n">
         <v>18556</v>
@@ -54309,7 +54309,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1860" t="n">
-        <v>0.579717218875885</v>
+        <v>0.57971727848053</v>
       </c>
       <c r="H1860" t="n">
         <v>4000</v>
@@ -54425,7 +54425,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1864" t="n">
-        <v>0.579717218875885</v>
+        <v>0.57971727848053</v>
       </c>
       <c r="H1864" t="n">
         <v>2015</v>
@@ -54454,7 +54454,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1865" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1865" t="n">
         <v>817</v>
@@ -54483,7 +54483,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1866" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1866" t="n">
         <v>8439</v>
@@ -54512,7 +54512,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1867" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1867" t="n">
         <v>0</v>
@@ -54541,7 +54541,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1868" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1868" t="n">
         <v>235</v>
@@ -54570,7 +54570,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1869" t="n">
-        <v>0.58351868391037</v>
+        <v>0.583518624305725</v>
       </c>
       <c r="H1869" t="n">
         <v>5034</v>
@@ -54599,7 +54599,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1870" t="n">
-        <v>0.58351868391037</v>
+        <v>0.583518624305725</v>
       </c>
       <c r="H1870" t="n">
         <v>1535</v>
@@ -54802,7 +54802,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1877" t="n">
-        <v>0.558809399604797</v>
+        <v>0.558809340000153</v>
       </c>
       <c r="H1877" t="n">
         <v>1202</v>
@@ -55092,7 +55092,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.558809399604797</v>
+        <v>0.558809340000153</v>
       </c>
       <c r="H1887" t="n">
         <v>2513</v>
@@ -55440,7 +55440,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1899" t="n">
-        <v>0.558809399604797</v>
+        <v>0.558809340000153</v>
       </c>
       <c r="H1899" t="n">
         <v>28638</v>
@@ -55527,7 +55527,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1902" t="n">
-        <v>0.558809399604797</v>
+        <v>0.558809340000153</v>
       </c>
       <c r="H1902" t="n">
         <v>2565</v>
@@ -56368,7 +56368,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1931" t="n">
-        <v>0.6063272356987</v>
+        <v>0.606327295303345</v>
       </c>
       <c r="H1931" t="n">
         <v>5238</v>
@@ -56484,7 +56484,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1935" t="n">
-        <v>0.591121554374695</v>
+        <v>0.59112149477005</v>
       </c>
       <c r="H1935" t="n">
         <v>12816</v>
@@ -56513,7 +56513,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1936" t="n">
-        <v>0.585419416427612</v>
+        <v>0.585419356822968</v>
       </c>
       <c r="H1936" t="n">
         <v>2748</v>
@@ -56571,7 +56571,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1938" t="n">
-        <v>0.579717218875885</v>
+        <v>0.57971727848053</v>
       </c>
       <c r="H1938" t="n">
         <v>3888</v>
@@ -56600,7 +56600,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1939" t="n">
-        <v>0.58351868391037</v>
+        <v>0.583518624305725</v>
       </c>
       <c r="H1939" t="n">
         <v>4503</v>
@@ -56977,7 +56977,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1952" t="n">
-        <v>0.558809399604797</v>
+        <v>0.558809340000153</v>
       </c>
       <c r="H1952" t="n">
         <v>220</v>
@@ -57035,7 +57035,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1954" t="n">
-        <v>0.558809399604797</v>
+        <v>0.558809340000153</v>
       </c>
       <c r="H1954" t="n">
         <v>701</v>
@@ -80096,6 +80096,35 @@
         <v>1525</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>1.19000005722046</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>1.14999997615814</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>1.1599999666214</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>7031</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G2" t="n">
-        <v>1.44454121589661</v>
+        <v>1.44454109668732</v>
       </c>
       <c r="H2" t="n">
         <v>5783</v>
@@ -456,7 +456,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G3" t="n">
-        <v>1.55858409404755</v>
+        <v>1.55858397483826</v>
       </c>
       <c r="H3" t="n">
         <v>10710</v>
@@ -485,7 +485,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G4" t="n">
-        <v>1.56808757781982</v>
+        <v>1.56808769702911</v>
       </c>
       <c r="H4" t="n">
         <v>7639</v>
@@ -543,7 +543,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G6" t="n">
-        <v>1.53482508659363</v>
+        <v>1.53482496738434</v>
       </c>
       <c r="H6" t="n">
         <v>31459</v>
@@ -572,7 +572,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>1.46354830265045</v>
+        <v>1.46354842185974</v>
       </c>
       <c r="H7" t="n">
         <v>39904</v>
@@ -601,7 +601,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G8" t="n">
-        <v>1.49205911159515</v>
+        <v>1.49205923080444</v>
       </c>
       <c r="H8" t="n">
         <v>9900</v>
@@ -688,7 +688,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G11" t="n">
-        <v>1.34000205993652</v>
+        <v>1.34000194072723</v>
       </c>
       <c r="H11" t="n">
         <v>24720</v>
@@ -746,7 +746,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3495055437088</v>
+        <v>1.34950566291809</v>
       </c>
       <c r="H13" t="n">
         <v>6400</v>
@@ -833,7 +833,7 @@
         <v>1.41999995708466</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3495055437088</v>
+        <v>1.34950566291809</v>
       </c>
       <c r="H16" t="n">
         <v>17034</v>
@@ -862,7 +862,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G17" t="n">
-        <v>1.30198788642883</v>
+        <v>1.30198776721954</v>
       </c>
       <c r="H17" t="n">
         <v>5838</v>
@@ -891,7 +891,7 @@
         <v>1.37000000476837</v>
       </c>
       <c r="G18" t="n">
-        <v>1.30198788642883</v>
+        <v>1.30198776721954</v>
       </c>
       <c r="H18" t="n">
         <v>4474</v>
@@ -978,7 +978,7 @@
         <v>1.375</v>
       </c>
       <c r="G21" t="n">
-        <v>1.30673968791962</v>
+        <v>1.30673956871033</v>
       </c>
       <c r="H21" t="n">
         <v>1302</v>
@@ -1036,7 +1036,7 @@
         <v>1.40699994564056</v>
       </c>
       <c r="G23" t="n">
-        <v>1.33715105056763</v>
+        <v>1.33715093135834</v>
       </c>
       <c r="H23" t="n">
         <v>2689</v>
@@ -1065,7 +1065,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G24" t="n">
-        <v>1.33049857616425</v>
+        <v>1.33049845695496</v>
       </c>
       <c r="H24" t="n">
         <v>8036</v>
@@ -1123,7 +1123,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G26" t="n">
-        <v>1.25447010993958</v>
+        <v>1.25447022914886</v>
       </c>
       <c r="H26" t="n">
         <v>11901</v>
@@ -1239,7 +1239,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G30" t="n">
-        <v>1.13662588596344</v>
+        <v>1.13662576675415</v>
       </c>
       <c r="H30" t="n">
         <v>1130</v>
@@ -1326,7 +1326,7 @@
         <v>1.375</v>
       </c>
       <c r="G33" t="n">
-        <v>1.30673968791962</v>
+        <v>1.30673956871033</v>
       </c>
       <c r="H33" t="n">
         <v>9139</v>
@@ -1413,7 +1413,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G36" t="n">
-        <v>1.25922179222107</v>
+        <v>1.25922191143036</v>
       </c>
       <c r="H36" t="n">
         <v>4117</v>
@@ -1500,7 +1500,7 @@
         <v>1.3860000371933</v>
       </c>
       <c r="G39" t="n">
-        <v>1.31719350814819</v>
+        <v>1.31719362735748</v>
       </c>
       <c r="H39" t="n">
         <v>13555</v>
@@ -1587,7 +1587,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G42" t="n">
-        <v>1.29723608493805</v>
+        <v>1.29723620414734</v>
       </c>
       <c r="H42" t="n">
         <v>3745</v>
@@ -1674,7 +1674,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G45" t="n">
-        <v>1.32099509239197</v>
+        <v>1.32099497318268</v>
       </c>
       <c r="H45" t="n">
         <v>1400</v>
@@ -1703,7 +1703,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>1.28773260116577</v>
+        <v>1.28773248195648</v>
       </c>
       <c r="H46" t="n">
         <v>3247</v>
@@ -1732,7 +1732,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G47" t="n">
-        <v>1.2810800075531</v>
+        <v>1.28108012676239</v>
       </c>
       <c r="H47" t="n">
         <v>4298</v>
@@ -1761,7 +1761,7 @@
         <v>1.34800004959106</v>
       </c>
       <c r="G48" t="n">
-        <v>1.2810800075531</v>
+        <v>1.28108012676239</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G49" t="n">
-        <v>1.30103754997253</v>
+        <v>1.30103743076324</v>
       </c>
       <c r="H49" t="n">
         <v>8270</v>
@@ -1848,7 +1848,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G51" t="n">
-        <v>1.33049857616425</v>
+        <v>1.33049845695496</v>
       </c>
       <c r="H51" t="n">
         <v>5788</v>
@@ -1935,7 +1935,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G54" t="n">
-        <v>1.32099509239197</v>
+        <v>1.32099497318268</v>
       </c>
       <c r="H54" t="n">
         <v>1500</v>
@@ -2051,7 +2051,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G58" t="n">
-        <v>1.26967573165894</v>
+        <v>1.26967561244965</v>
       </c>
       <c r="H58" t="n">
         <v>21406</v>
@@ -2080,7 +2080,7 @@
         <v>1.39499998092651</v>
       </c>
       <c r="G59" t="n">
-        <v>1.32574677467346</v>
+        <v>1.32574665546417</v>
       </c>
       <c r="H59" t="n">
         <v>560</v>
@@ -2254,7 +2254,7 @@
         <v>1.32599997520447</v>
       </c>
       <c r="G65" t="n">
-        <v>1.26017200946808</v>
+        <v>1.26017212867737</v>
       </c>
       <c r="H65" t="n">
         <v>13431</v>
@@ -2544,7 +2544,7 @@
         <v>1.31200003623962</v>
       </c>
       <c r="G75" t="n">
-        <v>1.2468672990799</v>
+        <v>1.24686717987061</v>
       </c>
       <c r="H75" t="n">
         <v>4961</v>
@@ -2573,7 +2573,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G76" t="n">
-        <v>1.26967573165894</v>
+        <v>1.26967561244965</v>
       </c>
       <c r="H76" t="n">
         <v>8995</v>
@@ -2602,7 +2602,7 @@
         <v>1.32700002193451</v>
       </c>
       <c r="G77" t="n">
-        <v>1.26112246513367</v>
+        <v>1.26112258434296</v>
       </c>
       <c r="H77" t="n">
         <v>14946</v>
@@ -2631,7 +2631,7 @@
         <v>1.34099996089935</v>
       </c>
       <c r="G78" t="n">
-        <v>1.27442753314972</v>
+        <v>1.27442741394043</v>
       </c>
       <c r="H78" t="n">
         <v>3828</v>
@@ -2660,7 +2660,7 @@
         <v>1.34700000286102</v>
       </c>
       <c r="G79" t="n">
-        <v>1.28012955188751</v>
+        <v>1.2801296710968</v>
       </c>
       <c r="H79" t="n">
         <v>6900</v>
@@ -2689,7 +2689,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G80" t="n">
-        <v>1.27917921543121</v>
+        <v>1.2791793346405</v>
       </c>
       <c r="H80" t="n">
         <v>1743</v>
@@ -2718,7 +2718,7 @@
         <v>1.34599995613098</v>
       </c>
       <c r="G81" t="n">
-        <v>1.27917921543121</v>
+        <v>1.2791793346405</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G84" t="n">
-        <v>1.27347719669342</v>
+        <v>1.27347731590271</v>
       </c>
       <c r="H84" t="n">
         <v>9423</v>
@@ -2979,7 +2979,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G90" t="n">
-        <v>1.30103754997253</v>
+        <v>1.30103743076324</v>
       </c>
       <c r="H90" t="n">
         <v>100</v>
@@ -3008,7 +3008,7 @@
         <v>1.36899995803833</v>
       </c>
       <c r="G91" t="n">
-        <v>1.30103754997253</v>
+        <v>1.30103743076324</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G92" t="n">
-        <v>1.25922179222107</v>
+        <v>1.25922191143036</v>
       </c>
       <c r="H92" t="n">
         <v>1792</v>
@@ -3095,7 +3095,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G94" t="n">
-        <v>1.25447010993958</v>
+        <v>1.25447022914886</v>
       </c>
       <c r="H94" t="n">
         <v>6526</v>
@@ -3153,7 +3153,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G96" t="n">
-        <v>1.19744873046875</v>
+        <v>1.19744861125946</v>
       </c>
       <c r="H96" t="n">
         <v>1704</v>
@@ -3182,7 +3182,7 @@
         <v>1.26900005340576</v>
       </c>
       <c r="G97" t="n">
-        <v>1.20600175857544</v>
+        <v>1.20600187778473</v>
       </c>
       <c r="H97" t="n">
         <v>1181</v>
@@ -3211,7 +3211,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G98" t="n">
-        <v>1.18034219741821</v>
+        <v>1.1803423166275</v>
       </c>
       <c r="H98" t="n">
         <v>765</v>
@@ -3240,7 +3240,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G99" t="n">
-        <v>1.18034219741821</v>
+        <v>1.1803423166275</v>
       </c>
       <c r="H99" t="n">
         <v>10250</v>
@@ -3298,7 +3298,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G101" t="n">
-        <v>1.19744873046875</v>
+        <v>1.19744861125946</v>
       </c>
       <c r="H101" t="n">
         <v>2109</v>
@@ -3414,7 +3414,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G105" t="n">
-        <v>1.17178905010223</v>
+        <v>1.17178916931152</v>
       </c>
       <c r="H105" t="n">
         <v>3950</v>
@@ -3472,7 +3472,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G107" t="n">
-        <v>1.17749130725861</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H107" t="n">
         <v>2700</v>
@@ -3501,7 +3501,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G108" t="n">
-        <v>1.17749130725861</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H108" t="n">
         <v>500</v>
@@ -3559,7 +3559,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>1.16893792152405</v>
+        <v>1.16893804073334</v>
       </c>
       <c r="H110" t="n">
         <v>3500</v>
@@ -3646,7 +3646,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G113" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H113" t="n">
         <v>202</v>
@@ -3762,7 +3762,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G117" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H117" t="n">
         <v>22400</v>
@@ -3791,7 +3791,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G118" t="n">
-        <v>1.17273950576782</v>
+        <v>1.17273938655853</v>
       </c>
       <c r="H118" t="n">
         <v>632</v>
@@ -3820,7 +3820,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G119" t="n">
-        <v>1.1869945526123</v>
+        <v>1.18699467182159</v>
       </c>
       <c r="H119" t="n">
         <v>7654</v>
@@ -3849,7 +3849,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G120" t="n">
-        <v>1.13092374801636</v>
+        <v>1.13092386722565</v>
       </c>
       <c r="H120" t="n">
         <v>5500</v>
@@ -3878,7 +3878,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G121" t="n">
-        <v>1.13187396526337</v>
+        <v>1.13187408447266</v>
       </c>
       <c r="H121" t="n">
         <v>5919</v>
@@ -3907,7 +3907,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G122" t="n">
-        <v>1.13092374801636</v>
+        <v>1.13092386722565</v>
       </c>
       <c r="H122" t="n">
         <v>1401</v>
@@ -3936,7 +3936,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G123" t="n">
-        <v>1.13662588596344</v>
+        <v>1.13662576675415</v>
       </c>
       <c r="H123" t="n">
         <v>15822</v>
@@ -3965,7 +3965,7 @@
         <v>1.02300000190735</v>
       </c>
       <c r="G124" t="n">
-        <v>0.972214341163635</v>
+        <v>0.97221428155899</v>
       </c>
       <c r="H124" t="n">
         <v>9233</v>
@@ -4023,7 +4023,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G126" t="n">
-        <v>0.975065410137177</v>
+        <v>0.975065350532532</v>
       </c>
       <c r="H126" t="n">
         <v>15762</v>
@@ -4081,7 +4081,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G128" t="n">
-        <v>1.12046992778778</v>
+        <v>1.12046980857849</v>
       </c>
       <c r="H128" t="n">
         <v>34445</v>
@@ -4226,7 +4226,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G133" t="n">
-        <v>0.99502295255661</v>
+        <v>0.995022833347321</v>
       </c>
       <c r="H133" t="n">
         <v>5798</v>
@@ -4255,7 +4255,7 @@
         <v>1.07400000095367</v>
       </c>
       <c r="G134" t="n">
-        <v>1.02068245410919</v>
+        <v>1.02068257331848</v>
       </c>
       <c r="H134" t="n">
         <v>1695</v>
@@ -4284,7 +4284,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G135" t="n">
-        <v>1.00547671318054</v>
+        <v>1.00547659397125</v>
       </c>
       <c r="H135" t="n">
         <v>11813</v>
@@ -4400,7 +4400,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G139" t="n">
-        <v>0.996923625469208</v>
+        <v>0.996923506259918</v>
       </c>
       <c r="H139" t="n">
         <v>1497</v>
@@ -4574,7 +4574,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G145" t="n">
-        <v>0.975065410137177</v>
+        <v>0.975065350532532</v>
       </c>
       <c r="H145" t="n">
         <v>6955</v>
@@ -4632,7 +4632,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G147" t="n">
-        <v>0.99502295255661</v>
+        <v>0.995022833347321</v>
       </c>
       <c r="H147" t="n">
         <v>10351</v>
@@ -4661,7 +4661,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>0.98837023973465</v>
+        <v>0.988370358943939</v>
       </c>
       <c r="H148" t="n">
         <v>13390</v>
@@ -4748,7 +4748,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G151" t="n">
-        <v>0.987419962882996</v>
+        <v>0.987420082092285</v>
       </c>
       <c r="H151" t="n">
         <v>15266</v>
@@ -4893,7 +4893,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G156" t="n">
-        <v>1.01402997970581</v>
+        <v>1.0140300989151</v>
       </c>
       <c r="H156" t="n">
         <v>4958</v>
@@ -4922,7 +4922,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G157" t="n">
-        <v>1.01402997970581</v>
+        <v>1.0140300989151</v>
       </c>
       <c r="H157" t="n">
         <v>3607</v>
@@ -4951,7 +4951,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G158" t="n">
-        <v>1.01402997970581</v>
+        <v>1.0140300989151</v>
       </c>
       <c r="H158" t="n">
         <v>1536</v>
@@ -4980,7 +4980,7 @@
         <v>1.07700002193451</v>
       </c>
       <c r="G159" t="n">
-        <v>1.02353346347809</v>
+        <v>1.02353358268738</v>
       </c>
       <c r="H159" t="n">
         <v>301</v>
@@ -5125,7 +5125,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G164" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866636753082</v>
       </c>
       <c r="H164" t="n">
         <v>250</v>
@@ -5154,7 +5154,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G165" t="n">
-        <v>0.963661074638367</v>
+        <v>0.963661134243011</v>
       </c>
       <c r="H165" t="n">
         <v>3542</v>
@@ -5212,7 +5212,7 @@
         <v>1.01699995994568</v>
       </c>
       <c r="G167" t="n">
-        <v>0.966512143611908</v>
+        <v>0.966512084007263</v>
       </c>
       <c r="H167" t="n">
         <v>5722</v>
@@ -5241,7 +5241,7 @@
         <v>1.02300000190735</v>
       </c>
       <c r="G168" t="n">
-        <v>0.972214341163635</v>
+        <v>0.97221428155899</v>
       </c>
       <c r="H168" t="n">
         <v>2389</v>
@@ -5299,7 +5299,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G170" t="n">
-        <v>0.973164796829224</v>
+        <v>0.973164677619934</v>
       </c>
       <c r="H170" t="n">
         <v>7003</v>
@@ -5328,7 +5328,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G171" t="n">
-        <v>0.99502295255661</v>
+        <v>0.995022833347321</v>
       </c>
       <c r="H171" t="n">
         <v>2072</v>
@@ -5357,7 +5357,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G172" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866636753082</v>
       </c>
       <c r="H172" t="n">
         <v>10607</v>
@@ -5386,7 +5386,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G173" t="n">
-        <v>1.00547671318054</v>
+        <v>1.00547659397125</v>
       </c>
       <c r="H173" t="n">
         <v>1</v>
@@ -5415,7 +5415,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G174" t="n">
-        <v>0.996923625469208</v>
+        <v>0.996923506259918</v>
       </c>
       <c r="H174" t="n">
         <v>500</v>
@@ -5531,7 +5531,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G178" t="n">
-        <v>1.1518315076828</v>
+        <v>1.15183162689209</v>
       </c>
       <c r="H178" t="n">
         <v>81424</v>
@@ -5560,7 +5560,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G179" t="n">
-        <v>1.12427127361298</v>
+        <v>1.12427115440369</v>
       </c>
       <c r="H179" t="n">
         <v>16527</v>
@@ -5792,7 +5792,7 @@
         <v>1.12699997425079</v>
       </c>
       <c r="G187" t="n">
-        <v>1.07105135917664</v>
+        <v>1.07105123996735</v>
       </c>
       <c r="H187" t="n">
         <v>100</v>
@@ -5908,7 +5908,7 @@
         <v>1.04299998283386</v>
       </c>
       <c r="G191" t="n">
-        <v>0.99122154712677</v>
+        <v>0.99122142791748</v>
       </c>
       <c r="H191" t="n">
         <v>16155</v>
@@ -5937,7 +5937,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G192" t="n">
-        <v>0.987419962882996</v>
+        <v>0.987420082092285</v>
       </c>
       <c r="H192" t="n">
         <v>2600</v>
@@ -5966,7 +5966,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G193" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H193" t="n">
         <v>3500</v>
@@ -5995,7 +5995,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G194" t="n">
-        <v>0.996923625469208</v>
+        <v>0.996923506259918</v>
       </c>
       <c r="H194" t="n">
         <v>3572</v>
@@ -6053,7 +6053,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G196" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866636753082</v>
       </c>
       <c r="H196" t="n">
         <v>305</v>
@@ -6082,7 +6082,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G197" t="n">
-        <v>0.989320576190948</v>
+        <v>0.989320695400238</v>
       </c>
       <c r="H197" t="n">
         <v>16909</v>
@@ -6169,7 +6169,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G200" t="n">
-        <v>0.984568953514099</v>
+        <v>0.984568893909454</v>
       </c>
       <c r="H200" t="n">
         <v>1505</v>
@@ -6198,7 +6198,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>0.98837023973465</v>
+        <v>0.988370358943939</v>
       </c>
       <c r="H201" t="n">
         <v>500</v>
@@ -6227,7 +6227,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G202" t="n">
-        <v>0.963661074638367</v>
+        <v>0.963661134243011</v>
       </c>
       <c r="H202" t="n">
         <v>4000</v>
@@ -6256,7 +6256,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G203" t="n">
-        <v>0.984568953514099</v>
+        <v>0.984568893909454</v>
       </c>
       <c r="H203" t="n">
         <v>10950</v>
@@ -6285,7 +6285,7 @@
         <v>1.02100002765656</v>
       </c>
       <c r="G204" t="n">
-        <v>0.970313608646393</v>
+        <v>0.970313549041748</v>
       </c>
       <c r="H204" t="n">
         <v>4160</v>
@@ -6314,7 +6314,7 @@
         <v>1.02100002765656</v>
       </c>
       <c r="G205" t="n">
-        <v>0.970313608646393</v>
+        <v>0.970313549041748</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>1.02100002765656</v>
       </c>
       <c r="G206" t="n">
-        <v>0.970313608646393</v>
+        <v>0.970313549041748</v>
       </c>
       <c r="H206" t="n">
         <v>1966</v>
@@ -6372,7 +6372,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G207" t="n">
-        <v>0.987419962882996</v>
+        <v>0.987420082092285</v>
       </c>
       <c r="H207" t="n">
         <v>9988</v>
@@ -6517,7 +6517,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G212" t="n">
-        <v>0.973164796829224</v>
+        <v>0.973164677619934</v>
       </c>
       <c r="H212" t="n">
         <v>900</v>
@@ -6836,7 +6836,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G223" t="n">
-        <v>0.973164796829224</v>
+        <v>0.973164677619934</v>
       </c>
       <c r="H223" t="n">
         <v>5403</v>
@@ -6865,7 +6865,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638483047485</v>
       </c>
       <c r="H224" t="n">
         <v>16296</v>
@@ -6923,7 +6923,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G226" t="n">
-        <v>0.961760401725769</v>
+        <v>0.961760342121124</v>
       </c>
       <c r="H226" t="n">
         <v>6335</v>
@@ -6981,7 +6981,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866636753082</v>
       </c>
       <c r="H228" t="n">
         <v>2724</v>
@@ -7010,7 +7010,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G229" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866636753082</v>
       </c>
       <c r="H229" t="n">
         <v>11827</v>
@@ -7039,7 +7039,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G230" t="n">
-        <v>0.984568953514099</v>
+        <v>0.984568893909454</v>
       </c>
       <c r="H230" t="n">
         <v>302145</v>
@@ -7068,7 +7068,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G231" t="n">
-        <v>0.984568953514099</v>
+        <v>0.984568893909454</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>0.998499989509583</v>
       </c>
       <c r="G232" t="n">
-        <v>0.948930501937866</v>
+        <v>0.948930561542511</v>
       </c>
       <c r="H232" t="n">
         <v>17878</v>
@@ -7184,7 +7184,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G235" t="n">
-        <v>0.989320576190948</v>
+        <v>0.989320695400238</v>
       </c>
       <c r="H235" t="n">
         <v>10528</v>
@@ -7213,7 +7213,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G236" t="n">
-        <v>0.973164796829224</v>
+        <v>0.973164677619934</v>
       </c>
       <c r="H236" t="n">
         <v>261</v>
@@ -7300,7 +7300,7 @@
         <v>1.01199996471405</v>
       </c>
       <c r="G239" t="n">
-        <v>0.961760401725769</v>
+        <v>0.961760342121124</v>
       </c>
       <c r="H239" t="n">
         <v>2678</v>
@@ -7474,7 +7474,7 @@
         <v>1.02600002288818</v>
       </c>
       <c r="G245" t="n">
-        <v>0.975065410137177</v>
+        <v>0.975065350532532</v>
       </c>
       <c r="H245" t="n">
         <v>2093</v>
@@ -7503,7 +7503,7 @@
         <v>1.00100004673004</v>
       </c>
       <c r="G246" t="n">
-        <v>0.951306462287903</v>
+        <v>0.951306521892548</v>
       </c>
       <c r="H246" t="n">
         <v>37497</v>
@@ -7532,7 +7532,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G247" t="n">
-        <v>0.984568953514099</v>
+        <v>0.984568893909454</v>
       </c>
       <c r="H247" t="n">
         <v>11434</v>
@@ -7561,7 +7561,7 @@
         <v>1.03900003433228</v>
       </c>
       <c r="G248" t="n">
-        <v>0.987419962882996</v>
+        <v>0.987420082092285</v>
       </c>
       <c r="H248" t="n">
         <v>20000</v>
@@ -7590,7 +7590,7 @@
         <v>1.03400003910065</v>
       </c>
       <c r="G249" t="n">
-        <v>0.982668220996857</v>
+        <v>0.982668280601501</v>
       </c>
       <c r="H249" t="n">
         <v>204848</v>
@@ -7619,7 +7619,7 @@
         <v>1.02400004863739</v>
       </c>
       <c r="G250" t="n">
-        <v>0.973164796829224</v>
+        <v>0.973164677619934</v>
       </c>
       <c r="H250" t="n">
         <v>51760</v>
@@ -7677,7 +7677,7 @@
         <v>1.01400005817413</v>
       </c>
       <c r="G252" t="n">
-        <v>0.963661074638367</v>
+        <v>0.963661134243011</v>
       </c>
       <c r="H252" t="n">
         <v>13025</v>
@@ -7764,7 +7764,7 @@
         <v>1.13300001621246</v>
       </c>
       <c r="G255" t="n">
-        <v>1.07675337791443</v>
+        <v>1.07675349712372</v>
       </c>
       <c r="H255" t="n">
         <v>230084</v>
@@ -7793,7 +7793,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G256" t="n">
-        <v>1.016881108284</v>
+        <v>1.01688098907471</v>
       </c>
       <c r="H256" t="n">
         <v>193164</v>
@@ -7822,7 +7822,7 @@
         <v>1.04100000858307</v>
       </c>
       <c r="G257" t="n">
-        <v>0.989320576190948</v>
+        <v>0.989320695400238</v>
       </c>
       <c r="H257" t="n">
         <v>97577</v>
@@ -7851,7 +7851,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G258" t="n">
-        <v>0.983618497848511</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H258" t="n">
         <v>98439</v>
@@ -7880,7 +7880,7 @@
         <v>1.03600001335144</v>
       </c>
       <c r="G259" t="n">
-        <v>0.984568953514099</v>
+        <v>0.984568893909454</v>
       </c>
       <c r="H259" t="n">
         <v>30635</v>
@@ -7909,7 +7909,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>0.98837023973465</v>
+        <v>0.988370358943939</v>
       </c>
       <c r="H260" t="n">
         <v>96748</v>
@@ -8083,7 +8083,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G266" t="n">
-        <v>1.39227175712585</v>
+        <v>1.39227163791656</v>
       </c>
       <c r="H266" t="n">
         <v>81832</v>
@@ -8141,7 +8141,7 @@
         <v>1.39999997615814</v>
       </c>
       <c r="G268" t="n">
-        <v>1.33049857616425</v>
+        <v>1.33049845695496</v>
       </c>
       <c r="H268" t="n">
         <v>188065</v>
@@ -8170,7 +8170,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G269" t="n">
-        <v>1.34000205993652</v>
+        <v>1.34000194072723</v>
       </c>
       <c r="H269" t="n">
         <v>298958</v>
@@ -8576,7 +8576,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G283" t="n">
-        <v>1.17749130725861</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H283" t="n">
         <v>73831</v>
@@ -8605,7 +8605,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G284" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H284" t="n">
         <v>55023</v>
@@ -8634,7 +8634,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G285" t="n">
-        <v>1.13947701454163</v>
+        <v>1.13947689533234</v>
       </c>
       <c r="H285" t="n">
         <v>47058</v>
@@ -8663,7 +8663,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G286" t="n">
-        <v>1.17178905010223</v>
+        <v>1.17178916931152</v>
       </c>
       <c r="H286" t="n">
         <v>51660</v>
@@ -8721,7 +8721,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G288" t="n">
-        <v>1.12142014503479</v>
+        <v>1.1214200258255</v>
       </c>
       <c r="H288" t="n">
         <v>46988</v>
@@ -8779,7 +8779,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G290" t="n">
-        <v>1.09671092033386</v>
+        <v>1.09671103954315</v>
       </c>
       <c r="H290" t="n">
         <v>65474</v>
@@ -8953,7 +8953,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G296" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H296" t="n">
         <v>5384</v>
@@ -9069,7 +9069,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>1.20695221424103</v>
+        <v>1.20695233345032</v>
       </c>
       <c r="H300" t="n">
         <v>416286</v>
@@ -9098,7 +9098,7 @@
         <v>1.21899998188019</v>
       </c>
       <c r="G301" t="n">
-        <v>1.15848422050476</v>
+        <v>1.15848410129547</v>
       </c>
       <c r="H301" t="n">
         <v>201854</v>
@@ -9156,7 +9156,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G303" t="n">
-        <v>1.16893792152405</v>
+        <v>1.16893804073334</v>
       </c>
       <c r="H303" t="n">
         <v>24748</v>
@@ -9214,7 +9214,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G305" t="n">
-        <v>1.13092374801636</v>
+        <v>1.13092386722565</v>
       </c>
       <c r="H305" t="n">
         <v>24968</v>
@@ -9301,7 +9301,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G308" t="n">
-        <v>1.15943455696106</v>
+        <v>1.15943443775177</v>
       </c>
       <c r="H308" t="n">
         <v>50763</v>
@@ -9330,7 +9330,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G309" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H309" t="n">
         <v>25871</v>
@@ -9359,7 +9359,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G310" t="n">
-        <v>1.13662588596344</v>
+        <v>1.13662576675415</v>
       </c>
       <c r="H310" t="n">
         <v>18377</v>
@@ -9388,7 +9388,7 @@
         <v>1.21200001239777</v>
       </c>
       <c r="G311" t="n">
-        <v>1.1518315076828</v>
+        <v>1.15183162689209</v>
       </c>
       <c r="H311" t="n">
         <v>17084</v>
@@ -9417,7 +9417,7 @@
         <v>1.19700002670288</v>
       </c>
       <c r="G312" t="n">
-        <v>1.13757622241974</v>
+        <v>1.13757634162903</v>
       </c>
       <c r="H312" t="n">
         <v>23203</v>
@@ -9475,7 +9475,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G314" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H314" t="n">
         <v>30226</v>
@@ -9533,7 +9533,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G316" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H316" t="n">
         <v>17705</v>
@@ -9562,7 +9562,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G317" t="n">
-        <v>1.12522161006927</v>
+        <v>1.12522172927856</v>
       </c>
       <c r="H317" t="n">
         <v>18494</v>
@@ -9649,7 +9649,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G320" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H320" t="n">
         <v>15262</v>
@@ -9736,7 +9736,7 @@
         <v>1.22300004959106</v>
       </c>
       <c r="G323" t="n">
-        <v>1.16228544712067</v>
+        <v>1.16228556632996</v>
       </c>
       <c r="H323" t="n">
         <v>12953</v>
@@ -9794,7 +9794,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G325" t="n">
-        <v>1.13092374801636</v>
+        <v>1.13092386722565</v>
       </c>
       <c r="H325" t="n">
         <v>16563</v>
@@ -9997,7 +9997,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G332" t="n">
-        <v>1.12046992778778</v>
+        <v>1.12046980857849</v>
       </c>
       <c r="H332" t="n">
         <v>29437</v>
@@ -10084,7 +10084,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G335" t="n">
-        <v>1.13092374801636</v>
+        <v>1.13092386722565</v>
       </c>
       <c r="H335" t="n">
         <v>29183</v>
@@ -10113,7 +10113,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G336" t="n">
-        <v>1.11666834354401</v>
+        <v>1.1166684627533</v>
       </c>
       <c r="H336" t="n">
         <v>13081</v>
@@ -10171,7 +10171,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G338" t="n">
-        <v>1.12046992778778</v>
+        <v>1.12046980857849</v>
       </c>
       <c r="H338" t="n">
         <v>12735</v>
@@ -10229,7 +10229,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>1.11286687850952</v>
+        <v>1.11286699771881</v>
       </c>
       <c r="H340" t="n">
         <v>7409</v>
@@ -10258,7 +10258,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G341" t="n">
-        <v>1.11856925487518</v>
+        <v>1.11856913566589</v>
       </c>
       <c r="H341" t="n">
         <v>13730</v>
@@ -10287,7 +10287,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G342" t="n">
-        <v>1.12142014503479</v>
+        <v>1.1214200258255</v>
       </c>
       <c r="H342" t="n">
         <v>14737</v>
@@ -10490,7 +10490,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G349" t="n">
-        <v>1.12522161006927</v>
+        <v>1.12522172927856</v>
       </c>
       <c r="H349" t="n">
         <v>11135</v>
@@ -10519,7 +10519,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G350" t="n">
-        <v>1.12142014503479</v>
+        <v>1.1214200258255</v>
       </c>
       <c r="H350" t="n">
         <v>2609</v>
@@ -10548,7 +10548,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G351" t="n">
-        <v>1.13092374801636</v>
+        <v>1.13092386722565</v>
       </c>
       <c r="H351" t="n">
         <v>34831</v>
@@ -10577,7 +10577,7 @@
         <v>1.13300001621246</v>
       </c>
       <c r="G352" t="n">
-        <v>1.07675337791443</v>
+        <v>1.07675349712372</v>
       </c>
       <c r="H352" t="n">
         <v>56977</v>
@@ -10722,7 +10722,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G357" t="n">
-        <v>1.07010102272034</v>
+        <v>1.07010114192963</v>
       </c>
       <c r="H357" t="n">
         <v>20350</v>
@@ -10751,7 +10751,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G358" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H358" t="n">
         <v>39402</v>
@@ -10780,7 +10780,7 @@
         <v>1.11800003051758</v>
       </c>
       <c r="G359" t="n">
-        <v>1.06249809265137</v>
+        <v>1.06249821186066</v>
       </c>
       <c r="H359" t="n">
         <v>87083</v>
@@ -10809,7 +10809,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G360" t="n">
-        <v>1.0491931438446</v>
+        <v>1.04919302463531</v>
       </c>
       <c r="H360" t="n">
         <v>10968</v>
@@ -10838,7 +10838,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G361" t="n">
-        <v>1.05489528179169</v>
+        <v>1.0548951625824</v>
       </c>
       <c r="H361" t="n">
         <v>6017</v>
@@ -10867,7 +10867,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G362" t="n">
-        <v>1.09956204891205</v>
+        <v>1.09956192970276</v>
       </c>
       <c r="H362" t="n">
         <v>393819</v>
@@ -10925,7 +10925,7 @@
         <v>1.12699997425079</v>
       </c>
       <c r="G364" t="n">
-        <v>1.07105135917664</v>
+        <v>1.07105123996735</v>
       </c>
       <c r="H364" t="n">
         <v>27841</v>
@@ -10983,7 +10983,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G366" t="n">
-        <v>1.0491931438446</v>
+        <v>1.04919302463531</v>
       </c>
       <c r="H366" t="n">
         <v>56985</v>
@@ -11128,7 +11128,7 @@
         <v>1.10099995136261</v>
       </c>
       <c r="G371" t="n">
-        <v>1.04634213447571</v>
+        <v>1.04634189605713</v>
       </c>
       <c r="H371" t="n">
         <v>16691</v>
@@ -11331,7 +11331,7 @@
         <v>1.13300001621246</v>
       </c>
       <c r="G378" t="n">
-        <v>1.07675337791443</v>
+        <v>1.07675349712372</v>
       </c>
       <c r="H378" t="n">
         <v>8636</v>
@@ -11476,7 +11476,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G383" t="n">
-        <v>1.0834059715271</v>
+        <v>1.08340585231781</v>
       </c>
       <c r="H383" t="n">
         <v>60477</v>
@@ -11592,7 +11592,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G387" t="n">
-        <v>1.11001598834991</v>
+        <v>1.11001586914062</v>
       </c>
       <c r="H387" t="n">
         <v>40810</v>
@@ -11650,7 +11650,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G389" t="n">
-        <v>1.13947701454163</v>
+        <v>1.13947689533234</v>
       </c>
       <c r="H389" t="n">
         <v>14550</v>
@@ -11679,7 +11679,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G390" t="n">
-        <v>1.13947701454163</v>
+        <v>1.13947689533234</v>
       </c>
       <c r="H390" t="n">
         <v>6972</v>
@@ -11737,7 +11737,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G392" t="n">
-        <v>1.17464005947113</v>
+        <v>1.17464017868042</v>
       </c>
       <c r="H392" t="n">
         <v>75009</v>
@@ -11795,7 +11795,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G394" t="n">
-        <v>1.12427127361298</v>
+        <v>1.12427115440369</v>
       </c>
       <c r="H394" t="n">
         <v>33424</v>
@@ -11824,7 +11824,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G395" t="n">
-        <v>1.13092374801636</v>
+        <v>1.13092386722565</v>
       </c>
       <c r="H395" t="n">
         <v>3110</v>
@@ -11911,7 +11911,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G398" t="n">
-        <v>1.13947701454163</v>
+        <v>1.13947689533234</v>
       </c>
       <c r="H398" t="n">
         <v>13357</v>
@@ -11969,7 +11969,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G400" t="n">
-        <v>1.11856925487518</v>
+        <v>1.11856913566589</v>
       </c>
       <c r="H400" t="n">
         <v>8359</v>
@@ -12056,7 +12056,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G403" t="n">
-        <v>1.11856925487518</v>
+        <v>1.11856913566589</v>
       </c>
       <c r="H403" t="n">
         <v>15262</v>
@@ -12201,7 +12201,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G408" t="n">
-        <v>1.11761868000031</v>
+        <v>1.11761879920959</v>
       </c>
       <c r="H408" t="n">
         <v>6600</v>
@@ -12259,7 +12259,7 @@
         <v>1.15299999713898</v>
       </c>
       <c r="G410" t="n">
-        <v>1.09576058387756</v>
+        <v>1.09576046466827</v>
       </c>
       <c r="H410" t="n">
         <v>2558</v>
@@ -12346,7 +12346,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G413" t="n">
-        <v>1.11381733417511</v>
+        <v>1.1138174533844</v>
       </c>
       <c r="H413" t="n">
         <v>2500</v>
@@ -12433,7 +12433,7 @@
         <v>1.15400004386902</v>
       </c>
       <c r="G416" t="n">
-        <v>1.09671092033386</v>
+        <v>1.09671103954315</v>
       </c>
       <c r="H416" t="n">
         <v>5579</v>
@@ -12491,7 +12491,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G418" t="n">
-        <v>1.11096632480621</v>
+        <v>1.1109664440155</v>
       </c>
       <c r="H418" t="n">
         <v>2516</v>
@@ -12607,7 +12607,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G422" t="n">
-        <v>1.13092374801636</v>
+        <v>1.13092386722565</v>
       </c>
       <c r="H422" t="n">
         <v>11271</v>
@@ -12636,7 +12636,7 @@
         <v>1.23000001907349</v>
       </c>
       <c r="G423" t="n">
-        <v>1.16893792152405</v>
+        <v>1.16893804073334</v>
       </c>
       <c r="H423" t="n">
         <v>227097</v>
@@ -12694,7 +12694,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G425" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H425" t="n">
         <v>23167</v>
@@ -12723,7 +12723,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G426" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H426" t="n">
         <v>2930</v>
@@ -12752,7 +12752,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G427" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H427" t="n">
         <v>23775</v>
@@ -12810,7 +12810,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G429" t="n">
-        <v>1.12427127361298</v>
+        <v>1.12427115440369</v>
       </c>
       <c r="H429" t="n">
         <v>17930</v>
@@ -12897,7 +12897,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G432" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H432" t="n">
         <v>23557</v>
@@ -12955,7 +12955,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G434" t="n">
-        <v>1.12142014503479</v>
+        <v>1.1214200258255</v>
       </c>
       <c r="H434" t="n">
         <v>31340</v>
@@ -12984,7 +12984,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G435" t="n">
-        <v>1.12142014503479</v>
+        <v>1.1214200258255</v>
       </c>
       <c r="H435" t="n">
         <v>7381</v>
@@ -13042,7 +13042,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G437" t="n">
-        <v>1.12522161006927</v>
+        <v>1.12522172927856</v>
       </c>
       <c r="H437" t="n">
         <v>13177</v>
@@ -13071,7 +13071,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G438" t="n">
-        <v>1.12142014503479</v>
+        <v>1.1214200258255</v>
       </c>
       <c r="H438" t="n">
         <v>706</v>
@@ -13100,7 +13100,7 @@
         <v>1.18400001525879</v>
       </c>
       <c r="G439" t="n">
-        <v>1.12522161006927</v>
+        <v>1.12522172927856</v>
       </c>
       <c r="H439" t="n">
         <v>55175</v>
@@ -13158,7 +13158,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G441" t="n">
-        <v>1.11286687850952</v>
+        <v>1.11286699771881</v>
       </c>
       <c r="H441" t="n">
         <v>9775</v>
@@ -13216,7 +13216,7 @@
         <v>1.17599999904633</v>
       </c>
       <c r="G443" t="n">
-        <v>1.11761868000031</v>
+        <v>1.11761879920959</v>
       </c>
       <c r="H443" t="n">
         <v>9327</v>
@@ -13245,7 +13245,7 @@
         <v>1.16799998283386</v>
       </c>
       <c r="G444" t="n">
-        <v>1.11001598834991</v>
+        <v>1.11001586914062</v>
       </c>
       <c r="H444" t="n">
         <v>1482</v>
@@ -13361,7 +13361,7 @@
         <v>1.22300004959106</v>
       </c>
       <c r="G448" t="n">
-        <v>1.16228544712067</v>
+        <v>1.16228556632996</v>
       </c>
       <c r="H448" t="n">
         <v>136567</v>
@@ -13448,7 +13448,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G451" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H451" t="n">
         <v>11298</v>
@@ -13506,7 +13506,7 @@
         <v>1.26800000667572</v>
       </c>
       <c r="G453" t="n">
-        <v>1.20505142211914</v>
+        <v>1.20505154132843</v>
       </c>
       <c r="H453" t="n">
         <v>91082</v>
@@ -13593,7 +13593,7 @@
         <v>1.23300004005432</v>
       </c>
       <c r="G456" t="n">
-        <v>1.17178905010223</v>
+        <v>1.17178916931152</v>
       </c>
       <c r="H456" t="n">
         <v>20072</v>
@@ -13622,7 +13622,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G457" t="n">
-        <v>1.17273950576782</v>
+        <v>1.17273938655853</v>
       </c>
       <c r="H457" t="n">
         <v>21775</v>
@@ -13709,7 +13709,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G460" t="n">
-        <v>1.17749130725861</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H460" t="n">
         <v>19410</v>
@@ -13738,7 +13738,7 @@
         <v>1.23599994182587</v>
       </c>
       <c r="G461" t="n">
-        <v>1.17464005947113</v>
+        <v>1.17464017868042</v>
       </c>
       <c r="H461" t="n">
         <v>4453</v>
@@ -13767,7 +13767,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G462" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H462" t="n">
         <v>20101</v>
@@ -13825,7 +13825,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G464" t="n">
-        <v>1.19744873046875</v>
+        <v>1.19744861125946</v>
       </c>
       <c r="H464" t="n">
         <v>125211</v>
@@ -13941,7 +13941,7 @@
         <v>1.22300004959106</v>
       </c>
       <c r="G468" t="n">
-        <v>1.16228544712067</v>
+        <v>1.16228556632996</v>
       </c>
       <c r="H468" t="n">
         <v>5718</v>
@@ -14115,7 +14115,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>1.20695221424103</v>
+        <v>1.20695233345032</v>
       </c>
       <c r="H474" t="n">
         <v>221096</v>
@@ -14173,7 +14173,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G476" t="n">
-        <v>1.17749130725861</v>
+        <v>1.17749118804932</v>
       </c>
       <c r="H476" t="n">
         <v>127242</v>
@@ -14202,7 +14202,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G477" t="n">
-        <v>1.1499308347702</v>
+        <v>1.14993095397949</v>
       </c>
       <c r="H477" t="n">
         <v>41948</v>
@@ -14231,7 +14231,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G478" t="n">
-        <v>1.16703724861145</v>
+        <v>1.16703736782074</v>
       </c>
       <c r="H478" t="n">
         <v>11110</v>
@@ -14347,7 +14347,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G482" t="n">
-        <v>1.12046992778778</v>
+        <v>1.12046980857849</v>
       </c>
       <c r="H482" t="n">
         <v>3732</v>
@@ -14376,7 +14376,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G483" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H483" t="n">
         <v>4602</v>
@@ -14434,7 +14434,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G485" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H485" t="n">
         <v>5311</v>
@@ -14463,7 +14463,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G486" t="n">
-        <v>1.11381733417511</v>
+        <v>1.1138174533844</v>
       </c>
       <c r="H486" t="n">
         <v>6100</v>
@@ -14521,7 +14521,7 @@
         <v>1.19700002670288</v>
       </c>
       <c r="G488" t="n">
-        <v>1.13757622241974</v>
+        <v>1.13757634162903</v>
       </c>
       <c r="H488" t="n">
         <v>13286</v>
@@ -14550,7 +14550,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G489" t="n">
-        <v>1.11856925487518</v>
+        <v>1.11856913566589</v>
       </c>
       <c r="H489" t="n">
         <v>10010</v>
@@ -14637,7 +14637,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G492" t="n">
-        <v>1.12046992778778</v>
+        <v>1.12046980857849</v>
       </c>
       <c r="H492" t="n">
         <v>5587</v>
@@ -14666,7 +14666,7 @@
         <v>1.17900002002716</v>
       </c>
       <c r="G493" t="n">
-        <v>1.12046992778778</v>
+        <v>1.12046980857849</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G498" t="n">
-        <v>1.11096632480621</v>
+        <v>1.1109664440155</v>
       </c>
       <c r="H498" t="n">
         <v>4720</v>
@@ -14840,7 +14840,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G499" t="n">
-        <v>1.11096632480621</v>
+        <v>1.1109664440155</v>
       </c>
       <c r="H499" t="n">
         <v>12294</v>
@@ -14869,7 +14869,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G500" t="n">
-        <v>1.11096632480621</v>
+        <v>1.1109664440155</v>
       </c>
       <c r="H500" t="n">
         <v>20280</v>
@@ -14985,7 +14985,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G504" t="n">
-        <v>1.11856925487518</v>
+        <v>1.11856913566589</v>
       </c>
       <c r="H504" t="n">
         <v>15643</v>
@@ -15014,7 +15014,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G505" t="n">
-        <v>1.12142014503479</v>
+        <v>1.1214200258255</v>
       </c>
       <c r="H505" t="n">
         <v>4635</v>
@@ -15101,7 +15101,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G508" t="n">
-        <v>1.10431385040283</v>
+        <v>1.10431373119354</v>
       </c>
       <c r="H508" t="n">
         <v>5415</v>
@@ -15130,7 +15130,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G509" t="n">
-        <v>1.11096632480621</v>
+        <v>1.1109664440155</v>
       </c>
       <c r="H509" t="n">
         <v>23824</v>
@@ -15159,7 +15159,7 @@
         <v>1.18299996852875</v>
       </c>
       <c r="G510" t="n">
-        <v>1.12427127361298</v>
+        <v>1.12427115440369</v>
       </c>
       <c r="H510" t="n">
         <v>3049</v>
@@ -15188,7 +15188,7 @@
         <v>1.19099998474121</v>
       </c>
       <c r="G511" t="n">
-        <v>1.13187396526337</v>
+        <v>1.13187408447266</v>
       </c>
       <c r="H511" t="n">
         <v>3108</v>
@@ -15217,7 +15217,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G512" t="n">
-        <v>1.11666834354401</v>
+        <v>1.1166684627533</v>
       </c>
       <c r="H512" t="n">
         <v>19476</v>
@@ -15246,7 +15246,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G513" t="n">
-        <v>1.13092374801636</v>
+        <v>1.13092386722565</v>
       </c>
       <c r="H513" t="n">
         <v>16760</v>
@@ -15275,7 +15275,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G514" t="n">
-        <v>1.13092374801636</v>
+        <v>1.13092386722565</v>
       </c>
       <c r="H514" t="n">
         <v>6300</v>
@@ -15304,7 +15304,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G515" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H515" t="n">
         <v>9430</v>
@@ -15333,7 +15333,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G516" t="n">
-        <v>1.13567554950714</v>
+        <v>1.13567566871643</v>
       </c>
       <c r="H516" t="n">
         <v>47735</v>
@@ -15391,7 +15391,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G518" t="n">
-        <v>1.11666834354401</v>
+        <v>1.1166684627533</v>
       </c>
       <c r="H518" t="n">
         <v>40844</v>
@@ -15739,7 +15739,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G530" t="n">
-        <v>1.11666834354401</v>
+        <v>1.1166684627533</v>
       </c>
       <c r="H530" t="n">
         <v>32447</v>
@@ -15768,7 +15768,7 @@
         <v>1.17999994754791</v>
       </c>
       <c r="G531" t="n">
-        <v>1.12142014503479</v>
+        <v>1.1214200258255</v>
       </c>
       <c r="H531" t="n">
         <v>8000</v>
@@ -15884,7 +15884,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G535" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H535" t="n">
         <v>6800</v>
@@ -15942,7 +15942,7 @@
         <v>1.125</v>
       </c>
       <c r="G537" t="n">
-        <v>1.06915068626404</v>
+        <v>1.06915056705475</v>
       </c>
       <c r="H537" t="n">
         <v>21910</v>
@@ -15971,7 +15971,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G538" t="n">
-        <v>1.0834059715271</v>
+        <v>1.08340585231781</v>
       </c>
       <c r="H538" t="n">
         <v>4582</v>
@@ -16000,7 +16000,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G539" t="n">
-        <v>1.0834059715271</v>
+        <v>1.08340585231781</v>
       </c>
       <c r="H539" t="n">
         <v>29</v>
@@ -16058,7 +16058,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H541" t="n">
         <v>1790</v>
@@ -16145,7 +16145,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G544" t="n">
-        <v>1.05489528179169</v>
+        <v>1.0548951625824</v>
       </c>
       <c r="H544" t="n">
         <v>6655</v>
@@ -16261,7 +16261,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G548" t="n">
-        <v>1.05489528179169</v>
+        <v>1.0548951625824</v>
       </c>
       <c r="H548" t="n">
         <v>1681</v>
@@ -16377,7 +16377,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G552" t="n">
-        <v>1.05489528179169</v>
+        <v>1.0548951625824</v>
       </c>
       <c r="H552" t="n">
         <v>11228</v>
@@ -16464,7 +16464,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G555" t="n">
-        <v>1.05489528179169</v>
+        <v>1.0548951625824</v>
       </c>
       <c r="H555" t="n">
         <v>14301</v>
@@ -16580,7 +16580,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G559" t="n">
-        <v>1.05489528179169</v>
+        <v>1.0548951625824</v>
       </c>
       <c r="H559" t="n">
         <v>4663</v>
@@ -16899,7 +16899,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G570" t="n">
-        <v>1.0834059715271</v>
+        <v>1.08340585231781</v>
       </c>
       <c r="H570" t="n">
         <v>4666</v>
@@ -16928,7 +16928,7 @@
         <v>1.125</v>
       </c>
       <c r="G571" t="n">
-        <v>1.06915068626404</v>
+        <v>1.06915056705475</v>
       </c>
       <c r="H571" t="n">
         <v>7222</v>
@@ -17015,7 +17015,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G574" t="n">
-        <v>1.05489528179169</v>
+        <v>1.0548951625824</v>
       </c>
       <c r="H574" t="n">
         <v>8714</v>
@@ -17044,7 +17044,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G575" t="n">
-        <v>1.05489528179169</v>
+        <v>1.0548951625824</v>
       </c>
       <c r="H575" t="n">
         <v>0</v>
@@ -17073,7 +17073,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G576" t="n">
-        <v>1.05489528179169</v>
+        <v>1.0548951625824</v>
       </c>
       <c r="H576" t="n">
         <v>10450</v>
@@ -17247,7 +17247,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G582" t="n">
-        <v>1.05489528179169</v>
+        <v>1.0548951625824</v>
       </c>
       <c r="H582" t="n">
         <v>6376</v>
@@ -17334,7 +17334,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G585" t="n">
-        <v>1.05489528179169</v>
+        <v>1.0548951625824</v>
       </c>
       <c r="H585" t="n">
         <v>3438</v>
@@ -17450,7 +17450,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G589" t="n">
-        <v>1.05489528179169</v>
+        <v>1.0548951625824</v>
       </c>
       <c r="H589" t="n">
         <v>14000</v>
@@ -17624,7 +17624,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G595" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638483047485</v>
       </c>
       <c r="H595" t="n">
         <v>4500</v>
@@ -17682,7 +17682,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G597" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638483047485</v>
       </c>
       <c r="H597" t="n">
         <v>17100</v>
@@ -17711,7 +17711,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G598" t="n">
-        <v>1.016881108284</v>
+        <v>1.01688098907471</v>
       </c>
       <c r="H598" t="n">
         <v>7224</v>
@@ -17769,7 +17769,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G600" t="n">
-        <v>1.05489528179169</v>
+        <v>1.0548951625824</v>
       </c>
       <c r="H600" t="n">
         <v>18102</v>
@@ -17914,7 +17914,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G605" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638483047485</v>
       </c>
       <c r="H605" t="n">
         <v>4449</v>
@@ -18146,7 +18146,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G613" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866636753082</v>
       </c>
       <c r="H613" t="n">
         <v>16207</v>
@@ -18233,7 +18233,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G616" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866636753082</v>
       </c>
       <c r="H616" t="n">
         <v>10854</v>
@@ -18320,7 +18320,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G619" t="n">
-        <v>0.974115073680878</v>
+        <v>0.974115014076233</v>
       </c>
       <c r="H619" t="n">
         <v>1495</v>
@@ -18349,7 +18349,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G620" t="n">
-        <v>0.974115073680878</v>
+        <v>0.974115014076233</v>
       </c>
       <c r="H620" t="n">
         <v>6029</v>
@@ -18407,7 +18407,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G622" t="n">
-        <v>0.948455333709717</v>
+        <v>0.948455393314362</v>
       </c>
       <c r="H622" t="n">
         <v>10698</v>
@@ -18552,7 +18552,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G627" t="n">
-        <v>0.918044030666351</v>
+        <v>0.918043971061707</v>
       </c>
       <c r="H627" t="n">
         <v>4175</v>
@@ -18639,7 +18639,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G630" t="n">
-        <v>0.948455333709717</v>
+        <v>0.948455393314362</v>
       </c>
       <c r="H630" t="n">
         <v>5204</v>
@@ -18668,7 +18668,7 @@
         <v>0.994000017642975</v>
       </c>
       <c r="G631" t="n">
-        <v>0.944653987884521</v>
+        <v>0.944653928279877</v>
       </c>
       <c r="H631" t="n">
         <v>2000</v>
@@ -18842,7 +18842,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G637" t="n">
-        <v>0.910441160202026</v>
+        <v>0.910441219806671</v>
       </c>
       <c r="H637" t="n">
         <v>7219</v>
@@ -18929,7 +18929,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G640" t="n">
-        <v>0.929448246955872</v>
+        <v>0.929448306560516</v>
       </c>
       <c r="H640" t="n">
         <v>7994</v>
@@ -18958,7 +18958,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G641" t="n">
-        <v>0.929448246955872</v>
+        <v>0.929448306560516</v>
       </c>
       <c r="H641" t="n">
         <v>0</v>
@@ -18987,7 +18987,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G642" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H642" t="n">
         <v>957</v>
@@ -19045,7 +19045,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G644" t="n">
-        <v>0.938951730728149</v>
+        <v>0.938951790332794</v>
       </c>
       <c r="H644" t="n">
         <v>822</v>
@@ -19132,7 +19132,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G647" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H647" t="n">
         <v>767</v>
@@ -19161,7 +19161,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G648" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H648" t="n">
         <v>0</v>
@@ -19219,7 +19219,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G650" t="n">
-        <v>0.895235478878021</v>
+        <v>0.895235419273376</v>
       </c>
       <c r="H650" t="n">
         <v>5923</v>
@@ -19277,7 +19277,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G652" t="n">
-        <v>0.923746109008789</v>
+        <v>0.923746168613434</v>
       </c>
       <c r="H652" t="n">
         <v>3847</v>
@@ -19393,7 +19393,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G656" t="n">
-        <v>0.904739081859589</v>
+        <v>0.904739022254944</v>
       </c>
       <c r="H656" t="n">
         <v>4776</v>
@@ -19654,7 +19654,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G665" t="n">
-        <v>0.910441160202026</v>
+        <v>0.910441219806671</v>
       </c>
       <c r="H665" t="n">
         <v>1224</v>
@@ -19799,7 +19799,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G670" t="n">
-        <v>0.899036824703217</v>
+        <v>0.899036884307861</v>
       </c>
       <c r="H670" t="n">
         <v>1010</v>
@@ -20147,7 +20147,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G682" t="n">
-        <v>0.866724729537964</v>
+        <v>0.866724789142609</v>
       </c>
       <c r="H682" t="n">
         <v>1730</v>
@@ -20176,7 +20176,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G683" t="n">
-        <v>0.868625521659851</v>
+        <v>0.868625462055206</v>
       </c>
       <c r="H683" t="n">
         <v>12885</v>
@@ -20263,7 +20263,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G686" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753195762634</v>
       </c>
       <c r="H686" t="n">
         <v>8065</v>
@@ -20379,7 +20379,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H690" t="n">
         <v>17802</v>
@@ -20437,7 +20437,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G692" t="n">
-        <v>0.904739081859589</v>
+        <v>0.904739022254944</v>
       </c>
       <c r="H692" t="n">
         <v>4862</v>
@@ -20466,7 +20466,7 @@
         <v>0.952000021934509</v>
       </c>
       <c r="G693" t="n">
-        <v>0.904739081859589</v>
+        <v>0.904739022254944</v>
       </c>
       <c r="H693" t="n">
         <v>4465</v>
@@ -20495,7 +20495,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G694" t="n">
-        <v>0.929448246955872</v>
+        <v>0.929448306560516</v>
       </c>
       <c r="H694" t="n">
         <v>5765</v>
@@ -20640,7 +20640,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G699" t="n">
-        <v>0.918044030666351</v>
+        <v>0.918043971061707</v>
       </c>
       <c r="H699" t="n">
         <v>20706</v>
@@ -20669,7 +20669,7 @@
         <v>0.977999985218048</v>
       </c>
       <c r="G700" t="n">
-        <v>0.929448246955872</v>
+        <v>0.929448306560516</v>
       </c>
       <c r="H700" t="n">
         <v>89315</v>
@@ -20785,7 +20785,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H704" t="n">
         <v>10874</v>
@@ -20814,7 +20814,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G705" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H705" t="n">
         <v>4170</v>
@@ -20872,7 +20872,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G707" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H707" t="n">
         <v>7325</v>
@@ -20901,7 +20901,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G708" t="n">
-        <v>0.836313366889954</v>
+        <v>0.836313426494598</v>
       </c>
       <c r="H708" t="n">
         <v>7415</v>
@@ -20959,7 +20959,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G710" t="n">
-        <v>0.826809823513031</v>
+        <v>0.826809763908386</v>
       </c>
       <c r="H710" t="n">
         <v>24474</v>
@@ -20988,7 +20988,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G711" t="n">
-        <v>0.828710556030273</v>
+        <v>0.828710496425629</v>
       </c>
       <c r="H711" t="n">
         <v>1614</v>
@@ -21162,7 +21162,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G717" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H717" t="n">
         <v>14233</v>
@@ -21278,7 +21278,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G721" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H721" t="n">
         <v>770</v>
@@ -21307,7 +21307,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G722" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H722" t="n">
         <v>632</v>
@@ -21336,7 +21336,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G723" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H723" t="n">
         <v>6360</v>
@@ -21365,7 +21365,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G724" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H724" t="n">
         <v>80</v>
@@ -21394,7 +21394,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G725" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H725" t="n">
         <v>1252</v>
@@ -21539,7 +21539,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G730" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H730" t="n">
         <v>3578</v>
@@ -21568,7 +21568,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G731" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H731" t="n">
         <v>6117</v>
@@ -21597,7 +21597,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G732" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H732" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G734" t="n">
-        <v>0.804001271724701</v>
+        <v>0.804001212120056</v>
       </c>
       <c r="H734" t="n">
         <v>15413</v>
@@ -21684,7 +21684,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G735" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H735" t="n">
         <v>10721</v>
@@ -21713,7 +21713,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G736" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391254901886</v>
       </c>
       <c r="H736" t="n">
         <v>1019</v>
@@ -21742,7 +21742,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G737" t="n">
-        <v>0.796398460865021</v>
+        <v>0.796398401260376</v>
       </c>
       <c r="H737" t="n">
         <v>1171</v>
@@ -21829,7 +21829,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G740" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H740" t="n">
         <v>11723</v>
@@ -21858,7 +21858,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G741" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H741" t="n">
         <v>610</v>
@@ -21887,7 +21887,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G742" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H742" t="n">
         <v>5461</v>
@@ -22003,7 +22003,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G746" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H746" t="n">
         <v>1260</v>
@@ -22032,7 +22032,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G747" t="n">
-        <v>0.796398460865021</v>
+        <v>0.796398401260376</v>
       </c>
       <c r="H747" t="n">
         <v>2094</v>
@@ -22264,7 +22264,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G755" t="n">
-        <v>0.798299074172974</v>
+        <v>0.798299133777618</v>
       </c>
       <c r="H755" t="n">
         <v>72</v>
@@ -22293,7 +22293,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G756" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H756" t="n">
         <v>3078</v>
@@ -22322,7 +22322,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G757" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H757" t="n">
         <v>2150</v>
@@ -22351,7 +22351,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G758" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H758" t="n">
         <v>0</v>
@@ -22467,7 +22467,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G762" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H762" t="n">
         <v>10920</v>
@@ -22583,7 +22583,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G766" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H766" t="n">
         <v>1790</v>
@@ -22612,7 +22612,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G767" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H767" t="n">
         <v>2524</v>
@@ -22641,7 +22641,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G768" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H768" t="n">
         <v>10514</v>
@@ -22670,7 +22670,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G769" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H769" t="n">
         <v>16652</v>
@@ -22699,7 +22699,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G770" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H770" t="n">
         <v>9656</v>
@@ -22757,7 +22757,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G772" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H772" t="n">
         <v>3569</v>
@@ -22786,7 +22786,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G773" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H773" t="n">
         <v>12</v>
@@ -22815,7 +22815,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G774" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H774" t="n">
         <v>1400</v>
@@ -22902,7 +22902,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G777" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H777" t="n">
         <v>20</v>
@@ -22989,7 +22989,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G780" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H780" t="n">
         <v>20726</v>
@@ -23018,7 +23018,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G781" t="n">
-        <v>0.918044030666351</v>
+        <v>0.918043971061707</v>
       </c>
       <c r="H781" t="n">
         <v>30874</v>
@@ -23076,7 +23076,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G783" t="n">
-        <v>0.874327600002289</v>
+        <v>0.874327659606934</v>
       </c>
       <c r="H783" t="n">
         <v>8033</v>
@@ -23163,7 +23163,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G786" t="n">
-        <v>0.868625521659851</v>
+        <v>0.868625462055206</v>
       </c>
       <c r="H786" t="n">
         <v>14022</v>
@@ -23250,7 +23250,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G789" t="n">
-        <v>0.874327600002289</v>
+        <v>0.874327659606934</v>
       </c>
       <c r="H789" t="n">
         <v>7232</v>
@@ -23279,7 +23279,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G790" t="n">
-        <v>0.868625521659851</v>
+        <v>0.868625462055206</v>
       </c>
       <c r="H790" t="n">
         <v>14705</v>
@@ -23308,7 +23308,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G791" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H791" t="n">
         <v>46594</v>
@@ -23366,7 +23366,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G793" t="n">
-        <v>0.843916296958923</v>
+        <v>0.843916237354279</v>
       </c>
       <c r="H793" t="n">
         <v>4060</v>
@@ -23453,7 +23453,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G796" t="n">
-        <v>0.819206893444061</v>
+        <v>0.819206953048706</v>
       </c>
       <c r="H796" t="n">
         <v>11904</v>
@@ -23482,7 +23482,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G797" t="n">
-        <v>0.836313366889954</v>
+        <v>0.836313426494598</v>
       </c>
       <c r="H797" t="n">
         <v>319</v>
@@ -23598,7 +23598,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G801" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H801" t="n">
         <v>16877</v>
@@ -23656,7 +23656,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G803" t="n">
-        <v>0.887632668018341</v>
+        <v>0.887632608413696</v>
       </c>
       <c r="H803" t="n">
         <v>44684</v>
@@ -23685,7 +23685,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G804" t="n">
-        <v>0.866724729537964</v>
+        <v>0.866724789142609</v>
       </c>
       <c r="H804" t="n">
         <v>682</v>
@@ -23714,7 +23714,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G805" t="n">
-        <v>0.876228272914886</v>
+        <v>0.876228332519531</v>
       </c>
       <c r="H805" t="n">
         <v>2557</v>
@@ -23772,7 +23772,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G807" t="n">
-        <v>0.868625521659851</v>
+        <v>0.868625462055206</v>
       </c>
       <c r="H807" t="n">
         <v>16010</v>
@@ -23917,7 +23917,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>0.853419840335846</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H812" t="n">
         <v>14750</v>
@@ -24207,7 +24207,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G822" t="n">
-        <v>0.843916296958923</v>
+        <v>0.843916237354279</v>
       </c>
       <c r="H822" t="n">
         <v>11961</v>
@@ -24410,7 +24410,7 @@
         <v>0.912000000476837</v>
       </c>
       <c r="G829" t="n">
-        <v>0.866724729537964</v>
+        <v>0.866724789142609</v>
       </c>
       <c r="H829" t="n">
         <v>22573</v>
@@ -24468,7 +24468,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G831" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H831" t="n">
         <v>22651</v>
@@ -24497,7 +24497,7 @@
         <v>0.921999990940094</v>
       </c>
       <c r="G832" t="n">
-        <v>0.876228272914886</v>
+        <v>0.876228332519531</v>
       </c>
       <c r="H832" t="n">
         <v>10810</v>
@@ -24555,7 +24555,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G834" t="n">
-        <v>0.885731816291809</v>
+        <v>0.885731875896454</v>
       </c>
       <c r="H834" t="n">
         <v>3610</v>
@@ -24729,7 +24729,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G840" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866636753082</v>
       </c>
       <c r="H840" t="n">
         <v>199532</v>
@@ -24816,7 +24816,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G843" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H843" t="n">
         <v>10650</v>
@@ -24874,7 +24874,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G845" t="n">
-        <v>0.98837023973465</v>
+        <v>0.988370358943939</v>
       </c>
       <c r="H845" t="n">
         <v>40133</v>
@@ -24932,7 +24932,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G847" t="n">
-        <v>0.974115073680878</v>
+        <v>0.974115014076233</v>
       </c>
       <c r="H847" t="n">
         <v>18414</v>
@@ -24961,7 +24961,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G848" t="n">
-        <v>0.964611411094666</v>
+        <v>0.96461147069931</v>
       </c>
       <c r="H848" t="n">
         <v>8252</v>
@@ -25019,7 +25019,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G850" t="n">
-        <v>0.938951730728149</v>
+        <v>0.938951790332794</v>
       </c>
       <c r="H850" t="n">
         <v>45709</v>
@@ -25077,7 +25077,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G852" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753195762634</v>
       </c>
       <c r="H852" t="n">
         <v>18857</v>
@@ -25135,7 +25135,7 @@
         <v>0.972000002861023</v>
       </c>
       <c r="G854" t="n">
-        <v>0.923746109008789</v>
+        <v>0.923746168613434</v>
       </c>
       <c r="H854" t="n">
         <v>5073</v>
@@ -25164,7 +25164,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G855" t="n">
-        <v>0.910441160202026</v>
+        <v>0.910441219806671</v>
       </c>
       <c r="H855" t="n">
         <v>5294</v>
@@ -25309,7 +25309,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G860" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H860" t="n">
         <v>74217</v>
@@ -25338,7 +25338,7 @@
         <v>0.998000025749207</v>
       </c>
       <c r="G861" t="n">
-        <v>0.948455333709717</v>
+        <v>0.948455393314362</v>
       </c>
       <c r="H861" t="n">
         <v>21200</v>
@@ -25483,7 +25483,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G866" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H866" t="n">
         <v>19486</v>
@@ -25570,7 +25570,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G869" t="n">
-        <v>0.887632668018341</v>
+        <v>0.887632608413696</v>
       </c>
       <c r="H869" t="n">
         <v>6207</v>
@@ -25599,7 +25599,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G870" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H870" t="n">
         <v>11502</v>
@@ -25628,7 +25628,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G871" t="n">
-        <v>0.895235478878021</v>
+        <v>0.895235419273376</v>
       </c>
       <c r="H871" t="n">
         <v>11</v>
@@ -25686,7 +25686,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G873" t="n">
-        <v>0.885731816291809</v>
+        <v>0.885731875896454</v>
       </c>
       <c r="H873" t="n">
         <v>2011</v>
@@ -25715,7 +25715,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G874" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H874" t="n">
         <v>1274</v>
@@ -25744,7 +25744,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G875" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H875" t="n">
         <v>2508</v>
@@ -25773,7 +25773,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G876" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H876" t="n">
         <v>2701</v>
@@ -25802,7 +25802,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G877" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H877" t="n">
         <v>5064</v>
@@ -25889,7 +25889,7 @@
         <v>0.920000016689301</v>
       </c>
       <c r="G880" t="n">
-        <v>0.874327600002289</v>
+        <v>0.874327659606934</v>
       </c>
       <c r="H880" t="n">
         <v>27077</v>
@@ -26063,7 +26063,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G886" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H886" t="n">
         <v>11911</v>
@@ -26324,7 +26324,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G895" t="n">
-        <v>0.849618315696716</v>
+        <v>0.849618375301361</v>
       </c>
       <c r="H895" t="n">
         <v>1766</v>
@@ -26353,7 +26353,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G896" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H896" t="n">
         <v>2121</v>
@@ -26382,7 +26382,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G897" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H897" t="n">
         <v>5200</v>
@@ -26411,7 +26411,7 @@
         <v>0.913999974727631</v>
       </c>
       <c r="G898" t="n">
-        <v>0.868625521659851</v>
+        <v>0.868625462055206</v>
       </c>
       <c r="H898" t="n">
         <v>30729</v>
@@ -26527,7 +26527,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G902" t="n">
-        <v>0.853419840335846</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H902" t="n">
         <v>2624</v>
@@ -26556,7 +26556,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G903" t="n">
-        <v>0.836313366889954</v>
+        <v>0.836313426494598</v>
       </c>
       <c r="H903" t="n">
         <v>1946</v>
@@ -26585,7 +26585,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G904" t="n">
-        <v>0.853419840335846</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H904" t="n">
         <v>1651</v>
@@ -26643,7 +26643,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G906" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H906" t="n">
         <v>10749</v>
@@ -26672,7 +26672,7 @@
         <v>0.898000001907349</v>
       </c>
       <c r="G907" t="n">
-        <v>0.853419840335846</v>
+        <v>0.853419780731201</v>
       </c>
       <c r="H907" t="n">
         <v>10040</v>
@@ -26904,7 +26904,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G915" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H915" t="n">
         <v>201</v>
@@ -26933,7 +26933,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G916" t="n">
-        <v>0.849618315696716</v>
+        <v>0.849618375301361</v>
       </c>
       <c r="H916" t="n">
         <v>4611</v>
@@ -26962,7 +26962,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G917" t="n">
-        <v>0.849618315696716</v>
+        <v>0.849618375301361</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G918" t="n">
-        <v>0.849618315696716</v>
+        <v>0.849618375301361</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -27165,7 +27165,7 @@
         <v>0.934000015258789</v>
       </c>
       <c r="G924" t="n">
-        <v>0.887632668018341</v>
+        <v>0.887632608413696</v>
       </c>
       <c r="H924" t="n">
         <v>33700</v>
@@ -27223,7 +27223,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G926" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H926" t="n">
         <v>260416</v>
@@ -27281,7 +27281,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G928" t="n">
-        <v>0.885731816291809</v>
+        <v>0.885731875896454</v>
       </c>
       <c r="H928" t="n">
         <v>6532</v>
@@ -27310,7 +27310,7 @@
         <v>0.931999981403351</v>
       </c>
       <c r="G929" t="n">
-        <v>0.885731816291809</v>
+        <v>0.885731875896454</v>
       </c>
       <c r="H929" t="n">
         <v>13529</v>
@@ -27397,7 +27397,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G932" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753195762634</v>
       </c>
       <c r="H932" t="n">
         <v>68362</v>
@@ -27542,7 +27542,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G937" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753195762634</v>
       </c>
       <c r="H937" t="n">
         <v>19326</v>
@@ -27571,7 +27571,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G938" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H938" t="n">
         <v>17014</v>
@@ -27658,7 +27658,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G941" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H941" t="n">
         <v>32693</v>
@@ -27774,7 +27774,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G945" t="n">
-        <v>0.895235478878021</v>
+        <v>0.895235419273376</v>
       </c>
       <c r="H945" t="n">
         <v>2460</v>
@@ -27803,7 +27803,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G946" t="n">
-        <v>0.98837023973465</v>
+        <v>0.988370358943939</v>
       </c>
       <c r="H946" t="n">
         <v>175676</v>
@@ -27861,7 +27861,7 @@
         <v>0.976000010967255</v>
       </c>
       <c r="G948" t="n">
-        <v>0.927547574043274</v>
+        <v>0.927547514438629</v>
       </c>
       <c r="H948" t="n">
         <v>21307</v>
@@ -27977,7 +27977,7 @@
         <v>0.991999983787537</v>
       </c>
       <c r="G952" t="n">
-        <v>0.942753255367279</v>
+        <v>0.942753195762634</v>
       </c>
       <c r="H952" t="n">
         <v>16989</v>
@@ -28035,7 +28035,7 @@
         <v>0.958000004291534</v>
       </c>
       <c r="G954" t="n">
-        <v>0.910441160202026</v>
+        <v>0.910441219806671</v>
       </c>
       <c r="H954" t="n">
         <v>12902</v>
@@ -28064,7 +28064,7 @@
         <v>0.966000020503998</v>
       </c>
       <c r="G955" t="n">
-        <v>0.918044030666351</v>
+        <v>0.918043971061707</v>
       </c>
       <c r="H955" t="n">
         <v>22612</v>
@@ -28180,7 +28180,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G959" t="n">
-        <v>0.899036824703217</v>
+        <v>0.899036884307861</v>
       </c>
       <c r="H959" t="n">
         <v>31567</v>
@@ -28296,7 +28296,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G963" t="n">
-        <v>0.895235478878021</v>
+        <v>0.895235419273376</v>
       </c>
       <c r="H963" t="n">
         <v>34081</v>
@@ -28412,7 +28412,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G967" t="n">
-        <v>0.899036824703217</v>
+        <v>0.899036884307861</v>
       </c>
       <c r="H967" t="n">
         <v>19223</v>
@@ -28441,7 +28441,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G968" t="n">
-        <v>0.899036824703217</v>
+        <v>0.899036884307861</v>
       </c>
       <c r="H968" t="n">
         <v>2280</v>
@@ -28499,7 +28499,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G970" t="n">
-        <v>0.899036824703217</v>
+        <v>0.899036884307861</v>
       </c>
       <c r="H970" t="n">
         <v>9218</v>
@@ -28528,7 +28528,7 @@
         <v>0.935999989509583</v>
       </c>
       <c r="G971" t="n">
-        <v>0.889533281326294</v>
+        <v>0.889533340930939</v>
       </c>
       <c r="H971" t="n">
         <v>3011</v>
@@ -28557,7 +28557,7 @@
         <v>0.945999979972839</v>
       </c>
       <c r="G972" t="n">
-        <v>0.899036824703217</v>
+        <v>0.899036884307861</v>
       </c>
       <c r="H972" t="n">
         <v>680</v>
@@ -28586,7 +28586,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G973" t="n">
-        <v>0.895235478878021</v>
+        <v>0.895235419273376</v>
       </c>
       <c r="H973" t="n">
         <v>8924</v>
@@ -28615,7 +28615,7 @@
         <v>0.941999971866608</v>
       </c>
       <c r="G974" t="n">
-        <v>0.895235478878021</v>
+        <v>0.895235419273376</v>
       </c>
       <c r="H974" t="n">
         <v>5067</v>
@@ -28644,7 +28644,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G975" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866636753082</v>
       </c>
       <c r="H975" t="n">
         <v>218368</v>
@@ -28702,7 +28702,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G977" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H977" t="n">
         <v>11890</v>
@@ -28731,7 +28731,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G978" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866636753082</v>
       </c>
       <c r="H978" t="n">
         <v>33171</v>
@@ -28818,7 +28818,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G981" t="n">
-        <v>0.993122100830078</v>
+        <v>0.993121981620789</v>
       </c>
       <c r="H981" t="n">
         <v>192780</v>
@@ -28847,7 +28847,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G982" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H982" t="n">
         <v>30123</v>
@@ -28876,7 +28876,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G983" t="n">
-        <v>0.974115073680878</v>
+        <v>0.974115014076233</v>
       </c>
       <c r="H983" t="n">
         <v>7760</v>
@@ -28905,7 +28905,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G984" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H984" t="n">
         <v>29319</v>
@@ -28963,7 +28963,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G986" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H986" t="n">
         <v>34613</v>
@@ -28992,7 +28992,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G987" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H987" t="n">
         <v>7153</v>
@@ -29021,7 +29021,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G988" t="n">
-        <v>0.974115073680878</v>
+        <v>0.974115014076233</v>
       </c>
       <c r="H988" t="n">
         <v>10066</v>
@@ -29137,7 +29137,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H992" t="n">
         <v>10082</v>
@@ -29166,7 +29166,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G993" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H993" t="n">
         <v>5731</v>
@@ -29195,7 +29195,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G994" t="n">
-        <v>0.964611411094666</v>
+        <v>0.96461147069931</v>
       </c>
       <c r="H994" t="n">
         <v>2711</v>
@@ -29224,7 +29224,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G995" t="n">
-        <v>0.964611411094666</v>
+        <v>0.96461147069931</v>
       </c>
       <c r="H995" t="n">
         <v>16059</v>
@@ -29253,7 +29253,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G996" t="n">
-        <v>0.983618497848511</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H996" t="n">
         <v>106619</v>
@@ -29282,7 +29282,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G997" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866636753082</v>
       </c>
       <c r="H997" t="n">
         <v>4524</v>
@@ -29311,7 +29311,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G998" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866636753082</v>
       </c>
       <c r="H998" t="n">
         <v>19085</v>
@@ -29340,7 +29340,7 @@
         <v>1.01499998569489</v>
       </c>
       <c r="G999" t="n">
-        <v>0.964611411094666</v>
+        <v>0.96461147069931</v>
       </c>
       <c r="H999" t="n">
         <v>93021</v>
@@ -29369,7 +29369,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1000" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H1000" t="n">
         <v>13855</v>
@@ -29398,7 +29398,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.974115073680878</v>
+        <v>0.974115014076233</v>
       </c>
       <c r="H1001" t="n">
         <v>8205</v>
@@ -29427,7 +29427,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1002" t="n">
-        <v>0.983618497848511</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H1002" t="n">
         <v>25401</v>
@@ -29572,7 +29572,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.05489528179169</v>
+        <v>1.0548951625824</v>
       </c>
       <c r="H1007" t="n">
         <v>9620</v>
@@ -29775,7 +29775,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.02638459205627</v>
+        <v>1.02638483047485</v>
       </c>
       <c r="H1014" t="n">
         <v>4819</v>
@@ -29891,7 +29891,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.016881108284</v>
+        <v>1.01688098907471</v>
       </c>
       <c r="H1018" t="n">
         <v>9804</v>
@@ -30007,7 +30007,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1022" t="n">
-        <v>0.98837023973465</v>
+        <v>0.988370358943939</v>
       </c>
       <c r="H1022" t="n">
         <v>30056</v>
@@ -30036,7 +30036,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1023" t="n">
-        <v>0.983618497848511</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H1023" t="n">
         <v>17131</v>
@@ -30123,7 +30123,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866636753082</v>
       </c>
       <c r="H1026" t="n">
         <v>14290</v>
@@ -30152,7 +30152,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1027" t="n">
-        <v>0.993122100830078</v>
+        <v>0.993121981620789</v>
       </c>
       <c r="H1027" t="n">
         <v>28649</v>
@@ -30181,7 +30181,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1028" t="n">
-        <v>0.993122100830078</v>
+        <v>0.993121981620789</v>
       </c>
       <c r="H1028" t="n">
         <v>20606</v>
@@ -30297,7 +30297,7 @@
         <v>1.04499995708466</v>
       </c>
       <c r="G1032" t="n">
-        <v>0.993122100830078</v>
+        <v>0.993121981620789</v>
       </c>
       <c r="H1032" t="n">
         <v>93979</v>
@@ -30326,7 +30326,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G1033" t="n">
-        <v>0.969363212585449</v>
+        <v>0.969363152980804</v>
       </c>
       <c r="H1033" t="n">
         <v>51868</v>
@@ -30355,7 +30355,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>0.98837023973465</v>
+        <v>0.988370358943939</v>
       </c>
       <c r="H1034" t="n">
         <v>57336</v>
@@ -30442,7 +30442,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.016881108284</v>
+        <v>1.01688098907471</v>
       </c>
       <c r="H1037" t="n">
         <v>180549</v>
@@ -30616,7 +30616,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.0834059715271</v>
+        <v>1.08340585231781</v>
       </c>
       <c r="H1043" t="n">
         <v>139130</v>
@@ -30645,7 +30645,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H1044" t="n">
         <v>40158</v>
@@ -30790,7 +30790,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.08815765380859</v>
+        <v>1.08815777301788</v>
       </c>
       <c r="H1049" t="n">
         <v>122643</v>
@@ -30848,7 +30848,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.05489528179169</v>
+        <v>1.0548951625824</v>
       </c>
       <c r="H1051" t="n">
         <v>89835</v>
@@ -30906,7 +30906,7 @@
         <v>1.0349999666214</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.983618497848511</v>
+        <v>0.983618557453156</v>
       </c>
       <c r="H1053" t="n">
         <v>115588</v>
@@ -30964,7 +30964,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.974115073680878</v>
+        <v>0.974115014076233</v>
       </c>
       <c r="H1055" t="n">
         <v>11641</v>
@@ -30993,7 +30993,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1056" t="n">
-        <v>0.978866815567017</v>
+        <v>0.978866636753082</v>
       </c>
       <c r="H1056" t="n">
         <v>34580</v>
@@ -31080,7 +31080,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1059" t="n">
-        <v>0.938951730728149</v>
+        <v>0.938951790332794</v>
       </c>
       <c r="H1059" t="n">
         <v>19870</v>
@@ -31196,7 +31196,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1063" t="n">
         <v>26146</v>
@@ -31225,7 +31225,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.826809823513031</v>
+        <v>0.826809763908386</v>
       </c>
       <c r="H1064" t="n">
         <v>25040</v>
@@ -31254,7 +31254,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1065" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H1065" t="n">
         <v>8706</v>
@@ -31312,7 +31312,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.819206893444061</v>
+        <v>0.819206953048706</v>
       </c>
       <c r="H1067" t="n">
         <v>22955</v>
@@ -31428,7 +31428,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.826809823513031</v>
+        <v>0.826809763908386</v>
       </c>
       <c r="H1071" t="n">
         <v>3693</v>
@@ -31457,7 +31457,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.836313366889954</v>
+        <v>0.836313426494598</v>
       </c>
       <c r="H1072" t="n">
         <v>10166</v>
@@ -31486,7 +31486,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H1073" t="n">
         <v>22248</v>
@@ -31544,7 +31544,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1075" t="n">
-        <v>0.826809823513031</v>
+        <v>0.826809763908386</v>
       </c>
       <c r="H1075" t="n">
         <v>44457</v>
@@ -31660,7 +31660,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.836313366889954</v>
+        <v>0.836313426494598</v>
       </c>
       <c r="H1079" t="n">
         <v>54931</v>
@@ -31805,7 +31805,7 @@
         <v>0.916000008583069</v>
       </c>
       <c r="G1084" t="n">
-        <v>0.870526194572449</v>
+        <v>0.870526134967804</v>
       </c>
       <c r="H1084" t="n">
         <v>14829</v>
@@ -31834,7 +31834,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H1085" t="n">
         <v>17000</v>
@@ -32037,7 +32037,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1092" t="n">
         <v>52209</v>
@@ -32095,7 +32095,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.804001271724701</v>
+        <v>0.804001212120056</v>
       </c>
       <c r="H1094" t="n">
         <v>1012</v>
@@ -32124,7 +32124,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.804001271724701</v>
+        <v>0.804001212120056</v>
       </c>
       <c r="H1095" t="n">
         <v>271</v>
@@ -32269,7 +32269,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.819206893444061</v>
+        <v>0.819206953048706</v>
       </c>
       <c r="H1100" t="n">
         <v>28856</v>
@@ -32385,7 +32385,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.813504874706268</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1104" t="n">
         <v>5636</v>
@@ -32501,7 +32501,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.805901944637299</v>
+        <v>0.805902004241943</v>
       </c>
       <c r="H1108" t="n">
         <v>23576</v>
@@ -32530,7 +32530,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.819206893444061</v>
+        <v>0.819206953048706</v>
       </c>
       <c r="H1109" t="n">
         <v>7100</v>
@@ -32791,7 +32791,7 @@
         <v>0.870000004768372</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.826809823513031</v>
+        <v>0.826809763908386</v>
       </c>
       <c r="H1118" t="n">
         <v>6758</v>
@@ -32878,7 +32878,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.836313366889954</v>
+        <v>0.836313426494598</v>
       </c>
       <c r="H1121" t="n">
         <v>545</v>
@@ -32907,7 +32907,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1122" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H1122" t="n">
         <v>28335</v>
@@ -32965,7 +32965,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.849618315696716</v>
+        <v>0.849618375301361</v>
       </c>
       <c r="H1124" t="n">
         <v>8344</v>
@@ -33081,7 +33081,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1128" t="n">
-        <v>0.819206893444061</v>
+        <v>0.819206953048706</v>
       </c>
       <c r="H1128" t="n">
         <v>3729</v>
@@ -33110,7 +33110,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.849618315696716</v>
+        <v>0.849618375301361</v>
       </c>
       <c r="H1129" t="n">
         <v>13547</v>
@@ -33139,7 +33139,7 @@
         <v>0.888000011444092</v>
       </c>
       <c r="G1130" t="n">
-        <v>0.843916296958923</v>
+        <v>0.843916237354279</v>
       </c>
       <c r="H1130" t="n">
         <v>1300</v>
@@ -33168,7 +33168,7 @@
         <v>0.896000027656555</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.851519107818604</v>
+        <v>0.851519048213959</v>
       </c>
       <c r="H1131" t="n">
         <v>54987</v>
@@ -33197,7 +33197,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.849618315696716</v>
+        <v>0.849618375301361</v>
       </c>
       <c r="H1132" t="n">
         <v>15701</v>
@@ -33226,7 +33226,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1133" t="n">
-        <v>0.828710556030273</v>
+        <v>0.828710496425629</v>
       </c>
       <c r="H1133" t="n">
         <v>12</v>
@@ -33545,7 +33545,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.828710556030273</v>
+        <v>0.828710496425629</v>
       </c>
       <c r="H1144" t="n">
         <v>3310</v>
@@ -33574,7 +33574,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.828710556030273</v>
+        <v>0.828710496425629</v>
       </c>
       <c r="H1145" t="n">
         <v>0</v>
@@ -33603,7 +33603,7 @@
         <v>0.871999979019165</v>
       </c>
       <c r="G1146" t="n">
-        <v>0.828710556030273</v>
+        <v>0.828710496425629</v>
       </c>
       <c r="H1146" t="n">
         <v>65</v>
@@ -33661,7 +33661,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1148" t="n">
-        <v>0.836313366889954</v>
+        <v>0.836313426494598</v>
       </c>
       <c r="H1148" t="n">
         <v>1242</v>
@@ -33719,7 +33719,7 @@
         <v>0.893999993801117</v>
       </c>
       <c r="G1150" t="n">
-        <v>0.849618315696716</v>
+        <v>0.849618375301361</v>
       </c>
       <c r="H1150" t="n">
         <v>1598</v>
@@ -33777,7 +33777,7 @@
         <v>0.879999995231628</v>
       </c>
       <c r="G1152" t="n">
-        <v>0.836313366889954</v>
+        <v>0.836313426494598</v>
       </c>
       <c r="H1152" t="n">
         <v>3507</v>
@@ -33864,7 +33864,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.824909031391144</v>
+        <v>0.824909090995789</v>
       </c>
       <c r="H1155" t="n">
         <v>805</v>
@@ -33893,7 +33893,7 @@
         <v>0.867999970912933</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.824909031391144</v>
+        <v>0.824909090995789</v>
       </c>
       <c r="H1156" t="n">
         <v>52496</v>
@@ -33922,7 +33922,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.813504874706268</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1157" t="n">
         <v>1157</v>
@@ -33980,7 +33980,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1159" t="n">
         <v>57439</v>
@@ -34038,7 +34038,7 @@
         <v>0.861999988555908</v>
       </c>
       <c r="G1161" t="n">
-        <v>0.819206893444061</v>
+        <v>0.819206953048706</v>
       </c>
       <c r="H1161" t="n">
         <v>20870</v>
@@ -34067,7 +34067,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.804001271724701</v>
+        <v>0.804001212120056</v>
       </c>
       <c r="H1162" t="n">
         <v>25013</v>
@@ -34125,7 +34125,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1164" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1164" t="n">
         <v>154</v>
@@ -34154,7 +34154,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.798299074172974</v>
+        <v>0.798299133777618</v>
       </c>
       <c r="H1165" t="n">
         <v>20</v>
@@ -34183,7 +34183,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.805901944637299</v>
+        <v>0.805902004241943</v>
       </c>
       <c r="H1166" t="n">
         <v>2124</v>
@@ -34212,7 +34212,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1167" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1167" t="n">
         <v>5059</v>
@@ -34241,7 +34241,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H1168" t="n">
         <v>2588</v>
@@ -34270,7 +34270,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1169" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1169" t="n">
         <v>1446</v>
@@ -34357,7 +34357,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.813504874706268</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1172" t="n">
         <v>1500</v>
@@ -34386,7 +34386,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.813504874706268</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1173" t="n">
         <v>0</v>
@@ -34415,7 +34415,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.813504874706268</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1174" t="n">
         <v>0</v>
@@ -34444,7 +34444,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1175" t="n">
-        <v>0.813504874706268</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1175" t="n">
         <v>0</v>
@@ -34473,7 +34473,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.811604082584381</v>
+        <v>0.811604142189026</v>
       </c>
       <c r="H1176" t="n">
         <v>1005</v>
@@ -34502,7 +34502,7 @@
         <v>0.853999972343445</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.811604082584381</v>
+        <v>0.811604142189026</v>
       </c>
       <c r="H1177" t="n">
         <v>0</v>
@@ -34531,7 +34531,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1178" t="n">
         <v>1540</v>
@@ -34560,7 +34560,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1179" t="n">
         <v>0</v>
@@ -34647,7 +34647,7 @@
         <v>0.846000015735626</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.804001271724701</v>
+        <v>0.804001212120056</v>
       </c>
       <c r="H1182" t="n">
         <v>10</v>
@@ -34676,7 +34676,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.775490522384644</v>
+        <v>0.775490581989288</v>
       </c>
       <c r="H1183" t="n">
         <v>3161</v>
@@ -34763,7 +34763,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.805901944637299</v>
+        <v>0.805902004241943</v>
       </c>
       <c r="H1186" t="n">
         <v>4330</v>
@@ -34850,7 +34850,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1189" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1189" t="n">
         <v>1063</v>
@@ -34879,7 +34879,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1190" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1190" t="n">
         <v>4195</v>
@@ -34908,7 +34908,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1191" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1191" t="n">
         <v>10276</v>
@@ -34937,7 +34937,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1192" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391254901886</v>
       </c>
       <c r="H1192" t="n">
         <v>11693</v>
@@ -34966,7 +34966,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391254901886</v>
       </c>
       <c r="H1193" t="n">
         <v>0</v>
@@ -34995,7 +34995,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1194" t="n">
         <v>6350</v>
@@ -35024,7 +35024,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1195" t="n">
         <v>2689</v>
@@ -35082,7 +35082,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H1197" t="n">
         <v>14658</v>
@@ -35140,7 +35140,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.805901944637299</v>
+        <v>0.805902004241943</v>
       </c>
       <c r="H1199" t="n">
         <v>7747</v>
@@ -35169,7 +35169,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1200" t="n">
         <v>4016</v>
@@ -35285,7 +35285,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1204" t="n">
-        <v>0.805901944637299</v>
+        <v>0.805902004241943</v>
       </c>
       <c r="H1204" t="n">
         <v>1326</v>
@@ -35401,7 +35401,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1208" t="n">
         <v>1034</v>
@@ -35430,7 +35430,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1209" t="n">
         <v>0</v>
@@ -35459,7 +35459,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1210" t="n">
-        <v>0.798299074172974</v>
+        <v>0.798299133777618</v>
       </c>
       <c r="H1210" t="n">
         <v>252</v>
@@ -35517,7 +35517,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.796398460865021</v>
+        <v>0.796398401260376</v>
       </c>
       <c r="H1212" t="n">
         <v>45975</v>
@@ -35546,7 +35546,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391254901886</v>
       </c>
       <c r="H1213" t="n">
         <v>19225</v>
@@ -35691,7 +35691,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1218" t="n">
         <v>13790</v>
@@ -35749,7 +35749,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752681970596313</v>
       </c>
       <c r="H1220" t="n">
         <v>18729</v>
@@ -35778,7 +35778,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752681970596313</v>
       </c>
       <c r="H1221" t="n">
         <v>5763</v>
@@ -35807,7 +35807,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1222" t="n">
         <v>9255</v>
@@ -35923,7 +35923,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.665249288082123</v>
+        <v>0.665249228477478</v>
       </c>
       <c r="H1226" t="n">
         <v>2220</v>
@@ -35952,7 +35952,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1227" t="n">
-        <v>0.693759977817535</v>
+        <v>0.69376003742218</v>
       </c>
       <c r="H1227" t="n">
         <v>10514</v>
@@ -35981,7 +35981,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.69756144285202</v>
+        <v>0.697561383247375</v>
       </c>
       <c r="H1228" t="n">
         <v>3123</v>
@@ -36010,7 +36010,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.689958572387695</v>
+        <v>0.689958512783051</v>
       </c>
       <c r="H1229" t="n">
         <v>1200</v>
@@ -36039,7 +36039,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.69756144285202</v>
+        <v>0.697561383247375</v>
       </c>
       <c r="H1230" t="n">
         <v>2138</v>
@@ -36068,7 +36068,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1231" t="n">
-        <v>0.69756144285202</v>
+        <v>0.697561383247375</v>
       </c>
       <c r="H1231" t="n">
         <v>5454</v>
@@ -36126,7 +36126,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1233" t="n">
-        <v>0.701362729072571</v>
+        <v>0.701362788677216</v>
       </c>
       <c r="H1233" t="n">
         <v>2151</v>
@@ -36213,7 +36213,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1236" t="n">
         <v>4134</v>
@@ -36271,7 +36271,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1238" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391254901886</v>
       </c>
       <c r="H1238" t="n">
         <v>13935</v>
@@ -36300,7 +36300,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1239" t="n">
         <v>32699</v>
@@ -36329,7 +36329,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1240" t="n">
         <v>9919</v>
@@ -36503,7 +36503,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1246" t="n">
         <v>16700</v>
@@ -36619,7 +36619,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1250" t="n">
-        <v>0.758384108543396</v>
+        <v>0.758384168148041</v>
       </c>
       <c r="H1250" t="n">
         <v>6647</v>
@@ -36648,7 +36648,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.754582822322845</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1251" t="n">
         <v>2313</v>
@@ -36677,7 +36677,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1252" t="n">
-        <v>0.758384108543396</v>
+        <v>0.758384168148041</v>
       </c>
       <c r="H1252" t="n">
         <v>7654</v>
@@ -36735,7 +36735,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1254" t="n">
-        <v>0.754582822322845</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1254" t="n">
         <v>2276</v>
@@ -36793,7 +36793,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1256" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1256" t="n">
         <v>2562</v>
@@ -36822,7 +36822,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.775490522384644</v>
+        <v>0.775490581989288</v>
       </c>
       <c r="H1257" t="n">
         <v>15595</v>
@@ -36851,7 +36851,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1258" t="n">
         <v>913</v>
@@ -36880,7 +36880,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1259" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1259" t="n">
         <v>25666</v>
@@ -36909,7 +36909,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1260" t="n">
         <v>38619</v>
@@ -36938,7 +36938,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1261" t="n">
         <v>1406</v>
@@ -36996,7 +36996,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1263" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1263" t="n">
         <v>2463</v>
@@ -37083,7 +37083,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1266" t="n">
         <v>3759</v>
@@ -37112,7 +37112,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1267" t="n">
         <v>0</v>
@@ -37170,7 +37170,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1269" t="n">
         <v>14270</v>
@@ -37199,7 +37199,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.758384108543396</v>
+        <v>0.758384168148041</v>
       </c>
       <c r="H1270" t="n">
         <v>8817</v>
@@ -37373,7 +37373,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1276" t="n">
         <v>26285</v>
@@ -37808,7 +37808,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1291" t="n">
         <v>10</v>
@@ -37837,7 +37837,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.720369875431061</v>
+        <v>0.720369935035706</v>
       </c>
       <c r="H1292" t="n">
         <v>33828</v>
@@ -37895,7 +37895,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1294" t="n">
         <v>30046</v>
@@ -38011,7 +38011,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.805901944637299</v>
+        <v>0.805902004241943</v>
       </c>
       <c r="H1298" t="n">
         <v>111797</v>
@@ -38214,7 +38214,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1305" t="n">
         <v>13544</v>
@@ -38272,7 +38272,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1307" t="n">
-        <v>0.796398460865021</v>
+        <v>0.796398401260376</v>
       </c>
       <c r="H1307" t="n">
         <v>12752</v>
@@ -38301,7 +38301,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1308" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1308" t="n">
         <v>10678</v>
@@ -38359,7 +38359,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1310" t="n">
         <v>77093</v>
@@ -38388,7 +38388,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H1311" t="n">
         <v>3023</v>
@@ -38417,7 +38417,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1312" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1312" t="n">
         <v>5581</v>
@@ -38446,7 +38446,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1313" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1313" t="n">
         <v>16652</v>
@@ -38475,7 +38475,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1314" t="n">
         <v>990</v>
@@ -38504,7 +38504,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1315" t="n">
         <v>0</v>
@@ -38562,7 +38562,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1317" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1317" t="n">
         <v>10278</v>
@@ -38591,7 +38591,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.758384108543396</v>
+        <v>0.758384168148041</v>
       </c>
       <c r="H1318" t="n">
         <v>14877</v>
@@ -38620,7 +38620,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1319" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752681970596313</v>
       </c>
       <c r="H1319" t="n">
         <v>44851</v>
@@ -38649,7 +38649,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1320" t="n">
-        <v>0.754582822322845</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1320" t="n">
         <v>37453</v>
@@ -38707,7 +38707,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1322" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1322" t="n">
         <v>6424</v>
@@ -38736,7 +38736,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1323" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1323" t="n">
         <v>7011</v>
@@ -38823,7 +38823,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1326" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1326" t="n">
         <v>4013</v>
@@ -38852,7 +38852,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1327" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1327" t="n">
         <v>2313</v>
@@ -38910,7 +38910,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1329" t="n">
-        <v>0.754582822322845</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1329" t="n">
         <v>143</v>
@@ -38939,7 +38939,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1330" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1330" t="n">
         <v>9538</v>
@@ -38997,7 +38997,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391254901886</v>
       </c>
       <c r="H1332" t="n">
         <v>36760</v>
@@ -39026,7 +39026,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391254901886</v>
       </c>
       <c r="H1333" t="n">
         <v>3523</v>
@@ -39055,7 +39055,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1334" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1334" t="n">
         <v>5578</v>
@@ -39113,7 +39113,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1336" t="n">
         <v>31378</v>
@@ -39142,7 +39142,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.775490522384644</v>
+        <v>0.775490581989288</v>
       </c>
       <c r="H1337" t="n">
         <v>36262</v>
@@ -39200,7 +39200,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.754582822322845</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1339" t="n">
         <v>5953</v>
@@ -39345,7 +39345,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1344" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1344" t="n">
         <v>16127</v>
@@ -39461,7 +39461,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1348" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1348" t="n">
         <v>169972</v>
@@ -39490,7 +39490,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1349" t="n">
         <v>16898</v>
@@ -39548,7 +39548,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1351" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1351" t="n">
         <v>38622</v>
@@ -39635,7 +39635,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1354" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752681970596313</v>
       </c>
       <c r="H1354" t="n">
         <v>45133</v>
@@ -39664,7 +39664,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1355" t="n">
-        <v>0.754582822322845</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1355" t="n">
         <v>24882</v>
@@ -39693,7 +39693,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1356" t="n">
         <v>34806</v>
@@ -39780,7 +39780,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1359" t="n">
-        <v>0.722270607948303</v>
+        <v>0.722270548343658</v>
       </c>
       <c r="H1359" t="n">
         <v>24873</v>
@@ -39838,7 +39838,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1361" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1361" t="n">
         <v>7927</v>
@@ -39896,7 +39896,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1363" t="n">
         <v>10616</v>
@@ -40099,7 +40099,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1370" t="n">
         <v>7560</v>
@@ -40128,7 +40128,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1371" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1371" t="n">
         <v>16407</v>
@@ -40186,7 +40186,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1373" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1373" t="n">
         <v>84131</v>
@@ -40215,7 +40215,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1374" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1374" t="n">
         <v>9611</v>
@@ -40244,7 +40244,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1375" t="n">
         <v>119857</v>
@@ -40273,7 +40273,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1376" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1376" t="n">
         <v>151700</v>
@@ -40389,7 +40389,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1380" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1380" t="n">
         <v>85030</v>
@@ -40418,7 +40418,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1381" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1381" t="n">
         <v>85408</v>
@@ -40447,7 +40447,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1382" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1382" t="n">
         <v>47262</v>
@@ -40476,7 +40476,7 @@
         <v>0.84799998998642</v>
       </c>
       <c r="G1383" t="n">
-        <v>0.805901944637299</v>
+        <v>0.805902004241943</v>
       </c>
       <c r="H1383" t="n">
         <v>284246</v>
@@ -40650,7 +40650,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.813504874706268</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1389" t="n">
         <v>86617</v>
@@ -40679,7 +40679,7 @@
         <v>0.856000006198883</v>
       </c>
       <c r="G1390" t="n">
-        <v>0.813504874706268</v>
+        <v>0.813504755496979</v>
       </c>
       <c r="H1390" t="n">
         <v>44133</v>
@@ -40708,7 +40708,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.798299074172974</v>
+        <v>0.798299133777618</v>
       </c>
       <c r="H1391" t="n">
         <v>25564</v>
@@ -40737,7 +40737,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1392" t="n">
-        <v>0.796398460865021</v>
+        <v>0.796398401260376</v>
       </c>
       <c r="H1392" t="n">
         <v>32493</v>
@@ -40795,7 +40795,7 @@
         <v>0.839999973773956</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.798299074172974</v>
+        <v>0.798299133777618</v>
       </c>
       <c r="H1394" t="n">
         <v>26614</v>
@@ -40824,7 +40824,7 @@
         <v>0.825999975204468</v>
       </c>
       <c r="G1395" t="n">
-        <v>0.784994065761566</v>
+        <v>0.784994125366211</v>
       </c>
       <c r="H1395" t="n">
         <v>26723</v>
@@ -40853,7 +40853,7 @@
         <v>0.836000025272369</v>
       </c>
       <c r="G1396" t="n">
-        <v>0.794497668743134</v>
+        <v>0.794497728347778</v>
       </c>
       <c r="H1396" t="n">
         <v>29317</v>
@@ -40882,7 +40882,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1397" t="n">
-        <v>0.796398460865021</v>
+        <v>0.796398401260376</v>
       </c>
       <c r="H1397" t="n">
         <v>49629</v>
@@ -40969,7 +40969,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1400" t="n">
-        <v>0.788795590400696</v>
+        <v>0.788795530796051</v>
       </c>
       <c r="H1400" t="n">
         <v>63141</v>
@@ -40998,7 +40998,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1401" t="n">
-        <v>0.786894917488098</v>
+        <v>0.786894857883453</v>
       </c>
       <c r="H1401" t="n">
         <v>55616</v>
@@ -41056,7 +41056,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1403" t="n">
-        <v>0.781192719936371</v>
+        <v>0.781192779541016</v>
       </c>
       <c r="H1403" t="n">
         <v>21218</v>
@@ -41114,7 +41114,7 @@
         <v>0.818000018596649</v>
       </c>
       <c r="G1405" t="n">
-        <v>0.777391314506531</v>
+        <v>0.777391254901886</v>
       </c>
       <c r="H1405" t="n">
         <v>14851</v>
@@ -41143,7 +41143,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1406" t="n">
-        <v>0.779292047023773</v>
+        <v>0.779291987419128</v>
       </c>
       <c r="H1406" t="n">
         <v>7404</v>
@@ -41230,7 +41230,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1409" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1409" t="n">
         <v>43653</v>
@@ -41288,7 +41288,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.754582822322845</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1411" t="n">
         <v>49753</v>
@@ -41317,7 +41317,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1412" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1412" t="n">
         <v>53142</v>
@@ -41346,7 +41346,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1413" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752681970596313</v>
       </c>
       <c r="H1413" t="n">
         <v>861</v>
@@ -41462,7 +41462,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.752682030200958</v>
+        <v>0.752681970596313</v>
       </c>
       <c r="H1417" t="n">
         <v>6109</v>
@@ -41578,7 +41578,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1421" t="n">
-        <v>0.748880565166473</v>
+        <v>0.748880624771118</v>
       </c>
       <c r="H1421" t="n">
         <v>20129</v>
@@ -41665,7 +41665,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.754582822322845</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1424" t="n">
         <v>13463</v>
@@ -41723,7 +41723,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1426" t="n">
-        <v>0.758384108543396</v>
+        <v>0.758384168148041</v>
       </c>
       <c r="H1426" t="n">
         <v>4889</v>
@@ -41810,7 +41810,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1429" t="n">
         <v>777</v>
@@ -41839,7 +41839,7 @@
         <v>0.783999979496002</v>
       </c>
       <c r="G1430" t="n">
-        <v>0.745079159736633</v>
+        <v>0.745079219341278</v>
       </c>
       <c r="H1430" t="n">
         <v>0</v>
@@ -41926,7 +41926,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1433" t="n">
-        <v>0.758384108543396</v>
+        <v>0.758384168148041</v>
       </c>
       <c r="H1433" t="n">
         <v>4016</v>
@@ -41984,7 +41984,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1435" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1435" t="n">
         <v>50781</v>
@@ -42042,7 +42042,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1437" t="n">
-        <v>0.758384108543396</v>
+        <v>0.758384168148041</v>
       </c>
       <c r="H1437" t="n">
         <v>25753</v>
@@ -42071,7 +42071,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1438" t="n">
-        <v>0.758384108543396</v>
+        <v>0.758384168148041</v>
       </c>
       <c r="H1438" t="n">
         <v>2223</v>
@@ -42100,7 +42100,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1439" t="n">
-        <v>0.767887711524963</v>
+        <v>0.767887771129608</v>
       </c>
       <c r="H1439" t="n">
         <v>1167</v>
@@ -42274,7 +42274,7 @@
         <v>0.815999984741211</v>
       </c>
       <c r="G1445" t="n">
-        <v>0.775490522384644</v>
+        <v>0.775490581989288</v>
       </c>
       <c r="H1445" t="n">
         <v>16945</v>
@@ -42477,7 +42477,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1452" t="n">
-        <v>0.758384108543396</v>
+        <v>0.758384168148041</v>
       </c>
       <c r="H1452" t="n">
         <v>3313</v>
@@ -42506,7 +42506,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1453" t="n">
-        <v>0.764086365699768</v>
+        <v>0.764086306095123</v>
       </c>
       <c r="H1453" t="n">
         <v>21018</v>
@@ -42564,7 +42564,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1455" t="n">
-        <v>0.754582822322845</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1455" t="n">
         <v>3339</v>
@@ -42593,7 +42593,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1456" t="n">
-        <v>0.754582822322845</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1456" t="n">
         <v>0</v>
@@ -42622,7 +42622,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1457" t="n">
-        <v>0.754582822322845</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1457" t="n">
         <v>1282</v>
@@ -42709,7 +42709,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1460" t="n">
-        <v>0.754582822322845</v>
+        <v>0.754582762718201</v>
       </c>
       <c r="H1460" t="n">
         <v>4863</v>
@@ -42854,7 +42854,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1465" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1465" t="n">
         <v>63301</v>
@@ -42912,7 +42912,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1467" t="n">
         <v>35377</v>
@@ -42999,7 +42999,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1470" t="n">
-        <v>0.718469202518463</v>
+        <v>0.718469262123108</v>
       </c>
       <c r="H1470" t="n">
         <v>16114</v>
@@ -43086,7 +43086,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1473" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1473" t="n">
         <v>35727</v>
@@ -43115,7 +43115,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1474" t="n">
-        <v>0.739377081394196</v>
+        <v>0.739377021789551</v>
       </c>
       <c r="H1474" t="n">
         <v>0</v>
@@ -43521,7 +43521,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.722270607948303</v>
+        <v>0.722270548343658</v>
       </c>
       <c r="H1488" t="n">
         <v>24502</v>
@@ -43608,7 +43608,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1491" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1491" t="n">
         <v>8016</v>
@@ -43637,7 +43637,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1492" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1492" t="n">
         <v>3065</v>
@@ -43666,7 +43666,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1493" t="n">
-        <v>0.731774151325226</v>
+        <v>0.731774210929871</v>
       </c>
       <c r="H1493" t="n">
         <v>3253</v>
@@ -43811,7 +43811,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1498" t="n">
-        <v>0.720369875431061</v>
+        <v>0.720369935035706</v>
       </c>
       <c r="H1498" t="n">
         <v>96906</v>
@@ -43869,7 +43869,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1500" t="n">
-        <v>0.708965659141541</v>
+        <v>0.708965599536896</v>
       </c>
       <c r="H1500" t="n">
         <v>36772</v>
@@ -43985,7 +43985,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1504" t="n">
-        <v>0.714667856693268</v>
+        <v>0.714667797088623</v>
       </c>
       <c r="H1504" t="n">
         <v>11995</v>
@@ -44159,7 +44159,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1510" t="n">
-        <v>0.689958572387695</v>
+        <v>0.689958512783051</v>
       </c>
       <c r="H1510" t="n">
         <v>1716</v>
@@ -44246,7 +44246,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1513" t="n">
-        <v>0.714667856693268</v>
+        <v>0.714667797088623</v>
       </c>
       <c r="H1513" t="n">
         <v>4895</v>
@@ -44304,7 +44304,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1515" t="n">
-        <v>0.701362729072571</v>
+        <v>0.701362788677216</v>
       </c>
       <c r="H1515" t="n">
         <v>3000</v>
@@ -44333,7 +44333,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1516" t="n">
-        <v>0.708965659141541</v>
+        <v>0.708965599536896</v>
       </c>
       <c r="H1516" t="n">
         <v>28188</v>
@@ -44362,7 +44362,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.701362729072571</v>
+        <v>0.701362788677216</v>
       </c>
       <c r="H1517" t="n">
         <v>2916</v>
@@ -44420,7 +44420,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1519" t="n">
-        <v>0.708965659141541</v>
+        <v>0.708965599536896</v>
       </c>
       <c r="H1519" t="n">
         <v>3267</v>
@@ -44449,7 +44449,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1520" t="n">
-        <v>0.708965659141541</v>
+        <v>0.708965599536896</v>
       </c>
       <c r="H1520" t="n">
         <v>0</v>
@@ -44710,7 +44710,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.693759977817535</v>
+        <v>0.69376003742218</v>
       </c>
       <c r="H1529" t="n">
         <v>31255</v>
@@ -44797,7 +44797,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1532" t="n">
-        <v>0.693759977817535</v>
+        <v>0.69376003742218</v>
       </c>
       <c r="H1532" t="n">
         <v>2091</v>
@@ -44855,7 +44855,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1534" t="n">
-        <v>0.701362729072571</v>
+        <v>0.701362788677216</v>
       </c>
       <c r="H1534" t="n">
         <v>13975</v>
@@ -44884,7 +44884,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1535" t="n">
-        <v>0.69756144285202</v>
+        <v>0.697561383247375</v>
       </c>
       <c r="H1535" t="n">
         <v>3000</v>
@@ -44913,7 +44913,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1536" t="n">
-        <v>0.69756144285202</v>
+        <v>0.697561383247375</v>
       </c>
       <c r="H1536" t="n">
         <v>2001</v>
@@ -44942,7 +44942,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1537" t="n">
-        <v>0.69756144285202</v>
+        <v>0.697561383247375</v>
       </c>
       <c r="H1537" t="n">
         <v>1094</v>
@@ -44971,7 +44971,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1538" t="n">
-        <v>0.693759977817535</v>
+        <v>0.69376003742218</v>
       </c>
       <c r="H1538" t="n">
         <v>1647</v>
@@ -45000,7 +45000,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1539" t="n">
-        <v>0.693759977817535</v>
+        <v>0.69376003742218</v>
       </c>
       <c r="H1539" t="n">
         <v>0</v>
@@ -45029,7 +45029,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.693759977817535</v>
+        <v>0.69376003742218</v>
       </c>
       <c r="H1540" t="n">
         <v>18889</v>
@@ -45174,7 +45174,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.689958572387695</v>
+        <v>0.689958512783051</v>
       </c>
       <c r="H1545" t="n">
         <v>4900</v>
@@ -45261,7 +45261,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.69756144285202</v>
+        <v>0.697561383247375</v>
       </c>
       <c r="H1548" t="n">
         <v>116</v>
@@ -45290,7 +45290,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1549" t="n">
-        <v>0.695660650730133</v>
+        <v>0.695660591125488</v>
       </c>
       <c r="H1549" t="n">
         <v>2218</v>
@@ -45319,7 +45319,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1550" t="n">
-        <v>0.689958572387695</v>
+        <v>0.689958512783051</v>
       </c>
       <c r="H1550" t="n">
         <v>10800</v>
@@ -45348,7 +45348,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1551" t="n">
-        <v>0.68615710735321</v>
+        <v>0.686157047748566</v>
       </c>
       <c r="H1551" t="n">
         <v>16</v>
@@ -45522,7 +45522,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.665249288082123</v>
+        <v>0.665249228477478</v>
       </c>
       <c r="H1557" t="n">
         <v>20167</v>
@@ -45551,7 +45551,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.701362729072571</v>
+        <v>0.701362788677216</v>
       </c>
       <c r="H1558" t="n">
         <v>45922</v>
@@ -45638,7 +45638,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1561" t="n">
-        <v>0.708965659141541</v>
+        <v>0.708965599536896</v>
       </c>
       <c r="H1561" t="n">
         <v>42743</v>
@@ -45696,7 +45696,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.672852158546448</v>
+        <v>0.672852098941803</v>
       </c>
       <c r="H1563" t="n">
         <v>2697</v>
@@ -45725,7 +45725,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1564" t="n">
-        <v>0.68615710735321</v>
+        <v>0.686157047748566</v>
       </c>
       <c r="H1564" t="n">
         <v>10278</v>
@@ -45754,7 +45754,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1565" t="n">
-        <v>0.665249288082123</v>
+        <v>0.665249228477478</v>
       </c>
       <c r="H1565" t="n">
         <v>39792</v>
@@ -45783,7 +45783,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1566" t="n">
-        <v>0.693759977817535</v>
+        <v>0.69376003742218</v>
       </c>
       <c r="H1566" t="n">
         <v>7267</v>
@@ -45841,7 +45841,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1568" t="n">
-        <v>0.676653504371643</v>
+        <v>0.676653563976288</v>
       </c>
       <c r="H1568" t="n">
         <v>23252</v>
@@ -45899,7 +45899,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.657646358013153</v>
+        <v>0.657646417617798</v>
       </c>
       <c r="H1570" t="n">
         <v>16550</v>
@@ -46073,7 +46073,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.627235054969788</v>
+        <v>0.627235114574432</v>
       </c>
       <c r="H1576" t="n">
         <v>32785</v>
@@ -46102,7 +46102,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1577" t="n">
-        <v>0.623433649539948</v>
+        <v>0.623433589935303</v>
       </c>
       <c r="H1577" t="n">
         <v>8418</v>
@@ -46189,7 +46189,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1580" t="n">
-        <v>0.674752771854401</v>
+        <v>0.674752831459045</v>
       </c>
       <c r="H1580" t="n">
         <v>7398</v>
@@ -46218,7 +46218,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1581" t="n">
-        <v>0.657646358013153</v>
+        <v>0.657646417617798</v>
       </c>
       <c r="H1581" t="n">
         <v>43198</v>
@@ -46305,7 +46305,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.64054000377655</v>
+        <v>0.640540063381195</v>
       </c>
       <c r="H1584" t="n">
         <v>1100</v>
@@ -46334,7 +46334,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1585" t="n">
-        <v>0.623433649539948</v>
+        <v>0.623433589935303</v>
       </c>
       <c r="H1585" t="n">
         <v>31781</v>
@@ -46508,7 +46508,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1591" t="n">
-        <v>0.64814281463623</v>
+        <v>0.648142755031586</v>
       </c>
       <c r="H1591" t="n">
         <v>1075</v>
@@ -46537,7 +46537,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1592" t="n">
-        <v>0.64814281463623</v>
+        <v>0.648142755031586</v>
       </c>
       <c r="H1592" t="n">
         <v>5713</v>
@@ -46653,7 +46653,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1596" t="n">
-        <v>0.634837865829468</v>
+        <v>0.634837806224823</v>
       </c>
       <c r="H1596" t="n">
         <v>4647</v>
@@ -46682,7 +46682,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1597" t="n">
-        <v>0.634837865829468</v>
+        <v>0.634837806224823</v>
       </c>
       <c r="H1597" t="n">
         <v>1316</v>
@@ -46711,7 +46711,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1598" t="n">
-        <v>0.627235054969788</v>
+        <v>0.627235114574432</v>
       </c>
       <c r="H1598" t="n">
         <v>2717</v>
@@ -46740,7 +46740,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1599" t="n">
-        <v>0.627235054969788</v>
+        <v>0.627235114574432</v>
       </c>
       <c r="H1599" t="n">
         <v>0</v>
@@ -46769,7 +46769,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1600" t="n">
-        <v>0.63673859834671</v>
+        <v>0.636738657951355</v>
       </c>
       <c r="H1600" t="n">
         <v>15305</v>
@@ -46856,7 +46856,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1603" t="n">
-        <v>0.63673859834671</v>
+        <v>0.636738657951355</v>
       </c>
       <c r="H1603" t="n">
         <v>13153</v>
@@ -46885,7 +46885,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.634837865829468</v>
+        <v>0.634837806224823</v>
       </c>
       <c r="H1604" t="n">
         <v>1929</v>
@@ -46914,7 +46914,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.627235054969788</v>
+        <v>0.627235114574432</v>
       </c>
       <c r="H1605" t="n">
         <v>1703</v>
@@ -46972,7 +46972,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.623433649539948</v>
+        <v>0.623433589935303</v>
       </c>
       <c r="H1607" t="n">
         <v>1695</v>
@@ -47175,7 +47175,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.606327295303345</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1614" t="n">
         <v>5966</v>
@@ -47204,7 +47204,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1615" t="n">
-        <v>0.612029254436493</v>
+        <v>0.612029314041138</v>
       </c>
       <c r="H1615" t="n">
         <v>2932</v>
@@ -47233,7 +47233,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1616" t="n">
-        <v>0.623433649539948</v>
+        <v>0.623433589935303</v>
       </c>
       <c r="H1616" t="n">
         <v>1329</v>
@@ -47262,7 +47262,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.623433649539948</v>
+        <v>0.623433589935303</v>
       </c>
       <c r="H1617" t="n">
         <v>0</v>
@@ -47291,7 +47291,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1618" t="n">
-        <v>0.623433649539948</v>
+        <v>0.623433589935303</v>
       </c>
       <c r="H1618" t="n">
         <v>0</v>
@@ -47349,7 +47349,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1620" t="n">
         <v>27183</v>
@@ -47436,7 +47436,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1623" t="n">
-        <v>0.623433649539948</v>
+        <v>0.623433589935303</v>
       </c>
       <c r="H1623" t="n">
         <v>28945</v>
@@ -47465,7 +47465,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1624" t="n">
-        <v>0.623433649539948</v>
+        <v>0.623433589935303</v>
       </c>
       <c r="H1624" t="n">
         <v>0</v>
@@ -47494,7 +47494,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1625" t="n">
-        <v>0.623433649539948</v>
+        <v>0.623433589935303</v>
       </c>
       <c r="H1625" t="n">
         <v>3239</v>
@@ -47523,7 +47523,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1626" t="n">
-        <v>0.623433649539948</v>
+        <v>0.623433589935303</v>
       </c>
       <c r="H1626" t="n">
         <v>5923</v>
@@ -47552,7 +47552,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1627" t="n">
-        <v>0.623433649539948</v>
+        <v>0.623433589935303</v>
       </c>
       <c r="H1627" t="n">
         <v>1050</v>
@@ -47581,7 +47581,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1628" t="n">
-        <v>0.627235054969788</v>
+        <v>0.627235114574432</v>
       </c>
       <c r="H1628" t="n">
         <v>11217</v>
@@ -47871,7 +47871,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1638" t="n">
         <v>9832</v>
@@ -47900,7 +47900,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1639" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1639" t="n">
         <v>8789</v>
@@ -47929,7 +47929,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1640" t="n">
-        <v>0.606327295303345</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1640" t="n">
         <v>23258</v>
@@ -47958,7 +47958,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1641" t="n">
-        <v>0.606327295303345</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1641" t="n">
         <v>0</v>
@@ -47987,7 +47987,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.606327295303345</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1642" t="n">
         <v>0</v>
@@ -48016,7 +48016,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1643" t="n">
-        <v>0.60252571105957</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1643" t="n">
         <v>500</v>
@@ -48190,7 +48190,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1649" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1649" t="n">
         <v>7918</v>
@@ -48219,7 +48219,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1650" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1650" t="n">
         <v>10632</v>
@@ -48248,7 +48248,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1651" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1651" t="n">
         <v>500</v>
@@ -48335,7 +48335,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1654" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1654" t="n">
         <v>1001</v>
@@ -48364,7 +48364,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.543603718280792</v>
+        <v>0.543603777885437</v>
       </c>
       <c r="H1655" t="n">
         <v>74811</v>
@@ -48480,7 +48480,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G1659" t="n">
-        <v>0.494185119867325</v>
+        <v>0.49418517947197</v>
       </c>
       <c r="H1659" t="n">
         <v>111650</v>
@@ -48509,7 +48509,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G1660" t="n">
-        <v>0.524596571922302</v>
+        <v>0.524596512317657</v>
       </c>
       <c r="H1660" t="n">
         <v>17827</v>
@@ -48538,7 +48538,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1661" t="n">
-        <v>0.54170298576355</v>
+        <v>0.541702926158905</v>
       </c>
       <c r="H1661" t="n">
         <v>8896</v>
@@ -48654,7 +48654,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1665" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1665" t="n">
         <v>288</v>
@@ -48683,7 +48683,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1666" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1666" t="n">
         <v>15</v>
@@ -48712,7 +48712,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1667" t="n">
         <v>2000</v>
@@ -48741,7 +48741,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1668" t="n">
         <v>39945</v>
@@ -48828,7 +48828,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1671" t="n">
-        <v>0.604426503181458</v>
+        <v>0.604426443576813</v>
       </c>
       <c r="H1671" t="n">
         <v>3877</v>
@@ -48915,7 +48915,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1674" t="n">
         <v>5204</v>
@@ -48944,7 +48944,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1675" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1675" t="n">
         <v>7316</v>
@@ -49089,7 +49089,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1680" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1680" t="n">
         <v>5826</v>
@@ -49118,7 +49118,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1681" t="n">
-        <v>0.604426503181458</v>
+        <v>0.604426443576813</v>
       </c>
       <c r="H1681" t="n">
         <v>5420</v>
@@ -49147,7 +49147,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.612029254436493</v>
+        <v>0.612029314041138</v>
       </c>
       <c r="H1682" t="n">
         <v>9272</v>
@@ -49263,7 +49263,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1686" t="n">
         <v>18805</v>
@@ -49292,7 +49292,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1687" t="n">
-        <v>0.60252571105957</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1687" t="n">
         <v>564</v>
@@ -49321,7 +49321,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1688" t="n">
-        <v>0.60252571105957</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1688" t="n">
         <v>1061</v>
@@ -49350,7 +49350,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.60252571105957</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1689" t="n">
         <v>1</v>
@@ -49408,7 +49408,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.604426503181458</v>
+        <v>0.604426443576813</v>
       </c>
       <c r="H1691" t="n">
         <v>677</v>
@@ -49466,7 +49466,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1693" t="n">
-        <v>0.604426503181458</v>
+        <v>0.604426443576813</v>
       </c>
       <c r="H1693" t="n">
         <v>832</v>
@@ -49495,7 +49495,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1694" t="n">
-        <v>0.604426503181458</v>
+        <v>0.604426443576813</v>
       </c>
       <c r="H1694" t="n">
         <v>950</v>
@@ -49524,7 +49524,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.60252571105957</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1695" t="n">
         <v>6536</v>
@@ -49553,7 +49553,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1696" t="n">
-        <v>0.606327295303345</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1696" t="n">
         <v>1080</v>
@@ -49582,7 +49582,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.606327295303345</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1697" t="n">
         <v>0</v>
@@ -49611,7 +49611,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1698" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1698" t="n">
         <v>3824</v>
@@ -49640,7 +49640,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1699" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1699" t="n">
         <v>1090</v>
@@ -49669,7 +49669,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1700" t="n">
         <v>1058</v>
@@ -49698,7 +49698,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.606327295303345</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1701" t="n">
         <v>16</v>
@@ -49756,7 +49756,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1703" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1703" t="n">
         <v>8574</v>
@@ -49901,7 +49901,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1708" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1708" t="n">
         <v>6016</v>
@@ -49988,7 +49988,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1711" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1711" t="n">
         <v>63</v>
@@ -50017,7 +50017,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1712" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1712" t="n">
         <v>10927</v>
@@ -50104,7 +50104,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1715" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1715" t="n">
         <v>794</v>
@@ -50220,7 +50220,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1719" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1719" t="n">
         <v>12381</v>
@@ -50249,7 +50249,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1720" t="n">
         <v>4551</v>
@@ -50307,7 +50307,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1722" t="n">
-        <v>0.57971727848053</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1722" t="n">
         <v>4854</v>
@@ -50394,7 +50394,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1725" t="n">
-        <v>0.57971727848053</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1725" t="n">
         <v>7417</v>
@@ -50597,7 +50597,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1732" t="n">
-        <v>0.57971727848053</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1732" t="n">
         <v>3355</v>
@@ -50858,7 +50858,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1741" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1741" t="n">
         <v>2611</v>
@@ -50916,7 +50916,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1743" t="n">
-        <v>0.5759157538414</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1743" t="n">
         <v>1000</v>
@@ -51032,7 +51032,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1747" t="n">
-        <v>0.5759157538414</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1747" t="n">
         <v>8200</v>
@@ -51148,7 +51148,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1751" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1751" t="n">
         <v>5540</v>
@@ -51293,7 +51293,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1756" t="n">
-        <v>0.583518624305725</v>
+        <v>0.58351868391037</v>
       </c>
       <c r="H1756" t="n">
         <v>209</v>
@@ -51351,7 +51351,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1758" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1758" t="n">
         <v>2396</v>
@@ -51380,7 +51380,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1759" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1759" t="n">
         <v>0</v>
@@ -51467,7 +51467,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1762" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1762" t="n">
         <v>615</v>
@@ -51496,7 +51496,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1763" t="n">
         <v>2731</v>
@@ -51525,7 +51525,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1764" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1764" t="n">
         <v>2755</v>
@@ -51554,7 +51554,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1765" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1765" t="n">
         <v>9533</v>
@@ -51583,7 +51583,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1766" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1766" t="n">
         <v>11513</v>
@@ -51612,7 +51612,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1767" t="n">
-        <v>0.60252571105957</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1767" t="n">
         <v>624</v>
@@ -51670,7 +51670,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1769" t="n">
-        <v>0.60252571105957</v>
+        <v>0.602525770664215</v>
       </c>
       <c r="H1769" t="n">
         <v>8114</v>
@@ -51699,7 +51699,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.604426503181458</v>
+        <v>0.604426443576813</v>
       </c>
       <c r="H1770" t="n">
         <v>19269</v>
@@ -51728,7 +51728,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1771" t="n">
-        <v>0.604426503181458</v>
+        <v>0.604426443576813</v>
       </c>
       <c r="H1771" t="n">
         <v>15200</v>
@@ -51786,7 +51786,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1773" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1773" t="n">
         <v>5522</v>
@@ -51931,7 +51931,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1778" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1778" t="n">
         <v>516</v>
@@ -51989,7 +51989,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1780" t="n">
-        <v>0.606327295303345</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1780" t="n">
         <v>20280</v>
@@ -52047,7 +52047,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1782" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1782" t="n">
         <v>633</v>
@@ -52076,7 +52076,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1783" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1783" t="n">
         <v>0</v>
@@ -52105,7 +52105,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1784" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1784" t="n">
         <v>0</v>
@@ -52163,7 +52163,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1786" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1786" t="n">
         <v>5365</v>
@@ -52250,7 +52250,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1789" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1789" t="n">
         <v>43189</v>
@@ -52279,7 +52279,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1790" t="n">
         <v>0</v>
@@ -52308,7 +52308,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1791" t="n">
-        <v>0.583518624305725</v>
+        <v>0.58351868391037</v>
       </c>
       <c r="H1791" t="n">
         <v>5017</v>
@@ -52337,7 +52337,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1792" t="n">
         <v>1109</v>
@@ -52395,7 +52395,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1794" t="n">
-        <v>0.604426503181458</v>
+        <v>0.604426443576813</v>
       </c>
       <c r="H1794" t="n">
         <v>1836</v>
@@ -52772,7 +52772,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1807" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1807" t="n">
         <v>7034</v>
@@ -52801,7 +52801,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1808" t="n">
-        <v>0.583518624305725</v>
+        <v>0.58351868391037</v>
       </c>
       <c r="H1808" t="n">
         <v>6391</v>
@@ -53091,7 +53091,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1818" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1818" t="n">
         <v>1892</v>
@@ -53178,7 +53178,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1821" t="n">
-        <v>0.5759157538414</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1821" t="n">
         <v>9490</v>
@@ -53236,7 +53236,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1823" t="n">
-        <v>0.583518624305725</v>
+        <v>0.58351868391037</v>
       </c>
       <c r="H1823" t="n">
         <v>4868</v>
@@ -53323,7 +53323,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1826" t="n">
         <v>73878</v>
@@ -53352,7 +53352,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1827" t="n">
-        <v>0.57971727848053</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1827" t="n">
         <v>12465</v>
@@ -53410,7 +53410,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1829" t="n">
         <v>1562</v>
@@ -53439,7 +53439,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1830" t="n">
-        <v>0.583518624305725</v>
+        <v>0.58351868391037</v>
       </c>
       <c r="H1830" t="n">
         <v>37386</v>
@@ -53468,7 +53468,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1831" t="n">
-        <v>0.600625097751617</v>
+        <v>0.600625157356262</v>
       </c>
       <c r="H1831" t="n">
         <v>18113</v>
@@ -53497,7 +53497,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.5759157538414</v>
+        <v>0.575915813446045</v>
       </c>
       <c r="H1832" t="n">
         <v>2559</v>
@@ -53526,7 +53526,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1833" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1833" t="n">
         <v>26592</v>
@@ -53584,7 +53584,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1835" t="n">
         <v>2647</v>
@@ -53613,7 +53613,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.558809340000153</v>
+        <v>0.558809399604797</v>
       </c>
       <c r="H1836" t="n">
         <v>518</v>
@@ -53642,7 +53642,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1837" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1837" t="n">
         <v>31108</v>
@@ -53729,7 +53729,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1840" t="n">
         <v>5059</v>
@@ -53758,7 +53758,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1841" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1841" t="n">
         <v>353</v>
@@ -53816,7 +53816,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1843" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1843" t="n">
         <v>1246</v>
@@ -53874,7 +53874,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1845" t="n">
-        <v>0.57971727848053</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1845" t="n">
         <v>4050</v>
@@ -53903,7 +53903,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1846" t="n">
-        <v>0.598724365234375</v>
+        <v>0.59872430562973</v>
       </c>
       <c r="H1846" t="n">
         <v>14297</v>
@@ -53932,7 +53932,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1847" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1847" t="n">
         <v>7661</v>
@@ -53961,7 +53961,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1848" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1848" t="n">
         <v>1162</v>
@@ -54019,7 +54019,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1850" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1850" t="n">
         <v>7024</v>
@@ -54251,7 +54251,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1858" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1858" t="n">
         <v>13779</v>
@@ -54280,7 +54280,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1859" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1859" t="n">
         <v>0</v>
@@ -54309,7 +54309,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1860" t="n">
-        <v>0.57971727848053</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1860" t="n">
         <v>4000</v>
@@ -54425,7 +54425,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1864" t="n">
-        <v>0.57971727848053</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1864" t="n">
         <v>2015</v>
@@ -54570,7 +54570,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1869" t="n">
-        <v>0.583518624305725</v>
+        <v>0.58351868391037</v>
       </c>
       <c r="H1869" t="n">
         <v>5034</v>
@@ -54599,7 +54599,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1870" t="n">
-        <v>0.583518624305725</v>
+        <v>0.58351868391037</v>
       </c>
       <c r="H1870" t="n">
         <v>1535</v>
@@ -54657,7 +54657,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1872" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1872" t="n">
         <v>11785</v>
@@ -54773,7 +54773,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1876" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1876" t="n">
         <v>32101</v>
@@ -54802,7 +54802,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1877" t="n">
-        <v>0.558809340000153</v>
+        <v>0.558809399604797</v>
       </c>
       <c r="H1877" t="n">
         <v>1202</v>
@@ -54831,7 +54831,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1878" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1878" t="n">
         <v>345</v>
@@ -55034,7 +55034,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1885" t="n">
         <v>10634</v>
@@ -55063,7 +55063,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1886" t="n">
         <v>7962</v>
@@ -55092,7 +55092,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.558809340000153</v>
+        <v>0.558809399604797</v>
       </c>
       <c r="H1887" t="n">
         <v>2513</v>
@@ -55121,7 +55121,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1888" t="n">
         <v>1701</v>
@@ -55150,7 +55150,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1889" t="n">
         <v>0</v>
@@ -55208,7 +55208,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1891" t="n">
         <v>4328</v>
@@ -55237,7 +55237,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1892" t="n">
         <v>4045</v>
@@ -55266,7 +55266,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1893" t="n">
         <v>0</v>
@@ -55295,7 +55295,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1894" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1894" t="n">
         <v>500</v>
@@ -55324,7 +55324,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1895" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1895" t="n">
         <v>1600</v>
@@ -55353,7 +55353,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1896" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1896" t="n">
         <v>0</v>
@@ -55382,7 +55382,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1897" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1897" t="n">
         <v>3982</v>
@@ -55440,7 +55440,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1899" t="n">
-        <v>0.558809340000153</v>
+        <v>0.558809399604797</v>
       </c>
       <c r="H1899" t="n">
         <v>28638</v>
@@ -55469,7 +55469,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1900" t="n">
-        <v>0.54170298576355</v>
+        <v>0.541702926158905</v>
       </c>
       <c r="H1900" t="n">
         <v>3769</v>
@@ -55498,7 +55498,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1901" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1901" t="n">
         <v>517</v>
@@ -55527,7 +55527,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1902" t="n">
-        <v>0.558809340000153</v>
+        <v>0.558809399604797</v>
       </c>
       <c r="H1902" t="n">
         <v>2565</v>
@@ -55556,7 +55556,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1903" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1903" t="n">
         <v>8412</v>
@@ -55585,7 +55585,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1904" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1904" t="n">
         <v>2017</v>
@@ -55643,7 +55643,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1906" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1906" t="n">
         <v>1018</v>
@@ -55672,7 +55672,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1907" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1907" t="n">
         <v>0</v>
@@ -55701,7 +55701,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1908" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1908" t="n">
         <v>0</v>
@@ -55730,7 +55730,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1909" t="n">
-        <v>0.562610805034637</v>
+        <v>0.562610864639282</v>
       </c>
       <c r="H1909" t="n">
         <v>1000</v>
@@ -55759,7 +55759,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1910" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1910" t="n">
         <v>3519</v>
@@ -55788,7 +55788,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1911" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1911" t="n">
         <v>10376</v>
@@ -55904,7 +55904,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G1915" t="n">
-        <v>0.54170298576355</v>
+        <v>0.541702926158905</v>
       </c>
       <c r="H1915" t="n">
         <v>2626</v>
@@ -55962,7 +55962,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G1917" t="n">
-        <v>0.543603718280792</v>
+        <v>0.543603777885437</v>
       </c>
       <c r="H1917" t="n">
         <v>5021</v>
@@ -56194,7 +56194,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1925" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1925" t="n">
         <v>27392</v>
@@ -56223,7 +56223,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1926" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1926" t="n">
         <v>2000</v>
@@ -56252,7 +56252,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1927" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1927" t="n">
         <v>1725</v>
@@ -56281,7 +56281,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1928" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1928" t="n">
         <v>18560</v>
@@ -56368,7 +56368,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1931" t="n">
-        <v>0.606327295303345</v>
+        <v>0.6063272356987</v>
       </c>
       <c r="H1931" t="n">
         <v>5238</v>
@@ -56397,7 +56397,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1932" t="n">
-        <v>0.612029254436493</v>
+        <v>0.612029314041138</v>
       </c>
       <c r="H1932" t="n">
         <v>18087</v>
@@ -56455,7 +56455,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1934" t="n">
-        <v>0.587320029735565</v>
+        <v>0.58732008934021</v>
       </c>
       <c r="H1934" t="n">
         <v>3890</v>
@@ -56571,7 +56571,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1938" t="n">
-        <v>0.57971727848053</v>
+        <v>0.579717218875885</v>
       </c>
       <c r="H1938" t="n">
         <v>3888</v>
@@ -56600,7 +56600,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1939" t="n">
-        <v>0.583518624305725</v>
+        <v>0.58351868391037</v>
       </c>
       <c r="H1939" t="n">
         <v>4503</v>
@@ -56658,7 +56658,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1941" t="n">
-        <v>0.56831294298172</v>
+        <v>0.568312883377075</v>
       </c>
       <c r="H1941" t="n">
         <v>1989</v>
@@ -56716,7 +56716,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1943" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1943" t="n">
         <v>8017</v>
@@ -56745,7 +56745,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1944" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1944" t="n">
         <v>0</v>
@@ -56774,7 +56774,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1945" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1945" t="n">
         <v>0</v>
@@ -56803,7 +56803,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1946" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1946" t="n">
         <v>11246</v>
@@ -56832,7 +56832,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1947" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1947" t="n">
         <v>525</v>
@@ -56861,7 +56861,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1948" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1948" t="n">
         <v>4089</v>
@@ -56919,7 +56919,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1950" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1950" t="n">
         <v>500</v>
@@ -56948,7 +56948,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1951" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1951" t="n">
         <v>8549</v>
@@ -56977,7 +56977,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1952" t="n">
-        <v>0.558809340000153</v>
+        <v>0.558809399604797</v>
       </c>
       <c r="H1952" t="n">
         <v>220</v>
@@ -57006,7 +57006,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1953" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1953" t="n">
         <v>2398</v>
@@ -57035,7 +57035,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G1954" t="n">
-        <v>0.558809340000153</v>
+        <v>0.558809399604797</v>
       </c>
       <c r="H1954" t="n">
         <v>701</v>
@@ -57064,7 +57064,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1955" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1955" t="n">
         <v>1419</v>
@@ -57093,7 +57093,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1956" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1956" t="n">
         <v>4</v>
@@ -57122,7 +57122,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1957" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1957" t="n">
         <v>978</v>
@@ -57151,7 +57151,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1958" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1958" t="n">
         <v>817</v>
@@ -57209,7 +57209,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1960" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1960" t="n">
         <v>15378</v>
@@ -57267,7 +57267,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1962" t="n">
-        <v>0.560710072517395</v>
+        <v>0.56071001291275</v>
       </c>
       <c r="H1962" t="n">
         <v>6069</v>
@@ -57354,7 +57354,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1965" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1965" t="n">
         <v>7</v>
@@ -57383,7 +57383,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1966" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1966" t="n">
         <v>1200</v>
@@ -57470,7 +57470,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1969" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1969" t="n">
         <v>8365</v>
@@ -57499,7 +57499,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1970" t="n">
-        <v>0.555007994174957</v>
+        <v>0.555007934570312</v>
       </c>
       <c r="H1970" t="n">
         <v>0</v>
@@ -57528,7 +57528,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1971" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1971" t="n">
         <v>4333</v>
@@ -57557,7 +57557,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G1972" t="n">
-        <v>0.556908667087555</v>
+        <v>0.5569087266922</v>
       </c>
       <c r="H1972" t="n">
         <v>1258</v>
@@ -57673,7 +57673,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G1976" t="n">
-        <v>0.55579799413681</v>
+        <v>0.555798053741455</v>
       </c>
       <c r="H1976" t="n">
         <v>46335</v>
@@ -57731,7 +57731,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G1978" t="n">
-        <v>0.55579799413681</v>
+        <v>0.555798053741455</v>
       </c>
       <c r="H1978" t="n">
         <v>120457</v>
@@ -57847,7 +57847,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G1982" t="n">
-        <v>0.55579799413681</v>
+        <v>0.555798053741455</v>
       </c>
       <c r="H1982" t="n">
         <v>45531</v>
@@ -58137,7 +58137,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1992" t="n">
-        <v>0.522990524768829</v>
+        <v>0.522990465164185</v>
       </c>
       <c r="H1992" t="n">
         <v>2</v>
@@ -58166,7 +58166,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G1993" t="n">
-        <v>0.511411309242249</v>
+        <v>0.511411368846893</v>
       </c>
       <c r="H1993" t="n">
         <v>5405</v>
@@ -58311,7 +58311,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G1998" t="n">
-        <v>0.522990524768829</v>
+        <v>0.522990465164185</v>
       </c>
       <c r="H1998" t="n">
         <v>3143</v>
@@ -58369,7 +58369,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2000" t="n">
-        <v>0.524920403957367</v>
+        <v>0.524920344352722</v>
       </c>
       <c r="H2000" t="n">
         <v>19211</v>
@@ -58456,7 +58456,7 @@
         <v>0.529999971389771</v>
       </c>
       <c r="G2003" t="n">
-        <v>0.511411309242249</v>
+        <v>0.511411368846893</v>
       </c>
       <c r="H2003" t="n">
         <v>3405</v>
@@ -58485,7 +58485,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2004" t="n">
-        <v>0.50176203250885</v>
+        <v>0.501762092113495</v>
       </c>
       <c r="H2004" t="n">
         <v>94494</v>
@@ -58572,7 +58572,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2007" t="n">
-        <v>0.524920403957367</v>
+        <v>0.524920344352722</v>
       </c>
       <c r="H2007" t="n">
         <v>8019</v>
@@ -58804,7 +58804,7 @@
         <v>0.519999980926514</v>
       </c>
       <c r="G2015" t="n">
-        <v>0.50176203250885</v>
+        <v>0.501762092113495</v>
       </c>
       <c r="H2015" t="n">
         <v>6429</v>
@@ -59413,7 +59413,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2036" t="n">
-        <v>0.492112845182419</v>
+        <v>0.492112815380096</v>
       </c>
       <c r="H2036" t="n">
         <v>5940</v>
@@ -59529,7 +59529,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2040" t="n">
-        <v>0.492112845182419</v>
+        <v>0.492112815380096</v>
       </c>
       <c r="H2040" t="n">
         <v>14595</v>
@@ -59558,7 +59558,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2041" t="n">
-        <v>0.492112845182419</v>
+        <v>0.492112815380096</v>
       </c>
       <c r="H2041" t="n">
         <v>4739</v>
@@ -59587,7 +59587,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2042" t="n">
-        <v>0.492112845182419</v>
+        <v>0.492112815380096</v>
       </c>
       <c r="H2042" t="n">
         <v>6416</v>
@@ -59790,7 +59790,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2049" t="n">
-        <v>0.492112845182419</v>
+        <v>0.492112815380096</v>
       </c>
       <c r="H2049" t="n">
         <v>9800</v>
@@ -59819,7 +59819,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2050" t="n">
-        <v>0.492112845182419</v>
+        <v>0.492112815380096</v>
       </c>
       <c r="H2050" t="n">
         <v>1000</v>
@@ -59848,7 +59848,7 @@
         <v>0.509999990463257</v>
       </c>
       <c r="G2051" t="n">
-        <v>0.492112845182419</v>
+        <v>0.492112815380096</v>
       </c>
       <c r="H2051" t="n">
         <v>14972</v>
@@ -60022,7 +60022,7 @@
         <v>0.481000006198883</v>
       </c>
       <c r="G2057" t="n">
-        <v>0.464129954576492</v>
+        <v>0.46412992477417</v>
       </c>
       <c r="H2057" t="n">
         <v>4024</v>
@@ -60167,7 +60167,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2062" t="n">
-        <v>0.463165014982224</v>
+        <v>0.463165044784546</v>
       </c>
       <c r="H2062" t="n">
         <v>13020</v>
@@ -60196,7 +60196,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G2063" t="n">
-        <v>0.46605983376503</v>
+        <v>0.466059803962708</v>
       </c>
       <c r="H2063" t="n">
         <v>10286</v>
@@ -60225,7 +60225,7 @@
         <v>0.483000010251999</v>
       </c>
       <c r="G2064" t="n">
-        <v>0.46605983376503</v>
+        <v>0.466059803962708</v>
       </c>
       <c r="H2064" t="n">
         <v>0</v>
@@ -60370,7 +60370,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2069" t="n">
-        <v>0.463165014982224</v>
+        <v>0.463165044784546</v>
       </c>
       <c r="H2069" t="n">
         <v>20731</v>
@@ -60544,7 +60544,7 @@
         <v>0.479999989271164</v>
       </c>
       <c r="G2075" t="n">
-        <v>0.463165014982224</v>
+        <v>0.463165044784546</v>
       </c>
       <c r="H2075" t="n">
         <v>11712</v>
@@ -60573,7 +60573,7 @@
         <v>0.479000002145767</v>
       </c>
       <c r="G2076" t="n">
-        <v>0.462200105190277</v>
+        <v>0.462200134992599</v>
       </c>
       <c r="H2076" t="n">
         <v>3818</v>
@@ -60602,7 +60602,7 @@
         <v>0.467000007629395</v>
       </c>
       <c r="G2077" t="n">
-        <v>0.450621008872986</v>
+        <v>0.450620979070663</v>
       </c>
       <c r="H2077" t="n">
         <v>3943</v>
@@ -60950,7 +60950,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2089" t="n">
-        <v>0.401409685611725</v>
+        <v>0.401409715414047</v>
       </c>
       <c r="H2089" t="n">
         <v>15614</v>
@@ -61008,7 +61008,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2091" t="n">
-        <v>0.383076101541519</v>
+        <v>0.383076071739197</v>
       </c>
       <c r="H2091" t="n">
         <v>12738</v>
@@ -61182,7 +61182,7 @@
         <v>0.397000014781952</v>
       </c>
       <c r="G2097" t="n">
-        <v>0.383076101541519</v>
+        <v>0.383076071739197</v>
       </c>
       <c r="H2097" t="n">
         <v>5500</v>
@@ -61298,7 +61298,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2101" t="n">
-        <v>0.378251403570175</v>
+        <v>0.378251433372498</v>
       </c>
       <c r="H2101" t="n">
         <v>31991</v>
@@ -61327,7 +61327,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2102" t="n">
-        <v>0.38211116194725</v>
+        <v>0.382111132144928</v>
       </c>
       <c r="H2102" t="n">
         <v>17631</v>
@@ -61414,7 +61414,7 @@
         <v>0.395999997854233</v>
       </c>
       <c r="G2105" t="n">
-        <v>0.38211116194725</v>
+        <v>0.382111132144928</v>
       </c>
       <c r="H2105" t="n">
         <v>27697</v>
@@ -61472,7 +61472,7 @@
         <v>0.375999987125397</v>
       </c>
       <c r="G2107" t="n">
-        <v>0.362812608480453</v>
+        <v>0.362812578678131</v>
       </c>
       <c r="H2107" t="n">
         <v>11537</v>
@@ -61559,7 +61559,7 @@
         <v>0.393999993801117</v>
       </c>
       <c r="G2110" t="n">
-        <v>0.380181282758713</v>
+        <v>0.380181312561035</v>
       </c>
       <c r="H2110" t="n">
         <v>7881</v>
@@ -61762,7 +61762,7 @@
         <v>0.368999987840652</v>
       </c>
       <c r="G2117" t="n">
-        <v>0.356058090925217</v>
+        <v>0.356058120727539</v>
       </c>
       <c r="H2117" t="n">
         <v>4033</v>
@@ -61936,7 +61936,7 @@
         <v>0.432000011205673</v>
       </c>
       <c r="G2123" t="n">
-        <v>0.416848510503769</v>
+        <v>0.416848540306091</v>
       </c>
       <c r="H2123" t="n">
         <v>68404</v>
@@ -61965,7 +61965,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2124" t="n">
-        <v>0.401409685611725</v>
+        <v>0.401409715414047</v>
       </c>
       <c r="H2124" t="n">
         <v>97328</v>
@@ -62052,7 +62052,7 @@
         <v>0.419999986886978</v>
       </c>
       <c r="G2127" t="n">
-        <v>0.405269384384155</v>
+        <v>0.405269354581833</v>
       </c>
       <c r="H2127" t="n">
         <v>52451</v>
@@ -62081,7 +62081,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2128" t="n">
-        <v>0.404304474592209</v>
+        <v>0.404304444789886</v>
       </c>
       <c r="H2128" t="n">
         <v>9875</v>
@@ -62139,7 +62139,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2130" t="n">
-        <v>0.404304474592209</v>
+        <v>0.404304444789886</v>
       </c>
       <c r="H2130" t="n">
         <v>18157</v>
@@ -62313,7 +62313,7 @@
         <v>0.391999989748001</v>
       </c>
       <c r="G2136" t="n">
-        <v>0.378251403570175</v>
+        <v>0.378251433372498</v>
       </c>
       <c r="H2136" t="n">
         <v>1237</v>
@@ -62806,7 +62806,7 @@
         <v>0.412999987602234</v>
       </c>
       <c r="G2153" t="n">
-        <v>0.398514866828918</v>
+        <v>0.398514896631241</v>
       </c>
       <c r="H2153" t="n">
         <v>7378</v>
@@ -62980,7 +62980,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2159" t="n">
-        <v>0.404304474592209</v>
+        <v>0.404304444789886</v>
       </c>
       <c r="H2159" t="n">
         <v>22868</v>
@@ -63009,7 +63009,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2160" t="n">
-        <v>0.404304474592209</v>
+        <v>0.404304444789886</v>
       </c>
       <c r="H2160" t="n">
         <v>2431</v>
@@ -63038,7 +63038,7 @@
         <v>0.418999999761581</v>
       </c>
       <c r="G2161" t="n">
-        <v>0.404304474592209</v>
+        <v>0.404304444789886</v>
       </c>
       <c r="H2161" t="n">
         <v>5285</v>
@@ -63096,7 +63096,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2163" t="n">
-        <v>0.401409685611725</v>
+        <v>0.401409715414047</v>
       </c>
       <c r="H2163" t="n">
         <v>11659</v>
@@ -63299,7 +63299,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2170" t="n">
-        <v>0.401409685611725</v>
+        <v>0.401409715414047</v>
       </c>
       <c r="H2170" t="n">
         <v>21037</v>
@@ -63328,7 +63328,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2171" t="n">
-        <v>0.401409685611725</v>
+        <v>0.401409715414047</v>
       </c>
       <c r="H2171" t="n">
         <v>31998</v>
@@ -63386,7 +63386,7 @@
         <v>0.416000008583069</v>
       </c>
       <c r="G2173" t="n">
-        <v>0.401409685611725</v>
+        <v>0.401409715414047</v>
       </c>
       <c r="H2173" t="n">
         <v>2007</v>
@@ -80125,6 +80125,35 @@
         <v>7031</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>1.14499998092651</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>1.17499995231628</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>1.12999999523163</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>1.14499998092651</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>1.14499998092651</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>7139</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/B.MI.xlsx
+++ b/data/B.MI.xlsx
@@ -456,7 +456,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G3" t="n">
-        <v>1.55858397483826</v>
+        <v>1.55858409404755</v>
       </c>
       <c r="H3" t="n">
         <v>10710</v>
@@ -485,7 +485,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G4" t="n">
-        <v>1.56808769702911</v>
+        <v>1.56808757781982</v>
       </c>
       <c r="H4" t="n">
         <v>7639</v>
@@ -601,7 +601,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G8" t="n">
-        <v>1.49205923080444</v>
+        <v>1.49205911159515</v>
       </c>
       <c r="H8" t="n">
         <v>9900</v>
@@ -688,7 +688,7 @@
         <v>1.4099999666214</v>
       </c>
       <c r="G11" t="n">
-        <v>1.34000194072723</v>
+        <v>1.34000205993652</v>
       </c>
       <c r="H11" t="n">
         <v>24720</v>
@@ -775,7 +775,7 @@
         <v>1.33500003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>1.26872551441193</v>
+        <v>1.26872539520264</v>
       </c>
       <c r="H14" t="n">
         <v>17780</v>
@@ -920,7 +920,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G19" t="n">
-        <v>1.36851274967194</v>
+        <v>1.36851286888123</v>
       </c>
       <c r="H19" t="n">
         <v>6521</v>
@@ -1007,7 +1007,7 @@
         <v>1.39600002765656</v>
       </c>
       <c r="G22" t="n">
-        <v>1.32669723033905</v>
+        <v>1.32669711112976</v>
       </c>
       <c r="H22" t="n">
         <v>7549</v>
@@ -1181,7 +1181,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G28" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H28" t="n">
         <v>6283</v>
@@ -1239,7 +1239,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G30" t="n">
-        <v>1.13662576675415</v>
+        <v>1.13662588596344</v>
       </c>
       <c r="H30" t="n">
         <v>1130</v>
@@ -1529,7 +1529,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G40" t="n">
-        <v>1.3114914894104</v>
+        <v>1.31149137020111</v>
       </c>
       <c r="H40" t="n">
         <v>13000</v>
@@ -1558,7 +1558,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G41" t="n">
-        <v>1.3114914894104</v>
+        <v>1.31149137020111</v>
       </c>
       <c r="H41" t="n">
         <v>9289</v>
@@ -1587,7 +1587,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G42" t="n">
-        <v>1.29723620414734</v>
+        <v>1.29723608493805</v>
       </c>
       <c r="H42" t="n">
         <v>3745</v>
@@ -1616,7 +1616,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G43" t="n">
-        <v>1.3114914894104</v>
+        <v>1.31149137020111</v>
       </c>
       <c r="H43" t="n">
         <v>65</v>
@@ -1674,7 +1674,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G45" t="n">
-        <v>1.32099497318268</v>
+        <v>1.32099509239197</v>
       </c>
       <c r="H45" t="n">
         <v>1400</v>
@@ -1703,7 +1703,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>1.28773248195648</v>
+        <v>1.28773260116577</v>
       </c>
       <c r="H46" t="n">
         <v>3247</v>
@@ -1877,7 +1877,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G52" t="n">
-        <v>1.32194542884827</v>
+        <v>1.32194530963898</v>
       </c>
       <c r="H52" t="n">
         <v>2834</v>
@@ -1906,7 +1906,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G53" t="n">
-        <v>1.32194542884827</v>
+        <v>1.32194530963898</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G54" t="n">
-        <v>1.32099497318268</v>
+        <v>1.32099509239197</v>
       </c>
       <c r="H54" t="n">
         <v>1500</v>
@@ -2167,7 +2167,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G62" t="n">
-        <v>1.26207292079926</v>
+        <v>1.26207304000854</v>
       </c>
       <c r="H62" t="n">
         <v>2000</v>
@@ -2341,7 +2341,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G68" t="n">
-        <v>1.30578935146332</v>
+        <v>1.30578923225403</v>
       </c>
       <c r="H68" t="n">
         <v>119</v>
@@ -2370,7 +2370,7 @@
         <v>1.37399995326996</v>
       </c>
       <c r="G69" t="n">
-        <v>1.30578935146332</v>
+        <v>1.30578923225403</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>1.31299996376038</v>
       </c>
       <c r="G70" t="n">
-        <v>1.2478175163269</v>
+        <v>1.24781739711761</v>
       </c>
       <c r="H70" t="n">
         <v>3528</v>
@@ -2457,7 +2457,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G72" t="n">
-        <v>1.30483889579773</v>
+        <v>1.30483901500702</v>
       </c>
       <c r="H72" t="n">
         <v>14416</v>
@@ -2486,7 +2486,7 @@
         <v>1.35800004005432</v>
       </c>
       <c r="G73" t="n">
-        <v>1.29058361053467</v>
+        <v>1.29058372974396</v>
       </c>
       <c r="H73" t="n">
         <v>5869</v>
@@ -2602,7 +2602,7 @@
         <v>1.32700002193451</v>
       </c>
       <c r="G77" t="n">
-        <v>1.26112258434296</v>
+        <v>1.26112270355225</v>
       </c>
       <c r="H77" t="n">
         <v>14946</v>
@@ -2776,7 +2776,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G83" t="n">
-        <v>1.26207292079926</v>
+        <v>1.26207304000854</v>
       </c>
       <c r="H83" t="n">
         <v>22657</v>
@@ -2805,7 +2805,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G84" t="n">
-        <v>1.27347731590271</v>
+        <v>1.27347719669342</v>
       </c>
       <c r="H84" t="n">
         <v>9423</v>
@@ -2834,7 +2834,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G85" t="n">
-        <v>1.26207292079926</v>
+        <v>1.26207304000854</v>
       </c>
       <c r="H85" t="n">
         <v>4053</v>
@@ -2921,7 +2921,7 @@
         <v>1.32799994945526</v>
       </c>
       <c r="G88" t="n">
-        <v>1.26207292079926</v>
+        <v>1.26207304000854</v>
       </c>
       <c r="H88" t="n">
         <v>2439</v>
@@ -2950,7 +2950,7 @@
         <v>1.37300002574921</v>
       </c>
       <c r="G89" t="n">
-        <v>1.30483889579773</v>
+        <v>1.30483901500702</v>
       </c>
       <c r="H89" t="n">
         <v>852</v>
@@ -3066,7 +3066,7 @@
         <v>1.29999995231628</v>
       </c>
       <c r="G93" t="n">
-        <v>1.23546278476715</v>
+        <v>1.23546290397644</v>
       </c>
       <c r="H93" t="n">
         <v>7369</v>
@@ -3153,7 +3153,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G96" t="n">
-        <v>1.19744861125946</v>
+        <v>1.19744873046875</v>
       </c>
       <c r="H96" t="n">
         <v>1704</v>
@@ -3211,7 +3211,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G98" t="n">
-        <v>1.1803423166275</v>
+        <v>1.18034219741821</v>
       </c>
       <c r="H98" t="n">
         <v>765</v>
@@ -3240,7 +3240,7 @@
         <v>1.24199998378754</v>
       </c>
       <c r="G99" t="n">
-        <v>1.1803423166275</v>
+        <v>1.18034219741821</v>
       </c>
       <c r="H99" t="n">
         <v>10250</v>
@@ -3298,7 +3298,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G101" t="n">
-        <v>1.19744861125946</v>
+        <v>1.19744873046875</v>
       </c>
       <c r="H101" t="n">
         <v>2109</v>
@@ -3327,7 +3327,7 @@
         <v>1.25899994373322</v>
       </c>
       <c r="G102" t="n">
-        <v>1.19649827480316</v>
+        <v>1.19649839401245</v>
       </c>
       <c r="H102" t="n">
         <v>12993</v>
@@ -3443,7 +3443,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G106" t="n">
-        <v>1.1784416437149</v>
+        <v>1.17844152450562</v>
       </c>
       <c r="H106" t="n">
         <v>2020</v>
@@ -3472,7 +3472,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G107" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749106884003</v>
       </c>
       <c r="H107" t="n">
         <v>2700</v>
@@ -3501,7 +3501,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G108" t="n">
-        <v>1.17749118804932</v>
+        <v>1.17749106884003</v>
       </c>
       <c r="H108" t="n">
         <v>500</v>
@@ -3936,7 +3936,7 @@
         <v>1.19599997997284</v>
       </c>
       <c r="G123" t="n">
-        <v>1.13662576675415</v>
+        <v>1.13662588596344</v>
       </c>
       <c r="H123" t="n">
         <v>15822</v>
@@ -4139,7 +4139,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G130" t="n">
-        <v>1.11191654205322</v>
+        <v>1.11191666126251</v>
       </c>
       <c r="H130" t="n">
         <v>9949</v>
@@ -4168,7 +4168,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G131" t="n">
-        <v>1.09005844593048</v>
+        <v>1.09005832672119</v>
       </c>
       <c r="H131" t="n">
         <v>4789</v>
@@ -4284,7 +4284,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G135" t="n">
-        <v>1.00547659397125</v>
+        <v>1.00547671318054</v>
       </c>
       <c r="H135" t="n">
         <v>11813</v>
@@ -4371,7 +4371,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G138" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873783111572</v>
       </c>
       <c r="H138" t="n">
         <v>2668</v>
@@ -4429,7 +4429,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G140" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873783111572</v>
       </c>
       <c r="H140" t="n">
         <v>819</v>
@@ -4458,7 +4458,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G141" t="n">
-        <v>0.997873902320862</v>
+        <v>0.997873783111572</v>
       </c>
       <c r="H141" t="n">
         <v>2583</v>
@@ -4487,7 +4487,7 @@
         <v>1.01300001144409</v>
       </c>
       <c r="G142" t="n">
-        <v>0.962710738182068</v>
+        <v>0.962710797786713</v>
       </c>
       <c r="H142" t="n">
         <v>500</v